--- a/docs/アクティビスト銘柄_資産判定.xlsx
+++ b/docs/アクティビスト銘柄_資産判定.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N152"/>
+  <dimension ref="A1:N154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>43.9</v>
+        <v>45.8</v>
       </c>
       <c r="D2" t="n">
-        <v>1354</v>
+        <v>1299</v>
       </c>
       <c r="E2" t="n">
         <v>1111.251693601708</v>
       </c>
       <c r="F2" t="n">
-        <v>21.8</v>
+        <v>16.9</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -537,7 +537,7 @@
         <v>213563000000</v>
       </c>
       <c r="N2" t="n">
-        <v>486129382160</v>
+        <v>466382619960</v>
       </c>
     </row>
     <row r="3">
@@ -552,16 +552,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>55.1</v>
+        <v>53.3</v>
       </c>
       <c r="D3" t="n">
-        <v>1155</v>
+        <v>1193</v>
       </c>
       <c r="E3" t="n">
         <v>1019.677694332945</v>
       </c>
       <c r="F3" t="n">
-        <v>13.3</v>
+        <v>17</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         <v>106991000000</v>
       </c>
       <c r="N3" t="n">
-        <v>194329385250</v>
+        <v>200722906150</v>
       </c>
     </row>
     <row r="4">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>3495</v>
+        <v>3455</v>
       </c>
       <c r="E4" t="n">
         <v>6116.356643776557</v>
       </c>
       <c r="F4" t="n">
-        <v>-42.9</v>
+        <v>-43.5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         <v>219041000000</v>
       </c>
       <c r="N4" t="n">
-        <v>3162129189030</v>
+        <v>3125938869270</v>
       </c>
     </row>
     <row r="5">
@@ -656,16 +656,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="D5" t="n">
-        <v>2108.5</v>
+        <v>2102</v>
       </c>
       <c r="E5" t="n">
         <v>1815.198567455447</v>
       </c>
       <c r="F5" t="n">
-        <v>16.2</v>
+        <v>15.8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         <v>168499000000</v>
       </c>
       <c r="N5" t="n">
-        <v>528426475842</v>
+        <v>526797463704</v>
       </c>
     </row>
     <row r="6">
@@ -708,16 +708,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>53.3</v>
+        <v>52.6</v>
       </c>
       <c r="D6" t="n">
-        <v>10940</v>
+        <v>11080</v>
       </c>
       <c r="E6" t="n">
         <v>5684.0003469471</v>
       </c>
       <c r="F6" t="n">
-        <v>92.5</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>91895000000</v>
       </c>
       <c r="N6" t="n">
-        <v>172415023580</v>
+        <v>174621431560</v>
       </c>
     </row>
     <row r="7">
@@ -760,16 +760,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>53.3</v>
+        <v>52.6</v>
       </c>
       <c r="D7" t="n">
-        <v>10940</v>
+        <v>11080</v>
       </c>
       <c r="E7" t="n">
         <v>4549.503641591014</v>
       </c>
       <c r="F7" t="n">
-        <v>140.5</v>
+        <v>143.5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>91895000000</v>
       </c>
       <c r="N7" t="n">
-        <v>172415023580</v>
+        <v>174621431560</v>
       </c>
     </row>
     <row r="8">
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>13.7</v>
       </c>
       <c r="D8" t="n">
-        <v>4005</v>
+        <v>4070</v>
       </c>
       <c r="E8" t="n">
         <v>1361.432492253209</v>
       </c>
       <c r="F8" t="n">
-        <v>194.2</v>
+        <v>198.9</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>12397436000</v>
       </c>
       <c r="N8" t="n">
-        <v>88844296725</v>
+        <v>90284008210</v>
       </c>
     </row>
     <row r="9">
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>30.2</v>
+        <v>30.7</v>
       </c>
       <c r="D9" t="n">
-        <v>3311</v>
+        <v>3255</v>
       </c>
       <c r="E9" t="n">
         <v>13739.64575539568</v>
       </c>
       <c r="F9" t="n">
-        <v>-75.90000000000001</v>
+        <v>-76.3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>325393000000</v>
       </c>
       <c r="N9" t="n">
-        <v>1078287840630</v>
+        <v>1060050414150</v>
       </c>
     </row>
     <row r="10">
@@ -916,16 +916,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>41.5</v>
+        <v>41.7</v>
       </c>
       <c r="D10" t="n">
-        <v>2331</v>
+        <v>2319</v>
       </c>
       <c r="E10" t="n">
         <v>1198.150742177053</v>
       </c>
       <c r="F10" t="n">
-        <v>94.5</v>
+        <v>93.5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>213966000000</v>
       </c>
       <c r="N10" t="n">
-        <v>516115430271</v>
+        <v>513458465379</v>
       </c>
     </row>
     <row r="11">
@@ -968,16 +968,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>41.5</v>
+        <v>41.7</v>
       </c>
       <c r="D11" t="n">
-        <v>2331</v>
+        <v>2319</v>
       </c>
       <c r="E11" t="n">
         <v>1188.162962482466</v>
       </c>
       <c r="F11" t="n">
-        <v>96.2</v>
+        <v>95.2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>213966000000</v>
       </c>
       <c r="N11" t="n">
-        <v>516115430271</v>
+        <v>513458465379</v>
       </c>
     </row>
     <row r="12">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24.2</v>
+        <v>24.6</v>
       </c>
       <c r="D12" t="n">
-        <v>3649</v>
+        <v>3591</v>
       </c>
       <c r="E12" t="n">
         <v>2995.424821743842</v>
       </c>
       <c r="F12" t="n">
-        <v>21.8</v>
+        <v>19.9</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>129979000000</v>
       </c>
       <c r="N12" t="n">
-        <v>536277780916</v>
+        <v>527753771244</v>
       </c>
     </row>
     <row r="13">
@@ -1072,16 +1072,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>72.09999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>4961</v>
+        <v>4939</v>
       </c>
       <c r="E13" t="n">
         <v>4991.027246539169</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>1007966000000</v>
       </c>
       <c r="N13" t="n">
-        <v>1397745606906</v>
+        <v>1391547178494</v>
       </c>
     </row>
     <row r="14">
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="D14" t="n">
-        <v>1880</v>
+        <v>1874.5</v>
       </c>
       <c r="E14" t="n">
         <v>1512.21980974841</v>
       </c>
       <c r="F14" t="n">
-        <v>24.3</v>
+        <v>24</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>120816000000</v>
       </c>
       <c r="N14" t="n">
-        <v>619303514440</v>
+        <v>617491722244</v>
       </c>
     </row>
     <row r="15">
@@ -1176,16 +1176,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="D15" t="n">
-        <v>2767.5</v>
+        <v>2694</v>
       </c>
       <c r="E15" t="n">
         <v>1827.011042553346</v>
       </c>
       <c r="F15" t="n">
-        <v>51.5</v>
+        <v>47.5</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>48336000000</v>
       </c>
       <c r="N15" t="n">
-        <v>680551674120</v>
+        <v>662477402016</v>
       </c>
     </row>
     <row r="16">
@@ -1228,16 +1228,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>129.5</v>
+        <v>134.2</v>
       </c>
       <c r="D16" t="n">
-        <v>1661</v>
+        <v>1603</v>
       </c>
       <c r="E16" t="n">
         <v>2122.579027791042</v>
       </c>
       <c r="F16" t="n">
-        <v>-21.7</v>
+        <v>-24.5</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>80333000000</v>
       </c>
       <c r="N16" t="n">
-        <v>62042381247</v>
+        <v>59875940481</v>
       </c>
     </row>
     <row r="17">
@@ -1280,16 +1280,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.2</v>
+        <v>17.4</v>
       </c>
       <c r="D17" t="n">
-        <v>2890</v>
+        <v>2866</v>
       </c>
       <c r="E17" t="n">
         <v>6272.971195510064</v>
       </c>
       <c r="F17" t="n">
-        <v>-53.9</v>
+        <v>-54.3</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>179622000000</v>
       </c>
       <c r="N17" t="n">
-        <v>1042352293260</v>
+        <v>1033696080444</v>
       </c>
     </row>
     <row r="18">
@@ -1332,16 +1332,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="D18" t="n">
-        <v>3547</v>
+        <v>3649</v>
       </c>
       <c r="E18" t="n">
         <v>1572.181660925393</v>
       </c>
       <c r="F18" t="n">
-        <v>125.6</v>
+        <v>132.1</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>35501000000</v>
       </c>
       <c r="N18" t="n">
-        <v>633363163179</v>
+        <v>651576594993</v>
       </c>
     </row>
     <row r="19">
@@ -1384,16 +1384,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="D19" t="n">
-        <v>3547</v>
+        <v>3649</v>
       </c>
       <c r="E19" t="n">
         <v>1141.512891683109</v>
       </c>
       <c r="F19" t="n">
-        <v>210.7</v>
+        <v>219.7</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>35501000000</v>
       </c>
       <c r="N19" t="n">
-        <v>633363163179</v>
+        <v>651576594993</v>
       </c>
     </row>
     <row r="20">
@@ -1436,16 +1436,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>43.7</v>
+        <v>44.6</v>
       </c>
       <c r="D20" t="n">
-        <v>6137</v>
+        <v>6025</v>
       </c>
       <c r="E20" t="n">
         <v>2836.942753814942</v>
       </c>
       <c r="F20" t="n">
-        <v>116.3</v>
+        <v>112.4</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>94351000000</v>
       </c>
       <c r="N20" t="n">
-        <v>215715065177</v>
+        <v>211585474025</v>
       </c>
     </row>
     <row r="21">
@@ -1488,16 +1488,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>57.6</v>
+        <v>54.9</v>
       </c>
       <c r="D21" t="n">
-        <v>3898</v>
+        <v>4091</v>
       </c>
       <c r="E21" t="n">
         <v>2863.970160821546</v>
       </c>
       <c r="F21" t="n">
-        <v>36.1</v>
+        <v>42.8</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>161529000000</v>
       </c>
       <c r="N21" t="n">
-        <v>280442245374</v>
+        <v>294327661833</v>
       </c>
     </row>
     <row r="22">
@@ -1540,16 +1540,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>50.4</v>
+        <v>50.1</v>
       </c>
       <c r="D22" t="n">
-        <v>4856</v>
+        <v>4881</v>
       </c>
       <c r="E22" t="n">
         <v>2566.284807227078</v>
       </c>
       <c r="F22" t="n">
-        <v>89.2</v>
+        <v>90.2</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>231575000000</v>
       </c>
       <c r="N22" t="n">
-        <v>459926833024</v>
+        <v>462294660624</v>
       </c>
     </row>
     <row r="23">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>29.1</v>
+        <v>28.9</v>
       </c>
       <c r="D23" t="n">
-        <v>5082</v>
+        <v>5120</v>
       </c>
       <c r="E23" t="n">
         <v>2779.139169918938</v>
       </c>
       <c r="F23" t="n">
-        <v>82.90000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>183216000000</v>
       </c>
       <c r="N23" t="n">
-        <v>630333017622</v>
+        <v>635046251520</v>
       </c>
     </row>
     <row r="24">
@@ -1647,13 +1647,13 @@
         <v>8.9</v>
       </c>
       <c r="D24" t="n">
-        <v>4128</v>
+        <v>4125</v>
       </c>
       <c r="E24" t="n">
         <v>2420.370957920882</v>
       </c>
       <c r="F24" t="n">
-        <v>70.59999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>18167000000</v>
       </c>
       <c r="N24" t="n">
-        <v>204076262112</v>
+        <v>203927950875</v>
       </c>
     </row>
     <row r="25">
@@ -1696,16 +1696,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>1829.5</v>
+        <v>1794.5</v>
       </c>
       <c r="E25" t="n">
         <v>1344.518957928979</v>
       </c>
       <c r="F25" t="n">
-        <v>36.1</v>
+        <v>33.5</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>45956000000</v>
       </c>
       <c r="N25" t="n">
-        <v>588653064864</v>
+        <v>577391596008</v>
       </c>
     </row>
     <row r="26">
@@ -1748,16 +1748,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>59.1</v>
+        <v>59.6</v>
       </c>
       <c r="D26" t="n">
-        <v>5064</v>
+        <v>5021</v>
       </c>
       <c r="E26" t="n">
         <v>4154.626869982095</v>
       </c>
       <c r="F26" t="n">
-        <v>21.9</v>
+        <v>20.9</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>179086000000</v>
       </c>
       <c r="N26" t="n">
-        <v>302830623264</v>
+        <v>300259194196</v>
       </c>
     </row>
     <row r="27">
@@ -1800,16 +1800,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>13.7</v>
+        <v>14.2</v>
       </c>
       <c r="D27" t="n">
-        <v>3992</v>
+        <v>3859</v>
       </c>
       <c r="E27" t="n">
         <v>2561.705402476645</v>
       </c>
       <c r="F27" t="n">
-        <v>55.8</v>
+        <v>50.6</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>100104000000</v>
       </c>
       <c r="N27" t="n">
-        <v>730461768760</v>
+        <v>706125241895</v>
       </c>
     </row>
     <row r="28">
@@ -1852,16 +1852,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>42.6</v>
+        <v>42.1</v>
       </c>
       <c r="D28" t="n">
-        <v>3632</v>
+        <v>3674</v>
       </c>
       <c r="E28" t="n">
         <v>2560</v>
       </c>
       <c r="F28" t="n">
-        <v>41.9</v>
+        <v>43.5</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>190312000000</v>
       </c>
       <c r="N28" t="n">
-        <v>447136631392</v>
+        <v>452307264244</v>
       </c>
     </row>
     <row r="29">
@@ -1904,16 +1904,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>85.7</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>4485</v>
+        <v>4425</v>
       </c>
       <c r="E29" t="n">
         <v>3449.780346820809</v>
       </c>
       <c r="F29" t="n">
-        <v>30</v>
+        <v>28.3</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>90928000000</v>
       </c>
       <c r="N29" t="n">
-        <v>106056848820</v>
+        <v>104638028100</v>
       </c>
     </row>
     <row r="30">
@@ -1956,16 +1956,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>58.2</v>
+        <v>61</v>
       </c>
       <c r="D30" t="n">
-        <v>1639</v>
+        <v>1566</v>
       </c>
       <c r="E30" t="n">
         <v>1746.940387696806</v>
       </c>
       <c r="F30" t="n">
-        <v>-6.2</v>
+        <v>-10.4</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>36070000000</v>
       </c>
       <c r="N30" t="n">
-        <v>61923867027</v>
+        <v>59165818038</v>
       </c>
     </row>
     <row r="31">
@@ -2008,16 +2008,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>104.7</v>
+        <v>104.9</v>
       </c>
       <c r="D31" t="n">
-        <v>1693</v>
+        <v>1690</v>
       </c>
       <c r="E31" t="n">
         <v>2298.672482457804</v>
       </c>
       <c r="F31" t="n">
-        <v>-26.3</v>
+        <v>-26.5</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>42752000000</v>
       </c>
       <c r="N31" t="n">
-        <v>40821086091</v>
+        <v>40748751030</v>
       </c>
     </row>
     <row r="32">
@@ -2060,16 +2060,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>69.59999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>2569</v>
+        <v>2596</v>
       </c>
       <c r="E32" t="n">
         <v>1270</v>
       </c>
       <c r="F32" t="n">
-        <v>102.3</v>
+        <v>104.4</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>31108000000</v>
       </c>
       <c r="N32" t="n">
-        <v>44668644209</v>
+        <v>45138108356</v>
       </c>
     </row>
     <row r="33">
@@ -2112,16 +2112,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>69.59999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>2569</v>
+        <v>2596</v>
       </c>
       <c r="E33" t="n">
         <v>1170</v>
       </c>
       <c r="F33" t="n">
-        <v>119.6</v>
+        <v>121.9</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>31108000000</v>
       </c>
       <c r="N33" t="n">
-        <v>44668644209</v>
+        <v>45138108356</v>
       </c>
     </row>
     <row r="34">
@@ -2167,13 +2167,13 @@
         <v>33.8</v>
       </c>
       <c r="D34" t="n">
-        <v>2810.5</v>
+        <v>2808</v>
       </c>
       <c r="E34" t="n">
         <v>2381.523440544182</v>
       </c>
       <c r="F34" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>168696000000</v>
       </c>
       <c r="N34" t="n">
-        <v>499118637056</v>
+        <v>498674660328</v>
       </c>
     </row>
     <row r="35">
@@ -2216,16 +2216,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>81.90000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="D35" t="n">
-        <v>2527</v>
+        <v>2509</v>
       </c>
       <c r="E35" t="n">
         <v>2939.562915943684</v>
       </c>
       <c r="F35" t="n">
-        <v>-14</v>
+        <v>-14.6</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>108430000000</v>
       </c>
       <c r="N35" t="n">
-        <v>132331115868</v>
+        <v>131388511956</v>
       </c>
     </row>
     <row r="36">
@@ -2268,16 +2268,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>48</v>
+        <v>48.5</v>
       </c>
       <c r="D36" t="n">
-        <v>13590</v>
+        <v>13450</v>
       </c>
       <c r="E36" t="n">
         <v>7040.15625</v>
       </c>
       <c r="F36" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>6799899000</v>
       </c>
       <c r="N36" t="n">
-        <v>14154895530</v>
+        <v>14009076150</v>
       </c>
     </row>
     <row r="37">
@@ -2320,16 +2320,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>48</v>
+        <v>48.5</v>
       </c>
       <c r="D37" t="n">
-        <v>13590</v>
+        <v>13450</v>
       </c>
       <c r="E37" t="n">
         <v>7040.15625</v>
       </c>
       <c r="F37" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>6799899000</v>
       </c>
       <c r="N37" t="n">
-        <v>14154895530</v>
+        <v>14009076150</v>
       </c>
     </row>
     <row r="38">
@@ -2372,16 +2372,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>86.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>2761</v>
+        <v>2777</v>
       </c>
       <c r="E38" t="n">
         <v>4265.455132343447</v>
       </c>
       <c r="F38" t="n">
-        <v>-35.3</v>
+        <v>-34.9</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>22869000000</v>
       </c>
       <c r="N38" t="n">
-        <v>26322871498</v>
+        <v>26475412586</v>
       </c>
     </row>
     <row r="39">
@@ -2424,16 +2424,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="D39" t="n">
-        <v>4810</v>
+        <v>4830</v>
       </c>
       <c r="E39" t="n">
         <v>2824.318397803668</v>
       </c>
       <c r="F39" t="n">
-        <v>70.3</v>
+        <v>71</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>61975000000</v>
       </c>
       <c r="N39" t="n">
-        <v>193509450550</v>
+        <v>194314063650</v>
       </c>
     </row>
     <row r="40">
@@ -2476,16 +2476,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>28.7</v>
+        <v>28</v>
       </c>
       <c r="D40" t="n">
-        <v>6720</v>
+        <v>6900</v>
       </c>
       <c r="E40" t="n">
         <v>3096.322467304314</v>
       </c>
       <c r="F40" t="n">
-        <v>117</v>
+        <v>122.8</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>52961000000</v>
       </c>
       <c r="N40" t="n">
-        <v>184350902400</v>
+        <v>189288873000</v>
       </c>
     </row>
     <row r="41">
@@ -2528,16 +2528,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="D41" t="n">
-        <v>6128</v>
+        <v>6163</v>
       </c>
       <c r="E41" t="n">
         <v>3322.047887165483</v>
       </c>
       <c r="F41" t="n">
-        <v>84.5</v>
+        <v>85.5</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>492847000000</v>
       </c>
       <c r="N41" t="n">
-        <v>2013078321344</v>
+        <v>2024575994524</v>
       </c>
     </row>
     <row r="42">
@@ -2580,16 +2580,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="D42" t="n">
-        <v>1771</v>
+        <v>1757</v>
       </c>
       <c r="E42" t="n">
         <v>2112.609181636727</v>
       </c>
       <c r="F42" t="n">
-        <v>-16.2</v>
+        <v>-16.8</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>52218000000</v>
       </c>
       <c r="N42" t="n">
-        <v>149493138410</v>
+        <v>149130417590</v>
       </c>
     </row>
     <row r="43">
@@ -2684,16 +2684,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="D44" t="n">
-        <v>2611</v>
+        <v>2812</v>
       </c>
       <c r="E44" t="n">
         <v>2220.184278344451</v>
       </c>
       <c r="F44" t="n">
-        <v>17.6</v>
+        <v>26.7</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>207116000000</v>
       </c>
       <c r="N44" t="n">
-        <v>2993014979185</v>
+        <v>3223423256020</v>
       </c>
     </row>
     <row r="45">
@@ -2736,16 +2736,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>20.3</v>
+        <v>19.9</v>
       </c>
       <c r="D45" t="n">
-        <v>22550</v>
+        <v>22980</v>
       </c>
       <c r="E45" t="n">
         <v>11879.91675437757</v>
       </c>
       <c r="F45" t="n">
-        <v>89.8</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>191958000000</v>
       </c>
       <c r="N45" t="n">
-        <v>947586065250</v>
+        <v>965655333900</v>
       </c>
     </row>
     <row r="46">
@@ -2788,16 +2788,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>74.7</v>
+        <v>75.8</v>
       </c>
       <c r="D46" t="n">
-        <v>1097</v>
+        <v>1081</v>
       </c>
       <c r="E46" t="n">
         <v>730</v>
       </c>
       <c r="F46" t="n">
-        <v>50.3</v>
+        <v>48.1</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>50027000000</v>
       </c>
       <c r="N46" t="n">
-        <v>66976442042</v>
+        <v>65999575066</v>
       </c>
     </row>
     <row r="47">
@@ -2840,16 +2840,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="D47" t="n">
-        <v>5612</v>
+        <v>5634</v>
       </c>
       <c r="E47" t="n">
         <v>3341.42986565678</v>
       </c>
       <c r="F47" t="n">
-        <v>68</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>311107000000</v>
       </c>
       <c r="N47" t="n">
-        <v>1333545287516</v>
+        <v>1338773013162</v>
       </c>
     </row>
     <row r="48">
@@ -2892,16 +2892,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>28</v>
+        <v>28.4</v>
       </c>
       <c r="D48" t="n">
-        <v>3300</v>
+        <v>3255</v>
       </c>
       <c r="E48" t="n">
         <v>2550.198980592041</v>
       </c>
       <c r="F48" t="n">
-        <v>29.4</v>
+        <v>27.6</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>32342000000</v>
       </c>
       <c r="N48" t="n">
-        <v>115559122800</v>
+        <v>113953045080</v>
       </c>
     </row>
     <row r="49">
@@ -2944,16 +2944,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>212.7</v>
+        <v>214.1</v>
       </c>
       <c r="D49" t="n">
-        <v>1627</v>
+        <v>1616.5</v>
       </c>
       <c r="E49" t="n">
         <v>1288.711724885291</v>
       </c>
       <c r="F49" t="n">
-        <v>26.3</v>
+        <v>25.4</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>747066000000</v>
       </c>
       <c r="N49" t="n">
-        <v>351243549471</v>
+        <v>348976765654</v>
       </c>
     </row>
     <row r="50">
@@ -2996,16 +2996,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>65.5</v>
+        <v>67.2</v>
       </c>
       <c r="D50" t="n">
-        <v>4197</v>
+        <v>4092</v>
       </c>
       <c r="E50" t="n">
         <v>3141.424011416125</v>
       </c>
       <c r="F50" t="n">
-        <v>33.6</v>
+        <v>30.3</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>391579000000</v>
       </c>
       <c r="N50" t="n">
-        <v>598054049988</v>
+        <v>583092011568</v>
       </c>
     </row>
     <row r="51">
@@ -3048,16 +3048,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>65.5</v>
+        <v>67.2</v>
       </c>
       <c r="D51" t="n">
-        <v>4197</v>
+        <v>4092</v>
       </c>
       <c r="E51" t="n">
         <v>2420</v>
       </c>
       <c r="F51" t="n">
-        <v>73.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>391579000000</v>
       </c>
       <c r="N51" t="n">
-        <v>598054049988</v>
+        <v>583092011568</v>
       </c>
     </row>
     <row r="52">
@@ -3100,16 +3100,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>40.6</v>
+        <v>42</v>
       </c>
       <c r="D52" t="n">
-        <v>4218</v>
+        <v>4072</v>
       </c>
       <c r="E52" t="n">
         <v>3047.091476167608</v>
       </c>
       <c r="F52" t="n">
-        <v>38.4</v>
+        <v>33.6</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>162458000000</v>
       </c>
       <c r="N52" t="n">
-        <v>400554216606</v>
+        <v>386689608824</v>
       </c>
     </row>
     <row r="53">
@@ -3152,16 +3152,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>44.2</v>
+        <v>45.1</v>
       </c>
       <c r="D53" t="n">
-        <v>3582</v>
+        <v>3514</v>
       </c>
       <c r="E53" t="n">
         <v>2844.704547285864</v>
       </c>
       <c r="F53" t="n">
-        <v>25.9</v>
+        <v>23.5</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>218675000000</v>
       </c>
       <c r="N53" t="n">
-        <v>494565350184</v>
+        <v>485176616568</v>
       </c>
     </row>
     <row r="54">
@@ -3204,16 +3204,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>55.7</v>
+        <v>55.6</v>
       </c>
       <c r="D54" t="n">
-        <v>2225.5</v>
+        <v>2232.5</v>
       </c>
       <c r="E54" t="n">
         <v>1556.090471804319</v>
       </c>
       <c r="F54" t="n">
-        <v>43</v>
+        <v>43.5</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>207466000000</v>
       </c>
       <c r="N54" t="n">
-        <v>372590105428</v>
+        <v>373399477662</v>
       </c>
     </row>
     <row r="55">
@@ -3256,16 +3256,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
       <c r="D55" t="n">
-        <v>1636</v>
+        <v>1639</v>
       </c>
       <c r="E55" t="n">
         <v>1529.631984751819</v>
       </c>
       <c r="F55" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>6024082000</v>
       </c>
       <c r="N55" t="n">
-        <v>11660048484</v>
+        <v>11681429991</v>
       </c>
     </row>
     <row r="56">
@@ -3308,16 +3308,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
       <c r="D56" t="n">
-        <v>1636</v>
+        <v>1639</v>
       </c>
       <c r="E56" t="n">
         <v>1449.995380693296</v>
       </c>
       <c r="F56" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>6024082000</v>
       </c>
       <c r="N56" t="n">
-        <v>11660048484</v>
+        <v>11681429991</v>
       </c>
     </row>
     <row r="57">
@@ -3360,16 +3360,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>67.7</v>
+        <v>68.7</v>
       </c>
       <c r="D57" t="n">
-        <v>2953</v>
+        <v>2910</v>
       </c>
       <c r="E57" t="n">
         <v>2696.128808062088</v>
       </c>
       <c r="F57" t="n">
-        <v>9.5</v>
+        <v>7.9</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>165282000000</v>
       </c>
       <c r="N57" t="n">
-        <v>244108368902</v>
+        <v>240553793940</v>
       </c>
     </row>
     <row r="58">
@@ -3412,16 +3412,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>121.9</v>
+        <v>121.3</v>
       </c>
       <c r="D58" t="n">
-        <v>1536.5</v>
+        <v>1543.5</v>
       </c>
       <c r="E58" t="n">
         <v>1160.8</v>
       </c>
       <c r="F58" t="n">
-        <v>32.4</v>
+        <v>33</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>493483000000</v>
       </c>
       <c r="N58" t="n">
-        <v>404877708056</v>
+        <v>406722253424</v>
       </c>
     </row>
     <row r="59">
@@ -3464,16 +3464,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="D59" t="n">
-        <v>3005</v>
+        <v>2981</v>
       </c>
       <c r="E59" t="n">
         <v>2007.754513143541</v>
       </c>
       <c r="F59" t="n">
-        <v>49.7</v>
+        <v>48.5</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>37208000000</v>
       </c>
       <c r="N59" t="n">
-        <v>160085157655</v>
+        <v>158806607311</v>
       </c>
     </row>
     <row r="60">
@@ -3516,16 +3516,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="D60" t="n">
-        <v>3010</v>
+        <v>3015</v>
       </c>
       <c r="E60" t="n">
         <v>2261.880826568852</v>
       </c>
       <c r="F60" t="n">
-        <v>33.1</v>
+        <v>33.3</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>102508000000</v>
       </c>
       <c r="N60" t="n">
-        <v>690084317930</v>
+        <v>691230637395</v>
       </c>
     </row>
     <row r="61">
@@ -3568,16 +3568,16 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="D61" t="n">
-        <v>3010</v>
+        <v>3015</v>
       </c>
       <c r="E61" t="n">
         <v>1970</v>
       </c>
       <c r="F61" t="n">
-        <v>52.8</v>
+        <v>53</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>102508000000</v>
       </c>
       <c r="N61" t="n">
-        <v>690084317930</v>
+        <v>691230637395</v>
       </c>
     </row>
     <row r="62">
@@ -3623,13 +3623,13 @@
         <v>9.6</v>
       </c>
       <c r="D62" t="n">
-        <v>2851</v>
+        <v>2852</v>
       </c>
       <c r="E62" t="n">
         <v>1910.426979628923</v>
       </c>
       <c r="F62" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>53660000000</v>
       </c>
       <c r="N62" t="n">
-        <v>556458527822</v>
+        <v>556653707944</v>
       </c>
     </row>
     <row r="63">
@@ -3672,16 +3672,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>48.6</v>
+        <v>49.4</v>
       </c>
       <c r="D63" t="n">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="E63" t="n">
         <v>290.3401328717133</v>
       </c>
       <c r="F63" t="n">
-        <v>5.4</v>
+        <v>3.7</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>5162755000</v>
       </c>
       <c r="N63" t="n">
-        <v>10619986734</v>
+        <v>10446457539</v>
       </c>
     </row>
     <row r="64">
@@ -3812,16 +3812,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>92.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="D66" t="n">
-        <v>2614</v>
+        <v>2612</v>
       </c>
       <c r="E66" t="n">
         <v>1748.071046781136</v>
       </c>
       <c r="F66" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>72190000000</v>
       </c>
       <c r="N66" t="n">
-        <v>78207060946</v>
+        <v>78147223868</v>
       </c>
     </row>
     <row r="67">
@@ -3864,16 +3864,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>73.90000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="D67" t="n">
-        <v>2620</v>
+        <v>2563</v>
       </c>
       <c r="E67" t="n">
         <v>2551.08574256026</v>
       </c>
       <c r="F67" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>179136000000</v>
       </c>
       <c r="N67" t="n">
-        <v>242380499420</v>
+        <v>237107335883</v>
       </c>
     </row>
     <row r="68">
@@ -3916,16 +3916,16 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>73.90000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="D68" t="n">
-        <v>2620</v>
+        <v>2563</v>
       </c>
       <c r="E68" t="n">
         <v>2260</v>
       </c>
       <c r="F68" t="n">
-        <v>15.9</v>
+        <v>13.4</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>179136000000</v>
       </c>
       <c r="N68" t="n">
-        <v>242380499420</v>
+        <v>237107335883</v>
       </c>
     </row>
     <row r="69">
@@ -3968,16 +3968,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>73.90000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="D69" t="n">
-        <v>2620</v>
+        <v>2563</v>
       </c>
       <c r="E69" t="n">
         <v>2260</v>
       </c>
       <c r="F69" t="n">
-        <v>15.9</v>
+        <v>13.4</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>179136000000</v>
       </c>
       <c r="N69" t="n">
-        <v>242380499420</v>
+        <v>237107335883</v>
       </c>
     </row>
     <row r="70">
@@ -4020,16 +4020,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>306.8</v>
+        <v>307.5</v>
       </c>
       <c r="D70" t="n">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="E70" t="n">
         <v>798.3805136422309</v>
       </c>
       <c r="F70" t="n">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>449038000000</v>
       </c>
       <c r="N70" t="n">
-        <v>146363913720</v>
+        <v>146021541992</v>
       </c>
     </row>
     <row r="71">
@@ -4072,16 +4072,16 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>41.7</v>
+        <v>41.9</v>
       </c>
       <c r="D71" t="n">
-        <v>2655.5</v>
+        <v>2639.5</v>
       </c>
       <c r="E71" t="n">
         <v>2032.365850102071</v>
       </c>
       <c r="F71" t="n">
-        <v>30.7</v>
+        <v>29.9</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>340592000000</v>
       </c>
       <c r="N71" t="n">
-        <v>817603344903</v>
+        <v>812677096167</v>
       </c>
     </row>
     <row r="72">
@@ -4124,16 +4124,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>63.3</v>
+        <v>63</v>
       </c>
       <c r="D72" t="n">
-        <v>3515</v>
+        <v>3531</v>
       </c>
       <c r="E72" t="n">
         <v>1716.713876475349</v>
       </c>
       <c r="F72" t="n">
-        <v>104.8</v>
+        <v>105.7</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>565345000000</v>
       </c>
       <c r="N72" t="n">
-        <v>893434924820</v>
+        <v>897501769428</v>
       </c>
     </row>
     <row r="73">
@@ -4177,16 +4177,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>32.2</v>
+        <v>29.8</v>
       </c>
       <c r="D73" t="n">
-        <v>8930</v>
+        <v>9640</v>
       </c>
       <c r="E73" t="n">
         <v>4037.502552255647</v>
       </c>
       <c r="F73" t="n">
-        <v>121.2</v>
+        <v>138.8</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>154738000000</v>
       </c>
       <c r="N73" t="n">
-        <v>480467603590</v>
+        <v>518668275320</v>
       </c>
     </row>
     <row r="74">
@@ -4230,16 +4230,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>32.2</v>
+        <v>29.8</v>
       </c>
       <c r="D74" t="n">
-        <v>8930</v>
+        <v>9640</v>
       </c>
       <c r="E74" t="n">
         <v>3950.736048458928</v>
       </c>
       <c r="F74" t="n">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>154738000000</v>
       </c>
       <c r="N74" t="n">
-        <v>480467603590</v>
+        <v>518668275320</v>
       </c>
     </row>
     <row r="75">
@@ -4283,16 +4283,16 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>32.2</v>
+        <v>29.8</v>
       </c>
       <c r="D75" t="n">
-        <v>8930</v>
+        <v>9640</v>
       </c>
       <c r="E75" t="n">
         <v>2030</v>
       </c>
       <c r="F75" t="n">
-        <v>339.9</v>
+        <v>374.9</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>154738000000</v>
       </c>
       <c r="N75" t="n">
-        <v>480467603590</v>
+        <v>518668275320</v>
       </c>
     </row>
     <row r="76">
@@ -4336,16 +4336,16 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>32.2</v>
+        <v>29.8</v>
       </c>
       <c r="D76" t="n">
-        <v>8930</v>
+        <v>9640</v>
       </c>
       <c r="E76" t="n">
         <v>2387</v>
       </c>
       <c r="F76" t="n">
-        <v>274.1</v>
+        <v>303.9</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>154738000000</v>
       </c>
       <c r="N76" t="n">
-        <v>480467603590</v>
+        <v>518668275320</v>
       </c>
     </row>
     <row r="77">
@@ -4388,16 +4388,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>78.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="D77" t="n">
-        <v>982</v>
+        <v>994</v>
       </c>
       <c r="E77" t="n">
         <v>668.9358717434869</v>
       </c>
       <c r="F77" t="n">
-        <v>46.8</v>
+        <v>48.6</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>12410000000</v>
       </c>
       <c r="N77" t="n">
-        <v>15725753892</v>
+        <v>15917921964</v>
       </c>
     </row>
     <row r="78">
@@ -4440,16 +4440,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>71.7</v>
+        <v>71</v>
       </c>
       <c r="D78" t="n">
-        <v>2653</v>
+        <v>2679</v>
       </c>
       <c r="E78" t="n">
         <v>1190</v>
       </c>
       <c r="F78" t="n">
-        <v>122.9</v>
+        <v>125.1</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>40500000000</v>
       </c>
       <c r="N78" t="n">
-        <v>56487270091</v>
+        <v>57040858113</v>
       </c>
     </row>
     <row r="79">
@@ -4492,16 +4492,16 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
       <c r="D79" t="n">
-        <v>6140</v>
+        <v>6090</v>
       </c>
       <c r="E79" t="n">
         <v>2617.980935875217</v>
       </c>
       <c r="F79" t="n">
-        <v>134.5</v>
+        <v>132.6</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>40238000000</v>
       </c>
       <c r="N79" t="n">
-        <v>220815951400</v>
+        <v>219017775900</v>
       </c>
     </row>
     <row r="80">
@@ -4544,16 +4544,16 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>19.9</v>
+        <v>19.4</v>
       </c>
       <c r="D80" t="n">
-        <v>2837</v>
+        <v>2898</v>
       </c>
       <c r="E80" t="n">
         <v>2084.177692465894</v>
       </c>
       <c r="F80" t="n">
-        <v>36.1</v>
+        <v>39</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         <v>15433000000</v>
       </c>
       <c r="N80" t="n">
-        <v>77697829677</v>
+        <v>79368456258</v>
       </c>
     </row>
     <row r="81">
@@ -4596,16 +4596,16 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="D81" t="n">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="E81" t="n">
         <v>448.6811097117532</v>
       </c>
       <c r="F81" t="n">
-        <v>16.1</v>
+        <v>17</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>13953300000</v>
       </c>
       <c r="N81" t="n">
-        <v>108078901789</v>
+        <v>107238960150</v>
       </c>
     </row>
     <row r="82">
@@ -4648,16 +4648,16 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>32.1</v>
+        <v>33.4</v>
       </c>
       <c r="D82" t="n">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="E82" t="n">
         <v>421.6950726175476</v>
       </c>
       <c r="F82" t="n">
-        <v>-18.2</v>
+        <v>-21.3</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>3109655000</v>
       </c>
       <c r="N82" t="n">
-        <v>9674692860</v>
+        <v>9310139216</v>
       </c>
     </row>
     <row r="83">
@@ -4700,16 +4700,16 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>71.5</v>
+        <v>72</v>
       </c>
       <c r="D83" t="n">
-        <v>3920</v>
+        <v>3895</v>
       </c>
       <c r="E83" t="n">
         <v>3530</v>
       </c>
       <c r="F83" t="n">
-        <v>11</v>
+        <v>10.3</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>106147000000</v>
       </c>
       <c r="N83" t="n">
-        <v>148443794800</v>
+        <v>147497086925</v>
       </c>
     </row>
     <row r="84">
@@ -4755,13 +4755,13 @@
         <v>33.2</v>
       </c>
       <c r="D84" t="n">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E84" t="n">
         <v>549.4799823005444</v>
       </c>
       <c r="F84" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>19115000000</v>
       </c>
       <c r="N84" t="n">
-        <v>57590037180</v>
+        <v>57493732770</v>
       </c>
     </row>
     <row r="85">
@@ -4804,16 +4804,16 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>44.9</v>
+        <v>45.6</v>
       </c>
       <c r="D85" t="n">
-        <v>1751</v>
+        <v>1725</v>
       </c>
       <c r="E85" t="n">
         <v>1752.426893379333</v>
       </c>
       <c r="F85" t="n">
-        <v>-0.1</v>
+        <v>-1.6</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>76232495000</v>
       </c>
       <c r="N85" t="n">
-        <v>169857681100</v>
+        <v>167335522500</v>
       </c>
     </row>
     <row r="86">
@@ -4856,16 +4856,16 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>44.9</v>
+        <v>45.6</v>
       </c>
       <c r="D86" t="n">
-        <v>1751</v>
+        <v>1725</v>
       </c>
       <c r="E86" t="n">
         <v>1576.721867844292</v>
       </c>
       <c r="F86" t="n">
-        <v>11.1</v>
+        <v>9.4</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>76232495000</v>
       </c>
       <c r="N86" t="n">
-        <v>169857681100</v>
+        <v>167335522500</v>
       </c>
     </row>
     <row r="87">
@@ -4908,16 +4908,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>61.6</v>
+        <v>62.9</v>
       </c>
       <c r="D87" t="n">
-        <v>2227</v>
+        <v>2181</v>
       </c>
       <c r="E87" t="n">
         <v>1101.400153022188</v>
       </c>
       <c r="F87" t="n">
-        <v>102.2</v>
+        <v>98</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>402053000000</v>
       </c>
       <c r="N87" t="n">
-        <v>652543068800</v>
+        <v>639064406400</v>
       </c>
     </row>
     <row r="88">
@@ -4960,16 +4960,16 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>61.6</v>
+        <v>62.9</v>
       </c>
       <c r="D88" t="n">
-        <v>2227</v>
+        <v>2181</v>
       </c>
       <c r="E88" t="n">
         <v>1101.400153022188</v>
       </c>
       <c r="F88" t="n">
-        <v>102.2</v>
+        <v>98</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>402053000000</v>
       </c>
       <c r="N88" t="n">
-        <v>652543068800</v>
+        <v>639064406400</v>
       </c>
     </row>
     <row r="89">
@@ -5012,16 +5012,16 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>45.1</v>
+        <v>44.6</v>
       </c>
       <c r="D89" t="n">
-        <v>3328</v>
+        <v>3363</v>
       </c>
       <c r="E89" t="n">
         <v>1492.806001579363</v>
       </c>
       <c r="F89" t="n">
-        <v>122.9</v>
+        <v>125.3</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>112301000000</v>
       </c>
       <c r="N89" t="n">
-        <v>248948660480</v>
+        <v>251566810455</v>
       </c>
     </row>
     <row r="90">
@@ -5064,16 +5064,16 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>81.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="D90" t="n">
-        <v>1120</v>
+        <v>1107</v>
       </c>
       <c r="E90" t="n">
         <v>1341.977644710579</v>
       </c>
       <c r="F90" t="n">
-        <v>-16.5</v>
+        <v>-17.5</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>86654000000</v>
       </c>
       <c r="N90" t="n">
-        <v>106853221440</v>
+        <v>105612960834</v>
       </c>
     </row>
     <row r="91">
@@ -5116,16 +5116,16 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>23.6</v>
+        <v>24.2</v>
       </c>
       <c r="D91" t="n">
-        <v>4443</v>
+        <v>4340</v>
       </c>
       <c r="E91" t="n">
         <v>2006.059650428343</v>
       </c>
       <c r="F91" t="n">
-        <v>121.5</v>
+        <v>116.3</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>173440000000</v>
       </c>
       <c r="N91" t="n">
-        <v>734074166112</v>
+        <v>717056466560</v>
       </c>
     </row>
     <row r="92">
@@ -5171,13 +5171,13 @@
         <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>1857.5</v>
+        <v>1851</v>
       </c>
       <c r="E92" t="n">
         <v>2697.360927565142</v>
       </c>
       <c r="F92" t="n">
-        <v>-31.1</v>
+        <v>-31.4</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
         <v>7339000000</v>
       </c>
       <c r="N92" t="n">
-        <v>724374828925</v>
+        <v>721840004490</v>
       </c>
     </row>
     <row r="93">
@@ -5220,16 +5220,16 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>17.2</v>
+        <v>17.4</v>
       </c>
       <c r="D93" t="n">
-        <v>4545</v>
+        <v>4495</v>
       </c>
       <c r="E93" t="n">
         <v>7960</v>
       </c>
       <c r="F93" t="n">
-        <v>-42.9</v>
+        <v>-43.5</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -5257,7 +5257,7 @@
         <v>29865000000</v>
       </c>
       <c r="N93" t="n">
-        <v>173714690430</v>
+        <v>171803637730</v>
       </c>
     </row>
     <row r="94">
@@ -5272,16 +5272,16 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="D94" t="n">
-        <v>5401</v>
+        <v>5419</v>
       </c>
       <c r="E94" t="n">
         <v>3735.709461270437</v>
       </c>
       <c r="F94" t="n">
-        <v>44.6</v>
+        <v>45.1</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>110688000000</v>
       </c>
       <c r="N94" t="n">
-        <v>619949091531</v>
+        <v>622015205889</v>
       </c>
     </row>
     <row r="95">
@@ -5324,10 +5324,10 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="D95" t="n">
-        <v>2172</v>
+        <v>2177</v>
       </c>
       <c r="E95" t="n">
         <v>5463.67048346056</v>
@@ -5361,7 +5361,7 @@
         <v>11249000000</v>
       </c>
       <c r="N95" t="n">
-        <v>37991733480</v>
+        <v>38079191430</v>
       </c>
     </row>
     <row r="96">
@@ -5379,7 +5379,7 @@
         <v>25.7</v>
       </c>
       <c r="D96" t="n">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="E96" t="n">
         <v>3234.727863989046</v>
@@ -5413,7 +5413,7 @@
         <v>52215000000</v>
       </c>
       <c r="N96" t="n">
-        <v>203414346800</v>
+        <v>203271097260</v>
       </c>
     </row>
     <row r="97">
@@ -5428,16 +5428,16 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>33.5</v>
+        <v>33.6</v>
       </c>
       <c r="D97" t="n">
-        <v>3270</v>
+        <v>3265</v>
       </c>
       <c r="E97" t="n">
         <v>3155.301177013616</v>
       </c>
       <c r="F97" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>70480000000</v>
       </c>
       <c r="N97" t="n">
-        <v>210087029460</v>
+        <v>209765795470</v>
       </c>
     </row>
     <row r="98">
@@ -5480,16 +5480,16 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="D98" t="n">
-        <v>3290</v>
+        <v>3217</v>
       </c>
       <c r="E98" t="n">
         <v>2655.311711736394</v>
       </c>
       <c r="F98" t="n">
-        <v>23.9</v>
+        <v>21.2</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>33115000000</v>
       </c>
       <c r="N98" t="n">
-        <v>583415716450</v>
+        <v>570470626085</v>
       </c>
     </row>
     <row r="99">
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>39.8</v>
+        <v>39.9</v>
       </c>
       <c r="D99" t="n">
-        <v>926.2999877929688</v>
+        <v>925.2000122070312</v>
       </c>
       <c r="E99" t="n">
         <v>2157.626835069302</v>
@@ -5569,7 +5569,7 @@
         <v>152963000000</v>
       </c>
       <c r="N99" t="n">
-        <v>383895832708</v>
+        <v>383439958748</v>
       </c>
     </row>
     <row r="100">
@@ -5584,16 +5584,16 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>97.59999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="D100" t="n">
-        <v>1177</v>
+        <v>1186</v>
       </c>
       <c r="E100" t="n">
         <v>810</v>
       </c>
       <c r="F100" t="n">
-        <v>45.3</v>
+        <v>46.4</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>50303000000</v>
       </c>
       <c r="N100" t="n">
-        <v>51562226683</v>
+        <v>51956500294</v>
       </c>
     </row>
     <row r="101">
@@ -5636,16 +5636,16 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="D101" t="n">
-        <v>2079</v>
+        <v>2043</v>
       </c>
       <c r="E101" t="n">
         <v>2300.974351689521</v>
       </c>
       <c r="F101" t="n">
-        <v>-9.6</v>
+        <v>-11.2</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         <v>8549173000</v>
       </c>
       <c r="N101" t="n">
-        <v>87225588450</v>
+        <v>85715188650</v>
       </c>
     </row>
     <row r="102">
@@ -5688,16 +5688,16 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>39.7</v>
+        <v>39.6</v>
       </c>
       <c r="D102" t="n">
-        <v>1609</v>
+        <v>1614</v>
       </c>
       <c r="E102" t="n">
-        <v>1180.463123164206</v>
+        <v>1180.450912709519</v>
       </c>
       <c r="F102" t="n">
-        <v>36.3</v>
+        <v>36.7</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="I102" t="n">
@@ -5725,7 +5725,7 @@
         <v>29529000000</v>
       </c>
       <c r="N102" t="n">
-        <v>74348009092</v>
+        <v>74585018832</v>
       </c>
     </row>
     <row r="103">
@@ -5740,16 +5740,16 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>39.7</v>
+        <v>39.6</v>
       </c>
       <c r="D103" t="n">
-        <v>1609</v>
+        <v>1614</v>
       </c>
       <c r="E103" t="n">
-        <v>1170.279952698077</v>
+        <v>1180.45745232471</v>
       </c>
       <c r="F103" t="n">
-        <v>37.5</v>
+        <v>36.7</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="I103" t="n">
@@ -5777,7 +5777,7 @@
         <v>29529000000</v>
       </c>
       <c r="N103" t="n">
-        <v>74348009092</v>
+        <v>74585018832</v>
       </c>
     </row>
     <row r="104">
@@ -5792,16 +5792,16 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>39.7</v>
+        <v>39.6</v>
       </c>
       <c r="D104" t="n">
-        <v>1609</v>
+        <v>1614</v>
       </c>
       <c r="E104" t="n">
-        <v>1169.924818603025</v>
+        <v>1180.463123164206</v>
       </c>
       <c r="F104" t="n">
-        <v>37.5</v>
+        <v>36.7</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="I104" t="n">
@@ -5829,7 +5829,7 @@
         <v>29529000000</v>
       </c>
       <c r="N104" t="n">
-        <v>74348009092</v>
+        <v>74585018832</v>
       </c>
     </row>
     <row r="105">
@@ -5844,16 +5844,16 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>39.7</v>
+        <v>39.6</v>
       </c>
       <c r="D105" t="n">
-        <v>1609</v>
+        <v>1614</v>
       </c>
       <c r="E105" t="n">
-        <v>1168.709522546084</v>
+        <v>1170.279952698077</v>
       </c>
       <c r="F105" t="n">
-        <v>37.7</v>
+        <v>37.9</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="I105" t="n">
@@ -5881,31 +5881,31 @@
         <v>29529000000</v>
       </c>
       <c r="N105" t="n">
-        <v>74348009092</v>
+        <v>74585018832</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>山洋電気株式会社</t>
+          <t>東亜道路工業株式会社</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>12</v>
+        <v>39.6</v>
       </c>
       <c r="D106" t="n">
-        <v>5170</v>
+        <v>1614</v>
       </c>
       <c r="E106" t="n">
-        <v>7052.737306843267</v>
+        <v>1169.924818603025</v>
       </c>
       <c r="F106" t="n">
-        <v>-26.7</v>
+        <v>38</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -5914,154 +5914,154 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>8317000000</v>
+        <v>11649000000</v>
       </c>
       <c r="J106" t="n">
-        <v>6048000000</v>
+        <v>13793000000</v>
       </c>
       <c r="K106" t="n">
-        <v>7673000000</v>
+        <v>4087000000</v>
       </c>
       <c r="L106" t="n">
-        <v>49734000000</v>
+        <v>50605000000</v>
       </c>
       <c r="M106" t="n">
-        <v>22038000000</v>
+        <v>29529000000</v>
       </c>
       <c r="N106" t="n">
-        <v>183612761970</v>
+        <v>74585018832</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ヘリオス テクノ ホールディング株式会社</t>
+          <t>東亜道路工業株式会社</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>53.1</v>
+        <v>39.6</v>
       </c>
       <c r="D107" t="n">
-        <v>993</v>
+        <v>1614</v>
       </c>
       <c r="E107" t="n">
-        <v>896.0103264198827</v>
+        <v>1168.709522546084</v>
       </c>
       <c r="F107" t="n">
-        <v>10.8</v>
+        <v>38.1</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>7851015000</v>
+        <v>11649000000</v>
       </c>
       <c r="J107" t="n">
-        <v>640317000</v>
+        <v>13793000000</v>
       </c>
       <c r="K107" t="n">
-        <v>1079200000</v>
+        <v>4087000000</v>
       </c>
       <c r="L107" t="n">
-        <v>13746774000</v>
+        <v>50605000000</v>
       </c>
       <c r="M107" t="n">
-        <v>9570532000</v>
+        <v>29529000000</v>
       </c>
       <c r="N107" t="n">
-        <v>18024605331</v>
+        <v>74585018832</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>シェアリングテクノロジー株式会社</t>
+          <t>山洋電気株式会社</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="D108" t="n">
-        <v>1523</v>
+        <v>5320</v>
       </c>
       <c r="E108" t="n">
-        <v>653.0713101160862</v>
+        <v>7052.737306843267</v>
       </c>
       <c r="F108" t="n">
-        <v>133.2</v>
+        <v>-24.6</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>4016706000</v>
+        <v>8317000000</v>
       </c>
       <c r="J108" t="n">
-        <v>309745000</v>
+        <v>6048000000</v>
       </c>
       <c r="K108" t="n">
-        <v>0</v>
+        <v>7673000000</v>
       </c>
       <c r="L108" t="n">
-        <v>185001000</v>
+        <v>49734000000</v>
       </c>
       <c r="M108" t="n">
-        <v>4326451000</v>
+        <v>22038000000</v>
       </c>
       <c r="N108" t="n">
-        <v>36447322687</v>
+        <v>188940018120</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>栄研化学株式会社</t>
+          <t>ヘリオス テクノ ホールディング株式会社</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>29.7</v>
+        <v>53.2</v>
       </c>
       <c r="D109" t="n">
-        <v>2341</v>
+        <v>992</v>
       </c>
       <c r="E109" t="n">
-        <v>1947.225264702313</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="F109" t="n">
-        <v>20.2</v>
+        <v>10.7</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -6070,50 +6070,50 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>10900000000</v>
+        <v>7851015000</v>
       </c>
       <c r="J109" t="n">
-        <v>11585000000</v>
+        <v>640317000</v>
       </c>
       <c r="K109" t="n">
-        <v>408000000</v>
+        <v>1079200000</v>
       </c>
       <c r="L109" t="n">
-        <v>45803000000</v>
+        <v>13746774000</v>
       </c>
       <c r="M109" t="n">
-        <v>22893000000</v>
+        <v>9570532000</v>
       </c>
       <c r="N109" t="n">
-        <v>77172406393</v>
+        <v>18006453664</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>栄研化学株式会社</t>
+          <t>シェアリングテクノロジー株式会社</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>29.7</v>
+        <v>11.9</v>
       </c>
       <c r="D110" t="n">
-        <v>2341</v>
+        <v>1520</v>
       </c>
       <c r="E110" t="n">
-        <v>1678.083113259255</v>
+        <v>653.0713101160862</v>
       </c>
       <c r="F110" t="n">
-        <v>39.5</v>
+        <v>132.7</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -6122,154 +6122,154 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>10900000000</v>
+        <v>4016706000</v>
       </c>
       <c r="J110" t="n">
-        <v>11585000000</v>
+        <v>309745000</v>
       </c>
       <c r="K110" t="n">
-        <v>408000000</v>
+        <v>0</v>
       </c>
       <c r="L110" t="n">
-        <v>45803000000</v>
+        <v>185001000</v>
       </c>
       <c r="M110" t="n">
-        <v>22893000000</v>
+        <v>4326451000</v>
       </c>
       <c r="N110" t="n">
-        <v>77172406393</v>
+        <v>36375528880</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>株式会社ヤマダホールディングス</t>
+          <t>栄研化学株式会社</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>9831</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>58.8</v>
+        <v>30.5</v>
       </c>
       <c r="D111" t="n">
-        <v>709</v>
+        <v>2279</v>
       </c>
       <c r="E111" t="n">
-        <v>530</v>
+        <v>1947.225264702313</v>
       </c>
       <c r="F111" t="n">
-        <v>33.8</v>
+        <v>17</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>56470000000</v>
+        <v>10900000000</v>
       </c>
       <c r="J111" t="n">
-        <v>210733000000</v>
+        <v>11585000000</v>
       </c>
       <c r="K111" t="n">
-        <v>9997000000</v>
+        <v>408000000</v>
       </c>
       <c r="L111" t="n">
-        <v>676277000000</v>
+        <v>45803000000</v>
       </c>
       <c r="M111" t="n">
-        <v>277200000000</v>
+        <v>22893000000</v>
       </c>
       <c r="N111" t="n">
-        <v>471467581997</v>
+        <v>75128540867</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>日本化薬株式会社</t>
+          <t>栄研化学株式会社</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>35.2</v>
+        <v>30.5</v>
       </c>
       <c r="D112" t="n">
-        <v>2061.5</v>
+        <v>2279</v>
       </c>
       <c r="E112" t="n">
-        <v>1111.90611839092</v>
+        <v>1678.083113259255</v>
       </c>
       <c r="F112" t="n">
-        <v>85.40000000000001</v>
+        <v>35.8</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>52962000000</v>
+        <v>10900000000</v>
       </c>
       <c r="J112" t="n">
-        <v>48231000000</v>
+        <v>11585000000</v>
       </c>
       <c r="K112" t="n">
-        <v>4337000000</v>
+        <v>408000000</v>
       </c>
       <c r="L112" t="n">
-        <v>246425000000</v>
+        <v>45803000000</v>
       </c>
       <c r="M112" t="n">
-        <v>105530000000</v>
+        <v>22893000000</v>
       </c>
       <c r="N112" t="n">
-        <v>299684404800</v>
+        <v>75128540867</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>王子ホールディングス株式会社</t>
+          <t>株式会社ヤマダホールディングス</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>9831</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>41.4</v>
+        <v>59.6</v>
       </c>
       <c r="D113" t="n">
-        <v>875.2000122070312</v>
+        <v>699.7999877929688</v>
       </c>
       <c r="E113" t="n">
-        <v>590</v>
+        <v>530</v>
       </c>
       <c r="F113" t="n">
-        <v>48.3</v>
+        <v>32</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -6278,310 +6278,310 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>55474000000</v>
+        <v>56470000000</v>
       </c>
       <c r="J113" t="n">
-        <v>244732000000</v>
+        <v>210733000000</v>
       </c>
       <c r="K113" t="n">
-        <v>7434000000</v>
+        <v>9997000000</v>
       </c>
       <c r="L113" t="n">
-        <v>875470000000</v>
+        <v>676277000000</v>
       </c>
       <c r="M113" t="n">
-        <v>307640000000</v>
+        <v>277200000000</v>
       </c>
       <c r="N113" t="n">
-        <v>743249863600</v>
+        <v>465349799896</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>東邦ホールディングス株式会社</t>
+          <t>日本化薬株式会社</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>51.2</v>
+        <v>35</v>
       </c>
       <c r="D114" t="n">
-        <v>3961</v>
+        <v>2072.5</v>
       </c>
       <c r="E114" t="n">
-        <v>3405.914389596362</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="F114" t="n">
-        <v>16.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>90014000000</v>
+        <v>52962000000</v>
       </c>
       <c r="J114" t="n">
-        <v>34220000000</v>
+        <v>48231000000</v>
       </c>
       <c r="K114" t="n">
-        <v>7000000000</v>
+        <v>4337000000</v>
       </c>
       <c r="L114" t="n">
-        <v>241281000000</v>
+        <v>246425000000</v>
       </c>
       <c r="M114" t="n">
-        <v>131234000000</v>
+        <v>105530000000</v>
       </c>
       <c r="N114" t="n">
-        <v>256283128703</v>
+        <v>301283496942</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>東邦ホールディングス株式会社</t>
+          <t>王子ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>51.2</v>
+        <v>41.5</v>
       </c>
       <c r="D115" t="n">
-        <v>3961</v>
+        <v>873.9000244140625</v>
       </c>
       <c r="E115" t="n">
-        <v>2714.613787300615</v>
+        <v>590</v>
       </c>
       <c r="F115" t="n">
-        <v>45.9</v>
+        <v>48.1</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>90014000000</v>
+        <v>55474000000</v>
       </c>
       <c r="J115" t="n">
-        <v>34220000000</v>
+        <v>244732000000</v>
       </c>
       <c r="K115" t="n">
-        <v>7000000000</v>
+        <v>7434000000</v>
       </c>
       <c r="L115" t="n">
-        <v>241281000000</v>
+        <v>875470000000</v>
       </c>
       <c r="M115" t="n">
-        <v>131234000000</v>
+        <v>307640000000</v>
       </c>
       <c r="N115" t="n">
-        <v>256283128703</v>
+        <v>742145869386</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>株式会社アイネス</t>
+          <t>東邦ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>9742</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>33.3</v>
+        <v>51.4</v>
       </c>
       <c r="D116" t="n">
-        <v>2183</v>
+        <v>3944</v>
       </c>
       <c r="E116" t="n">
-        <v>1879.137815927515</v>
+        <v>3405.914389596362</v>
       </c>
       <c r="F116" t="n">
-        <v>16.2</v>
+        <v>15.8</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>9731000000</v>
+        <v>90014000000</v>
       </c>
       <c r="J116" t="n">
-        <v>5286000000</v>
+        <v>34220000000</v>
       </c>
       <c r="K116" t="n">
-        <v>100000000</v>
+        <v>7000000000</v>
       </c>
       <c r="L116" t="n">
-        <v>34620000000</v>
+        <v>241281000000</v>
       </c>
       <c r="M116" t="n">
-        <v>15117000000</v>
+        <v>131234000000</v>
       </c>
       <c r="N116" t="n">
-        <v>45455401801</v>
+        <v>255183201112</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>日本ゼオン株式会社</t>
+          <t>東邦ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>34.3</v>
+        <v>51.4</v>
       </c>
       <c r="D117" t="n">
-        <v>2458</v>
+        <v>3944</v>
       </c>
       <c r="E117" t="n">
-        <v>1721.078563209627</v>
+        <v>2714.613787300615</v>
       </c>
       <c r="F117" t="n">
-        <v>42.8</v>
+        <v>45.3</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>44521000000</v>
+        <v>90014000000</v>
       </c>
       <c r="J117" t="n">
-        <v>45382000000</v>
+        <v>34220000000</v>
       </c>
       <c r="K117" t="n">
-        <v>71191000000</v>
+        <v>7000000000</v>
       </c>
       <c r="L117" t="n">
-        <v>321836000000</v>
+        <v>241281000000</v>
       </c>
       <c r="M117" t="n">
-        <v>161094000000</v>
+        <v>131234000000</v>
       </c>
       <c r="N117" t="n">
-        <v>470327256206</v>
+        <v>255183201112</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>太陽ホールディングス株式会社</t>
+          <t>株式会社アイネス</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>9742</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>16.4</v>
+        <v>34.5</v>
       </c>
       <c r="D118" t="n">
-        <v>4724</v>
+        <v>2105</v>
       </c>
       <c r="E118" t="n">
-        <v>2199.643244598912</v>
+        <v>1879.137815927515</v>
       </c>
       <c r="F118" t="n">
-        <v>114.8</v>
+        <v>12</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>51152000000</v>
+        <v>9731000000</v>
       </c>
       <c r="J118" t="n">
-        <v>30337000000</v>
+        <v>5286000000</v>
       </c>
       <c r="K118" t="n">
-        <v>4870000000</v>
+        <v>100000000</v>
       </c>
       <c r="L118" t="n">
-        <v>85466000000</v>
+        <v>34620000000</v>
       </c>
       <c r="M118" t="n">
-        <v>86359000000</v>
+        <v>15117000000</v>
       </c>
       <c r="N118" t="n">
-        <v>525671045768</v>
+        <v>43831250935</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>太陽ホールディングス株式会社</t>
+          <t>日本ゼオン株式会社</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>16.4</v>
+        <v>34.4</v>
       </c>
       <c r="D119" t="n">
-        <v>4724</v>
+        <v>2447</v>
       </c>
       <c r="E119" t="n">
-        <v>3565.648720929983</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="F119" t="n">
-        <v>32.5</v>
+        <v>42.2</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -6590,50 +6590,50 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>51152000000</v>
+        <v>44521000000</v>
       </c>
       <c r="J119" t="n">
-        <v>30337000000</v>
+        <v>45382000000</v>
       </c>
       <c r="K119" t="n">
-        <v>4870000000</v>
+        <v>71191000000</v>
       </c>
       <c r="L119" t="n">
-        <v>85466000000</v>
+        <v>321836000000</v>
       </c>
       <c r="M119" t="n">
-        <v>86359000000</v>
+        <v>161094000000</v>
       </c>
       <c r="N119" t="n">
-        <v>525671045768</v>
+        <v>468222455629</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>株式会社エス・エム・エス</t>
+          <t>太陽ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>8.800000000000001</v>
+        <v>16.4</v>
       </c>
       <c r="D120" t="n">
-        <v>2518</v>
+        <v>4722</v>
       </c>
       <c r="E120" t="n">
-        <v>1478.127248828989</v>
+        <v>2199.643244598912</v>
       </c>
       <c r="F120" t="n">
-        <v>70.40000000000001</v>
+        <v>114.7</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -6642,102 +6642,102 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>14126000000</v>
+        <v>51152000000</v>
       </c>
       <c r="J120" t="n">
-        <v>1187000000</v>
+        <v>30337000000</v>
       </c>
       <c r="K120" t="n">
-        <v>2875000000</v>
+        <v>4870000000</v>
       </c>
       <c r="L120" t="n">
-        <v>29991000000</v>
+        <v>85466000000</v>
       </c>
       <c r="M120" t="n">
-        <v>18188000000</v>
+        <v>86359000000</v>
       </c>
       <c r="N120" t="n">
-        <v>206678570582</v>
+        <v>525448492404</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>アニコム ホールディングス株式会社</t>
+          <t>太陽ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>8715</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>39.3</v>
+        <v>16.4</v>
       </c>
       <c r="D121" t="n">
-        <v>1076</v>
+        <v>4722</v>
       </c>
       <c r="E121" t="n">
-        <v>656.2604975855553</v>
+        <v>3565.648720929983</v>
       </c>
       <c r="F121" t="n">
-        <v>64</v>
+        <v>32.4</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>27691000000</v>
+        <v>51152000000</v>
       </c>
       <c r="J121" t="n">
-        <v>3070000000</v>
+        <v>30337000000</v>
       </c>
       <c r="K121" t="n">
-        <v>3000000</v>
+        <v>4870000000</v>
       </c>
       <c r="L121" t="n">
-        <v>27316000000</v>
+        <v>85466000000</v>
       </c>
       <c r="M121" t="n">
-        <v>30764000000</v>
+        <v>86359000000</v>
       </c>
       <c r="N121" t="n">
-        <v>78355632720</v>
+        <v>525448492404</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>東京製鐵株式会社</t>
+          <t>株式会社エス・エム・エス</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>102.3</v>
+        <v>8.6</v>
       </c>
       <c r="D122" t="n">
-        <v>1701</v>
+        <v>2568</v>
       </c>
       <c r="E122" t="n">
-        <v>1605.452212379354</v>
+        <v>1478.127248828989</v>
       </c>
       <c r="F122" t="n">
-        <v>6</v>
+        <v>73.7</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -6746,102 +6746,102 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>68644000000</v>
+        <v>14126000000</v>
       </c>
       <c r="J122" t="n">
-        <v>33060000000</v>
+        <v>1187000000</v>
       </c>
       <c r="K122" t="n">
-        <v>75000000000</v>
+        <v>2875000000</v>
       </c>
       <c r="L122" t="n">
-        <v>158280000000</v>
+        <v>29991000000</v>
       </c>
       <c r="M122" t="n">
-        <v>176704000000</v>
+        <v>18188000000</v>
       </c>
       <c r="N122" t="n">
-        <v>172815035841</v>
+        <v>210782593032</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ウェーブロックホールディングス株式会社</t>
+          <t>アニコム ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>7940</t>
+          <t>8715</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>62.5</v>
+        <v>39.4</v>
       </c>
       <c r="D123" t="n">
-        <v>1057</v>
+        <v>1073</v>
       </c>
       <c r="E123" t="n">
-        <v>1010</v>
+        <v>656.2604975855553</v>
       </c>
       <c r="F123" t="n">
-        <v>4.7</v>
+        <v>63.5</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1961626000</v>
+        <v>27691000000</v>
       </c>
       <c r="J123" t="n">
-        <v>2544946000</v>
+        <v>3070000000</v>
       </c>
       <c r="K123" t="n">
-        <v>1068366000</v>
+        <v>3000000</v>
       </c>
       <c r="L123" t="n">
-        <v>13761535000</v>
+        <v>27316000000</v>
       </c>
       <c r="M123" t="n">
-        <v>5574938000</v>
+        <v>30764000000</v>
       </c>
       <c r="N123" t="n">
-        <v>8926497125</v>
+        <v>78137169060</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>近畿車輛株式会社</t>
+          <t>東京製鐵株式会社</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>7122</t>
+          <t>5423</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>105.9</v>
+        <v>101.7</v>
       </c>
       <c r="D124" t="n">
-        <v>2436</v>
+        <v>1711</v>
       </c>
       <c r="E124" t="n">
-        <v>2144.894901144641</v>
+        <v>1605.452212379354</v>
       </c>
       <c r="F124" t="n">
-        <v>13.6</v>
+        <v>6.6</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -6850,206 +6850,206 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>6847000000</v>
+        <v>68644000000</v>
       </c>
       <c r="J124" t="n">
-        <v>4580000000</v>
+        <v>33060000000</v>
       </c>
       <c r="K124" t="n">
-        <v>6329000000</v>
+        <v>75000000000</v>
       </c>
       <c r="L124" t="n">
-        <v>24474000000</v>
+        <v>158280000000</v>
       </c>
       <c r="M124" t="n">
-        <v>17756000000</v>
+        <v>176704000000</v>
       </c>
       <c r="N124" t="n">
-        <v>16759877316</v>
+        <v>173830997251</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>株式会社三陽商会</t>
+          <t>ウェーブロックホールディングス株式会社</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>7940</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>61</v>
+        <v>62.5</v>
       </c>
       <c r="D125" t="n">
-        <v>1429</v>
+        <v>1057</v>
       </c>
       <c r="E125" t="n">
-        <v>3321.975331035734</v>
+        <v>1010</v>
       </c>
       <c r="F125" t="n">
-        <v>-57</v>
+        <v>4.7</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>16287000000</v>
+        <v>1961626000</v>
       </c>
       <c r="J125" t="n">
-        <v>3021000000</v>
+        <v>2544946000</v>
       </c>
       <c r="K125" t="n">
-        <v>6298000000</v>
+        <v>1068366000</v>
       </c>
       <c r="L125" t="n">
-        <v>33920000000</v>
+        <v>13761535000</v>
       </c>
       <c r="M125" t="n">
-        <v>25606000000</v>
+        <v>5574938000</v>
       </c>
       <c r="N125" t="n">
-        <v>41992639728</v>
+        <v>8926497125</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>月島ホールディングス株式会社</t>
+          <t>近畿車輛株式会社</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>6332</t>
+          <t>7122</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>46.3</v>
+        <v>105.5</v>
       </c>
       <c r="D126" t="n">
-        <v>2788</v>
+        <v>2446</v>
       </c>
       <c r="E126" t="n">
-        <v>1410</v>
+        <v>2144.894901144641</v>
       </c>
       <c r="F126" t="n">
-        <v>97.7</v>
+        <v>14</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>28795000000</v>
+        <v>6847000000</v>
       </c>
       <c r="J126" t="n">
-        <v>22203000000</v>
+        <v>4580000000</v>
       </c>
       <c r="K126" t="n">
-        <v>100000000</v>
+        <v>6329000000</v>
       </c>
       <c r="L126" t="n">
-        <v>80949000000</v>
+        <v>24474000000</v>
       </c>
       <c r="M126" t="n">
-        <v>51098000000</v>
+        <v>17756000000</v>
       </c>
       <c r="N126" t="n">
-        <v>110408209724</v>
+        <v>16828678126</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>マネックスグループ株式会社</t>
+          <t>株式会社三陽商会</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>8698</t>
+          <t>8011</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>14.9</v>
+        <v>61.8</v>
       </c>
       <c r="D127" t="n">
-        <v>734</v>
+        <v>1411</v>
       </c>
       <c r="E127" t="n">
-        <v>510.1850530906719</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="F127" t="n">
-        <v>43.9</v>
+        <v>-57.5</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>17794000000</v>
+        <v>16287000000</v>
       </c>
       <c r="J127" t="n">
-        <v>412000000</v>
+        <v>3021000000</v>
       </c>
       <c r="K127" t="n">
-        <v>9312000000</v>
+        <v>6298000000</v>
       </c>
       <c r="L127" t="n">
-        <v>98001000000</v>
+        <v>33920000000</v>
       </c>
       <c r="M127" t="n">
-        <v>27518000000</v>
+        <v>25606000000</v>
       </c>
       <c r="N127" t="n">
-        <v>184500944056</v>
+        <v>41463691152</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>株式会社あおぞら銀行</t>
+          <t>月島ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>230.1</v>
+        <v>45.5</v>
       </c>
       <c r="D128" t="n">
-        <v>3405</v>
+        <v>2838</v>
       </c>
       <c r="E128" t="n">
-        <v>2190</v>
+        <v>1410</v>
       </c>
       <c r="F128" t="n">
-        <v>55.5</v>
+        <v>101.3</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -7058,154 +7058,154 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1061743000000</v>
+        <v>28795000000</v>
       </c>
       <c r="J128" t="n">
-        <v>22385000000</v>
+        <v>22203000000</v>
       </c>
       <c r="K128" t="n">
-        <v>0</v>
+        <v>100000000</v>
       </c>
       <c r="L128" t="n">
-        <v>487265000000</v>
+        <v>80949000000</v>
       </c>
       <c r="M128" t="n">
-        <v>1084128000000</v>
+        <v>51098000000</v>
       </c>
       <c r="N128" t="n">
-        <v>471187563780</v>
+        <v>112388270874</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>日本製紙株式会社</t>
+          <t>マネックスグループ株式会社</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>8698</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>306.1</v>
+        <v>15</v>
       </c>
       <c r="D129" t="n">
-        <v>1306</v>
+        <v>732</v>
       </c>
       <c r="E129" t="n">
-        <v>1250</v>
+        <v>510.1850530906719</v>
       </c>
       <c r="F129" t="n">
-        <v>4.5</v>
+        <v>43.5</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>136216000000</v>
+        <v>17794000000</v>
       </c>
       <c r="J129" t="n">
-        <v>151771000000</v>
+        <v>412000000</v>
       </c>
       <c r="K129" t="n">
-        <v>172984000000</v>
+        <v>9312000000</v>
       </c>
       <c r="L129" t="n">
-        <v>438604000000</v>
+        <v>98001000000</v>
       </c>
       <c r="M129" t="n">
-        <v>460971000000</v>
+        <v>27518000000</v>
       </c>
       <c r="N129" t="n">
-        <v>150592904918</v>
+        <v>183998216688</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>カルビー株式会社</t>
+          <t>株式会社あおぞら銀行</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>33.3</v>
+        <v>230</v>
       </c>
       <c r="D130" t="n">
-        <v>3043</v>
+        <v>3406</v>
       </c>
       <c r="E130" t="n">
-        <v>2919.137515755844</v>
+        <v>2190</v>
       </c>
       <c r="F130" t="n">
-        <v>4.2</v>
+        <v>55.5</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>49670000000</v>
+        <v>1061743000000</v>
       </c>
       <c r="J130" t="n">
-        <v>70285000000</v>
+        <v>22385000000</v>
       </c>
       <c r="K130" t="n">
-        <v>3263000000</v>
+        <v>0</v>
       </c>
       <c r="L130" t="n">
-        <v>183458000000</v>
+        <v>487265000000</v>
       </c>
       <c r="M130" t="n">
-        <v>123218000000</v>
+        <v>1084128000000</v>
       </c>
       <c r="N130" t="n">
-        <v>369991839722</v>
+        <v>471326108344</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ＮＩＴＴＯＫＵ株式会社</t>
+          <t>日本製紙株式会社</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>51.3</v>
+        <v>309.4</v>
       </c>
       <c r="D131" t="n">
-        <v>2432</v>
+        <v>1292</v>
       </c>
       <c r="E131" t="n">
-        <v>1710</v>
+        <v>1250</v>
       </c>
       <c r="F131" t="n">
-        <v>42.2</v>
+        <v>3.4</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -7214,102 +7214,102 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>11768000000</v>
+        <v>136216000000</v>
       </c>
       <c r="J131" t="n">
-        <v>6299000000</v>
+        <v>151771000000</v>
       </c>
       <c r="K131" t="n">
-        <v>2999000000</v>
+        <v>172984000000</v>
       </c>
       <c r="L131" t="n">
-        <v>33919000000</v>
+        <v>438604000000</v>
       </c>
       <c r="M131" t="n">
-        <v>21066000000</v>
+        <v>460971000000</v>
       </c>
       <c r="N131" t="n">
-        <v>41038740224</v>
+        <v>148978585876</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ＮＩＴＴＯＫＵ株式会社</t>
+          <t>カルビー株式会社</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>51.3</v>
+        <v>33.8</v>
       </c>
       <c r="D132" t="n">
-        <v>2432</v>
+        <v>3002</v>
       </c>
       <c r="E132" t="n">
-        <v>1710</v>
+        <v>2919.137515755844</v>
       </c>
       <c r="F132" t="n">
-        <v>42.2</v>
+        <v>2.8</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>11768000000</v>
+        <v>49670000000</v>
       </c>
       <c r="J132" t="n">
-        <v>6299000000</v>
+        <v>70285000000</v>
       </c>
       <c r="K132" t="n">
-        <v>2999000000</v>
+        <v>3263000000</v>
       </c>
       <c r="L132" t="n">
-        <v>33919000000</v>
+        <v>183458000000</v>
       </c>
       <c r="M132" t="n">
-        <v>21066000000</v>
+        <v>123218000000</v>
       </c>
       <c r="N132" t="n">
-        <v>41038740224</v>
+        <v>365006737708</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>新光商事株式会社</t>
+          <t>ＮＩＴＴＯＫＵ株式会社</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>8141</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>30.8</v>
+        <v>50.6</v>
       </c>
       <c r="D133" t="n">
-        <v>1567</v>
+        <v>2468</v>
       </c>
       <c r="E133" t="n">
-        <v>930</v>
+        <v>1710</v>
       </c>
       <c r="F133" t="n">
-        <v>68.5</v>
+        <v>44.3</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -7318,50 +7318,50 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>10579000000</v>
+        <v>11768000000</v>
       </c>
       <c r="J133" t="n">
-        <v>195000000</v>
+        <v>6299000000</v>
       </c>
       <c r="K133" t="n">
-        <v>2995000000</v>
+        <v>2999000000</v>
       </c>
       <c r="L133" t="n">
-        <v>51945000000</v>
+        <v>33919000000</v>
       </c>
       <c r="M133" t="n">
-        <v>13769000000</v>
+        <v>21066000000</v>
       </c>
       <c r="N133" t="n">
-        <v>44737691733</v>
+        <v>41646221576</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>株式会社メガチップス</t>
+          <t>ＮＩＴＴＯＫＵ株式会社</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>6875</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>87.90000000000001</v>
+        <v>50.6</v>
       </c>
       <c r="D134" t="n">
-        <v>10690</v>
+        <v>2468</v>
       </c>
       <c r="E134" t="n">
-        <v>4870</v>
+        <v>1710</v>
       </c>
       <c r="F134" t="n">
-        <v>119.5</v>
+        <v>44.3</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -7370,102 +7370,102 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>25769446000</v>
+        <v>11768000000</v>
       </c>
       <c r="J134" t="n">
-        <v>2249411000</v>
+        <v>6299000000</v>
       </c>
       <c r="K134" t="n">
-        <v>101636005000</v>
+        <v>2999000000</v>
       </c>
       <c r="L134" t="n">
-        <v>67428618000</v>
+        <v>33919000000</v>
       </c>
       <c r="M134" t="n">
-        <v>129654862000</v>
+        <v>21066000000</v>
       </c>
       <c r="N134" t="n">
-        <v>147531631690</v>
+        <v>41646221576</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>株式会社青山財産ネットワークス</t>
+          <t>新光商事株式会社</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>8929</t>
+          <t>8141</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>41.8</v>
+        <v>30.8</v>
       </c>
       <c r="D135" t="n">
-        <v>1387</v>
+        <v>1567</v>
       </c>
       <c r="E135" t="n">
-        <v>1347.74653160027</v>
+        <v>930</v>
       </c>
       <c r="F135" t="n">
-        <v>2.9</v>
+        <v>68.5</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>10862000000</v>
+        <v>10579000000</v>
       </c>
       <c r="J135" t="n">
-        <v>245000000</v>
+        <v>195000000</v>
       </c>
       <c r="K135" t="n">
-        <v>2845000000</v>
+        <v>2995000000</v>
       </c>
       <c r="L135" t="n">
-        <v>7128000000</v>
+        <v>51945000000</v>
       </c>
       <c r="M135" t="n">
-        <v>13952000000</v>
+        <v>13769000000</v>
       </c>
       <c r="N135" t="n">
-        <v>33378485106</v>
+        <v>44737691733</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>平和不動産株式会社</t>
+          <t>株式会社メガチップス</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>8803</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>72.09999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="D136" t="n">
-        <v>2381</v>
+        <v>11170</v>
       </c>
       <c r="E136" t="n">
-        <v>3610</v>
+        <v>4870</v>
       </c>
       <c r="F136" t="n">
-        <v>-34</v>
+        <v>129.4</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -7474,106 +7474,106 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>28111000000</v>
+        <v>25769446000</v>
       </c>
       <c r="J136" t="n">
-        <v>79319000000</v>
+        <v>2249411000</v>
       </c>
       <c r="K136" t="n">
-        <v>5997000000</v>
+        <v>101636005000</v>
       </c>
       <c r="L136" t="n">
-        <v>119278000000</v>
+        <v>67428618000</v>
       </c>
       <c r="M136" t="n">
-        <v>113427000000</v>
+        <v>129654862000</v>
       </c>
       <c r="N136" t="n">
-        <v>157313284298</v>
+        <v>154156064170</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>小林製薬株式会社</t>
+          <t>株式会社青山財産ネットワークス</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>8929</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>30.5</v>
+        <v>41.6</v>
       </c>
       <c r="D137" t="n">
-        <v>5695</v>
+        <v>1394</v>
       </c>
       <c r="E137" t="n">
-        <v>2148.936934940886</v>
+        <v>1347.74653160027</v>
       </c>
       <c r="F137" t="n">
-        <v>165</v>
+        <v>3.4</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>81987000000</v>
+        <v>10862000000</v>
       </c>
       <c r="J137" t="n">
-        <v>32461000000</v>
+        <v>245000000</v>
       </c>
       <c r="K137" t="n">
-        <v>14872000000</v>
+        <v>2845000000</v>
       </c>
       <c r="L137" t="n">
-        <v>195600000000</v>
+        <v>7128000000</v>
       </c>
       <c r="M137" t="n">
-        <v>129320000000</v>
+        <v>13952000000</v>
       </c>
       <c r="N137" t="n">
-        <v>423358446595</v>
+        <v>33546941772</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>小林製薬株式会社</t>
+          <t>平和不動産株式会社</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>30.5</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="D138" t="n">
-        <v>5695</v>
+        <v>2350</v>
       </c>
       <c r="E138" t="n">
-        <v>5066.092575838703</v>
+        <v>3610</v>
       </c>
       <c r="F138" t="n">
-        <v>12.4</v>
+        <v>-34.9</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -7582,46 +7582,46 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>81987000000</v>
+        <v>28111000000</v>
       </c>
       <c r="J138" t="n">
-        <v>32461000000</v>
+        <v>79319000000</v>
       </c>
       <c r="K138" t="n">
-        <v>14872000000</v>
+        <v>5997000000</v>
       </c>
       <c r="L138" t="n">
-        <v>195600000000</v>
+        <v>119278000000</v>
       </c>
       <c r="M138" t="n">
-        <v>129320000000</v>
+        <v>113427000000</v>
       </c>
       <c r="N138" t="n">
-        <v>423358446595</v>
+        <v>155265106300</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>セーレン株式会社</t>
+          <t>小林製薬株式会社</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>3569</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>35.2</v>
+        <v>30.8</v>
       </c>
       <c r="D139" t="n">
-        <v>3405</v>
+        <v>5654</v>
       </c>
       <c r="E139" t="n">
-        <v>1359.655069733296</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="F139" t="n">
-        <v>150.4</v>
+        <v>163.1</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -7630,50 +7630,50 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>35451000000</v>
+        <v>81987000000</v>
       </c>
       <c r="J139" t="n">
-        <v>25813000000</v>
+        <v>32461000000</v>
       </c>
       <c r="K139" t="n">
-        <v>8891000000</v>
+        <v>14872000000</v>
       </c>
       <c r="L139" t="n">
-        <v>91845000000</v>
+        <v>195600000000</v>
       </c>
       <c r="M139" t="n">
-        <v>70155000000</v>
+        <v>129320000000</v>
       </c>
       <c r="N139" t="n">
-        <v>199411240605</v>
+        <v>420310563134</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>データセクション株式会社</t>
+          <t>小林製薬株式会社</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>2.6</v>
+        <v>30.8</v>
       </c>
       <c r="D140" t="n">
-        <v>1529</v>
+        <v>5654</v>
       </c>
       <c r="E140" t="n">
-        <v>5143.276404494382</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="F140" t="n">
-        <v>-70.3</v>
+        <v>11.6</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -7682,650 +7682,754 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1420430000</v>
+        <v>81987000000</v>
       </c>
       <c r="J140" t="n">
-        <v>1162000</v>
+        <v>32461000000</v>
       </c>
       <c r="K140" t="n">
-        <v>49326000</v>
+        <v>14872000000</v>
       </c>
       <c r="L140" t="n">
-        <v>2818110000</v>
+        <v>195600000000</v>
       </c>
       <c r="M140" t="n">
-        <v>1470918000</v>
+        <v>129320000000</v>
       </c>
       <c r="N140" t="n">
-        <v>57279865874</v>
+        <v>420310563134</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>愛眼株式会社</t>
+          <t>セーレン株式会社</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>9854</t>
+          <t>3569</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>69.2</v>
+        <v>35</v>
       </c>
       <c r="D141" t="n">
-        <v>287</v>
+        <v>3420</v>
       </c>
       <c r="E141" t="n">
-        <v>246.9708756284982</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="F141" t="n">
-        <v>16.2</v>
+        <v>151.5</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2219000000</v>
+        <v>35451000000</v>
       </c>
       <c r="J141" t="n">
-        <v>1030000000</v>
+        <v>25813000000</v>
       </c>
       <c r="K141" t="n">
-        <v>604000000</v>
+        <v>8891000000</v>
       </c>
       <c r="L141" t="n">
-        <v>12920000000</v>
+        <v>91845000000</v>
       </c>
       <c r="M141" t="n">
-        <v>3853000000</v>
+        <v>70155000000</v>
       </c>
       <c r="N141" t="n">
-        <v>5569727205</v>
+        <v>200289704220</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>株式会社アシロ</t>
+          <t>データセクション株式会社</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>14</v>
+        <v>2.5</v>
       </c>
       <c r="D142" t="n">
-        <v>1553</v>
+        <v>1577</v>
       </c>
       <c r="E142" t="n">
-        <v>1396.628697042366</v>
+        <v>5143.276404494382</v>
       </c>
       <c r="F142" t="n">
-        <v>11.2</v>
+        <v>-69.3</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1428281000</v>
+        <v>1420430000</v>
       </c>
       <c r="J142" t="n">
-        <v>102238000</v>
+        <v>1162000</v>
       </c>
       <c r="K142" t="n">
-        <v>0</v>
+        <v>49326000</v>
       </c>
       <c r="L142" t="n">
-        <v>1804458000</v>
+        <v>2818110000</v>
       </c>
       <c r="M142" t="n">
-        <v>1530519000</v>
+        <v>1470918000</v>
       </c>
       <c r="N142" t="n">
-        <v>10916948611</v>
+        <v>59078056562</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>三浦工業株式会社</t>
+          <t>愛眼株式会社</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>11.5</v>
+        <v>67.5</v>
       </c>
       <c r="D143" t="n">
-        <v>3181</v>
+        <v>294</v>
       </c>
       <c r="E143" t="n">
-        <v>3147.518794622453</v>
+        <v>246.9708756284982</v>
       </c>
       <c r="F143" t="n">
-        <v>1.1</v>
+        <v>19</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>20794000000</v>
+        <v>2219000000</v>
       </c>
       <c r="J143" t="n">
-        <v>10600000000</v>
+        <v>1030000000</v>
       </c>
       <c r="K143" t="n">
-        <v>10773000000</v>
+        <v>604000000</v>
       </c>
       <c r="L143" t="n">
-        <v>138378000000</v>
+        <v>12920000000</v>
       </c>
       <c r="M143" t="n">
-        <v>42167000000</v>
+        <v>3853000000</v>
       </c>
       <c r="N143" t="n">
-        <v>368198714160</v>
+        <v>5705574210</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>株式会社カカクコム</t>
+          <t>株式会社アシロ</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>7378</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>7</v>
+        <v>13.8</v>
       </c>
       <c r="D144" t="n">
-        <v>3690</v>
+        <v>1575</v>
       </c>
       <c r="E144" t="n">
-        <v>2318.314890576102</v>
+        <v>1396.628697042366</v>
       </c>
       <c r="F144" t="n">
-        <v>59.2</v>
+        <v>12.8</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>46452000000</v>
+        <v>1428281000</v>
       </c>
       <c r="J144" t="n">
-        <v>68000000</v>
+        <v>102238000</v>
       </c>
       <c r="K144" t="n">
-        <v>4669000000</v>
+        <v>0</v>
       </c>
       <c r="L144" t="n">
-        <v>45479000000</v>
+        <v>1804458000</v>
       </c>
       <c r="M144" t="n">
-        <v>51189000000</v>
+        <v>1530519000</v>
       </c>
       <c r="N144" t="n">
-        <v>730015825230</v>
+        <v>11071599525</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>古河機械金属株式会社</t>
+          <t>三浦工業株式会社</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>44</v>
+        <v>11.3</v>
       </c>
       <c r="D145" t="n">
-        <v>4240</v>
+        <v>3223</v>
       </c>
       <c r="E145" t="n">
-        <v>1600</v>
+        <v>3147.518794622453</v>
       </c>
       <c r="F145" t="n">
-        <v>165</v>
+        <v>2.4</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>14468000000</v>
+        <v>20794000000</v>
       </c>
       <c r="J145" t="n">
-        <v>26121000000</v>
+        <v>10600000000</v>
       </c>
       <c r="K145" t="n">
-        <v>19903000000</v>
+        <v>10773000000</v>
       </c>
       <c r="L145" t="n">
-        <v>100075000000</v>
+        <v>138378000000</v>
       </c>
       <c r="M145" t="n">
-        <v>60492000000</v>
+        <v>42167000000</v>
       </c>
       <c r="N145" t="n">
-        <v>137506829440</v>
+        <v>373060187280</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>多木化学株式会社</t>
+          <t>株式会社カカクコム</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>4025</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>30.1</v>
+        <v>7</v>
       </c>
       <c r="D146" t="n">
-        <v>5810</v>
+        <v>3700</v>
       </c>
       <c r="E146" t="n">
-        <v>4695.956053243186</v>
+        <v>2318.314890576102</v>
       </c>
       <c r="F146" t="n">
-        <v>23.7</v>
+        <v>59.6</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>6433000000</v>
+        <v>46452000000</v>
       </c>
       <c r="J146" t="n">
-        <v>7985000000</v>
+        <v>68000000</v>
       </c>
       <c r="K146" t="n">
-        <v>199000000</v>
+        <v>4669000000</v>
       </c>
       <c r="L146" t="n">
-        <v>29378000000</v>
+        <v>45479000000</v>
       </c>
       <c r="M146" t="n">
-        <v>14617000000</v>
+        <v>51189000000</v>
       </c>
       <c r="N146" t="n">
-        <v>48498213890</v>
+        <v>731994187900</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>エムスリー株式会社</t>
+          <t>古河機械金属株式会社</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2413</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>7.4</v>
+        <v>43.7</v>
       </c>
       <c r="D147" t="n">
-        <v>1789.5</v>
+        <v>4265</v>
       </c>
       <c r="E147" t="n">
-        <v>1638.585693292194</v>
+        <v>1600</v>
       </c>
       <c r="F147" t="n">
-        <v>9.199999999999999</v>
+        <v>166.6</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>78812000000</v>
+        <v>14468000000</v>
       </c>
       <c r="J147" t="n">
-        <v>345000000</v>
+        <v>26121000000</v>
       </c>
       <c r="K147" t="n">
-        <v>9506000000</v>
+        <v>19903000000</v>
       </c>
       <c r="L147" t="n">
-        <v>152472000000</v>
+        <v>100075000000</v>
       </c>
       <c r="M147" t="n">
-        <v>88663000000</v>
+        <v>60492000000</v>
       </c>
       <c r="N147" t="n">
-        <v>1194366094160</v>
+        <v>138317600840</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>三井松島ホールディングス株式会社</t>
+          <t>多木化学株式会社</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="D148" t="n">
-        <v>2289</v>
+        <v>5650</v>
       </c>
       <c r="E148" t="n">
-        <v>2920</v>
+        <v>4695.956053243186</v>
       </c>
       <c r="F148" t="n">
-        <v>-21.6</v>
+        <v>20.3</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>19413000000</v>
+        <v>6433000000</v>
       </c>
       <c r="J148" t="n">
-        <v>3540000000</v>
+        <v>7985000000</v>
       </c>
       <c r="K148" t="n">
-        <v>10945000000</v>
+        <v>199000000</v>
       </c>
       <c r="L148" t="n">
-        <v>35537000000</v>
+        <v>29378000000</v>
       </c>
       <c r="M148" t="n">
-        <v>33898000000</v>
+        <v>14617000000</v>
       </c>
       <c r="N148" t="n">
-        <v>84757000440</v>
+        <v>47162634850</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ノリタケ株式会社</t>
+          <t>エムスリー株式会社</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>38.9</v>
+        <v>7.8</v>
       </c>
       <c r="D149" t="n">
-        <v>3500</v>
+        <v>1703.5</v>
       </c>
       <c r="E149" t="n">
-        <v>3573.410502159827</v>
+        <v>1638.585693292194</v>
       </c>
       <c r="F149" t="n">
-        <v>-2.1</v>
+        <v>4</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>11733000000</v>
+        <v>78812000000</v>
       </c>
       <c r="J149" t="n">
-        <v>20204000000</v>
+        <v>345000000</v>
       </c>
       <c r="K149" t="n">
-        <v>42879000000</v>
+        <v>9506000000</v>
       </c>
       <c r="L149" t="n">
-        <v>118800000000</v>
+        <v>152472000000</v>
       </c>
       <c r="M149" t="n">
-        <v>74816000000</v>
+        <v>88663000000</v>
       </c>
       <c r="N149" t="n">
-        <v>192549959000</v>
+        <v>1136967108914</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>株式会社ＡＣＳＬ</t>
+          <t>三井松島ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>7.4</v>
+        <v>39.8</v>
       </c>
       <c r="D150" t="n">
-        <v>1450</v>
+        <v>2301</v>
       </c>
       <c r="E150" t="n">
-        <v>913.2768512341561</v>
+        <v>2920</v>
       </c>
       <c r="F150" t="n">
-        <v>58.8</v>
+        <v>-21.2</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1891731000</v>
+        <v>19413000000</v>
       </c>
       <c r="J150" t="n">
-        <v>3724000</v>
+        <v>3540000000</v>
       </c>
       <c r="K150" t="n">
-        <v>197577000</v>
+        <v>10945000000</v>
       </c>
       <c r="L150" t="n">
-        <v>3572642000</v>
+        <v>35537000000</v>
       </c>
       <c r="M150" t="n">
-        <v>2093032000</v>
+        <v>33898000000</v>
       </c>
       <c r="N150" t="n">
-        <v>28379750900</v>
+        <v>85201335960</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>株式会社スズケン</t>
+          <t>ノリタケ株式会社</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>9987</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>78.09999999999999</v>
+        <v>38</v>
       </c>
       <c r="D151" t="n">
-        <v>5162</v>
+        <v>3580</v>
       </c>
       <c r="E151" t="n">
-        <v>4137.137750115735</v>
+        <v>3573.410502159827</v>
       </c>
       <c r="F151" t="n">
-        <v>24.8</v>
+        <v>0.2</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>168215000000</v>
+        <v>11733000000</v>
       </c>
       <c r="J151" t="n">
-        <v>65453000000</v>
+        <v>20204000000</v>
       </c>
       <c r="K151" t="n">
-        <v>38927000000</v>
+        <v>42879000000</v>
       </c>
       <c r="L151" t="n">
-        <v>418062000000</v>
+        <v>118800000000</v>
       </c>
       <c r="M151" t="n">
-        <v>272595000000</v>
+        <v>74816000000</v>
       </c>
       <c r="N151" t="n">
-        <v>349146555890</v>
+        <v>196951100920</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
+          <t>株式会社ＡＣＳＬ</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>6232</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="D152" t="n">
+        <v>1464</v>
+      </c>
+      <c r="E152" t="n">
+        <v>913.2768512341561</v>
+      </c>
+      <c r="F152" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>1891731000</v>
+      </c>
+      <c r="J152" t="n">
+        <v>3724000</v>
+      </c>
+      <c r="K152" t="n">
+        <v>197577000</v>
+      </c>
+      <c r="L152" t="n">
+        <v>3572642000</v>
+      </c>
+      <c r="M152" t="n">
+        <v>2093032000</v>
+      </c>
+      <c r="N152" t="n">
+        <v>28653762288</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>株式会社スズケン</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="D153" t="n">
+        <v>5122</v>
+      </c>
+      <c r="E153" t="n">
+        <v>4137.137750115735</v>
+      </c>
+      <c r="F153" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
+        <v>168215000000</v>
+      </c>
+      <c r="J153" t="n">
+        <v>65453000000</v>
+      </c>
+      <c r="K153" t="n">
+        <v>38927000000</v>
+      </c>
+      <c r="L153" t="n">
+        <v>418062000000</v>
+      </c>
+      <c r="M153" t="n">
+        <v>272595000000</v>
+      </c>
+      <c r="N153" t="n">
+        <v>346441042090</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
           <t>フォスター電機株式会社</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
+      <c r="B154" t="inlineStr">
         <is>
           <t>6794</t>
         </is>
       </c>
-      <c r="C152" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="D152" t="n">
-        <v>3025</v>
-      </c>
-      <c r="E152" t="n">
+      <c r="C154" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="D154" t="n">
+        <v>3035</v>
+      </c>
+      <c r="E154" t="n">
         <v>2681.96152003832</v>
       </c>
-      <c r="F152" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="G152" t="inlineStr">
+      <c r="F154" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="G154" t="inlineStr">
         <is>
           <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
+      <c r="H154" t="inlineStr">
         <is>
           <t>2026-01-22</t>
         </is>
       </c>
-      <c r="I152" t="n">
+      <c r="I154" t="n">
         <v>12089000000</v>
       </c>
-      <c r="J152" t="n">
+      <c r="J154" t="n">
         <v>7327000000</v>
       </c>
-      <c r="K152" t="n">
+      <c r="K154" t="n">
         <v>1115000000</v>
       </c>
-      <c r="L152" t="n">
+      <c r="L154" t="n">
         <v>51632000000</v>
       </c>
-      <c r="M152" t="n">
+      <c r="M154" t="n">
         <v>20531000000</v>
       </c>
-      <c r="N152" t="n">
-        <v>67965116175</v>
+      <c r="N154" t="n">
+        <v>68189794245</v>
       </c>
     </row>
   </sheetData>

--- a/docs/アクティビスト銘柄_資産判定.xlsx
+++ b/docs/アクティビスト銘柄_資産判定.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N154"/>
+  <dimension ref="A1:N156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>45.8</v>
+        <v>45.7</v>
       </c>
       <c r="D2" t="n">
-        <v>1299</v>
+        <v>1301.5</v>
       </c>
       <c r="E2" t="n">
         <v>1111.251693601708</v>
       </c>
       <c r="F2" t="n">
-        <v>16.9</v>
+        <v>17.1</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -537,7 +537,7 @@
         <v>213563000000</v>
       </c>
       <c r="N2" t="n">
-        <v>466382619960</v>
+        <v>467280200060</v>
       </c>
     </row>
     <row r="3">
@@ -552,16 +552,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>53.3</v>
+        <v>55.7</v>
       </c>
       <c r="D3" t="n">
-        <v>1193</v>
+        <v>1142</v>
       </c>
       <c r="E3" t="n">
         <v>1019.677694332945</v>
       </c>
       <c r="F3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         <v>106991000000</v>
       </c>
       <c r="N3" t="n">
-        <v>200722906150</v>
+        <v>192142128100</v>
       </c>
     </row>
     <row r="4">
@@ -607,13 +607,13 @@
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>3455</v>
+        <v>3443</v>
       </c>
       <c r="E4" t="n">
         <v>6116.356643776557</v>
       </c>
       <c r="F4" t="n">
-        <v>-43.5</v>
+        <v>-43.7</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         <v>219041000000</v>
       </c>
       <c r="N4" t="n">
-        <v>3125938869270</v>
+        <v>3115081773342</v>
       </c>
     </row>
     <row r="5">
@@ -656,16 +656,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>32</v>
+        <v>31.3</v>
       </c>
       <c r="D5" t="n">
-        <v>2102</v>
+        <v>2150</v>
       </c>
       <c r="E5" t="n">
         <v>1815.198567455447</v>
       </c>
       <c r="F5" t="n">
-        <v>15.8</v>
+        <v>18.4</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         <v>168499000000</v>
       </c>
       <c r="N5" t="n">
-        <v>526797463704</v>
+        <v>538827091800</v>
       </c>
     </row>
     <row r="6">
@@ -708,16 +708,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>52.6</v>
+        <v>53.9</v>
       </c>
       <c r="D6" t="n">
-        <v>11080</v>
+        <v>10820</v>
       </c>
       <c r="E6" t="n">
         <v>5684.0003469471</v>
       </c>
       <c r="F6" t="n">
-        <v>94.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>91895000000</v>
       </c>
       <c r="N6" t="n">
-        <v>174621431560</v>
+        <v>170523816740</v>
       </c>
     </row>
     <row r="7">
@@ -760,16 +760,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>52.6</v>
+        <v>53.9</v>
       </c>
       <c r="D7" t="n">
-        <v>11080</v>
+        <v>10820</v>
       </c>
       <c r="E7" t="n">
         <v>4549.503641591014</v>
       </c>
       <c r="F7" t="n">
-        <v>143.5</v>
+        <v>137.8</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>91895000000</v>
       </c>
       <c r="N7" t="n">
-        <v>174621431560</v>
+        <v>170523816740</v>
       </c>
     </row>
     <row r="8">
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13.7</v>
+        <v>14.8</v>
       </c>
       <c r="D8" t="n">
-        <v>4070</v>
+        <v>3770</v>
       </c>
       <c r="E8" t="n">
         <v>1361.432492253209</v>
       </c>
       <c r="F8" t="n">
-        <v>198.9</v>
+        <v>176.9</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>12397436000</v>
       </c>
       <c r="N8" t="n">
-        <v>90284008210</v>
+        <v>83629167310</v>
       </c>
     </row>
     <row r="9">
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>30.7</v>
+        <v>30.4</v>
       </c>
       <c r="D9" t="n">
-        <v>3255</v>
+        <v>3290</v>
       </c>
       <c r="E9" t="n">
         <v>13739.64575539568</v>
       </c>
       <c r="F9" t="n">
-        <v>-76.3</v>
+        <v>-76.09999999999999</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>325393000000</v>
       </c>
       <c r="N9" t="n">
-        <v>1060050414150</v>
+        <v>1071659201200</v>
       </c>
     </row>
     <row r="10">
@@ -916,16 +916,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>41.7</v>
+        <v>45.8</v>
       </c>
       <c r="D10" t="n">
-        <v>2319</v>
+        <v>2108.5</v>
       </c>
       <c r="E10" t="n">
         <v>1198.150742177053</v>
       </c>
       <c r="F10" t="n">
-        <v>93.5</v>
+        <v>76</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>213966000000</v>
       </c>
       <c r="N10" t="n">
-        <v>513458465379</v>
+        <v>466850872898</v>
       </c>
     </row>
     <row r="11">
@@ -968,16 +968,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>41.7</v>
+        <v>45.8</v>
       </c>
       <c r="D11" t="n">
-        <v>2319</v>
+        <v>2108.5</v>
       </c>
       <c r="E11" t="n">
         <v>1188.162962482466</v>
       </c>
       <c r="F11" t="n">
-        <v>95.2</v>
+        <v>77.5</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>213966000000</v>
       </c>
       <c r="N11" t="n">
-        <v>513458465379</v>
+        <v>466850872898</v>
       </c>
     </row>
     <row r="12">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24.6</v>
+        <v>24.4</v>
       </c>
       <c r="D12" t="n">
-        <v>3591</v>
+        <v>3621</v>
       </c>
       <c r="E12" t="n">
         <v>2995.424821743842</v>
       </c>
       <c r="F12" t="n">
-        <v>19.9</v>
+        <v>20.9</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>129979000000</v>
       </c>
       <c r="N12" t="n">
-        <v>527753771244</v>
+        <v>532162741764</v>
       </c>
     </row>
     <row r="13">
@@ -1072,16 +1072,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>72.40000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="D13" t="n">
-        <v>4939</v>
+        <v>4820</v>
       </c>
       <c r="E13" t="n">
         <v>4991.027246539169</v>
       </c>
       <c r="F13" t="n">
-        <v>-1</v>
+        <v>-3.4</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>1007966000000</v>
       </c>
       <c r="N13" t="n">
-        <v>1391547178494</v>
+        <v>1358019315720</v>
       </c>
     </row>
     <row r="14">
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>19.6</v>
+        <v>20.2</v>
       </c>
       <c r="D14" t="n">
-        <v>1874.5</v>
+        <v>1816</v>
       </c>
       <c r="E14" t="n">
         <v>1512.21980974841</v>
       </c>
       <c r="F14" t="n">
-        <v>24</v>
+        <v>20.1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>120816000000</v>
       </c>
       <c r="N14" t="n">
-        <v>617491722244</v>
+        <v>598220841608</v>
       </c>
     </row>
     <row r="15">
@@ -1176,16 +1176,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="D15" t="n">
-        <v>2694</v>
+        <v>2614.5</v>
       </c>
       <c r="E15" t="n">
         <v>1827.011042553346</v>
       </c>
       <c r="F15" t="n">
-        <v>47.5</v>
+        <v>43.1</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>48336000000</v>
       </c>
       <c r="N15" t="n">
-        <v>662477402016</v>
+        <v>642927679128</v>
       </c>
     </row>
     <row r="16">
@@ -1228,16 +1228,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>134.2</v>
+        <v>134.8</v>
       </c>
       <c r="D16" t="n">
-        <v>1603</v>
+        <v>1596</v>
       </c>
       <c r="E16" t="n">
         <v>2122.579027791042</v>
       </c>
       <c r="F16" t="n">
-        <v>-24.5</v>
+        <v>-24.8</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>80333000000</v>
       </c>
       <c r="N16" t="n">
-        <v>59875940481</v>
+        <v>59614473492</v>
       </c>
     </row>
     <row r="17">
@@ -1332,16 +1332,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="D18" t="n">
-        <v>3649</v>
+        <v>3445</v>
       </c>
       <c r="E18" t="n">
         <v>1572.181660925393</v>
       </c>
       <c r="F18" t="n">
-        <v>132.1</v>
+        <v>119.1</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>35501000000</v>
       </c>
       <c r="N18" t="n">
-        <v>651576594993</v>
+        <v>615149731365</v>
       </c>
     </row>
     <row r="19">
@@ -1384,16 +1384,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="D19" t="n">
-        <v>3649</v>
+        <v>3445</v>
       </c>
       <c r="E19" t="n">
         <v>1141.512891683109</v>
       </c>
       <c r="F19" t="n">
-        <v>219.7</v>
+        <v>201.8</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>35501000000</v>
       </c>
       <c r="N19" t="n">
-        <v>651576594993</v>
+        <v>615149731365</v>
       </c>
     </row>
     <row r="20">
@@ -1436,16 +1436,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>44.6</v>
+        <v>45</v>
       </c>
       <c r="D20" t="n">
-        <v>6025</v>
+        <v>5977</v>
       </c>
       <c r="E20" t="n">
         <v>2836.942753814942</v>
       </c>
       <c r="F20" t="n">
-        <v>112.4</v>
+        <v>110.7</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>94351000000</v>
       </c>
       <c r="N20" t="n">
-        <v>211585474025</v>
+        <v>209899813817</v>
       </c>
     </row>
     <row r="21">
@@ -1488,16 +1488,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>54.9</v>
+        <v>57.3</v>
       </c>
       <c r="D21" t="n">
-        <v>4091</v>
+        <v>3921</v>
       </c>
       <c r="E21" t="n">
         <v>2863.970160821546</v>
       </c>
       <c r="F21" t="n">
-        <v>42.8</v>
+        <v>36.9</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>161529000000</v>
       </c>
       <c r="N21" t="n">
-        <v>294327661833</v>
+        <v>282096984123</v>
       </c>
     </row>
     <row r="22">
@@ -1540,16 +1540,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>50.1</v>
+        <v>53.1</v>
       </c>
       <c r="D22" t="n">
-        <v>4881</v>
+        <v>4608</v>
       </c>
       <c r="E22" t="n">
         <v>2566.284807227078</v>
       </c>
       <c r="F22" t="n">
-        <v>90.2</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>231575000000</v>
       </c>
       <c r="N22" t="n">
-        <v>462294660624</v>
+        <v>436437983232</v>
       </c>
     </row>
     <row r="23">
@@ -1595,13 +1595,13 @@
         <v>28.9</v>
       </c>
       <c r="D23" t="n">
-        <v>5120</v>
+        <v>5112</v>
       </c>
       <c r="E23" t="n">
         <v>2779.139169918938</v>
       </c>
       <c r="F23" t="n">
-        <v>84.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>183216000000</v>
       </c>
       <c r="N23" t="n">
-        <v>635046251520</v>
+        <v>634053991752</v>
       </c>
     </row>
     <row r="24">
@@ -1644,16 +1644,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="D24" t="n">
-        <v>4125</v>
+        <v>4072</v>
       </c>
       <c r="E24" t="n">
         <v>2420.370957920882</v>
       </c>
       <c r="F24" t="n">
-        <v>70.40000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>18167000000</v>
       </c>
       <c r="N24" t="n">
-        <v>203927950875</v>
+        <v>201307785688</v>
       </c>
     </row>
     <row r="25">
@@ -1696,16 +1696,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="D25" t="n">
-        <v>1794.5</v>
+        <v>1766.5</v>
       </c>
       <c r="E25" t="n">
         <v>1344.518957928979</v>
       </c>
       <c r="F25" t="n">
-        <v>33.5</v>
+        <v>31.4</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>45956000000</v>
       </c>
       <c r="N25" t="n">
-        <v>577391596008</v>
+        <v>568382420924</v>
       </c>
     </row>
     <row r="26">
@@ -1748,16 +1748,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>59.6</v>
+        <v>58.9</v>
       </c>
       <c r="D26" t="n">
-        <v>5021</v>
+        <v>5081</v>
       </c>
       <c r="E26" t="n">
         <v>4154.626869982095</v>
       </c>
       <c r="F26" t="n">
-        <v>20.9</v>
+        <v>22.3</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>179086000000</v>
       </c>
       <c r="N26" t="n">
-        <v>300259194196</v>
+        <v>303847234756</v>
       </c>
     </row>
     <row r="27">
@@ -1800,16 +1800,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="D27" t="n">
-        <v>3859</v>
+        <v>3831</v>
       </c>
       <c r="E27" t="n">
         <v>2561.705402476645</v>
       </c>
       <c r="F27" t="n">
-        <v>50.6</v>
+        <v>49.5</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>100104000000</v>
       </c>
       <c r="N27" t="n">
-        <v>706125241895</v>
+        <v>701001762555</v>
       </c>
     </row>
     <row r="28">
@@ -1852,16 +1852,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>42.1</v>
+        <v>44.8</v>
       </c>
       <c r="D28" t="n">
-        <v>3674</v>
+        <v>3449</v>
       </c>
       <c r="E28" t="n">
         <v>2560</v>
       </c>
       <c r="F28" t="n">
-        <v>43.5</v>
+        <v>34.7</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>190312000000</v>
       </c>
       <c r="N28" t="n">
-        <v>452307264244</v>
+        <v>424607445394</v>
       </c>
     </row>
     <row r="29">
@@ -1904,16 +1904,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>86.90000000000001</v>
+        <v>91</v>
       </c>
       <c r="D29" t="n">
-        <v>4425</v>
+        <v>4225</v>
       </c>
       <c r="E29" t="n">
         <v>3449.780346820809</v>
       </c>
       <c r="F29" t="n">
-        <v>28.3</v>
+        <v>22.5</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>90928000000</v>
       </c>
       <c r="N29" t="n">
-        <v>104638028100</v>
+        <v>99908625700</v>
       </c>
     </row>
     <row r="30">
@@ -1959,13 +1959,13 @@
         <v>61</v>
       </c>
       <c r="D30" t="n">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="E30" t="n">
         <v>1746.940387696806</v>
       </c>
       <c r="F30" t="n">
-        <v>-10.4</v>
+        <v>-10.5</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>36070000000</v>
       </c>
       <c r="N30" t="n">
-        <v>59165818038</v>
+        <v>59090255052</v>
       </c>
     </row>
     <row r="31">
@@ -2008,16 +2008,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>104.9</v>
+        <v>106.6</v>
       </c>
       <c r="D31" t="n">
-        <v>1690</v>
+        <v>1663</v>
       </c>
       <c r="E31" t="n">
         <v>2298.672482457804</v>
       </c>
       <c r="F31" t="n">
-        <v>-26.5</v>
+        <v>-27.7</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>42752000000</v>
       </c>
       <c r="N31" t="n">
-        <v>40748751030</v>
+        <v>40097735481</v>
       </c>
     </row>
     <row r="32">
@@ -2060,16 +2060,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>68.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="D32" t="n">
-        <v>2596</v>
+        <v>2539</v>
       </c>
       <c r="E32" t="n">
         <v>1270</v>
       </c>
       <c r="F32" t="n">
-        <v>104.4</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>31108000000</v>
       </c>
       <c r="N32" t="n">
-        <v>45138108356</v>
+        <v>44147017379</v>
       </c>
     </row>
     <row r="33">
@@ -2112,16 +2112,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>68.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="D33" t="n">
-        <v>2596</v>
+        <v>2539</v>
       </c>
       <c r="E33" t="n">
         <v>1170</v>
       </c>
       <c r="F33" t="n">
-        <v>121.9</v>
+        <v>117</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>31108000000</v>
       </c>
       <c r="N33" t="n">
-        <v>45138108356</v>
+        <v>44147017379</v>
       </c>
     </row>
     <row r="34">
@@ -2216,16 +2216,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>82.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>2509</v>
+        <v>2484</v>
       </c>
       <c r="E35" t="n">
         <v>2939.562915943684</v>
       </c>
       <c r="F35" t="n">
-        <v>-14.6</v>
+        <v>-15.5</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>108430000000</v>
       </c>
       <c r="N35" t="n">
-        <v>131388511956</v>
+        <v>130079339856</v>
       </c>
     </row>
     <row r="36">
@@ -2268,16 +2268,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="D36" t="n">
-        <v>13450</v>
+        <v>13420</v>
       </c>
       <c r="E36" t="n">
         <v>7040.15625</v>
       </c>
       <c r="F36" t="n">
-        <v>91</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>6799899000</v>
       </c>
       <c r="N36" t="n">
-        <v>14009076150</v>
+        <v>13977829140</v>
       </c>
     </row>
     <row r="37">
@@ -2320,16 +2320,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="D37" t="n">
-        <v>13450</v>
+        <v>13420</v>
       </c>
       <c r="E37" t="n">
         <v>7040.15625</v>
       </c>
       <c r="F37" t="n">
-        <v>91</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>6799899000</v>
       </c>
       <c r="N37" t="n">
-        <v>14009076150</v>
+        <v>13977829140</v>
       </c>
     </row>
     <row r="38">
@@ -2372,16 +2372,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>86.40000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="D38" t="n">
-        <v>2777</v>
+        <v>2782</v>
       </c>
       <c r="E38" t="n">
         <v>4265.455132343447</v>
       </c>
       <c r="F38" t="n">
-        <v>-34.9</v>
+        <v>-34.8</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>22869000000</v>
       </c>
       <c r="N38" t="n">
-        <v>26475412586</v>
+        <v>26523081676</v>
       </c>
     </row>
     <row r="39">
@@ -2424,16 +2424,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>31.9</v>
+        <v>33.1</v>
       </c>
       <c r="D39" t="n">
-        <v>4830</v>
+        <v>4655</v>
       </c>
       <c r="E39" t="n">
         <v>2824.318397803668</v>
       </c>
       <c r="F39" t="n">
-        <v>71</v>
+        <v>64.8</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>61975000000</v>
       </c>
       <c r="N39" t="n">
-        <v>194314063650</v>
+        <v>187273699025</v>
       </c>
     </row>
     <row r="40">
@@ -2476,16 +2476,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>28</v>
+        <v>29.4</v>
       </c>
       <c r="D40" t="n">
-        <v>6900</v>
+        <v>6570</v>
       </c>
       <c r="E40" t="n">
         <v>3096.322467304314</v>
       </c>
       <c r="F40" t="n">
-        <v>122.8</v>
+        <v>112.2</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>52961000000</v>
       </c>
       <c r="N40" t="n">
-        <v>189288873000</v>
+        <v>180235926900</v>
       </c>
     </row>
     <row r="41">
@@ -2528,16 +2528,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="D41" t="n">
-        <v>6163</v>
+        <v>6147</v>
       </c>
       <c r="E41" t="n">
         <v>3322.047887165483</v>
       </c>
       <c r="F41" t="n">
-        <v>85.5</v>
+        <v>85</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>492847000000</v>
       </c>
       <c r="N41" t="n">
-        <v>2024575994524</v>
+        <v>2019319915356</v>
       </c>
     </row>
     <row r="42">
@@ -2580,16 +2580,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>35</v>
+        <v>35.3</v>
       </c>
       <c r="D42" t="n">
-        <v>1757</v>
+        <v>1745</v>
       </c>
       <c r="E42" t="n">
         <v>2112.609181636727</v>
       </c>
       <c r="F42" t="n">
-        <v>-16.8</v>
+        <v>-17.4</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>52218000000</v>
       </c>
       <c r="N42" t="n">
-        <v>149130417590</v>
+        <v>148111883150</v>
       </c>
     </row>
     <row r="43">
@@ -2635,13 +2635,13 @@
         <v>3.8</v>
       </c>
       <c r="D43" t="n">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="E43" t="n">
         <v>404.9347366248775</v>
       </c>
       <c r="F43" t="n">
-        <v>72.90000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>7044972000</v>
       </c>
       <c r="N43" t="n">
-        <v>186610273500</v>
+        <v>187410031815</v>
       </c>
     </row>
     <row r="44">
@@ -2684,16 +2684,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="D44" t="n">
-        <v>2812</v>
+        <v>2722</v>
       </c>
       <c r="E44" t="n">
         <v>2220.184278344451</v>
       </c>
       <c r="F44" t="n">
-        <v>26.7</v>
+        <v>22.6</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>207116000000</v>
       </c>
       <c r="N44" t="n">
-        <v>3223423256020</v>
+        <v>3120255370870</v>
       </c>
     </row>
     <row r="45">
@@ -2736,16 +2736,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>19.9</v>
+        <v>21.1</v>
       </c>
       <c r="D45" t="n">
-        <v>22980</v>
+        <v>21610</v>
       </c>
       <c r="E45" t="n">
         <v>11879.91675437757</v>
       </c>
       <c r="F45" t="n">
-        <v>93.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>191958000000</v>
       </c>
       <c r="N45" t="n">
-        <v>965655333900</v>
+        <v>908085803550</v>
       </c>
     </row>
     <row r="46">
@@ -2788,16 +2788,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>75.8</v>
+        <v>77.8</v>
       </c>
       <c r="D46" t="n">
-        <v>1081</v>
+        <v>1053</v>
       </c>
       <c r="E46" t="n">
         <v>730</v>
       </c>
       <c r="F46" t="n">
-        <v>48.1</v>
+        <v>44.2</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>50027000000</v>
       </c>
       <c r="N46" t="n">
-        <v>65999575066</v>
+        <v>64290057858</v>
       </c>
     </row>
     <row r="47">
@@ -2840,16 +2840,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>23.2</v>
+        <v>24.2</v>
       </c>
       <c r="D47" t="n">
-        <v>5634</v>
+        <v>5399</v>
       </c>
       <c r="E47" t="n">
         <v>3341.42986565678</v>
       </c>
       <c r="F47" t="n">
-        <v>68.59999999999999</v>
+        <v>61.6</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>311107000000</v>
       </c>
       <c r="N47" t="n">
-        <v>1338773013162</v>
+        <v>1282931398307</v>
       </c>
     </row>
     <row r="48">
@@ -2892,16 +2892,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>28.4</v>
+        <v>29.3</v>
       </c>
       <c r="D48" t="n">
-        <v>3255</v>
+        <v>3150</v>
       </c>
       <c r="E48" t="n">
         <v>2550.198980592041</v>
       </c>
       <c r="F48" t="n">
-        <v>27.6</v>
+        <v>23.5</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>32342000000</v>
       </c>
       <c r="N48" t="n">
-        <v>113953045080</v>
+        <v>110277140400</v>
       </c>
     </row>
     <row r="49">
@@ -2944,16 +2944,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>214.1</v>
+        <v>216.3</v>
       </c>
       <c r="D49" t="n">
-        <v>1616.5</v>
+        <v>1600</v>
       </c>
       <c r="E49" t="n">
         <v>1288.711724885291</v>
       </c>
       <c r="F49" t="n">
-        <v>25.4</v>
+        <v>24.2</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>747066000000</v>
       </c>
       <c r="N49" t="n">
-        <v>348976765654</v>
+        <v>345414676800</v>
       </c>
     </row>
     <row r="50">
@@ -2996,16 +2996,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>67.2</v>
+        <v>67.7</v>
       </c>
       <c r="D50" t="n">
-        <v>4092</v>
+        <v>4062</v>
       </c>
       <c r="E50" t="n">
         <v>3141.424011416125</v>
       </c>
       <c r="F50" t="n">
-        <v>30.3</v>
+        <v>29.3</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>391579000000</v>
       </c>
       <c r="N50" t="n">
-        <v>583092011568</v>
+        <v>578817143448</v>
       </c>
     </row>
     <row r="51">
@@ -3048,16 +3048,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>67.2</v>
+        <v>67.7</v>
       </c>
       <c r="D51" t="n">
-        <v>4092</v>
+        <v>4062</v>
       </c>
       <c r="E51" t="n">
         <v>2420</v>
       </c>
       <c r="F51" t="n">
-        <v>69.09999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>391579000000</v>
       </c>
       <c r="N51" t="n">
-        <v>583092011568</v>
+        <v>578817143448</v>
       </c>
     </row>
     <row r="52">
@@ -3100,16 +3100,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>42</v>
+        <v>41.4</v>
       </c>
       <c r="D52" t="n">
-        <v>4072</v>
+        <v>4132</v>
       </c>
       <c r="E52" t="n">
         <v>3047.091476167608</v>
       </c>
       <c r="F52" t="n">
-        <v>33.6</v>
+        <v>35.6</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>162458000000</v>
       </c>
       <c r="N52" t="n">
-        <v>386689608824</v>
+        <v>392387392844</v>
       </c>
     </row>
     <row r="53">
@@ -3152,16 +3152,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>45.1</v>
+        <v>45.4</v>
       </c>
       <c r="D53" t="n">
-        <v>3514</v>
+        <v>3491</v>
       </c>
       <c r="E53" t="n">
         <v>2844.704547285864</v>
       </c>
       <c r="F53" t="n">
-        <v>23.5</v>
+        <v>22.7</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>218675000000</v>
       </c>
       <c r="N53" t="n">
-        <v>485176616568</v>
+        <v>482001015492</v>
       </c>
     </row>
     <row r="54">
@@ -3204,16 +3204,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>55.6</v>
+        <v>55.9</v>
       </c>
       <c r="D54" t="n">
-        <v>2232.5</v>
+        <v>2217</v>
       </c>
       <c r="E54" t="n">
         <v>1556.090471804319</v>
       </c>
       <c r="F54" t="n">
-        <v>43.5</v>
+        <v>42.5</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>207466000000</v>
       </c>
       <c r="N54" t="n">
-        <v>373399477662</v>
+        <v>370807006485</v>
       </c>
     </row>
     <row r="55">
@@ -3256,16 +3256,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>51.6</v>
+        <v>51</v>
       </c>
       <c r="D55" t="n">
-        <v>1639</v>
+        <v>1658</v>
       </c>
       <c r="E55" t="n">
         <v>1529.631984751819</v>
       </c>
       <c r="F55" t="n">
-        <v>7.1</v>
+        <v>8.4</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>6024082000</v>
       </c>
       <c r="N55" t="n">
-        <v>11681429991</v>
+        <v>11816846202</v>
       </c>
     </row>
     <row r="56">
@@ -3308,16 +3308,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>51.6</v>
+        <v>51</v>
       </c>
       <c r="D56" t="n">
-        <v>1639</v>
+        <v>1658</v>
       </c>
       <c r="E56" t="n">
         <v>1449.995380693296</v>
       </c>
       <c r="F56" t="n">
-        <v>13</v>
+        <v>14.3</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>6024082000</v>
       </c>
       <c r="N56" t="n">
-        <v>11681429991</v>
+        <v>11816846202</v>
       </c>
     </row>
     <row r="57">
@@ -3360,16 +3360,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>68.7</v>
+        <v>67.7</v>
       </c>
       <c r="D57" t="n">
-        <v>2910</v>
+        <v>2952</v>
       </c>
       <c r="E57" t="n">
         <v>2696.128808062088</v>
       </c>
       <c r="F57" t="n">
-        <v>7.9</v>
+        <v>9.5</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>165282000000</v>
       </c>
       <c r="N57" t="n">
-        <v>240553793940</v>
+        <v>244025704368</v>
       </c>
     </row>
     <row r="58">
@@ -3412,16 +3412,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>121.3</v>
+        <v>119.9</v>
       </c>
       <c r="D58" t="n">
-        <v>1543.5</v>
+        <v>1561.5</v>
       </c>
       <c r="E58" t="n">
         <v>1160.8</v>
       </c>
       <c r="F58" t="n">
-        <v>33</v>
+        <v>34.5</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>493483000000</v>
       </c>
       <c r="N58" t="n">
-        <v>406722253424</v>
+        <v>411465370082</v>
       </c>
     </row>
     <row r="59">
@@ -3464,16 +3464,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="D59" t="n">
-        <v>2981</v>
+        <v>2972</v>
       </c>
       <c r="E59" t="n">
         <v>2007.754513143541</v>
       </c>
       <c r="F59" t="n">
-        <v>48.5</v>
+        <v>48</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>37208000000</v>
       </c>
       <c r="N59" t="n">
-        <v>158806607311</v>
+        <v>158327150932</v>
       </c>
     </row>
     <row r="60">
@@ -3623,7 +3623,7 @@
         <v>9.6</v>
       </c>
       <c r="D62" t="n">
-        <v>2852</v>
+        <v>2853</v>
       </c>
       <c r="E62" t="n">
         <v>1910.426979628923</v>
@@ -3657,7 +3657,7 @@
         <v>53660000000</v>
       </c>
       <c r="N62" t="n">
-        <v>556653707944</v>
+        <v>556848888066</v>
       </c>
     </row>
     <row r="63">
@@ -3672,16 +3672,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>49.4</v>
+        <v>50.3</v>
       </c>
       <c r="D63" t="n">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="E63" t="n">
         <v>290.3401328717133</v>
       </c>
       <c r="F63" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>5162755000</v>
       </c>
       <c r="N63" t="n">
-        <v>10446457539</v>
+        <v>10272928344</v>
       </c>
     </row>
     <row r="64">
@@ -3812,16 +3812,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>92.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="D66" t="n">
-        <v>2612</v>
+        <v>2550</v>
       </c>
       <c r="E66" t="n">
         <v>1748.071046781136</v>
       </c>
       <c r="F66" t="n">
-        <v>49.4</v>
+        <v>45.9</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>72190000000</v>
       </c>
       <c r="N66" t="n">
-        <v>78147223868</v>
+        <v>76292274450</v>
       </c>
     </row>
     <row r="67">
@@ -3864,16 +3864,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>75.59999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="D67" t="n">
-        <v>2563</v>
+        <v>2610.5</v>
       </c>
       <c r="E67" t="n">
         <v>2551.08574256026</v>
       </c>
       <c r="F67" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>179136000000</v>
       </c>
       <c r="N67" t="n">
-        <v>237107335883</v>
+        <v>241501638830</v>
       </c>
     </row>
     <row r="68">
@@ -3916,16 +3916,16 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>75.59999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="D68" t="n">
-        <v>2563</v>
+        <v>2610.5</v>
       </c>
       <c r="E68" t="n">
         <v>2260</v>
       </c>
       <c r="F68" t="n">
-        <v>13.4</v>
+        <v>15.5</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>179136000000</v>
       </c>
       <c r="N68" t="n">
-        <v>237107335883</v>
+        <v>241501638830</v>
       </c>
     </row>
     <row r="69">
@@ -3968,16 +3968,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>75.59999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="D69" t="n">
-        <v>2563</v>
+        <v>2610.5</v>
       </c>
       <c r="E69" t="n">
         <v>2260</v>
       </c>
       <c r="F69" t="n">
-        <v>13.4</v>
+        <v>15.5</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>179136000000</v>
       </c>
       <c r="N69" t="n">
-        <v>237107335883</v>
+        <v>241501638830</v>
       </c>
     </row>
     <row r="70">
@@ -4020,16 +4020,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>307.5</v>
+        <v>309.7</v>
       </c>
       <c r="D70" t="n">
-        <v>853</v>
+        <v>847</v>
       </c>
       <c r="E70" t="n">
         <v>798.3805136422309</v>
       </c>
       <c r="F70" t="n">
-        <v>6.8</v>
+        <v>6.1</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>449038000000</v>
       </c>
       <c r="N70" t="n">
-        <v>146021541992</v>
+        <v>144994426808</v>
       </c>
     </row>
     <row r="71">
@@ -4072,16 +4072,16 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>41.9</v>
+        <v>43.2</v>
       </c>
       <c r="D71" t="n">
-        <v>2639.5</v>
+        <v>2562.5</v>
       </c>
       <c r="E71" t="n">
         <v>2032.365850102071</v>
       </c>
       <c r="F71" t="n">
-        <v>29.9</v>
+        <v>26.1</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>340592000000</v>
       </c>
       <c r="N71" t="n">
-        <v>812677096167</v>
+        <v>788969524125</v>
       </c>
     </row>
     <row r="72">
@@ -4124,16 +4124,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>63</v>
+        <v>61.8</v>
       </c>
       <c r="D72" t="n">
-        <v>3531</v>
+        <v>3600</v>
       </c>
       <c r="E72" t="n">
         <v>1716.713876475349</v>
       </c>
       <c r="F72" t="n">
-        <v>105.7</v>
+        <v>109.7</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>565345000000</v>
       </c>
       <c r="N72" t="n">
-        <v>897501769428</v>
+        <v>915040036800</v>
       </c>
     </row>
     <row r="73">
@@ -4177,16 +4177,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>29.8</v>
+        <v>31.5</v>
       </c>
       <c r="D73" t="n">
-        <v>9640</v>
+        <v>9130</v>
       </c>
       <c r="E73" t="n">
         <v>4037.502552255647</v>
       </c>
       <c r="F73" t="n">
-        <v>138.8</v>
+        <v>126.1</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>154738000000</v>
       </c>
       <c r="N73" t="n">
-        <v>518668275320</v>
+        <v>491228356190</v>
       </c>
     </row>
     <row r="74">
@@ -4230,16 +4230,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>29.8</v>
+        <v>31.5</v>
       </c>
       <c r="D74" t="n">
-        <v>9640</v>
+        <v>9130</v>
       </c>
       <c r="E74" t="n">
         <v>3950.736048458928</v>
       </c>
       <c r="F74" t="n">
-        <v>144</v>
+        <v>131.1</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>154738000000</v>
       </c>
       <c r="N74" t="n">
-        <v>518668275320</v>
+        <v>491228356190</v>
       </c>
     </row>
     <row r="75">
@@ -4283,16 +4283,16 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>29.8</v>
+        <v>31.5</v>
       </c>
       <c r="D75" t="n">
-        <v>9640</v>
+        <v>9130</v>
       </c>
       <c r="E75" t="n">
         <v>2030</v>
       </c>
       <c r="F75" t="n">
-        <v>374.9</v>
+        <v>349.8</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>154738000000</v>
       </c>
       <c r="N75" t="n">
-        <v>518668275320</v>
+        <v>491228356190</v>
       </c>
     </row>
     <row r="76">
@@ -4336,16 +4336,16 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>29.8</v>
+        <v>31.5</v>
       </c>
       <c r="D76" t="n">
-        <v>9640</v>
+        <v>9130</v>
       </c>
       <c r="E76" t="n">
         <v>2387</v>
       </c>
       <c r="F76" t="n">
-        <v>303.9</v>
+        <v>282.5</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>154738000000</v>
       </c>
       <c r="N76" t="n">
-        <v>518668275320</v>
+        <v>491228356190</v>
       </c>
     </row>
     <row r="77">
@@ -4391,13 +4391,13 @@
         <v>78</v>
       </c>
       <c r="D77" t="n">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="E77" t="n">
         <v>668.9358717434869</v>
       </c>
       <c r="F77" t="n">
-        <v>48.6</v>
+        <v>48.4</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>12410000000</v>
       </c>
       <c r="N77" t="n">
-        <v>15917921964</v>
+        <v>15901907958</v>
       </c>
     </row>
     <row r="78">
@@ -4440,16 +4440,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>71</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D78" t="n">
-        <v>2679</v>
+        <v>2640</v>
       </c>
       <c r="E78" t="n">
         <v>1190</v>
       </c>
       <c r="F78" t="n">
-        <v>125.1</v>
+        <v>121.8</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>40500000000</v>
       </c>
       <c r="N78" t="n">
-        <v>57040858113</v>
+        <v>56210476080</v>
       </c>
     </row>
     <row r="79">
@@ -4492,16 +4492,16 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>18.4</v>
+        <v>18.9</v>
       </c>
       <c r="D79" t="n">
-        <v>6090</v>
+        <v>5910</v>
       </c>
       <c r="E79" t="n">
         <v>2617.980935875217</v>
       </c>
       <c r="F79" t="n">
-        <v>132.6</v>
+        <v>125.7</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>40238000000</v>
       </c>
       <c r="N79" t="n">
-        <v>219017775900</v>
+        <v>212544344100</v>
       </c>
     </row>
     <row r="80">
@@ -4544,16 +4544,16 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>19.4</v>
+        <v>20.5</v>
       </c>
       <c r="D80" t="n">
-        <v>2898</v>
+        <v>2750</v>
       </c>
       <c r="E80" t="n">
         <v>2084.177692465894</v>
       </c>
       <c r="F80" t="n">
-        <v>39</v>
+        <v>31.9</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         <v>15433000000</v>
       </c>
       <c r="N80" t="n">
-        <v>79368456258</v>
+        <v>75315132750</v>
       </c>
     </row>
     <row r="81">
@@ -4596,16 +4596,16 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>13</v>
+        <v>13.3</v>
       </c>
       <c r="D81" t="n">
-        <v>525</v>
+        <v>514</v>
       </c>
       <c r="E81" t="n">
         <v>448.6811097117532</v>
       </c>
       <c r="F81" t="n">
-        <v>17</v>
+        <v>14.6</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>13953300000</v>
       </c>
       <c r="N81" t="n">
-        <v>107238960150</v>
+        <v>104992048604</v>
       </c>
     </row>
     <row r="82">
@@ -4648,16 +4648,16 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>33.4</v>
+        <v>34.5</v>
       </c>
       <c r="D82" t="n">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="E82" t="n">
         <v>421.6950726175476</v>
       </c>
       <c r="F82" t="n">
-        <v>-21.3</v>
+        <v>-23.9</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>3109655000</v>
       </c>
       <c r="N82" t="n">
-        <v>9310139216</v>
+        <v>9001670748</v>
       </c>
     </row>
     <row r="83">
@@ -4700,16 +4700,16 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>72</v>
+        <v>71.8</v>
       </c>
       <c r="D83" t="n">
-        <v>3895</v>
+        <v>3905</v>
       </c>
       <c r="E83" t="n">
         <v>3530</v>
       </c>
       <c r="F83" t="n">
-        <v>10.3</v>
+        <v>10.6</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>106147000000</v>
       </c>
       <c r="N83" t="n">
-        <v>147497086925</v>
+        <v>147875770075</v>
       </c>
     </row>
     <row r="84">
@@ -4752,16 +4752,16 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>33.2</v>
+        <v>35.3</v>
       </c>
       <c r="D84" t="n">
-        <v>597</v>
+        <v>563</v>
       </c>
       <c r="E84" t="n">
         <v>549.4799823005444</v>
       </c>
       <c r="F84" t="n">
-        <v>8.6</v>
+        <v>2.5</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>19115000000</v>
       </c>
       <c r="N84" t="n">
-        <v>57493732770</v>
+        <v>54219382830</v>
       </c>
     </row>
     <row r="85">
@@ -4804,16 +4804,16 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>45.6</v>
+        <v>46.3</v>
       </c>
       <c r="D85" t="n">
-        <v>1725</v>
+        <v>1699</v>
       </c>
       <c r="E85" t="n">
         <v>1752.426893379333</v>
       </c>
       <c r="F85" t="n">
-        <v>-1.6</v>
+        <v>-3</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>76232495000</v>
       </c>
       <c r="N85" t="n">
-        <v>167335522500</v>
+        <v>164813363900</v>
       </c>
     </row>
     <row r="86">
@@ -4856,16 +4856,16 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>45.6</v>
+        <v>46.3</v>
       </c>
       <c r="D86" t="n">
-        <v>1725</v>
+        <v>1699</v>
       </c>
       <c r="E86" t="n">
         <v>1576.721867844292</v>
       </c>
       <c r="F86" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>76232495000</v>
       </c>
       <c r="N86" t="n">
-        <v>167335522500</v>
+        <v>164813363900</v>
       </c>
     </row>
     <row r="87">
@@ -4908,16 +4908,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>62.9</v>
+        <v>64.8</v>
       </c>
       <c r="D87" t="n">
-        <v>2181</v>
+        <v>2117</v>
       </c>
       <c r="E87" t="n">
         <v>1101.400153022188</v>
       </c>
       <c r="F87" t="n">
-        <v>98</v>
+        <v>92.2</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>402053000000</v>
       </c>
       <c r="N87" t="n">
-        <v>639064406400</v>
+        <v>620311484800</v>
       </c>
     </row>
     <row r="88">
@@ -4960,16 +4960,16 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>62.9</v>
+        <v>64.8</v>
       </c>
       <c r="D88" t="n">
-        <v>2181</v>
+        <v>2117</v>
       </c>
       <c r="E88" t="n">
         <v>1101.400153022188</v>
       </c>
       <c r="F88" t="n">
-        <v>98</v>
+        <v>92.2</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>402053000000</v>
       </c>
       <c r="N88" t="n">
-        <v>639064406400</v>
+        <v>620311484800</v>
       </c>
     </row>
     <row r="89">
@@ -5012,16 +5012,16 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>44.6</v>
+        <v>44.9</v>
       </c>
       <c r="D89" t="n">
-        <v>3363</v>
+        <v>3342</v>
       </c>
       <c r="E89" t="n">
         <v>1492.806001579363</v>
       </c>
       <c r="F89" t="n">
-        <v>125.3</v>
+        <v>123.9</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>112301000000</v>
       </c>
       <c r="N89" t="n">
-        <v>251566810455</v>
+        <v>249995920470</v>
       </c>
     </row>
     <row r="90">
@@ -5064,16 +5064,16 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>82</v>
+        <v>81.5</v>
       </c>
       <c r="D90" t="n">
-        <v>1107</v>
+        <v>1115</v>
       </c>
       <c r="E90" t="n">
         <v>1341.977644710579</v>
       </c>
       <c r="F90" t="n">
-        <v>-17.5</v>
+        <v>-16.9</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>86654000000</v>
       </c>
       <c r="N90" t="n">
-        <v>105612960834</v>
+        <v>106376198130</v>
       </c>
     </row>
     <row r="91">
@@ -5116,16 +5116,16 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>24.2</v>
+        <v>25.9</v>
       </c>
       <c r="D91" t="n">
-        <v>4340</v>
+        <v>4100</v>
       </c>
       <c r="E91" t="n">
         <v>2006.059650428343</v>
       </c>
       <c r="F91" t="n">
-        <v>116.3</v>
+        <v>104.4</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>173440000000</v>
       </c>
       <c r="N91" t="n">
-        <v>717056466560</v>
+        <v>669040529700</v>
       </c>
     </row>
     <row r="92">
@@ -5171,13 +5171,13 @@
         <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>1851</v>
+        <v>1876</v>
       </c>
       <c r="E92" t="n">
         <v>2697.360927565142</v>
       </c>
       <c r="F92" t="n">
-        <v>-31.4</v>
+        <v>-30.5</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
         <v>7339000000</v>
       </c>
       <c r="N92" t="n">
-        <v>721840004490</v>
+        <v>731589329240</v>
       </c>
     </row>
     <row r="93">
@@ -5220,16 +5220,16 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>17.4</v>
+        <v>17.7</v>
       </c>
       <c r="D93" t="n">
-        <v>4495</v>
+        <v>4410</v>
       </c>
       <c r="E93" t="n">
         <v>7960</v>
       </c>
       <c r="F93" t="n">
-        <v>-43.5</v>
+        <v>-44.6</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -5257,7 +5257,7 @@
         <v>29865000000</v>
       </c>
       <c r="N93" t="n">
-        <v>171803637730</v>
+        <v>168554848140</v>
       </c>
     </row>
     <row r="94">
@@ -5272,16 +5272,16 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="D94" t="n">
-        <v>5419</v>
+        <v>5459</v>
       </c>
       <c r="E94" t="n">
         <v>3735.709461270437</v>
       </c>
       <c r="F94" t="n">
-        <v>45.1</v>
+        <v>46.1</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>110688000000</v>
       </c>
       <c r="N94" t="n">
-        <v>622015205889</v>
+        <v>626606571129</v>
       </c>
     </row>
     <row r="95">
@@ -5324,16 +5324,16 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>29.5</v>
+        <v>29.9</v>
       </c>
       <c r="D95" t="n">
-        <v>2177</v>
+        <v>2151</v>
       </c>
       <c r="E95" t="n">
         <v>5463.67048346056</v>
       </c>
       <c r="F95" t="n">
-        <v>-60.2</v>
+        <v>-60.6</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v>11249000000</v>
       </c>
       <c r="N95" t="n">
-        <v>38079191430</v>
+        <v>37624410090</v>
       </c>
     </row>
     <row r="96">
@@ -5376,16 +5376,16 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>25.7</v>
+        <v>26.1</v>
       </c>
       <c r="D96" t="n">
-        <v>1419</v>
+        <v>1398</v>
       </c>
       <c r="E96" t="n">
         <v>3234.727863989046</v>
       </c>
       <c r="F96" t="n">
-        <v>-56.1</v>
+        <v>-56.8</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>52215000000</v>
       </c>
       <c r="N96" t="n">
-        <v>203271097260</v>
+        <v>200262856920</v>
       </c>
     </row>
     <row r="97">
@@ -5428,16 +5428,16 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>33.6</v>
+        <v>34.2</v>
       </c>
       <c r="D97" t="n">
-        <v>3265</v>
+        <v>3205</v>
       </c>
       <c r="E97" t="n">
         <v>3155.301177013616</v>
       </c>
       <c r="F97" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>70480000000</v>
       </c>
       <c r="N97" t="n">
-        <v>209765795470</v>
+        <v>205910987590</v>
       </c>
     </row>
     <row r="98">
@@ -5483,13 +5483,13 @@
         <v>5.8</v>
       </c>
       <c r="D98" t="n">
-        <v>3217</v>
+        <v>3213</v>
       </c>
       <c r="E98" t="n">
         <v>2655.311711736394</v>
       </c>
       <c r="F98" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>33115000000</v>
       </c>
       <c r="N98" t="n">
-        <v>570470626085</v>
+        <v>569761306065</v>
       </c>
     </row>
     <row r="99">
@@ -5532,16 +5532,16 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>39.9</v>
+        <v>40.4</v>
       </c>
       <c r="D99" t="n">
-        <v>925.2000122070312</v>
+        <v>912.9000244140625</v>
       </c>
       <c r="E99" t="n">
         <v>2157.626835069302</v>
       </c>
       <c r="F99" t="n">
-        <v>-57.1</v>
+        <v>-57.7</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>152963000000</v>
       </c>
       <c r="N99" t="n">
-        <v>383439958748</v>
+        <v>378342350934</v>
       </c>
     </row>
     <row r="100">
@@ -5584,16 +5584,16 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>96.8</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="D100" t="n">
-        <v>1186</v>
+        <v>1164</v>
       </c>
       <c r="E100" t="n">
         <v>810</v>
       </c>
       <c r="F100" t="n">
-        <v>46.4</v>
+        <v>43.7</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>50303000000</v>
       </c>
       <c r="N100" t="n">
-        <v>51956500294</v>
+        <v>50992720356</v>
       </c>
     </row>
     <row r="101">
@@ -5639,13 +5639,13 @@
         <v>10</v>
       </c>
       <c r="D101" t="n">
-        <v>2043</v>
+        <v>2037</v>
       </c>
       <c r="E101" t="n">
         <v>2300.974351689521</v>
       </c>
       <c r="F101" t="n">
-        <v>-11.2</v>
+        <v>-11.5</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         <v>8549173000</v>
       </c>
       <c r="N101" t="n">
-        <v>85715188650</v>
+        <v>85463455350</v>
       </c>
     </row>
     <row r="102">
@@ -5691,13 +5691,13 @@
         <v>39.6</v>
       </c>
       <c r="D102" t="n">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="E102" t="n">
-        <v>1180.450912709519</v>
+        <v>1180.431728045326</v>
       </c>
       <c r="F102" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="I102" t="n">
@@ -5725,7 +5725,7 @@
         <v>29529000000</v>
       </c>
       <c r="N102" t="n">
-        <v>74585018832</v>
+        <v>74492596256</v>
       </c>
     </row>
     <row r="103">
@@ -5743,13 +5743,13 @@
         <v>39.6</v>
       </c>
       <c r="D103" t="n">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="E103" t="n">
-        <v>1180.45745232471</v>
+        <v>1180.442269658324</v>
       </c>
       <c r="F103" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="I103" t="n">
@@ -5777,7 +5777,7 @@
         <v>29529000000</v>
       </c>
       <c r="N103" t="n">
-        <v>74585018832</v>
+        <v>74492596256</v>
       </c>
     </row>
     <row r="104">
@@ -5795,13 +5795,13 @@
         <v>39.6</v>
       </c>
       <c r="D104" t="n">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="E104" t="n">
-        <v>1180.463123164206</v>
+        <v>1180.450912709519</v>
       </c>
       <c r="F104" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="I104" t="n">
@@ -5829,7 +5829,7 @@
         <v>29529000000</v>
       </c>
       <c r="N104" t="n">
-        <v>74585018832</v>
+        <v>74492596256</v>
       </c>
     </row>
     <row r="105">
@@ -5847,13 +5847,13 @@
         <v>39.6</v>
       </c>
       <c r="D105" t="n">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="E105" t="n">
-        <v>1170.279952698077</v>
+        <v>1180.45745232471</v>
       </c>
       <c r="F105" t="n">
-        <v>37.9</v>
+        <v>36.6</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="I105" t="n">
@@ -5881,7 +5881,7 @@
         <v>29529000000</v>
       </c>
       <c r="N105" t="n">
-        <v>74585018832</v>
+        <v>74492596256</v>
       </c>
     </row>
     <row r="106">
@@ -5899,13 +5899,13 @@
         <v>39.6</v>
       </c>
       <c r="D106" t="n">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="E106" t="n">
-        <v>1169.924818603025</v>
+        <v>1180.463123164206</v>
       </c>
       <c r="F106" t="n">
-        <v>38</v>
+        <v>36.6</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="I106" t="n">
@@ -5933,7 +5933,7 @@
         <v>29529000000</v>
       </c>
       <c r="N106" t="n">
-        <v>74585018832</v>
+        <v>74492596256</v>
       </c>
     </row>
     <row r="107">
@@ -5951,13 +5951,13 @@
         <v>39.6</v>
       </c>
       <c r="D107" t="n">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="E107" t="n">
-        <v>1168.709522546084</v>
+        <v>1170.279952698077</v>
       </c>
       <c r="F107" t="n">
-        <v>38.1</v>
+        <v>37.7</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="I107" t="n">
@@ -5985,31 +5985,31 @@
         <v>29529000000</v>
       </c>
       <c r="N107" t="n">
-        <v>74585018832</v>
+        <v>74492596256</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>山洋電気株式会社</t>
+          <t>東亜道路工業株式会社</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>11.7</v>
+        <v>39.6</v>
       </c>
       <c r="D108" t="n">
-        <v>5320</v>
+        <v>1612</v>
       </c>
       <c r="E108" t="n">
-        <v>7052.737306843267</v>
+        <v>1169.924818603025</v>
       </c>
       <c r="F108" t="n">
-        <v>-24.6</v>
+        <v>37.8</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -6018,154 +6018,154 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>8317000000</v>
+        <v>11649000000</v>
       </c>
       <c r="J108" t="n">
-        <v>6048000000</v>
+        <v>13793000000</v>
       </c>
       <c r="K108" t="n">
-        <v>7673000000</v>
+        <v>4087000000</v>
       </c>
       <c r="L108" t="n">
-        <v>49734000000</v>
+        <v>50605000000</v>
       </c>
       <c r="M108" t="n">
-        <v>22038000000</v>
+        <v>29529000000</v>
       </c>
       <c r="N108" t="n">
-        <v>188940018120</v>
+        <v>74492596256</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ヘリオス テクノ ホールディング株式会社</t>
+          <t>東亜道路工業株式会社</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>53.2</v>
+        <v>39.6</v>
       </c>
       <c r="D109" t="n">
-        <v>992</v>
+        <v>1612</v>
       </c>
       <c r="E109" t="n">
-        <v>896.0103264198827</v>
+        <v>1168.709522546084</v>
       </c>
       <c r="F109" t="n">
-        <v>10.7</v>
+        <v>37.9</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>7851015000</v>
+        <v>11649000000</v>
       </c>
       <c r="J109" t="n">
-        <v>640317000</v>
+        <v>13793000000</v>
       </c>
       <c r="K109" t="n">
-        <v>1079200000</v>
+        <v>4087000000</v>
       </c>
       <c r="L109" t="n">
-        <v>13746774000</v>
+        <v>50605000000</v>
       </c>
       <c r="M109" t="n">
-        <v>9570532000</v>
+        <v>29529000000</v>
       </c>
       <c r="N109" t="n">
-        <v>18006453664</v>
+        <v>74492596256</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>シェアリングテクノロジー株式会社</t>
+          <t>山洋電気株式会社</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>11.9</v>
+        <v>12.2</v>
       </c>
       <c r="D110" t="n">
-        <v>1520</v>
+        <v>5070</v>
       </c>
       <c r="E110" t="n">
-        <v>653.0713101160862</v>
+        <v>7052.737306843267</v>
       </c>
       <c r="F110" t="n">
-        <v>132.7</v>
+        <v>-28.1</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>4016706000</v>
+        <v>8317000000</v>
       </c>
       <c r="J110" t="n">
-        <v>309745000</v>
+        <v>6048000000</v>
       </c>
       <c r="K110" t="n">
-        <v>0</v>
+        <v>7673000000</v>
       </c>
       <c r="L110" t="n">
-        <v>185001000</v>
+        <v>49734000000</v>
       </c>
       <c r="M110" t="n">
-        <v>4326451000</v>
+        <v>22038000000</v>
       </c>
       <c r="N110" t="n">
-        <v>36375528880</v>
+        <v>180061257870</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>栄研化学株式会社</t>
+          <t>ヘリオス テクノ ホールディング株式会社</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>30.5</v>
+        <v>53.7</v>
       </c>
       <c r="D111" t="n">
-        <v>2279</v>
+        <v>982</v>
       </c>
       <c r="E111" t="n">
-        <v>1947.225264702313</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="F111" t="n">
-        <v>17</v>
+        <v>9.6</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -6174,50 +6174,50 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>10900000000</v>
+        <v>7851015000</v>
       </c>
       <c r="J111" t="n">
-        <v>11585000000</v>
+        <v>640317000</v>
       </c>
       <c r="K111" t="n">
-        <v>408000000</v>
+        <v>1079200000</v>
       </c>
       <c r="L111" t="n">
-        <v>45803000000</v>
+        <v>13746774000</v>
       </c>
       <c r="M111" t="n">
-        <v>22893000000</v>
+        <v>9570532000</v>
       </c>
       <c r="N111" t="n">
-        <v>75128540867</v>
+        <v>17824936994</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>栄研化学株式会社</t>
+          <t>シェアリングテクノロジー株式会社</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>30.5</v>
+        <v>12.1</v>
       </c>
       <c r="D112" t="n">
-        <v>2279</v>
+        <v>1498</v>
       </c>
       <c r="E112" t="n">
-        <v>1678.083113259255</v>
+        <v>653.0713101160862</v>
       </c>
       <c r="F112" t="n">
-        <v>35.8</v>
+        <v>129.4</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -6226,154 +6226,154 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>10900000000</v>
+        <v>4016706000</v>
       </c>
       <c r="J112" t="n">
-        <v>11585000000</v>
+        <v>309745000</v>
       </c>
       <c r="K112" t="n">
-        <v>408000000</v>
+        <v>0</v>
       </c>
       <c r="L112" t="n">
-        <v>45803000000</v>
+        <v>185001000</v>
       </c>
       <c r="M112" t="n">
-        <v>22893000000</v>
+        <v>4326451000</v>
       </c>
       <c r="N112" t="n">
-        <v>75128540867</v>
+        <v>35849040962</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>株式会社ヤマダホールディングス</t>
+          <t>栄研化学株式会社</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>9831</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>59.6</v>
+        <v>30.7</v>
       </c>
       <c r="D113" t="n">
-        <v>699.7999877929688</v>
+        <v>2263</v>
       </c>
       <c r="E113" t="n">
-        <v>530</v>
+        <v>1947.225264702313</v>
       </c>
       <c r="F113" t="n">
-        <v>32</v>
+        <v>16.2</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>56470000000</v>
+        <v>10900000000</v>
       </c>
       <c r="J113" t="n">
-        <v>210733000000</v>
+        <v>11585000000</v>
       </c>
       <c r="K113" t="n">
-        <v>9997000000</v>
+        <v>408000000</v>
       </c>
       <c r="L113" t="n">
-        <v>676277000000</v>
+        <v>45803000000</v>
       </c>
       <c r="M113" t="n">
-        <v>277200000000</v>
+        <v>22893000000</v>
       </c>
       <c r="N113" t="n">
-        <v>465349799896</v>
+        <v>74601091699</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>日本化薬株式会社</t>
+          <t>栄研化学株式会社</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>35</v>
+        <v>30.7</v>
       </c>
       <c r="D114" t="n">
-        <v>2072.5</v>
+        <v>2263</v>
       </c>
       <c r="E114" t="n">
-        <v>1111.90611839092</v>
+        <v>1678.083113259255</v>
       </c>
       <c r="F114" t="n">
-        <v>86.40000000000001</v>
+        <v>34.9</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>52962000000</v>
+        <v>10900000000</v>
       </c>
       <c r="J114" t="n">
-        <v>48231000000</v>
+        <v>11585000000</v>
       </c>
       <c r="K114" t="n">
-        <v>4337000000</v>
+        <v>408000000</v>
       </c>
       <c r="L114" t="n">
-        <v>246425000000</v>
+        <v>45803000000</v>
       </c>
       <c r="M114" t="n">
-        <v>105530000000</v>
+        <v>22893000000</v>
       </c>
       <c r="N114" t="n">
-        <v>301283496942</v>
+        <v>74601091699</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>王子ホールディングス株式会社</t>
+          <t>株式会社ヤマダホールディングス</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>9831</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>41.5</v>
+        <v>60.2</v>
       </c>
       <c r="D115" t="n">
-        <v>873.9000244140625</v>
+        <v>693</v>
       </c>
       <c r="E115" t="n">
-        <v>590</v>
+        <v>530</v>
       </c>
       <c r="F115" t="n">
-        <v>48.1</v>
+        <v>30.8</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -6382,310 +6382,310 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>55474000000</v>
+        <v>56470000000</v>
       </c>
       <c r="J115" t="n">
-        <v>244732000000</v>
+        <v>210733000000</v>
       </c>
       <c r="K115" t="n">
-        <v>7434000000</v>
+        <v>9997000000</v>
       </c>
       <c r="L115" t="n">
-        <v>875470000000</v>
+        <v>676277000000</v>
       </c>
       <c r="M115" t="n">
-        <v>307640000000</v>
+        <v>277200000000</v>
       </c>
       <c r="N115" t="n">
-        <v>742145869386</v>
+        <v>460827975069</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>東邦ホールディングス株式会社</t>
+          <t>日本化薬株式会社</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>51.4</v>
+        <v>36.1</v>
       </c>
       <c r="D116" t="n">
-        <v>3944</v>
+        <v>2013</v>
       </c>
       <c r="E116" t="n">
-        <v>3405.914389596362</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="F116" t="n">
-        <v>15.8</v>
+        <v>81</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>90014000000</v>
+        <v>52962000000</v>
       </c>
       <c r="J116" t="n">
-        <v>34220000000</v>
+        <v>48231000000</v>
       </c>
       <c r="K116" t="n">
-        <v>7000000000</v>
+        <v>4337000000</v>
       </c>
       <c r="L116" t="n">
-        <v>241281000000</v>
+        <v>246425000000</v>
       </c>
       <c r="M116" t="n">
-        <v>131234000000</v>
+        <v>105530000000</v>
       </c>
       <c r="N116" t="n">
-        <v>255183201112</v>
+        <v>292633862169</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>東邦ホールディングス株式会社</t>
+          <t>王子ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>51.4</v>
+        <v>41.6</v>
       </c>
       <c r="D117" t="n">
-        <v>3944</v>
+        <v>870.2000122070312</v>
       </c>
       <c r="E117" t="n">
-        <v>2714.613787300615</v>
+        <v>590</v>
       </c>
       <c r="F117" t="n">
-        <v>45.3</v>
+        <v>47.5</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>90014000000</v>
+        <v>55474000000</v>
       </c>
       <c r="J117" t="n">
-        <v>34220000000</v>
+        <v>244732000000</v>
       </c>
       <c r="K117" t="n">
-        <v>7000000000</v>
+        <v>7434000000</v>
       </c>
       <c r="L117" t="n">
-        <v>241281000000</v>
+        <v>875470000000</v>
       </c>
       <c r="M117" t="n">
-        <v>131234000000</v>
+        <v>307640000000</v>
       </c>
       <c r="N117" t="n">
-        <v>255183201112</v>
+        <v>739003692135</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>株式会社アイネス</t>
+          <t>東邦ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>9742</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>34.5</v>
+        <v>50.9</v>
       </c>
       <c r="D118" t="n">
-        <v>2105</v>
+        <v>3987</v>
       </c>
       <c r="E118" t="n">
-        <v>1879.137815927515</v>
+        <v>3405.914389596362</v>
       </c>
       <c r="F118" t="n">
-        <v>12</v>
+        <v>17.1</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>9731000000</v>
+        <v>90014000000</v>
       </c>
       <c r="J118" t="n">
-        <v>5286000000</v>
+        <v>34220000000</v>
       </c>
       <c r="K118" t="n">
-        <v>100000000</v>
+        <v>7000000000</v>
       </c>
       <c r="L118" t="n">
-        <v>34620000000</v>
+        <v>241281000000</v>
       </c>
       <c r="M118" t="n">
-        <v>15117000000</v>
+        <v>131234000000</v>
       </c>
       <c r="N118" t="n">
-        <v>43831250935</v>
+        <v>257965370901</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>日本ゼオン株式会社</t>
+          <t>東邦ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>34.4</v>
+        <v>50.9</v>
       </c>
       <c r="D119" t="n">
-        <v>2447</v>
+        <v>3987</v>
       </c>
       <c r="E119" t="n">
-        <v>1721.078563209627</v>
+        <v>2714.613787300615</v>
       </c>
       <c r="F119" t="n">
-        <v>42.2</v>
+        <v>46.9</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>44521000000</v>
+        <v>90014000000</v>
       </c>
       <c r="J119" t="n">
-        <v>45382000000</v>
+        <v>34220000000</v>
       </c>
       <c r="K119" t="n">
-        <v>71191000000</v>
+        <v>7000000000</v>
       </c>
       <c r="L119" t="n">
-        <v>321836000000</v>
+        <v>241281000000</v>
       </c>
       <c r="M119" t="n">
-        <v>161094000000</v>
+        <v>131234000000</v>
       </c>
       <c r="N119" t="n">
-        <v>468222455629</v>
+        <v>257965370901</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>太陽ホールディングス株式会社</t>
+          <t>株式会社アイネス</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>9742</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>16.4</v>
+        <v>35.1</v>
       </c>
       <c r="D120" t="n">
-        <v>4722</v>
+        <v>2070</v>
       </c>
       <c r="E120" t="n">
-        <v>2199.643244598912</v>
+        <v>1879.137815927515</v>
       </c>
       <c r="F120" t="n">
-        <v>114.7</v>
+        <v>10.2</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>51152000000</v>
+        <v>9731000000</v>
       </c>
       <c r="J120" t="n">
-        <v>30337000000</v>
+        <v>5286000000</v>
       </c>
       <c r="K120" t="n">
-        <v>4870000000</v>
+        <v>100000000</v>
       </c>
       <c r="L120" t="n">
-        <v>85466000000</v>
+        <v>34620000000</v>
       </c>
       <c r="M120" t="n">
-        <v>86359000000</v>
+        <v>15117000000</v>
       </c>
       <c r="N120" t="n">
-        <v>525448492404</v>
+        <v>43102465290</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>太陽ホールディングス株式会社</t>
+          <t>日本ゼオン株式会社</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>16.4</v>
+        <v>35.8</v>
       </c>
       <c r="D121" t="n">
-        <v>4722</v>
+        <v>2354</v>
       </c>
       <c r="E121" t="n">
-        <v>3565.648720929983</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="F121" t="n">
-        <v>32.4</v>
+        <v>36.8</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -6694,50 +6694,50 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>51152000000</v>
+        <v>44521000000</v>
       </c>
       <c r="J121" t="n">
-        <v>30337000000</v>
+        <v>45382000000</v>
       </c>
       <c r="K121" t="n">
-        <v>4870000000</v>
+        <v>71191000000</v>
       </c>
       <c r="L121" t="n">
-        <v>85466000000</v>
+        <v>321836000000</v>
       </c>
       <c r="M121" t="n">
-        <v>86359000000</v>
+        <v>161094000000</v>
       </c>
       <c r="N121" t="n">
-        <v>525448492404</v>
+        <v>450427323478</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>株式会社エス・エム・エス</t>
+          <t>太陽ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>8.6</v>
+        <v>16.5</v>
       </c>
       <c r="D122" t="n">
-        <v>2568</v>
+        <v>4710</v>
       </c>
       <c r="E122" t="n">
-        <v>1478.127248828989</v>
+        <v>2199.643244598912</v>
       </c>
       <c r="F122" t="n">
-        <v>73.7</v>
+        <v>114.1</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -6746,102 +6746,102 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>14126000000</v>
+        <v>51152000000</v>
       </c>
       <c r="J122" t="n">
-        <v>1187000000</v>
+        <v>30337000000</v>
       </c>
       <c r="K122" t="n">
-        <v>2875000000</v>
+        <v>4870000000</v>
       </c>
       <c r="L122" t="n">
-        <v>29991000000</v>
+        <v>85466000000</v>
       </c>
       <c r="M122" t="n">
-        <v>18188000000</v>
+        <v>86359000000</v>
       </c>
       <c r="N122" t="n">
-        <v>210782593032</v>
+        <v>524113172220</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>アニコム ホールディングス株式会社</t>
+          <t>太陽ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>8715</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>39.4</v>
+        <v>16.5</v>
       </c>
       <c r="D123" t="n">
-        <v>1073</v>
+        <v>4710</v>
       </c>
       <c r="E123" t="n">
-        <v>656.2604975855553</v>
+        <v>3565.648720929983</v>
       </c>
       <c r="F123" t="n">
-        <v>63.5</v>
+        <v>32.1</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>27691000000</v>
+        <v>51152000000</v>
       </c>
       <c r="J123" t="n">
-        <v>3070000000</v>
+        <v>30337000000</v>
       </c>
       <c r="K123" t="n">
-        <v>3000000</v>
+        <v>4870000000</v>
       </c>
       <c r="L123" t="n">
-        <v>27316000000</v>
+        <v>85466000000</v>
       </c>
       <c r="M123" t="n">
-        <v>30764000000</v>
+        <v>86359000000</v>
       </c>
       <c r="N123" t="n">
-        <v>78137169060</v>
+        <v>524113172220</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>東京製鐵株式会社</t>
+          <t>株式会社エス・エム・エス</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>101.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D124" t="n">
-        <v>1711</v>
+        <v>2532</v>
       </c>
       <c r="E124" t="n">
-        <v>1605.452212379354</v>
+        <v>1478.127248828989</v>
       </c>
       <c r="F124" t="n">
-        <v>6.6</v>
+        <v>71.3</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -6850,102 +6850,102 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>68644000000</v>
+        <v>14126000000</v>
       </c>
       <c r="J124" t="n">
-        <v>33060000000</v>
+        <v>1187000000</v>
       </c>
       <c r="K124" t="n">
-        <v>75000000000</v>
+        <v>2875000000</v>
       </c>
       <c r="L124" t="n">
-        <v>158280000000</v>
+        <v>29991000000</v>
       </c>
       <c r="M124" t="n">
-        <v>176704000000</v>
+        <v>18188000000</v>
       </c>
       <c r="N124" t="n">
-        <v>173830997251</v>
+        <v>207827696868</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ウェーブロックホールディングス株式会社</t>
+          <t>アニコム ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>7940</t>
+          <t>8715</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>62.5</v>
+        <v>41</v>
       </c>
       <c r="D125" t="n">
-        <v>1057</v>
+        <v>1031</v>
       </c>
       <c r="E125" t="n">
-        <v>1010</v>
+        <v>656.2604975855553</v>
       </c>
       <c r="F125" t="n">
-        <v>4.7</v>
+        <v>57.1</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1961626000</v>
+        <v>27691000000</v>
       </c>
       <c r="J125" t="n">
-        <v>2544946000</v>
+        <v>3070000000</v>
       </c>
       <c r="K125" t="n">
-        <v>1068366000</v>
+        <v>3000000</v>
       </c>
       <c r="L125" t="n">
-        <v>13761535000</v>
+        <v>27316000000</v>
       </c>
       <c r="M125" t="n">
-        <v>5574938000</v>
+        <v>30764000000</v>
       </c>
       <c r="N125" t="n">
-        <v>8926497125</v>
+        <v>75078677820</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>近畿車輛株式会社</t>
+          <t>東京製鐵株式会社</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>7122</t>
+          <t>5423</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>105.5</v>
+        <v>103.2</v>
       </c>
       <c r="D126" t="n">
-        <v>2446</v>
+        <v>1685</v>
       </c>
       <c r="E126" t="n">
-        <v>2144.894901144641</v>
+        <v>1605.452212379354</v>
       </c>
       <c r="F126" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -6954,206 +6954,206 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>6847000000</v>
+        <v>68644000000</v>
       </c>
       <c r="J126" t="n">
-        <v>4580000000</v>
+        <v>33060000000</v>
       </c>
       <c r="K126" t="n">
-        <v>6329000000</v>
+        <v>75000000000</v>
       </c>
       <c r="L126" t="n">
-        <v>24474000000</v>
+        <v>158280000000</v>
       </c>
       <c r="M126" t="n">
-        <v>17756000000</v>
+        <v>176704000000</v>
       </c>
       <c r="N126" t="n">
-        <v>16828678126</v>
+        <v>171189497585</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>株式会社三陽商会</t>
+          <t>ウェーブロックホールディングス株式会社</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>7940</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>61.8</v>
+        <v>62.5</v>
       </c>
       <c r="D127" t="n">
-        <v>1411</v>
+        <v>1057</v>
       </c>
       <c r="E127" t="n">
-        <v>3321.975331035734</v>
+        <v>1010</v>
       </c>
       <c r="F127" t="n">
-        <v>-57.5</v>
+        <v>4.7</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>16287000000</v>
+        <v>1961626000</v>
       </c>
       <c r="J127" t="n">
-        <v>3021000000</v>
+        <v>2544946000</v>
       </c>
       <c r="K127" t="n">
-        <v>6298000000</v>
+        <v>1068366000</v>
       </c>
       <c r="L127" t="n">
-        <v>33920000000</v>
+        <v>13761535000</v>
       </c>
       <c r="M127" t="n">
-        <v>25606000000</v>
+        <v>5574938000</v>
       </c>
       <c r="N127" t="n">
-        <v>41463691152</v>
+        <v>8926497125</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>月島ホールディングス株式会社</t>
+          <t>近畿車輛株式会社</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>6332</t>
+          <t>7122</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>45.5</v>
+        <v>107.4</v>
       </c>
       <c r="D128" t="n">
-        <v>2838</v>
+        <v>2402</v>
       </c>
       <c r="E128" t="n">
-        <v>1410</v>
+        <v>2144.894901144641</v>
       </c>
       <c r="F128" t="n">
-        <v>101.3</v>
+        <v>12</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>28795000000</v>
+        <v>6847000000</v>
       </c>
       <c r="J128" t="n">
-        <v>22203000000</v>
+        <v>4580000000</v>
       </c>
       <c r="K128" t="n">
-        <v>100000000</v>
+        <v>6329000000</v>
       </c>
       <c r="L128" t="n">
-        <v>80949000000</v>
+        <v>24474000000</v>
       </c>
       <c r="M128" t="n">
-        <v>51098000000</v>
+        <v>17756000000</v>
       </c>
       <c r="N128" t="n">
-        <v>112388270874</v>
+        <v>16525954562</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>マネックスグループ株式会社</t>
+          <t>株式会社三陽商会</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>8698</t>
+          <t>8011</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>15</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D129" t="n">
-        <v>732</v>
+        <v>1333</v>
       </c>
       <c r="E129" t="n">
-        <v>510.1850530906719</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="F129" t="n">
-        <v>43.5</v>
+        <v>-59.9</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>17794000000</v>
+        <v>16287000000</v>
       </c>
       <c r="J129" t="n">
-        <v>412000000</v>
+        <v>3021000000</v>
       </c>
       <c r="K129" t="n">
-        <v>9312000000</v>
+        <v>6298000000</v>
       </c>
       <c r="L129" t="n">
-        <v>98001000000</v>
+        <v>33920000000</v>
       </c>
       <c r="M129" t="n">
-        <v>27518000000</v>
+        <v>25606000000</v>
       </c>
       <c r="N129" t="n">
-        <v>183998216688</v>
+        <v>39171580656</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>株式会社あおぞら銀行</t>
+          <t>月島ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>230</v>
+        <v>47.1</v>
       </c>
       <c r="D130" t="n">
-        <v>3406</v>
+        <v>2738</v>
       </c>
       <c r="E130" t="n">
-        <v>2190</v>
+        <v>1410</v>
       </c>
       <c r="F130" t="n">
-        <v>55.5</v>
+        <v>94.2</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -7162,154 +7162,154 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1061743000000</v>
+        <v>28795000000</v>
       </c>
       <c r="J130" t="n">
-        <v>22385000000</v>
+        <v>22203000000</v>
       </c>
       <c r="K130" t="n">
-        <v>0</v>
+        <v>100000000</v>
       </c>
       <c r="L130" t="n">
-        <v>487265000000</v>
+        <v>80949000000</v>
       </c>
       <c r="M130" t="n">
-        <v>1084128000000</v>
+        <v>51098000000</v>
       </c>
       <c r="N130" t="n">
-        <v>471326108344</v>
+        <v>108428148574</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>日本製紙株式会社</t>
+          <t>マネックスグループ株式会社</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>8698</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>309.4</v>
+        <v>15.1</v>
       </c>
       <c r="D131" t="n">
-        <v>1292</v>
+        <v>725</v>
       </c>
       <c r="E131" t="n">
-        <v>1250</v>
+        <v>510.1850530906719</v>
       </c>
       <c r="F131" t="n">
-        <v>3.4</v>
+        <v>42.1</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>136216000000</v>
+        <v>17794000000</v>
       </c>
       <c r="J131" t="n">
-        <v>151771000000</v>
+        <v>412000000</v>
       </c>
       <c r="K131" t="n">
-        <v>172984000000</v>
+        <v>9312000000</v>
       </c>
       <c r="L131" t="n">
-        <v>438604000000</v>
+        <v>98001000000</v>
       </c>
       <c r="M131" t="n">
-        <v>460971000000</v>
+        <v>27518000000</v>
       </c>
       <c r="N131" t="n">
-        <v>148978585876</v>
+        <v>182238670900</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>カルビー株式会社</t>
+          <t>株式会社あおぞら銀行</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>33.8</v>
+        <v>231.7</v>
       </c>
       <c r="D132" t="n">
-        <v>3002</v>
+        <v>3381</v>
       </c>
       <c r="E132" t="n">
-        <v>2919.137515755844</v>
+        <v>2190</v>
       </c>
       <c r="F132" t="n">
-        <v>2.8</v>
+        <v>54.4</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>49670000000</v>
+        <v>1061743000000</v>
       </c>
       <c r="J132" t="n">
-        <v>70285000000</v>
+        <v>22385000000</v>
       </c>
       <c r="K132" t="n">
-        <v>3263000000</v>
+        <v>0</v>
       </c>
       <c r="L132" t="n">
-        <v>183458000000</v>
+        <v>487265000000</v>
       </c>
       <c r="M132" t="n">
-        <v>123218000000</v>
+        <v>1084128000000</v>
       </c>
       <c r="N132" t="n">
-        <v>365006737708</v>
+        <v>467866580244</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ＮＩＴＴＯＫＵ株式会社</t>
+          <t>日本製紙株式会社</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>50.6</v>
+        <v>312.8</v>
       </c>
       <c r="D133" t="n">
-        <v>2468</v>
+        <v>1278</v>
       </c>
       <c r="E133" t="n">
-        <v>1710</v>
+        <v>1250</v>
       </c>
       <c r="F133" t="n">
-        <v>44.3</v>
+        <v>2.2</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -7318,102 +7318,102 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>11768000000</v>
+        <v>136216000000</v>
       </c>
       <c r="J133" t="n">
-        <v>6299000000</v>
+        <v>151771000000</v>
       </c>
       <c r="K133" t="n">
-        <v>2999000000</v>
+        <v>172984000000</v>
       </c>
       <c r="L133" t="n">
-        <v>33919000000</v>
+        <v>438604000000</v>
       </c>
       <c r="M133" t="n">
-        <v>21066000000</v>
+        <v>460971000000</v>
       </c>
       <c r="N133" t="n">
-        <v>41646221576</v>
+        <v>147364266834</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ＮＩＴＴＯＫＵ株式会社</t>
+          <t>カルビー株式会社</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>50.6</v>
+        <v>33.1</v>
       </c>
       <c r="D134" t="n">
-        <v>2468</v>
+        <v>3059</v>
       </c>
       <c r="E134" t="n">
-        <v>1710</v>
+        <v>2919.137515755844</v>
       </c>
       <c r="F134" t="n">
-        <v>44.3</v>
+        <v>4.8</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>11768000000</v>
+        <v>49670000000</v>
       </c>
       <c r="J134" t="n">
-        <v>6299000000</v>
+        <v>70285000000</v>
       </c>
       <c r="K134" t="n">
-        <v>2999000000</v>
+        <v>3263000000</v>
       </c>
       <c r="L134" t="n">
-        <v>33919000000</v>
+        <v>183458000000</v>
       </c>
       <c r="M134" t="n">
-        <v>21066000000</v>
+        <v>123218000000</v>
       </c>
       <c r="N134" t="n">
-        <v>41646221576</v>
+        <v>371937245386</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>新光商事株式会社</t>
+          <t>ＮＩＴＴＯＫＵ株式会社</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>8141</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>30.8</v>
+        <v>50.7</v>
       </c>
       <c r="D135" t="n">
-        <v>1567</v>
+        <v>2462</v>
       </c>
       <c r="E135" t="n">
-        <v>930</v>
+        <v>1710</v>
       </c>
       <c r="F135" t="n">
-        <v>68.5</v>
+        <v>44</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -7422,50 +7422,50 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>10579000000</v>
+        <v>11768000000</v>
       </c>
       <c r="J135" t="n">
-        <v>195000000</v>
+        <v>6299000000</v>
       </c>
       <c r="K135" t="n">
-        <v>2995000000</v>
+        <v>2999000000</v>
       </c>
       <c r="L135" t="n">
-        <v>51945000000</v>
+        <v>33919000000</v>
       </c>
       <c r="M135" t="n">
-        <v>13769000000</v>
+        <v>21066000000</v>
       </c>
       <c r="N135" t="n">
-        <v>44737691733</v>
+        <v>41544974684</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>株式会社メガチップス</t>
+          <t>ＮＩＴＴＯＫＵ株式会社</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>6875</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>84.09999999999999</v>
+        <v>50.7</v>
       </c>
       <c r="D136" t="n">
-        <v>11170</v>
+        <v>2462</v>
       </c>
       <c r="E136" t="n">
-        <v>4870</v>
+        <v>1710</v>
       </c>
       <c r="F136" t="n">
-        <v>129.4</v>
+        <v>44</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -7474,102 +7474,102 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>25769446000</v>
+        <v>11768000000</v>
       </c>
       <c r="J136" t="n">
-        <v>2249411000</v>
+        <v>6299000000</v>
       </c>
       <c r="K136" t="n">
-        <v>101636005000</v>
+        <v>2999000000</v>
       </c>
       <c r="L136" t="n">
-        <v>67428618000</v>
+        <v>33919000000</v>
       </c>
       <c r="M136" t="n">
-        <v>129654862000</v>
+        <v>21066000000</v>
       </c>
       <c r="N136" t="n">
-        <v>154156064170</v>
+        <v>41544974684</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>株式会社青山財産ネットワークス</t>
+          <t>新光商事株式会社</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>8929</t>
+          <t>8141</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>41.6</v>
+        <v>30.8</v>
       </c>
       <c r="D137" t="n">
-        <v>1394</v>
+        <v>1567</v>
       </c>
       <c r="E137" t="n">
-        <v>1347.74653160027</v>
+        <v>930</v>
       </c>
       <c r="F137" t="n">
-        <v>3.4</v>
+        <v>68.5</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>10862000000</v>
+        <v>10579000000</v>
       </c>
       <c r="J137" t="n">
-        <v>245000000</v>
+        <v>195000000</v>
       </c>
       <c r="K137" t="n">
-        <v>2845000000</v>
+        <v>2995000000</v>
       </c>
       <c r="L137" t="n">
-        <v>7128000000</v>
+        <v>51945000000</v>
       </c>
       <c r="M137" t="n">
-        <v>13952000000</v>
+        <v>13769000000</v>
       </c>
       <c r="N137" t="n">
-        <v>33546941772</v>
+        <v>44737691733</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>平和不動産株式会社</t>
+          <t>株式会社メガチップス</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>8803</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>73.09999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="D138" t="n">
-        <v>2350</v>
+        <v>10530</v>
       </c>
       <c r="E138" t="n">
-        <v>3610</v>
+        <v>4870</v>
       </c>
       <c r="F138" t="n">
-        <v>-34.9</v>
+        <v>116.2</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -7578,106 +7578,106 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>28111000000</v>
+        <v>25769446000</v>
       </c>
       <c r="J138" t="n">
-        <v>79319000000</v>
+        <v>2249411000</v>
       </c>
       <c r="K138" t="n">
-        <v>5997000000</v>
+        <v>101636005000</v>
       </c>
       <c r="L138" t="n">
-        <v>119278000000</v>
+        <v>67428618000</v>
       </c>
       <c r="M138" t="n">
-        <v>113427000000</v>
+        <v>129654862000</v>
       </c>
       <c r="N138" t="n">
-        <v>155265106300</v>
+        <v>145323487530</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>小林製薬株式会社</t>
+          <t>株式会社青山財産ネットワークス</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>8929</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>30.8</v>
+        <v>42</v>
       </c>
       <c r="D139" t="n">
-        <v>5654</v>
+        <v>1379</v>
       </c>
       <c r="E139" t="n">
-        <v>2148.936934940886</v>
+        <v>1347.74653160027</v>
       </c>
       <c r="F139" t="n">
-        <v>163.1</v>
+        <v>2.3</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>81987000000</v>
+        <v>10862000000</v>
       </c>
       <c r="J139" t="n">
-        <v>32461000000</v>
+        <v>245000000</v>
       </c>
       <c r="K139" t="n">
-        <v>14872000000</v>
+        <v>2845000000</v>
       </c>
       <c r="L139" t="n">
-        <v>195600000000</v>
+        <v>7128000000</v>
       </c>
       <c r="M139" t="n">
-        <v>129320000000</v>
+        <v>13952000000</v>
       </c>
       <c r="N139" t="n">
-        <v>420310563134</v>
+        <v>33185963202</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>小林製薬株式会社</t>
+          <t>平和不動産株式会社</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>30.8</v>
+        <v>72.8</v>
       </c>
       <c r="D140" t="n">
-        <v>5654</v>
+        <v>2358</v>
       </c>
       <c r="E140" t="n">
-        <v>5066.092575838703</v>
+        <v>3610</v>
       </c>
       <c r="F140" t="n">
-        <v>11.6</v>
+        <v>-34.7</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -7686,46 +7686,46 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>81987000000</v>
+        <v>28111000000</v>
       </c>
       <c r="J140" t="n">
-        <v>32461000000</v>
+        <v>79319000000</v>
       </c>
       <c r="K140" t="n">
-        <v>14872000000</v>
+        <v>5997000000</v>
       </c>
       <c r="L140" t="n">
-        <v>195600000000</v>
+        <v>119278000000</v>
       </c>
       <c r="M140" t="n">
-        <v>129320000000</v>
+        <v>113427000000</v>
       </c>
       <c r="N140" t="n">
-        <v>420310563134</v>
+        <v>155793668364</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>セーレン株式会社</t>
+          <t>小林製薬株式会社</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>3569</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>35</v>
+        <v>29.4</v>
       </c>
       <c r="D141" t="n">
-        <v>3420</v>
+        <v>5913</v>
       </c>
       <c r="E141" t="n">
-        <v>1359.655069733296</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="F141" t="n">
-        <v>151.5</v>
+        <v>175.2</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -7734,50 +7734,50 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>35451000000</v>
+        <v>81987000000</v>
       </c>
       <c r="J141" t="n">
-        <v>25813000000</v>
+        <v>32461000000</v>
       </c>
       <c r="K141" t="n">
-        <v>8891000000</v>
+        <v>14872000000</v>
       </c>
       <c r="L141" t="n">
-        <v>91845000000</v>
+        <v>195600000000</v>
       </c>
       <c r="M141" t="n">
-        <v>70155000000</v>
+        <v>129320000000</v>
       </c>
       <c r="N141" t="n">
-        <v>200289704220</v>
+        <v>439564265973</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>データセクション株式会社</t>
+          <t>小林製薬株式会社</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>2.5</v>
+        <v>29.4</v>
       </c>
       <c r="D142" t="n">
-        <v>1577</v>
+        <v>5913</v>
       </c>
       <c r="E142" t="n">
-        <v>5143.276404494382</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="F142" t="n">
-        <v>-69.3</v>
+        <v>16.7</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -7786,650 +7786,754 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1420430000</v>
+        <v>81987000000</v>
       </c>
       <c r="J142" t="n">
-        <v>1162000</v>
+        <v>32461000000</v>
       </c>
       <c r="K142" t="n">
-        <v>49326000</v>
+        <v>14872000000</v>
       </c>
       <c r="L142" t="n">
-        <v>2818110000</v>
+        <v>195600000000</v>
       </c>
       <c r="M142" t="n">
-        <v>1470918000</v>
+        <v>129320000000</v>
       </c>
       <c r="N142" t="n">
-        <v>59078056562</v>
+        <v>439564265973</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>愛眼株式会社</t>
+          <t>セーレン株式会社</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>9854</t>
+          <t>3569</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>67.5</v>
+        <v>36.7</v>
       </c>
       <c r="D143" t="n">
-        <v>294</v>
+        <v>3265</v>
       </c>
       <c r="E143" t="n">
-        <v>246.9708756284982</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="F143" t="n">
-        <v>19</v>
+        <v>140.1</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2219000000</v>
+        <v>35451000000</v>
       </c>
       <c r="J143" t="n">
-        <v>1030000000</v>
+        <v>25813000000</v>
       </c>
       <c r="K143" t="n">
-        <v>604000000</v>
+        <v>8891000000</v>
       </c>
       <c r="L143" t="n">
-        <v>12920000000</v>
+        <v>91845000000</v>
       </c>
       <c r="M143" t="n">
-        <v>3853000000</v>
+        <v>70155000000</v>
       </c>
       <c r="N143" t="n">
-        <v>5705574210</v>
+        <v>191212246865</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>株式会社アシロ</t>
+          <t>データセクション株式会社</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>13.8</v>
+        <v>2.6</v>
       </c>
       <c r="D144" t="n">
-        <v>1575</v>
+        <v>1514</v>
       </c>
       <c r="E144" t="n">
-        <v>1396.628697042366</v>
+        <v>5143.276404494382</v>
       </c>
       <c r="F144" t="n">
-        <v>12.8</v>
+        <v>-70.59999999999999</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1428281000</v>
+        <v>1420430000</v>
       </c>
       <c r="J144" t="n">
-        <v>102238000</v>
+        <v>1162000</v>
       </c>
       <c r="K144" t="n">
-        <v>0</v>
+        <v>49326000</v>
       </c>
       <c r="L144" t="n">
-        <v>1804458000</v>
+        <v>2818110000</v>
       </c>
       <c r="M144" t="n">
-        <v>1530519000</v>
+        <v>1470918000</v>
       </c>
       <c r="N144" t="n">
-        <v>11071599525</v>
+        <v>56717931284</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>三浦工業株式会社</t>
+          <t>愛眼株式会社</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>11.3</v>
+        <v>69.7</v>
       </c>
       <c r="D145" t="n">
-        <v>3223</v>
+        <v>285</v>
       </c>
       <c r="E145" t="n">
-        <v>3147.518794622453</v>
+        <v>246.9708756284982</v>
       </c>
       <c r="F145" t="n">
-        <v>2.4</v>
+        <v>15.4</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>20794000000</v>
+        <v>2219000000</v>
       </c>
       <c r="J145" t="n">
-        <v>10600000000</v>
+        <v>1030000000</v>
       </c>
       <c r="K145" t="n">
-        <v>10773000000</v>
+        <v>604000000</v>
       </c>
       <c r="L145" t="n">
-        <v>138378000000</v>
+        <v>12920000000</v>
       </c>
       <c r="M145" t="n">
-        <v>42167000000</v>
+        <v>3853000000</v>
       </c>
       <c r="N145" t="n">
-        <v>373060187280</v>
+        <v>5530913775</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>株式会社カカクコム</t>
+          <t>株式会社アシロ</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>7378</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D146" t="n">
-        <v>3700</v>
+        <v>1551</v>
       </c>
       <c r="E146" t="n">
-        <v>2318.314890576102</v>
+        <v>1396.628697042366</v>
       </c>
       <c r="F146" t="n">
-        <v>59.6</v>
+        <v>11.1</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>46452000000</v>
+        <v>1428281000</v>
       </c>
       <c r="J146" t="n">
-        <v>68000000</v>
+        <v>102238000</v>
       </c>
       <c r="K146" t="n">
-        <v>4669000000</v>
+        <v>0</v>
       </c>
       <c r="L146" t="n">
-        <v>45479000000</v>
+        <v>1804458000</v>
       </c>
       <c r="M146" t="n">
-        <v>51189000000</v>
+        <v>1530519000</v>
       </c>
       <c r="N146" t="n">
-        <v>731994187900</v>
+        <v>10902889437</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>古河機械金属株式会社</t>
+          <t>三浦工業株式会社</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>43.7</v>
+        <v>11.4</v>
       </c>
       <c r="D147" t="n">
-        <v>4265</v>
+        <v>3184</v>
       </c>
       <c r="E147" t="n">
-        <v>1600</v>
+        <v>3147.518794622453</v>
       </c>
       <c r="F147" t="n">
-        <v>166.6</v>
+        <v>1.2</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>14468000000</v>
+        <v>20794000000</v>
       </c>
       <c r="J147" t="n">
-        <v>26121000000</v>
+        <v>10600000000</v>
       </c>
       <c r="K147" t="n">
-        <v>19903000000</v>
+        <v>10773000000</v>
       </c>
       <c r="L147" t="n">
-        <v>100075000000</v>
+        <v>138378000000</v>
       </c>
       <c r="M147" t="n">
-        <v>60492000000</v>
+        <v>42167000000</v>
       </c>
       <c r="N147" t="n">
-        <v>138317600840</v>
+        <v>368545962240</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>多木化学株式会社</t>
+          <t>株式会社カカクコム</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>4025</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="D148" t="n">
-        <v>5650</v>
+        <v>3691</v>
       </c>
       <c r="E148" t="n">
-        <v>4695.956053243186</v>
+        <v>2318.314890576102</v>
       </c>
       <c r="F148" t="n">
-        <v>20.3</v>
+        <v>59.2</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>6433000000</v>
+        <v>46452000000</v>
       </c>
       <c r="J148" t="n">
-        <v>7985000000</v>
+        <v>68000000</v>
       </c>
       <c r="K148" t="n">
-        <v>199000000</v>
+        <v>4669000000</v>
       </c>
       <c r="L148" t="n">
-        <v>29378000000</v>
+        <v>45479000000</v>
       </c>
       <c r="M148" t="n">
-        <v>14617000000</v>
+        <v>51189000000</v>
       </c>
       <c r="N148" t="n">
-        <v>47162634850</v>
+        <v>730213661497</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>エムスリー株式会社</t>
+          <t>古河機械金属株式会社</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2413</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>7.8</v>
+        <v>44.6</v>
       </c>
       <c r="D149" t="n">
-        <v>1703.5</v>
+        <v>4180</v>
       </c>
       <c r="E149" t="n">
-        <v>1638.585693292194</v>
+        <v>1600</v>
       </c>
       <c r="F149" t="n">
-        <v>4</v>
+        <v>161.2</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>78812000000</v>
+        <v>14468000000</v>
       </c>
       <c r="J149" t="n">
-        <v>345000000</v>
+        <v>26121000000</v>
       </c>
       <c r="K149" t="n">
-        <v>9506000000</v>
+        <v>19903000000</v>
       </c>
       <c r="L149" t="n">
-        <v>152472000000</v>
+        <v>100075000000</v>
       </c>
       <c r="M149" t="n">
-        <v>88663000000</v>
+        <v>60492000000</v>
       </c>
       <c r="N149" t="n">
-        <v>1136967108914</v>
+        <v>135560978080</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>三井松島ホールディングス株式会社</t>
+          <t>多木化学株式会社</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>39.8</v>
+        <v>31.3</v>
       </c>
       <c r="D150" t="n">
-        <v>2301</v>
+        <v>5600</v>
       </c>
       <c r="E150" t="n">
-        <v>2920</v>
+        <v>4695.956053243186</v>
       </c>
       <c r="F150" t="n">
-        <v>-21.2</v>
+        <v>19.3</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>19413000000</v>
+        <v>6433000000</v>
       </c>
       <c r="J150" t="n">
-        <v>3540000000</v>
+        <v>7985000000</v>
       </c>
       <c r="K150" t="n">
-        <v>10945000000</v>
+        <v>199000000</v>
       </c>
       <c r="L150" t="n">
-        <v>35537000000</v>
+        <v>29378000000</v>
       </c>
       <c r="M150" t="n">
-        <v>33898000000</v>
+        <v>14617000000</v>
       </c>
       <c r="N150" t="n">
-        <v>85201335960</v>
+        <v>46745266400</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ノリタケ株式会社</t>
+          <t>エムスリー株式会社</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>38</v>
+        <v>7.7</v>
       </c>
       <c r="D151" t="n">
-        <v>3580</v>
+        <v>1720.5</v>
       </c>
       <c r="E151" t="n">
-        <v>3573.410502159827</v>
+        <v>1638.585693292194</v>
       </c>
       <c r="F151" t="n">
-        <v>0.2</v>
+        <v>5</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>11733000000</v>
+        <v>78812000000</v>
       </c>
       <c r="J151" t="n">
-        <v>20204000000</v>
+        <v>345000000</v>
       </c>
       <c r="K151" t="n">
-        <v>42879000000</v>
+        <v>9506000000</v>
       </c>
       <c r="L151" t="n">
-        <v>118800000000</v>
+        <v>152472000000</v>
       </c>
       <c r="M151" t="n">
-        <v>74816000000</v>
+        <v>88663000000</v>
       </c>
       <c r="N151" t="n">
-        <v>196951100920</v>
+        <v>1146397127050</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>株式会社ＡＣＳＬ</t>
+          <t>三井松島ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>7.3</v>
+        <v>40</v>
       </c>
       <c r="D152" t="n">
-        <v>1464</v>
+        <v>2291</v>
       </c>
       <c r="E152" t="n">
-        <v>913.2768512341561</v>
+        <v>2920</v>
       </c>
       <c r="F152" t="n">
-        <v>60.3</v>
+        <v>-21.5</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1891731000</v>
+        <v>19413000000</v>
       </c>
       <c r="J152" t="n">
-        <v>3724000</v>
+        <v>3540000000</v>
       </c>
       <c r="K152" t="n">
-        <v>197577000</v>
+        <v>10945000000</v>
       </c>
       <c r="L152" t="n">
-        <v>3572642000</v>
+        <v>35537000000</v>
       </c>
       <c r="M152" t="n">
-        <v>2093032000</v>
+        <v>33898000000</v>
       </c>
       <c r="N152" t="n">
-        <v>28653762288</v>
+        <v>84831056360</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>株式会社スズケン</t>
+          <t>ノリタケ株式会社</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>9987</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>78.7</v>
+        <v>39.1</v>
       </c>
       <c r="D153" t="n">
-        <v>5122</v>
+        <v>3480</v>
       </c>
       <c r="E153" t="n">
-        <v>4137.137750115735</v>
+        <v>3573.410502159827</v>
       </c>
       <c r="F153" t="n">
-        <v>23.8</v>
+        <v>-2.6</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>168215000000</v>
+        <v>11733000000</v>
       </c>
       <c r="J153" t="n">
-        <v>65453000000</v>
+        <v>20204000000</v>
       </c>
       <c r="K153" t="n">
-        <v>38927000000</v>
+        <v>42879000000</v>
       </c>
       <c r="L153" t="n">
-        <v>418062000000</v>
+        <v>118800000000</v>
       </c>
       <c r="M153" t="n">
-        <v>272595000000</v>
+        <v>74816000000</v>
       </c>
       <c r="N153" t="n">
-        <v>346441042090</v>
+        <v>191449673520</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
+          <t>株式会社ＡＣＳＬ</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>6232</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="D154" t="n">
+        <v>1381</v>
+      </c>
+      <c r="E154" t="n">
+        <v>913.2768512341561</v>
+      </c>
+      <c r="F154" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
+        <v>1891731000</v>
+      </c>
+      <c r="J154" t="n">
+        <v>3724000</v>
+      </c>
+      <c r="K154" t="n">
+        <v>197577000</v>
+      </c>
+      <c r="L154" t="n">
+        <v>3572642000</v>
+      </c>
+      <c r="M154" t="n">
+        <v>2093032000</v>
+      </c>
+      <c r="N154" t="n">
+        <v>27029266202</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>株式会社スズケン</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="D155" t="n">
+        <v>5187</v>
+      </c>
+      <c r="E155" t="n">
+        <v>4137.137750115735</v>
+      </c>
+      <c r="F155" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>168215000000</v>
+      </c>
+      <c r="J155" t="n">
+        <v>65453000000</v>
+      </c>
+      <c r="K155" t="n">
+        <v>38927000000</v>
+      </c>
+      <c r="L155" t="n">
+        <v>418062000000</v>
+      </c>
+      <c r="M155" t="n">
+        <v>272595000000</v>
+      </c>
+      <c r="N155" t="n">
+        <v>350837502015</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
           <t>フォスター電機株式会社</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
+      <c r="B156" t="inlineStr">
         <is>
           <t>6794</t>
         </is>
       </c>
-      <c r="C154" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="D154" t="n">
-        <v>3035</v>
-      </c>
-      <c r="E154" t="n">
+      <c r="C156" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="D156" t="n">
+        <v>2902</v>
+      </c>
+      <c r="E156" t="n">
         <v>2681.96152003832</v>
       </c>
-      <c r="F154" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="G154" t="inlineStr">
+      <c r="F156" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="G156" t="inlineStr">
         <is>
           <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
+      <c r="H156" t="inlineStr">
         <is>
           <t>2026-01-22</t>
         </is>
       </c>
-      <c r="I154" t="n">
+      <c r="I156" t="n">
         <v>12089000000</v>
       </c>
-      <c r="J154" t="n">
+      <c r="J156" t="n">
         <v>7327000000</v>
       </c>
-      <c r="K154" t="n">
+      <c r="K156" t="n">
         <v>1115000000</v>
       </c>
-      <c r="L154" t="n">
+      <c r="L156" t="n">
         <v>51632000000</v>
       </c>
-      <c r="M154" t="n">
+      <c r="M156" t="n">
         <v>20531000000</v>
       </c>
-      <c r="N154" t="n">
-        <v>68189794245</v>
+      <c r="N156" t="n">
+        <v>65201575914</v>
       </c>
     </row>
   </sheetData>

--- a/docs/アクティビスト銘柄_資産判定.xlsx
+++ b/docs/アクティビスト銘柄_資産判定.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N156"/>
+  <dimension ref="A1:N158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>45.7</v>
+        <v>46</v>
       </c>
       <c r="D2" t="n">
-        <v>1301.5</v>
+        <v>1294</v>
       </c>
       <c r="E2" t="n">
         <v>1111.251693601708</v>
       </c>
       <c r="F2" t="n">
-        <v>17.1</v>
+        <v>16.4</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -537,7 +537,7 @@
         <v>213563000000</v>
       </c>
       <c r="N2" t="n">
-        <v>467280200060</v>
+        <v>464587459760</v>
       </c>
     </row>
     <row r="3">
@@ -552,16 +552,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>55.7</v>
+        <v>55.1</v>
       </c>
       <c r="D3" t="n">
-        <v>1142</v>
+        <v>1154</v>
       </c>
       <c r="E3" t="n">
         <v>1019.677694332945</v>
       </c>
       <c r="F3" t="n">
-        <v>12</v>
+        <v>13.2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         <v>106991000000</v>
       </c>
       <c r="N3" t="n">
-        <v>192142128100</v>
+        <v>194161134700</v>
       </c>
     </row>
     <row r="4">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="D4" t="n">
-        <v>3443</v>
+        <v>3413</v>
       </c>
       <c r="E4" t="n">
         <v>6116.356643776557</v>
       </c>
       <c r="F4" t="n">
-        <v>-43.7</v>
+        <v>-44.2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         <v>219041000000</v>
       </c>
       <c r="N4" t="n">
-        <v>3115081773342</v>
+        <v>3087939033522</v>
       </c>
     </row>
     <row r="5">
@@ -656,16 +656,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="D5" t="n">
-        <v>2150</v>
+        <v>2142</v>
       </c>
       <c r="E5" t="n">
         <v>1815.198567455447</v>
       </c>
       <c r="F5" t="n">
-        <v>18.4</v>
+        <v>18</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         <v>168499000000</v>
       </c>
       <c r="N5" t="n">
-        <v>538827091800</v>
+        <v>536822153784</v>
       </c>
     </row>
     <row r="6">
@@ -708,16 +708,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>53.9</v>
+        <v>53</v>
       </c>
       <c r="D6" t="n">
-        <v>10820</v>
+        <v>11010</v>
       </c>
       <c r="E6" t="n">
         <v>5684.0003469471</v>
       </c>
       <c r="F6" t="n">
-        <v>90.40000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>91895000000</v>
       </c>
       <c r="N6" t="n">
-        <v>170523816740</v>
+        <v>173518227570</v>
       </c>
     </row>
     <row r="7">
@@ -760,16 +760,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>53.9</v>
+        <v>53</v>
       </c>
       <c r="D7" t="n">
-        <v>10820</v>
+        <v>11010</v>
       </c>
       <c r="E7" t="n">
         <v>4549.503641591014</v>
       </c>
       <c r="F7" t="n">
-        <v>137.8</v>
+        <v>142</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>91895000000</v>
       </c>
       <c r="N7" t="n">
-        <v>170523816740</v>
+        <v>173518227570</v>
       </c>
     </row>
     <row r="8">
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14.8</v>
+        <v>14.6</v>
       </c>
       <c r="D8" t="n">
-        <v>3770</v>
+        <v>3835</v>
       </c>
       <c r="E8" t="n">
         <v>1361.432492253209</v>
       </c>
       <c r="F8" t="n">
-        <v>176.9</v>
+        <v>181.7</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>12397436000</v>
       </c>
       <c r="N8" t="n">
-        <v>83629167310</v>
+        <v>85071049505</v>
       </c>
     </row>
     <row r="9">
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="D9" t="n">
-        <v>3290</v>
+        <v>3301</v>
       </c>
       <c r="E9" t="n">
         <v>13739.64575539568</v>
       </c>
       <c r="F9" t="n">
-        <v>-76.09999999999999</v>
+        <v>-76</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>325393000000</v>
       </c>
       <c r="N9" t="n">
-        <v>1071659201200</v>
+        <v>1075242256280</v>
       </c>
     </row>
     <row r="10">
@@ -916,16 +916,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>45.8</v>
+        <v>46.4</v>
       </c>
       <c r="D10" t="n">
-        <v>2108.5</v>
+        <v>2081</v>
       </c>
       <c r="E10" t="n">
         <v>1198.150742177053</v>
       </c>
       <c r="F10" t="n">
-        <v>76</v>
+        <v>73.7</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>213966000000</v>
       </c>
       <c r="N10" t="n">
-        <v>466850872898</v>
+        <v>460761995021</v>
       </c>
     </row>
     <row r="11">
@@ -968,16 +968,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>45.8</v>
+        <v>46.4</v>
       </c>
       <c r="D11" t="n">
-        <v>2108.5</v>
+        <v>2081</v>
       </c>
       <c r="E11" t="n">
         <v>1188.162962482466</v>
       </c>
       <c r="F11" t="n">
-        <v>77.5</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>213966000000</v>
       </c>
       <c r="N11" t="n">
-        <v>466850872898</v>
+        <v>460761995021</v>
       </c>
     </row>
     <row r="12">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24.4</v>
+        <v>24.8</v>
       </c>
       <c r="D12" t="n">
-        <v>3621</v>
+        <v>3570</v>
       </c>
       <c r="E12" t="n">
         <v>2995.424821743842</v>
       </c>
       <c r="F12" t="n">
-        <v>20.9</v>
+        <v>19.2</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>129979000000</v>
       </c>
       <c r="N12" t="n">
-        <v>532162741764</v>
+        <v>524667491880</v>
       </c>
     </row>
     <row r="13">
@@ -1072,16 +1072,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>74.2</v>
+        <v>75.3</v>
       </c>
       <c r="D13" t="n">
-        <v>4820</v>
+        <v>4753</v>
       </c>
       <c r="E13" t="n">
         <v>4991.027246539169</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.4</v>
+        <v>-4.8</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>1007966000000</v>
       </c>
       <c r="N13" t="n">
-        <v>1358019315720</v>
+        <v>1339142283738</v>
       </c>
     </row>
     <row r="14">
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>20.2</v>
+        <v>21.1</v>
       </c>
       <c r="D14" t="n">
-        <v>1816</v>
+        <v>1740</v>
       </c>
       <c r="E14" t="n">
         <v>1512.21980974841</v>
       </c>
       <c r="F14" t="n">
-        <v>20.1</v>
+        <v>15.1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>120816000000</v>
       </c>
       <c r="N14" t="n">
-        <v>598220841608</v>
+        <v>573185167620</v>
       </c>
     </row>
     <row r="15">
@@ -1176,16 +1176,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="D15" t="n">
-        <v>2614.5</v>
+        <v>2600</v>
       </c>
       <c r="E15" t="n">
         <v>1827.011042553346</v>
       </c>
       <c r="F15" t="n">
-        <v>43.1</v>
+        <v>42.3</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>48336000000</v>
       </c>
       <c r="N15" t="n">
-        <v>642927679128</v>
+        <v>639362006400</v>
       </c>
     </row>
     <row r="16">
@@ -1228,16 +1228,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>134.8</v>
+        <v>136.1</v>
       </c>
       <c r="D16" t="n">
-        <v>1596</v>
+        <v>1580</v>
       </c>
       <c r="E16" t="n">
         <v>2122.579027791042</v>
       </c>
       <c r="F16" t="n">
-        <v>-24.8</v>
+        <v>-25.6</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>80333000000</v>
       </c>
       <c r="N16" t="n">
-        <v>59614473492</v>
+        <v>59016834660</v>
       </c>
     </row>
     <row r="17">
@@ -1280,16 +1280,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.4</v>
+        <v>17.6</v>
       </c>
       <c r="D17" t="n">
-        <v>2866</v>
+        <v>2827</v>
       </c>
       <c r="E17" t="n">
         <v>6272.971195510064</v>
       </c>
       <c r="F17" t="n">
-        <v>-54.3</v>
+        <v>-54.9</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>179622000000</v>
       </c>
       <c r="N17" t="n">
-        <v>1033696080444</v>
+        <v>1019629734618</v>
       </c>
     </row>
     <row r="18">
@@ -1332,16 +1332,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="D18" t="n">
-        <v>3445</v>
+        <v>3551</v>
       </c>
       <c r="E18" t="n">
         <v>1572.181660925393</v>
       </c>
       <c r="F18" t="n">
-        <v>119.1</v>
+        <v>125.9</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>35501000000</v>
       </c>
       <c r="N18" t="n">
-        <v>615149731365</v>
+        <v>634077415407</v>
       </c>
     </row>
     <row r="19">
@@ -1384,16 +1384,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="D19" t="n">
-        <v>3445</v>
+        <v>3551</v>
       </c>
       <c r="E19" t="n">
         <v>1141.512891683109</v>
       </c>
       <c r="F19" t="n">
-        <v>201.8</v>
+        <v>211.1</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>35501000000</v>
       </c>
       <c r="N19" t="n">
-        <v>615149731365</v>
+        <v>634077415407</v>
       </c>
     </row>
     <row r="20">
@@ -1436,16 +1436,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>45</v>
+        <v>46.1</v>
       </c>
       <c r="D20" t="n">
-        <v>5977</v>
+        <v>5825</v>
       </c>
       <c r="E20" t="n">
         <v>2836.942753814942</v>
       </c>
       <c r="F20" t="n">
-        <v>110.7</v>
+        <v>105.3</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>94351000000</v>
       </c>
       <c r="N20" t="n">
-        <v>209899813817</v>
+        <v>204561889825</v>
       </c>
     </row>
     <row r="21">
@@ -1488,16 +1488,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>57.3</v>
+        <v>55.7</v>
       </c>
       <c r="D21" t="n">
-        <v>3921</v>
+        <v>4032</v>
       </c>
       <c r="E21" t="n">
         <v>2863.970160821546</v>
       </c>
       <c r="F21" t="n">
-        <v>36.9</v>
+        <v>40.8</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>161529000000</v>
       </c>
       <c r="N21" t="n">
-        <v>282096984123</v>
+        <v>290082897216</v>
       </c>
     </row>
     <row r="22">
@@ -1540,16 +1540,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>53.1</v>
+        <v>52.6</v>
       </c>
       <c r="D22" t="n">
-        <v>4608</v>
+        <v>4646</v>
       </c>
       <c r="E22" t="n">
         <v>2566.284807227078</v>
       </c>
       <c r="F22" t="n">
-        <v>79.59999999999999</v>
+        <v>81</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>231575000000</v>
       </c>
       <c r="N22" t="n">
-        <v>436437983232</v>
+        <v>440037081184</v>
       </c>
     </row>
     <row r="23">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28.9</v>
+        <v>29.1</v>
       </c>
       <c r="D23" t="n">
-        <v>5112</v>
+        <v>5081</v>
       </c>
       <c r="E23" t="n">
         <v>2779.139169918938</v>
       </c>
       <c r="F23" t="n">
-        <v>83.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>183216000000</v>
       </c>
       <c r="N23" t="n">
-        <v>634053991752</v>
+        <v>630208985151</v>
       </c>
     </row>
     <row r="24">
@@ -1644,16 +1644,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>4072</v>
+        <v>3986</v>
       </c>
       <c r="E24" t="n">
         <v>2420.370957920882</v>
       </c>
       <c r="F24" t="n">
-        <v>68.2</v>
+        <v>64.7</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>18167000000</v>
       </c>
       <c r="N24" t="n">
-        <v>201307785688</v>
+        <v>197056196894</v>
       </c>
     </row>
     <row r="25">
@@ -1699,13 +1699,13 @@
         <v>8.1</v>
       </c>
       <c r="D25" t="n">
-        <v>1766.5</v>
+        <v>1758.5</v>
       </c>
       <c r="E25" t="n">
         <v>1344.518957928979</v>
       </c>
       <c r="F25" t="n">
-        <v>31.4</v>
+        <v>30.8</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>45956000000</v>
       </c>
       <c r="N25" t="n">
-        <v>568382420924</v>
+        <v>565808370900</v>
       </c>
     </row>
     <row r="26">
@@ -1748,16 +1748,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>58.9</v>
+        <v>60.1</v>
       </c>
       <c r="D26" t="n">
-        <v>5081</v>
+        <v>4980</v>
       </c>
       <c r="E26" t="n">
         <v>4154.626869982095</v>
       </c>
       <c r="F26" t="n">
-        <v>22.3</v>
+        <v>19.9</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>179086000000</v>
       </c>
       <c r="N26" t="n">
-        <v>303847234756</v>
+        <v>297807366480</v>
       </c>
     </row>
     <row r="27">
@@ -1800,16 +1800,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="D27" t="n">
-        <v>3831</v>
+        <v>3797</v>
       </c>
       <c r="E27" t="n">
         <v>2561.705402476645</v>
       </c>
       <c r="F27" t="n">
-        <v>49.5</v>
+        <v>48.2</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>100104000000</v>
       </c>
       <c r="N27" t="n">
-        <v>701001762555</v>
+        <v>694780394785</v>
       </c>
     </row>
     <row r="28">
@@ -1852,16 +1852,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>44.8</v>
+        <v>45.2</v>
       </c>
       <c r="D28" t="n">
-        <v>3449</v>
+        <v>3420</v>
       </c>
       <c r="E28" t="n">
         <v>2560</v>
       </c>
       <c r="F28" t="n">
-        <v>34.7</v>
+        <v>33.6</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>190312000000</v>
       </c>
       <c r="N28" t="n">
-        <v>424607445394</v>
+        <v>421037246520</v>
       </c>
     </row>
     <row r="29">
@@ -1904,16 +1904,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>91</v>
+        <v>91.2</v>
       </c>
       <c r="D29" t="n">
-        <v>4225</v>
+        <v>4215</v>
       </c>
       <c r="E29" t="n">
         <v>3449.780346820809</v>
       </c>
       <c r="F29" t="n">
-        <v>22.5</v>
+        <v>22.2</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>90928000000</v>
       </c>
       <c r="N29" t="n">
-        <v>99908625700</v>
+        <v>99672155580</v>
       </c>
     </row>
     <row r="30">
@@ -1956,16 +1956,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>61</v>
+        <v>62.2</v>
       </c>
       <c r="D30" t="n">
-        <v>1564</v>
+        <v>1534</v>
       </c>
       <c r="E30" t="n">
         <v>1746.940387696806</v>
       </c>
       <c r="F30" t="n">
-        <v>-10.5</v>
+        <v>-12.2</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>36070000000</v>
       </c>
       <c r="N30" t="n">
-        <v>59090255052</v>
+        <v>57956810262</v>
       </c>
     </row>
     <row r="31">
@@ -2008,16 +2008,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>106.6</v>
+        <v>106.4</v>
       </c>
       <c r="D31" t="n">
-        <v>1663</v>
+        <v>1666</v>
       </c>
       <c r="E31" t="n">
         <v>2298.672482457804</v>
       </c>
       <c r="F31" t="n">
-        <v>-27.7</v>
+        <v>-27.5</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>42752000000</v>
       </c>
       <c r="N31" t="n">
-        <v>40097735481</v>
+        <v>40170070542</v>
       </c>
     </row>
     <row r="32">
@@ -2060,16 +2060,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>70.5</v>
+        <v>67.5</v>
       </c>
       <c r="D32" t="n">
-        <v>2539</v>
+        <v>2651</v>
       </c>
       <c r="E32" t="n">
         <v>1270</v>
       </c>
       <c r="F32" t="n">
-        <v>99.90000000000001</v>
+        <v>108.7</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>31108000000</v>
       </c>
       <c r="N32" t="n">
-        <v>44147017379</v>
+        <v>46094424211</v>
       </c>
     </row>
     <row r="33">
@@ -2112,16 +2112,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>70.5</v>
+        <v>67.5</v>
       </c>
       <c r="D33" t="n">
-        <v>2539</v>
+        <v>2651</v>
       </c>
       <c r="E33" t="n">
         <v>1170</v>
       </c>
       <c r="F33" t="n">
-        <v>117</v>
+        <v>126.6</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>31108000000</v>
       </c>
       <c r="N33" t="n">
-        <v>44147017379</v>
+        <v>46094424211</v>
       </c>
     </row>
     <row r="34">
@@ -2164,16 +2164,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>33.8</v>
+        <v>34</v>
       </c>
       <c r="D34" t="n">
-        <v>2808</v>
+        <v>2797</v>
       </c>
       <c r="E34" t="n">
         <v>2381.523440544182</v>
       </c>
       <c r="F34" t="n">
-        <v>17.9</v>
+        <v>17.4</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>168696000000</v>
       </c>
       <c r="N34" t="n">
-        <v>498674660328</v>
+        <v>496721162727</v>
       </c>
     </row>
     <row r="35">
@@ -2216,16 +2216,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>83.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="D35" t="n">
-        <v>2484</v>
+        <v>2450</v>
       </c>
       <c r="E35" t="n">
         <v>2939.562915943684</v>
       </c>
       <c r="F35" t="n">
-        <v>-15.5</v>
+        <v>-16.7</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>108430000000</v>
       </c>
       <c r="N35" t="n">
-        <v>130079339856</v>
+        <v>128298865800</v>
       </c>
     </row>
     <row r="36">
@@ -2271,13 +2271,13 @@
         <v>48.6</v>
       </c>
       <c r="D36" t="n">
-        <v>13420</v>
+        <v>13440</v>
       </c>
       <c r="E36" t="n">
         <v>7040.15625</v>
       </c>
       <c r="F36" t="n">
-        <v>90.59999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>6799899000</v>
       </c>
       <c r="N36" t="n">
-        <v>13977829140</v>
+        <v>13998660480</v>
       </c>
     </row>
     <row r="37">
@@ -2323,13 +2323,13 @@
         <v>48.6</v>
       </c>
       <c r="D37" t="n">
-        <v>13420</v>
+        <v>13440</v>
       </c>
       <c r="E37" t="n">
         <v>7040.15625</v>
       </c>
       <c r="F37" t="n">
-        <v>90.59999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>6799899000</v>
       </c>
       <c r="N37" t="n">
-        <v>13977829140</v>
+        <v>13998660480</v>
       </c>
     </row>
     <row r="38">
@@ -2372,16 +2372,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>86.2</v>
+        <v>86.7</v>
       </c>
       <c r="D38" t="n">
-        <v>2782</v>
+        <v>2767</v>
       </c>
       <c r="E38" t="n">
         <v>4265.455132343447</v>
       </c>
       <c r="F38" t="n">
-        <v>-34.8</v>
+        <v>-35.1</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>22869000000</v>
       </c>
       <c r="N38" t="n">
-        <v>26523081676</v>
+        <v>26380074406</v>
       </c>
     </row>
     <row r="39">
@@ -2427,13 +2427,13 @@
         <v>33.1</v>
       </c>
       <c r="D39" t="n">
-        <v>4655</v>
+        <v>4660</v>
       </c>
       <c r="E39" t="n">
         <v>2824.318397803668</v>
       </c>
       <c r="F39" t="n">
-        <v>64.8</v>
+        <v>65</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>61975000000</v>
       </c>
       <c r="N39" t="n">
-        <v>187273699025</v>
+        <v>187474852300</v>
       </c>
     </row>
     <row r="40">
@@ -2476,16 +2476,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>29.4</v>
+        <v>29.7</v>
       </c>
       <c r="D40" t="n">
-        <v>6570</v>
+        <v>6500</v>
       </c>
       <c r="E40" t="n">
         <v>3096.322467304314</v>
       </c>
       <c r="F40" t="n">
-        <v>112.2</v>
+        <v>109.9</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>52961000000</v>
       </c>
       <c r="N40" t="n">
-        <v>180235926900</v>
+        <v>178315605000</v>
       </c>
     </row>
     <row r="41">
@@ -2528,16 +2528,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>24.4</v>
+        <v>24</v>
       </c>
       <c r="D41" t="n">
-        <v>6147</v>
+        <v>6253</v>
       </c>
       <c r="E41" t="n">
         <v>3322.047887165483</v>
       </c>
       <c r="F41" t="n">
-        <v>85</v>
+        <v>88.2</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>492847000000</v>
       </c>
       <c r="N41" t="n">
-        <v>2019319915356</v>
+        <v>2054141439844</v>
       </c>
     </row>
     <row r="42">
@@ -2580,16 +2580,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>35.3</v>
+        <v>35.5</v>
       </c>
       <c r="D42" t="n">
-        <v>1745</v>
+        <v>1731</v>
       </c>
       <c r="E42" t="n">
         <v>2112.609181636727</v>
       </c>
       <c r="F42" t="n">
-        <v>-17.4</v>
+        <v>-18.1</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>52218000000</v>
       </c>
       <c r="N42" t="n">
-        <v>148111883150</v>
+        <v>146923592970</v>
       </c>
     </row>
     <row r="43">
@@ -2635,13 +2635,13 @@
         <v>3.8</v>
       </c>
       <c r="D43" t="n">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="E43" t="n">
         <v>404.9347366248775</v>
       </c>
       <c r="F43" t="n">
-        <v>73.59999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>7044972000</v>
       </c>
       <c r="N43" t="n">
-        <v>187410031815</v>
+        <v>186876859605</v>
       </c>
     </row>
     <row r="44">
@@ -2684,16 +2684,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="D44" t="n">
-        <v>2722</v>
+        <v>2591</v>
       </c>
       <c r="E44" t="n">
         <v>2220.184278344451</v>
       </c>
       <c r="F44" t="n">
-        <v>22.6</v>
+        <v>16.7</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>207116000000</v>
       </c>
       <c r="N44" t="n">
-        <v>3120255370870</v>
+        <v>2970088782485</v>
       </c>
     </row>
     <row r="45">
@@ -2736,16 +2736,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="D45" t="n">
-        <v>21610</v>
+        <v>21885</v>
       </c>
       <c r="E45" t="n">
         <v>11879.91675437757</v>
       </c>
       <c r="F45" t="n">
-        <v>81.90000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>191958000000</v>
       </c>
       <c r="N45" t="n">
-        <v>908085803550</v>
+        <v>919641731175</v>
       </c>
     </row>
     <row r="46">
@@ -2788,16 +2788,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>77.8</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>1053</v>
+        <v>1079</v>
       </c>
       <c r="E46" t="n">
         <v>730</v>
       </c>
       <c r="F46" t="n">
-        <v>44.2</v>
+        <v>47.8</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>50027000000</v>
       </c>
       <c r="N46" t="n">
-        <v>64290057858</v>
+        <v>65877466694</v>
       </c>
     </row>
     <row r="47">
@@ -2840,16 +2840,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>24.2</v>
+        <v>24.7</v>
       </c>
       <c r="D47" t="n">
-        <v>5399</v>
+        <v>5291</v>
       </c>
       <c r="E47" t="n">
         <v>3341.42986565678</v>
       </c>
       <c r="F47" t="n">
-        <v>61.6</v>
+        <v>58.3</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>311107000000</v>
       </c>
       <c r="N47" t="n">
-        <v>1282931398307</v>
+        <v>1257268017863</v>
       </c>
     </row>
     <row r="48">
@@ -2892,16 +2892,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>29.3</v>
+        <v>28.7</v>
       </c>
       <c r="D48" t="n">
-        <v>3150</v>
+        <v>3215</v>
       </c>
       <c r="E48" t="n">
         <v>2550.198980592041</v>
       </c>
       <c r="F48" t="n">
-        <v>23.5</v>
+        <v>26.1</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>32342000000</v>
       </c>
       <c r="N48" t="n">
-        <v>110277140400</v>
+        <v>112552700440</v>
       </c>
     </row>
     <row r="49">
@@ -2944,16 +2944,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>216.3</v>
+        <v>217.4</v>
       </c>
       <c r="D49" t="n">
-        <v>1600</v>
+        <v>1592</v>
       </c>
       <c r="E49" t="n">
         <v>1288.711724885291</v>
       </c>
       <c r="F49" t="n">
-        <v>24.2</v>
+        <v>23.5</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>747066000000</v>
       </c>
       <c r="N49" t="n">
-        <v>345414676800</v>
+        <v>343687603416</v>
       </c>
     </row>
     <row r="50">
@@ -2996,16 +2996,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>67.7</v>
+        <v>68.3</v>
       </c>
       <c r="D50" t="n">
-        <v>4062</v>
+        <v>4022</v>
       </c>
       <c r="E50" t="n">
         <v>3141.424011416125</v>
       </c>
       <c r="F50" t="n">
-        <v>29.3</v>
+        <v>28</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>391579000000</v>
       </c>
       <c r="N50" t="n">
-        <v>578817143448</v>
+        <v>573117319288</v>
       </c>
     </row>
     <row r="51">
@@ -3048,16 +3048,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>67.7</v>
+        <v>68.3</v>
       </c>
       <c r="D51" t="n">
-        <v>4062</v>
+        <v>4022</v>
       </c>
       <c r="E51" t="n">
         <v>2420</v>
       </c>
       <c r="F51" t="n">
-        <v>67.90000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>391579000000</v>
       </c>
       <c r="N51" t="n">
-        <v>578817143448</v>
+        <v>573117319288</v>
       </c>
     </row>
     <row r="52">
@@ -3100,16 +3100,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>41.4</v>
+        <v>42.6</v>
       </c>
       <c r="D52" t="n">
-        <v>4132</v>
+        <v>4015</v>
       </c>
       <c r="E52" t="n">
         <v>3047.091476167608</v>
       </c>
       <c r="F52" t="n">
-        <v>35.6</v>
+        <v>31.8</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>162458000000</v>
       </c>
       <c r="N52" t="n">
-        <v>392387392844</v>
+        <v>381276714005</v>
       </c>
     </row>
     <row r="53">
@@ -3152,16 +3152,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>45.4</v>
+        <v>45.8</v>
       </c>
       <c r="D53" t="n">
-        <v>3491</v>
+        <v>3460</v>
       </c>
       <c r="E53" t="n">
         <v>2844.704547285864</v>
       </c>
       <c r="F53" t="n">
-        <v>22.7</v>
+        <v>21.6</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>218675000000</v>
       </c>
       <c r="N53" t="n">
-        <v>482001015492</v>
+        <v>477720857520</v>
       </c>
     </row>
     <row r="54">
@@ -3207,13 +3207,13 @@
         <v>55.9</v>
       </c>
       <c r="D54" t="n">
-        <v>2217</v>
+        <v>2220</v>
       </c>
       <c r="E54" t="n">
         <v>1556.090471804319</v>
       </c>
       <c r="F54" t="n">
-        <v>42.5</v>
+        <v>42.7</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>207466000000</v>
       </c>
       <c r="N54" t="n">
-        <v>370807006485</v>
+        <v>371308775100</v>
       </c>
     </row>
     <row r="55">
@@ -3256,16 +3256,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="D55" t="n">
-        <v>1658</v>
+        <v>1652</v>
       </c>
       <c r="E55" t="n">
         <v>1529.631984751819</v>
       </c>
       <c r="F55" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>6024082000</v>
       </c>
       <c r="N55" t="n">
-        <v>11816846202</v>
+        <v>11774083188</v>
       </c>
     </row>
     <row r="56">
@@ -3308,16 +3308,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="D56" t="n">
-        <v>1658</v>
+        <v>1652</v>
       </c>
       <c r="E56" t="n">
         <v>1449.995380693296</v>
       </c>
       <c r="F56" t="n">
-        <v>14.3</v>
+        <v>13.9</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>6024082000</v>
       </c>
       <c r="N56" t="n">
-        <v>11816846202</v>
+        <v>11774083188</v>
       </c>
     </row>
     <row r="57">
@@ -3360,16 +3360,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>67.7</v>
+        <v>67.5</v>
       </c>
       <c r="D57" t="n">
-        <v>2952</v>
+        <v>2962</v>
       </c>
       <c r="E57" t="n">
         <v>2696.128808062088</v>
       </c>
       <c r="F57" t="n">
-        <v>9.5</v>
+        <v>9.9</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>165282000000</v>
       </c>
       <c r="N57" t="n">
-        <v>244025704368</v>
+        <v>244852349708</v>
       </c>
     </row>
     <row r="58">
@@ -3412,16 +3412,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>119.9</v>
+        <v>120.1</v>
       </c>
       <c r="D58" t="n">
-        <v>1561.5</v>
+        <v>1559.5</v>
       </c>
       <c r="E58" t="n">
         <v>1160.8</v>
       </c>
       <c r="F58" t="n">
-        <v>34.5</v>
+        <v>34.3</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>493483000000</v>
       </c>
       <c r="N58" t="n">
-        <v>411465370082</v>
+        <v>410938357120</v>
       </c>
     </row>
     <row r="59">
@@ -3464,16 +3464,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="D59" t="n">
-        <v>2972</v>
+        <v>2959</v>
       </c>
       <c r="E59" t="n">
         <v>2007.754513143541</v>
       </c>
       <c r="F59" t="n">
-        <v>48</v>
+        <v>47.4</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>37208000000</v>
       </c>
       <c r="N59" t="n">
-        <v>158327150932</v>
+        <v>157634602829</v>
       </c>
     </row>
     <row r="60">
@@ -3516,16 +3516,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>14.8</v>
+        <v>15.3</v>
       </c>
       <c r="D60" t="n">
-        <v>3015</v>
+        <v>2920</v>
       </c>
       <c r="E60" t="n">
         <v>2261.880826568852</v>
       </c>
       <c r="F60" t="n">
-        <v>33.3</v>
+        <v>29.1</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>102508000000</v>
       </c>
       <c r="N60" t="n">
-        <v>691230637395</v>
+        <v>669450567560</v>
       </c>
     </row>
     <row r="61">
@@ -3568,16 +3568,16 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>14.8</v>
+        <v>15.3</v>
       </c>
       <c r="D61" t="n">
-        <v>3015</v>
+        <v>2920</v>
       </c>
       <c r="E61" t="n">
         <v>1970</v>
       </c>
       <c r="F61" t="n">
-        <v>53</v>
+        <v>48.2</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>102508000000</v>
       </c>
       <c r="N61" t="n">
-        <v>691230637395</v>
+        <v>669450567560</v>
       </c>
     </row>
     <row r="62">
@@ -3623,13 +3623,13 @@
         <v>9.6</v>
       </c>
       <c r="D62" t="n">
-        <v>2853</v>
+        <v>2854</v>
       </c>
       <c r="E62" t="n">
         <v>1910.426979628923</v>
       </c>
       <c r="F62" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>53660000000</v>
       </c>
       <c r="N62" t="n">
-        <v>556848888066</v>
+        <v>557044068188</v>
       </c>
     </row>
     <row r="63">
@@ -3672,16 +3672,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>50.3</v>
+        <v>50.6</v>
       </c>
       <c r="D63" t="n">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E63" t="n">
         <v>290.3401328717133</v>
       </c>
       <c r="F63" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>5162755000</v>
       </c>
       <c r="N63" t="n">
-        <v>10272928344</v>
+        <v>10203516666</v>
       </c>
     </row>
     <row r="64">
@@ -3864,16 +3864,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>74.2</v>
+        <v>77.8</v>
       </c>
       <c r="D67" t="n">
-        <v>2610.5</v>
+        <v>2489</v>
       </c>
       <c r="E67" t="n">
         <v>2551.08574256026</v>
       </c>
       <c r="F67" t="n">
-        <v>2.3</v>
+        <v>-2.4</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>179136000000</v>
       </c>
       <c r="N67" t="n">
-        <v>241501638830</v>
+        <v>230261474449</v>
       </c>
     </row>
     <row r="68">
@@ -3916,16 +3916,16 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>74.2</v>
+        <v>77.8</v>
       </c>
       <c r="D68" t="n">
-        <v>2610.5</v>
+        <v>2489</v>
       </c>
       <c r="E68" t="n">
         <v>2260</v>
       </c>
       <c r="F68" t="n">
-        <v>15.5</v>
+        <v>10.1</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>179136000000</v>
       </c>
       <c r="N68" t="n">
-        <v>241501638830</v>
+        <v>230261474449</v>
       </c>
     </row>
     <row r="69">
@@ -3968,16 +3968,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>74.2</v>
+        <v>77.8</v>
       </c>
       <c r="D69" t="n">
-        <v>2610.5</v>
+        <v>2489</v>
       </c>
       <c r="E69" t="n">
         <v>2260</v>
       </c>
       <c r="F69" t="n">
-        <v>15.5</v>
+        <v>10.1</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>179136000000</v>
       </c>
       <c r="N69" t="n">
-        <v>241501638830</v>
+        <v>230261474449</v>
       </c>
     </row>
     <row r="70">
@@ -4020,16 +4020,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>309.7</v>
+        <v>312.3</v>
       </c>
       <c r="D70" t="n">
-        <v>847</v>
+        <v>840</v>
       </c>
       <c r="E70" t="n">
         <v>798.3805136422309</v>
       </c>
       <c r="F70" t="n">
-        <v>6.1</v>
+        <v>5.2</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>449038000000</v>
       </c>
       <c r="N70" t="n">
-        <v>144994426808</v>
+        <v>143796125760</v>
       </c>
     </row>
     <row r="71">
@@ -4072,16 +4072,16 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>43.2</v>
+        <v>42.6</v>
       </c>
       <c r="D71" t="n">
-        <v>2562.5</v>
+        <v>2594</v>
       </c>
       <c r="E71" t="n">
         <v>2032.365850102071</v>
       </c>
       <c r="F71" t="n">
-        <v>26.1</v>
+        <v>27.6</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>340592000000</v>
       </c>
       <c r="N71" t="n">
-        <v>788969524125</v>
+        <v>798668076324</v>
       </c>
     </row>
     <row r="72">
@@ -4124,16 +4124,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>61.8</v>
+        <v>61.1</v>
       </c>
       <c r="D72" t="n">
-        <v>3600</v>
+        <v>3638</v>
       </c>
       <c r="E72" t="n">
         <v>1716.713876475349</v>
       </c>
       <c r="F72" t="n">
-        <v>109.7</v>
+        <v>111.9</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>565345000000</v>
       </c>
       <c r="N72" t="n">
-        <v>915040036800</v>
+        <v>924698792744</v>
       </c>
     </row>
     <row r="73">
@@ -4177,16 +4177,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>31.5</v>
+        <v>30.7</v>
       </c>
       <c r="D73" t="n">
-        <v>9130</v>
+        <v>9370</v>
       </c>
       <c r="E73" t="n">
         <v>4037.502552255647</v>
       </c>
       <c r="F73" t="n">
-        <v>126.1</v>
+        <v>132.1</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>154738000000</v>
       </c>
       <c r="N73" t="n">
-        <v>491228356190</v>
+        <v>504141259310</v>
       </c>
     </row>
     <row r="74">
@@ -4230,16 +4230,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>31.5</v>
+        <v>30.7</v>
       </c>
       <c r="D74" t="n">
-        <v>9130</v>
+        <v>9370</v>
       </c>
       <c r="E74" t="n">
         <v>3950.736048458928</v>
       </c>
       <c r="F74" t="n">
-        <v>131.1</v>
+        <v>137.2</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>154738000000</v>
       </c>
       <c r="N74" t="n">
-        <v>491228356190</v>
+        <v>504141259310</v>
       </c>
     </row>
     <row r="75">
@@ -4283,16 +4283,16 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>31.5</v>
+        <v>30.7</v>
       </c>
       <c r="D75" t="n">
-        <v>9130</v>
+        <v>9370</v>
       </c>
       <c r="E75" t="n">
         <v>2030</v>
       </c>
       <c r="F75" t="n">
-        <v>349.8</v>
+        <v>361.6</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>154738000000</v>
       </c>
       <c r="N75" t="n">
-        <v>491228356190</v>
+        <v>504141259310</v>
       </c>
     </row>
     <row r="76">
@@ -4336,16 +4336,16 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>31.5</v>
+        <v>30.7</v>
       </c>
       <c r="D76" t="n">
-        <v>9130</v>
+        <v>9370</v>
       </c>
       <c r="E76" t="n">
         <v>2387</v>
       </c>
       <c r="F76" t="n">
-        <v>282.5</v>
+        <v>292.5</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>154738000000</v>
       </c>
       <c r="N76" t="n">
-        <v>491228356190</v>
+        <v>504141259310</v>
       </c>
     </row>
     <row r="77">
@@ -4388,16 +4388,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>78</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="D77" t="n">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="E77" t="n">
         <v>668.9358717434869</v>
       </c>
       <c r="F77" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>12410000000</v>
       </c>
       <c r="N77" t="n">
-        <v>15901907958</v>
+        <v>15885893952</v>
       </c>
     </row>
     <row r="78">
@@ -4440,16 +4440,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>72.09999999999999</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D78" t="n">
-        <v>2640</v>
+        <v>2610</v>
       </c>
       <c r="E78" t="n">
         <v>1190</v>
       </c>
       <c r="F78" t="n">
-        <v>121.8</v>
+        <v>119.3</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>40500000000</v>
       </c>
       <c r="N78" t="n">
-        <v>56210476080</v>
+        <v>55571720670</v>
       </c>
     </row>
     <row r="79">
@@ -4492,16 +4492,16 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="D79" t="n">
-        <v>5910</v>
+        <v>5890</v>
       </c>
       <c r="E79" t="n">
         <v>2617.980935875217</v>
       </c>
       <c r="F79" t="n">
-        <v>125.7</v>
+        <v>125</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>40238000000</v>
       </c>
       <c r="N79" t="n">
-        <v>212544344100</v>
+        <v>211825073900</v>
       </c>
     </row>
     <row r="80">
@@ -4544,16 +4544,16 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>20.5</v>
+        <v>20.1</v>
       </c>
       <c r="D80" t="n">
-        <v>2750</v>
+        <v>2803</v>
       </c>
       <c r="E80" t="n">
         <v>2084.177692465894</v>
       </c>
       <c r="F80" t="n">
-        <v>31.9</v>
+        <v>34.5</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         <v>15433000000</v>
       </c>
       <c r="N80" t="n">
-        <v>75315132750</v>
+        <v>76766660763</v>
       </c>
     </row>
     <row r="81">
@@ -4596,16 +4596,16 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="D81" t="n">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="E81" t="n">
         <v>448.6811097117532</v>
       </c>
       <c r="F81" t="n">
-        <v>14.6</v>
+        <v>12.8</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>13953300000</v>
       </c>
       <c r="N81" t="n">
-        <v>104992048604</v>
+        <v>103357931116</v>
       </c>
     </row>
     <row r="82">
@@ -4648,16 +4648,16 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>34.5</v>
+        <v>35.2</v>
       </c>
       <c r="D82" t="n">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="E82" t="n">
         <v>421.6950726175476</v>
       </c>
       <c r="F82" t="n">
-        <v>-23.9</v>
+        <v>-25.3</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>3109655000</v>
       </c>
       <c r="N82" t="n">
-        <v>9001670748</v>
+        <v>8833415220</v>
       </c>
     </row>
     <row r="83">
@@ -4700,16 +4700,16 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>71.8</v>
+        <v>72.5</v>
       </c>
       <c r="D83" t="n">
-        <v>3905</v>
+        <v>3865</v>
       </c>
       <c r="E83" t="n">
         <v>3530</v>
       </c>
       <c r="F83" t="n">
-        <v>10.6</v>
+        <v>9.5</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>106147000000</v>
       </c>
       <c r="N83" t="n">
-        <v>147875770075</v>
+        <v>146361037475</v>
       </c>
     </row>
     <row r="84">
@@ -4752,16 +4752,16 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>35.3</v>
+        <v>36</v>
       </c>
       <c r="D84" t="n">
-        <v>563</v>
+        <v>552</v>
       </c>
       <c r="E84" t="n">
         <v>549.4799823005444</v>
       </c>
       <c r="F84" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>19115000000</v>
       </c>
       <c r="N84" t="n">
-        <v>54219382830</v>
+        <v>53160034320</v>
       </c>
     </row>
     <row r="85">
@@ -4804,16 +4804,16 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>46.3</v>
+        <v>46.4</v>
       </c>
       <c r="D85" t="n">
-        <v>1699</v>
+        <v>1695</v>
       </c>
       <c r="E85" t="n">
         <v>1752.426893379333</v>
       </c>
       <c r="F85" t="n">
-        <v>-3</v>
+        <v>-3.3</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>76232495000</v>
       </c>
       <c r="N85" t="n">
-        <v>164813363900</v>
+        <v>164425339500</v>
       </c>
     </row>
     <row r="86">
@@ -4856,16 +4856,16 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>46.3</v>
+        <v>46.4</v>
       </c>
       <c r="D86" t="n">
-        <v>1699</v>
+        <v>1695</v>
       </c>
       <c r="E86" t="n">
         <v>1576.721867844292</v>
       </c>
       <c r="F86" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>76232495000</v>
       </c>
       <c r="N86" t="n">
-        <v>164813363900</v>
+        <v>164425339500</v>
       </c>
     </row>
     <row r="87">
@@ -4908,16 +4908,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>64.8</v>
+        <v>65.3</v>
       </c>
       <c r="D87" t="n">
-        <v>2117</v>
+        <v>2101</v>
       </c>
       <c r="E87" t="n">
         <v>1101.400153022188</v>
       </c>
       <c r="F87" t="n">
-        <v>92.2</v>
+        <v>90.8</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>402053000000</v>
       </c>
       <c r="N87" t="n">
-        <v>620311484800</v>
+        <v>615623254400</v>
       </c>
     </row>
     <row r="88">
@@ -4960,16 +4960,16 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>64.8</v>
+        <v>65.3</v>
       </c>
       <c r="D88" t="n">
-        <v>2117</v>
+        <v>2101</v>
       </c>
       <c r="E88" t="n">
         <v>1101.400153022188</v>
       </c>
       <c r="F88" t="n">
-        <v>92.2</v>
+        <v>90.8</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>402053000000</v>
       </c>
       <c r="N88" t="n">
-        <v>620311484800</v>
+        <v>615623254400</v>
       </c>
     </row>
     <row r="89">
@@ -5012,16 +5012,16 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>44.9</v>
+        <v>44.8</v>
       </c>
       <c r="D89" t="n">
-        <v>3342</v>
+        <v>3353</v>
       </c>
       <c r="E89" t="n">
         <v>1492.806001579363</v>
       </c>
       <c r="F89" t="n">
-        <v>123.9</v>
+        <v>124.6</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>112301000000</v>
       </c>
       <c r="N89" t="n">
-        <v>249995920470</v>
+        <v>250818767605</v>
       </c>
     </row>
     <row r="90">
@@ -5064,16 +5064,16 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>81.5</v>
+        <v>81</v>
       </c>
       <c r="D90" t="n">
-        <v>1115</v>
+        <v>1121</v>
       </c>
       <c r="E90" t="n">
         <v>1341.977644710579</v>
       </c>
       <c r="F90" t="n">
-        <v>-16.9</v>
+        <v>-16.5</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>86654000000</v>
       </c>
       <c r="N90" t="n">
-        <v>106376198130</v>
+        <v>106948626102</v>
       </c>
     </row>
     <row r="91">
@@ -5116,16 +5116,16 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>25.9</v>
+        <v>26.8</v>
       </c>
       <c r="D91" t="n">
-        <v>4100</v>
+        <v>3967</v>
       </c>
       <c r="E91" t="n">
         <v>2006.059650428343</v>
       </c>
       <c r="F91" t="n">
-        <v>104.4</v>
+        <v>97.8</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>173440000000</v>
       </c>
       <c r="N91" t="n">
-        <v>669040529700</v>
+        <v>647337507639</v>
       </c>
     </row>
     <row r="92">
@@ -5171,13 +5171,13 @@
         <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>1876</v>
+        <v>1845</v>
       </c>
       <c r="E92" t="n">
         <v>2697.360927565142</v>
       </c>
       <c r="F92" t="n">
-        <v>-30.5</v>
+        <v>-31.6</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
         <v>7339000000</v>
       </c>
       <c r="N92" t="n">
-        <v>731589329240</v>
+        <v>719500166550</v>
       </c>
     </row>
     <row r="93">
@@ -5220,16 +5220,16 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>17.7</v>
+        <v>17.5</v>
       </c>
       <c r="D93" t="n">
-        <v>4410</v>
+        <v>4470</v>
       </c>
       <c r="E93" t="n">
         <v>7960</v>
       </c>
       <c r="F93" t="n">
-        <v>-44.6</v>
+        <v>-43.8</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -5257,7 +5257,7 @@
         <v>29865000000</v>
       </c>
       <c r="N93" t="n">
-        <v>168554848140</v>
+        <v>170848111380</v>
       </c>
     </row>
     <row r="94">
@@ -5272,16 +5272,16 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="D94" t="n">
-        <v>5459</v>
+        <v>5467</v>
       </c>
       <c r="E94" t="n">
         <v>3735.709461270437</v>
       </c>
       <c r="F94" t="n">
-        <v>46.1</v>
+        <v>46.3</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>110688000000</v>
       </c>
       <c r="N94" t="n">
-        <v>626606571129</v>
+        <v>627524844177</v>
       </c>
     </row>
     <row r="95">
@@ -5324,16 +5324,16 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>29.9</v>
+        <v>30.2</v>
       </c>
       <c r="D95" t="n">
-        <v>2151</v>
+        <v>2129</v>
       </c>
       <c r="E95" t="n">
         <v>5463.67048346056</v>
       </c>
       <c r="F95" t="n">
-        <v>-60.6</v>
+        <v>-61</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v>11249000000</v>
       </c>
       <c r="N95" t="n">
-        <v>37624410090</v>
+        <v>37239595110</v>
       </c>
     </row>
     <row r="96">
@@ -5376,16 +5376,16 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>26.1</v>
+        <v>25.9</v>
       </c>
       <c r="D96" t="n">
-        <v>1398</v>
+        <v>1406</v>
       </c>
       <c r="E96" t="n">
         <v>3234.727863989046</v>
       </c>
       <c r="F96" t="n">
-        <v>-56.8</v>
+        <v>-56.5</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>52215000000</v>
       </c>
       <c r="N96" t="n">
-        <v>200262856920</v>
+        <v>201408853240</v>
       </c>
     </row>
     <row r="97">
@@ -5428,16 +5428,16 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>34.2</v>
+        <v>34.9</v>
       </c>
       <c r="D97" t="n">
-        <v>3205</v>
+        <v>3140</v>
       </c>
       <c r="E97" t="n">
         <v>3155.301177013616</v>
       </c>
       <c r="F97" t="n">
-        <v>1.6</v>
+        <v>-0.5</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>70480000000</v>
       </c>
       <c r="N97" t="n">
-        <v>205910987590</v>
+        <v>201734945720</v>
       </c>
     </row>
     <row r="98">
@@ -5483,13 +5483,13 @@
         <v>5.8</v>
       </c>
       <c r="D98" t="n">
-        <v>3213</v>
+        <v>3231</v>
       </c>
       <c r="E98" t="n">
         <v>2655.311711736394</v>
       </c>
       <c r="F98" t="n">
-        <v>21</v>
+        <v>21.7</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>33115000000</v>
       </c>
       <c r="N98" t="n">
-        <v>569761306065</v>
+        <v>572953246155</v>
       </c>
     </row>
     <row r="99">
@@ -5532,16 +5532,16 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="D99" t="n">
-        <v>912.9000244140625</v>
+        <v>915</v>
       </c>
       <c r="E99" t="n">
         <v>2157.626835069302</v>
       </c>
       <c r="F99" t="n">
-        <v>-57.7</v>
+        <v>-57.6</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>152963000000</v>
       </c>
       <c r="N99" t="n">
-        <v>378342350934</v>
+        <v>379212664965</v>
       </c>
     </row>
     <row r="100">
@@ -5639,13 +5639,13 @@
         <v>10</v>
       </c>
       <c r="D101" t="n">
-        <v>2037</v>
+        <v>2047</v>
       </c>
       <c r="E101" t="n">
         <v>2300.974351689521</v>
       </c>
       <c r="F101" t="n">
-        <v>-11.5</v>
+        <v>-11</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         <v>8549173000</v>
       </c>
       <c r="N101" t="n">
-        <v>85463455350</v>
+        <v>85883010850</v>
       </c>
     </row>
     <row r="102">
@@ -5688,16 +5688,16 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>39.6</v>
+        <v>39.8</v>
       </c>
       <c r="D102" t="n">
-        <v>1612</v>
+        <v>1605</v>
       </c>
       <c r="E102" t="n">
-        <v>1180.431728045326</v>
+        <v>1180.406015389293</v>
       </c>
       <c r="F102" t="n">
-        <v>36.6</v>
+        <v>36</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="I102" t="n">
@@ -5725,7 +5725,7 @@
         <v>29529000000</v>
       </c>
       <c r="N102" t="n">
-        <v>74492596256</v>
+        <v>74169117240</v>
       </c>
     </row>
     <row r="103">
@@ -5740,16 +5740,16 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>39.6</v>
+        <v>39.8</v>
       </c>
       <c r="D103" t="n">
-        <v>1612</v>
+        <v>1605</v>
       </c>
       <c r="E103" t="n">
-        <v>1180.442269658324</v>
+        <v>1180.420176850555</v>
       </c>
       <c r="F103" t="n">
-        <v>36.6</v>
+        <v>36</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="I103" t="n">
@@ -5777,7 +5777,7 @@
         <v>29529000000</v>
       </c>
       <c r="N103" t="n">
-        <v>74492596256</v>
+        <v>74169117240</v>
       </c>
     </row>
     <row r="104">
@@ -5792,16 +5792,16 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>39.6</v>
+        <v>39.8</v>
       </c>
       <c r="D104" t="n">
-        <v>1612</v>
+        <v>1605</v>
       </c>
       <c r="E104" t="n">
-        <v>1180.450912709519</v>
+        <v>1180.431728045326</v>
       </c>
       <c r="F104" t="n">
-        <v>36.6</v>
+        <v>36</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="I104" t="n">
@@ -5829,7 +5829,7 @@
         <v>29529000000</v>
       </c>
       <c r="N104" t="n">
-        <v>74492596256</v>
+        <v>74169117240</v>
       </c>
     </row>
     <row r="105">
@@ -5844,16 +5844,16 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>39.6</v>
+        <v>39.8</v>
       </c>
       <c r="D105" t="n">
-        <v>1612</v>
+        <v>1605</v>
       </c>
       <c r="E105" t="n">
-        <v>1180.45745232471</v>
+        <v>1180.442269658324</v>
       </c>
       <c r="F105" t="n">
-        <v>36.6</v>
+        <v>36</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="I105" t="n">
@@ -5881,7 +5881,7 @@
         <v>29529000000</v>
       </c>
       <c r="N105" t="n">
-        <v>74492596256</v>
+        <v>74169117240</v>
       </c>
     </row>
     <row r="106">
@@ -5896,16 +5896,16 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>39.6</v>
+        <v>39.8</v>
       </c>
       <c r="D106" t="n">
-        <v>1612</v>
+        <v>1605</v>
       </c>
       <c r="E106" t="n">
-        <v>1180.463123164206</v>
+        <v>1180.450912709519</v>
       </c>
       <c r="F106" t="n">
-        <v>36.6</v>
+        <v>36</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="I106" t="n">
@@ -5933,7 +5933,7 @@
         <v>29529000000</v>
       </c>
       <c r="N106" t="n">
-        <v>74492596256</v>
+        <v>74169117240</v>
       </c>
     </row>
     <row r="107">
@@ -5948,16 +5948,16 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>39.6</v>
+        <v>39.8</v>
       </c>
       <c r="D107" t="n">
-        <v>1612</v>
+        <v>1605</v>
       </c>
       <c r="E107" t="n">
-        <v>1170.279952698077</v>
+        <v>1180.45745232471</v>
       </c>
       <c r="F107" t="n">
-        <v>37.7</v>
+        <v>36</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="I107" t="n">
@@ -5985,7 +5985,7 @@
         <v>29529000000</v>
       </c>
       <c r="N107" t="n">
-        <v>74492596256</v>
+        <v>74169117240</v>
       </c>
     </row>
     <row r="108">
@@ -6000,16 +6000,16 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>39.6</v>
+        <v>39.8</v>
       </c>
       <c r="D108" t="n">
-        <v>1612</v>
+        <v>1605</v>
       </c>
       <c r="E108" t="n">
-        <v>1169.924818603025</v>
+        <v>1180.463123164206</v>
       </c>
       <c r="F108" t="n">
-        <v>37.8</v>
+        <v>36</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="I108" t="n">
@@ -6037,7 +6037,7 @@
         <v>29529000000</v>
       </c>
       <c r="N108" t="n">
-        <v>74492596256</v>
+        <v>74169117240</v>
       </c>
     </row>
     <row r="109">
@@ -6052,16 +6052,16 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>39.6</v>
+        <v>39.8</v>
       </c>
       <c r="D109" t="n">
-        <v>1612</v>
+        <v>1605</v>
       </c>
       <c r="E109" t="n">
-        <v>1168.709522546084</v>
+        <v>1170.279952698077</v>
       </c>
       <c r="F109" t="n">
-        <v>37.9</v>
+        <v>37.1</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="I109" t="n">
@@ -6089,31 +6089,31 @@
         <v>29529000000</v>
       </c>
       <c r="N109" t="n">
-        <v>74492596256</v>
+        <v>74169117240</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>山洋電気株式会社</t>
+          <t>東亜道路工業株式会社</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>12.2</v>
+        <v>39.8</v>
       </c>
       <c r="D110" t="n">
-        <v>5070</v>
+        <v>1605</v>
       </c>
       <c r="E110" t="n">
-        <v>7052.737306843267</v>
+        <v>1169.924818603025</v>
       </c>
       <c r="F110" t="n">
-        <v>-28.1</v>
+        <v>37.2</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -6122,154 +6122,154 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>8317000000</v>
+        <v>11649000000</v>
       </c>
       <c r="J110" t="n">
-        <v>6048000000</v>
+        <v>13793000000</v>
       </c>
       <c r="K110" t="n">
-        <v>7673000000</v>
+        <v>4087000000</v>
       </c>
       <c r="L110" t="n">
-        <v>49734000000</v>
+        <v>50605000000</v>
       </c>
       <c r="M110" t="n">
-        <v>22038000000</v>
+        <v>29529000000</v>
       </c>
       <c r="N110" t="n">
-        <v>180061257870</v>
+        <v>74169117240</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ヘリオス テクノ ホールディング株式会社</t>
+          <t>東亜道路工業株式会社</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>53.7</v>
+        <v>39.8</v>
       </c>
       <c r="D111" t="n">
-        <v>982</v>
+        <v>1605</v>
       </c>
       <c r="E111" t="n">
-        <v>896.0103264198827</v>
+        <v>1168.709522546084</v>
       </c>
       <c r="F111" t="n">
-        <v>9.6</v>
+        <v>37.3</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>7851015000</v>
+        <v>11649000000</v>
       </c>
       <c r="J111" t="n">
-        <v>640317000</v>
+        <v>13793000000</v>
       </c>
       <c r="K111" t="n">
-        <v>1079200000</v>
+        <v>4087000000</v>
       </c>
       <c r="L111" t="n">
-        <v>13746774000</v>
+        <v>50605000000</v>
       </c>
       <c r="M111" t="n">
-        <v>9570532000</v>
+        <v>29529000000</v>
       </c>
       <c r="N111" t="n">
-        <v>17824936994</v>
+        <v>74169117240</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>シェアリングテクノロジー株式会社</t>
+          <t>山洋電気株式会社</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="D112" t="n">
-        <v>1498</v>
+        <v>5180</v>
       </c>
       <c r="E112" t="n">
-        <v>653.0713101160862</v>
+        <v>7052.737306843267</v>
       </c>
       <c r="F112" t="n">
-        <v>129.4</v>
+        <v>-26.6</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>4016706000</v>
+        <v>8317000000</v>
       </c>
       <c r="J112" t="n">
-        <v>309745000</v>
+        <v>6048000000</v>
       </c>
       <c r="K112" t="n">
-        <v>0</v>
+        <v>7673000000</v>
       </c>
       <c r="L112" t="n">
-        <v>185001000</v>
+        <v>49734000000</v>
       </c>
       <c r="M112" t="n">
-        <v>4326451000</v>
+        <v>22038000000</v>
       </c>
       <c r="N112" t="n">
-        <v>35849040962</v>
+        <v>183967912380</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>栄研化学株式会社</t>
+          <t>ヘリオス テクノ ホールディング株式会社</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>30.7</v>
+        <v>54.6</v>
       </c>
       <c r="D113" t="n">
-        <v>2263</v>
+        <v>966</v>
       </c>
       <c r="E113" t="n">
-        <v>1947.225264702313</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="F113" t="n">
-        <v>16.2</v>
+        <v>7.8</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -6278,50 +6278,50 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>10900000000</v>
+        <v>7851015000</v>
       </c>
       <c r="J113" t="n">
-        <v>11585000000</v>
+        <v>640317000</v>
       </c>
       <c r="K113" t="n">
-        <v>408000000</v>
+        <v>1079200000</v>
       </c>
       <c r="L113" t="n">
-        <v>45803000000</v>
+        <v>13746774000</v>
       </c>
       <c r="M113" t="n">
-        <v>22893000000</v>
+        <v>9570532000</v>
       </c>
       <c r="N113" t="n">
-        <v>74601091699</v>
+        <v>17534510322</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>栄研化学株式会社</t>
+          <t>シェアリングテクノロジー株式会社</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>30.7</v>
+        <v>12.3</v>
       </c>
       <c r="D114" t="n">
-        <v>2263</v>
+        <v>1465</v>
       </c>
       <c r="E114" t="n">
-        <v>1678.083113259255</v>
+        <v>653.0713101160862</v>
       </c>
       <c r="F114" t="n">
-        <v>34.9</v>
+        <v>124.3</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -6330,154 +6330,154 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>10900000000</v>
+        <v>4016706000</v>
       </c>
       <c r="J114" t="n">
-        <v>11585000000</v>
+        <v>309745000</v>
       </c>
       <c r="K114" t="n">
-        <v>408000000</v>
+        <v>0</v>
       </c>
       <c r="L114" t="n">
-        <v>45803000000</v>
+        <v>185001000</v>
       </c>
       <c r="M114" t="n">
-        <v>22893000000</v>
+        <v>4326451000</v>
       </c>
       <c r="N114" t="n">
-        <v>74601091699</v>
+        <v>35059309085</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>株式会社ヤマダホールディングス</t>
+          <t>栄研化学株式会社</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>9831</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>60.2</v>
+        <v>30.7</v>
       </c>
       <c r="D115" t="n">
-        <v>693</v>
+        <v>2262</v>
       </c>
       <c r="E115" t="n">
-        <v>530</v>
+        <v>1947.225264702313</v>
       </c>
       <c r="F115" t="n">
-        <v>30.8</v>
+        <v>16.2</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>56470000000</v>
+        <v>10900000000</v>
       </c>
       <c r="J115" t="n">
-        <v>210733000000</v>
+        <v>11585000000</v>
       </c>
       <c r="K115" t="n">
-        <v>9997000000</v>
+        <v>408000000</v>
       </c>
       <c r="L115" t="n">
-        <v>676277000000</v>
+        <v>45803000000</v>
       </c>
       <c r="M115" t="n">
-        <v>277200000000</v>
+        <v>22893000000</v>
       </c>
       <c r="N115" t="n">
-        <v>460827975069</v>
+        <v>74568126126</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>日本化薬株式会社</t>
+          <t>栄研化学株式会社</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>36.1</v>
+        <v>30.7</v>
       </c>
       <c r="D116" t="n">
-        <v>2013</v>
+        <v>2262</v>
       </c>
       <c r="E116" t="n">
-        <v>1111.90611839092</v>
+        <v>1678.083113259255</v>
       </c>
       <c r="F116" t="n">
-        <v>81</v>
+        <v>34.8</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>52962000000</v>
+        <v>10900000000</v>
       </c>
       <c r="J116" t="n">
-        <v>48231000000</v>
+        <v>11585000000</v>
       </c>
       <c r="K116" t="n">
-        <v>4337000000</v>
+        <v>408000000</v>
       </c>
       <c r="L116" t="n">
-        <v>246425000000</v>
+        <v>45803000000</v>
       </c>
       <c r="M116" t="n">
-        <v>105530000000</v>
+        <v>22893000000</v>
       </c>
       <c r="N116" t="n">
-        <v>292633862169</v>
+        <v>74568126126</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>王子ホールディングス株式会社</t>
+          <t>株式会社ヤマダホールディングス</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>9831</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>41.6</v>
+        <v>60.1</v>
       </c>
       <c r="D117" t="n">
-        <v>870.2000122070312</v>
+        <v>693.0999755859375</v>
       </c>
       <c r="E117" t="n">
-        <v>590</v>
+        <v>530</v>
       </c>
       <c r="F117" t="n">
-        <v>47.5</v>
+        <v>30.8</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -6486,310 +6486,310 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>55474000000</v>
+        <v>56470000000</v>
       </c>
       <c r="J117" t="n">
-        <v>244732000000</v>
+        <v>210733000000</v>
       </c>
       <c r="K117" t="n">
-        <v>7434000000</v>
+        <v>9997000000</v>
       </c>
       <c r="L117" t="n">
-        <v>875470000000</v>
+        <v>676277000000</v>
       </c>
       <c r="M117" t="n">
-        <v>307640000000</v>
+        <v>277200000000</v>
       </c>
       <c r="N117" t="n">
-        <v>739003692135</v>
+        <v>460894456378</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>東邦ホールディングス株式会社</t>
+          <t>日本化薬株式会社</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>50.9</v>
+        <v>35.7</v>
       </c>
       <c r="D118" t="n">
-        <v>3987</v>
+        <v>2033.5</v>
       </c>
       <c r="E118" t="n">
-        <v>3405.914389596362</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="F118" t="n">
-        <v>17.1</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>90014000000</v>
+        <v>52962000000</v>
       </c>
       <c r="J118" t="n">
-        <v>34220000000</v>
+        <v>48231000000</v>
       </c>
       <c r="K118" t="n">
-        <v>7000000000</v>
+        <v>4337000000</v>
       </c>
       <c r="L118" t="n">
-        <v>241281000000</v>
+        <v>246425000000</v>
       </c>
       <c r="M118" t="n">
-        <v>131234000000</v>
+        <v>105530000000</v>
       </c>
       <c r="N118" t="n">
-        <v>257965370901</v>
+        <v>295613988436</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>東邦ホールディングス株式会社</t>
+          <t>王子ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>50.9</v>
+        <v>41.9</v>
       </c>
       <c r="D119" t="n">
-        <v>3987</v>
+        <v>864</v>
       </c>
       <c r="E119" t="n">
-        <v>2714.613787300615</v>
+        <v>590</v>
       </c>
       <c r="F119" t="n">
-        <v>46.9</v>
+        <v>46.4</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>90014000000</v>
+        <v>55474000000</v>
       </c>
       <c r="J119" t="n">
-        <v>34220000000</v>
+        <v>244732000000</v>
       </c>
       <c r="K119" t="n">
-        <v>7000000000</v>
+        <v>7434000000</v>
       </c>
       <c r="L119" t="n">
-        <v>241281000000</v>
+        <v>875470000000</v>
       </c>
       <c r="M119" t="n">
-        <v>131234000000</v>
+        <v>307640000000</v>
       </c>
       <c r="N119" t="n">
-        <v>257965370901</v>
+        <v>733738429152</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>株式会社アイネス</t>
+          <t>東邦ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>9742</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>35.1</v>
+        <v>51.3</v>
       </c>
       <c r="D120" t="n">
-        <v>2070</v>
+        <v>3954</v>
       </c>
       <c r="E120" t="n">
-        <v>1879.137815927515</v>
+        <v>3405.914389596362</v>
       </c>
       <c r="F120" t="n">
-        <v>10.2</v>
+        <v>16.1</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>9731000000</v>
+        <v>90014000000</v>
       </c>
       <c r="J120" t="n">
-        <v>5286000000</v>
+        <v>34220000000</v>
       </c>
       <c r="K120" t="n">
-        <v>100000000</v>
+        <v>7000000000</v>
       </c>
       <c r="L120" t="n">
-        <v>34620000000</v>
+        <v>241281000000</v>
       </c>
       <c r="M120" t="n">
-        <v>15117000000</v>
+        <v>131234000000</v>
       </c>
       <c r="N120" t="n">
-        <v>43102465290</v>
+        <v>255830217342</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>日本ゼオン株式会社</t>
+          <t>東邦ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>35.8</v>
+        <v>51.3</v>
       </c>
       <c r="D121" t="n">
-        <v>2354</v>
+        <v>3954</v>
       </c>
       <c r="E121" t="n">
-        <v>1721.078563209627</v>
+        <v>2714.613787300615</v>
       </c>
       <c r="F121" t="n">
-        <v>36.8</v>
+        <v>45.7</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>44521000000</v>
+        <v>90014000000</v>
       </c>
       <c r="J121" t="n">
-        <v>45382000000</v>
+        <v>34220000000</v>
       </c>
       <c r="K121" t="n">
-        <v>71191000000</v>
+        <v>7000000000</v>
       </c>
       <c r="L121" t="n">
-        <v>321836000000</v>
+        <v>241281000000</v>
       </c>
       <c r="M121" t="n">
-        <v>161094000000</v>
+        <v>131234000000</v>
       </c>
       <c r="N121" t="n">
-        <v>450427323478</v>
+        <v>255830217342</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>太陽ホールディングス株式会社</t>
+          <t>株式会社アイネス</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>9742</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>16.5</v>
+        <v>35.5</v>
       </c>
       <c r="D122" t="n">
-        <v>4710</v>
+        <v>2047</v>
       </c>
       <c r="E122" t="n">
-        <v>2199.643244598912</v>
+        <v>1879.137815927515</v>
       </c>
       <c r="F122" t="n">
-        <v>114.1</v>
+        <v>8.9</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>51152000000</v>
+        <v>9731000000</v>
       </c>
       <c r="J122" t="n">
-        <v>30337000000</v>
+        <v>5286000000</v>
       </c>
       <c r="K122" t="n">
-        <v>4870000000</v>
+        <v>100000000</v>
       </c>
       <c r="L122" t="n">
-        <v>85466000000</v>
+        <v>34620000000</v>
       </c>
       <c r="M122" t="n">
-        <v>86359000000</v>
+        <v>15117000000</v>
       </c>
       <c r="N122" t="n">
-        <v>524113172220</v>
+        <v>42623549009</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>太陽ホールディングス株式会社</t>
+          <t>日本ゼオン株式会社</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>16.5</v>
+        <v>35.9</v>
       </c>
       <c r="D123" t="n">
-        <v>4710</v>
+        <v>2347.5</v>
       </c>
       <c r="E123" t="n">
-        <v>3565.648720929983</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="F123" t="n">
-        <v>32.1</v>
+        <v>36.4</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -6798,50 +6798,50 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>51152000000</v>
+        <v>44521000000</v>
       </c>
       <c r="J123" t="n">
-        <v>30337000000</v>
+        <v>45382000000</v>
       </c>
       <c r="K123" t="n">
-        <v>4870000000</v>
+        <v>71191000000</v>
       </c>
       <c r="L123" t="n">
-        <v>85466000000</v>
+        <v>321836000000</v>
       </c>
       <c r="M123" t="n">
-        <v>86359000000</v>
+        <v>161094000000</v>
       </c>
       <c r="N123" t="n">
-        <v>524113172220</v>
+        <v>449183577682</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>株式会社エス・エム・エス</t>
+          <t>太陽ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>8.800000000000001</v>
+        <v>16.4</v>
       </c>
       <c r="D124" t="n">
-        <v>2532</v>
+        <v>4720</v>
       </c>
       <c r="E124" t="n">
-        <v>1478.127248828989</v>
+        <v>2199.643244598912</v>
       </c>
       <c r="F124" t="n">
-        <v>71.3</v>
+        <v>114.6</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -6850,102 +6850,102 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>14126000000</v>
+        <v>51152000000</v>
       </c>
       <c r="J124" t="n">
-        <v>1187000000</v>
+        <v>30337000000</v>
       </c>
       <c r="K124" t="n">
-        <v>2875000000</v>
+        <v>4870000000</v>
       </c>
       <c r="L124" t="n">
-        <v>29991000000</v>
+        <v>85466000000</v>
       </c>
       <c r="M124" t="n">
-        <v>18188000000</v>
+        <v>86359000000</v>
       </c>
       <c r="N124" t="n">
-        <v>207827696868</v>
+        <v>525225939040</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>アニコム ホールディングス株式会社</t>
+          <t>太陽ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>8715</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>41</v>
+        <v>16.4</v>
       </c>
       <c r="D125" t="n">
-        <v>1031</v>
+        <v>4720</v>
       </c>
       <c r="E125" t="n">
-        <v>656.2604975855553</v>
+        <v>3565.648720929983</v>
       </c>
       <c r="F125" t="n">
-        <v>57.1</v>
+        <v>32.4</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>27691000000</v>
+        <v>51152000000</v>
       </c>
       <c r="J125" t="n">
-        <v>3070000000</v>
+        <v>30337000000</v>
       </c>
       <c r="K125" t="n">
-        <v>3000000</v>
+        <v>4870000000</v>
       </c>
       <c r="L125" t="n">
-        <v>27316000000</v>
+        <v>85466000000</v>
       </c>
       <c r="M125" t="n">
-        <v>30764000000</v>
+        <v>86359000000</v>
       </c>
       <c r="N125" t="n">
-        <v>75078677820</v>
+        <v>525225939040</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>東京製鐵株式会社</t>
+          <t>株式会社エス・エム・エス</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>103.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D126" t="n">
-        <v>1685</v>
+        <v>2531</v>
       </c>
       <c r="E126" t="n">
-        <v>1605.452212379354</v>
+        <v>1478.127248828989</v>
       </c>
       <c r="F126" t="n">
-        <v>5</v>
+        <v>71.2</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -6954,102 +6954,102 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>68644000000</v>
+        <v>14126000000</v>
       </c>
       <c r="J126" t="n">
-        <v>33060000000</v>
+        <v>1187000000</v>
       </c>
       <c r="K126" t="n">
-        <v>75000000000</v>
+        <v>2875000000</v>
       </c>
       <c r="L126" t="n">
-        <v>158280000000</v>
+        <v>29991000000</v>
       </c>
       <c r="M126" t="n">
-        <v>176704000000</v>
+        <v>18188000000</v>
       </c>
       <c r="N126" t="n">
-        <v>171189497585</v>
+        <v>207745616419</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ウェーブロックホールディングス株式会社</t>
+          <t>アニコム ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>7940</t>
+          <t>8715</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>62.5</v>
+        <v>41.5</v>
       </c>
       <c r="D127" t="n">
-        <v>1057</v>
+        <v>1017</v>
       </c>
       <c r="E127" t="n">
-        <v>1010</v>
+        <v>656.2604975855553</v>
       </c>
       <c r="F127" t="n">
-        <v>4.7</v>
+        <v>55</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1961626000</v>
+        <v>27691000000</v>
       </c>
       <c r="J127" t="n">
-        <v>2544946000</v>
+        <v>3070000000</v>
       </c>
       <c r="K127" t="n">
-        <v>1068366000</v>
+        <v>3000000</v>
       </c>
       <c r="L127" t="n">
-        <v>13761535000</v>
+        <v>27316000000</v>
       </c>
       <c r="M127" t="n">
-        <v>5574938000</v>
+        <v>30764000000</v>
       </c>
       <c r="N127" t="n">
-        <v>8926497125</v>
+        <v>74059180740</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>近畿車輛株式会社</t>
+          <t>東京製鐵株式会社</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>7122</t>
+          <t>5423</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>107.4</v>
+        <v>102.2</v>
       </c>
       <c r="D128" t="n">
-        <v>2402</v>
+        <v>1702</v>
       </c>
       <c r="E128" t="n">
-        <v>2144.894901144641</v>
+        <v>1605.452212379354</v>
       </c>
       <c r="F128" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -7058,206 +7058,198 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>6847000000</v>
+        <v>68644000000</v>
       </c>
       <c r="J128" t="n">
-        <v>4580000000</v>
+        <v>33060000000</v>
       </c>
       <c r="K128" t="n">
-        <v>6329000000</v>
+        <v>75000000000</v>
       </c>
       <c r="L128" t="n">
-        <v>24474000000</v>
+        <v>158280000000</v>
       </c>
       <c r="M128" t="n">
-        <v>17756000000</v>
+        <v>176704000000</v>
       </c>
       <c r="N128" t="n">
-        <v>16525954562</v>
+        <v>172916631982</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>株式会社三陽商会</t>
+          <t>ウェーブロックホールディングス株式会社</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>8011</t>
-        </is>
-      </c>
-      <c r="C129" t="n">
-        <v>65.40000000000001</v>
-      </c>
-      <c r="D129" t="n">
-        <v>1333</v>
-      </c>
+          <t>7940</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr"/>
       <c r="E129" t="n">
-        <v>3321.975331035734</v>
-      </c>
-      <c r="F129" t="n">
-        <v>-59.9</v>
-      </c>
+        <v>1010</v>
+      </c>
+      <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>16287000000</v>
+        <v>1961626000</v>
       </c>
       <c r="J129" t="n">
-        <v>3021000000</v>
+        <v>2544946000</v>
       </c>
       <c r="K129" t="n">
-        <v>6298000000</v>
+        <v>1068366000</v>
       </c>
       <c r="L129" t="n">
-        <v>33920000000</v>
+        <v>13761535000</v>
       </c>
       <c r="M129" t="n">
-        <v>25606000000</v>
-      </c>
-      <c r="N129" t="n">
-        <v>39171580656</v>
-      </c>
+        <v>5574938000</v>
+      </c>
+      <c r="N129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>月島ホールディングス株式会社</t>
+          <t>近畿車輛株式会社</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>6332</t>
+          <t>7122</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>47.1</v>
+        <v>110.1</v>
       </c>
       <c r="D130" t="n">
-        <v>2738</v>
+        <v>2345</v>
       </c>
       <c r="E130" t="n">
-        <v>1410</v>
+        <v>2144.894901144641</v>
       </c>
       <c r="F130" t="n">
-        <v>94.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>28795000000</v>
+        <v>6847000000</v>
       </c>
       <c r="J130" t="n">
-        <v>22203000000</v>
+        <v>4580000000</v>
       </c>
       <c r="K130" t="n">
-        <v>100000000</v>
+        <v>6329000000</v>
       </c>
       <c r="L130" t="n">
-        <v>80949000000</v>
+        <v>24474000000</v>
       </c>
       <c r="M130" t="n">
-        <v>51098000000</v>
+        <v>17756000000</v>
       </c>
       <c r="N130" t="n">
-        <v>108428148574</v>
+        <v>16133789945</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>マネックスグループ株式会社</t>
+          <t>株式会社三陽商会</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>8698</t>
+          <t>8011</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>15.1</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="D131" t="n">
-        <v>725</v>
+        <v>1302</v>
       </c>
       <c r="E131" t="n">
-        <v>510.1850530906719</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="F131" t="n">
-        <v>42.1</v>
+        <v>-60.8</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>17794000000</v>
+        <v>16287000000</v>
       </c>
       <c r="J131" t="n">
-        <v>412000000</v>
+        <v>3021000000</v>
       </c>
       <c r="K131" t="n">
-        <v>9312000000</v>
+        <v>6298000000</v>
       </c>
       <c r="L131" t="n">
-        <v>98001000000</v>
+        <v>33920000000</v>
       </c>
       <c r="M131" t="n">
-        <v>27518000000</v>
+        <v>25606000000</v>
       </c>
       <c r="N131" t="n">
-        <v>182238670900</v>
+        <v>38260613664</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>株式会社あおぞら銀行</t>
+          <t>月島ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>231.7</v>
+        <v>46.4</v>
       </c>
       <c r="D132" t="n">
-        <v>3381</v>
+        <v>2778</v>
       </c>
       <c r="E132" t="n">
-        <v>2190</v>
+        <v>1410</v>
       </c>
       <c r="F132" t="n">
-        <v>54.4</v>
+        <v>97</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -7266,154 +7258,154 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1061743000000</v>
+        <v>28795000000</v>
       </c>
       <c r="J132" t="n">
-        <v>22385000000</v>
+        <v>22203000000</v>
       </c>
       <c r="K132" t="n">
-        <v>0</v>
+        <v>100000000</v>
       </c>
       <c r="L132" t="n">
-        <v>487265000000</v>
+        <v>80949000000</v>
       </c>
       <c r="M132" t="n">
-        <v>1084128000000</v>
+        <v>51098000000</v>
       </c>
       <c r="N132" t="n">
-        <v>467866580244</v>
+        <v>110012197494</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>日本製紙株式会社</t>
+          <t>マネックスグループ株式会社</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>8698</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>312.8</v>
+        <v>15.3</v>
       </c>
       <c r="D133" t="n">
-        <v>1278</v>
+        <v>717</v>
       </c>
       <c r="E133" t="n">
-        <v>1250</v>
+        <v>510.1850530906719</v>
       </c>
       <c r="F133" t="n">
-        <v>2.2</v>
+        <v>40.5</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>136216000000</v>
+        <v>17794000000</v>
       </c>
       <c r="J133" t="n">
-        <v>151771000000</v>
+        <v>412000000</v>
       </c>
       <c r="K133" t="n">
-        <v>172984000000</v>
+        <v>9312000000</v>
       </c>
       <c r="L133" t="n">
-        <v>438604000000</v>
+        <v>98001000000</v>
       </c>
       <c r="M133" t="n">
-        <v>460971000000</v>
+        <v>27518000000</v>
       </c>
       <c r="N133" t="n">
-        <v>147364266834</v>
+        <v>180227761428</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>カルビー株式会社</t>
+          <t>株式会社あおぞら銀行</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>33.1</v>
+        <v>233.3</v>
       </c>
       <c r="D134" t="n">
-        <v>3059</v>
+        <v>3358</v>
       </c>
       <c r="E134" t="n">
-        <v>2919.137515755844</v>
+        <v>2190</v>
       </c>
       <c r="F134" t="n">
-        <v>4.8</v>
+        <v>53.3</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>49670000000</v>
+        <v>1061743000000</v>
       </c>
       <c r="J134" t="n">
-        <v>70285000000</v>
+        <v>22385000000</v>
       </c>
       <c r="K134" t="n">
-        <v>3263000000</v>
+        <v>0</v>
       </c>
       <c r="L134" t="n">
-        <v>183458000000</v>
+        <v>487265000000</v>
       </c>
       <c r="M134" t="n">
-        <v>123218000000</v>
+        <v>1084128000000</v>
       </c>
       <c r="N134" t="n">
-        <v>371937245386</v>
+        <v>464683814392</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ＮＩＴＴＯＫＵ株式会社</t>
+          <t>日本製紙株式会社</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>50.7</v>
+        <v>307.5</v>
       </c>
       <c r="D135" t="n">
-        <v>2462</v>
+        <v>1300</v>
       </c>
       <c r="E135" t="n">
-        <v>1710</v>
+        <v>1250</v>
       </c>
       <c r="F135" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -7422,102 +7414,102 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>11768000000</v>
+        <v>136216000000</v>
       </c>
       <c r="J135" t="n">
-        <v>6299000000</v>
+        <v>151771000000</v>
       </c>
       <c r="K135" t="n">
-        <v>2999000000</v>
+        <v>172984000000</v>
       </c>
       <c r="L135" t="n">
-        <v>33919000000</v>
+        <v>438604000000</v>
       </c>
       <c r="M135" t="n">
-        <v>21066000000</v>
+        <v>460971000000</v>
       </c>
       <c r="N135" t="n">
-        <v>41544974684</v>
+        <v>149901053900</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ＮＩＴＴＯＫＵ株式会社</t>
+          <t>カルビー株式会社</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>50.7</v>
+        <v>33.6</v>
       </c>
       <c r="D136" t="n">
-        <v>2462</v>
+        <v>3020</v>
       </c>
       <c r="E136" t="n">
-        <v>1710</v>
+        <v>2919.137515755844</v>
       </c>
       <c r="F136" t="n">
-        <v>44</v>
+        <v>3.5</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>11768000000</v>
+        <v>49670000000</v>
       </c>
       <c r="J136" t="n">
-        <v>6299000000</v>
+        <v>70285000000</v>
       </c>
       <c r="K136" t="n">
-        <v>2999000000</v>
+        <v>3263000000</v>
       </c>
       <c r="L136" t="n">
-        <v>33919000000</v>
+        <v>183458000000</v>
       </c>
       <c r="M136" t="n">
-        <v>21066000000</v>
+        <v>123218000000</v>
       </c>
       <c r="N136" t="n">
-        <v>41544974684</v>
+        <v>367195319080</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>新光商事株式会社</t>
+          <t>ＮＩＴＴＯＫＵ株式会社</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>8141</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>30.8</v>
+        <v>51.2</v>
       </c>
       <c r="D137" t="n">
-        <v>1567</v>
+        <v>2438</v>
       </c>
       <c r="E137" t="n">
-        <v>930</v>
+        <v>1710</v>
       </c>
       <c r="F137" t="n">
-        <v>68.5</v>
+        <v>42.6</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -7526,50 +7518,50 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>10579000000</v>
+        <v>11768000000</v>
       </c>
       <c r="J137" t="n">
-        <v>195000000</v>
+        <v>6299000000</v>
       </c>
       <c r="K137" t="n">
-        <v>2995000000</v>
+        <v>2999000000</v>
       </c>
       <c r="L137" t="n">
-        <v>51945000000</v>
+        <v>33919000000</v>
       </c>
       <c r="M137" t="n">
-        <v>13769000000</v>
+        <v>21066000000</v>
       </c>
       <c r="N137" t="n">
-        <v>44737691733</v>
+        <v>41139987116</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>株式会社メガチップス</t>
+          <t>ＮＩＴＴＯＫＵ株式会社</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>6875</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>89.2</v>
+        <v>51.2</v>
       </c>
       <c r="D138" t="n">
-        <v>10530</v>
+        <v>2438</v>
       </c>
       <c r="E138" t="n">
-        <v>4870</v>
+        <v>1710</v>
       </c>
       <c r="F138" t="n">
-        <v>116.2</v>
+        <v>42.6</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -7578,102 +7570,102 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>25769446000</v>
+        <v>11768000000</v>
       </c>
       <c r="J138" t="n">
-        <v>2249411000</v>
+        <v>6299000000</v>
       </c>
       <c r="K138" t="n">
-        <v>101636005000</v>
+        <v>2999000000</v>
       </c>
       <c r="L138" t="n">
-        <v>67428618000</v>
+        <v>33919000000</v>
       </c>
       <c r="M138" t="n">
-        <v>129654862000</v>
+        <v>21066000000</v>
       </c>
       <c r="N138" t="n">
-        <v>145323487530</v>
+        <v>41139987116</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>株式会社青山財産ネットワークス</t>
+          <t>新光商事株式会社</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>8929</t>
+          <t>8141</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>42</v>
+        <v>30.8</v>
       </c>
       <c r="D139" t="n">
-        <v>1379</v>
+        <v>1567</v>
       </c>
       <c r="E139" t="n">
-        <v>1347.74653160027</v>
+        <v>930</v>
       </c>
       <c r="F139" t="n">
-        <v>2.3</v>
+        <v>68.5</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>10862000000</v>
+        <v>10579000000</v>
       </c>
       <c r="J139" t="n">
-        <v>245000000</v>
+        <v>195000000</v>
       </c>
       <c r="K139" t="n">
-        <v>2845000000</v>
+        <v>2995000000</v>
       </c>
       <c r="L139" t="n">
-        <v>7128000000</v>
+        <v>51945000000</v>
       </c>
       <c r="M139" t="n">
-        <v>13952000000</v>
+        <v>13769000000</v>
       </c>
       <c r="N139" t="n">
-        <v>33185963202</v>
+        <v>44737691733</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>平和不動産株式会社</t>
+          <t>株式会社メガチップス</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>8803</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>72.8</v>
+        <v>87.7</v>
       </c>
       <c r="D140" t="n">
-        <v>2358</v>
+        <v>10710</v>
       </c>
       <c r="E140" t="n">
-        <v>3610</v>
+        <v>4870</v>
       </c>
       <c r="F140" t="n">
-        <v>-34.7</v>
+        <v>119.9</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -7682,106 +7674,106 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>28111000000</v>
+        <v>25769446000</v>
       </c>
       <c r="J140" t="n">
-        <v>79319000000</v>
+        <v>2249411000</v>
       </c>
       <c r="K140" t="n">
-        <v>5997000000</v>
+        <v>101636005000</v>
       </c>
       <c r="L140" t="n">
-        <v>119278000000</v>
+        <v>67428618000</v>
       </c>
       <c r="M140" t="n">
-        <v>113427000000</v>
+        <v>129654862000</v>
       </c>
       <c r="N140" t="n">
-        <v>155793668364</v>
+        <v>147807649710</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>小林製薬株式会社</t>
+          <t>株式会社青山財産ネットワークス</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>8929</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>29.4</v>
+        <v>42.6</v>
       </c>
       <c r="D141" t="n">
-        <v>5913</v>
+        <v>1360</v>
       </c>
       <c r="E141" t="n">
-        <v>2148.936934940886</v>
+        <v>1347.74653160027</v>
       </c>
       <c r="F141" t="n">
-        <v>175.2</v>
+        <v>0.9</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>81987000000</v>
+        <v>10862000000</v>
       </c>
       <c r="J141" t="n">
-        <v>32461000000</v>
+        <v>245000000</v>
       </c>
       <c r="K141" t="n">
-        <v>14872000000</v>
+        <v>2845000000</v>
       </c>
       <c r="L141" t="n">
-        <v>195600000000</v>
+        <v>7128000000</v>
       </c>
       <c r="M141" t="n">
-        <v>129320000000</v>
+        <v>13952000000</v>
       </c>
       <c r="N141" t="n">
-        <v>439564265973</v>
+        <v>32728723680</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>小林製薬株式会社</t>
+          <t>平和不動産株式会社</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>29.4</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="D142" t="n">
-        <v>5913</v>
+        <v>2347</v>
       </c>
       <c r="E142" t="n">
-        <v>5066.092575838703</v>
+        <v>3610</v>
       </c>
       <c r="F142" t="n">
-        <v>16.7</v>
+        <v>-35</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -7790,46 +7782,46 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>81987000000</v>
+        <v>28111000000</v>
       </c>
       <c r="J142" t="n">
-        <v>32461000000</v>
+        <v>79319000000</v>
       </c>
       <c r="K142" t="n">
-        <v>14872000000</v>
+        <v>5997000000</v>
       </c>
       <c r="L142" t="n">
-        <v>195600000000</v>
+        <v>119278000000</v>
       </c>
       <c r="M142" t="n">
-        <v>129320000000</v>
+        <v>113427000000</v>
       </c>
       <c r="N142" t="n">
-        <v>439564265973</v>
+        <v>155066895526</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>セーレン株式会社</t>
+          <t>小林製薬株式会社</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>3569</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>36.7</v>
+        <v>30.5</v>
       </c>
       <c r="D143" t="n">
-        <v>3265</v>
+        <v>5700</v>
       </c>
       <c r="E143" t="n">
-        <v>1359.655069733296</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="F143" t="n">
-        <v>140.1</v>
+        <v>165.2</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -7838,50 +7830,50 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>35451000000</v>
+        <v>81987000000</v>
       </c>
       <c r="J143" t="n">
-        <v>25813000000</v>
+        <v>32461000000</v>
       </c>
       <c r="K143" t="n">
-        <v>8891000000</v>
+        <v>14872000000</v>
       </c>
       <c r="L143" t="n">
-        <v>91845000000</v>
+        <v>195600000000</v>
       </c>
       <c r="M143" t="n">
-        <v>70155000000</v>
+        <v>129320000000</v>
       </c>
       <c r="N143" t="n">
-        <v>191212246865</v>
+        <v>423730139700</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>データセクション株式会社</t>
+          <t>小林製薬株式会社</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>2.6</v>
+        <v>30.5</v>
       </c>
       <c r="D144" t="n">
-        <v>1514</v>
+        <v>5700</v>
       </c>
       <c r="E144" t="n">
-        <v>5143.276404494382</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="F144" t="n">
-        <v>-70.59999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -7890,650 +7882,754 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1420430000</v>
+        <v>81987000000</v>
       </c>
       <c r="J144" t="n">
-        <v>1162000</v>
+        <v>32461000000</v>
       </c>
       <c r="K144" t="n">
-        <v>49326000</v>
+        <v>14872000000</v>
       </c>
       <c r="L144" t="n">
-        <v>2818110000</v>
+        <v>195600000000</v>
       </c>
       <c r="M144" t="n">
-        <v>1470918000</v>
+        <v>129320000000</v>
       </c>
       <c r="N144" t="n">
-        <v>56717931284</v>
+        <v>423730139700</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>愛眼株式会社</t>
+          <t>セーレン株式会社</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>9854</t>
+          <t>3569</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>69.7</v>
+        <v>36.4</v>
       </c>
       <c r="D145" t="n">
-        <v>285</v>
+        <v>3295</v>
       </c>
       <c r="E145" t="n">
-        <v>246.9708756284982</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="F145" t="n">
-        <v>15.4</v>
+        <v>142.3</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2219000000</v>
+        <v>35451000000</v>
       </c>
       <c r="J145" t="n">
-        <v>1030000000</v>
+        <v>25813000000</v>
       </c>
       <c r="K145" t="n">
-        <v>604000000</v>
+        <v>8891000000</v>
       </c>
       <c r="L145" t="n">
-        <v>12920000000</v>
+        <v>91845000000</v>
       </c>
       <c r="M145" t="n">
-        <v>3853000000</v>
+        <v>70155000000</v>
       </c>
       <c r="N145" t="n">
-        <v>5530913775</v>
+        <v>192969174095</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>株式会社アシロ</t>
+          <t>データセクション株式会社</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>14</v>
+        <v>2.6</v>
       </c>
       <c r="D146" t="n">
-        <v>1551</v>
+        <v>1532</v>
       </c>
       <c r="E146" t="n">
-        <v>1396.628697042366</v>
+        <v>5143.276404494382</v>
       </c>
       <c r="F146" t="n">
-        <v>11.1</v>
+        <v>-70.2</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1428281000</v>
+        <v>1420430000</v>
       </c>
       <c r="J146" t="n">
-        <v>102238000</v>
+        <v>1162000</v>
       </c>
       <c r="K146" t="n">
-        <v>0</v>
+        <v>49326000</v>
       </c>
       <c r="L146" t="n">
-        <v>1804458000</v>
+        <v>2818110000</v>
       </c>
       <c r="M146" t="n">
-        <v>1530519000</v>
+        <v>1470918000</v>
       </c>
       <c r="N146" t="n">
-        <v>10902889437</v>
+        <v>57392252792</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>三浦工業株式会社</t>
+          <t>愛眼株式会社</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>11.4</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="D147" t="n">
-        <v>3184</v>
+        <v>282</v>
       </c>
       <c r="E147" t="n">
-        <v>3147.518794622453</v>
+        <v>246.9708756284982</v>
       </c>
       <c r="F147" t="n">
-        <v>1.2</v>
+        <v>14.2</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>20794000000</v>
+        <v>2219000000</v>
       </c>
       <c r="J147" t="n">
-        <v>10600000000</v>
+        <v>1030000000</v>
       </c>
       <c r="K147" t="n">
-        <v>10773000000</v>
+        <v>604000000</v>
       </c>
       <c r="L147" t="n">
-        <v>138378000000</v>
+        <v>12920000000</v>
       </c>
       <c r="M147" t="n">
-        <v>42167000000</v>
+        <v>3853000000</v>
       </c>
       <c r="N147" t="n">
-        <v>368545962240</v>
+        <v>5472693630</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>株式会社カカクコム</t>
+          <t>株式会社アシロ</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>7378</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>7</v>
+        <v>14.1</v>
       </c>
       <c r="D148" t="n">
-        <v>3691</v>
+        <v>1545</v>
       </c>
       <c r="E148" t="n">
-        <v>2318.314890576102</v>
+        <v>1396.628697042366</v>
       </c>
       <c r="F148" t="n">
-        <v>59.2</v>
+        <v>10.6</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>46452000000</v>
+        <v>1428281000</v>
       </c>
       <c r="J148" t="n">
-        <v>68000000</v>
+        <v>102238000</v>
       </c>
       <c r="K148" t="n">
-        <v>4669000000</v>
+        <v>0</v>
       </c>
       <c r="L148" t="n">
-        <v>45479000000</v>
+        <v>1804458000</v>
       </c>
       <c r="M148" t="n">
-        <v>51189000000</v>
+        <v>1530519000</v>
       </c>
       <c r="N148" t="n">
-        <v>730213661497</v>
+        <v>10860711915</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>古河機械金属株式会社</t>
+          <t>三浦工業株式会社</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>44.6</v>
+        <v>11.8</v>
       </c>
       <c r="D149" t="n">
-        <v>4180</v>
+        <v>3082</v>
       </c>
       <c r="E149" t="n">
-        <v>1600</v>
+        <v>3147.518794622453</v>
       </c>
       <c r="F149" t="n">
-        <v>161.2</v>
+        <v>-2.1</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>14468000000</v>
+        <v>20794000000</v>
       </c>
       <c r="J149" t="n">
-        <v>26121000000</v>
+        <v>10600000000</v>
       </c>
       <c r="K149" t="n">
-        <v>19903000000</v>
+        <v>10773000000</v>
       </c>
       <c r="L149" t="n">
-        <v>100075000000</v>
+        <v>138378000000</v>
       </c>
       <c r="M149" t="n">
-        <v>60492000000</v>
+        <v>42167000000</v>
       </c>
       <c r="N149" t="n">
-        <v>135560978080</v>
+        <v>356739527520</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>多木化学株式会社</t>
+          <t>株式会社カカクコム</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>4025</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>31.3</v>
+        <v>7</v>
       </c>
       <c r="D150" t="n">
-        <v>5600</v>
+        <v>3702</v>
       </c>
       <c r="E150" t="n">
-        <v>4695.956053243186</v>
+        <v>2318.314890576102</v>
       </c>
       <c r="F150" t="n">
-        <v>19.3</v>
+        <v>59.7</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>6433000000</v>
+        <v>46452000000</v>
       </c>
       <c r="J150" t="n">
-        <v>7985000000</v>
+        <v>68000000</v>
       </c>
       <c r="K150" t="n">
-        <v>199000000</v>
+        <v>4669000000</v>
       </c>
       <c r="L150" t="n">
-        <v>29378000000</v>
+        <v>45479000000</v>
       </c>
       <c r="M150" t="n">
-        <v>14617000000</v>
+        <v>51189000000</v>
       </c>
       <c r="N150" t="n">
-        <v>46745266400</v>
+        <v>732389860434</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>エムスリー株式会社</t>
+          <t>古河機械金属株式会社</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2413</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>7.7</v>
+        <v>42.6</v>
       </c>
       <c r="D151" t="n">
-        <v>1720.5</v>
+        <v>4380</v>
       </c>
       <c r="E151" t="n">
-        <v>1638.585693292194</v>
+        <v>1600</v>
       </c>
       <c r="F151" t="n">
-        <v>5</v>
+        <v>173.8</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>78812000000</v>
+        <v>14468000000</v>
       </c>
       <c r="J151" t="n">
-        <v>345000000</v>
+        <v>26121000000</v>
       </c>
       <c r="K151" t="n">
-        <v>9506000000</v>
+        <v>19903000000</v>
       </c>
       <c r="L151" t="n">
-        <v>152472000000</v>
+        <v>100075000000</v>
       </c>
       <c r="M151" t="n">
-        <v>88663000000</v>
+        <v>60492000000</v>
       </c>
       <c r="N151" t="n">
-        <v>1146397127050</v>
+        <v>142047149280</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>三井松島ホールディングス株式会社</t>
+          <t>多木化学株式会社</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>40</v>
+        <v>31.2</v>
       </c>
       <c r="D152" t="n">
-        <v>2291</v>
+        <v>5610</v>
       </c>
       <c r="E152" t="n">
-        <v>2920</v>
+        <v>4695.956053243186</v>
       </c>
       <c r="F152" t="n">
-        <v>-21.5</v>
+        <v>19.5</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>19413000000</v>
+        <v>6433000000</v>
       </c>
       <c r="J152" t="n">
-        <v>3540000000</v>
+        <v>7985000000</v>
       </c>
       <c r="K152" t="n">
-        <v>10945000000</v>
+        <v>199000000</v>
       </c>
       <c r="L152" t="n">
-        <v>35537000000</v>
+        <v>29378000000</v>
       </c>
       <c r="M152" t="n">
-        <v>33898000000</v>
+        <v>14617000000</v>
       </c>
       <c r="N152" t="n">
-        <v>84831056360</v>
+        <v>46828740090</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ノリタケ株式会社</t>
+          <t>エムスリー株式会社</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>39.1</v>
+        <v>8</v>
       </c>
       <c r="D153" t="n">
-        <v>3480</v>
+        <v>1666</v>
       </c>
       <c r="E153" t="n">
-        <v>3573.410502159827</v>
+        <v>1638.585693292194</v>
       </c>
       <c r="F153" t="n">
-        <v>-2.6</v>
+        <v>1.7</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>11733000000</v>
+        <v>78812000000</v>
       </c>
       <c r="J153" t="n">
-        <v>20204000000</v>
+        <v>345000000</v>
       </c>
       <c r="K153" t="n">
-        <v>42879000000</v>
+        <v>9506000000</v>
       </c>
       <c r="L153" t="n">
-        <v>118800000000</v>
+        <v>152472000000</v>
       </c>
       <c r="M153" t="n">
-        <v>74816000000</v>
+        <v>88663000000</v>
       </c>
       <c r="N153" t="n">
-        <v>191449673520</v>
+        <v>1110082890826</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>株式会社ＡＣＳＬ</t>
+          <t>三井松島ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>7.7</v>
+        <v>40.1</v>
       </c>
       <c r="D154" t="n">
-        <v>1381</v>
+        <v>2283</v>
       </c>
       <c r="E154" t="n">
-        <v>913.2768512341561</v>
+        <v>2920</v>
       </c>
       <c r="F154" t="n">
-        <v>51.2</v>
+        <v>-21.8</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1891731000</v>
+        <v>19413000000</v>
       </c>
       <c r="J154" t="n">
-        <v>3724000</v>
+        <v>3540000000</v>
       </c>
       <c r="K154" t="n">
-        <v>197577000</v>
+        <v>10945000000</v>
       </c>
       <c r="L154" t="n">
-        <v>3572642000</v>
+        <v>35537000000</v>
       </c>
       <c r="M154" t="n">
-        <v>2093032000</v>
+        <v>33898000000</v>
       </c>
       <c r="N154" t="n">
-        <v>27029266202</v>
+        <v>84534832680</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>株式会社スズケン</t>
+          <t>ノリタケ株式会社</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>9987</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>77.7</v>
+        <v>38.9</v>
       </c>
       <c r="D155" t="n">
-        <v>5187</v>
+        <v>3500</v>
       </c>
       <c r="E155" t="n">
-        <v>4137.137750115735</v>
+        <v>3573.410502159827</v>
       </c>
       <c r="F155" t="n">
-        <v>25.4</v>
+        <v>-2.1</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="I155" t="n">
-        <v>168215000000</v>
+        <v>11733000000</v>
       </c>
       <c r="J155" t="n">
-        <v>65453000000</v>
+        <v>20204000000</v>
       </c>
       <c r="K155" t="n">
-        <v>38927000000</v>
+        <v>42879000000</v>
       </c>
       <c r="L155" t="n">
-        <v>418062000000</v>
+        <v>118800000000</v>
       </c>
       <c r="M155" t="n">
-        <v>272595000000</v>
+        <v>74816000000</v>
       </c>
       <c r="N155" t="n">
-        <v>350837502015</v>
+        <v>192549959000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
+          <t>株式会社ＡＣＳＬ</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>6232</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="D156" t="n">
+        <v>1316</v>
+      </c>
+      <c r="E156" t="n">
+        <v>913.2768512341561</v>
+      </c>
+      <c r="F156" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>1891731000</v>
+      </c>
+      <c r="J156" t="n">
+        <v>3724000</v>
+      </c>
+      <c r="K156" t="n">
+        <v>197577000</v>
+      </c>
+      <c r="L156" t="n">
+        <v>3572642000</v>
+      </c>
+      <c r="M156" t="n">
+        <v>2093032000</v>
+      </c>
+      <c r="N156" t="n">
+        <v>25757070472</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>株式会社スズケン</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="D157" t="n">
+        <v>5177</v>
+      </c>
+      <c r="E157" t="n">
+        <v>4137.137750115735</v>
+      </c>
+      <c r="F157" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>168215000000</v>
+      </c>
+      <c r="J157" t="n">
+        <v>65453000000</v>
+      </c>
+      <c r="K157" t="n">
+        <v>38927000000</v>
+      </c>
+      <c r="L157" t="n">
+        <v>418062000000</v>
+      </c>
+      <c r="M157" t="n">
+        <v>272595000000</v>
+      </c>
+      <c r="N157" t="n">
+        <v>350161123565</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
           <t>フォスター電機株式会社</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
+      <c r="B158" t="inlineStr">
         <is>
           <t>6794</t>
         </is>
       </c>
-      <c r="C156" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="D156" t="n">
-        <v>2902</v>
-      </c>
-      <c r="E156" t="n">
+      <c r="C158" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="D158" t="n">
+        <v>2896</v>
+      </c>
+      <c r="E158" t="n">
         <v>2681.96152003832</v>
       </c>
-      <c r="F156" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="G156" t="inlineStr">
+      <c r="F158" t="n">
+        <v>8</v>
+      </c>
+      <c r="G158" t="inlineStr">
         <is>
           <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
+      <c r="H158" t="inlineStr">
         <is>
           <t>2026-01-22</t>
         </is>
       </c>
-      <c r="I156" t="n">
+      <c r="I158" t="n">
         <v>12089000000</v>
       </c>
-      <c r="J156" t="n">
+      <c r="J158" t="n">
         <v>7327000000</v>
       </c>
-      <c r="K156" t="n">
+      <c r="K158" t="n">
         <v>1115000000</v>
       </c>
-      <c r="L156" t="n">
+      <c r="L158" t="n">
         <v>51632000000</v>
       </c>
-      <c r="M156" t="n">
+      <c r="M158" t="n">
         <v>20531000000</v>
       </c>
-      <c r="N156" t="n">
-        <v>65201575914</v>
+      <c r="N158" t="n">
+        <v>65066769072</v>
       </c>
     </row>
   </sheetData>

--- a/docs/アクティビスト銘柄_資産判定.xlsx
+++ b/docs/アクティビスト銘柄_資産判定.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N158"/>
+  <dimension ref="A1:N159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>46</v>
+        <v>45.5</v>
       </c>
       <c r="D2" t="n">
-        <v>1294</v>
+        <v>1308</v>
       </c>
       <c r="E2" t="n">
         <v>1111.251693601708</v>
       </c>
       <c r="F2" t="n">
-        <v>16.4</v>
+        <v>17.7</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -537,7 +537,7 @@
         <v>213563000000</v>
       </c>
       <c r="N2" t="n">
-        <v>464587459760</v>
+        <v>469613908320</v>
       </c>
     </row>
     <row r="3">
@@ -552,16 +552,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>55.1</v>
+        <v>55.7</v>
       </c>
       <c r="D3" t="n">
-        <v>1154</v>
+        <v>1142</v>
       </c>
       <c r="E3" t="n">
         <v>1019.677694332945</v>
       </c>
       <c r="F3" t="n">
-        <v>13.2</v>
+        <v>12</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         <v>106991000000</v>
       </c>
       <c r="N3" t="n">
-        <v>194161134700</v>
+        <v>192142128100</v>
       </c>
     </row>
     <row r="4">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>3413</v>
+        <v>3439</v>
       </c>
       <c r="E4" t="n">
         <v>6116.356643776557</v>
       </c>
       <c r="F4" t="n">
-        <v>-44.2</v>
+        <v>-43.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         <v>219041000000</v>
       </c>
       <c r="N4" t="n">
-        <v>3087939033522</v>
+        <v>3111462741366</v>
       </c>
     </row>
     <row r="5">
@@ -656,16 +656,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>31.4</v>
+        <v>31.2</v>
       </c>
       <c r="D5" t="n">
-        <v>2142</v>
+        <v>2152.5</v>
       </c>
       <c r="E5" t="n">
         <v>1815.198567455447</v>
       </c>
       <c r="F5" t="n">
-        <v>18</v>
+        <v>18.6</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         <v>168499000000</v>
       </c>
       <c r="N5" t="n">
-        <v>536822153784</v>
+        <v>539453634930</v>
       </c>
     </row>
     <row r="6">
@@ -708,16 +708,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>53</v>
+        <v>54.2</v>
       </c>
       <c r="D6" t="n">
-        <v>11010</v>
+        <v>10750</v>
       </c>
       <c r="E6" t="n">
         <v>5684.0003469471</v>
       </c>
       <c r="F6" t="n">
-        <v>93.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>91895000000</v>
       </c>
       <c r="N6" t="n">
-        <v>173518227570</v>
+        <v>169420612750</v>
       </c>
     </row>
     <row r="7">
@@ -760,16 +760,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>53</v>
+        <v>54.2</v>
       </c>
       <c r="D7" t="n">
-        <v>11010</v>
+        <v>10750</v>
       </c>
       <c r="E7" t="n">
         <v>4549.503641591014</v>
       </c>
       <c r="F7" t="n">
-        <v>142</v>
+        <v>136.3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>91895000000</v>
       </c>
       <c r="N7" t="n">
-        <v>173518227570</v>
+        <v>169420612750</v>
       </c>
     </row>
     <row r="8">
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="D8" t="n">
-        <v>3835</v>
+        <v>3865</v>
       </c>
       <c r="E8" t="n">
         <v>1361.432492253209</v>
       </c>
       <c r="F8" t="n">
-        <v>181.7</v>
+        <v>183.9</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>12397436000</v>
       </c>
       <c r="N8" t="n">
-        <v>85071049505</v>
+        <v>85738628425</v>
       </c>
     </row>
     <row r="9">
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="D9" t="n">
-        <v>3301</v>
+        <v>3283</v>
       </c>
       <c r="E9" t="n">
         <v>13739.64575539568</v>
       </c>
       <c r="F9" t="n">
-        <v>-76</v>
+        <v>-76.09999999999999</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>325393000000</v>
       </c>
       <c r="N9" t="n">
-        <v>1075242256280</v>
+        <v>1069379075240</v>
       </c>
     </row>
     <row r="10">
@@ -916,16 +916,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>46.4</v>
+        <v>46.9</v>
       </c>
       <c r="D10" t="n">
-        <v>2081</v>
+        <v>2061</v>
       </c>
       <c r="E10" t="n">
         <v>1198.150742177053</v>
       </c>
       <c r="F10" t="n">
-        <v>73.7</v>
+        <v>72</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>213966000000</v>
       </c>
       <c r="N10" t="n">
-        <v>460761995021</v>
+        <v>456333720201</v>
       </c>
     </row>
     <row r="11">
@@ -968,16 +968,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>46.4</v>
+        <v>46.9</v>
       </c>
       <c r="D11" t="n">
-        <v>2081</v>
+        <v>2061</v>
       </c>
       <c r="E11" t="n">
         <v>1188.162962482466</v>
       </c>
       <c r="F11" t="n">
-        <v>75.09999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>213966000000</v>
       </c>
       <c r="N11" t="n">
-        <v>460761995021</v>
+        <v>456333720201</v>
       </c>
     </row>
     <row r="12">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24.8</v>
+        <v>24.6</v>
       </c>
       <c r="D12" t="n">
-        <v>3570</v>
+        <v>3599</v>
       </c>
       <c r="E12" t="n">
         <v>2995.424821743842</v>
       </c>
       <c r="F12" t="n">
-        <v>19.2</v>
+        <v>20.1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>129979000000</v>
       </c>
       <c r="N12" t="n">
-        <v>524667491880</v>
+        <v>528929496716</v>
       </c>
     </row>
     <row r="13">
@@ -1072,16 +1072,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>75.3</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>4753</v>
+        <v>4893</v>
       </c>
       <c r="E13" t="n">
         <v>4991.027246539169</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.8</v>
+        <v>-2</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>1007966000000</v>
       </c>
       <c r="N13" t="n">
-        <v>1339142283738</v>
+        <v>1378586828178</v>
       </c>
     </row>
     <row r="14">
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="D14" t="n">
-        <v>1740</v>
+        <v>1721.5</v>
       </c>
       <c r="E14" t="n">
         <v>1512.21980974841</v>
       </c>
       <c r="F14" t="n">
-        <v>15.1</v>
+        <v>13.8</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>120816000000</v>
       </c>
       <c r="N14" t="n">
-        <v>573185167620</v>
+        <v>567090957504</v>
       </c>
     </row>
     <row r="15">
@@ -1179,13 +1179,13 @@
         <v>7.6</v>
       </c>
       <c r="D15" t="n">
-        <v>2600</v>
+        <v>2604</v>
       </c>
       <c r="E15" t="n">
         <v>1827.011042553346</v>
       </c>
       <c r="F15" t="n">
-        <v>42.3</v>
+        <v>42.5</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>48336000000</v>
       </c>
       <c r="N15" t="n">
-        <v>639362006400</v>
+        <v>635565495684</v>
       </c>
     </row>
     <row r="16">
@@ -1228,16 +1228,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>136.1</v>
+        <v>136.8</v>
       </c>
       <c r="D16" t="n">
-        <v>1580</v>
+        <v>1572</v>
       </c>
       <c r="E16" t="n">
         <v>2122.579027791042</v>
       </c>
       <c r="F16" t="n">
-        <v>-25.6</v>
+        <v>-25.9</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>80333000000</v>
       </c>
       <c r="N16" t="n">
-        <v>59016834660</v>
+        <v>58718015244</v>
       </c>
     </row>
     <row r="17">
@@ -1280,16 +1280,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.6</v>
+        <v>17.4</v>
       </c>
       <c r="D17" t="n">
-        <v>2827</v>
+        <v>2855.5</v>
       </c>
       <c r="E17" t="n">
         <v>6272.971195510064</v>
       </c>
       <c r="F17" t="n">
-        <v>-54.9</v>
+        <v>-54.5</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>179622000000</v>
       </c>
       <c r="N17" t="n">
-        <v>1019629734618</v>
+        <v>1029908987337</v>
       </c>
     </row>
     <row r="18">
@@ -1332,16 +1332,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="D18" t="n">
-        <v>3551</v>
+        <v>3674</v>
       </c>
       <c r="E18" t="n">
         <v>1572.181660925393</v>
       </c>
       <c r="F18" t="n">
-        <v>125.9</v>
+        <v>133.7</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>35501000000</v>
       </c>
       <c r="N18" t="n">
-        <v>634077415407</v>
+        <v>656040671418</v>
       </c>
     </row>
     <row r="19">
@@ -1384,16 +1384,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="D19" t="n">
-        <v>3551</v>
+        <v>3674</v>
       </c>
       <c r="E19" t="n">
         <v>1141.512891683109</v>
       </c>
       <c r="F19" t="n">
-        <v>211.1</v>
+        <v>221.9</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>35501000000</v>
       </c>
       <c r="N19" t="n">
-        <v>634077415407</v>
+        <v>656040671418</v>
       </c>
     </row>
     <row r="20">
@@ -1436,16 +1436,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>46.1</v>
+        <v>45.5</v>
       </c>
       <c r="D20" t="n">
-        <v>5825</v>
+        <v>5905</v>
       </c>
       <c r="E20" t="n">
         <v>2836.942753814942</v>
       </c>
       <c r="F20" t="n">
-        <v>105.3</v>
+        <v>108.1</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>94351000000</v>
       </c>
       <c r="N20" t="n">
-        <v>204561889825</v>
+        <v>207560283505</v>
       </c>
     </row>
     <row r="21">
@@ -1488,16 +1488,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>55.7</v>
+        <v>55.4</v>
       </c>
       <c r="D21" t="n">
-        <v>4032</v>
+        <v>4052</v>
       </c>
       <c r="E21" t="n">
         <v>2863.970160821546</v>
       </c>
       <c r="F21" t="n">
-        <v>40.8</v>
+        <v>41.5</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>161529000000</v>
       </c>
       <c r="N21" t="n">
-        <v>290082897216</v>
+        <v>291521800476</v>
       </c>
     </row>
     <row r="22">
@@ -1543,7 +1543,7 @@
         <v>52.6</v>
       </c>
       <c r="D22" t="n">
-        <v>4646</v>
+        <v>4645</v>
       </c>
       <c r="E22" t="n">
         <v>2566.284807227078</v>
@@ -1577,7 +1577,7 @@
         <v>231575000000</v>
       </c>
       <c r="N22" t="n">
-        <v>440037081184</v>
+        <v>439942368080</v>
       </c>
     </row>
     <row r="23">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>29.1</v>
+        <v>28.9</v>
       </c>
       <c r="D23" t="n">
-        <v>5081</v>
+        <v>5115</v>
       </c>
       <c r="E23" t="n">
         <v>2779.139169918938</v>
       </c>
       <c r="F23" t="n">
-        <v>82.8</v>
+        <v>84</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>183216000000</v>
       </c>
       <c r="N23" t="n">
-        <v>630208985151</v>
+        <v>634426089165</v>
       </c>
     </row>
     <row r="24">
@@ -1647,13 +1647,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>3986</v>
+        <v>4002</v>
       </c>
       <c r="E24" t="n">
         <v>2420.370957920882</v>
       </c>
       <c r="F24" t="n">
-        <v>64.7</v>
+        <v>65.3</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>18167000000</v>
       </c>
       <c r="N24" t="n">
-        <v>197056196894</v>
+        <v>197847190158</v>
       </c>
     </row>
     <row r="25">
@@ -1696,16 +1696,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>1758.5</v>
+        <v>1745</v>
       </c>
       <c r="E25" t="n">
         <v>1344.518957928979</v>
       </c>
       <c r="F25" t="n">
-        <v>30.8</v>
+        <v>29.8</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>45956000000</v>
       </c>
       <c r="N25" t="n">
-        <v>565808370900</v>
+        <v>561464661485</v>
       </c>
     </row>
     <row r="26">
@@ -1748,16 +1748,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>60.1</v>
+        <v>59.9</v>
       </c>
       <c r="D26" t="n">
-        <v>4980</v>
+        <v>4998</v>
       </c>
       <c r="E26" t="n">
         <v>4154.626869982095</v>
       </c>
       <c r="F26" t="n">
-        <v>19.9</v>
+        <v>20.3</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>179086000000</v>
       </c>
       <c r="N26" t="n">
-        <v>297807366480</v>
+        <v>298883778648</v>
       </c>
     </row>
     <row r="27">
@@ -1800,16 +1800,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="D27" t="n">
-        <v>3797</v>
+        <v>3828</v>
       </c>
       <c r="E27" t="n">
         <v>2561.705402476645</v>
       </c>
       <c r="F27" t="n">
-        <v>48.2</v>
+        <v>49.4</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>100104000000</v>
       </c>
       <c r="N27" t="n">
-        <v>694780394785</v>
+        <v>700452818340</v>
       </c>
     </row>
     <row r="28">
@@ -1852,16 +1852,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
       <c r="D28" t="n">
-        <v>3420</v>
+        <v>3412</v>
       </c>
       <c r="E28" t="n">
         <v>2560</v>
       </c>
       <c r="F28" t="n">
-        <v>33.6</v>
+        <v>33.3</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>190312000000</v>
       </c>
       <c r="N28" t="n">
-        <v>421037246520</v>
+        <v>420052364072</v>
       </c>
     </row>
     <row r="29">
@@ -1904,16 +1904,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>91.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>4215</v>
+        <v>4245</v>
       </c>
       <c r="E29" t="n">
         <v>3449.780346820809</v>
       </c>
       <c r="F29" t="n">
-        <v>22.2</v>
+        <v>23.1</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>90928000000</v>
       </c>
       <c r="N29" t="n">
-        <v>99672155580</v>
+        <v>100381565940</v>
       </c>
     </row>
     <row r="30">
@@ -1956,16 +1956,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>62.2</v>
+        <v>60.7</v>
       </c>
       <c r="D30" t="n">
-        <v>1534</v>
+        <v>1572</v>
       </c>
       <c r="E30" t="n">
         <v>1746.940387696806</v>
       </c>
       <c r="F30" t="n">
-        <v>-12.2</v>
+        <v>-10</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>36070000000</v>
       </c>
       <c r="N30" t="n">
-        <v>57956810262</v>
+        <v>59392506996</v>
       </c>
     </row>
     <row r="31">
@@ -2008,16 +2008,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>106.4</v>
+        <v>106.6</v>
       </c>
       <c r="D31" t="n">
-        <v>1666</v>
+        <v>1664</v>
       </c>
       <c r="E31" t="n">
         <v>2298.672482457804</v>
       </c>
       <c r="F31" t="n">
-        <v>-27.5</v>
+        <v>-27.6</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>42752000000</v>
       </c>
       <c r="N31" t="n">
-        <v>40170070542</v>
+        <v>40121847168</v>
       </c>
     </row>
     <row r="32">
@@ -2060,16 +2060,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>67.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>2651</v>
+        <v>2729</v>
       </c>
       <c r="E32" t="n">
         <v>1270</v>
       </c>
       <c r="F32" t="n">
-        <v>108.7</v>
+        <v>114.9</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>31108000000</v>
       </c>
       <c r="N32" t="n">
-        <v>46094424211</v>
+        <v>47450653969</v>
       </c>
     </row>
     <row r="33">
@@ -2112,16 +2112,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>67.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>2651</v>
+        <v>2729</v>
       </c>
       <c r="E33" t="n">
         <v>1170</v>
       </c>
       <c r="F33" t="n">
-        <v>126.6</v>
+        <v>133.2</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>31108000000</v>
       </c>
       <c r="N33" t="n">
-        <v>46094424211</v>
+        <v>47450653969</v>
       </c>
     </row>
     <row r="34">
@@ -2164,16 +2164,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="D34" t="n">
-        <v>2797</v>
+        <v>2802.5</v>
       </c>
       <c r="E34" t="n">
         <v>2381.523440544182</v>
       </c>
       <c r="F34" t="n">
-        <v>17.4</v>
+        <v>17.7</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>168696000000</v>
       </c>
       <c r="N34" t="n">
-        <v>496721162727</v>
+        <v>497697911528</v>
       </c>
     </row>
     <row r="35">
@@ -2216,16 +2216,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>84.5</v>
+        <v>83.2</v>
       </c>
       <c r="D35" t="n">
-        <v>2450</v>
+        <v>2488</v>
       </c>
       <c r="E35" t="n">
         <v>2939.562915943684</v>
       </c>
       <c r="F35" t="n">
-        <v>-16.7</v>
+        <v>-15.4</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>108430000000</v>
       </c>
       <c r="N35" t="n">
-        <v>128298865800</v>
+        <v>130288807392</v>
       </c>
     </row>
     <row r="36">
@@ -2268,16 +2268,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>48.6</v>
+        <v>49.2</v>
       </c>
       <c r="D36" t="n">
-        <v>13440</v>
+        <v>13270</v>
       </c>
       <c r="E36" t="n">
         <v>7040.15625</v>
       </c>
       <c r="F36" t="n">
-        <v>90.90000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>6799899000</v>
       </c>
       <c r="N36" t="n">
-        <v>13998660480</v>
+        <v>13821594090</v>
       </c>
     </row>
     <row r="37">
@@ -2320,16 +2320,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>48.6</v>
+        <v>49.2</v>
       </c>
       <c r="D37" t="n">
-        <v>13440</v>
+        <v>13270</v>
       </c>
       <c r="E37" t="n">
         <v>7040.15625</v>
       </c>
       <c r="F37" t="n">
-        <v>90.90000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>6799899000</v>
       </c>
       <c r="N37" t="n">
-        <v>13998660480</v>
+        <v>13821594090</v>
       </c>
     </row>
     <row r="38">
@@ -2372,16 +2372,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>86.7</v>
+        <v>87.3</v>
       </c>
       <c r="D38" t="n">
-        <v>2767</v>
+        <v>2747</v>
       </c>
       <c r="E38" t="n">
         <v>4265.455132343447</v>
       </c>
       <c r="F38" t="n">
-        <v>-35.1</v>
+        <v>-35.6</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>22869000000</v>
       </c>
       <c r="N38" t="n">
-        <v>26380074406</v>
+        <v>26189398046</v>
       </c>
     </row>
     <row r="39">
@@ -2424,16 +2424,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>33.1</v>
+        <v>33.4</v>
       </c>
       <c r="D39" t="n">
-        <v>4660</v>
+        <v>4610</v>
       </c>
       <c r="E39" t="n">
         <v>2824.318397803668</v>
       </c>
       <c r="F39" t="n">
-        <v>65</v>
+        <v>63.2</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>61975000000</v>
       </c>
       <c r="N39" t="n">
-        <v>187474852300</v>
+        <v>185463319550</v>
       </c>
     </row>
     <row r="40">
@@ -2528,16 +2528,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="D41" t="n">
-        <v>6253</v>
+        <v>6267</v>
       </c>
       <c r="E41" t="n">
         <v>3322.047887165483</v>
       </c>
       <c r="F41" t="n">
-        <v>88.2</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>492847000000</v>
       </c>
       <c r="N41" t="n">
-        <v>2054141439844</v>
+        <v>2058740509116</v>
       </c>
     </row>
     <row r="42">
@@ -2580,16 +2580,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>35.5</v>
+        <v>36.2</v>
       </c>
       <c r="D42" t="n">
-        <v>1731</v>
+        <v>1718</v>
       </c>
       <c r="E42" t="n">
         <v>2112.609181636727</v>
       </c>
       <c r="F42" t="n">
-        <v>-18.1</v>
+        <v>-18.7</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>52218000000</v>
       </c>
       <c r="N42" t="n">
-        <v>146923592970</v>
+        <v>144243297180</v>
       </c>
     </row>
     <row r="43">
@@ -2632,16 +2632,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="D43" t="n">
-        <v>701</v>
+        <v>714</v>
       </c>
       <c r="E43" t="n">
         <v>404.9347366248775</v>
       </c>
       <c r="F43" t="n">
-        <v>73.09999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>7044972000</v>
       </c>
       <c r="N43" t="n">
-        <v>186876859605</v>
+        <v>190342478970</v>
       </c>
     </row>
     <row r="44">
@@ -2684,16 +2684,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="D44" t="n">
-        <v>2591</v>
+        <v>2737</v>
       </c>
       <c r="E44" t="n">
         <v>2220.184278344451</v>
       </c>
       <c r="F44" t="n">
-        <v>16.7</v>
+        <v>23.3</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>207116000000</v>
       </c>
       <c r="N44" t="n">
-        <v>2970088782485</v>
+        <v>3137450018395</v>
       </c>
     </row>
     <row r="45">
@@ -2736,16 +2736,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="D45" t="n">
-        <v>21885</v>
+        <v>22100</v>
       </c>
       <c r="E45" t="n">
         <v>11879.91675437757</v>
       </c>
       <c r="F45" t="n">
-        <v>84.2</v>
+        <v>86</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>191958000000</v>
       </c>
       <c r="N45" t="n">
-        <v>919641731175</v>
+        <v>928676365500</v>
       </c>
     </row>
     <row r="46">
@@ -2788,16 +2788,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>75.90000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="D46" t="n">
-        <v>1079</v>
+        <v>1085</v>
       </c>
       <c r="E46" t="n">
         <v>730</v>
       </c>
       <c r="F46" t="n">
-        <v>47.8</v>
+        <v>48.6</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>50027000000</v>
       </c>
       <c r="N46" t="n">
-        <v>65877466694</v>
+        <v>66243791810</v>
       </c>
     </row>
     <row r="47">
@@ -2840,16 +2840,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="D47" t="n">
-        <v>5291</v>
+        <v>5328</v>
       </c>
       <c r="E47" t="n">
         <v>3341.42986565678</v>
       </c>
       <c r="F47" t="n">
-        <v>58.3</v>
+        <v>59.5</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>311107000000</v>
       </c>
       <c r="N47" t="n">
-        <v>1257268017863</v>
+        <v>1266060101904</v>
       </c>
     </row>
     <row r="48">
@@ -2892,16 +2892,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>28.7</v>
+        <v>29.1</v>
       </c>
       <c r="D48" t="n">
-        <v>3215</v>
+        <v>3175</v>
       </c>
       <c r="E48" t="n">
         <v>2550.198980592041</v>
       </c>
       <c r="F48" t="n">
-        <v>26.1</v>
+        <v>24.5</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>32342000000</v>
       </c>
       <c r="N48" t="n">
-        <v>112552700440</v>
+        <v>111181883300</v>
       </c>
     </row>
     <row r="49">
@@ -2944,16 +2944,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>217.4</v>
+        <v>212.2</v>
       </c>
       <c r="D49" t="n">
-        <v>1592</v>
+        <v>1631</v>
       </c>
       <c r="E49" t="n">
         <v>1288.711724885291</v>
       </c>
       <c r="F49" t="n">
-        <v>23.5</v>
+        <v>26.6</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>747066000000</v>
       </c>
       <c r="N49" t="n">
-        <v>343687603416</v>
+        <v>352107086163</v>
       </c>
     </row>
     <row r="50">
@@ -2996,16 +2996,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>68.3</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>4022</v>
+        <v>4049</v>
       </c>
       <c r="E50" t="n">
         <v>3141.424011416125</v>
       </c>
       <c r="F50" t="n">
-        <v>28</v>
+        <v>28.9</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>391579000000</v>
       </c>
       <c r="N50" t="n">
-        <v>573117319288</v>
+        <v>576964700596</v>
       </c>
     </row>
     <row r="51">
@@ -3048,16 +3048,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>68.3</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="D51" t="n">
-        <v>4022</v>
+        <v>4049</v>
       </c>
       <c r="E51" t="n">
         <v>2420</v>
       </c>
       <c r="F51" t="n">
-        <v>66.2</v>
+        <v>67.3</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>391579000000</v>
       </c>
       <c r="N51" t="n">
-        <v>573117319288</v>
+        <v>576964700596</v>
       </c>
     </row>
     <row r="52">
@@ -3100,16 +3100,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="D52" t="n">
-        <v>4015</v>
+        <v>4026</v>
       </c>
       <c r="E52" t="n">
         <v>3047.091476167608</v>
       </c>
       <c r="F52" t="n">
-        <v>31.8</v>
+        <v>32.1</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>162458000000</v>
       </c>
       <c r="N52" t="n">
-        <v>381276714005</v>
+        <v>382321307742</v>
       </c>
     </row>
     <row r="53">
@@ -3155,7 +3155,7 @@
         <v>45.8</v>
       </c>
       <c r="D53" t="n">
-        <v>3460</v>
+        <v>3458</v>
       </c>
       <c r="E53" t="n">
         <v>2844.704547285864</v>
@@ -3189,7 +3189,7 @@
         <v>218675000000</v>
       </c>
       <c r="N53" t="n">
-        <v>477720857520</v>
+        <v>477444718296</v>
       </c>
     </row>
     <row r="54">
@@ -3204,16 +3204,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>55.9</v>
+        <v>55.5</v>
       </c>
       <c r="D54" t="n">
-        <v>2220</v>
+        <v>2234</v>
       </c>
       <c r="E54" t="n">
         <v>1556.090471804319</v>
       </c>
       <c r="F54" t="n">
-        <v>42.7</v>
+        <v>43.6</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>207466000000</v>
       </c>
       <c r="N54" t="n">
-        <v>371308775100</v>
+        <v>374013163570</v>
       </c>
     </row>
     <row r="55">
@@ -3256,16 +3256,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>51.2</v>
+        <v>47.6</v>
       </c>
       <c r="D55" t="n">
-        <v>1652</v>
+        <v>1774</v>
       </c>
       <c r="E55" t="n">
         <v>1529.631984751819</v>
       </c>
       <c r="F55" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>6024082000</v>
       </c>
       <c r="N55" t="n">
-        <v>11774083188</v>
+        <v>12643597806</v>
       </c>
     </row>
     <row r="56">
@@ -3308,16 +3308,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>51.2</v>
+        <v>47.6</v>
       </c>
       <c r="D56" t="n">
-        <v>1652</v>
+        <v>1774</v>
       </c>
       <c r="E56" t="n">
         <v>1449.995380693296</v>
       </c>
       <c r="F56" t="n">
-        <v>13.9</v>
+        <v>22.3</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>6024082000</v>
       </c>
       <c r="N56" t="n">
-        <v>11774083188</v>
+        <v>12643597806</v>
       </c>
     </row>
     <row r="57">
@@ -3360,16 +3360,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>67.5</v>
+        <v>67.7</v>
       </c>
       <c r="D57" t="n">
-        <v>2962</v>
+        <v>2955</v>
       </c>
       <c r="E57" t="n">
         <v>2696.128808062088</v>
       </c>
       <c r="F57" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>165282000000</v>
       </c>
       <c r="N57" t="n">
-        <v>244852349708</v>
+        <v>244273697970</v>
       </c>
     </row>
     <row r="58">
@@ -3412,16 +3412,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>120.1</v>
+        <v>119.8</v>
       </c>
       <c r="D58" t="n">
-        <v>1559.5</v>
+        <v>1563</v>
       </c>
       <c r="E58" t="n">
         <v>1160.8</v>
       </c>
       <c r="F58" t="n">
-        <v>34.3</v>
+        <v>34.6</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>493483000000</v>
       </c>
       <c r="N58" t="n">
-        <v>410938357120</v>
+        <v>411860629803</v>
       </c>
     </row>
     <row r="59">
@@ -3464,16 +3464,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="D59" t="n">
-        <v>2959</v>
+        <v>2981</v>
       </c>
       <c r="E59" t="n">
         <v>2007.754513143541</v>
       </c>
       <c r="F59" t="n">
-        <v>47.4</v>
+        <v>48.5</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>37208000000</v>
       </c>
       <c r="N59" t="n">
-        <v>157634602829</v>
+        <v>158806607311</v>
       </c>
     </row>
     <row r="60">
@@ -3516,16 +3516,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>15.3</v>
+        <v>15</v>
       </c>
       <c r="D60" t="n">
-        <v>2920</v>
+        <v>2980</v>
       </c>
       <c r="E60" t="n">
         <v>2261.880826568852</v>
       </c>
       <c r="F60" t="n">
-        <v>29.1</v>
+        <v>31.7</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>102508000000</v>
       </c>
       <c r="N60" t="n">
-        <v>669450567560</v>
+        <v>683206401140</v>
       </c>
     </row>
     <row r="61">
@@ -3568,16 +3568,16 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>15.3</v>
+        <v>15</v>
       </c>
       <c r="D61" t="n">
-        <v>2920</v>
+        <v>2980</v>
       </c>
       <c r="E61" t="n">
         <v>1970</v>
       </c>
       <c r="F61" t="n">
-        <v>48.2</v>
+        <v>51.3</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>102508000000</v>
       </c>
       <c r="N61" t="n">
-        <v>669450567560</v>
+        <v>683206401140</v>
       </c>
     </row>
     <row r="62">
@@ -3623,13 +3623,13 @@
         <v>9.6</v>
       </c>
       <c r="D62" t="n">
-        <v>2854</v>
+        <v>2859</v>
       </c>
       <c r="E62" t="n">
         <v>1910.426979628923</v>
       </c>
       <c r="F62" t="n">
-        <v>49.4</v>
+        <v>49.7</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>53660000000</v>
       </c>
       <c r="N62" t="n">
-        <v>557044068188</v>
+        <v>558019968798</v>
       </c>
     </row>
     <row r="63">
@@ -3672,16 +3672,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>50.6</v>
+        <v>51.3</v>
       </c>
       <c r="D63" t="n">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="E63" t="n">
         <v>290.3401328717133</v>
       </c>
       <c r="F63" t="n">
-        <v>1.3</v>
+        <v>-0.1</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>5162755000</v>
       </c>
       <c r="N63" t="n">
-        <v>10203516666</v>
+        <v>10064693310</v>
       </c>
     </row>
     <row r="64">
@@ -3812,16 +3812,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>94.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D66" t="n">
-        <v>2550</v>
+        <v>2573</v>
       </c>
       <c r="E66" t="n">
         <v>1748.071046781136</v>
       </c>
       <c r="F66" t="n">
-        <v>45.9</v>
+        <v>47.2</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>72190000000</v>
       </c>
       <c r="N66" t="n">
-        <v>76292274450</v>
+        <v>76980400847</v>
       </c>
     </row>
     <row r="67">
@@ -3864,16 +3864,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>77.8</v>
+        <v>77.2</v>
       </c>
       <c r="D67" t="n">
-        <v>2489</v>
+        <v>2509.5</v>
       </c>
       <c r="E67" t="n">
         <v>2551.08574256026</v>
       </c>
       <c r="F67" t="n">
-        <v>-2.4</v>
+        <v>-1.6</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>179136000000</v>
       </c>
       <c r="N67" t="n">
-        <v>230261474449</v>
+        <v>232157963090</v>
       </c>
     </row>
     <row r="68">
@@ -3916,16 +3916,16 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>77.8</v>
+        <v>77.2</v>
       </c>
       <c r="D68" t="n">
-        <v>2489</v>
+        <v>2509.5</v>
       </c>
       <c r="E68" t="n">
         <v>2260</v>
       </c>
       <c r="F68" t="n">
-        <v>10.1</v>
+        <v>11</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>179136000000</v>
       </c>
       <c r="N68" t="n">
-        <v>230261474449</v>
+        <v>232157963090</v>
       </c>
     </row>
     <row r="69">
@@ -3968,16 +3968,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>77.8</v>
+        <v>77.2</v>
       </c>
       <c r="D69" t="n">
-        <v>2489</v>
+        <v>2509.5</v>
       </c>
       <c r="E69" t="n">
         <v>2260</v>
       </c>
       <c r="F69" t="n">
-        <v>10.1</v>
+        <v>11</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>179136000000</v>
       </c>
       <c r="N69" t="n">
-        <v>230261474449</v>
+        <v>232157963090</v>
       </c>
     </row>
     <row r="70">
@@ -4020,16 +4020,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>312.3</v>
+        <v>311.2</v>
       </c>
       <c r="D70" t="n">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="E70" t="n">
         <v>798.3805136422309</v>
       </c>
       <c r="F70" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>449038000000</v>
       </c>
       <c r="N70" t="n">
-        <v>143796125760</v>
+        <v>144309683352</v>
       </c>
     </row>
     <row r="71">
@@ -4072,16 +4072,16 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>42.6</v>
+        <v>42.9</v>
       </c>
       <c r="D71" t="n">
-        <v>2594</v>
+        <v>2581</v>
       </c>
       <c r="E71" t="n">
         <v>2032.365850102071</v>
       </c>
       <c r="F71" t="n">
-        <v>27.6</v>
+        <v>27</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>340592000000</v>
       </c>
       <c r="N71" t="n">
-        <v>798668076324</v>
+        <v>794665499226</v>
       </c>
     </row>
     <row r="72">
@@ -4124,16 +4124,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>61.1</v>
+        <v>62.4</v>
       </c>
       <c r="D72" t="n">
-        <v>3638</v>
+        <v>3566</v>
       </c>
       <c r="E72" t="n">
         <v>1716.713876475349</v>
       </c>
       <c r="F72" t="n">
-        <v>111.9</v>
+        <v>107.7</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>565345000000</v>
       </c>
       <c r="N72" t="n">
-        <v>924698792744</v>
+        <v>906397992008</v>
       </c>
     </row>
     <row r="73">
@@ -4177,16 +4177,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>30.7</v>
+        <v>31.3</v>
       </c>
       <c r="D73" t="n">
-        <v>9370</v>
+        <v>9200</v>
       </c>
       <c r="E73" t="n">
         <v>4037.502552255647</v>
       </c>
       <c r="F73" t="n">
-        <v>132.1</v>
+        <v>127.9</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>154738000000</v>
       </c>
       <c r="N73" t="n">
-        <v>504141259310</v>
+        <v>494994619600</v>
       </c>
     </row>
     <row r="74">
@@ -4230,16 +4230,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>30.7</v>
+        <v>31.3</v>
       </c>
       <c r="D74" t="n">
-        <v>9370</v>
+        <v>9200</v>
       </c>
       <c r="E74" t="n">
         <v>3950.736048458928</v>
       </c>
       <c r="F74" t="n">
-        <v>137.2</v>
+        <v>132.9</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>154738000000</v>
       </c>
       <c r="N74" t="n">
-        <v>504141259310</v>
+        <v>494994619600</v>
       </c>
     </row>
     <row r="75">
@@ -4283,16 +4283,16 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>30.7</v>
+        <v>31.3</v>
       </c>
       <c r="D75" t="n">
-        <v>9370</v>
+        <v>9200</v>
       </c>
       <c r="E75" t="n">
         <v>2030</v>
       </c>
       <c r="F75" t="n">
-        <v>361.6</v>
+        <v>353.2</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>154738000000</v>
       </c>
       <c r="N75" t="n">
-        <v>504141259310</v>
+        <v>494994619600</v>
       </c>
     </row>
     <row r="76">
@@ -4336,16 +4336,16 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>30.7</v>
+        <v>31.3</v>
       </c>
       <c r="D76" t="n">
-        <v>9370</v>
+        <v>9200</v>
       </c>
       <c r="E76" t="n">
         <v>2387</v>
       </c>
       <c r="F76" t="n">
-        <v>292.5</v>
+        <v>285.4</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>154738000000</v>
       </c>
       <c r="N76" t="n">
-        <v>504141259310</v>
+        <v>494994619600</v>
       </c>
     </row>
     <row r="77">
@@ -4388,16 +4388,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>78.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="D77" t="n">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="E77" t="n">
         <v>668.9358717434869</v>
       </c>
       <c r="F77" t="n">
-        <v>48.3</v>
+        <v>48.1</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>12410000000</v>
       </c>
       <c r="N77" t="n">
-        <v>15885893952</v>
+        <v>15869879946</v>
       </c>
     </row>
     <row r="78">
@@ -4440,16 +4440,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="D78" t="n">
-        <v>2610</v>
+        <v>2601</v>
       </c>
       <c r="E78" t="n">
         <v>1190</v>
       </c>
       <c r="F78" t="n">
-        <v>119.3</v>
+        <v>118.6</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>40500000000</v>
       </c>
       <c r="N78" t="n">
-        <v>55571720670</v>
+        <v>55380094047</v>
       </c>
     </row>
     <row r="79">
@@ -4492,16 +4492,16 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>19</v>
+        <v>19.2</v>
       </c>
       <c r="D79" t="n">
-        <v>5890</v>
+        <v>5870</v>
       </c>
       <c r="E79" t="n">
         <v>2617.980935875217</v>
       </c>
       <c r="F79" t="n">
-        <v>125</v>
+        <v>124.2</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>40238000000</v>
       </c>
       <c r="N79" t="n">
-        <v>211825073900</v>
+        <v>210108232420</v>
       </c>
     </row>
     <row r="80">
@@ -4544,16 +4544,16 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>20.1</v>
+        <v>19.8</v>
       </c>
       <c r="D80" t="n">
-        <v>2803</v>
+        <v>2853</v>
       </c>
       <c r="E80" t="n">
         <v>2084.177692465894</v>
       </c>
       <c r="F80" t="n">
-        <v>34.5</v>
+        <v>36.9</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         <v>15433000000</v>
       </c>
       <c r="N80" t="n">
-        <v>76766660763</v>
+        <v>78136026813</v>
       </c>
     </row>
     <row r="81">
@@ -4596,16 +4596,16 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>13.5</v>
+        <v>13.2</v>
       </c>
       <c r="D81" t="n">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="E81" t="n">
         <v>448.6811097117532</v>
       </c>
       <c r="F81" t="n">
-        <v>12.8</v>
+        <v>13.4</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>13953300000</v>
       </c>
       <c r="N81" t="n">
-        <v>103357931116</v>
+        <v>105589560481</v>
       </c>
     </row>
     <row r="82">
@@ -4648,16 +4648,16 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>35.2</v>
+        <v>34.2</v>
       </c>
       <c r="D82" t="n">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="E82" t="n">
         <v>421.6950726175476</v>
       </c>
       <c r="F82" t="n">
-        <v>-25.3</v>
+        <v>-23.2</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>3109655000</v>
       </c>
       <c r="N82" t="n">
-        <v>8833415220</v>
+        <v>9085798512</v>
       </c>
     </row>
     <row r="83">
@@ -4700,16 +4700,16 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>72.5</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="D83" t="n">
-        <v>3865</v>
+        <v>3835</v>
       </c>
       <c r="E83" t="n">
         <v>3530</v>
       </c>
       <c r="F83" t="n">
-        <v>9.5</v>
+        <v>8.6</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>106147000000</v>
       </c>
       <c r="N83" t="n">
-        <v>146361037475</v>
+        <v>145224988025</v>
       </c>
     </row>
     <row r="84">
@@ -4752,16 +4752,16 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>36</v>
+        <v>35.6</v>
       </c>
       <c r="D84" t="n">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="E84" t="n">
         <v>549.4799823005444</v>
       </c>
       <c r="F84" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>19115000000</v>
       </c>
       <c r="N84" t="n">
-        <v>53160034320</v>
+        <v>53641556370</v>
       </c>
     </row>
     <row r="85">
@@ -4804,16 +4804,16 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>46.4</v>
+        <v>46.8</v>
       </c>
       <c r="D85" t="n">
-        <v>1695</v>
+        <v>1680</v>
       </c>
       <c r="E85" t="n">
         <v>1752.426893379333</v>
       </c>
       <c r="F85" t="n">
-        <v>-3.3</v>
+        <v>-4.1</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>76232495000</v>
       </c>
       <c r="N85" t="n">
-        <v>164425339500</v>
+        <v>162970248000</v>
       </c>
     </row>
     <row r="86">
@@ -4856,16 +4856,16 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>46.4</v>
+        <v>46.8</v>
       </c>
       <c r="D86" t="n">
-        <v>1695</v>
+        <v>1680</v>
       </c>
       <c r="E86" t="n">
         <v>1576.721867844292</v>
       </c>
       <c r="F86" t="n">
-        <v>7.5</v>
+        <v>6.6</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>76232495000</v>
       </c>
       <c r="N86" t="n">
-        <v>164425339500</v>
+        <v>162970248000</v>
       </c>
     </row>
     <row r="87">
@@ -4908,16 +4908,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>65.3</v>
+        <v>64.8</v>
       </c>
       <c r="D87" t="n">
-        <v>2101</v>
+        <v>2118.5</v>
       </c>
       <c r="E87" t="n">
         <v>1101.400153022188</v>
       </c>
       <c r="F87" t="n">
-        <v>90.8</v>
+        <v>92.3</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>402053000000</v>
       </c>
       <c r="N87" t="n">
-        <v>615623254400</v>
+        <v>620751006400</v>
       </c>
     </row>
     <row r="88">
@@ -4960,16 +4960,16 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>65.3</v>
+        <v>64.8</v>
       </c>
       <c r="D88" t="n">
-        <v>2101</v>
+        <v>2118.5</v>
       </c>
       <c r="E88" t="n">
         <v>1101.400153022188</v>
       </c>
       <c r="F88" t="n">
-        <v>90.8</v>
+        <v>92.3</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>402053000000</v>
       </c>
       <c r="N88" t="n">
-        <v>615623254400</v>
+        <v>620751006400</v>
       </c>
     </row>
     <row r="89">
@@ -5012,16 +5012,16 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>44.8</v>
+        <v>45</v>
       </c>
       <c r="D89" t="n">
-        <v>3353</v>
+        <v>3339</v>
       </c>
       <c r="E89" t="n">
         <v>1492.806001579363</v>
       </c>
       <c r="F89" t="n">
-        <v>124.6</v>
+        <v>123.7</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>112301000000</v>
       </c>
       <c r="N89" t="n">
-        <v>250818767605</v>
+        <v>249771507615</v>
       </c>
     </row>
     <row r="90">
@@ -5064,10 +5064,10 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>81</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D90" t="n">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="E90" t="n">
         <v>1341.977644710579</v>
@@ -5101,7 +5101,7 @@
         <v>86654000000</v>
       </c>
       <c r="N90" t="n">
-        <v>106948626102</v>
+        <v>106853221440</v>
       </c>
     </row>
     <row r="91">
@@ -5116,16 +5116,16 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>26.8</v>
+        <v>27.1</v>
       </c>
       <c r="D91" t="n">
-        <v>3967</v>
+        <v>3921</v>
       </c>
       <c r="E91" t="n">
         <v>2006.059650428343</v>
       </c>
       <c r="F91" t="n">
-        <v>97.8</v>
+        <v>95.5</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>173440000000</v>
       </c>
       <c r="N91" t="n">
-        <v>647337507639</v>
+        <v>639831199257</v>
       </c>
     </row>
     <row r="92">
@@ -5171,7 +5171,7 @@
         <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="E92" t="n">
         <v>2697.360927565142</v>
@@ -5205,7 +5205,7 @@
         <v>7339000000</v>
       </c>
       <c r="N92" t="n">
-        <v>719500166550</v>
+        <v>719110193560</v>
       </c>
     </row>
     <row r="93">
@@ -5220,16 +5220,16 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="D93" t="n">
-        <v>4470</v>
+        <v>4345</v>
       </c>
       <c r="E93" t="n">
         <v>7960</v>
       </c>
       <c r="F93" t="n">
-        <v>-43.8</v>
+        <v>-45.4</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -5257,7 +5257,7 @@
         <v>29865000000</v>
       </c>
       <c r="N93" t="n">
-        <v>170848111380</v>
+        <v>166070479630</v>
       </c>
     </row>
     <row r="94">
@@ -5272,16 +5272,16 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>17.6</v>
+        <v>18</v>
       </c>
       <c r="D94" t="n">
-        <v>5467</v>
+        <v>5357</v>
       </c>
       <c r="E94" t="n">
         <v>3735.709461270437</v>
       </c>
       <c r="F94" t="n">
-        <v>46.3</v>
+        <v>43.4</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>110688000000</v>
       </c>
       <c r="N94" t="n">
-        <v>627524844177</v>
+        <v>614898589767</v>
       </c>
     </row>
     <row r="95">
@@ -5324,16 +5324,16 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>30.2</v>
+        <v>30.8</v>
       </c>
       <c r="D95" t="n">
-        <v>2129</v>
+        <v>2089</v>
       </c>
       <c r="E95" t="n">
         <v>5463.67048346056</v>
       </c>
       <c r="F95" t="n">
-        <v>-61</v>
+        <v>-61.8</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v>11249000000</v>
       </c>
       <c r="N95" t="n">
-        <v>37239595110</v>
+        <v>36539931510</v>
       </c>
     </row>
     <row r="96">
@@ -5376,16 +5376,16 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="D96" t="n">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="E96" t="n">
         <v>3234.727863989046</v>
       </c>
       <c r="F96" t="n">
-        <v>-56.5</v>
+        <v>-56.7</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>52215000000</v>
       </c>
       <c r="N96" t="n">
-        <v>201408853240</v>
+        <v>200835855080</v>
       </c>
     </row>
     <row r="97">
@@ -5428,16 +5428,16 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>34.9</v>
+        <v>35.2</v>
       </c>
       <c r="D97" t="n">
-        <v>3140</v>
+        <v>3115</v>
       </c>
       <c r="E97" t="n">
         <v>3155.301177013616</v>
       </c>
       <c r="F97" t="n">
-        <v>-0.5</v>
+        <v>-1.3</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>70480000000</v>
       </c>
       <c r="N97" t="n">
-        <v>201734945720</v>
+        <v>200128775770</v>
       </c>
     </row>
     <row r="98">
@@ -5480,16 +5480,16 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="D98" t="n">
-        <v>3231</v>
+        <v>3299</v>
       </c>
       <c r="E98" t="n">
         <v>2655.311711736394</v>
       </c>
       <c r="F98" t="n">
-        <v>21.7</v>
+        <v>24.2</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>33115000000</v>
       </c>
       <c r="N98" t="n">
-        <v>572953246155</v>
+        <v>585011686495</v>
       </c>
     </row>
     <row r="99">
@@ -5532,16 +5532,16 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>40.3</v>
+        <v>40.5</v>
       </c>
       <c r="D99" t="n">
-        <v>915</v>
+        <v>911.2999877929688</v>
       </c>
       <c r="E99" t="n">
         <v>2157.626835069302</v>
       </c>
       <c r="F99" t="n">
-        <v>-57.6</v>
+        <v>-57.8</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>152963000000</v>
       </c>
       <c r="N99" t="n">
-        <v>379212664965</v>
+        <v>377679231643</v>
       </c>
     </row>
     <row r="100">
@@ -5584,16 +5584,16 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>98.59999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="D100" t="n">
-        <v>1164</v>
+        <v>1181</v>
       </c>
       <c r="E100" t="n">
         <v>810</v>
       </c>
       <c r="F100" t="n">
-        <v>43.7</v>
+        <v>45.8</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>50303000000</v>
       </c>
       <c r="N100" t="n">
-        <v>50992720356</v>
+        <v>51737459399</v>
       </c>
     </row>
     <row r="101">
@@ -5639,13 +5639,13 @@
         <v>10</v>
       </c>
       <c r="D101" t="n">
-        <v>2047</v>
+        <v>2042</v>
       </c>
       <c r="E101" t="n">
         <v>2300.974351689521</v>
       </c>
       <c r="F101" t="n">
-        <v>-11</v>
+        <v>-11.3</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         <v>8549173000</v>
       </c>
       <c r="N101" t="n">
-        <v>85883010850</v>
+        <v>85673233100</v>
       </c>
     </row>
     <row r="102">
@@ -5688,16 +5688,16 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>39.8</v>
+        <v>40.1</v>
       </c>
       <c r="D102" t="n">
-        <v>1605</v>
+        <v>1592</v>
       </c>
       <c r="E102" t="n">
-        <v>1180.406015389293</v>
+        <v>1180.31326635551</v>
       </c>
       <c r="F102" t="n">
-        <v>36</v>
+        <v>34.9</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="I102" t="n">
@@ -5725,7 +5725,7 @@
         <v>29529000000</v>
       </c>
       <c r="N102" t="n">
-        <v>74169117240</v>
+        <v>73562480096</v>
       </c>
     </row>
     <row r="103">
@@ -5740,16 +5740,16 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>39.8</v>
+        <v>40.1</v>
       </c>
       <c r="D103" t="n">
-        <v>1605</v>
+        <v>1592</v>
       </c>
       <c r="E103" t="n">
-        <v>1180.420176850555</v>
+        <v>1180.406015389293</v>
       </c>
       <c r="F103" t="n">
-        <v>36</v>
+        <v>34.9</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="I103" t="n">
@@ -5777,7 +5777,7 @@
         <v>29529000000</v>
       </c>
       <c r="N103" t="n">
-        <v>74169117240</v>
+        <v>73562480096</v>
       </c>
     </row>
     <row r="104">
@@ -5792,16 +5792,16 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>39.8</v>
+        <v>40.1</v>
       </c>
       <c r="D104" t="n">
-        <v>1605</v>
+        <v>1592</v>
       </c>
       <c r="E104" t="n">
-        <v>1180.431728045326</v>
+        <v>1180.420176850555</v>
       </c>
       <c r="F104" t="n">
-        <v>36</v>
+        <v>34.9</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="I104" t="n">
@@ -5829,7 +5829,7 @@
         <v>29529000000</v>
       </c>
       <c r="N104" t="n">
-        <v>74169117240</v>
+        <v>73562480096</v>
       </c>
     </row>
     <row r="105">
@@ -5844,16 +5844,16 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>39.8</v>
+        <v>40.1</v>
       </c>
       <c r="D105" t="n">
-        <v>1605</v>
+        <v>1592</v>
       </c>
       <c r="E105" t="n">
-        <v>1180.442269658324</v>
+        <v>1180.431728045326</v>
       </c>
       <c r="F105" t="n">
-        <v>36</v>
+        <v>34.9</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="I105" t="n">
@@ -5881,7 +5881,7 @@
         <v>29529000000</v>
       </c>
       <c r="N105" t="n">
-        <v>74169117240</v>
+        <v>73562480096</v>
       </c>
     </row>
     <row r="106">
@@ -5896,16 +5896,16 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>39.8</v>
+        <v>40.1</v>
       </c>
       <c r="D106" t="n">
-        <v>1605</v>
+        <v>1592</v>
       </c>
       <c r="E106" t="n">
-        <v>1180.450912709519</v>
+        <v>1180.442269658324</v>
       </c>
       <c r="F106" t="n">
-        <v>36</v>
+        <v>34.9</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="I106" t="n">
@@ -5933,7 +5933,7 @@
         <v>29529000000</v>
       </c>
       <c r="N106" t="n">
-        <v>74169117240</v>
+        <v>73562480096</v>
       </c>
     </row>
     <row r="107">
@@ -5948,16 +5948,16 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>39.8</v>
+        <v>40.1</v>
       </c>
       <c r="D107" t="n">
-        <v>1605</v>
+        <v>1592</v>
       </c>
       <c r="E107" t="n">
-        <v>1180.45745232471</v>
+        <v>1180.450912709519</v>
       </c>
       <c r="F107" t="n">
-        <v>36</v>
+        <v>34.9</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="I107" t="n">
@@ -5985,7 +5985,7 @@
         <v>29529000000</v>
       </c>
       <c r="N107" t="n">
-        <v>74169117240</v>
+        <v>73562480096</v>
       </c>
     </row>
     <row r="108">
@@ -6000,16 +6000,16 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>39.8</v>
+        <v>40.1</v>
       </c>
       <c r="D108" t="n">
-        <v>1605</v>
+        <v>1592</v>
       </c>
       <c r="E108" t="n">
-        <v>1180.463123164206</v>
+        <v>1180.45745232471</v>
       </c>
       <c r="F108" t="n">
-        <v>36</v>
+        <v>34.9</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="I108" t="n">
@@ -6037,7 +6037,7 @@
         <v>29529000000</v>
       </c>
       <c r="N108" t="n">
-        <v>74169117240</v>
+        <v>73562480096</v>
       </c>
     </row>
     <row r="109">
@@ -6052,16 +6052,16 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>39.8</v>
+        <v>40.1</v>
       </c>
       <c r="D109" t="n">
-        <v>1605</v>
+        <v>1592</v>
       </c>
       <c r="E109" t="n">
-        <v>1170.279952698077</v>
+        <v>1180.463123164206</v>
       </c>
       <c r="F109" t="n">
-        <v>37.1</v>
+        <v>34.9</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="I109" t="n">
@@ -6089,7 +6089,7 @@
         <v>29529000000</v>
       </c>
       <c r="N109" t="n">
-        <v>74169117240</v>
+        <v>73562480096</v>
       </c>
     </row>
     <row r="110">
@@ -6104,16 +6104,16 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>39.8</v>
+        <v>40.1</v>
       </c>
       <c r="D110" t="n">
-        <v>1605</v>
+        <v>1592</v>
       </c>
       <c r="E110" t="n">
-        <v>1169.924818603025</v>
+        <v>1170.279952698077</v>
       </c>
       <c r="F110" t="n">
-        <v>37.2</v>
+        <v>36</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="I110" t="n">
@@ -6141,7 +6141,7 @@
         <v>29529000000</v>
       </c>
       <c r="N110" t="n">
-        <v>74169117240</v>
+        <v>73562480096</v>
       </c>
     </row>
     <row r="111">
@@ -6156,16 +6156,16 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>39.8</v>
+        <v>40.1</v>
       </c>
       <c r="D111" t="n">
-        <v>1605</v>
+        <v>1592</v>
       </c>
       <c r="E111" t="n">
-        <v>1168.709522546084</v>
+        <v>1169.924818603025</v>
       </c>
       <c r="F111" t="n">
-        <v>37.3</v>
+        <v>36.1</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="I111" t="n">
@@ -6193,31 +6193,31 @@
         <v>29529000000</v>
       </c>
       <c r="N111" t="n">
-        <v>74169117240</v>
+        <v>73562480096</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>山洋電気株式会社</t>
+          <t>東亜道路工業株式会社</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>12</v>
+        <v>40.1</v>
       </c>
       <c r="D112" t="n">
-        <v>5180</v>
+        <v>1592</v>
       </c>
       <c r="E112" t="n">
-        <v>7052.737306843267</v>
+        <v>1168.709522546084</v>
       </c>
       <c r="F112" t="n">
-        <v>-26.6</v>
+        <v>36.2</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -6226,102 +6226,102 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>8317000000</v>
+        <v>11649000000</v>
       </c>
       <c r="J112" t="n">
-        <v>6048000000</v>
+        <v>13793000000</v>
       </c>
       <c r="K112" t="n">
-        <v>7673000000</v>
+        <v>4087000000</v>
       </c>
       <c r="L112" t="n">
-        <v>49734000000</v>
+        <v>50605000000</v>
       </c>
       <c r="M112" t="n">
-        <v>22038000000</v>
+        <v>29529000000</v>
       </c>
       <c r="N112" t="n">
-        <v>183967912380</v>
+        <v>73562480096</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ヘリオス テクノ ホールディング株式会社</t>
+          <t>山洋電気株式会社</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>54.6</v>
+        <v>12</v>
       </c>
       <c r="D113" t="n">
-        <v>966</v>
+        <v>5180</v>
       </c>
       <c r="E113" t="n">
-        <v>896.0103264198827</v>
+        <v>7052.737306843267</v>
       </c>
       <c r="F113" t="n">
-        <v>7.8</v>
+        <v>-26.6</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>7851015000</v>
+        <v>8317000000</v>
       </c>
       <c r="J113" t="n">
-        <v>640317000</v>
+        <v>6048000000</v>
       </c>
       <c r="K113" t="n">
-        <v>1079200000</v>
+        <v>7673000000</v>
       </c>
       <c r="L113" t="n">
-        <v>13746774000</v>
+        <v>49734000000</v>
       </c>
       <c r="M113" t="n">
-        <v>9570532000</v>
+        <v>22038000000</v>
       </c>
       <c r="N113" t="n">
-        <v>17534510322</v>
+        <v>183967912380</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>シェアリングテクノロジー株式会社</t>
+          <t>ヘリオス テクノ ホールディング株式会社</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>12.3</v>
+        <v>54.4</v>
       </c>
       <c r="D114" t="n">
-        <v>1465</v>
+        <v>970</v>
       </c>
       <c r="E114" t="n">
-        <v>653.0713101160862</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="F114" t="n">
-        <v>124.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -6330,50 +6330,50 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>4016706000</v>
+        <v>7851015000</v>
       </c>
       <c r="J114" t="n">
-        <v>309745000</v>
+        <v>640317000</v>
       </c>
       <c r="K114" t="n">
-        <v>0</v>
+        <v>1079200000</v>
       </c>
       <c r="L114" t="n">
-        <v>185001000</v>
+        <v>13746774000</v>
       </c>
       <c r="M114" t="n">
-        <v>4326451000</v>
+        <v>9570532000</v>
       </c>
       <c r="N114" t="n">
-        <v>35059309085</v>
+        <v>17607116990</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>栄研化学株式会社</t>
+          <t>シェアリングテクノロジー株式会社</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>30.7</v>
+        <v>11.7</v>
       </c>
       <c r="D115" t="n">
-        <v>2262</v>
+        <v>1545</v>
       </c>
       <c r="E115" t="n">
-        <v>1947.225264702313</v>
+        <v>653.0713101160862</v>
       </c>
       <c r="F115" t="n">
-        <v>16.2</v>
+        <v>136.6</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -6382,26 +6382,26 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>10900000000</v>
+        <v>4016706000</v>
       </c>
       <c r="J115" t="n">
-        <v>11585000000</v>
+        <v>309745000</v>
       </c>
       <c r="K115" t="n">
-        <v>408000000</v>
+        <v>0</v>
       </c>
       <c r="L115" t="n">
-        <v>45803000000</v>
+        <v>185001000</v>
       </c>
       <c r="M115" t="n">
-        <v>22893000000</v>
+        <v>4326451000</v>
       </c>
       <c r="N115" t="n">
-        <v>74568126126</v>
+        <v>36973810605</v>
       </c>
     </row>
     <row r="116">
@@ -6416,16 +6416,16 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>30.7</v>
+        <v>31</v>
       </c>
       <c r="D116" t="n">
-        <v>2262</v>
+        <v>2237</v>
       </c>
       <c r="E116" t="n">
-        <v>1678.083113259255</v>
+        <v>1947.225264702313</v>
       </c>
       <c r="F116" t="n">
-        <v>34.8</v>
+        <v>14.9</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="I116" t="n">
@@ -6453,215 +6453,215 @@
         <v>22893000000</v>
       </c>
       <c r="N116" t="n">
-        <v>74568126126</v>
+        <v>73743986801</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>株式会社ヤマダホールディングス</t>
+          <t>栄研化学株式会社</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>9831</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>60.1</v>
+        <v>31</v>
       </c>
       <c r="D117" t="n">
-        <v>693.0999755859375</v>
+        <v>2237</v>
       </c>
       <c r="E117" t="n">
-        <v>530</v>
+        <v>1678.083113259255</v>
       </c>
       <c r="F117" t="n">
-        <v>30.8</v>
+        <v>33.3</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>56470000000</v>
+        <v>10900000000</v>
       </c>
       <c r="J117" t="n">
-        <v>210733000000</v>
+        <v>11585000000</v>
       </c>
       <c r="K117" t="n">
-        <v>9997000000</v>
+        <v>408000000</v>
       </c>
       <c r="L117" t="n">
-        <v>676277000000</v>
+        <v>45803000000</v>
       </c>
       <c r="M117" t="n">
-        <v>277200000000</v>
+        <v>22893000000</v>
       </c>
       <c r="N117" t="n">
-        <v>460894456378</v>
+        <v>73743986801</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>日本化薬株式会社</t>
+          <t>株式会社ヤマダホールディングス</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>9831</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>35.7</v>
+        <v>58.5</v>
       </c>
       <c r="D118" t="n">
-        <v>2033.5</v>
+        <v>712.0999755859375</v>
       </c>
       <c r="E118" t="n">
-        <v>1111.90611839092</v>
+        <v>530</v>
       </c>
       <c r="F118" t="n">
-        <v>82.90000000000001</v>
+        <v>34.4</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>52962000000</v>
+        <v>56470000000</v>
       </c>
       <c r="J118" t="n">
-        <v>48231000000</v>
+        <v>210733000000</v>
       </c>
       <c r="K118" t="n">
-        <v>4337000000</v>
+        <v>9997000000</v>
       </c>
       <c r="L118" t="n">
-        <v>246425000000</v>
+        <v>676277000000</v>
       </c>
       <c r="M118" t="n">
-        <v>105530000000</v>
+        <v>277200000000</v>
       </c>
       <c r="N118" t="n">
-        <v>295613988436</v>
+        <v>473528989605</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>王子ホールディングス株式会社</t>
+          <t>日本化薬株式会社</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>41.9</v>
+        <v>35.6</v>
       </c>
       <c r="D119" t="n">
-        <v>864</v>
+        <v>2039</v>
       </c>
       <c r="E119" t="n">
-        <v>590</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="F119" t="n">
-        <v>46.4</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>55474000000</v>
+        <v>52962000000</v>
       </c>
       <c r="J119" t="n">
-        <v>244732000000</v>
+        <v>48231000000</v>
       </c>
       <c r="K119" t="n">
-        <v>7434000000</v>
+        <v>4337000000</v>
       </c>
       <c r="L119" t="n">
-        <v>875470000000</v>
+        <v>246425000000</v>
       </c>
       <c r="M119" t="n">
-        <v>307640000000</v>
+        <v>105530000000</v>
       </c>
       <c r="N119" t="n">
-        <v>733738429152</v>
+        <v>296413534507</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>東邦ホールディングス株式会社</t>
+          <t>王子ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>51.3</v>
+        <v>42.1</v>
       </c>
       <c r="D120" t="n">
-        <v>3954</v>
+        <v>859.9000244140625</v>
       </c>
       <c r="E120" t="n">
-        <v>3405.914389596362</v>
+        <v>590</v>
       </c>
       <c r="F120" t="n">
-        <v>16.1</v>
+        <v>45.7</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>90014000000</v>
+        <v>55474000000</v>
       </c>
       <c r="J120" t="n">
-        <v>34220000000</v>
+        <v>244732000000</v>
       </c>
       <c r="K120" t="n">
-        <v>7000000000</v>
+        <v>7434000000</v>
       </c>
       <c r="L120" t="n">
-        <v>241281000000</v>
+        <v>875470000000</v>
       </c>
       <c r="M120" t="n">
-        <v>131234000000</v>
+        <v>307640000000</v>
       </c>
       <c r="N120" t="n">
-        <v>255830217342</v>
+        <v>730256589284</v>
       </c>
     </row>
     <row r="121">
@@ -6679,13 +6679,13 @@
         <v>51.3</v>
       </c>
       <c r="D121" t="n">
-        <v>3954</v>
+        <v>3952</v>
       </c>
       <c r="E121" t="n">
-        <v>2714.613787300615</v>
+        <v>3405.914389596362</v>
       </c>
       <c r="F121" t="n">
-        <v>45.7</v>
+        <v>16</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="I121" t="n">
@@ -6713,135 +6713,135 @@
         <v>131234000000</v>
       </c>
       <c r="N121" t="n">
-        <v>255830217342</v>
+        <v>255700814096</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>株式会社アイネス</t>
+          <t>東邦ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>9742</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>35.5</v>
+        <v>51.3</v>
       </c>
       <c r="D122" t="n">
-        <v>2047</v>
+        <v>3952</v>
       </c>
       <c r="E122" t="n">
-        <v>1879.137815927515</v>
+        <v>2714.613787300615</v>
       </c>
       <c r="F122" t="n">
-        <v>8.9</v>
+        <v>45.6</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>9731000000</v>
+        <v>90014000000</v>
       </c>
       <c r="J122" t="n">
-        <v>5286000000</v>
+        <v>34220000000</v>
       </c>
       <c r="K122" t="n">
-        <v>100000000</v>
+        <v>7000000000</v>
       </c>
       <c r="L122" t="n">
-        <v>34620000000</v>
+        <v>241281000000</v>
       </c>
       <c r="M122" t="n">
-        <v>15117000000</v>
+        <v>131234000000</v>
       </c>
       <c r="N122" t="n">
-        <v>42623549009</v>
+        <v>255700814096</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>日本ゼオン株式会社</t>
+          <t>株式会社アイネス</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>9742</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>35.9</v>
+        <v>35.4</v>
       </c>
       <c r="D123" t="n">
-        <v>2347.5</v>
+        <v>2049</v>
       </c>
       <c r="E123" t="n">
-        <v>1721.078563209627</v>
+        <v>1879.137815927515</v>
       </c>
       <c r="F123" t="n">
-        <v>36.4</v>
+        <v>9</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>44521000000</v>
+        <v>9731000000</v>
       </c>
       <c r="J123" t="n">
-        <v>45382000000</v>
+        <v>5286000000</v>
       </c>
       <c r="K123" t="n">
-        <v>71191000000</v>
+        <v>100000000</v>
       </c>
       <c r="L123" t="n">
-        <v>321836000000</v>
+        <v>34620000000</v>
       </c>
       <c r="M123" t="n">
-        <v>161094000000</v>
+        <v>15117000000</v>
       </c>
       <c r="N123" t="n">
-        <v>449183577682</v>
+        <v>42665193903</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>太陽ホールディングス株式会社</t>
+          <t>日本ゼオン株式会社</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>16.4</v>
+        <v>35.8</v>
       </c>
       <c r="D124" t="n">
-        <v>4720</v>
+        <v>2352.5</v>
       </c>
       <c r="E124" t="n">
-        <v>2199.643244598912</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="F124" t="n">
-        <v>114.6</v>
+        <v>36.7</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -6850,26 +6850,26 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>51152000000</v>
+        <v>44521000000</v>
       </c>
       <c r="J124" t="n">
-        <v>30337000000</v>
+        <v>45382000000</v>
       </c>
       <c r="K124" t="n">
-        <v>4870000000</v>
+        <v>71191000000</v>
       </c>
       <c r="L124" t="n">
-        <v>85466000000</v>
+        <v>321836000000</v>
       </c>
       <c r="M124" t="n">
-        <v>86359000000</v>
+        <v>161094000000</v>
       </c>
       <c r="N124" t="n">
-        <v>525225939040</v>
+        <v>450140305218</v>
       </c>
     </row>
     <row r="125">
@@ -6887,13 +6887,13 @@
         <v>16.4</v>
       </c>
       <c r="D125" t="n">
-        <v>4720</v>
+        <v>4719</v>
       </c>
       <c r="E125" t="n">
-        <v>3565.648720929983</v>
+        <v>2199.643244598912</v>
       </c>
       <c r="F125" t="n">
-        <v>32.4</v>
+        <v>114.5</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="I125" t="n">
@@ -6921,31 +6921,31 @@
         <v>86359000000</v>
       </c>
       <c r="N125" t="n">
-        <v>525225939040</v>
+        <v>525114662358</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>株式会社エス・エム・エス</t>
+          <t>太陽ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>8.800000000000001</v>
+        <v>16.4</v>
       </c>
       <c r="D126" t="n">
-        <v>2531</v>
+        <v>4719</v>
       </c>
       <c r="E126" t="n">
-        <v>1478.127248828989</v>
+        <v>3565.648720929983</v>
       </c>
       <c r="F126" t="n">
-        <v>71.2</v>
+        <v>32.3</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -6954,458 +6954,458 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>14126000000</v>
+        <v>51152000000</v>
       </c>
       <c r="J126" t="n">
-        <v>1187000000</v>
+        <v>30337000000</v>
       </c>
       <c r="K126" t="n">
-        <v>2875000000</v>
+        <v>4870000000</v>
       </c>
       <c r="L126" t="n">
-        <v>29991000000</v>
+        <v>85466000000</v>
       </c>
       <c r="M126" t="n">
-        <v>18188000000</v>
+        <v>86359000000</v>
       </c>
       <c r="N126" t="n">
-        <v>207745616419</v>
+        <v>525114662358</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>アニコム ホールディングス株式会社</t>
+          <t>株式会社エス・エム・エス</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>8715</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>41.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D127" t="n">
-        <v>1017</v>
+        <v>2538</v>
       </c>
       <c r="E127" t="n">
-        <v>656.2604975855553</v>
+        <v>1478.127248828989</v>
       </c>
       <c r="F127" t="n">
-        <v>55</v>
+        <v>71.7</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>27691000000</v>
+        <v>14126000000</v>
       </c>
       <c r="J127" t="n">
-        <v>3070000000</v>
+        <v>1187000000</v>
       </c>
       <c r="K127" t="n">
-        <v>3000000</v>
+        <v>2875000000</v>
       </c>
       <c r="L127" t="n">
-        <v>27316000000</v>
+        <v>29991000000</v>
       </c>
       <c r="M127" t="n">
-        <v>30764000000</v>
+        <v>18188000000</v>
       </c>
       <c r="N127" t="n">
-        <v>74059180740</v>
+        <v>208320179562</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>東京製鐵株式会社</t>
+          <t>アニコム ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>8715</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>102.2</v>
+        <v>41.5</v>
       </c>
       <c r="D128" t="n">
-        <v>1702</v>
+        <v>1018</v>
       </c>
       <c r="E128" t="n">
-        <v>1605.452212379354</v>
+        <v>656.2604975855553</v>
       </c>
       <c r="F128" t="n">
-        <v>6</v>
+        <v>55.1</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>68644000000</v>
+        <v>27691000000</v>
       </c>
       <c r="J128" t="n">
-        <v>33060000000</v>
+        <v>3070000000</v>
       </c>
       <c r="K128" t="n">
-        <v>75000000000</v>
+        <v>3000000</v>
       </c>
       <c r="L128" t="n">
-        <v>158280000000</v>
+        <v>27316000000</v>
       </c>
       <c r="M128" t="n">
-        <v>176704000000</v>
+        <v>30764000000</v>
       </c>
       <c r="N128" t="n">
-        <v>172916631982</v>
+        <v>74132001960</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ウェーブロックホールディングス株式会社</t>
+          <t>東京製鐵株式会社</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>7940</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr"/>
-      <c r="D129" t="inlineStr"/>
+          <t>5423</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="D129" t="n">
+        <v>1687</v>
+      </c>
       <c r="E129" t="n">
-        <v>1010</v>
-      </c>
-      <c r="F129" t="inlineStr"/>
+        <v>1605.452212379354</v>
+      </c>
+      <c r="F129" t="n">
+        <v>5.1</v>
+      </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1961626000</v>
+        <v>68644000000</v>
       </c>
       <c r="J129" t="n">
-        <v>2544946000</v>
+        <v>33060000000</v>
       </c>
       <c r="K129" t="n">
-        <v>1068366000</v>
+        <v>75000000000</v>
       </c>
       <c r="L129" t="n">
-        <v>13761535000</v>
+        <v>158280000000</v>
       </c>
       <c r="M129" t="n">
-        <v>5574938000</v>
-      </c>
-      <c r="N129" t="inlineStr"/>
+        <v>176704000000</v>
+      </c>
+      <c r="N129" t="n">
+        <v>171392689867</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>近畿車輛株式会社</t>
+          <t>ウェーブロックホールディングス株式会社</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>7122</t>
-        </is>
-      </c>
-      <c r="C130" t="n">
-        <v>110.1</v>
-      </c>
-      <c r="D130" t="n">
-        <v>2345</v>
-      </c>
+          <t>7940</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="n">
-        <v>2144.894901144641</v>
-      </c>
-      <c r="F130" t="n">
-        <v>9.300000000000001</v>
-      </c>
+        <v>1010</v>
+      </c>
+      <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>6847000000</v>
+        <v>1961626000</v>
       </c>
       <c r="J130" t="n">
-        <v>4580000000</v>
+        <v>2544946000</v>
       </c>
       <c r="K130" t="n">
-        <v>6329000000</v>
+        <v>1068366000</v>
       </c>
       <c r="L130" t="n">
-        <v>24474000000</v>
+        <v>13761535000</v>
       </c>
       <c r="M130" t="n">
-        <v>17756000000</v>
-      </c>
-      <c r="N130" t="n">
-        <v>16133789945</v>
-      </c>
+        <v>5574938000</v>
+      </c>
+      <c r="N130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>株式会社三陽商会</t>
+          <t>近畿車輛株式会社</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>7122</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>66.90000000000001</v>
+        <v>110</v>
       </c>
       <c r="D131" t="n">
-        <v>1302</v>
+        <v>2347</v>
       </c>
       <c r="E131" t="n">
-        <v>3321.975331035734</v>
+        <v>2144.894901144641</v>
       </c>
       <c r="F131" t="n">
-        <v>-60.8</v>
+        <v>9.4</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>16287000000</v>
+        <v>6847000000</v>
       </c>
       <c r="J131" t="n">
-        <v>3021000000</v>
+        <v>4580000000</v>
       </c>
       <c r="K131" t="n">
-        <v>6298000000</v>
+        <v>6329000000</v>
       </c>
       <c r="L131" t="n">
-        <v>33920000000</v>
+        <v>24474000000</v>
       </c>
       <c r="M131" t="n">
-        <v>25606000000</v>
+        <v>17756000000</v>
       </c>
       <c r="N131" t="n">
-        <v>38260613664</v>
+        <v>16147550107</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>月島ホールディングス株式会社</t>
+          <t>株式会社三陽商会</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>6332</t>
+          <t>8011</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>46.4</v>
+        <v>66.2</v>
       </c>
       <c r="D132" t="n">
-        <v>2778</v>
+        <v>1317</v>
       </c>
       <c r="E132" t="n">
-        <v>1410</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="F132" t="n">
-        <v>97</v>
+        <v>-60.4</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>28795000000</v>
+        <v>16287000000</v>
       </c>
       <c r="J132" t="n">
-        <v>22203000000</v>
+        <v>3021000000</v>
       </c>
       <c r="K132" t="n">
-        <v>100000000</v>
+        <v>6298000000</v>
       </c>
       <c r="L132" t="n">
-        <v>80949000000</v>
+        <v>33920000000</v>
       </c>
       <c r="M132" t="n">
-        <v>51098000000</v>
+        <v>25606000000</v>
       </c>
       <c r="N132" t="n">
-        <v>110012197494</v>
+        <v>38701404144</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>マネックスグループ株式会社</t>
+          <t>月島ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>8698</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>15.3</v>
+        <v>47.8</v>
       </c>
       <c r="D133" t="n">
-        <v>717</v>
+        <v>2700</v>
       </c>
       <c r="E133" t="n">
-        <v>510.1850530906719</v>
+        <v>1410</v>
       </c>
       <c r="F133" t="n">
-        <v>40.5</v>
+        <v>91.5</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>17794000000</v>
+        <v>28795000000</v>
       </c>
       <c r="J133" t="n">
-        <v>412000000</v>
+        <v>22203000000</v>
       </c>
       <c r="K133" t="n">
-        <v>9312000000</v>
+        <v>100000000</v>
       </c>
       <c r="L133" t="n">
-        <v>98001000000</v>
+        <v>80949000000</v>
       </c>
       <c r="M133" t="n">
-        <v>27518000000</v>
+        <v>51098000000</v>
       </c>
       <c r="N133" t="n">
-        <v>180227761428</v>
+        <v>106923302100</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>株式会社あおぞら銀行</t>
+          <t>マネックスグループ株式会社</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>8698</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>233.3</v>
+        <v>15.2</v>
       </c>
       <c r="D134" t="n">
-        <v>3358</v>
+        <v>722</v>
       </c>
       <c r="E134" t="n">
-        <v>2190</v>
+        <v>510.1850530906719</v>
       </c>
       <c r="F134" t="n">
-        <v>53.3</v>
+        <v>41.5</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1061743000000</v>
+        <v>17794000000</v>
       </c>
       <c r="J134" t="n">
-        <v>22385000000</v>
+        <v>412000000</v>
       </c>
       <c r="K134" t="n">
-        <v>0</v>
+        <v>9312000000</v>
       </c>
       <c r="L134" t="n">
-        <v>487265000000</v>
+        <v>98001000000</v>
       </c>
       <c r="M134" t="n">
-        <v>1084128000000</v>
+        <v>27518000000</v>
       </c>
       <c r="N134" t="n">
-        <v>464683814392</v>
+        <v>181484579848</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>日本製紙株式会社</t>
+          <t>株式会社あおぞら銀行</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>307.5</v>
+        <v>226.6</v>
       </c>
       <c r="D135" t="n">
-        <v>1300</v>
+        <v>3457</v>
       </c>
       <c r="E135" t="n">
-        <v>1250</v>
+        <v>2190</v>
       </c>
       <c r="F135" t="n">
-        <v>4</v>
+        <v>57.9</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -7414,130 +7414,130 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>136216000000</v>
+        <v>1061743000000</v>
       </c>
       <c r="J135" t="n">
-        <v>151771000000</v>
+        <v>22385000000</v>
       </c>
       <c r="K135" t="n">
-        <v>172984000000</v>
+        <v>0</v>
       </c>
       <c r="L135" t="n">
-        <v>438604000000</v>
+        <v>487265000000</v>
       </c>
       <c r="M135" t="n">
-        <v>460971000000</v>
+        <v>1084128000000</v>
       </c>
       <c r="N135" t="n">
-        <v>149901053900</v>
+        <v>478383379732</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>カルビー株式会社</t>
+          <t>日本製紙株式会社</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>33.6</v>
+        <v>305.9</v>
       </c>
       <c r="D136" t="n">
-        <v>3020</v>
+        <v>1307</v>
       </c>
       <c r="E136" t="n">
-        <v>2919.137515755844</v>
+        <v>1250</v>
       </c>
       <c r="F136" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>49670000000</v>
+        <v>136216000000</v>
       </c>
       <c r="J136" t="n">
-        <v>70285000000</v>
+        <v>151771000000</v>
       </c>
       <c r="K136" t="n">
-        <v>3263000000</v>
+        <v>172984000000</v>
       </c>
       <c r="L136" t="n">
-        <v>183458000000</v>
+        <v>438604000000</v>
       </c>
       <c r="M136" t="n">
-        <v>123218000000</v>
+        <v>460971000000</v>
       </c>
       <c r="N136" t="n">
-        <v>367195319080</v>
+        <v>150708213421</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ＮＩＴＴＯＫＵ株式会社</t>
+          <t>カルビー株式会社</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>51.2</v>
+        <v>33.5</v>
       </c>
       <c r="D137" t="n">
-        <v>2438</v>
+        <v>3024</v>
       </c>
       <c r="E137" t="n">
-        <v>1710</v>
+        <v>2919.137515755844</v>
       </c>
       <c r="F137" t="n">
-        <v>42.6</v>
+        <v>3.6</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>11768000000</v>
+        <v>49670000000</v>
       </c>
       <c r="J137" t="n">
-        <v>6299000000</v>
+        <v>70285000000</v>
       </c>
       <c r="K137" t="n">
-        <v>2999000000</v>
+        <v>3263000000</v>
       </c>
       <c r="L137" t="n">
-        <v>33919000000</v>
+        <v>183458000000</v>
       </c>
       <c r="M137" t="n">
-        <v>21066000000</v>
+        <v>123218000000</v>
       </c>
       <c r="N137" t="n">
-        <v>41139987116</v>
+        <v>367681670496</v>
       </c>
     </row>
     <row r="138">
@@ -7552,16 +7552,16 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>51.2</v>
+        <v>50</v>
       </c>
       <c r="D138" t="n">
-        <v>2438</v>
+        <v>2497</v>
       </c>
       <c r="E138" t="n">
         <v>1710</v>
       </c>
       <c r="F138" t="n">
-        <v>42.6</v>
+        <v>46</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="I138" t="n">
@@ -7589,31 +7589,31 @@
         <v>21066000000</v>
       </c>
       <c r="N138" t="n">
-        <v>41139987116</v>
+        <v>42135581554</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>新光商事株式会社</t>
+          <t>ＮＩＴＴＯＫＵ株式会社</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>8141</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>30.8</v>
+        <v>50</v>
       </c>
       <c r="D139" t="n">
-        <v>1567</v>
+        <v>2497</v>
       </c>
       <c r="E139" t="n">
-        <v>930</v>
+        <v>1710</v>
       </c>
       <c r="F139" t="n">
-        <v>68.5</v>
+        <v>46</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -7622,50 +7622,50 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>10579000000</v>
+        <v>11768000000</v>
       </c>
       <c r="J139" t="n">
-        <v>195000000</v>
+        <v>6299000000</v>
       </c>
       <c r="K139" t="n">
-        <v>2995000000</v>
+        <v>2999000000</v>
       </c>
       <c r="L139" t="n">
-        <v>51945000000</v>
+        <v>33919000000</v>
       </c>
       <c r="M139" t="n">
-        <v>13769000000</v>
+        <v>21066000000</v>
       </c>
       <c r="N139" t="n">
-        <v>44737691733</v>
+        <v>42135581554</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>株式会社メガチップス</t>
+          <t>新光商事株式会社</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>6875</t>
+          <t>8141</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>87.7</v>
+        <v>30.8</v>
       </c>
       <c r="D140" t="n">
-        <v>10710</v>
+        <v>1567</v>
       </c>
       <c r="E140" t="n">
-        <v>4870</v>
+        <v>930</v>
       </c>
       <c r="F140" t="n">
-        <v>119.9</v>
+        <v>68.5</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -7674,158 +7674,158 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>25769446000</v>
+        <v>10579000000</v>
       </c>
       <c r="J140" t="n">
-        <v>2249411000</v>
+        <v>195000000</v>
       </c>
       <c r="K140" t="n">
-        <v>101636005000</v>
+        <v>2995000000</v>
       </c>
       <c r="L140" t="n">
-        <v>67428618000</v>
+        <v>51945000000</v>
       </c>
       <c r="M140" t="n">
-        <v>129654862000</v>
+        <v>13769000000</v>
       </c>
       <c r="N140" t="n">
-        <v>147807649710</v>
+        <v>44737691733</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>株式会社青山財産ネットワークス</t>
+          <t>株式会社メガチップス</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>8929</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>42.6</v>
+        <v>88.5</v>
       </c>
       <c r="D141" t="n">
-        <v>1360</v>
+        <v>10620</v>
       </c>
       <c r="E141" t="n">
-        <v>1347.74653160027</v>
+        <v>4870</v>
       </c>
       <c r="F141" t="n">
-        <v>0.9</v>
+        <v>118.1</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>10862000000</v>
+        <v>25769446000</v>
       </c>
       <c r="J141" t="n">
-        <v>245000000</v>
+        <v>2249411000</v>
       </c>
       <c r="K141" t="n">
-        <v>2845000000</v>
+        <v>101636005000</v>
       </c>
       <c r="L141" t="n">
-        <v>7128000000</v>
+        <v>67428618000</v>
       </c>
       <c r="M141" t="n">
-        <v>13952000000</v>
+        <v>129654862000</v>
       </c>
       <c r="N141" t="n">
-        <v>32728723680</v>
+        <v>146565568620</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>平和不動産株式会社</t>
+          <t>株式会社青山財産ネットワークス</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>8803</t>
+          <t>8929</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>73.09999999999999</v>
+        <v>43.4</v>
       </c>
       <c r="D142" t="n">
-        <v>2347</v>
+        <v>1335</v>
       </c>
       <c r="E142" t="n">
-        <v>3610</v>
+        <v>1347.74653160027</v>
       </c>
       <c r="F142" t="n">
-        <v>-35</v>
+        <v>-0.9</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>28111000000</v>
+        <v>10862000000</v>
       </c>
       <c r="J142" t="n">
-        <v>79319000000</v>
+        <v>245000000</v>
       </c>
       <c r="K142" t="n">
-        <v>5997000000</v>
+        <v>2845000000</v>
       </c>
       <c r="L142" t="n">
-        <v>119278000000</v>
+        <v>7128000000</v>
       </c>
       <c r="M142" t="n">
-        <v>113427000000</v>
+        <v>13952000000</v>
       </c>
       <c r="N142" t="n">
-        <v>155066895526</v>
+        <v>32127092730</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>小林製薬株式会社</t>
+          <t>平和不動産株式会社</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>30.5</v>
+        <v>73.8</v>
       </c>
       <c r="D143" t="n">
-        <v>5700</v>
+        <v>2325</v>
       </c>
       <c r="E143" t="n">
-        <v>2148.936934940886</v>
+        <v>3610</v>
       </c>
       <c r="F143" t="n">
-        <v>165.2</v>
+        <v>-35.6</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -7834,22 +7834,22 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>81987000000</v>
+        <v>28111000000</v>
       </c>
       <c r="J143" t="n">
-        <v>32461000000</v>
+        <v>79319000000</v>
       </c>
       <c r="K143" t="n">
-        <v>14872000000</v>
+        <v>5997000000</v>
       </c>
       <c r="L143" t="n">
-        <v>195600000000</v>
+        <v>119278000000</v>
       </c>
       <c r="M143" t="n">
-        <v>129320000000</v>
+        <v>113427000000</v>
       </c>
       <c r="N143" t="n">
-        <v>423730139700</v>
+        <v>153613349850</v>
       </c>
     </row>
     <row r="144">
@@ -7864,16 +7864,16 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>30.5</v>
+        <v>30.1</v>
       </c>
       <c r="D144" t="n">
-        <v>5700</v>
+        <v>5777</v>
       </c>
       <c r="E144" t="n">
-        <v>5066.092575838703</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="F144" t="n">
-        <v>12.5</v>
+        <v>168.8</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -7901,31 +7901,31 @@
         <v>129320000000</v>
       </c>
       <c r="N144" t="n">
-        <v>423730139700</v>
+        <v>429454213517</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>セーレン株式会社</t>
+          <t>小林製薬株式会社</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>3569</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>36.4</v>
+        <v>30.1</v>
       </c>
       <c r="D145" t="n">
-        <v>3295</v>
+        <v>5777</v>
       </c>
       <c r="E145" t="n">
-        <v>1359.655069733296</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="F145" t="n">
-        <v>142.3</v>
+        <v>14</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -7934,50 +7934,50 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>35451000000</v>
+        <v>81987000000</v>
       </c>
       <c r="J145" t="n">
-        <v>25813000000</v>
+        <v>32461000000</v>
       </c>
       <c r="K145" t="n">
-        <v>8891000000</v>
+        <v>14872000000</v>
       </c>
       <c r="L145" t="n">
-        <v>91845000000</v>
+        <v>195600000000</v>
       </c>
       <c r="M145" t="n">
-        <v>70155000000</v>
+        <v>129320000000</v>
       </c>
       <c r="N145" t="n">
-        <v>192969174095</v>
+        <v>429454213517</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>データセクション株式会社</t>
+          <t>セーレン株式会社</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>3569</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>2.6</v>
+        <v>36.9</v>
       </c>
       <c r="D146" t="n">
-        <v>1532</v>
+        <v>3250</v>
       </c>
       <c r="E146" t="n">
-        <v>5143.276404494382</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="F146" t="n">
-        <v>-70.2</v>
+        <v>139</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -7986,102 +7986,102 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1420430000</v>
+        <v>35451000000</v>
       </c>
       <c r="J146" t="n">
-        <v>1162000</v>
+        <v>25813000000</v>
       </c>
       <c r="K146" t="n">
-        <v>49326000</v>
+        <v>8891000000</v>
       </c>
       <c r="L146" t="n">
-        <v>2818110000</v>
+        <v>91845000000</v>
       </c>
       <c r="M146" t="n">
-        <v>1470918000</v>
+        <v>70155000000</v>
       </c>
       <c r="N146" t="n">
-        <v>57392252792</v>
+        <v>190333783250</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>愛眼株式会社</t>
+          <t>データセクション株式会社</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>9854</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>70.40000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="D147" t="n">
-        <v>282</v>
+        <v>1605</v>
       </c>
       <c r="E147" t="n">
-        <v>246.9708756284982</v>
+        <v>5143.276404494382</v>
       </c>
       <c r="F147" t="n">
-        <v>14.2</v>
+        <v>-68.8</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2219000000</v>
+        <v>1420430000</v>
       </c>
       <c r="J147" t="n">
-        <v>1030000000</v>
+        <v>1162000</v>
       </c>
       <c r="K147" t="n">
-        <v>604000000</v>
+        <v>49326000</v>
       </c>
       <c r="L147" t="n">
-        <v>12920000000</v>
+        <v>2818110000</v>
       </c>
       <c r="M147" t="n">
-        <v>3853000000</v>
+        <v>1470918000</v>
       </c>
       <c r="N147" t="n">
-        <v>5472693630</v>
+        <v>60127001130</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>株式会社アシロ</t>
+          <t>愛眼株式会社</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>14.1</v>
+        <v>70.7</v>
       </c>
       <c r="D148" t="n">
-        <v>1545</v>
+        <v>281</v>
       </c>
       <c r="E148" t="n">
-        <v>1396.628697042366</v>
+        <v>246.9708756284982</v>
       </c>
       <c r="F148" t="n">
-        <v>10.6</v>
+        <v>13.8</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -8090,546 +8090,598 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1428281000</v>
+        <v>2219000000</v>
       </c>
       <c r="J148" t="n">
-        <v>102238000</v>
+        <v>1030000000</v>
       </c>
       <c r="K148" t="n">
-        <v>0</v>
+        <v>604000000</v>
       </c>
       <c r="L148" t="n">
-        <v>1804458000</v>
+        <v>12920000000</v>
       </c>
       <c r="M148" t="n">
-        <v>1530519000</v>
+        <v>3853000000</v>
       </c>
       <c r="N148" t="n">
-        <v>10860711915</v>
+        <v>5453286915</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>三浦工業株式会社</t>
+          <t>株式会社アシロ</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>7378</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>11.8</v>
+        <v>14</v>
       </c>
       <c r="D149" t="n">
-        <v>3082</v>
+        <v>1560</v>
       </c>
       <c r="E149" t="n">
-        <v>3147.518794622453</v>
+        <v>1396.628697042366</v>
       </c>
       <c r="F149" t="n">
-        <v>-2.1</v>
+        <v>11.7</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>20794000000</v>
+        <v>1428281000</v>
       </c>
       <c r="J149" t="n">
-        <v>10600000000</v>
+        <v>102238000</v>
       </c>
       <c r="K149" t="n">
-        <v>10773000000</v>
+        <v>0</v>
       </c>
       <c r="L149" t="n">
-        <v>138378000000</v>
+        <v>1804458000</v>
       </c>
       <c r="M149" t="n">
-        <v>42167000000</v>
+        <v>1530519000</v>
       </c>
       <c r="N149" t="n">
-        <v>356739527520</v>
+        <v>10966155720</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>株式会社カカクコム</t>
+          <t>三浦工業株式会社</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>7</v>
+        <v>11.9</v>
       </c>
       <c r="D150" t="n">
-        <v>3702</v>
+        <v>3054</v>
       </c>
       <c r="E150" t="n">
-        <v>2318.314890576102</v>
+        <v>3147.518794622453</v>
       </c>
       <c r="F150" t="n">
-        <v>59.7</v>
+        <v>-3</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>46452000000</v>
+        <v>20794000000</v>
       </c>
       <c r="J150" t="n">
-        <v>68000000</v>
+        <v>10600000000</v>
       </c>
       <c r="K150" t="n">
-        <v>4669000000</v>
+        <v>10773000000</v>
       </c>
       <c r="L150" t="n">
-        <v>45479000000</v>
+        <v>138378000000</v>
       </c>
       <c r="M150" t="n">
-        <v>51189000000</v>
+        <v>42167000000</v>
       </c>
       <c r="N150" t="n">
-        <v>732389860434</v>
+        <v>353498545440</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>古河機械金属株式会社</t>
+          <t>株式会社カカクコム</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>42.6</v>
+        <v>7</v>
       </c>
       <c r="D151" t="n">
-        <v>4380</v>
+        <v>3695</v>
       </c>
       <c r="E151" t="n">
-        <v>1600</v>
+        <v>2318.314890576102</v>
       </c>
       <c r="F151" t="n">
-        <v>173.8</v>
+        <v>59.4</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>14468000000</v>
+        <v>46452000000</v>
       </c>
       <c r="J151" t="n">
-        <v>26121000000</v>
+        <v>68000000</v>
       </c>
       <c r="K151" t="n">
-        <v>19903000000</v>
+        <v>4669000000</v>
       </c>
       <c r="L151" t="n">
-        <v>100075000000</v>
+        <v>45479000000</v>
       </c>
       <c r="M151" t="n">
-        <v>60492000000</v>
+        <v>51189000000</v>
       </c>
       <c r="N151" t="n">
-        <v>142047149280</v>
+        <v>731005006565</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>多木化学株式会社</t>
+          <t>古河機械金属株式会社</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>4025</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>31.2</v>
+        <v>44.6</v>
       </c>
       <c r="D152" t="n">
-        <v>5610</v>
+        <v>4265</v>
       </c>
       <c r="E152" t="n">
-        <v>4695.956053243186</v>
+        <v>1600</v>
       </c>
       <c r="F152" t="n">
-        <v>19.5</v>
+        <v>166.6</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>6433000000</v>
+        <v>14468000000</v>
       </c>
       <c r="J152" t="n">
-        <v>7985000000</v>
+        <v>26121000000</v>
       </c>
       <c r="K152" t="n">
-        <v>199000000</v>
+        <v>19903000000</v>
       </c>
       <c r="L152" t="n">
-        <v>29378000000</v>
+        <v>100075000000</v>
       </c>
       <c r="M152" t="n">
-        <v>14617000000</v>
+        <v>60492000000</v>
       </c>
       <c r="N152" t="n">
-        <v>46828740090</v>
+        <v>135499549005</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>エムスリー株式会社</t>
+          <t>多木化学株式会社</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2413</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>8</v>
+        <v>30.8</v>
       </c>
       <c r="D153" t="n">
-        <v>1666</v>
+        <v>5680</v>
       </c>
       <c r="E153" t="n">
-        <v>1638.585693292194</v>
+        <v>4695.956053243186</v>
       </c>
       <c r="F153" t="n">
-        <v>1.7</v>
+        <v>21</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>78812000000</v>
+        <v>6433000000</v>
       </c>
       <c r="J153" t="n">
-        <v>345000000</v>
+        <v>7985000000</v>
       </c>
       <c r="K153" t="n">
-        <v>9506000000</v>
+        <v>199000000</v>
       </c>
       <c r="L153" t="n">
-        <v>152472000000</v>
+        <v>29378000000</v>
       </c>
       <c r="M153" t="n">
-        <v>88663000000</v>
+        <v>14617000000</v>
       </c>
       <c r="N153" t="n">
-        <v>1110082890826</v>
+        <v>47413055920</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>三井松島ホールディングス株式会社</t>
+          <t>エムスリー株式会社</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>40.1</v>
+        <v>7.8</v>
       </c>
       <c r="D154" t="n">
-        <v>2283</v>
+        <v>1701</v>
       </c>
       <c r="E154" t="n">
-        <v>2920</v>
+        <v>1638.585693292194</v>
       </c>
       <c r="F154" t="n">
-        <v>-21.8</v>
+        <v>3.8</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>19413000000</v>
+        <v>78812000000</v>
       </c>
       <c r="J154" t="n">
-        <v>3540000000</v>
+        <v>345000000</v>
       </c>
       <c r="K154" t="n">
-        <v>10945000000</v>
+        <v>9506000000</v>
       </c>
       <c r="L154" t="n">
-        <v>35537000000</v>
+        <v>152472000000</v>
       </c>
       <c r="M154" t="n">
-        <v>33898000000</v>
+        <v>88663000000</v>
       </c>
       <c r="N154" t="n">
-        <v>84534832680</v>
+        <v>1133403959961</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ノリタケ株式会社</t>
+          <t>三井松島ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>38.9</v>
+        <v>40.2</v>
       </c>
       <c r="D155" t="n">
-        <v>3500</v>
+        <v>2275</v>
       </c>
       <c r="E155" t="n">
-        <v>3573.410502159827</v>
+        <v>2920</v>
       </c>
       <c r="F155" t="n">
-        <v>-2.1</v>
+        <v>-22.1</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="I155" t="n">
-        <v>11733000000</v>
+        <v>19413000000</v>
       </c>
       <c r="J155" t="n">
-        <v>20204000000</v>
+        <v>3540000000</v>
       </c>
       <c r="K155" t="n">
-        <v>42879000000</v>
+        <v>10945000000</v>
       </c>
       <c r="L155" t="n">
-        <v>118800000000</v>
+        <v>35537000000</v>
       </c>
       <c r="M155" t="n">
-        <v>74816000000</v>
+        <v>33898000000</v>
       </c>
       <c r="N155" t="n">
-        <v>192549959000</v>
+        <v>84238609000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>株式会社ＡＣＳＬ</t>
+          <t>ノリタケ株式会社</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>8.1</v>
+        <v>39.2</v>
       </c>
       <c r="D156" t="n">
-        <v>1316</v>
+        <v>3470</v>
       </c>
       <c r="E156" t="n">
-        <v>913.2768512341561</v>
+        <v>3573.410502159827</v>
       </c>
       <c r="F156" t="n">
-        <v>44.1</v>
+        <v>-2.9</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1891731000</v>
+        <v>11733000000</v>
       </c>
       <c r="J156" t="n">
-        <v>3724000</v>
+        <v>20204000000</v>
       </c>
       <c r="K156" t="n">
-        <v>197577000</v>
+        <v>42879000000</v>
       </c>
       <c r="L156" t="n">
-        <v>3572642000</v>
+        <v>118800000000</v>
       </c>
       <c r="M156" t="n">
-        <v>2093032000</v>
+        <v>74816000000</v>
       </c>
       <c r="N156" t="n">
-        <v>25757070472</v>
+        <v>190899530780</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>株式会社スズケン</t>
+          <t>株式会社ＡＣＳＬ</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>9987</t>
+          <t>6232</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>77.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D157" t="n">
-        <v>5177</v>
+        <v>1304</v>
       </c>
       <c r="E157" t="n">
-        <v>4137.137750115735</v>
+        <v>913.2768512341561</v>
       </c>
       <c r="F157" t="n">
-        <v>25.1</v>
+        <v>42.8</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="I157" t="n">
-        <v>168215000000</v>
+        <v>1891731000</v>
       </c>
       <c r="J157" t="n">
-        <v>65453000000</v>
+        <v>3724000</v>
       </c>
       <c r="K157" t="n">
-        <v>38927000000</v>
+        <v>197577000</v>
       </c>
       <c r="L157" t="n">
-        <v>418062000000</v>
+        <v>3572642000</v>
       </c>
       <c r="M157" t="n">
-        <v>272595000000</v>
+        <v>2093032000</v>
       </c>
       <c r="N157" t="n">
-        <v>350161123565</v>
+        <v>25522203568</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
+          <t>株式会社スズケン</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="D158" t="n">
+        <v>5197</v>
+      </c>
+      <c r="E158" t="n">
+        <v>4137.137750115735</v>
+      </c>
+      <c r="F158" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>168215000000</v>
+      </c>
+      <c r="J158" t="n">
+        <v>65453000000</v>
+      </c>
+      <c r="K158" t="n">
+        <v>38927000000</v>
+      </c>
+      <c r="L158" t="n">
+        <v>418062000000</v>
+      </c>
+      <c r="M158" t="n">
+        <v>272595000000</v>
+      </c>
+      <c r="N158" t="n">
+        <v>351513880465</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
           <t>フォスター電機株式会社</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
+      <c r="B159" t="inlineStr">
         <is>
           <t>6794</t>
         </is>
       </c>
-      <c r="C158" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="D158" t="n">
-        <v>2896</v>
-      </c>
-      <c r="E158" t="n">
+      <c r="C159" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="D159" t="n">
+        <v>2965</v>
+      </c>
+      <c r="E159" t="n">
         <v>2681.96152003832</v>
       </c>
-      <c r="F158" t="n">
-        <v>8</v>
-      </c>
-      <c r="G158" t="inlineStr">
+      <c r="F159" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="G159" t="inlineStr">
         <is>
           <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
+      <c r="H159" t="inlineStr">
         <is>
           <t>2026-01-22</t>
         </is>
       </c>
-      <c r="I158" t="n">
+      <c r="I159" t="n">
         <v>12089000000</v>
       </c>
-      <c r="J158" t="n">
+      <c r="J159" t="n">
         <v>7327000000</v>
       </c>
-      <c r="K158" t="n">
+      <c r="K159" t="n">
         <v>1115000000</v>
       </c>
-      <c r="L158" t="n">
+      <c r="L159" t="n">
         <v>51632000000</v>
       </c>
-      <c r="M158" t="n">
+      <c r="M159" t="n">
         <v>20531000000</v>
       </c>
-      <c r="N158" t="n">
-        <v>65066769072</v>
+      <c r="N159" t="n">
+        <v>66617047755</v>
       </c>
     </row>
   </sheetData>

--- a/docs/アクティビスト銘柄_資産判定.xlsx
+++ b/docs/アクティビスト銘柄_資産判定.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N159"/>
+  <dimension ref="A1:N161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>45.5</v>
+        <v>45.7</v>
       </c>
       <c r="D2" t="n">
-        <v>1308</v>
+        <v>1302</v>
       </c>
       <c r="E2" t="n">
         <v>1111.251693601708</v>
       </c>
       <c r="F2" t="n">
-        <v>17.7</v>
+        <v>17.2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -537,7 +537,7 @@
         <v>213563000000</v>
       </c>
       <c r="N2" t="n">
-        <v>469613908320</v>
+        <v>467459716080</v>
       </c>
     </row>
     <row r="3">
@@ -552,16 +552,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>55.7</v>
+        <v>55.4</v>
       </c>
       <c r="D3" t="n">
-        <v>1142</v>
+        <v>1147</v>
       </c>
       <c r="E3" t="n">
         <v>1019.677694332945</v>
       </c>
       <c r="F3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         <v>106991000000</v>
       </c>
       <c r="N3" t="n">
-        <v>192142128100</v>
+        <v>192983380850</v>
       </c>
     </row>
     <row r="4">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="D4" t="n">
-        <v>3439</v>
+        <v>3387</v>
       </c>
       <c r="E4" t="n">
         <v>6116.356643776557</v>
       </c>
       <c r="F4" t="n">
-        <v>-43.8</v>
+        <v>-44.6</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         <v>219041000000</v>
       </c>
       <c r="N4" t="n">
-        <v>3111462741366</v>
+        <v>3064415325678</v>
       </c>
     </row>
     <row r="5">
@@ -656,16 +656,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>31.2</v>
+        <v>31</v>
       </c>
       <c r="D5" t="n">
-        <v>2152.5</v>
+        <v>2171</v>
       </c>
       <c r="E5" t="n">
         <v>1815.198567455447</v>
       </c>
       <c r="F5" t="n">
-        <v>18.6</v>
+        <v>19.6</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         <v>168499000000</v>
       </c>
       <c r="N5" t="n">
-        <v>539453634930</v>
+        <v>544090054092</v>
       </c>
     </row>
     <row r="6">
@@ -708,16 +708,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>54.2</v>
+        <v>55.1</v>
       </c>
       <c r="D6" t="n">
-        <v>10750</v>
+        <v>10620</v>
       </c>
       <c r="E6" t="n">
         <v>5684.0003469471</v>
       </c>
       <c r="F6" t="n">
-        <v>89.09999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>91895000000</v>
       </c>
       <c r="N6" t="n">
-        <v>169420612750</v>
+        <v>166851435960</v>
       </c>
     </row>
     <row r="7">
@@ -760,16 +760,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>54.2</v>
+        <v>55.1</v>
       </c>
       <c r="D7" t="n">
-        <v>10750</v>
+        <v>10620</v>
       </c>
       <c r="E7" t="n">
         <v>4549.503641591014</v>
       </c>
       <c r="F7" t="n">
-        <v>136.3</v>
+        <v>133.4</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>91895000000</v>
       </c>
       <c r="N7" t="n">
-        <v>169420612750</v>
+        <v>166851435960</v>
       </c>
     </row>
     <row r="8">
@@ -815,13 +815,13 @@
         <v>14.5</v>
       </c>
       <c r="D8" t="n">
-        <v>3865</v>
+        <v>3860</v>
       </c>
       <c r="E8" t="n">
         <v>1361.432492253209</v>
       </c>
       <c r="F8" t="n">
-        <v>183.9</v>
+        <v>183.5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>12397436000</v>
       </c>
       <c r="N8" t="n">
-        <v>85738628425</v>
+        <v>85627711700</v>
       </c>
     </row>
     <row r="9">
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="D9" t="n">
-        <v>3283</v>
+        <v>3298</v>
       </c>
       <c r="E9" t="n">
         <v>13739.64575539568</v>
       </c>
       <c r="F9" t="n">
-        <v>-76.09999999999999</v>
+        <v>-76</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>325393000000</v>
       </c>
       <c r="N9" t="n">
-        <v>1069379075240</v>
+        <v>1074265059440</v>
       </c>
     </row>
     <row r="10">
@@ -916,16 +916,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>46.9</v>
+        <v>48.2</v>
       </c>
       <c r="D10" t="n">
-        <v>2061</v>
+        <v>2004.5</v>
       </c>
       <c r="E10" t="n">
         <v>1198.150742177053</v>
       </c>
       <c r="F10" t="n">
-        <v>72</v>
+        <v>67.3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>213966000000</v>
       </c>
       <c r="N10" t="n">
-        <v>456333720201</v>
+        <v>443823843834</v>
       </c>
     </row>
     <row r="11">
@@ -968,16 +968,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>46.9</v>
+        <v>48.2</v>
       </c>
       <c r="D11" t="n">
-        <v>2061</v>
+        <v>2004.5</v>
       </c>
       <c r="E11" t="n">
         <v>1188.162962482466</v>
       </c>
       <c r="F11" t="n">
-        <v>73.5</v>
+        <v>68.7</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>213966000000</v>
       </c>
       <c r="N11" t="n">
-        <v>456333720201</v>
+        <v>443823843834</v>
       </c>
     </row>
     <row r="12">
@@ -1023,13 +1023,13 @@
         <v>24.6</v>
       </c>
       <c r="D12" t="n">
-        <v>3599</v>
+        <v>3588</v>
       </c>
       <c r="E12" t="n">
         <v>2995.424821743842</v>
       </c>
       <c r="F12" t="n">
-        <v>20.1</v>
+        <v>19.8</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>129979000000</v>
       </c>
       <c r="N12" t="n">
-        <v>528929496716</v>
+        <v>527312874192</v>
       </c>
     </row>
     <row r="13">
@@ -1072,16 +1072,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>73.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="D13" t="n">
-        <v>4893</v>
+        <v>4815</v>
       </c>
       <c r="E13" t="n">
         <v>4991.027246539169</v>
       </c>
       <c r="F13" t="n">
-        <v>-2</v>
+        <v>-3.5</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>1007966000000</v>
       </c>
       <c r="N13" t="n">
-        <v>1378586828178</v>
+        <v>1349267610690</v>
       </c>
     </row>
     <row r="14">
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="D14" t="n">
-        <v>1721.5</v>
+        <v>1702.5</v>
       </c>
       <c r="E14" t="n">
         <v>1512.21980974841</v>
       </c>
       <c r="F14" t="n">
-        <v>13.8</v>
+        <v>12.6</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>120816000000</v>
       </c>
       <c r="N14" t="n">
-        <v>567090957504</v>
+        <v>560832039008</v>
       </c>
     </row>
     <row r="15">
@@ -1179,13 +1179,13 @@
         <v>7.6</v>
       </c>
       <c r="D15" t="n">
-        <v>2604</v>
+        <v>2607</v>
       </c>
       <c r="E15" t="n">
         <v>1827.011042553346</v>
       </c>
       <c r="F15" t="n">
-        <v>42.5</v>
+        <v>42.7</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>48336000000</v>
       </c>
       <c r="N15" t="n">
-        <v>635565495684</v>
+        <v>636297713997</v>
       </c>
     </row>
     <row r="16">
@@ -1228,16 +1228,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>136.8</v>
+        <v>140.4</v>
       </c>
       <c r="D16" t="n">
-        <v>1572</v>
+        <v>1532</v>
       </c>
       <c r="E16" t="n">
         <v>2122.579027791042</v>
       </c>
       <c r="F16" t="n">
-        <v>-25.9</v>
+        <v>-27.8</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>80333000000</v>
       </c>
       <c r="N16" t="n">
-        <v>58718015244</v>
+        <v>57223918164</v>
       </c>
     </row>
     <row r="17">
@@ -1280,16 +1280,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="D17" t="n">
-        <v>2855.5</v>
+        <v>2881</v>
       </c>
       <c r="E17" t="n">
         <v>6272.971195510064</v>
       </c>
       <c r="F17" t="n">
-        <v>-54.5</v>
+        <v>-54.1</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>179622000000</v>
       </c>
       <c r="N17" t="n">
-        <v>1029908987337</v>
+        <v>1039106213454</v>
       </c>
     </row>
     <row r="18">
@@ -1332,16 +1332,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="D18" t="n">
-        <v>3674</v>
+        <v>3761</v>
       </c>
       <c r="E18" t="n">
         <v>1572.181660925393</v>
       </c>
       <c r="F18" t="n">
-        <v>133.7</v>
+        <v>139.2</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>35501000000</v>
       </c>
       <c r="N18" t="n">
-        <v>656040671418</v>
+        <v>671575657377</v>
       </c>
     </row>
     <row r="19">
@@ -1384,16 +1384,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="D19" t="n">
-        <v>3674</v>
+        <v>3761</v>
       </c>
       <c r="E19" t="n">
         <v>1141.512891683109</v>
       </c>
       <c r="F19" t="n">
-        <v>221.9</v>
+        <v>229.5</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>35501000000</v>
       </c>
       <c r="N19" t="n">
-        <v>656040671418</v>
+        <v>671575657377</v>
       </c>
     </row>
     <row r="20">
@@ -1436,16 +1436,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>45.5</v>
+        <v>45.8</v>
       </c>
       <c r="D20" t="n">
-        <v>5905</v>
+        <v>5863</v>
       </c>
       <c r="E20" t="n">
         <v>2836.942753814942</v>
       </c>
       <c r="F20" t="n">
-        <v>108.1</v>
+        <v>106.7</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>94351000000</v>
       </c>
       <c r="N20" t="n">
-        <v>207560283505</v>
+        <v>206083986823</v>
       </c>
     </row>
     <row r="21">
@@ -1488,16 +1488,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>55.4</v>
+        <v>55.3</v>
       </c>
       <c r="D21" t="n">
-        <v>4052</v>
+        <v>4063</v>
       </c>
       <c r="E21" t="n">
         <v>2863.970160821546</v>
       </c>
       <c r="F21" t="n">
-        <v>41.5</v>
+        <v>41.9</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>161529000000</v>
       </c>
       <c r="N21" t="n">
-        <v>291521800476</v>
+        <v>292313197269</v>
       </c>
     </row>
     <row r="22">
@@ -1540,16 +1540,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>52.6</v>
+        <v>53.3</v>
       </c>
       <c r="D22" t="n">
-        <v>4645</v>
+        <v>4612</v>
       </c>
       <c r="E22" t="n">
         <v>2566.284807227078</v>
       </c>
       <c r="F22" t="n">
-        <v>81</v>
+        <v>79.7</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>231575000000</v>
       </c>
       <c r="N22" t="n">
-        <v>439942368080</v>
+        <v>434852105200</v>
       </c>
     </row>
     <row r="23">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28.9</v>
+        <v>29</v>
       </c>
       <c r="D23" t="n">
-        <v>5115</v>
+        <v>5093</v>
       </c>
       <c r="E23" t="n">
         <v>2779.139169918938</v>
       </c>
       <c r="F23" t="n">
-        <v>84</v>
+        <v>83.3</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>183216000000</v>
       </c>
       <c r="N23" t="n">
-        <v>634426089165</v>
+        <v>631697374803</v>
       </c>
     </row>
     <row r="24">
@@ -1644,16 +1644,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>4002</v>
+        <v>3950</v>
       </c>
       <c r="E24" t="n">
         <v>2420.370957920882</v>
       </c>
       <c r="F24" t="n">
-        <v>65.3</v>
+        <v>63.2</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>18167000000</v>
       </c>
       <c r="N24" t="n">
-        <v>197847190158</v>
+        <v>195276462050</v>
       </c>
     </row>
     <row r="25">
@@ -1696,16 +1696,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>1745</v>
+        <v>1725</v>
       </c>
       <c r="E25" t="n">
         <v>1344.518957928979</v>
       </c>
       <c r="F25" t="n">
-        <v>29.8</v>
+        <v>28.3</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>45956000000</v>
       </c>
       <c r="N25" t="n">
-        <v>561464661485</v>
+        <v>555029536425</v>
       </c>
     </row>
     <row r="26">
@@ -1748,16 +1748,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>59.9</v>
+        <v>60.1</v>
       </c>
       <c r="D26" t="n">
-        <v>4998</v>
+        <v>4984</v>
       </c>
       <c r="E26" t="n">
         <v>4154.626869982095</v>
       </c>
       <c r="F26" t="n">
-        <v>20.3</v>
+        <v>20</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>179086000000</v>
       </c>
       <c r="N26" t="n">
-        <v>298883778648</v>
+        <v>298046569184</v>
       </c>
     </row>
     <row r="27">
@@ -1800,16 +1800,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="D27" t="n">
-        <v>3828</v>
+        <v>3810</v>
       </c>
       <c r="E27" t="n">
         <v>2561.705402476645</v>
       </c>
       <c r="F27" t="n">
-        <v>49.4</v>
+        <v>48.7</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>100104000000</v>
       </c>
       <c r="N27" t="n">
-        <v>700452818340</v>
+        <v>697159153050</v>
       </c>
     </row>
     <row r="28">
@@ -1852,16 +1852,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>45.3</v>
+        <v>44.7</v>
       </c>
       <c r="D28" t="n">
-        <v>3412</v>
+        <v>3461</v>
       </c>
       <c r="E28" t="n">
         <v>2560</v>
       </c>
       <c r="F28" t="n">
-        <v>33.3</v>
+        <v>35.2</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>190312000000</v>
       </c>
       <c r="N28" t="n">
-        <v>420052364072</v>
+        <v>426084769066</v>
       </c>
     </row>
     <row r="29">
@@ -1904,16 +1904,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>90.59999999999999</v>
+        <v>91</v>
       </c>
       <c r="D29" t="n">
-        <v>4245</v>
+        <v>4225</v>
       </c>
       <c r="E29" t="n">
         <v>3449.780346820809</v>
       </c>
       <c r="F29" t="n">
-        <v>23.1</v>
+        <v>22.5</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>90928000000</v>
       </c>
       <c r="N29" t="n">
-        <v>100381565940</v>
+        <v>99908625700</v>
       </c>
     </row>
     <row r="30">
@@ -1956,16 +1956,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>60.7</v>
+        <v>59.6</v>
       </c>
       <c r="D30" t="n">
-        <v>1572</v>
+        <v>1603</v>
       </c>
       <c r="E30" t="n">
         <v>1746.940387696806</v>
       </c>
       <c r="F30" t="n">
-        <v>-10</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>36070000000</v>
       </c>
       <c r="N30" t="n">
-        <v>59392506996</v>
+        <v>60563733279</v>
       </c>
     </row>
     <row r="31">
@@ -2008,16 +2008,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>106.6</v>
+        <v>105.7</v>
       </c>
       <c r="D31" t="n">
-        <v>1664</v>
+        <v>1677</v>
       </c>
       <c r="E31" t="n">
         <v>2298.672482457804</v>
       </c>
       <c r="F31" t="n">
-        <v>-27.6</v>
+        <v>-27</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>42752000000</v>
       </c>
       <c r="N31" t="n">
-        <v>40121847168</v>
+        <v>40435299099</v>
       </c>
     </row>
     <row r="32">
@@ -2060,16 +2060,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>65.59999999999999</v>
+        <v>68</v>
       </c>
       <c r="D32" t="n">
-        <v>2729</v>
+        <v>2630</v>
       </c>
       <c r="E32" t="n">
         <v>1270</v>
       </c>
       <c r="F32" t="n">
-        <v>114.9</v>
+        <v>107.1</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>31108000000</v>
       </c>
       <c r="N32" t="n">
-        <v>47450653969</v>
+        <v>45729285430</v>
       </c>
     </row>
     <row r="33">
@@ -2112,16 +2112,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>65.59999999999999</v>
+        <v>68</v>
       </c>
       <c r="D33" t="n">
-        <v>2729</v>
+        <v>2630</v>
       </c>
       <c r="E33" t="n">
         <v>1170</v>
       </c>
       <c r="F33" t="n">
-        <v>133.2</v>
+        <v>124.8</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>31108000000</v>
       </c>
       <c r="N33" t="n">
-        <v>47450653969</v>
+        <v>45729285430</v>
       </c>
     </row>
     <row r="34">
@@ -2164,16 +2164,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="D34" t="n">
-        <v>2802.5</v>
+        <v>2812.5</v>
       </c>
       <c r="E34" t="n">
         <v>2381.523440544182</v>
       </c>
       <c r="F34" t="n">
-        <v>17.7</v>
+        <v>18.1</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>168696000000</v>
       </c>
       <c r="N34" t="n">
-        <v>497697911528</v>
+        <v>499473818438</v>
       </c>
     </row>
     <row r="35">
@@ -2216,16 +2216,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>83.2</v>
+        <v>82.5</v>
       </c>
       <c r="D35" t="n">
-        <v>2488</v>
+        <v>2509</v>
       </c>
       <c r="E35" t="n">
         <v>2939.562915943684</v>
       </c>
       <c r="F35" t="n">
-        <v>-15.4</v>
+        <v>-14.6</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>108430000000</v>
       </c>
       <c r="N35" t="n">
-        <v>130288807392</v>
+        <v>131388511956</v>
       </c>
     </row>
     <row r="36">
@@ -2268,16 +2268,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>49.2</v>
+        <v>48.7</v>
       </c>
       <c r="D36" t="n">
-        <v>13270</v>
+        <v>13410</v>
       </c>
       <c r="E36" t="n">
         <v>7040.15625</v>
       </c>
       <c r="F36" t="n">
-        <v>88.5</v>
+        <v>90.5</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>6799899000</v>
       </c>
       <c r="N36" t="n">
-        <v>13821594090</v>
+        <v>13967413470</v>
       </c>
     </row>
     <row r="37">
@@ -2320,16 +2320,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>49.2</v>
+        <v>48.7</v>
       </c>
       <c r="D37" t="n">
-        <v>13270</v>
+        <v>13410</v>
       </c>
       <c r="E37" t="n">
         <v>7040.15625</v>
       </c>
       <c r="F37" t="n">
-        <v>88.5</v>
+        <v>90.5</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>6799899000</v>
       </c>
       <c r="N37" t="n">
-        <v>13821594090</v>
+        <v>13967413470</v>
       </c>
     </row>
     <row r="38">
@@ -2372,16 +2372,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>87.3</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>2747</v>
+        <v>2737</v>
       </c>
       <c r="E38" t="n">
         <v>4265.455132343447</v>
       </c>
       <c r="F38" t="n">
-        <v>-35.6</v>
+        <v>-35.8</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>22869000000</v>
       </c>
       <c r="N38" t="n">
-        <v>26189398046</v>
+        <v>26094059866</v>
       </c>
     </row>
     <row r="39">
@@ -2424,16 +2424,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>33.4</v>
+        <v>33.1</v>
       </c>
       <c r="D39" t="n">
-        <v>4610</v>
+        <v>4660</v>
       </c>
       <c r="E39" t="n">
         <v>2824.318397803668</v>
       </c>
       <c r="F39" t="n">
-        <v>63.2</v>
+        <v>65</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>61975000000</v>
       </c>
       <c r="N39" t="n">
-        <v>185463319550</v>
+        <v>187474852300</v>
       </c>
     </row>
     <row r="40">
@@ -2476,16 +2476,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>29.7</v>
+        <v>29.3</v>
       </c>
       <c r="D40" t="n">
-        <v>6500</v>
+        <v>6600</v>
       </c>
       <c r="E40" t="n">
         <v>3096.322467304314</v>
       </c>
       <c r="F40" t="n">
-        <v>109.9</v>
+        <v>113.2</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>52961000000</v>
       </c>
       <c r="N40" t="n">
-        <v>178315605000</v>
+        <v>181058922000</v>
       </c>
     </row>
     <row r="41">
@@ -2531,13 +2531,13 @@
         <v>23.9</v>
       </c>
       <c r="D41" t="n">
-        <v>6267</v>
+        <v>6275</v>
       </c>
       <c r="E41" t="n">
         <v>3322.047887165483</v>
       </c>
       <c r="F41" t="n">
-        <v>88.59999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>492847000000</v>
       </c>
       <c r="N41" t="n">
-        <v>2058740509116</v>
+        <v>2061368548700</v>
       </c>
     </row>
     <row r="42">
@@ -2580,16 +2580,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>36.2</v>
+        <v>36</v>
       </c>
       <c r="D42" t="n">
-        <v>1718</v>
+        <v>1726</v>
       </c>
       <c r="E42" t="n">
         <v>2112.609181636727</v>
       </c>
       <c r="F42" t="n">
-        <v>-18.7</v>
+        <v>-18.3</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>52218000000</v>
       </c>
       <c r="N42" t="n">
-        <v>144243297180</v>
+        <v>144914977260</v>
       </c>
     </row>
     <row r="43">
@@ -2632,16 +2632,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="D43" t="n">
-        <v>714</v>
+        <v>700</v>
       </c>
       <c r="E43" t="n">
         <v>404.9347366248775</v>
       </c>
       <c r="F43" t="n">
-        <v>76.3</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>7044972000</v>
       </c>
       <c r="N43" t="n">
-        <v>190342478970</v>
+        <v>186610273500</v>
       </c>
     </row>
     <row r="44">
@@ -2684,16 +2684,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="D44" t="n">
-        <v>2737</v>
+        <v>2691</v>
       </c>
       <c r="E44" t="n">
         <v>2220.184278344451</v>
       </c>
       <c r="F44" t="n">
-        <v>23.3</v>
+        <v>21.2</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>207116000000</v>
       </c>
       <c r="N44" t="n">
-        <v>3137450018395</v>
+        <v>3084719765985</v>
       </c>
     </row>
     <row r="45">
@@ -2736,16 +2736,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>20.7</v>
+        <v>21.3</v>
       </c>
       <c r="D45" t="n">
-        <v>22100</v>
+        <v>21490</v>
       </c>
       <c r="E45" t="n">
         <v>11879.91675437757</v>
       </c>
       <c r="F45" t="n">
-        <v>86</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>191958000000</v>
       </c>
       <c r="N45" t="n">
-        <v>928676365500</v>
+        <v>903043216950</v>
       </c>
     </row>
     <row r="46">
@@ -2788,16 +2788,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>75.5</v>
+        <v>75</v>
       </c>
       <c r="D46" t="n">
-        <v>1085</v>
+        <v>1093</v>
       </c>
       <c r="E46" t="n">
         <v>730</v>
       </c>
       <c r="F46" t="n">
-        <v>48.6</v>
+        <v>49.7</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>50027000000</v>
       </c>
       <c r="N46" t="n">
-        <v>66243791810</v>
+        <v>66732225298</v>
       </c>
     </row>
     <row r="47">
@@ -2840,16 +2840,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>24.6</v>
+        <v>24.2</v>
       </c>
       <c r="D47" t="n">
-        <v>5328</v>
+        <v>5402</v>
       </c>
       <c r="E47" t="n">
         <v>3341.42986565678</v>
       </c>
       <c r="F47" t="n">
-        <v>59.5</v>
+        <v>61.7</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>311107000000</v>
       </c>
       <c r="N47" t="n">
-        <v>1266060101904</v>
+        <v>1283644269986</v>
       </c>
     </row>
     <row r="48">
@@ -2892,16 +2892,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>29.1</v>
+        <v>29</v>
       </c>
       <c r="D48" t="n">
-        <v>3175</v>
+        <v>3185</v>
       </c>
       <c r="E48" t="n">
         <v>2550.198980592041</v>
       </c>
       <c r="F48" t="n">
-        <v>24.5</v>
+        <v>24.9</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>32342000000</v>
       </c>
       <c r="N48" t="n">
-        <v>111181883300</v>
+        <v>111532062460</v>
       </c>
     </row>
     <row r="49">
@@ -2944,16 +2944,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>212.2</v>
+        <v>211.5</v>
       </c>
       <c r="D49" t="n">
-        <v>1631</v>
+        <v>1636</v>
       </c>
       <c r="E49" t="n">
         <v>1288.711724885291</v>
       </c>
       <c r="F49" t="n">
-        <v>26.6</v>
+        <v>26.9</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>747066000000</v>
       </c>
       <c r="N49" t="n">
-        <v>352107086163</v>
+        <v>353186507028</v>
       </c>
     </row>
     <row r="50">
@@ -2996,16 +2996,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>67.90000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>4049</v>
+        <v>4034</v>
       </c>
       <c r="E50" t="n">
         <v>3141.424011416125</v>
       </c>
       <c r="F50" t="n">
-        <v>28.9</v>
+        <v>28.4</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>391579000000</v>
       </c>
       <c r="N50" t="n">
-        <v>576964700596</v>
+        <v>574827266536</v>
       </c>
     </row>
     <row r="51">
@@ -3048,16 +3048,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>67.90000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="D51" t="n">
-        <v>4049</v>
+        <v>4034</v>
       </c>
       <c r="E51" t="n">
         <v>2420</v>
       </c>
       <c r="F51" t="n">
-        <v>67.3</v>
+        <v>66.7</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>391579000000</v>
       </c>
       <c r="N51" t="n">
-        <v>576964700596</v>
+        <v>574827266536</v>
       </c>
     </row>
     <row r="52">
@@ -3100,16 +3100,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>42.5</v>
+        <v>42.8</v>
       </c>
       <c r="D52" t="n">
-        <v>4026</v>
+        <v>4000</v>
       </c>
       <c r="E52" t="n">
         <v>3047.091476167608</v>
       </c>
       <c r="F52" t="n">
-        <v>32.1</v>
+        <v>31.3</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>162458000000</v>
       </c>
       <c r="N52" t="n">
-        <v>382321307742</v>
+        <v>379852268000</v>
       </c>
     </row>
     <row r="53">
@@ -3152,16 +3152,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>45.8</v>
+        <v>46.1</v>
       </c>
       <c r="D53" t="n">
-        <v>3458</v>
+        <v>3432</v>
       </c>
       <c r="E53" t="n">
         <v>2844.704547285864</v>
       </c>
       <c r="F53" t="n">
-        <v>21.6</v>
+        <v>20.6</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>218675000000</v>
       </c>
       <c r="N53" t="n">
-        <v>477444718296</v>
+        <v>473854908384</v>
       </c>
     </row>
     <row r="54">
@@ -3204,16 +3204,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>55.5</v>
+        <v>54.8</v>
       </c>
       <c r="D54" t="n">
-        <v>2234</v>
+        <v>2262.5</v>
       </c>
       <c r="E54" t="n">
         <v>1556.090471804319</v>
       </c>
       <c r="F54" t="n">
-        <v>43.6</v>
+        <v>45.4</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>207466000000</v>
       </c>
       <c r="N54" t="n">
-        <v>374013163570</v>
+        <v>378784593812</v>
       </c>
     </row>
     <row r="55">
@@ -3256,16 +3256,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
       <c r="D55" t="n">
-        <v>1774</v>
+        <v>1780</v>
       </c>
       <c r="E55" t="n">
         <v>1529.631984751819</v>
       </c>
       <c r="F55" t="n">
-        <v>16</v>
+        <v>16.4</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>6024082000</v>
       </c>
       <c r="N55" t="n">
-        <v>12643597806</v>
+        <v>12686360820</v>
       </c>
     </row>
     <row r="56">
@@ -3308,16 +3308,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
       <c r="D56" t="n">
-        <v>1774</v>
+        <v>1780</v>
       </c>
       <c r="E56" t="n">
         <v>1449.995380693296</v>
       </c>
       <c r="F56" t="n">
-        <v>22.3</v>
+        <v>22.8</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>6024082000</v>
       </c>
       <c r="N56" t="n">
-        <v>12643597806</v>
+        <v>12686360820</v>
       </c>
     </row>
     <row r="57">
@@ -3360,16 +3360,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>67.7</v>
+        <v>67.3</v>
       </c>
       <c r="D57" t="n">
-        <v>2955</v>
+        <v>2970</v>
       </c>
       <c r="E57" t="n">
         <v>2696.128808062088</v>
       </c>
       <c r="F57" t="n">
-        <v>9.6</v>
+        <v>10.2</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -3397,163 +3397,163 @@
         <v>165282000000</v>
       </c>
       <c r="N57" t="n">
-        <v>244273697970</v>
+        <v>245513665980</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>京浜急行電鉄株式会社</t>
+          <t>株式会社ニップン</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>119.8</v>
+        <v>67.3</v>
       </c>
       <c r="D58" t="n">
-        <v>1563</v>
+        <v>2970</v>
       </c>
       <c r="E58" t="n">
-        <v>1160.8</v>
+        <v>2696.128808062088</v>
       </c>
       <c r="F58" t="n">
-        <v>34.6</v>
+        <v>10.2</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>61234000000</v>
+        <v>31215000000</v>
       </c>
       <c r="J58" t="n">
-        <v>318113000000</v>
+        <v>48537000000</v>
       </c>
       <c r="K58" t="n">
-        <v>114136000000</v>
+        <v>85530000000</v>
       </c>
       <c r="L58" t="n">
-        <v>256898000000</v>
+        <v>178697000000</v>
       </c>
       <c r="M58" t="n">
-        <v>493483000000</v>
+        <v>165282000000</v>
       </c>
       <c r="N58" t="n">
-        <v>411860629803</v>
+        <v>245513665980</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>あいホールディングス株式会社</t>
+          <t>京浜急行電鉄株式会社</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>3076</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>23.4</v>
+        <v>120</v>
       </c>
       <c r="D59" t="n">
-        <v>2981</v>
+        <v>1560.5</v>
       </c>
       <c r="E59" t="n">
-        <v>2007.754513143541</v>
+        <v>1160.8</v>
       </c>
       <c r="F59" t="n">
-        <v>48.5</v>
+        <v>34.4</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>32012000000</v>
+        <v>61234000000</v>
       </c>
       <c r="J59" t="n">
-        <v>1646000000</v>
+        <v>318113000000</v>
       </c>
       <c r="K59" t="n">
-        <v>3550000000</v>
+        <v>114136000000</v>
       </c>
       <c r="L59" t="n">
-        <v>53765000000</v>
+        <v>256898000000</v>
       </c>
       <c r="M59" t="n">
-        <v>37208000000</v>
+        <v>493483000000</v>
       </c>
       <c r="N59" t="n">
-        <v>158806607311</v>
+        <v>411201863600</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>エア・ウォーター株式会社</t>
+          <t>あいホールディングス株式会社</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>15</v>
+        <v>23.5</v>
       </c>
       <c r="D60" t="n">
-        <v>2980</v>
+        <v>2975</v>
       </c>
       <c r="E60" t="n">
-        <v>2261.880826568852</v>
+        <v>2007.754513143541</v>
       </c>
       <c r="F60" t="n">
-        <v>31.7</v>
+        <v>48.2</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>29189000000</v>
+        <v>32012000000</v>
       </c>
       <c r="J60" t="n">
-        <v>31318000000</v>
+        <v>1646000000</v>
       </c>
       <c r="K60" t="n">
-        <v>42001000000</v>
+        <v>3550000000</v>
       </c>
       <c r="L60" t="n">
-        <v>194657000000</v>
+        <v>53765000000</v>
       </c>
       <c r="M60" t="n">
-        <v>102508000000</v>
+        <v>37208000000</v>
       </c>
       <c r="N60" t="n">
-        <v>683206401140</v>
+        <v>158486969725</v>
       </c>
     </row>
     <row r="61">
@@ -3571,22 +3571,22 @@
         <v>15</v>
       </c>
       <c r="D61" t="n">
-        <v>2980</v>
+        <v>2990</v>
       </c>
       <c r="E61" t="n">
-        <v>1970</v>
+        <v>2261.880826568852</v>
       </c>
       <c r="F61" t="n">
-        <v>51.3</v>
+        <v>32.2</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I61" t="n">
@@ -3605,156 +3605,164 @@
         <v>102508000000</v>
       </c>
       <c r="N61" t="n">
-        <v>683206401140</v>
+        <v>685499040070</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>株式会社電通総研</t>
+          <t>エア・ウォーター株式会社</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>9.6</v>
+        <v>15</v>
       </c>
       <c r="D62" t="n">
-        <v>2859</v>
+        <v>2990</v>
       </c>
       <c r="E62" t="n">
-        <v>1910.426979628923</v>
+        <v>1970</v>
       </c>
       <c r="F62" t="n">
-        <v>49.7</v>
+        <v>51.8</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>49748000000</v>
+        <v>29189000000</v>
       </c>
       <c r="J62" t="n">
-        <v>524000000</v>
+        <v>31318000000</v>
       </c>
       <c r="K62" t="n">
-        <v>3388000000</v>
+        <v>42001000000</v>
       </c>
       <c r="L62" t="n">
-        <v>65471000000</v>
+        <v>194657000000</v>
       </c>
       <c r="M62" t="n">
-        <v>53660000000</v>
+        <v>102508000000</v>
       </c>
       <c r="N62" t="n">
-        <v>558019968798</v>
+        <v>685499040070</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>わかもと製薬株式会社</t>
+          <t>株式会社電通総研</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>4812</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>51.3</v>
+        <v>9.6</v>
       </c>
       <c r="D63" t="n">
-        <v>290</v>
+        <v>2859</v>
       </c>
       <c r="E63" t="n">
-        <v>290.3401328717133</v>
+        <v>1910.426979628923</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.1</v>
+        <v>49.7</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3231889000</v>
+        <v>49748000000</v>
       </c>
       <c r="J63" t="n">
-        <v>82947000</v>
+        <v>524000000</v>
       </c>
       <c r="K63" t="n">
-        <v>1847919000</v>
+        <v>3388000000</v>
       </c>
       <c r="L63" t="n">
-        <v>11480803000</v>
+        <v>65471000000</v>
       </c>
       <c r="M63" t="n">
-        <v>5162755000</v>
+        <v>53660000000</v>
       </c>
       <c r="N63" t="n">
-        <v>10064693310</v>
+        <v>558019968798</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>株式会社豊田自動織機</t>
+          <t>わかもと製薬株式会社</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>6201</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
+          <t>4512</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="D64" t="n">
+        <v>290</v>
+      </c>
       <c r="E64" t="n">
-        <v>16430.4430802409</v>
-      </c>
-      <c r="F64" t="inlineStr"/>
+        <v>290.3401328717133</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-0.1</v>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>281605000000</v>
+        <v>3231889000</v>
       </c>
       <c r="J64" t="n">
-        <v>87540000000</v>
+        <v>82947000</v>
       </c>
       <c r="K64" t="n">
-        <v>730709000000</v>
+        <v>1847919000</v>
       </c>
       <c r="L64" t="n">
-        <v>3246174000000</v>
+        <v>11480803000</v>
       </c>
       <c r="M64" t="n">
-        <v>1099854000000</v>
-      </c>
-      <c r="N64" t="inlineStr"/>
+        <v>5162755000</v>
+      </c>
+      <c r="N64" t="n">
+        <v>10064693310</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3770,7 +3778,7 @@
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="n">
-        <v>16430443.10823975</v>
+        <v>16430.4430802409</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
@@ -3803,105 +3811,97 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>大阪製鐵株式会社</t>
+          <t>株式会社豊田自動織機</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5449</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>93.8</v>
-      </c>
-      <c r="D66" t="n">
-        <v>2573</v>
-      </c>
+          <t>6201</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="n">
-        <v>1748.071046781136</v>
-      </c>
-      <c r="F66" t="n">
-        <v>47.2</v>
-      </c>
+        <v>16430443.10823975</v>
+      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>62396000000</v>
+        <v>281605000000</v>
       </c>
       <c r="J66" t="n">
-        <v>9241000000</v>
+        <v>87540000000</v>
       </c>
       <c r="K66" t="n">
-        <v>553000000</v>
+        <v>730709000000</v>
       </c>
       <c r="L66" t="n">
-        <v>151028000000</v>
+        <v>3246174000000</v>
       </c>
       <c r="M66" t="n">
-        <v>72190000000</v>
-      </c>
-      <c r="N66" t="n">
-        <v>76980400847</v>
-      </c>
+        <v>1099854000000</v>
+      </c>
+      <c r="N66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>株式会社ディー・エヌ・エー</t>
+          <t>大阪製鐵株式会社</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>5449</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>77.2</v>
+        <v>92.8</v>
       </c>
       <c r="D67" t="n">
-        <v>2509.5</v>
+        <v>2600</v>
       </c>
       <c r="E67" t="n">
-        <v>2551.08574256026</v>
+        <v>1748.071046781136</v>
       </c>
       <c r="F67" t="n">
-        <v>-1.6</v>
+        <v>48.7</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>85363000000</v>
+        <v>62396000000</v>
       </c>
       <c r="J67" t="n">
-        <v>221000000</v>
+        <v>9241000000</v>
       </c>
       <c r="K67" t="n">
-        <v>93552000000</v>
+        <v>553000000</v>
       </c>
       <c r="L67" t="n">
-        <v>177857000000</v>
+        <v>151028000000</v>
       </c>
       <c r="M67" t="n">
-        <v>179136000000</v>
+        <v>72190000000</v>
       </c>
       <c r="N67" t="n">
-        <v>232157963090</v>
+        <v>77788201400</v>
       </c>
     </row>
     <row r="68">
@@ -3916,16 +3916,16 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>77.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="D68" t="n">
-        <v>2509.5</v>
+        <v>2496</v>
       </c>
       <c r="E68" t="n">
-        <v>2260</v>
+        <v>2551.08574256026</v>
       </c>
       <c r="F68" t="n">
-        <v>11</v>
+        <v>-2.2</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="I68" t="n">
@@ -3953,7 +3953,7 @@
         <v>179136000000</v>
       </c>
       <c r="N68" t="n">
-        <v>232157963090</v>
+        <v>230909055936</v>
       </c>
     </row>
     <row r="69">
@@ -3968,16 +3968,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>77.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="D69" t="n">
-        <v>2509.5</v>
+        <v>2496</v>
       </c>
       <c r="E69" t="n">
         <v>2260</v>
       </c>
       <c r="F69" t="n">
-        <v>11</v>
+        <v>10.4</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -4005,503 +4005,503 @@
         <v>179136000000</v>
       </c>
       <c r="N69" t="n">
-        <v>232157963090</v>
+        <v>230909055936</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>株式会社オリエントコーポレーション</t>
+          <t>株式会社ディー・エヌ・エー</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>8585</t>
+          <t>2432</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>311.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="D70" t="n">
-        <v>843</v>
+        <v>2496</v>
       </c>
       <c r="E70" t="n">
-        <v>798.3805136422309</v>
+        <v>2260</v>
       </c>
       <c r="F70" t="n">
-        <v>5.6</v>
+        <v>10.4</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>408187000000</v>
+        <v>85363000000</v>
       </c>
       <c r="J70" t="n">
-        <v>18930000000</v>
+        <v>221000000</v>
       </c>
       <c r="K70" t="n">
-        <v>21921000000</v>
+        <v>93552000000</v>
       </c>
       <c r="L70" t="n">
-        <v>216837000000</v>
+        <v>177857000000</v>
       </c>
       <c r="M70" t="n">
-        <v>449038000000</v>
+        <v>179136000000</v>
       </c>
       <c r="N70" t="n">
-        <v>144309683352</v>
+        <v>230909055936</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>東ソー株式会社</t>
+          <t>株式会社オリエントコーポレーション</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>4042</t>
+          <t>8585</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>42.9</v>
+        <v>309</v>
       </c>
       <c r="D71" t="n">
-        <v>2581</v>
+        <v>849</v>
       </c>
       <c r="E71" t="n">
-        <v>2032.365850102071</v>
+        <v>798.3805136422309</v>
       </c>
       <c r="F71" t="n">
-        <v>27</v>
+        <v>6.3</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>160812000000</v>
+        <v>408187000000</v>
       </c>
       <c r="J71" t="n">
-        <v>109648000000</v>
+        <v>18930000000</v>
       </c>
       <c r="K71" t="n">
-        <v>70132000000</v>
+        <v>21921000000</v>
       </c>
       <c r="L71" t="n">
-        <v>759724000000</v>
+        <v>216837000000</v>
       </c>
       <c r="M71" t="n">
-        <v>340592000000</v>
+        <v>449038000000</v>
       </c>
       <c r="N71" t="n">
-        <v>794665499226</v>
+        <v>145336798536</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>株式会社西武ホールディングス</t>
+          <t>東ソー株式会社</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>4042</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>62.4</v>
+        <v>43.1</v>
       </c>
       <c r="D72" t="n">
-        <v>3566</v>
+        <v>2566</v>
       </c>
       <c r="E72" t="n">
-        <v>1716.713876475349</v>
+        <v>2032.365850102071</v>
       </c>
       <c r="F72" t="n">
-        <v>107.7</v>
+        <v>26.3</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>87210000000</v>
+        <v>160812000000</v>
       </c>
       <c r="J72" t="n">
-        <v>428181000000</v>
+        <v>109648000000</v>
       </c>
       <c r="K72" t="n">
-        <v>49954000000</v>
+        <v>70132000000</v>
       </c>
       <c r="L72" t="n">
-        <v>387217000000</v>
+        <v>759724000000</v>
       </c>
       <c r="M72" t="n">
-        <v>565345000000</v>
+        <v>340592000000</v>
       </c>
       <c r="N72" t="n">
-        <v>906397992008</v>
+        <v>790047141036</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>株式会社西武ホールディングス</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>9024</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="D73" t="n">
+        <v>3507</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1716.713876475349</v>
+      </c>
+      <c r="F73" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>87210000000</v>
+      </c>
+      <c r="J73" t="n">
+        <v>428181000000</v>
+      </c>
+      <c r="K73" t="n">
+        <v>49954000000</v>
+      </c>
+      <c r="L73" t="n">
+        <v>387217000000</v>
+      </c>
+      <c r="M73" t="n">
+        <v>565345000000</v>
+      </c>
+      <c r="N73" t="n">
+        <v>891401502516</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
           <t>株式会社フェローテック
 （旧会社名　株式会社フェローテックホールディングス）</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>6890</t>
         </is>
       </c>
-      <c r="C73" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="D73" t="n">
-        <v>9200</v>
-      </c>
-      <c r="E73" t="n">
+      <c r="C74" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="D74" t="n">
+        <v>8620</v>
+      </c>
+      <c r="E74" t="n">
         <v>4037.502552255647</v>
       </c>
-      <c r="F73" t="n">
-        <v>127.9</v>
-      </c>
-      <c r="G73" t="inlineStr">
+      <c r="F74" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="G74" t="inlineStr">
         <is>
           <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="I73" t="n">
+      <c r="I74" t="n">
         <v>52579000000</v>
       </c>
-      <c r="J73" t="n">
+      <c r="J74" t="n">
         <v>90505000000</v>
       </c>
-      <c r="K73" t="n">
+      <c r="K74" t="n">
         <v>11654000000</v>
       </c>
-      <c r="L73" t="n">
+      <c r="L74" t="n">
         <v>160957000000</v>
       </c>
-      <c r="M73" t="n">
+      <c r="M74" t="n">
         <v>154738000000</v>
       </c>
-      <c r="N73" t="n">
-        <v>494994619600</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="N74" t="n">
+        <v>463788437060</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>株式会社フェローテック
 （旧会社名　株式会社フェローテックホールディングス）</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>6890</t>
         </is>
       </c>
-      <c r="C74" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="D74" t="n">
-        <v>9200</v>
-      </c>
-      <c r="E74" t="n">
+      <c r="C75" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="D75" t="n">
+        <v>8620</v>
+      </c>
+      <c r="E75" t="n">
         <v>3950.736048458928</v>
       </c>
-      <c r="F74" t="n">
-        <v>132.9</v>
-      </c>
-      <c r="G74" t="inlineStr">
+      <c r="F75" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="G75" t="inlineStr">
         <is>
           <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="I74" t="n">
+      <c r="I75" t="n">
         <v>52579000000</v>
       </c>
-      <c r="J74" t="n">
+      <c r="J75" t="n">
         <v>90505000000</v>
       </c>
-      <c r="K74" t="n">
+      <c r="K75" t="n">
         <v>11654000000</v>
       </c>
-      <c r="L74" t="n">
+      <c r="L75" t="n">
         <v>160957000000</v>
       </c>
-      <c r="M74" t="n">
+      <c r="M75" t="n">
         <v>154738000000</v>
       </c>
-      <c r="N74" t="n">
-        <v>494994619600</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="N75" t="n">
+        <v>463788437060</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>株式会社フェローテック
 （旧会社名　株式会社フェローテックホールディングス）</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>6890</t>
         </is>
       </c>
-      <c r="C75" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="D75" t="n">
-        <v>9200</v>
-      </c>
-      <c r="E75" t="n">
+      <c r="C76" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="D76" t="n">
+        <v>8620</v>
+      </c>
+      <c r="E76" t="n">
         <v>2030</v>
       </c>
-      <c r="F75" t="n">
-        <v>353.2</v>
-      </c>
-      <c r="G75" t="inlineStr">
+      <c r="F76" t="n">
+        <v>324.6</v>
+      </c>
+      <c r="G76" t="inlineStr">
         <is>
           <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>2025-10-22</t>
         </is>
       </c>
-      <c r="I75" t="n">
+      <c r="I76" t="n">
         <v>52579000000</v>
       </c>
-      <c r="J75" t="n">
+      <c r="J76" t="n">
         <v>90505000000</v>
       </c>
-      <c r="K75" t="n">
+      <c r="K76" t="n">
         <v>11654000000</v>
       </c>
-      <c r="L75" t="n">
+      <c r="L76" t="n">
         <v>160957000000</v>
       </c>
-      <c r="M75" t="n">
+      <c r="M76" t="n">
         <v>154738000000</v>
       </c>
-      <c r="N75" t="n">
-        <v>494994619600</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="N76" t="n">
+        <v>463788437060</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>株式会社フェローテック
 （旧会社名　株式会社フェローテックホールディングス）</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>6890</t>
         </is>
       </c>
-      <c r="C76" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="D76" t="n">
-        <v>9200</v>
-      </c>
-      <c r="E76" t="n">
+      <c r="C77" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="D77" t="n">
+        <v>8620</v>
+      </c>
+      <c r="E77" t="n">
         <v>2387</v>
       </c>
-      <c r="F76" t="n">
-        <v>285.4</v>
-      </c>
-      <c r="G76" t="inlineStr">
+      <c r="F77" t="n">
+        <v>261.1</v>
+      </c>
+      <c r="G77" t="inlineStr">
         <is>
           <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>2025-03-07</t>
         </is>
       </c>
-      <c r="I76" t="n">
+      <c r="I77" t="n">
         <v>52579000000</v>
       </c>
-      <c r="J76" t="n">
+      <c r="J77" t="n">
         <v>90505000000</v>
       </c>
-      <c r="K76" t="n">
+      <c r="K77" t="n">
         <v>11654000000</v>
       </c>
-      <c r="L76" t="n">
+      <c r="L77" t="n">
         <v>160957000000</v>
       </c>
-      <c r="M76" t="n">
+      <c r="M77" t="n">
         <v>154738000000</v>
       </c>
-      <c r="N76" t="n">
-        <v>494994619600</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>アツギ株式会社</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>3529</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="D77" t="n">
-        <v>991</v>
-      </c>
-      <c r="E77" t="n">
-        <v>668.9358717434869</v>
-      </c>
-      <c r="F77" t="n">
-        <v>48.1</v>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="I77" t="n">
-        <v>5500000000</v>
-      </c>
-      <c r="J77" t="n">
-        <v>3208000000</v>
-      </c>
-      <c r="K77" t="n">
-        <v>3702000000</v>
-      </c>
-      <c r="L77" t="n">
-        <v>32145000000</v>
-      </c>
-      <c r="M77" t="n">
-        <v>12410000000</v>
-      </c>
       <c r="N77" t="n">
-        <v>15869879946</v>
+        <v>463788437060</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>日本特殊塗料株式会社</t>
+          <t>アツギ株式会社</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>4619</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>73.09999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="D78" t="n">
-        <v>2601</v>
+        <v>1016</v>
       </c>
       <c r="E78" t="n">
-        <v>1190</v>
+        <v>668.9358717434869</v>
       </c>
       <c r="F78" t="n">
-        <v>118.6</v>
+        <v>51.9</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>8931000000</v>
+        <v>5500000000</v>
       </c>
       <c r="J78" t="n">
-        <v>9514000000</v>
+        <v>3208000000</v>
       </c>
       <c r="K78" t="n">
-        <v>22055000000</v>
+        <v>3702000000</v>
       </c>
       <c r="L78" t="n">
-        <v>49725000000</v>
+        <v>32145000000</v>
       </c>
       <c r="M78" t="n">
-        <v>40500000000</v>
+        <v>12410000000</v>
       </c>
       <c r="N78" t="n">
-        <v>55380094047</v>
+        <v>16270230096</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>株式会社エクセディ</t>
+          <t>日本特殊塗料株式会社</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>7278</t>
+          <t>4619</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>19.2</v>
+        <v>72.7</v>
       </c>
       <c r="D79" t="n">
-        <v>5870</v>
+        <v>2615</v>
       </c>
       <c r="E79" t="n">
-        <v>2617.980935875217</v>
+        <v>1190</v>
       </c>
       <c r="F79" t="n">
-        <v>124.2</v>
+        <v>119.7</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -4510,338 +4510,338 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>30019000000</v>
+        <v>8931000000</v>
       </c>
       <c r="J79" t="n">
-        <v>6792000000</v>
+        <v>9514000000</v>
       </c>
       <c r="K79" t="n">
-        <v>3427000000</v>
+        <v>22055000000</v>
       </c>
       <c r="L79" t="n">
-        <v>119460000000</v>
+        <v>49725000000</v>
       </c>
       <c r="M79" t="n">
-        <v>40238000000</v>
+        <v>40500000000</v>
       </c>
       <c r="N79" t="n">
-        <v>210108232420</v>
+        <v>55678179905</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>株式会社Ａ＆Ｄホロンホールディングス</t>
+          <t>株式会社エクセディ</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>7745</t>
+          <t>7278</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>19.8</v>
+        <v>19.3</v>
       </c>
       <c r="D80" t="n">
-        <v>2853</v>
+        <v>5810</v>
       </c>
       <c r="E80" t="n">
-        <v>2084.177692465894</v>
+        <v>2617.980935875217</v>
       </c>
       <c r="F80" t="n">
-        <v>36.9</v>
+        <v>121.9</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>11012000000</v>
+        <v>30019000000</v>
       </c>
       <c r="J80" t="n">
-        <v>4106000000</v>
+        <v>6792000000</v>
       </c>
       <c r="K80" t="n">
-        <v>315000000</v>
+        <v>3427000000</v>
       </c>
       <c r="L80" t="n">
-        <v>27041000000</v>
+        <v>119460000000</v>
       </c>
       <c r="M80" t="n">
-        <v>15433000000</v>
+        <v>40238000000</v>
       </c>
       <c r="N80" t="n">
-        <v>78136026813</v>
+        <v>207960618460</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>株式会社セプテーニ・ホールディングス</t>
+          <t>株式会社Ａ＆Ｄホロンホールディングス</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>4293</t>
+          <t>7745</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>13.2</v>
+        <v>19.9</v>
       </c>
       <c r="D81" t="n">
-        <v>509</v>
+        <v>2828</v>
       </c>
       <c r="E81" t="n">
-        <v>448.6811097117532</v>
+        <v>2084.177692465894</v>
       </c>
       <c r="F81" t="n">
-        <v>13.4</v>
+        <v>35.7</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>12184507000</v>
+        <v>11012000000</v>
       </c>
       <c r="J81" t="n">
-        <v>168073000</v>
+        <v>4106000000</v>
       </c>
       <c r="K81" t="n">
-        <v>1600720000</v>
+        <v>315000000</v>
       </c>
       <c r="L81" t="n">
-        <v>11861578000</v>
+        <v>27041000000</v>
       </c>
       <c r="M81" t="n">
-        <v>13953300000</v>
+        <v>15433000000</v>
       </c>
       <c r="N81" t="n">
-        <v>105589560481</v>
+        <v>77451343788</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>株式会社シンクロ・フード</t>
+          <t>株式会社セプテーニ・ホールディングス</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>4293</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>34.2</v>
+        <v>13.3</v>
       </c>
       <c r="D82" t="n">
-        <v>324</v>
+        <v>506</v>
       </c>
       <c r="E82" t="n">
-        <v>421.6950726175476</v>
+        <v>448.6811097117532</v>
       </c>
       <c r="F82" t="n">
-        <v>-23.2</v>
+        <v>12.8</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3037851000</v>
+        <v>12184507000</v>
       </c>
       <c r="J82" t="n">
-        <v>56852000</v>
+        <v>168073000</v>
       </c>
       <c r="K82" t="n">
-        <v>14952000</v>
+        <v>1600720000</v>
       </c>
       <c r="L82" t="n">
-        <v>2871237000</v>
+        <v>11861578000</v>
       </c>
       <c r="M82" t="n">
-        <v>3109655000</v>
+        <v>13953300000</v>
       </c>
       <c r="N82" t="n">
-        <v>9085798512</v>
+        <v>104967225154</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>科研製薬株式会社</t>
+          <t>株式会社シンクロ・フード</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>73.09999999999999</v>
+        <v>34.2</v>
       </c>
       <c r="D83" t="n">
-        <v>3835</v>
+        <v>324</v>
       </c>
       <c r="E83" t="n">
-        <v>3530</v>
+        <v>421.6950726175476</v>
       </c>
       <c r="F83" t="n">
-        <v>8.6</v>
+        <v>-23.2</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>74625000000</v>
+        <v>3037851000</v>
       </c>
       <c r="J83" t="n">
-        <v>15530000000</v>
+        <v>56852000</v>
       </c>
       <c r="K83" t="n">
-        <v>15992000000</v>
+        <v>14952000</v>
       </c>
       <c r="L83" t="n">
-        <v>138325000000</v>
+        <v>2871237000</v>
       </c>
       <c r="M83" t="n">
-        <v>106147000000</v>
+        <v>3109655000</v>
       </c>
       <c r="N83" t="n">
-        <v>145224988025</v>
+        <v>9085798512</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>市光工業株式会社</t>
+          <t>科研製薬株式会社</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>7244</t>
+          <t>4521</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>35.6</v>
+        <v>73.2</v>
       </c>
       <c r="D84" t="n">
-        <v>557</v>
+        <v>3830</v>
       </c>
       <c r="E84" t="n">
-        <v>549.4799823005444</v>
+        <v>3530</v>
       </c>
       <c r="F84" t="n">
-        <v>1.4</v>
+        <v>8.5</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>5720000000</v>
+        <v>74625000000</v>
       </c>
       <c r="J84" t="n">
-        <v>9921000000</v>
+        <v>15530000000</v>
       </c>
       <c r="K84" t="n">
-        <v>3474000000</v>
+        <v>15992000000</v>
       </c>
       <c r="L84" t="n">
-        <v>49523000000</v>
+        <v>138325000000</v>
       </c>
       <c r="M84" t="n">
-        <v>19115000000</v>
+        <v>106147000000</v>
       </c>
       <c r="N84" t="n">
-        <v>53641556370</v>
+        <v>145035646450</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>トーセイ株式会社</t>
+          <t>市光工業株式会社</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>46.8</v>
+        <v>35.8</v>
       </c>
       <c r="D85" t="n">
-        <v>1680</v>
+        <v>554</v>
       </c>
       <c r="E85" t="n">
-        <v>1752.426893379333</v>
+        <v>549.4799823005444</v>
       </c>
       <c r="F85" t="n">
-        <v>-4.1</v>
+        <v>0.8</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>20753937000</v>
+        <v>5720000000</v>
       </c>
       <c r="J85" t="n">
-        <v>46868512000</v>
+        <v>9921000000</v>
       </c>
       <c r="K85" t="n">
-        <v>8610046000</v>
+        <v>3474000000</v>
       </c>
       <c r="L85" t="n">
-        <v>59467346000</v>
+        <v>49523000000</v>
       </c>
       <c r="M85" t="n">
-        <v>76232495000</v>
+        <v>19115000000</v>
       </c>
       <c r="N85" t="n">
-        <v>162970248000</v>
+        <v>53352643140</v>
       </c>
     </row>
     <row r="86">
@@ -4856,16 +4856,16 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>46.8</v>
+        <v>47</v>
       </c>
       <c r="D86" t="n">
-        <v>1680</v>
+        <v>1672</v>
       </c>
       <c r="E86" t="n">
-        <v>1576.721867844292</v>
+        <v>1752.426893379333</v>
       </c>
       <c r="F86" t="n">
-        <v>6.6</v>
+        <v>-4.6</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="I86" t="n">
@@ -4893,59 +4893,59 @@
         <v>76232495000</v>
       </c>
       <c r="N86" t="n">
-        <v>162970248000</v>
+        <v>162194199200</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>株式会社髙島屋</t>
+          <t>トーセイ株式会社</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>64.8</v>
+        <v>47</v>
       </c>
       <c r="D87" t="n">
-        <v>2118.5</v>
+        <v>1672</v>
       </c>
       <c r="E87" t="n">
-        <v>1101.400153022188</v>
+        <v>1576.721867844292</v>
       </c>
       <c r="F87" t="n">
-        <v>92.3</v>
+        <v>6</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>88996000000</v>
+        <v>20753937000</v>
       </c>
       <c r="J87" t="n">
-        <v>193090000000</v>
+        <v>46868512000</v>
       </c>
       <c r="K87" t="n">
-        <v>119967000000</v>
+        <v>8610046000</v>
       </c>
       <c r="L87" t="n">
-        <v>420489000000</v>
+        <v>59467346000</v>
       </c>
       <c r="M87" t="n">
-        <v>402053000000</v>
+        <v>76232495000</v>
       </c>
       <c r="N87" t="n">
-        <v>620751006400</v>
+        <v>162194199200</v>
       </c>
     </row>
     <row r="88">
@@ -4960,16 +4960,16 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>64.8</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D88" t="n">
-        <v>2118.5</v>
+        <v>2099.5</v>
       </c>
       <c r="E88" t="n">
         <v>1101.400153022188</v>
       </c>
       <c r="F88" t="n">
-        <v>92.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="I88" t="n">
@@ -4997,551 +4997,551 @@
         <v>402053000000</v>
       </c>
       <c r="N88" t="n">
-        <v>620751006400</v>
+        <v>615183732800</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>三井倉庫ホールディングス株式会社</t>
+          <t>株式会社髙島屋</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>9302</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>45</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D89" t="n">
-        <v>3339</v>
+        <v>2099.5</v>
       </c>
       <c r="E89" t="n">
-        <v>1492.806001579363</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="F89" t="n">
-        <v>123.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>22822000000</v>
+        <v>88996000000</v>
       </c>
       <c r="J89" t="n">
-        <v>72331000000</v>
+        <v>193090000000</v>
       </c>
       <c r="K89" t="n">
-        <v>17148000000</v>
+        <v>119967000000</v>
       </c>
       <c r="L89" t="n">
-        <v>88631000000</v>
+        <v>420489000000</v>
       </c>
       <c r="M89" t="n">
-        <v>112301000000</v>
+        <v>402053000000</v>
       </c>
       <c r="N89" t="n">
-        <v>249771507615</v>
+        <v>615183732800</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>京阪神ビルディング株式会社</t>
+          <t>三井倉庫ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>8818</t>
+          <t>9302</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>81.09999999999999</v>
+        <v>45.6</v>
       </c>
       <c r="D90" t="n">
-        <v>1120</v>
+        <v>3295</v>
       </c>
       <c r="E90" t="n">
-        <v>1341.977644710579</v>
+        <v>1492.806001579363</v>
       </c>
       <c r="F90" t="n">
-        <v>-16.5</v>
+        <v>120.7</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>9876000000</v>
+        <v>22822000000</v>
       </c>
       <c r="J90" t="n">
-        <v>54379000000</v>
+        <v>72331000000</v>
       </c>
       <c r="K90" t="n">
-        <v>22399000000</v>
+        <v>17148000000</v>
       </c>
       <c r="L90" t="n">
-        <v>70510000000</v>
+        <v>88631000000</v>
       </c>
       <c r="M90" t="n">
-        <v>86654000000</v>
+        <v>112301000000</v>
       </c>
       <c r="N90" t="n">
-        <v>106853221440</v>
+        <v>246480119075</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>株式会社メルカリ</t>
+          <t>京阪神ビルディング株式会社</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>8818</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>27.1</v>
+        <v>81.2</v>
       </c>
       <c r="D91" t="n">
-        <v>3921</v>
+        <v>1118</v>
       </c>
       <c r="E91" t="n">
-        <v>2006.059650428343</v>
+        <v>1341.977644710579</v>
       </c>
       <c r="F91" t="n">
-        <v>95.5</v>
+        <v>-16.7</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>171463000000</v>
+        <v>9876000000</v>
       </c>
       <c r="J91" t="n">
-        <v>434000000</v>
+        <v>54379000000</v>
       </c>
       <c r="K91" t="n">
-        <v>1543000000</v>
+        <v>22399000000</v>
       </c>
       <c r="L91" t="n">
-        <v>40013000000</v>
+        <v>70510000000</v>
       </c>
       <c r="M91" t="n">
-        <v>173440000000</v>
+        <v>86654000000</v>
       </c>
       <c r="N91" t="n">
-        <v>639831199257</v>
+        <v>106662412116</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>サッポロホールディングス株式会社</t>
+          <t>株式会社メルカリ</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2501</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>27.8</v>
       </c>
       <c r="D92" t="n">
-        <v>1844</v>
+        <v>3826</v>
       </c>
       <c r="E92" t="n">
-        <v>2697.360927565142</v>
+        <v>2006.059650428343</v>
       </c>
       <c r="F92" t="n">
-        <v>-31.6</v>
+        <v>90.7</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2925000000</v>
+        <v>171463000000</v>
       </c>
       <c r="J92" t="n">
-        <v>23000000</v>
+        <v>434000000</v>
       </c>
       <c r="K92" t="n">
-        <v>4391000000</v>
+        <v>1543000000</v>
       </c>
       <c r="L92" t="n">
-        <v>142395000000</v>
+        <v>40013000000</v>
       </c>
       <c r="M92" t="n">
-        <v>7339000000</v>
+        <v>173440000000</v>
       </c>
       <c r="N92" t="n">
-        <v>719110193560</v>
+        <v>624329040642</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>株式会社クレハ</t>
+          <t>サッポロホールディングス株式会社</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>4345</v>
+        <v>1838</v>
       </c>
       <c r="E93" t="n">
-        <v>7960</v>
+        <v>2697.360927565142</v>
       </c>
       <c r="F93" t="n">
-        <v>-45.4</v>
+        <v>-31.9</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>5294000000</v>
+        <v>2925000000</v>
       </c>
       <c r="J93" t="n">
-        <v>5963000000</v>
+        <v>23000000</v>
       </c>
       <c r="K93" t="n">
-        <v>18608000000</v>
+        <v>4391000000</v>
       </c>
       <c r="L93" t="n">
-        <v>155874000000</v>
+        <v>142395000000</v>
       </c>
       <c r="M93" t="n">
-        <v>29865000000</v>
+        <v>7339000000</v>
       </c>
       <c r="N93" t="n">
-        <v>166070479630</v>
+        <v>716770355620</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>コムシスホールディングス株式会社</t>
+          <t>株式会社クレハ</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>4023</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="D94" t="n">
-        <v>5357</v>
+        <v>4325</v>
       </c>
       <c r="E94" t="n">
-        <v>3735.709461270437</v>
+        <v>7960</v>
       </c>
       <c r="F94" t="n">
-        <v>43.4</v>
+        <v>-45.7</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>34033000000</v>
+        <v>5294000000</v>
       </c>
       <c r="J94" t="n">
-        <v>45394000000</v>
+        <v>5963000000</v>
       </c>
       <c r="K94" t="n">
-        <v>31261000000</v>
+        <v>18608000000</v>
       </c>
       <c r="L94" t="n">
-        <v>343489000000</v>
+        <v>155874000000</v>
       </c>
       <c r="M94" t="n">
-        <v>110688000000</v>
+        <v>29865000000</v>
       </c>
       <c r="N94" t="n">
-        <v>614898589767</v>
+        <v>165306058550</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>サクサ株式会社</t>
+          <t>コムシスホールディングス株式会社</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>6675</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>30.8</v>
+        <v>18</v>
       </c>
       <c r="D95" t="n">
-        <v>2089</v>
+        <v>5372</v>
       </c>
       <c r="E95" t="n">
-        <v>5463.67048346056</v>
+        <v>3735.709461270437</v>
       </c>
       <c r="F95" t="n">
-        <v>-61.8</v>
+        <v>43.8</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>6993000000</v>
+        <v>34033000000</v>
       </c>
       <c r="J95" t="n">
-        <v>1323000000</v>
+        <v>45394000000</v>
       </c>
       <c r="K95" t="n">
-        <v>2933000000</v>
+        <v>31261000000</v>
       </c>
       <c r="L95" t="n">
-        <v>23497000000</v>
+        <v>343489000000</v>
       </c>
       <c r="M95" t="n">
-        <v>11249000000</v>
+        <v>110688000000</v>
       </c>
       <c r="N95" t="n">
-        <v>36539931510</v>
+        <v>616620351732</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>株式会社ヨドコウ（旧会社名：株式会社淀川製鋼所）</t>
+          <t>サクサ株式会社</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5451</t>
+          <t>6675</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>26</v>
+        <v>30.6</v>
       </c>
       <c r="D96" t="n">
-        <v>1402</v>
+        <v>2102</v>
       </c>
       <c r="E96" t="n">
-        <v>3234.727863989046</v>
+        <v>5463.67048346056</v>
       </c>
       <c r="F96" t="n">
-        <v>-56.7</v>
+        <v>-61.5</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>30961000000</v>
+        <v>6993000000</v>
       </c>
       <c r="J96" t="n">
-        <v>18259000000</v>
+        <v>1323000000</v>
       </c>
       <c r="K96" t="n">
-        <v>2995000000</v>
+        <v>2933000000</v>
       </c>
       <c r="L96" t="n">
-        <v>191937000000</v>
+        <v>23497000000</v>
       </c>
       <c r="M96" t="n">
-        <v>52215000000</v>
+        <v>11249000000</v>
       </c>
       <c r="N96" t="n">
-        <v>200835855080</v>
+        <v>36767322180</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>愛知製鋼株式会社</t>
+          <t>株式会社ヨドコウ（旧会社名：株式会社淀川製鋼所）</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>5451</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>35.2</v>
+        <v>25.8</v>
       </c>
       <c r="D97" t="n">
-        <v>3115</v>
+        <v>1414</v>
       </c>
       <c r="E97" t="n">
-        <v>3155.301177013616</v>
+        <v>3234.727863989046</v>
       </c>
       <c r="F97" t="n">
-        <v>-1.3</v>
+        <v>-56.3</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>32866000000</v>
+        <v>30961000000</v>
       </c>
       <c r="J97" t="n">
-        <v>11000000000</v>
+        <v>18259000000</v>
       </c>
       <c r="K97" t="n">
-        <v>26614000000</v>
+        <v>2995000000</v>
       </c>
       <c r="L97" t="n">
-        <v>186904000000</v>
+        <v>191937000000</v>
       </c>
       <c r="M97" t="n">
-        <v>70480000000</v>
+        <v>52215000000</v>
       </c>
       <c r="N97" t="n">
-        <v>200128775770</v>
+        <v>202554849560</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>株式会社インターネットイニシアティブ</t>
+          <t>愛知製鋼株式会社</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>3774</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>5.7</v>
+        <v>35.2</v>
       </c>
       <c r="D98" t="n">
-        <v>3299</v>
+        <v>3115</v>
       </c>
       <c r="E98" t="n">
-        <v>2655.311711736394</v>
+        <v>3155.301177013616</v>
       </c>
       <c r="F98" t="n">
-        <v>24.2</v>
+        <v>-1.3</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>16367000000</v>
+        <v>32866000000</v>
       </c>
       <c r="J98" t="n">
-        <v>1522000000</v>
+        <v>11000000000</v>
       </c>
       <c r="K98" t="n">
-        <v>15226000000</v>
+        <v>26614000000</v>
       </c>
       <c r="L98" t="n">
-        <v>87924000000</v>
+        <v>186904000000</v>
       </c>
       <c r="M98" t="n">
-        <v>33115000000</v>
+        <v>70480000000</v>
       </c>
       <c r="N98" t="n">
-        <v>585011686495</v>
+        <v>200128775770</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>コクヨ株式会社</t>
+          <t>株式会社インターネットイニシアティブ</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>7984</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>40.5</v>
+        <v>5.6</v>
       </c>
       <c r="D99" t="n">
-        <v>911.2999877929688</v>
+        <v>3340</v>
       </c>
       <c r="E99" t="n">
-        <v>2157.626835069302</v>
+        <v>2655.311711736394</v>
       </c>
       <c r="F99" t="n">
-        <v>-57.8</v>
+        <v>25.8</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -5550,182 +5550,182 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>100575000000</v>
+        <v>16367000000</v>
       </c>
       <c r="J99" t="n">
-        <v>22282000000</v>
+        <v>1522000000</v>
       </c>
       <c r="K99" t="n">
-        <v>30106000000</v>
+        <v>15226000000</v>
       </c>
       <c r="L99" t="n">
-        <v>230105000000</v>
+        <v>87924000000</v>
       </c>
       <c r="M99" t="n">
-        <v>152963000000</v>
+        <v>33115000000</v>
       </c>
       <c r="N99" t="n">
-        <v>377679231643</v>
+        <v>592282216700</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>三菱製紙株式会社</t>
+          <t>コクヨ株式会社</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>7984</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>97.2</v>
+        <v>40.7</v>
       </c>
       <c r="D100" t="n">
-        <v>1181</v>
+        <v>905.7999877929688</v>
       </c>
       <c r="E100" t="n">
-        <v>810</v>
+        <v>2157.626835069302</v>
       </c>
       <c r="F100" t="n">
-        <v>45.8</v>
+        <v>-58</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>9047000000</v>
+        <v>100575000000</v>
       </c>
       <c r="J100" t="n">
-        <v>16443000000</v>
+        <v>22282000000</v>
       </c>
       <c r="K100" t="n">
-        <v>24813000000</v>
+        <v>30106000000</v>
       </c>
       <c r="L100" t="n">
-        <v>69613000000</v>
+        <v>230105000000</v>
       </c>
       <c r="M100" t="n">
-        <v>50303000000</v>
+        <v>152963000000</v>
       </c>
       <c r="N100" t="n">
-        <v>51737459399</v>
+        <v>375399811253</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>株式会社プラスアルファ・コンサルティング</t>
+          <t>三菱製紙株式会社</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>4071</t>
+          <t>3864</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>10</v>
+        <v>98.2</v>
       </c>
       <c r="D101" t="n">
-        <v>2042</v>
+        <v>1169</v>
       </c>
       <c r="E101" t="n">
-        <v>2300.974351689521</v>
+        <v>810</v>
       </c>
       <c r="F101" t="n">
-        <v>-11.3</v>
+        <v>44.3</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>8278003000</v>
+        <v>9047000000</v>
       </c>
       <c r="J101" t="n">
-        <v>271170000</v>
+        <v>16443000000</v>
       </c>
       <c r="K101" t="n">
-        <v>0</v>
+        <v>24813000000</v>
       </c>
       <c r="L101" t="n">
-        <v>9445733000</v>
+        <v>69613000000</v>
       </c>
       <c r="M101" t="n">
-        <v>8549173000</v>
+        <v>50303000000</v>
       </c>
       <c r="N101" t="n">
-        <v>85673233100</v>
+        <v>51211761251</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>東亜道路工業株式会社</t>
+          <t>株式会社プラスアルファ・コンサルティング</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>4071</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>40.1</v>
+        <v>10</v>
       </c>
       <c r="D102" t="n">
-        <v>1592</v>
+        <v>2028</v>
       </c>
       <c r="E102" t="n">
-        <v>1180.31326635551</v>
+        <v>2300.974351689521</v>
       </c>
       <c r="F102" t="n">
-        <v>34.9</v>
+        <v>-11.9</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>11649000000</v>
+        <v>8278003000</v>
       </c>
       <c r="J102" t="n">
-        <v>13793000000</v>
+        <v>271170000</v>
       </c>
       <c r="K102" t="n">
-        <v>4087000000</v>
+        <v>0</v>
       </c>
       <c r="L102" t="n">
-        <v>50605000000</v>
+        <v>9445733000</v>
       </c>
       <c r="M102" t="n">
-        <v>29529000000</v>
+        <v>8549173000</v>
       </c>
       <c r="N102" t="n">
-        <v>73562480096</v>
+        <v>85085855400</v>
       </c>
     </row>
     <row r="103">
@@ -5740,16 +5740,16 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>40.1</v>
+        <v>40.3</v>
       </c>
       <c r="D103" t="n">
-        <v>1592</v>
+        <v>1585</v>
       </c>
       <c r="E103" t="n">
-        <v>1180.406015389293</v>
+        <v>1180.253227905114</v>
       </c>
       <c r="F103" t="n">
-        <v>34.9</v>
+        <v>34.3</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="I103" t="n">
@@ -5777,7 +5777,7 @@
         <v>29529000000</v>
       </c>
       <c r="N103" t="n">
-        <v>73562480096</v>
+        <v>73239026980</v>
       </c>
     </row>
     <row r="104">
@@ -5792,16 +5792,16 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>40.1</v>
+        <v>40.3</v>
       </c>
       <c r="D104" t="n">
-        <v>1592</v>
+        <v>1585</v>
       </c>
       <c r="E104" t="n">
-        <v>1180.420176850555</v>
+        <v>1180.31326635551</v>
       </c>
       <c r="F104" t="n">
-        <v>34.9</v>
+        <v>34.3</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="I104" t="n">
@@ -5829,7 +5829,7 @@
         <v>29529000000</v>
       </c>
       <c r="N104" t="n">
-        <v>73562480096</v>
+        <v>73239026980</v>
       </c>
     </row>
     <row r="105">
@@ -5844,16 +5844,16 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>40.1</v>
+        <v>40.3</v>
       </c>
       <c r="D105" t="n">
-        <v>1592</v>
+        <v>1585</v>
       </c>
       <c r="E105" t="n">
-        <v>1180.431728045326</v>
+        <v>1180.406015389293</v>
       </c>
       <c r="F105" t="n">
-        <v>34.9</v>
+        <v>34.3</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="I105" t="n">
@@ -5881,7 +5881,7 @@
         <v>29529000000</v>
       </c>
       <c r="N105" t="n">
-        <v>73562480096</v>
+        <v>73239026980</v>
       </c>
     </row>
     <row r="106">
@@ -5896,16 +5896,16 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>40.1</v>
+        <v>40.3</v>
       </c>
       <c r="D106" t="n">
-        <v>1592</v>
+        <v>1585</v>
       </c>
       <c r="E106" t="n">
-        <v>1180.442269658324</v>
+        <v>1180.420176850555</v>
       </c>
       <c r="F106" t="n">
-        <v>34.9</v>
+        <v>34.3</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="I106" t="n">
@@ -5933,7 +5933,7 @@
         <v>29529000000</v>
       </c>
       <c r="N106" t="n">
-        <v>73562480096</v>
+        <v>73239026980</v>
       </c>
     </row>
     <row r="107">
@@ -5948,16 +5948,16 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>40.1</v>
+        <v>40.3</v>
       </c>
       <c r="D107" t="n">
-        <v>1592</v>
+        <v>1585</v>
       </c>
       <c r="E107" t="n">
-        <v>1180.450912709519</v>
+        <v>1180.431728045326</v>
       </c>
       <c r="F107" t="n">
-        <v>34.9</v>
+        <v>34.3</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="I107" t="n">
@@ -5985,7 +5985,7 @@
         <v>29529000000</v>
       </c>
       <c r="N107" t="n">
-        <v>73562480096</v>
+        <v>73239026980</v>
       </c>
     </row>
     <row r="108">
@@ -6000,16 +6000,16 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>40.1</v>
+        <v>40.3</v>
       </c>
       <c r="D108" t="n">
-        <v>1592</v>
+        <v>1585</v>
       </c>
       <c r="E108" t="n">
-        <v>1180.45745232471</v>
+        <v>1180.442269658324</v>
       </c>
       <c r="F108" t="n">
-        <v>34.9</v>
+        <v>34.3</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="I108" t="n">
@@ -6037,7 +6037,7 @@
         <v>29529000000</v>
       </c>
       <c r="N108" t="n">
-        <v>73562480096</v>
+        <v>73239026980</v>
       </c>
     </row>
     <row r="109">
@@ -6052,16 +6052,16 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>40.1</v>
+        <v>40.3</v>
       </c>
       <c r="D109" t="n">
-        <v>1592</v>
+        <v>1585</v>
       </c>
       <c r="E109" t="n">
-        <v>1180.463123164206</v>
+        <v>1180.450912709519</v>
       </c>
       <c r="F109" t="n">
-        <v>34.9</v>
+        <v>34.3</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="I109" t="n">
@@ -6089,7 +6089,7 @@
         <v>29529000000</v>
       </c>
       <c r="N109" t="n">
-        <v>73562480096</v>
+        <v>73239026980</v>
       </c>
     </row>
     <row r="110">
@@ -6104,16 +6104,16 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>40.1</v>
+        <v>40.3</v>
       </c>
       <c r="D110" t="n">
-        <v>1592</v>
+        <v>1585</v>
       </c>
       <c r="E110" t="n">
-        <v>1170.279952698077</v>
+        <v>1180.45745232471</v>
       </c>
       <c r="F110" t="n">
-        <v>36</v>
+        <v>34.3</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="I110" t="n">
@@ -6141,7 +6141,7 @@
         <v>29529000000</v>
       </c>
       <c r="N110" t="n">
-        <v>73562480096</v>
+        <v>73239026980</v>
       </c>
     </row>
     <row r="111">
@@ -6156,16 +6156,16 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>40.1</v>
+        <v>40.3</v>
       </c>
       <c r="D111" t="n">
-        <v>1592</v>
+        <v>1585</v>
       </c>
       <c r="E111" t="n">
-        <v>1169.924818603025</v>
+        <v>1180.463123164206</v>
       </c>
       <c r="F111" t="n">
-        <v>36.1</v>
+        <v>34.3</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="I111" t="n">
@@ -6193,7 +6193,7 @@
         <v>29529000000</v>
       </c>
       <c r="N111" t="n">
-        <v>73562480096</v>
+        <v>73239026980</v>
       </c>
     </row>
     <row r="112">
@@ -6208,16 +6208,16 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>40.1</v>
+        <v>40.3</v>
       </c>
       <c r="D112" t="n">
-        <v>1592</v>
+        <v>1585</v>
       </c>
       <c r="E112" t="n">
-        <v>1168.709522546084</v>
+        <v>1170.279952698077</v>
       </c>
       <c r="F112" t="n">
-        <v>36.2</v>
+        <v>35.4</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="I112" t="n">
@@ -6245,31 +6245,31 @@
         <v>29529000000</v>
       </c>
       <c r="N112" t="n">
-        <v>73562480096</v>
+        <v>73239026980</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>山洋電気株式会社</t>
+          <t>東亜道路工業株式会社</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>12</v>
+        <v>40.3</v>
       </c>
       <c r="D113" t="n">
-        <v>5180</v>
+        <v>1585</v>
       </c>
       <c r="E113" t="n">
-        <v>7052.737306843267</v>
+        <v>1169.924818603025</v>
       </c>
       <c r="F113" t="n">
-        <v>-26.6</v>
+        <v>35.5</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -6278,154 +6278,154 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>8317000000</v>
+        <v>11649000000</v>
       </c>
       <c r="J113" t="n">
-        <v>6048000000</v>
+        <v>13793000000</v>
       </c>
       <c r="K113" t="n">
-        <v>7673000000</v>
+        <v>4087000000</v>
       </c>
       <c r="L113" t="n">
-        <v>49734000000</v>
+        <v>50605000000</v>
       </c>
       <c r="M113" t="n">
-        <v>22038000000</v>
+        <v>29529000000</v>
       </c>
       <c r="N113" t="n">
-        <v>183967912380</v>
+        <v>73239026980</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ヘリオス テクノ ホールディング株式会社</t>
+          <t>東亜道路工業株式会社</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>54.4</v>
+        <v>40.3</v>
       </c>
       <c r="D114" t="n">
-        <v>970</v>
+        <v>1585</v>
       </c>
       <c r="E114" t="n">
-        <v>896.0103264198827</v>
+        <v>1168.709522546084</v>
       </c>
       <c r="F114" t="n">
-        <v>8.300000000000001</v>
+        <v>35.6</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>7851015000</v>
+        <v>11649000000</v>
       </c>
       <c r="J114" t="n">
-        <v>640317000</v>
+        <v>13793000000</v>
       </c>
       <c r="K114" t="n">
-        <v>1079200000</v>
+        <v>4087000000</v>
       </c>
       <c r="L114" t="n">
-        <v>13746774000</v>
+        <v>50605000000</v>
       </c>
       <c r="M114" t="n">
-        <v>9570532000</v>
+        <v>29529000000</v>
       </c>
       <c r="N114" t="n">
-        <v>17607116990</v>
+        <v>73239026980</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>シェアリングテクノロジー株式会社</t>
+          <t>山洋電気株式会社</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>11.7</v>
+        <v>12</v>
       </c>
       <c r="D115" t="n">
-        <v>1545</v>
+        <v>5180</v>
       </c>
       <c r="E115" t="n">
-        <v>653.0713101160862</v>
+        <v>7052.737306843267</v>
       </c>
       <c r="F115" t="n">
-        <v>136.6</v>
+        <v>-26.6</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>4016706000</v>
+        <v>8317000000</v>
       </c>
       <c r="J115" t="n">
-        <v>309745000</v>
+        <v>6048000000</v>
       </c>
       <c r="K115" t="n">
-        <v>0</v>
+        <v>7673000000</v>
       </c>
       <c r="L115" t="n">
-        <v>185001000</v>
+        <v>49734000000</v>
       </c>
       <c r="M115" t="n">
-        <v>4326451000</v>
+        <v>22038000000</v>
       </c>
       <c r="N115" t="n">
-        <v>36973810605</v>
+        <v>183967912380</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>栄研化学株式会社</t>
+          <t>ヘリオス テクノ ホールディング株式会社</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>31</v>
+        <v>54.5</v>
       </c>
       <c r="D116" t="n">
-        <v>2237</v>
+        <v>967</v>
       </c>
       <c r="E116" t="n">
-        <v>1947.225264702313</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="F116" t="n">
-        <v>14.9</v>
+        <v>7.9</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -6434,50 +6434,50 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>10900000000</v>
+        <v>7851015000</v>
       </c>
       <c r="J116" t="n">
-        <v>11585000000</v>
+        <v>640317000</v>
       </c>
       <c r="K116" t="n">
-        <v>408000000</v>
+        <v>1079200000</v>
       </c>
       <c r="L116" t="n">
-        <v>45803000000</v>
+        <v>13746774000</v>
       </c>
       <c r="M116" t="n">
-        <v>22893000000</v>
+        <v>9570532000</v>
       </c>
       <c r="N116" t="n">
-        <v>73743986801</v>
+        <v>17552661989</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>栄研化学株式会社</t>
+          <t>シェアリングテクノロジー株式会社</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>31</v>
+        <v>11.7</v>
       </c>
       <c r="D117" t="n">
-        <v>2237</v>
+        <v>1544</v>
       </c>
       <c r="E117" t="n">
-        <v>1678.083113259255</v>
+        <v>653.0713101160862</v>
       </c>
       <c r="F117" t="n">
-        <v>33.3</v>
+        <v>136.4</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -6486,154 +6486,154 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>10900000000</v>
+        <v>4016706000</v>
       </c>
       <c r="J117" t="n">
-        <v>11585000000</v>
+        <v>309745000</v>
       </c>
       <c r="K117" t="n">
-        <v>408000000</v>
+        <v>0</v>
       </c>
       <c r="L117" t="n">
-        <v>45803000000</v>
+        <v>185001000</v>
       </c>
       <c r="M117" t="n">
-        <v>22893000000</v>
+        <v>4326451000</v>
       </c>
       <c r="N117" t="n">
-        <v>73743986801</v>
+        <v>36949879336</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>株式会社ヤマダホールディングス</t>
+          <t>栄研化学株式会社</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>9831</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>58.5</v>
+        <v>31.3</v>
       </c>
       <c r="D118" t="n">
-        <v>712.0999755859375</v>
+        <v>2216</v>
       </c>
       <c r="E118" t="n">
-        <v>530</v>
+        <v>1947.225264702313</v>
       </c>
       <c r="F118" t="n">
-        <v>34.4</v>
+        <v>13.8</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>56470000000</v>
+        <v>10900000000</v>
       </c>
       <c r="J118" t="n">
-        <v>210733000000</v>
+        <v>11585000000</v>
       </c>
       <c r="K118" t="n">
-        <v>9997000000</v>
+        <v>408000000</v>
       </c>
       <c r="L118" t="n">
-        <v>676277000000</v>
+        <v>45803000000</v>
       </c>
       <c r="M118" t="n">
-        <v>277200000000</v>
+        <v>22893000000</v>
       </c>
       <c r="N118" t="n">
-        <v>473528989605</v>
+        <v>73051709768</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>日本化薬株式会社</t>
+          <t>栄研化学株式会社</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>35.6</v>
+        <v>31.3</v>
       </c>
       <c r="D119" t="n">
-        <v>2039</v>
+        <v>2216</v>
       </c>
       <c r="E119" t="n">
-        <v>1111.90611839092</v>
+        <v>1678.083113259255</v>
       </c>
       <c r="F119" t="n">
-        <v>83.40000000000001</v>
+        <v>32.1</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>52962000000</v>
+        <v>10900000000</v>
       </c>
       <c r="J119" t="n">
-        <v>48231000000</v>
+        <v>11585000000</v>
       </c>
       <c r="K119" t="n">
-        <v>4337000000</v>
+        <v>408000000</v>
       </c>
       <c r="L119" t="n">
-        <v>246425000000</v>
+        <v>45803000000</v>
       </c>
       <c r="M119" t="n">
-        <v>105530000000</v>
+        <v>22893000000</v>
       </c>
       <c r="N119" t="n">
-        <v>296413534507</v>
+        <v>73051709768</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>王子ホールディングス株式会社</t>
+          <t>株式会社ヤマダホールディングス</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>9831</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>42.1</v>
+        <v>58.1</v>
       </c>
       <c r="D120" t="n">
-        <v>859.9000244140625</v>
+        <v>717.7000122070312</v>
       </c>
       <c r="E120" t="n">
-        <v>590</v>
+        <v>530</v>
       </c>
       <c r="F120" t="n">
-        <v>45.7</v>
+        <v>35.4</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -6642,310 +6642,310 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>55474000000</v>
+        <v>56470000000</v>
       </c>
       <c r="J120" t="n">
-        <v>244732000000</v>
+        <v>210733000000</v>
       </c>
       <c r="K120" t="n">
-        <v>7434000000</v>
+        <v>9997000000</v>
       </c>
       <c r="L120" t="n">
-        <v>875470000000</v>
+        <v>676277000000</v>
       </c>
       <c r="M120" t="n">
-        <v>307640000000</v>
+        <v>277200000000</v>
       </c>
       <c r="N120" t="n">
-        <v>730256589284</v>
+        <v>477252876381</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>東邦ホールディングス株式会社</t>
+          <t>日本化薬株式会社</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>51.3</v>
+        <v>35.9</v>
       </c>
       <c r="D121" t="n">
-        <v>3952</v>
+        <v>2036</v>
       </c>
       <c r="E121" t="n">
-        <v>3405.914389596362</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="F121" t="n">
-        <v>16</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>90014000000</v>
+        <v>52962000000</v>
       </c>
       <c r="J121" t="n">
-        <v>34220000000</v>
+        <v>48231000000</v>
       </c>
       <c r="K121" t="n">
-        <v>7000000000</v>
+        <v>4337000000</v>
       </c>
       <c r="L121" t="n">
-        <v>241281000000</v>
+        <v>246425000000</v>
       </c>
       <c r="M121" t="n">
-        <v>131234000000</v>
+        <v>105530000000</v>
       </c>
       <c r="N121" t="n">
-        <v>255700814096</v>
+        <v>293567560004</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>東邦ホールディングス株式会社</t>
+          <t>王子ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>51.3</v>
+        <v>41.8</v>
       </c>
       <c r="D122" t="n">
-        <v>3952</v>
+        <v>867.2999877929688</v>
       </c>
       <c r="E122" t="n">
-        <v>2714.613787300615</v>
+        <v>590</v>
       </c>
       <c r="F122" t="n">
-        <v>45.6</v>
+        <v>47</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>90014000000</v>
+        <v>55474000000</v>
       </c>
       <c r="J122" t="n">
-        <v>34220000000</v>
+        <v>244732000000</v>
       </c>
       <c r="K122" t="n">
-        <v>7000000000</v>
+        <v>7434000000</v>
       </c>
       <c r="L122" t="n">
-        <v>241281000000</v>
+        <v>875470000000</v>
       </c>
       <c r="M122" t="n">
-        <v>131234000000</v>
+        <v>307640000000</v>
       </c>
       <c r="N122" t="n">
-        <v>255700814096</v>
+        <v>736540891952</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>株式会社アイネス</t>
+          <t>東邦ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>9742</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>35.4</v>
+        <v>51.5</v>
       </c>
       <c r="D123" t="n">
-        <v>2049</v>
+        <v>3940</v>
       </c>
       <c r="E123" t="n">
-        <v>1879.137815927515</v>
+        <v>3405.914389596362</v>
       </c>
       <c r="F123" t="n">
-        <v>9</v>
+        <v>15.7</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>9731000000</v>
+        <v>90014000000</v>
       </c>
       <c r="J123" t="n">
-        <v>5286000000</v>
+        <v>34220000000</v>
       </c>
       <c r="K123" t="n">
-        <v>100000000</v>
+        <v>7000000000</v>
       </c>
       <c r="L123" t="n">
-        <v>34620000000</v>
+        <v>241281000000</v>
       </c>
       <c r="M123" t="n">
-        <v>15117000000</v>
+        <v>131234000000</v>
       </c>
       <c r="N123" t="n">
-        <v>42665193903</v>
+        <v>254924394620</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>日本ゼオン株式会社</t>
+          <t>東邦ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>35.8</v>
+        <v>51.5</v>
       </c>
       <c r="D124" t="n">
-        <v>2352.5</v>
+        <v>3940</v>
       </c>
       <c r="E124" t="n">
-        <v>1721.078563209627</v>
+        <v>2714.613787300615</v>
       </c>
       <c r="F124" t="n">
-        <v>36.7</v>
+        <v>45.1</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>44521000000</v>
+        <v>90014000000</v>
       </c>
       <c r="J124" t="n">
-        <v>45382000000</v>
+        <v>34220000000</v>
       </c>
       <c r="K124" t="n">
-        <v>71191000000</v>
+        <v>7000000000</v>
       </c>
       <c r="L124" t="n">
-        <v>321836000000</v>
+        <v>241281000000</v>
       </c>
       <c r="M124" t="n">
-        <v>161094000000</v>
+        <v>131234000000</v>
       </c>
       <c r="N124" t="n">
-        <v>450140305218</v>
+        <v>254924394620</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>太陽ホールディングス株式会社</t>
+          <t>株式会社アイネス</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>9742</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>16.4</v>
+        <v>35.5</v>
       </c>
       <c r="D125" t="n">
-        <v>4719</v>
+        <v>2045</v>
       </c>
       <c r="E125" t="n">
-        <v>2199.643244598912</v>
+        <v>1879.137815927515</v>
       </c>
       <c r="F125" t="n">
-        <v>114.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>51152000000</v>
+        <v>9731000000</v>
       </c>
       <c r="J125" t="n">
-        <v>30337000000</v>
+        <v>5286000000</v>
       </c>
       <c r="K125" t="n">
-        <v>4870000000</v>
+        <v>100000000</v>
       </c>
       <c r="L125" t="n">
-        <v>85466000000</v>
+        <v>34620000000</v>
       </c>
       <c r="M125" t="n">
-        <v>86359000000</v>
+        <v>15117000000</v>
       </c>
       <c r="N125" t="n">
-        <v>525114662358</v>
+        <v>42581904115</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>太陽ホールディングス株式会社</t>
+          <t>日本ゼオン株式会社</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>16.4</v>
+        <v>36.2</v>
       </c>
       <c r="D126" t="n">
-        <v>4719</v>
+        <v>2326</v>
       </c>
       <c r="E126" t="n">
-        <v>3565.648720929983</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="F126" t="n">
-        <v>32.3</v>
+        <v>35.1</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -6954,50 +6954,50 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>51152000000</v>
+        <v>44521000000</v>
       </c>
       <c r="J126" t="n">
-        <v>30337000000</v>
+        <v>45382000000</v>
       </c>
       <c r="K126" t="n">
-        <v>4870000000</v>
+        <v>71191000000</v>
       </c>
       <c r="L126" t="n">
-        <v>85466000000</v>
+        <v>321836000000</v>
       </c>
       <c r="M126" t="n">
-        <v>86359000000</v>
+        <v>161094000000</v>
       </c>
       <c r="N126" t="n">
-        <v>525114662358</v>
+        <v>445069649282</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>株式会社エス・エム・エス</t>
+          <t>太陽ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>8.699999999999999</v>
+        <v>16.4</v>
       </c>
       <c r="D127" t="n">
-        <v>2538</v>
+        <v>4720</v>
       </c>
       <c r="E127" t="n">
-        <v>1478.127248828989</v>
+        <v>2199.643244598912</v>
       </c>
       <c r="F127" t="n">
-        <v>71.7</v>
+        <v>114.6</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -7006,102 +7006,102 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>14126000000</v>
+        <v>51152000000</v>
       </c>
       <c r="J127" t="n">
-        <v>1187000000</v>
+        <v>30337000000</v>
       </c>
       <c r="K127" t="n">
-        <v>2875000000</v>
+        <v>4870000000</v>
       </c>
       <c r="L127" t="n">
-        <v>29991000000</v>
+        <v>85466000000</v>
       </c>
       <c r="M127" t="n">
-        <v>18188000000</v>
+        <v>86359000000</v>
       </c>
       <c r="N127" t="n">
-        <v>208320179562</v>
+        <v>525225939040</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>アニコム ホールディングス株式会社</t>
+          <t>太陽ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>8715</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>41.5</v>
+        <v>16.4</v>
       </c>
       <c r="D128" t="n">
-        <v>1018</v>
+        <v>4720</v>
       </c>
       <c r="E128" t="n">
-        <v>656.2604975855553</v>
+        <v>3565.648720929983</v>
       </c>
       <c r="F128" t="n">
-        <v>55.1</v>
+        <v>32.4</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>27691000000</v>
+        <v>51152000000</v>
       </c>
       <c r="J128" t="n">
-        <v>3070000000</v>
+        <v>30337000000</v>
       </c>
       <c r="K128" t="n">
-        <v>3000000</v>
+        <v>4870000000</v>
       </c>
       <c r="L128" t="n">
-        <v>27316000000</v>
+        <v>85466000000</v>
       </c>
       <c r="M128" t="n">
-        <v>30764000000</v>
+        <v>86359000000</v>
       </c>
       <c r="N128" t="n">
-        <v>74132001960</v>
+        <v>525225939040</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>東京製鐵株式会社</t>
+          <t>株式会社エス・エム・エス</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>103.1</v>
+        <v>8.6</v>
       </c>
       <c r="D129" t="n">
-        <v>1687</v>
+        <v>2583</v>
       </c>
       <c r="E129" t="n">
-        <v>1605.452212379354</v>
+        <v>1478.127248828989</v>
       </c>
       <c r="F129" t="n">
-        <v>5.1</v>
+        <v>74.7</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -7110,94 +7110,102 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>68644000000</v>
+        <v>14126000000</v>
       </c>
       <c r="J129" t="n">
-        <v>33060000000</v>
+        <v>1187000000</v>
       </c>
       <c r="K129" t="n">
-        <v>75000000000</v>
+        <v>2875000000</v>
       </c>
       <c r="L129" t="n">
-        <v>158280000000</v>
+        <v>29991000000</v>
       </c>
       <c r="M129" t="n">
-        <v>176704000000</v>
+        <v>18188000000</v>
       </c>
       <c r="N129" t="n">
-        <v>171392689867</v>
+        <v>212013799767</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ウェーブロックホールディングス株式会社</t>
+          <t>アニコム ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>7940</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr"/>
-      <c r="D130" t="inlineStr"/>
+          <t>8715</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="D130" t="n">
+        <v>1017</v>
+      </c>
       <c r="E130" t="n">
-        <v>1010</v>
-      </c>
-      <c r="F130" t="inlineStr"/>
+        <v>656.2604975855553</v>
+      </c>
+      <c r="F130" t="n">
+        <v>55</v>
+      </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1961626000</v>
+        <v>27691000000</v>
       </c>
       <c r="J130" t="n">
-        <v>2544946000</v>
+        <v>3070000000</v>
       </c>
       <c r="K130" t="n">
-        <v>1068366000</v>
+        <v>3000000</v>
       </c>
       <c r="L130" t="n">
-        <v>13761535000</v>
+        <v>27316000000</v>
       </c>
       <c r="M130" t="n">
-        <v>5574938000</v>
-      </c>
-      <c r="N130" t="inlineStr"/>
+        <v>30764000000</v>
+      </c>
+      <c r="N130" t="n">
+        <v>74059180740</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>近畿車輛株式会社</t>
+          <t>東京製鐵株式会社</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>7122</t>
+          <t>5423</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D131" t="n">
-        <v>2347</v>
+        <v>1706</v>
       </c>
       <c r="E131" t="n">
-        <v>2144.894901144641</v>
+        <v>1605.452212379354</v>
       </c>
       <c r="F131" t="n">
-        <v>9.4</v>
+        <v>6.3</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -7206,206 +7214,198 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>6847000000</v>
+        <v>68644000000</v>
       </c>
       <c r="J131" t="n">
-        <v>4580000000</v>
+        <v>33060000000</v>
       </c>
       <c r="K131" t="n">
-        <v>6329000000</v>
+        <v>75000000000</v>
       </c>
       <c r="L131" t="n">
-        <v>24474000000</v>
+        <v>158280000000</v>
       </c>
       <c r="M131" t="n">
-        <v>17756000000</v>
+        <v>176704000000</v>
       </c>
       <c r="N131" t="n">
-        <v>16147550107</v>
+        <v>173323016546</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>株式会社三陽商会</t>
+          <t>ウェーブロックホールディングス株式会社</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>8011</t>
-        </is>
-      </c>
-      <c r="C132" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="D132" t="n">
-        <v>1317</v>
-      </c>
+          <t>7940</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr"/>
       <c r="E132" t="n">
-        <v>3321.975331035734</v>
-      </c>
-      <c r="F132" t="n">
-        <v>-60.4</v>
-      </c>
+        <v>1010</v>
+      </c>
+      <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>16287000000</v>
+        <v>1961626000</v>
       </c>
       <c r="J132" t="n">
-        <v>3021000000</v>
+        <v>2544946000</v>
       </c>
       <c r="K132" t="n">
-        <v>6298000000</v>
+        <v>1068366000</v>
       </c>
       <c r="L132" t="n">
-        <v>33920000000</v>
+        <v>13761535000</v>
       </c>
       <c r="M132" t="n">
-        <v>25606000000</v>
-      </c>
-      <c r="N132" t="n">
-        <v>38701404144</v>
-      </c>
+        <v>5574938000</v>
+      </c>
+      <c r="N132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>月島ホールディングス株式会社</t>
+          <t>近畿車輛株式会社</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>6332</t>
+          <t>7122</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>47.8</v>
+        <v>109.4</v>
       </c>
       <c r="D133" t="n">
-        <v>2700</v>
+        <v>2358</v>
       </c>
       <c r="E133" t="n">
-        <v>1410</v>
+        <v>2144.894901144641</v>
       </c>
       <c r="F133" t="n">
-        <v>91.5</v>
+        <v>9.9</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>28795000000</v>
+        <v>6847000000</v>
       </c>
       <c r="J133" t="n">
-        <v>22203000000</v>
+        <v>4580000000</v>
       </c>
       <c r="K133" t="n">
-        <v>100000000</v>
+        <v>6329000000</v>
       </c>
       <c r="L133" t="n">
-        <v>80949000000</v>
+        <v>24474000000</v>
       </c>
       <c r="M133" t="n">
-        <v>51098000000</v>
+        <v>17756000000</v>
       </c>
       <c r="N133" t="n">
-        <v>106923302100</v>
+        <v>16223230998</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>マネックスグループ株式会社</t>
+          <t>株式会社三陽商会</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>8698</t>
+          <t>8011</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>15.2</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D134" t="n">
-        <v>722</v>
+        <v>1313</v>
       </c>
       <c r="E134" t="n">
-        <v>510.1850530906719</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="F134" t="n">
-        <v>41.5</v>
+        <v>-60.5</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>17794000000</v>
+        <v>16287000000</v>
       </c>
       <c r="J134" t="n">
-        <v>412000000</v>
+        <v>3021000000</v>
       </c>
       <c r="K134" t="n">
-        <v>9312000000</v>
+        <v>6298000000</v>
       </c>
       <c r="L134" t="n">
-        <v>98001000000</v>
+        <v>33920000000</v>
       </c>
       <c r="M134" t="n">
-        <v>27518000000</v>
+        <v>25606000000</v>
       </c>
       <c r="N134" t="n">
-        <v>181484579848</v>
+        <v>38583860016</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>株式会社あおぞら銀行</t>
+          <t>月島ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>226.6</v>
+        <v>48.3</v>
       </c>
       <c r="D135" t="n">
-        <v>3457</v>
+        <v>2669</v>
       </c>
       <c r="E135" t="n">
-        <v>2190</v>
+        <v>1410</v>
       </c>
       <c r="F135" t="n">
-        <v>57.9</v>
+        <v>89.3</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -7414,154 +7414,154 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1061743000000</v>
+        <v>28795000000</v>
       </c>
       <c r="J135" t="n">
-        <v>22385000000</v>
+        <v>22203000000</v>
       </c>
       <c r="K135" t="n">
-        <v>0</v>
+        <v>100000000</v>
       </c>
       <c r="L135" t="n">
-        <v>487265000000</v>
+        <v>80949000000</v>
       </c>
       <c r="M135" t="n">
-        <v>1084128000000</v>
+        <v>51098000000</v>
       </c>
       <c r="N135" t="n">
-        <v>478383379732</v>
+        <v>105695664187</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>日本製紙株式会社</t>
+          <t>マネックスグループ株式会社</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>8698</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>305.9</v>
+        <v>15.3</v>
       </c>
       <c r="D136" t="n">
-        <v>1307</v>
+        <v>714</v>
       </c>
       <c r="E136" t="n">
-        <v>1250</v>
+        <v>510.1850530906719</v>
       </c>
       <c r="F136" t="n">
-        <v>4.6</v>
+        <v>39.9</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>136216000000</v>
+        <v>17794000000</v>
       </c>
       <c r="J136" t="n">
-        <v>151771000000</v>
+        <v>412000000</v>
       </c>
       <c r="K136" t="n">
-        <v>172984000000</v>
+        <v>9312000000</v>
       </c>
       <c r="L136" t="n">
-        <v>438604000000</v>
+        <v>98001000000</v>
       </c>
       <c r="M136" t="n">
-        <v>460971000000</v>
+        <v>27518000000</v>
       </c>
       <c r="N136" t="n">
-        <v>150708213421</v>
+        <v>179473670376</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>カルビー株式会社</t>
+          <t>株式会社あおぞら銀行</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>33.5</v>
+        <v>226.6</v>
       </c>
       <c r="D137" t="n">
-        <v>3024</v>
+        <v>3457</v>
       </c>
       <c r="E137" t="n">
-        <v>2919.137515755844</v>
+        <v>2190</v>
       </c>
       <c r="F137" t="n">
-        <v>3.6</v>
+        <v>57.9</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>49670000000</v>
+        <v>1061743000000</v>
       </c>
       <c r="J137" t="n">
-        <v>70285000000</v>
+        <v>22385000000</v>
       </c>
       <c r="K137" t="n">
-        <v>3263000000</v>
+        <v>0</v>
       </c>
       <c r="L137" t="n">
-        <v>183458000000</v>
+        <v>487265000000</v>
       </c>
       <c r="M137" t="n">
-        <v>123218000000</v>
+        <v>1084128000000</v>
       </c>
       <c r="N137" t="n">
-        <v>367681670496</v>
+        <v>478383379732</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ＮＩＴＴＯＫＵ株式会社</t>
+          <t>日本製紙株式会社</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>50</v>
+        <v>307.8</v>
       </c>
       <c r="D138" t="n">
-        <v>2497</v>
+        <v>1299</v>
       </c>
       <c r="E138" t="n">
-        <v>1710</v>
+        <v>1250</v>
       </c>
       <c r="F138" t="n">
-        <v>46</v>
+        <v>3.9</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -7570,102 +7570,102 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>11768000000</v>
+        <v>136216000000</v>
       </c>
       <c r="J138" t="n">
-        <v>6299000000</v>
+        <v>151771000000</v>
       </c>
       <c r="K138" t="n">
-        <v>2999000000</v>
+        <v>172984000000</v>
       </c>
       <c r="L138" t="n">
-        <v>33919000000</v>
+        <v>438604000000</v>
       </c>
       <c r="M138" t="n">
-        <v>21066000000</v>
+        <v>460971000000</v>
       </c>
       <c r="N138" t="n">
-        <v>42135581554</v>
+        <v>149785745397</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ＮＩＴＴＯＫＵ株式会社</t>
+          <t>カルビー株式会社</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>50</v>
+        <v>33.7</v>
       </c>
       <c r="D139" t="n">
-        <v>2497</v>
+        <v>3009</v>
       </c>
       <c r="E139" t="n">
-        <v>1710</v>
+        <v>2919.137515755844</v>
       </c>
       <c r="F139" t="n">
-        <v>46</v>
+        <v>3.1</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>11768000000</v>
+        <v>49670000000</v>
       </c>
       <c r="J139" t="n">
-        <v>6299000000</v>
+        <v>70285000000</v>
       </c>
       <c r="K139" t="n">
-        <v>2999000000</v>
+        <v>3263000000</v>
       </c>
       <c r="L139" t="n">
-        <v>33919000000</v>
+        <v>183458000000</v>
       </c>
       <c r="M139" t="n">
-        <v>21066000000</v>
+        <v>123218000000</v>
       </c>
       <c r="N139" t="n">
-        <v>42135581554</v>
+        <v>365857852686</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>新光商事株式会社</t>
+          <t>ＮＩＴＴＯＫＵ株式会社</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>8141</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>30.8</v>
+        <v>51.2</v>
       </c>
       <c r="D140" t="n">
-        <v>1567</v>
+        <v>2439</v>
       </c>
       <c r="E140" t="n">
-        <v>930</v>
+        <v>1710</v>
       </c>
       <c r="F140" t="n">
-        <v>68.5</v>
+        <v>42.6</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -7674,50 +7674,50 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>10579000000</v>
+        <v>11768000000</v>
       </c>
       <c r="J140" t="n">
-        <v>195000000</v>
+        <v>6299000000</v>
       </c>
       <c r="K140" t="n">
-        <v>2995000000</v>
+        <v>2999000000</v>
       </c>
       <c r="L140" t="n">
-        <v>51945000000</v>
+        <v>33919000000</v>
       </c>
       <c r="M140" t="n">
-        <v>13769000000</v>
+        <v>21066000000</v>
       </c>
       <c r="N140" t="n">
-        <v>44737691733</v>
+        <v>41156861598</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>株式会社メガチップス</t>
+          <t>ＮＩＴＴＯＫＵ株式会社</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>6875</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>88.5</v>
+        <v>51.2</v>
       </c>
       <c r="D141" t="n">
-        <v>10620</v>
+        <v>2439</v>
       </c>
       <c r="E141" t="n">
-        <v>4870</v>
+        <v>1710</v>
       </c>
       <c r="F141" t="n">
-        <v>118.1</v>
+        <v>42.6</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -7726,102 +7726,102 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>25769446000</v>
+        <v>11768000000</v>
       </c>
       <c r="J141" t="n">
-        <v>2249411000</v>
+        <v>6299000000</v>
       </c>
       <c r="K141" t="n">
-        <v>101636005000</v>
+        <v>2999000000</v>
       </c>
       <c r="L141" t="n">
-        <v>67428618000</v>
+        <v>33919000000</v>
       </c>
       <c r="M141" t="n">
-        <v>129654862000</v>
+        <v>21066000000</v>
       </c>
       <c r="N141" t="n">
-        <v>146565568620</v>
+        <v>41156861598</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>株式会社青山財産ネットワークス</t>
+          <t>新光商事株式会社</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>8929</t>
+          <t>8141</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>43.4</v>
+        <v>30.8</v>
       </c>
       <c r="D142" t="n">
-        <v>1335</v>
+        <v>1565</v>
       </c>
       <c r="E142" t="n">
-        <v>1347.74653160027</v>
+        <v>930</v>
       </c>
       <c r="F142" t="n">
-        <v>-0.9</v>
+        <v>68.3</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>10862000000</v>
+        <v>10579000000</v>
       </c>
       <c r="J142" t="n">
-        <v>245000000</v>
+        <v>195000000</v>
       </c>
       <c r="K142" t="n">
-        <v>2845000000</v>
+        <v>2995000000</v>
       </c>
       <c r="L142" t="n">
-        <v>7128000000</v>
+        <v>51945000000</v>
       </c>
       <c r="M142" t="n">
-        <v>13952000000</v>
+        <v>13769000000</v>
       </c>
       <c r="N142" t="n">
-        <v>32127092730</v>
+        <v>44680591935</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>平和不動産株式会社</t>
+          <t>株式会社メガチップス</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>8803</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>73.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D143" t="n">
-        <v>2325</v>
+        <v>10490</v>
       </c>
       <c r="E143" t="n">
-        <v>3610</v>
+        <v>4870</v>
       </c>
       <c r="F143" t="n">
-        <v>-35.6</v>
+        <v>115.4</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -7830,106 +7830,106 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>28111000000</v>
+        <v>25769446000</v>
       </c>
       <c r="J143" t="n">
-        <v>79319000000</v>
+        <v>2249411000</v>
       </c>
       <c r="K143" t="n">
-        <v>5997000000</v>
+        <v>101636005000</v>
       </c>
       <c r="L143" t="n">
-        <v>119278000000</v>
+        <v>67428618000</v>
       </c>
       <c r="M143" t="n">
-        <v>113427000000</v>
+        <v>129654862000</v>
       </c>
       <c r="N143" t="n">
-        <v>153613349850</v>
+        <v>144771451490</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>小林製薬株式会社</t>
+          <t>株式会社青山財産ネットワークス</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>8929</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>30.1</v>
+        <v>43.4</v>
       </c>
       <c r="D144" t="n">
-        <v>5777</v>
+        <v>1335</v>
       </c>
       <c r="E144" t="n">
-        <v>2148.936934940886</v>
+        <v>1347.74653160027</v>
       </c>
       <c r="F144" t="n">
-        <v>168.8</v>
+        <v>-0.9</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>81987000000</v>
+        <v>10862000000</v>
       </c>
       <c r="J144" t="n">
-        <v>32461000000</v>
+        <v>245000000</v>
       </c>
       <c r="K144" t="n">
-        <v>14872000000</v>
+        <v>2845000000</v>
       </c>
       <c r="L144" t="n">
-        <v>195600000000</v>
+        <v>7128000000</v>
       </c>
       <c r="M144" t="n">
-        <v>129320000000</v>
+        <v>13952000000</v>
       </c>
       <c r="N144" t="n">
-        <v>429454213517</v>
+        <v>32127092730</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>小林製薬株式会社</t>
+          <t>平和不動産株式会社</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>30.1</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="D145" t="n">
-        <v>5777</v>
+        <v>2318</v>
       </c>
       <c r="E145" t="n">
-        <v>5066.092575838703</v>
+        <v>3610</v>
       </c>
       <c r="F145" t="n">
-        <v>14</v>
+        <v>-35.8</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -7938,46 +7938,46 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>81987000000</v>
+        <v>28111000000</v>
       </c>
       <c r="J145" t="n">
-        <v>32461000000</v>
+        <v>79319000000</v>
       </c>
       <c r="K145" t="n">
-        <v>14872000000</v>
+        <v>5997000000</v>
       </c>
       <c r="L145" t="n">
-        <v>195600000000</v>
+        <v>119278000000</v>
       </c>
       <c r="M145" t="n">
-        <v>129320000000</v>
+        <v>113427000000</v>
       </c>
       <c r="N145" t="n">
-        <v>429454213517</v>
+        <v>153150858044</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>セーレン株式会社</t>
+          <t>小林製薬株式会社</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>3569</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>36.9</v>
+        <v>30.2</v>
       </c>
       <c r="D146" t="n">
-        <v>3250</v>
+        <v>5768</v>
       </c>
       <c r="E146" t="n">
-        <v>1359.655069733296</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="F146" t="n">
-        <v>139</v>
+        <v>168.4</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -7986,50 +7986,50 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>35451000000</v>
+        <v>81987000000</v>
       </c>
       <c r="J146" t="n">
-        <v>25813000000</v>
+        <v>32461000000</v>
       </c>
       <c r="K146" t="n">
-        <v>8891000000</v>
+        <v>14872000000</v>
       </c>
       <c r="L146" t="n">
-        <v>91845000000</v>
+        <v>195600000000</v>
       </c>
       <c r="M146" t="n">
-        <v>70155000000</v>
+        <v>129320000000</v>
       </c>
       <c r="N146" t="n">
-        <v>190333783250</v>
+        <v>428785165928</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>データセクション株式会社</t>
+          <t>小林製薬株式会社</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>2.4</v>
+        <v>30.2</v>
       </c>
       <c r="D147" t="n">
-        <v>1605</v>
+        <v>5768</v>
       </c>
       <c r="E147" t="n">
-        <v>5143.276404494382</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="F147" t="n">
-        <v>-68.8</v>
+        <v>13.9</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -8038,650 +8038,754 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1420430000</v>
+        <v>81987000000</v>
       </c>
       <c r="J147" t="n">
-        <v>1162000</v>
+        <v>32461000000</v>
       </c>
       <c r="K147" t="n">
-        <v>49326000</v>
+        <v>14872000000</v>
       </c>
       <c r="L147" t="n">
-        <v>2818110000</v>
+        <v>195600000000</v>
       </c>
       <c r="M147" t="n">
-        <v>1470918000</v>
+        <v>129320000000</v>
       </c>
       <c r="N147" t="n">
-        <v>60127001130</v>
+        <v>428785165928</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>愛眼株式会社</t>
+          <t>セーレン株式会社</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>9854</t>
+          <t>3569</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>70.7</v>
+        <v>37.6</v>
       </c>
       <c r="D148" t="n">
-        <v>281</v>
+        <v>3195</v>
       </c>
       <c r="E148" t="n">
-        <v>246.9708756284982</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="F148" t="n">
-        <v>13.8</v>
+        <v>135</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2219000000</v>
+        <v>35451000000</v>
       </c>
       <c r="J148" t="n">
-        <v>1030000000</v>
+        <v>25813000000</v>
       </c>
       <c r="K148" t="n">
-        <v>604000000</v>
+        <v>8891000000</v>
       </c>
       <c r="L148" t="n">
-        <v>12920000000</v>
+        <v>91845000000</v>
       </c>
       <c r="M148" t="n">
-        <v>3853000000</v>
+        <v>70155000000</v>
       </c>
       <c r="N148" t="n">
-        <v>5453286915</v>
+        <v>186458413995</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>株式会社アシロ</t>
+          <t>データセクション株式会社</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>14</v>
+        <v>2.5</v>
       </c>
       <c r="D149" t="n">
-        <v>1560</v>
+        <v>1547</v>
       </c>
       <c r="E149" t="n">
-        <v>1396.628697042366</v>
+        <v>5143.276404494382</v>
       </c>
       <c r="F149" t="n">
-        <v>11.7</v>
+        <v>-69.90000000000001</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1428281000</v>
+        <v>1420430000</v>
       </c>
       <c r="J149" t="n">
-        <v>102238000</v>
+        <v>1162000</v>
       </c>
       <c r="K149" t="n">
-        <v>0</v>
+        <v>49326000</v>
       </c>
       <c r="L149" t="n">
-        <v>1804458000</v>
+        <v>2818110000</v>
       </c>
       <c r="M149" t="n">
-        <v>1530519000</v>
+        <v>1470918000</v>
       </c>
       <c r="N149" t="n">
-        <v>10966155720</v>
+        <v>57954187382</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>三浦工業株式会社</t>
+          <t>愛眼株式会社</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>11.9</v>
+        <v>72.2</v>
       </c>
       <c r="D150" t="n">
-        <v>3054</v>
+        <v>275</v>
       </c>
       <c r="E150" t="n">
-        <v>3147.518794622453</v>
+        <v>246.9708756284982</v>
       </c>
       <c r="F150" t="n">
-        <v>-3</v>
+        <v>11.3</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>20794000000</v>
+        <v>2219000000</v>
       </c>
       <c r="J150" t="n">
-        <v>10600000000</v>
+        <v>1030000000</v>
       </c>
       <c r="K150" t="n">
-        <v>10773000000</v>
+        <v>604000000</v>
       </c>
       <c r="L150" t="n">
-        <v>138378000000</v>
+        <v>12920000000</v>
       </c>
       <c r="M150" t="n">
-        <v>42167000000</v>
+        <v>3853000000</v>
       </c>
       <c r="N150" t="n">
-        <v>353498545440</v>
+        <v>5336846625</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>株式会社カカクコム</t>
+          <t>株式会社アシロ</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>7378</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>7</v>
+        <v>13.9</v>
       </c>
       <c r="D151" t="n">
-        <v>3695</v>
+        <v>1561</v>
       </c>
       <c r="E151" t="n">
-        <v>2318.314890576102</v>
+        <v>1396.628697042366</v>
       </c>
       <c r="F151" t="n">
-        <v>59.4</v>
+        <v>11.8</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>46452000000</v>
+        <v>1428281000</v>
       </c>
       <c r="J151" t="n">
-        <v>68000000</v>
+        <v>102238000</v>
       </c>
       <c r="K151" t="n">
-        <v>4669000000</v>
+        <v>0</v>
       </c>
       <c r="L151" t="n">
-        <v>45479000000</v>
+        <v>1804458000</v>
       </c>
       <c r="M151" t="n">
-        <v>51189000000</v>
+        <v>1530519000</v>
       </c>
       <c r="N151" t="n">
-        <v>731005006565</v>
+        <v>10973185307</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>古河機械金属株式会社</t>
+          <t>三浦工業株式会社</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>44.6</v>
+        <v>12.1</v>
       </c>
       <c r="D152" t="n">
-        <v>4265</v>
+        <v>3005</v>
       </c>
       <c r="E152" t="n">
-        <v>1600</v>
+        <v>3147.518794622453</v>
       </c>
       <c r="F152" t="n">
-        <v>166.6</v>
+        <v>-4.5</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>14468000000</v>
+        <v>20794000000</v>
       </c>
       <c r="J152" t="n">
-        <v>26121000000</v>
+        <v>10600000000</v>
       </c>
       <c r="K152" t="n">
-        <v>19903000000</v>
+        <v>10773000000</v>
       </c>
       <c r="L152" t="n">
-        <v>100075000000</v>
+        <v>138378000000</v>
       </c>
       <c r="M152" t="n">
-        <v>60492000000</v>
+        <v>42167000000</v>
       </c>
       <c r="N152" t="n">
-        <v>135499549005</v>
+        <v>347826826800</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>多木化学株式会社</t>
+          <t>株式会社カカクコム</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>4025</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>30.8</v>
+        <v>6.8</v>
       </c>
       <c r="D153" t="n">
-        <v>5680</v>
+        <v>3796</v>
       </c>
       <c r="E153" t="n">
-        <v>4695.956053243186</v>
+        <v>2318.314890576102</v>
       </c>
       <c r="F153" t="n">
-        <v>21</v>
+        <v>63.7</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>6433000000</v>
+        <v>46452000000</v>
       </c>
       <c r="J153" t="n">
-        <v>7985000000</v>
+        <v>68000000</v>
       </c>
       <c r="K153" t="n">
-        <v>199000000</v>
+        <v>4669000000</v>
       </c>
       <c r="L153" t="n">
-        <v>29378000000</v>
+        <v>45479000000</v>
       </c>
       <c r="M153" t="n">
-        <v>14617000000</v>
+        <v>51189000000</v>
       </c>
       <c r="N153" t="n">
-        <v>47413055920</v>
+        <v>750986469532</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>エムスリー株式会社</t>
+          <t>古河機械金属株式会社</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2413</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>7.8</v>
+        <v>47.1</v>
       </c>
       <c r="D154" t="n">
-        <v>1701</v>
+        <v>4045</v>
       </c>
       <c r="E154" t="n">
-        <v>1638.585693292194</v>
+        <v>1600</v>
       </c>
       <c r="F154" t="n">
-        <v>3.8</v>
+        <v>152.8</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>78812000000</v>
+        <v>14468000000</v>
       </c>
       <c r="J154" t="n">
-        <v>345000000</v>
+        <v>26121000000</v>
       </c>
       <c r="K154" t="n">
-        <v>9506000000</v>
+        <v>19903000000</v>
       </c>
       <c r="L154" t="n">
-        <v>152472000000</v>
+        <v>100075000000</v>
       </c>
       <c r="M154" t="n">
-        <v>88663000000</v>
+        <v>60492000000</v>
       </c>
       <c r="N154" t="n">
-        <v>1133403959961</v>
+        <v>128510123265</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>三井松島ホールディングス株式会社</t>
+          <t>多木化学株式会社</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>40.2</v>
+        <v>31.6</v>
       </c>
       <c r="D155" t="n">
-        <v>2275</v>
+        <v>5550</v>
       </c>
       <c r="E155" t="n">
-        <v>2920</v>
+        <v>4695.956053243186</v>
       </c>
       <c r="F155" t="n">
-        <v>-22.1</v>
+        <v>18.2</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I155" t="n">
-        <v>19413000000</v>
+        <v>6433000000</v>
       </c>
       <c r="J155" t="n">
-        <v>3540000000</v>
+        <v>7985000000</v>
       </c>
       <c r="K155" t="n">
-        <v>10945000000</v>
+        <v>199000000</v>
       </c>
       <c r="L155" t="n">
-        <v>35537000000</v>
+        <v>29378000000</v>
       </c>
       <c r="M155" t="n">
-        <v>33898000000</v>
+        <v>14617000000</v>
       </c>
       <c r="N155" t="n">
-        <v>84238609000</v>
+        <v>46327897950</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ノリタケ株式会社</t>
+          <t>エムスリー株式会社</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>39.2</v>
+        <v>7.9</v>
       </c>
       <c r="D156" t="n">
-        <v>3470</v>
+        <v>1690</v>
       </c>
       <c r="E156" t="n">
-        <v>3573.410502159827</v>
+        <v>1638.585693292194</v>
       </c>
       <c r="F156" t="n">
-        <v>-2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I156" t="n">
-        <v>11733000000</v>
+        <v>78812000000</v>
       </c>
       <c r="J156" t="n">
-        <v>20204000000</v>
+        <v>345000000</v>
       </c>
       <c r="K156" t="n">
-        <v>42879000000</v>
+        <v>9506000000</v>
       </c>
       <c r="L156" t="n">
-        <v>118800000000</v>
+        <v>152472000000</v>
       </c>
       <c r="M156" t="n">
-        <v>74816000000</v>
+        <v>88663000000</v>
       </c>
       <c r="N156" t="n">
-        <v>190899530780</v>
+        <v>1126074481090</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>株式会社ＡＣＳＬ</t>
+          <t>三井松島ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>8.199999999999999</v>
+        <v>41.2</v>
       </c>
       <c r="D157" t="n">
-        <v>1304</v>
+        <v>2223</v>
       </c>
       <c r="E157" t="n">
-        <v>913.2768512341561</v>
+        <v>2920</v>
       </c>
       <c r="F157" t="n">
-        <v>42.8</v>
+        <v>-23.9</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1891731000</v>
+        <v>19413000000</v>
       </c>
       <c r="J157" t="n">
-        <v>3724000</v>
+        <v>3540000000</v>
       </c>
       <c r="K157" t="n">
-        <v>197577000</v>
+        <v>10945000000</v>
       </c>
       <c r="L157" t="n">
-        <v>3572642000</v>
+        <v>35537000000</v>
       </c>
       <c r="M157" t="n">
-        <v>2093032000</v>
+        <v>33898000000</v>
       </c>
       <c r="N157" t="n">
-        <v>25522203568</v>
+        <v>82313155080</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>株式会社スズケン</t>
+          <t>ノリタケ株式会社</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>9987</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>77.5</v>
+        <v>39.8</v>
       </c>
       <c r="D158" t="n">
-        <v>5197</v>
+        <v>3420</v>
       </c>
       <c r="E158" t="n">
-        <v>4137.137750115735</v>
+        <v>3573.410502159827</v>
       </c>
       <c r="F158" t="n">
-        <v>25.6</v>
+        <v>-4.3</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>168215000000</v>
+        <v>11733000000</v>
       </c>
       <c r="J158" t="n">
-        <v>65453000000</v>
+        <v>20204000000</v>
       </c>
       <c r="K158" t="n">
-        <v>38927000000</v>
+        <v>42879000000</v>
       </c>
       <c r="L158" t="n">
-        <v>418062000000</v>
+        <v>118800000000</v>
       </c>
       <c r="M158" t="n">
-        <v>272595000000</v>
+        <v>74816000000</v>
       </c>
       <c r="N158" t="n">
-        <v>351513880465</v>
+        <v>188148817080</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
+          <t>株式会社ＡＣＳＬ</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>6232</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="D159" t="n">
+        <v>1303</v>
+      </c>
+      <c r="E159" t="n">
+        <v>913.2768512341561</v>
+      </c>
+      <c r="F159" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
+        <v>1891731000</v>
+      </c>
+      <c r="J159" t="n">
+        <v>3724000</v>
+      </c>
+      <c r="K159" t="n">
+        <v>197577000</v>
+      </c>
+      <c r="L159" t="n">
+        <v>3572642000</v>
+      </c>
+      <c r="M159" t="n">
+        <v>2093032000</v>
+      </c>
+      <c r="N159" t="n">
+        <v>25502631326</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>株式会社スズケン</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>79</v>
+      </c>
+      <c r="D160" t="n">
+        <v>5173</v>
+      </c>
+      <c r="E160" t="n">
+        <v>4137.137750115735</v>
+      </c>
+      <c r="F160" t="n">
+        <v>25</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>168215000000</v>
+      </c>
+      <c r="J160" t="n">
+        <v>65453000000</v>
+      </c>
+      <c r="K160" t="n">
+        <v>38927000000</v>
+      </c>
+      <c r="L160" t="n">
+        <v>418062000000</v>
+      </c>
+      <c r="M160" t="n">
+        <v>272595000000</v>
+      </c>
+      <c r="N160" t="n">
+        <v>344957309697</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
           <t>フォスター電機株式会社</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
+      <c r="B161" t="inlineStr">
         <is>
           <t>6794</t>
         </is>
       </c>
-      <c r="C159" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="D159" t="n">
-        <v>2965</v>
-      </c>
-      <c r="E159" t="n">
+      <c r="C161" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="D161" t="n">
+        <v>2990</v>
+      </c>
+      <c r="E161" t="n">
         <v>2681.96152003832</v>
       </c>
-      <c r="F159" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="G159" t="inlineStr">
+      <c r="F161" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G161" t="inlineStr">
         <is>
           <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
+      <c r="H161" t="inlineStr">
         <is>
           <t>2026-01-22</t>
         </is>
       </c>
-      <c r="I159" t="n">
+      <c r="I161" t="n">
         <v>12089000000</v>
       </c>
-      <c r="J159" t="n">
+      <c r="J161" t="n">
         <v>7327000000</v>
       </c>
-      <c r="K159" t="n">
+      <c r="K161" t="n">
         <v>1115000000</v>
       </c>
-      <c r="L159" t="n">
+      <c r="L161" t="n">
         <v>51632000000</v>
       </c>
-      <c r="M159" t="n">
+      <c r="M161" t="n">
         <v>20531000000</v>
       </c>
-      <c r="N159" t="n">
-        <v>66617047755</v>
+      <c r="N161" t="n">
+        <v>67178742930</v>
       </c>
     </row>
   </sheetData>

--- a/docs/アクティビスト銘柄_資産判定.xlsx
+++ b/docs/アクティビスト銘柄_資産判定.xlsx
@@ -8265,7 +8265,7 @@
         <v>1530519000</v>
       </c>
       <c r="N151" t="n">
-        <v>10973185307</v>
+        <v>10976307307</v>
       </c>
     </row>
     <row r="152">

--- a/docs/アクティビスト銘柄_資産判定.xlsx
+++ b/docs/アクティビスト銘柄_資産判定.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N161"/>
+  <dimension ref="A1:N162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>45.7</v>
+        <v>44.9</v>
       </c>
       <c r="D2" t="n">
-        <v>1302</v>
+        <v>1325.5</v>
       </c>
       <c r="E2" t="n">
         <v>1111.251693601708</v>
       </c>
       <c r="F2" t="n">
-        <v>17.2</v>
+        <v>19.3</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -537,7 +537,7 @@
         <v>213563000000</v>
       </c>
       <c r="N2" t="n">
-        <v>467459716080</v>
+        <v>475896969020</v>
       </c>
     </row>
     <row r="3">
@@ -552,16 +552,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>55.4</v>
+        <v>54.8</v>
       </c>
       <c r="D3" t="n">
-        <v>1147</v>
+        <v>1160</v>
       </c>
       <c r="E3" t="n">
         <v>1019.677694332945</v>
       </c>
       <c r="F3" t="n">
-        <v>12.5</v>
+        <v>13.8</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         <v>106991000000</v>
       </c>
       <c r="N3" t="n">
-        <v>192983380850</v>
+        <v>195170638000</v>
       </c>
     </row>
     <row r="4">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>3387</v>
+        <v>3455</v>
       </c>
       <c r="E4" t="n">
         <v>6116.356643776557</v>
       </c>
       <c r="F4" t="n">
-        <v>-44.6</v>
+        <v>-43.5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         <v>219041000000</v>
       </c>
       <c r="N4" t="n">
-        <v>3064415325678</v>
+        <v>3125938869270</v>
       </c>
     </row>
     <row r="5">
@@ -656,16 +656,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>31</v>
+        <v>30.2</v>
       </c>
       <c r="D5" t="n">
-        <v>2171</v>
+        <v>2227</v>
       </c>
       <c r="E5" t="n">
         <v>1815.198567455447</v>
       </c>
       <c r="F5" t="n">
-        <v>19.6</v>
+        <v>22.7</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         <v>168499000000</v>
       </c>
       <c r="N5" t="n">
-        <v>544090054092</v>
+        <v>558124620204</v>
       </c>
     </row>
     <row r="6">
@@ -708,16 +708,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>55.1</v>
+        <v>54.2</v>
       </c>
       <c r="D6" t="n">
-        <v>10620</v>
+        <v>10790</v>
       </c>
       <c r="E6" t="n">
         <v>5684.0003469471</v>
       </c>
       <c r="F6" t="n">
-        <v>86.8</v>
+        <v>89.8</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>91895000000</v>
       </c>
       <c r="N6" t="n">
-        <v>166851435960</v>
+        <v>169522315820</v>
       </c>
     </row>
     <row r="7">
@@ -760,16 +760,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>55.1</v>
+        <v>54.2</v>
       </c>
       <c r="D7" t="n">
-        <v>10620</v>
+        <v>10790</v>
       </c>
       <c r="E7" t="n">
         <v>4549.503641591014</v>
       </c>
       <c r="F7" t="n">
-        <v>133.4</v>
+        <v>137.2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>91895000000</v>
       </c>
       <c r="N7" t="n">
-        <v>166851435960</v>
+        <v>169522315820</v>
       </c>
     </row>
     <row r="8">
@@ -815,13 +815,13 @@
         <v>14.5</v>
       </c>
       <c r="D8" t="n">
-        <v>3860</v>
+        <v>3855</v>
       </c>
       <c r="E8" t="n">
         <v>1361.432492253209</v>
       </c>
       <c r="F8" t="n">
-        <v>183.5</v>
+        <v>183.2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>12397436000</v>
       </c>
       <c r="N8" t="n">
-        <v>85627711700</v>
+        <v>85516794975</v>
       </c>
     </row>
     <row r="9">
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>30.3</v>
+        <v>29.8</v>
       </c>
       <c r="D9" t="n">
-        <v>3298</v>
+        <v>3352</v>
       </c>
       <c r="E9" t="n">
         <v>13739.64575539568</v>
       </c>
       <c r="F9" t="n">
-        <v>-76</v>
+        <v>-75.59999999999999</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>325393000000</v>
       </c>
       <c r="N9" t="n">
-        <v>1074265059440</v>
+        <v>1091854602560</v>
       </c>
     </row>
     <row r="10">
@@ -916,16 +916,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>48.2</v>
+        <v>47.2</v>
       </c>
       <c r="D10" t="n">
-        <v>2004.5</v>
+        <v>2048.5</v>
       </c>
       <c r="E10" t="n">
         <v>1198.150742177053</v>
       </c>
       <c r="F10" t="n">
-        <v>67.3</v>
+        <v>71</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>213966000000</v>
       </c>
       <c r="N10" t="n">
-        <v>443823843834</v>
+        <v>453566048438</v>
       </c>
     </row>
     <row r="11">
@@ -968,16 +968,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>48.2</v>
+        <v>47.2</v>
       </c>
       <c r="D11" t="n">
-        <v>2004.5</v>
+        <v>2048.5</v>
       </c>
       <c r="E11" t="n">
         <v>1188.162962482466</v>
       </c>
       <c r="F11" t="n">
-        <v>68.7</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>213966000000</v>
       </c>
       <c r="N11" t="n">
-        <v>443823843834</v>
+        <v>453566048438</v>
       </c>
     </row>
     <row r="12">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>3588</v>
+        <v>3682</v>
       </c>
       <c r="E12" t="n">
         <v>2995.424821743842</v>
       </c>
       <c r="F12" t="n">
-        <v>19.8</v>
+        <v>22.9</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>129979000000</v>
       </c>
       <c r="N12" t="n">
-        <v>527312874192</v>
+        <v>541127648488</v>
       </c>
     </row>
     <row r="13">
@@ -1072,16 +1072,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>74.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>4815</v>
+        <v>4900</v>
       </c>
       <c r="E13" t="n">
         <v>4991.027246539169</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.5</v>
+        <v>-1.8</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>1007966000000</v>
       </c>
       <c r="N13" t="n">
-        <v>1349267610690</v>
+        <v>1373086457400</v>
       </c>
     </row>
     <row r="14">
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="D14" t="n">
-        <v>1702.5</v>
+        <v>1710</v>
       </c>
       <c r="E14" t="n">
         <v>1512.21980974841</v>
       </c>
       <c r="F14" t="n">
-        <v>12.6</v>
+        <v>13.1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>120816000000</v>
       </c>
       <c r="N14" t="n">
-        <v>560832039008</v>
+        <v>563302664730</v>
       </c>
     </row>
     <row r="15">
@@ -1176,16 +1176,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="D15" t="n">
-        <v>2607</v>
+        <v>2582.5</v>
       </c>
       <c r="E15" t="n">
         <v>1827.011042553346</v>
       </c>
       <c r="F15" t="n">
-        <v>42.7</v>
+        <v>41.4</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>48336000000</v>
       </c>
       <c r="N15" t="n">
-        <v>636297713997</v>
+        <v>630317931108</v>
       </c>
     </row>
     <row r="16">
@@ -1228,16 +1228,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>140.4</v>
+        <v>137.2</v>
       </c>
       <c r="D16" t="n">
-        <v>1532</v>
+        <v>1567</v>
       </c>
       <c r="E16" t="n">
         <v>2122.579027791042</v>
       </c>
       <c r="F16" t="n">
-        <v>-27.8</v>
+        <v>-26.2</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>80333000000</v>
       </c>
       <c r="N16" t="n">
-        <v>57223918164</v>
+        <v>58531253109</v>
       </c>
     </row>
     <row r="17">
@@ -1280,16 +1280,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.3</v>
+        <v>16.7</v>
       </c>
       <c r="D17" t="n">
-        <v>2881</v>
+        <v>2987</v>
       </c>
       <c r="E17" t="n">
         <v>6272.971195510064</v>
       </c>
       <c r="F17" t="n">
-        <v>-54.1</v>
+        <v>-52.4</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>179622000000</v>
       </c>
       <c r="N17" t="n">
-        <v>1039106213454</v>
+        <v>1077337820058</v>
       </c>
     </row>
     <row r="18">
@@ -1335,7 +1335,7 @@
         <v>5.3</v>
       </c>
       <c r="D18" t="n">
-        <v>3761</v>
+        <v>3760</v>
       </c>
       <c r="E18" t="n">
         <v>1572.181660925393</v>
@@ -1369,7 +1369,7 @@
         <v>35501000000</v>
       </c>
       <c r="N18" t="n">
-        <v>671575657377</v>
+        <v>671397094320</v>
       </c>
     </row>
     <row r="19">
@@ -1387,13 +1387,13 @@
         <v>5.3</v>
       </c>
       <c r="D19" t="n">
-        <v>3761</v>
+        <v>3760</v>
       </c>
       <c r="E19" t="n">
         <v>1141.512891683109</v>
       </c>
       <c r="F19" t="n">
-        <v>229.5</v>
+        <v>229.4</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>35501000000</v>
       </c>
       <c r="N19" t="n">
-        <v>671575657377</v>
+        <v>671397094320</v>
       </c>
     </row>
     <row r="20">
@@ -1436,16 +1436,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>45.8</v>
+        <v>44.6</v>
       </c>
       <c r="D20" t="n">
-        <v>5863</v>
+        <v>6021</v>
       </c>
       <c r="E20" t="n">
         <v>2836.942753814942</v>
       </c>
       <c r="F20" t="n">
-        <v>106.7</v>
+        <v>112.2</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>94351000000</v>
       </c>
       <c r="N20" t="n">
-        <v>206083986823</v>
+        <v>211637674341</v>
       </c>
     </row>
     <row r="21">
@@ -1488,16 +1488,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>55.3</v>
+        <v>55.9</v>
       </c>
       <c r="D21" t="n">
-        <v>4063</v>
+        <v>4019</v>
       </c>
       <c r="E21" t="n">
         <v>2863.970160821546</v>
       </c>
       <c r="F21" t="n">
-        <v>41.9</v>
+        <v>40.3</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>161529000000</v>
       </c>
       <c r="N21" t="n">
-        <v>292313197269</v>
+        <v>289147610097</v>
       </c>
     </row>
     <row r="22">
@@ -1540,16 +1540,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>53.3</v>
+        <v>53.1</v>
       </c>
       <c r="D22" t="n">
-        <v>4612</v>
+        <v>4625</v>
       </c>
       <c r="E22" t="n">
         <v>2566.284807227078</v>
       </c>
       <c r="F22" t="n">
-        <v>79.7</v>
+        <v>80.2</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>231575000000</v>
       </c>
       <c r="N22" t="n">
-        <v>434852105200</v>
+        <v>436077837500</v>
       </c>
     </row>
     <row r="23">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>29</v>
+        <v>28.7</v>
       </c>
       <c r="D23" t="n">
-        <v>5093</v>
+        <v>5140</v>
       </c>
       <c r="E23" t="n">
         <v>2779.139169918938</v>
       </c>
       <c r="F23" t="n">
-        <v>83.3</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>183216000000</v>
       </c>
       <c r="N23" t="n">
-        <v>631697374803</v>
+        <v>637526900940</v>
       </c>
     </row>
     <row r="24">
@@ -1644,16 +1644,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>3950</v>
+        <v>4002</v>
       </c>
       <c r="E24" t="n">
         <v>2420.370957920882</v>
       </c>
       <c r="F24" t="n">
-        <v>63.2</v>
+        <v>65.3</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>18167000000</v>
       </c>
       <c r="N24" t="n">
-        <v>195276462050</v>
+        <v>197847190158</v>
       </c>
     </row>
     <row r="25">
@@ -1696,16 +1696,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>1725</v>
+        <v>1743</v>
       </c>
       <c r="E25" t="n">
         <v>1344.518957928979</v>
       </c>
       <c r="F25" t="n">
-        <v>28.3</v>
+        <v>29.6</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>45956000000</v>
       </c>
       <c r="N25" t="n">
-        <v>555029536425</v>
+        <v>560821148979</v>
       </c>
     </row>
     <row r="26">
@@ -1748,16 +1748,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>60.1</v>
+        <v>59.5</v>
       </c>
       <c r="D26" t="n">
-        <v>4984</v>
+        <v>5031</v>
       </c>
       <c r="E26" t="n">
         <v>4154.626869982095</v>
       </c>
       <c r="F26" t="n">
-        <v>20</v>
+        <v>21.1</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>179086000000</v>
       </c>
       <c r="N26" t="n">
-        <v>298046569184</v>
+        <v>300857200956</v>
       </c>
     </row>
     <row r="27">
@@ -1800,16 +1800,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>14.4</v>
+        <v>13.8</v>
       </c>
       <c r="D27" t="n">
-        <v>3810</v>
+        <v>3964</v>
       </c>
       <c r="E27" t="n">
         <v>2561.705402476645</v>
       </c>
       <c r="F27" t="n">
-        <v>48.7</v>
+        <v>54.7</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>100104000000</v>
       </c>
       <c r="N27" t="n">
-        <v>697159153050</v>
+        <v>725338289420</v>
       </c>
     </row>
     <row r="28">
@@ -1852,16 +1852,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>44.7</v>
+        <v>44.8</v>
       </c>
       <c r="D28" t="n">
-        <v>3461</v>
+        <v>3447</v>
       </c>
       <c r="E28" t="n">
         <v>2560</v>
       </c>
       <c r="F28" t="n">
-        <v>35.2</v>
+        <v>34.6</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>190312000000</v>
       </c>
       <c r="N28" t="n">
-        <v>426084769066</v>
+        <v>424361224782</v>
       </c>
     </row>
     <row r="29">
@@ -1904,16 +1904,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>91</v>
+        <v>90.8</v>
       </c>
       <c r="D29" t="n">
-        <v>4225</v>
+        <v>4235</v>
       </c>
       <c r="E29" t="n">
         <v>3449.780346820809</v>
       </c>
       <c r="F29" t="n">
-        <v>22.5</v>
+        <v>22.8</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>90928000000</v>
       </c>
       <c r="N29" t="n">
-        <v>99908625700</v>
+        <v>100145095820</v>
       </c>
     </row>
     <row r="30">
@@ -1956,16 +1956,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>59.6</v>
+        <v>57.9</v>
       </c>
       <c r="D30" t="n">
-        <v>1603</v>
+        <v>1648</v>
       </c>
       <c r="E30" t="n">
         <v>1746.940387696806</v>
       </c>
       <c r="F30" t="n">
-        <v>-8.199999999999999</v>
+        <v>-5.7</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>36070000000</v>
       </c>
       <c r="N30" t="n">
-        <v>60563733279</v>
+        <v>62263900464</v>
       </c>
     </row>
     <row r="31">
@@ -2008,16 +2008,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>105.7</v>
+        <v>104.9</v>
       </c>
       <c r="D31" t="n">
-        <v>1677</v>
+        <v>1690</v>
       </c>
       <c r="E31" t="n">
         <v>2298.672482457804</v>
       </c>
       <c r="F31" t="n">
-        <v>-27</v>
+        <v>-26.5</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>42752000000</v>
       </c>
       <c r="N31" t="n">
-        <v>40435299099</v>
+        <v>40748751030</v>
       </c>
     </row>
     <row r="32">
@@ -2060,16 +2060,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>68</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>2630</v>
+        <v>2666</v>
       </c>
       <c r="E32" t="n">
         <v>1270</v>
       </c>
       <c r="F32" t="n">
-        <v>107.1</v>
+        <v>109.9</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>31108000000</v>
       </c>
       <c r="N32" t="n">
-        <v>45729285430</v>
+        <v>46355237626</v>
       </c>
     </row>
     <row r="33">
@@ -2112,16 +2112,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>68</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>2630</v>
+        <v>2666</v>
       </c>
       <c r="E33" t="n">
         <v>1170</v>
       </c>
       <c r="F33" t="n">
-        <v>124.8</v>
+        <v>127.9</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>31108000000</v>
       </c>
       <c r="N33" t="n">
-        <v>45729285430</v>
+        <v>46355237626</v>
       </c>
     </row>
     <row r="34">
@@ -2164,16 +2164,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>33.8</v>
+        <v>33.1</v>
       </c>
       <c r="D34" t="n">
-        <v>2812.5</v>
+        <v>2869</v>
       </c>
       <c r="E34" t="n">
         <v>2381.523440544182</v>
       </c>
       <c r="F34" t="n">
-        <v>18.1</v>
+        <v>20.5</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>168696000000</v>
       </c>
       <c r="N34" t="n">
-        <v>499473818438</v>
+        <v>509507692479</v>
       </c>
     </row>
     <row r="35">
@@ -2216,16 +2216,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>82.5</v>
+        <v>80.8</v>
       </c>
       <c r="D35" t="n">
-        <v>2509</v>
+        <v>2564</v>
       </c>
       <c r="E35" t="n">
         <v>2939.562915943684</v>
       </c>
       <c r="F35" t="n">
-        <v>-14.6</v>
+        <v>-12.8</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>108430000000</v>
       </c>
       <c r="N35" t="n">
-        <v>131388511956</v>
+        <v>134268690576</v>
       </c>
     </row>
     <row r="36">
@@ -2268,16 +2268,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>48.7</v>
+        <v>46.2</v>
       </c>
       <c r="D36" t="n">
-        <v>13410</v>
+        <v>14130</v>
       </c>
       <c r="E36" t="n">
         <v>7040.15625</v>
       </c>
       <c r="F36" t="n">
-        <v>90.5</v>
+        <v>100.7</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>6799899000</v>
       </c>
       <c r="N36" t="n">
-        <v>13967413470</v>
+        <v>14717341710</v>
       </c>
     </row>
     <row r="37">
@@ -2320,16 +2320,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>48.7</v>
+        <v>46.2</v>
       </c>
       <c r="D37" t="n">
-        <v>13410</v>
+        <v>14130</v>
       </c>
       <c r="E37" t="n">
         <v>7040.15625</v>
       </c>
       <c r="F37" t="n">
-        <v>90.5</v>
+        <v>100.7</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>6799899000</v>
       </c>
       <c r="N37" t="n">
-        <v>13967413470</v>
+        <v>14717341710</v>
       </c>
     </row>
     <row r="38">
@@ -2372,16 +2372,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>87.59999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="D38" t="n">
-        <v>2737</v>
+        <v>2762</v>
       </c>
       <c r="E38" t="n">
         <v>4265.455132343447</v>
       </c>
       <c r="F38" t="n">
-        <v>-35.8</v>
+        <v>-35.2</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>22869000000</v>
       </c>
       <c r="N38" t="n">
-        <v>26094059866</v>
+        <v>26332405316</v>
       </c>
     </row>
     <row r="39">
@@ -2424,16 +2424,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="D39" t="n">
-        <v>4660</v>
+        <v>4640</v>
       </c>
       <c r="E39" t="n">
         <v>2824.318397803668</v>
       </c>
       <c r="F39" t="n">
-        <v>65</v>
+        <v>64.3</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>61975000000</v>
       </c>
       <c r="N39" t="n">
-        <v>187474852300</v>
+        <v>186670239200</v>
       </c>
     </row>
     <row r="40">
@@ -2476,16 +2476,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="D40" t="n">
-        <v>6600</v>
+        <v>6610</v>
       </c>
       <c r="E40" t="n">
         <v>3096.322467304314</v>
       </c>
       <c r="F40" t="n">
-        <v>113.2</v>
+        <v>113.5</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>52961000000</v>
       </c>
       <c r="N40" t="n">
-        <v>181058922000</v>
+        <v>181333253700</v>
       </c>
     </row>
     <row r="41">
@@ -2528,16 +2528,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>23.9</v>
+        <v>23.5</v>
       </c>
       <c r="D41" t="n">
-        <v>6275</v>
+        <v>6386</v>
       </c>
       <c r="E41" t="n">
         <v>3322.047887165483</v>
       </c>
       <c r="F41" t="n">
-        <v>88.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>492847000000</v>
       </c>
       <c r="N41" t="n">
-        <v>2061368548700</v>
+        <v>2097832597928</v>
       </c>
     </row>
     <row r="42">
@@ -2580,16 +2580,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>36</v>
+        <v>35.4</v>
       </c>
       <c r="D42" t="n">
-        <v>1726</v>
+        <v>1759</v>
       </c>
       <c r="E42" t="n">
         <v>2112.609181636727</v>
       </c>
       <c r="F42" t="n">
-        <v>-18.3</v>
+        <v>-16.7</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>52218000000</v>
       </c>
       <c r="N42" t="n">
-        <v>144914977260</v>
+        <v>147685657590</v>
       </c>
     </row>
     <row r="43">
@@ -2632,16 +2632,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="D43" t="n">
-        <v>700</v>
+        <v>714</v>
       </c>
       <c r="E43" t="n">
         <v>404.9347366248775</v>
       </c>
       <c r="F43" t="n">
-        <v>72.90000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>7044972000</v>
       </c>
       <c r="N43" t="n">
-        <v>186610273500</v>
+        <v>190342478970</v>
       </c>
     </row>
     <row r="44">
@@ -2684,16 +2684,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="D44" t="n">
-        <v>2691</v>
+        <v>2655</v>
       </c>
       <c r="E44" t="n">
         <v>2220.184278344451</v>
       </c>
       <c r="F44" t="n">
-        <v>21.2</v>
+        <v>19.6</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>207116000000</v>
       </c>
       <c r="N44" t="n">
-        <v>3084719765985</v>
+        <v>3043452611925</v>
       </c>
     </row>
     <row r="45">
@@ -2736,16 +2736,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="D45" t="n">
-        <v>21490</v>
+        <v>21550</v>
       </c>
       <c r="E45" t="n">
         <v>11879.91675437757</v>
       </c>
       <c r="F45" t="n">
-        <v>80.90000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>191958000000</v>
       </c>
       <c r="N45" t="n">
-        <v>903043216950</v>
+        <v>905564510250</v>
       </c>
     </row>
     <row r="46">
@@ -2788,16 +2788,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>75</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="E46" t="n">
         <v>730</v>
       </c>
       <c r="F46" t="n">
-        <v>49.7</v>
+        <v>48.9</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>50027000000</v>
       </c>
       <c r="N46" t="n">
-        <v>66732225298</v>
+        <v>66365900182</v>
       </c>
     </row>
     <row r="47">
@@ -2840,16 +2840,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="D47" t="n">
-        <v>5402</v>
+        <v>5435</v>
       </c>
       <c r="E47" t="n">
         <v>3341.42986565678</v>
       </c>
       <c r="F47" t="n">
-        <v>61.7</v>
+        <v>62.7</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>311107000000</v>
       </c>
       <c r="N47" t="n">
-        <v>1283644269986</v>
+        <v>1291485858455</v>
       </c>
     </row>
     <row r="48">
@@ -2892,16 +2892,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>29</v>
+        <v>29.2</v>
       </c>
       <c r="D48" t="n">
-        <v>3185</v>
+        <v>3160</v>
       </c>
       <c r="E48" t="n">
         <v>2550.198980592041</v>
       </c>
       <c r="F48" t="n">
-        <v>24.9</v>
+        <v>23.9</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>32342000000</v>
       </c>
       <c r="N48" t="n">
-        <v>111532062460</v>
+        <v>110656614560</v>
       </c>
     </row>
     <row r="49">
@@ -2944,16 +2944,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>211.5</v>
+        <v>210</v>
       </c>
       <c r="D49" t="n">
-        <v>1636</v>
+        <v>1647.5</v>
       </c>
       <c r="E49" t="n">
         <v>1288.711724885291</v>
       </c>
       <c r="F49" t="n">
-        <v>26.9</v>
+        <v>27.8</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>747066000000</v>
       </c>
       <c r="N49" t="n">
-        <v>353186507028</v>
+        <v>355669175018</v>
       </c>
     </row>
     <row r="50">
@@ -2996,16 +2996,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>68.09999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>4034</v>
+        <v>4108</v>
       </c>
       <c r="E50" t="n">
         <v>3141.424011416125</v>
       </c>
       <c r="F50" t="n">
-        <v>28.4</v>
+        <v>30.8</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>391579000000</v>
       </c>
       <c r="N50" t="n">
-        <v>574827266536</v>
+        <v>585371941232</v>
       </c>
     </row>
     <row r="51">
@@ -3048,16 +3048,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>68.09999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="D51" t="n">
-        <v>4034</v>
+        <v>4108</v>
       </c>
       <c r="E51" t="n">
         <v>2420</v>
       </c>
       <c r="F51" t="n">
-        <v>66.7</v>
+        <v>69.8</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>391579000000</v>
       </c>
       <c r="N51" t="n">
-        <v>574827266536</v>
+        <v>585371941232</v>
       </c>
     </row>
     <row r="52">
@@ -3100,16 +3100,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>42.8</v>
+        <v>41.9</v>
       </c>
       <c r="D52" t="n">
-        <v>4000</v>
+        <v>4083</v>
       </c>
       <c r="E52" t="n">
         <v>3047.091476167608</v>
       </c>
       <c r="F52" t="n">
-        <v>31.3</v>
+        <v>34</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>162458000000</v>
       </c>
       <c r="N52" t="n">
-        <v>379852268000</v>
+        <v>387734202561</v>
       </c>
     </row>
     <row r="53">
@@ -3152,16 +3152,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>46.1</v>
+        <v>45.3</v>
       </c>
       <c r="D53" t="n">
-        <v>3432</v>
+        <v>3497</v>
       </c>
       <c r="E53" t="n">
         <v>2844.704547285864</v>
       </c>
       <c r="F53" t="n">
-        <v>20.6</v>
+        <v>22.9</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>218675000000</v>
       </c>
       <c r="N53" t="n">
-        <v>473854908384</v>
+        <v>482829433164</v>
       </c>
     </row>
     <row r="54">
@@ -3204,16 +3204,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>54.8</v>
+        <v>54.4</v>
       </c>
       <c r="D54" t="n">
-        <v>2262.5</v>
+        <v>2278.5</v>
       </c>
       <c r="E54" t="n">
         <v>1556.090471804319</v>
       </c>
       <c r="F54" t="n">
-        <v>45.4</v>
+        <v>46.4</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>207466000000</v>
       </c>
       <c r="N54" t="n">
-        <v>378784593812</v>
+        <v>381463291492</v>
       </c>
     </row>
     <row r="55">
@@ -3256,16 +3256,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>47.5</v>
+        <v>46.4</v>
       </c>
       <c r="D55" t="n">
-        <v>1780</v>
+        <v>1823</v>
       </c>
       <c r="E55" t="n">
         <v>1529.631984751819</v>
       </c>
       <c r="F55" t="n">
-        <v>16.4</v>
+        <v>19.2</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>6024082000</v>
       </c>
       <c r="N55" t="n">
-        <v>12686360820</v>
+        <v>12992829087</v>
       </c>
     </row>
     <row r="56">
@@ -3308,16 +3308,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>47.5</v>
+        <v>46.4</v>
       </c>
       <c r="D56" t="n">
-        <v>1780</v>
+        <v>1823</v>
       </c>
       <c r="E56" t="n">
         <v>1449.995380693296</v>
       </c>
       <c r="F56" t="n">
-        <v>22.8</v>
+        <v>25.7</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>6024082000</v>
       </c>
       <c r="N56" t="n">
-        <v>12686360820</v>
+        <v>12992829087</v>
       </c>
     </row>
     <row r="57">
@@ -3360,16 +3360,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>67.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D57" t="n">
-        <v>2970</v>
+        <v>3010</v>
       </c>
       <c r="E57" t="n">
-        <v>2696.128808062088</v>
+        <v>2723.418631349517</v>
       </c>
       <c r="F57" t="n">
-        <v>10.2</v>
+        <v>10.5</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -3397,7 +3397,7 @@
         <v>165282000000</v>
       </c>
       <c r="N57" t="n">
-        <v>245513665980</v>
+        <v>248820247340</v>
       </c>
     </row>
     <row r="58">
@@ -3412,16 +3412,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>67.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D58" t="n">
-        <v>2970</v>
+        <v>3010</v>
       </c>
       <c r="E58" t="n">
-        <v>2696.128808062088</v>
+        <v>2709.132103263819</v>
       </c>
       <c r="F58" t="n">
-        <v>10.2</v>
+        <v>11.1</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="I58" t="n">
@@ -3449,239 +3449,239 @@
         <v>165282000000</v>
       </c>
       <c r="N58" t="n">
-        <v>245513665980</v>
+        <v>248820247340</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>京浜急行電鉄株式会社</t>
+          <t>株式会社ニップン</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>120</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D59" t="n">
-        <v>1560.5</v>
+        <v>3010</v>
       </c>
       <c r="E59" t="n">
-        <v>1160.8</v>
+        <v>2696.128808062088</v>
       </c>
       <c r="F59" t="n">
-        <v>34.4</v>
+        <v>11.6</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>61234000000</v>
+        <v>31215000000</v>
       </c>
       <c r="J59" t="n">
-        <v>318113000000</v>
+        <v>48537000000</v>
       </c>
       <c r="K59" t="n">
-        <v>114136000000</v>
+        <v>85530000000</v>
       </c>
       <c r="L59" t="n">
-        <v>256898000000</v>
+        <v>178697000000</v>
       </c>
       <c r="M59" t="n">
-        <v>493483000000</v>
+        <v>165282000000</v>
       </c>
       <c r="N59" t="n">
-        <v>411201863600</v>
+        <v>248820247340</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>あいホールディングス株式会社</t>
+          <t>株式会社ニップン</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>3076</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>23.5</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D60" t="n">
-        <v>2975</v>
+        <v>3010</v>
       </c>
       <c r="E60" t="n">
-        <v>2007.754513143541</v>
+        <v>2696.128808062088</v>
       </c>
       <c r="F60" t="n">
-        <v>48.2</v>
+        <v>11.6</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>32012000000</v>
+        <v>31215000000</v>
       </c>
       <c r="J60" t="n">
-        <v>1646000000</v>
+        <v>48537000000</v>
       </c>
       <c r="K60" t="n">
-        <v>3550000000</v>
+        <v>85530000000</v>
       </c>
       <c r="L60" t="n">
-        <v>53765000000</v>
+        <v>178697000000</v>
       </c>
       <c r="M60" t="n">
-        <v>37208000000</v>
+        <v>165282000000</v>
       </c>
       <c r="N60" t="n">
-        <v>158486969725</v>
+        <v>248820247340</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>エア・ウォーター株式会社</t>
+          <t>京浜急行電鉄株式会社</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>15</v>
+        <v>119.1</v>
       </c>
       <c r="D61" t="n">
-        <v>2990</v>
+        <v>1572</v>
       </c>
       <c r="E61" t="n">
-        <v>2261.880826568852</v>
+        <v>1160.8</v>
       </c>
       <c r="F61" t="n">
-        <v>32.2</v>
+        <v>35.4</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>29189000000</v>
+        <v>61234000000</v>
       </c>
       <c r="J61" t="n">
-        <v>31318000000</v>
+        <v>318113000000</v>
       </c>
       <c r="K61" t="n">
-        <v>42001000000</v>
+        <v>114136000000</v>
       </c>
       <c r="L61" t="n">
-        <v>194657000000</v>
+        <v>256898000000</v>
       </c>
       <c r="M61" t="n">
-        <v>102508000000</v>
+        <v>493483000000</v>
       </c>
       <c r="N61" t="n">
-        <v>685499040070</v>
+        <v>414232188132</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>エア・ウォーター株式会社</t>
+          <t>あいホールディングス株式会社</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>15</v>
+        <v>23.3</v>
       </c>
       <c r="D62" t="n">
-        <v>2990</v>
+        <v>2996</v>
       </c>
       <c r="E62" t="n">
-        <v>1970</v>
+        <v>2007.754513143541</v>
       </c>
       <c r="F62" t="n">
-        <v>51.8</v>
+        <v>49.2</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>29189000000</v>
+        <v>32012000000</v>
       </c>
       <c r="J62" t="n">
-        <v>31318000000</v>
+        <v>1646000000</v>
       </c>
       <c r="K62" t="n">
-        <v>42001000000</v>
+        <v>3550000000</v>
       </c>
       <c r="L62" t="n">
-        <v>194657000000</v>
+        <v>53765000000</v>
       </c>
       <c r="M62" t="n">
-        <v>102508000000</v>
+        <v>37208000000</v>
       </c>
       <c r="N62" t="n">
-        <v>685499040070</v>
+        <v>159605701276</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>株式会社電通総研</t>
+          <t>エア・ウォーター株式会社</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>9.6</v>
+        <v>15</v>
       </c>
       <c r="D63" t="n">
-        <v>2859</v>
+        <v>2972</v>
       </c>
       <c r="E63" t="n">
-        <v>1910.426979628923</v>
+        <v>2261.880826568852</v>
       </c>
       <c r="F63" t="n">
-        <v>49.7</v>
+        <v>31.4</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3690,322 +3690,322 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>49748000000</v>
+        <v>29189000000</v>
       </c>
       <c r="J63" t="n">
-        <v>524000000</v>
+        <v>31318000000</v>
       </c>
       <c r="K63" t="n">
-        <v>3388000000</v>
+        <v>42001000000</v>
       </c>
       <c r="L63" t="n">
-        <v>65471000000</v>
+        <v>194657000000</v>
       </c>
       <c r="M63" t="n">
-        <v>53660000000</v>
+        <v>102508000000</v>
       </c>
       <c r="N63" t="n">
-        <v>558019968798</v>
+        <v>681372289996</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>わかもと製薬株式会社</t>
+          <t>エア・ウォーター株式会社</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>51.3</v>
+        <v>15</v>
       </c>
       <c r="D64" t="n">
-        <v>290</v>
+        <v>2972</v>
       </c>
       <c r="E64" t="n">
-        <v>290.3401328717133</v>
+        <v>1970</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.1</v>
+        <v>50.9</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3231889000</v>
+        <v>29189000000</v>
       </c>
       <c r="J64" t="n">
-        <v>82947000</v>
+        <v>31318000000</v>
       </c>
       <c r="K64" t="n">
-        <v>1847919000</v>
+        <v>42001000000</v>
       </c>
       <c r="L64" t="n">
-        <v>11480803000</v>
+        <v>194657000000</v>
       </c>
       <c r="M64" t="n">
-        <v>5162755000</v>
+        <v>102508000000</v>
       </c>
       <c r="N64" t="n">
-        <v>10064693310</v>
+        <v>681372289996</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>株式会社豊田自動織機</t>
+          <t>株式会社電通総研</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>6201</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
+          <t>4812</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="D65" t="n">
+        <v>2864</v>
+      </c>
       <c r="E65" t="n">
-        <v>16430.4430802409</v>
-      </c>
-      <c r="F65" t="inlineStr"/>
+        <v>1910.426979628923</v>
+      </c>
+      <c r="F65" t="n">
+        <v>49.9</v>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>281605000000</v>
+        <v>49748000000</v>
       </c>
       <c r="J65" t="n">
-        <v>87540000000</v>
+        <v>524000000</v>
       </c>
       <c r="K65" t="n">
-        <v>730709000000</v>
+        <v>3388000000</v>
       </c>
       <c r="L65" t="n">
-        <v>3246174000000</v>
+        <v>65471000000</v>
       </c>
       <c r="M65" t="n">
-        <v>1099854000000</v>
-      </c>
-      <c r="N65" t="inlineStr"/>
+        <v>53660000000</v>
+      </c>
+      <c r="N65" t="n">
+        <v>558995869408</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>株式会社豊田自動織機</t>
+          <t>わかもと製薬株式会社</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>6201</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
+          <t>4512</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="D66" t="n">
+        <v>297</v>
+      </c>
       <c r="E66" t="n">
-        <v>16430443.10823975</v>
-      </c>
-      <c r="F66" t="inlineStr"/>
+        <v>290.3401328717133</v>
+      </c>
+      <c r="F66" t="n">
+        <v>2.3</v>
+      </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>281605000000</v>
+        <v>3231889000</v>
       </c>
       <c r="J66" t="n">
-        <v>87540000000</v>
+        <v>82947000</v>
       </c>
       <c r="K66" t="n">
-        <v>730709000000</v>
+        <v>1847919000</v>
       </c>
       <c r="L66" t="n">
-        <v>3246174000000</v>
+        <v>11480803000</v>
       </c>
       <c r="M66" t="n">
-        <v>1099854000000</v>
-      </c>
-      <c r="N66" t="inlineStr"/>
+        <v>5162755000</v>
+      </c>
+      <c r="N66" t="n">
+        <v>10307634183</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>大阪製鐵株式会社</t>
+          <t>株式会社豊田自動織機</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5449</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="D67" t="n">
-        <v>2600</v>
-      </c>
+          <t>6201</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="n">
-        <v>1748.071046781136</v>
-      </c>
-      <c r="F67" t="n">
-        <v>48.7</v>
-      </c>
+        <v>16430.4430802409</v>
+      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>62396000000</v>
+        <v>281605000000</v>
       </c>
       <c r="J67" t="n">
-        <v>9241000000</v>
+        <v>87540000000</v>
       </c>
       <c r="K67" t="n">
-        <v>553000000</v>
+        <v>730709000000</v>
       </c>
       <c r="L67" t="n">
-        <v>151028000000</v>
+        <v>3246174000000</v>
       </c>
       <c r="M67" t="n">
-        <v>72190000000</v>
-      </c>
-      <c r="N67" t="n">
-        <v>77788201400</v>
-      </c>
+        <v>1099854000000</v>
+      </c>
+      <c r="N67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>株式会社ディー・エヌ・エー</t>
+          <t>株式会社豊田自動織機</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2432</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>77.59999999999999</v>
-      </c>
-      <c r="D68" t="n">
-        <v>2496</v>
-      </c>
+          <t>6201</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="n">
-        <v>2551.08574256026</v>
-      </c>
-      <c r="F68" t="n">
-        <v>-2.2</v>
-      </c>
+        <v>16430443.10823975</v>
+      </c>
+      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>85363000000</v>
+        <v>281605000000</v>
       </c>
       <c r="J68" t="n">
-        <v>221000000</v>
+        <v>87540000000</v>
       </c>
       <c r="K68" t="n">
-        <v>93552000000</v>
+        <v>730709000000</v>
       </c>
       <c r="L68" t="n">
-        <v>177857000000</v>
+        <v>3246174000000</v>
       </c>
       <c r="M68" t="n">
-        <v>179136000000</v>
-      </c>
-      <c r="N68" t="n">
-        <v>230909055936</v>
-      </c>
+        <v>1099854000000</v>
+      </c>
+      <c r="N68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>株式会社ディー・エヌ・エー</t>
+          <t>大阪製鐵株式会社</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>5449</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>77.59999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="D69" t="n">
-        <v>2496</v>
+        <v>2610</v>
       </c>
       <c r="E69" t="n">
-        <v>2260</v>
+        <v>1748.071046781136</v>
       </c>
       <c r="F69" t="n">
-        <v>10.4</v>
+        <v>49.3</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>85363000000</v>
+        <v>62396000000</v>
       </c>
       <c r="J69" t="n">
-        <v>221000000</v>
+        <v>9241000000</v>
       </c>
       <c r="K69" t="n">
-        <v>93552000000</v>
+        <v>553000000</v>
       </c>
       <c r="L69" t="n">
-        <v>177857000000</v>
+        <v>151028000000</v>
       </c>
       <c r="M69" t="n">
-        <v>179136000000</v>
+        <v>72190000000</v>
       </c>
       <c r="N69" t="n">
-        <v>230909055936</v>
+        <v>78087386790</v>
       </c>
     </row>
     <row r="70">
@@ -4020,16 +4020,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>77.59999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="D70" t="n">
-        <v>2496</v>
+        <v>2552</v>
       </c>
       <c r="E70" t="n">
-        <v>2260</v>
+        <v>2551.08574256026</v>
       </c>
       <c r="F70" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="I70" t="n">
@@ -4057,1543 +4057,1543 @@
         <v>179136000000</v>
       </c>
       <c r="N70" t="n">
-        <v>230909055936</v>
+        <v>236089707832</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>株式会社オリエントコーポレーション</t>
+          <t>株式会社ディー・エヌ・エー</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>8585</t>
+          <t>2432</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>309</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="D71" t="n">
-        <v>849</v>
+        <v>2552</v>
       </c>
       <c r="E71" t="n">
-        <v>798.3805136422309</v>
+        <v>2260</v>
       </c>
       <c r="F71" t="n">
-        <v>6.3</v>
+        <v>12.9</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>408187000000</v>
+        <v>85363000000</v>
       </c>
       <c r="J71" t="n">
-        <v>18930000000</v>
+        <v>221000000</v>
       </c>
       <c r="K71" t="n">
-        <v>21921000000</v>
+        <v>93552000000</v>
       </c>
       <c r="L71" t="n">
-        <v>216837000000</v>
+        <v>177857000000</v>
       </c>
       <c r="M71" t="n">
-        <v>449038000000</v>
+        <v>179136000000</v>
       </c>
       <c r="N71" t="n">
-        <v>145336798536</v>
+        <v>236089707832</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>東ソー株式会社</t>
+          <t>株式会社ディー・エヌ・エー</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>4042</t>
+          <t>2432</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>43.1</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="D72" t="n">
-        <v>2566</v>
+        <v>2552</v>
       </c>
       <c r="E72" t="n">
-        <v>2032.365850102071</v>
+        <v>2260</v>
       </c>
       <c r="F72" t="n">
-        <v>26.3</v>
+        <v>12.9</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>160812000000</v>
+        <v>85363000000</v>
       </c>
       <c r="J72" t="n">
-        <v>109648000000</v>
+        <v>221000000</v>
       </c>
       <c r="K72" t="n">
-        <v>70132000000</v>
+        <v>93552000000</v>
       </c>
       <c r="L72" t="n">
-        <v>759724000000</v>
+        <v>177857000000</v>
       </c>
       <c r="M72" t="n">
-        <v>340592000000</v>
+        <v>179136000000</v>
       </c>
       <c r="N72" t="n">
-        <v>790047141036</v>
+        <v>236089707832</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>株式会社西武ホールディングス</t>
+          <t>株式会社オリエントコーポレーション</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>8585</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>63.4</v>
+        <v>304.7</v>
       </c>
       <c r="D73" t="n">
-        <v>3507</v>
+        <v>861</v>
       </c>
       <c r="E73" t="n">
-        <v>1716.713876475349</v>
+        <v>798.3805136422309</v>
       </c>
       <c r="F73" t="n">
-        <v>104.3</v>
+        <v>7.8</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>87210000000</v>
+        <v>408187000000</v>
       </c>
       <c r="J73" t="n">
-        <v>428181000000</v>
+        <v>18930000000</v>
       </c>
       <c r="K73" t="n">
-        <v>49954000000</v>
+        <v>21921000000</v>
       </c>
       <c r="L73" t="n">
-        <v>387217000000</v>
+        <v>216837000000</v>
       </c>
       <c r="M73" t="n">
-        <v>565345000000</v>
+        <v>449038000000</v>
       </c>
       <c r="N73" t="n">
-        <v>891401502516</v>
+        <v>147391028904</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>東ソー株式会社</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>4042</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="D74" t="n">
+        <v>2541</v>
+      </c>
+      <c r="E74" t="n">
+        <v>2032.365850102071</v>
+      </c>
+      <c r="F74" t="n">
+        <v>25</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>2024-06-04</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>160812000000</v>
+      </c>
+      <c r="J74" t="n">
+        <v>109648000000</v>
+      </c>
+      <c r="K74" t="n">
+        <v>70132000000</v>
+      </c>
+      <c r="L74" t="n">
+        <v>759724000000</v>
+      </c>
+      <c r="M74" t="n">
+        <v>340592000000</v>
+      </c>
+      <c r="N74" t="n">
+        <v>782349877386</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>株式会社西武ホールディングス</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>9024</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3609</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1716.713876475349</v>
+      </c>
+      <c r="F75" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>87210000000</v>
+      </c>
+      <c r="J75" t="n">
+        <v>428181000000</v>
+      </c>
+      <c r="K75" t="n">
+        <v>49954000000</v>
+      </c>
+      <c r="L75" t="n">
+        <v>387217000000</v>
+      </c>
+      <c r="M75" t="n">
+        <v>565345000000</v>
+      </c>
+      <c r="N75" t="n">
+        <v>917327636892</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>株式会社フェローテック
 （旧会社名　株式会社フェローテックホールディングス）</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>6890</t>
         </is>
       </c>
-      <c r="C74" t="n">
+      <c r="C76" t="n">
         <v>33.4</v>
       </c>
-      <c r="D74" t="n">
-        <v>8620</v>
-      </c>
-      <c r="E74" t="n">
+      <c r="D76" t="n">
+        <v>8600</v>
+      </c>
+      <c r="E76" t="n">
         <v>4037.502552255647</v>
       </c>
-      <c r="F74" t="n">
-        <v>113.5</v>
-      </c>
-      <c r="G74" t="inlineStr">
+      <c r="F76" t="n">
+        <v>113</v>
+      </c>
+      <c r="G76" t="inlineStr">
         <is>
           <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="I74" t="n">
+      <c r="I76" t="n">
         <v>52579000000</v>
       </c>
-      <c r="J74" t="n">
+      <c r="J76" t="n">
         <v>90505000000</v>
       </c>
-      <c r="K74" t="n">
+      <c r="K76" t="n">
         <v>11654000000</v>
       </c>
-      <c r="L74" t="n">
+      <c r="L76" t="n">
         <v>160957000000</v>
       </c>
-      <c r="M74" t="n">
+      <c r="M76" t="n">
         <v>154738000000</v>
       </c>
-      <c r="N74" t="n">
-        <v>463788437060</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="N76" t="n">
+        <v>462712361800</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>株式会社フェローテック
 （旧会社名　株式会社フェローテックホールディングス）</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>6890</t>
         </is>
       </c>
-      <c r="C75" t="n">
+      <c r="C77" t="n">
         <v>33.4</v>
       </c>
-      <c r="D75" t="n">
-        <v>8620</v>
-      </c>
-      <c r="E75" t="n">
+      <c r="D77" t="n">
+        <v>8600</v>
+      </c>
+      <c r="E77" t="n">
         <v>3950.736048458928</v>
       </c>
-      <c r="F75" t="n">
-        <v>118.2</v>
-      </c>
-      <c r="G75" t="inlineStr">
+      <c r="F77" t="n">
+        <v>117.7</v>
+      </c>
+      <c r="G77" t="inlineStr">
         <is>
           <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="I75" t="n">
+      <c r="I77" t="n">
         <v>52579000000</v>
       </c>
-      <c r="J75" t="n">
+      <c r="J77" t="n">
         <v>90505000000</v>
       </c>
-      <c r="K75" t="n">
+      <c r="K77" t="n">
         <v>11654000000</v>
       </c>
-      <c r="L75" t="n">
+      <c r="L77" t="n">
         <v>160957000000</v>
       </c>
-      <c r="M75" t="n">
+      <c r="M77" t="n">
         <v>154738000000</v>
       </c>
-      <c r="N75" t="n">
-        <v>463788437060</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="N77" t="n">
+        <v>462712361800</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>株式会社フェローテック
 （旧会社名　株式会社フェローテックホールディングス）</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>6890</t>
         </is>
       </c>
-      <c r="C76" t="n">
+      <c r="C78" t="n">
         <v>33.4</v>
       </c>
-      <c r="D76" t="n">
-        <v>8620</v>
-      </c>
-      <c r="E76" t="n">
+      <c r="D78" t="n">
+        <v>8600</v>
+      </c>
+      <c r="E78" t="n">
         <v>2030</v>
       </c>
-      <c r="F76" t="n">
-        <v>324.6</v>
-      </c>
-      <c r="G76" t="inlineStr">
+      <c r="F78" t="n">
+        <v>323.6</v>
+      </c>
+      <c r="G78" t="inlineStr">
         <is>
           <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>2025-10-22</t>
         </is>
       </c>
-      <c r="I76" t="n">
+      <c r="I78" t="n">
         <v>52579000000</v>
       </c>
-      <c r="J76" t="n">
+      <c r="J78" t="n">
         <v>90505000000</v>
       </c>
-      <c r="K76" t="n">
+      <c r="K78" t="n">
         <v>11654000000</v>
       </c>
-      <c r="L76" t="n">
+      <c r="L78" t="n">
         <v>160957000000</v>
       </c>
-      <c r="M76" t="n">
+      <c r="M78" t="n">
         <v>154738000000</v>
       </c>
-      <c r="N76" t="n">
-        <v>463788437060</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="N78" t="n">
+        <v>462712361800</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>株式会社フェローテック
 （旧会社名　株式会社フェローテックホールディングス）</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>6890</t>
         </is>
       </c>
-      <c r="C77" t="n">
+      <c r="C79" t="n">
         <v>33.4</v>
       </c>
-      <c r="D77" t="n">
-        <v>8620</v>
-      </c>
-      <c r="E77" t="n">
+      <c r="D79" t="n">
+        <v>8600</v>
+      </c>
+      <c r="E79" t="n">
         <v>2387</v>
       </c>
-      <c r="F77" t="n">
-        <v>261.1</v>
-      </c>
-      <c r="G77" t="inlineStr">
+      <c r="F79" t="n">
+        <v>260.3</v>
+      </c>
+      <c r="G79" t="inlineStr">
         <is>
           <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>2025-03-07</t>
         </is>
       </c>
-      <c r="I77" t="n">
+      <c r="I79" t="n">
         <v>52579000000</v>
       </c>
-      <c r="J77" t="n">
+      <c r="J79" t="n">
         <v>90505000000</v>
       </c>
-      <c r="K77" t="n">
+      <c r="K79" t="n">
         <v>11654000000</v>
       </c>
-      <c r="L77" t="n">
+      <c r="L79" t="n">
         <v>160957000000</v>
       </c>
-      <c r="M77" t="n">
+      <c r="M79" t="n">
         <v>154738000000</v>
       </c>
-      <c r="N77" t="n">
-        <v>463788437060</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>アツギ株式会社</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>3529</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>76.3</v>
-      </c>
-      <c r="D78" t="n">
-        <v>1016</v>
-      </c>
-      <c r="E78" t="n">
-        <v>668.9358717434869</v>
-      </c>
-      <c r="F78" t="n">
-        <v>51.9</v>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="I78" t="n">
-        <v>5500000000</v>
-      </c>
-      <c r="J78" t="n">
-        <v>3208000000</v>
-      </c>
-      <c r="K78" t="n">
-        <v>3702000000</v>
-      </c>
-      <c r="L78" t="n">
-        <v>32145000000</v>
-      </c>
-      <c r="M78" t="n">
-        <v>12410000000</v>
-      </c>
-      <c r="N78" t="n">
-        <v>16270230096</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>日本特殊塗料株式会社</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>4619</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>72.7</v>
-      </c>
-      <c r="D79" t="n">
-        <v>2615</v>
-      </c>
-      <c r="E79" t="n">
-        <v>1190</v>
-      </c>
-      <c r="F79" t="n">
-        <v>119.7</v>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="I79" t="n">
-        <v>8931000000</v>
-      </c>
-      <c r="J79" t="n">
-        <v>9514000000</v>
-      </c>
-      <c r="K79" t="n">
-        <v>22055000000</v>
-      </c>
-      <c r="L79" t="n">
-        <v>49725000000</v>
-      </c>
-      <c r="M79" t="n">
-        <v>40500000000</v>
-      </c>
       <c r="N79" t="n">
-        <v>55678179905</v>
+        <v>462712361800</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>株式会社エクセディ</t>
+          <t>アツギ株式会社</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>7278</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>19.3</v>
+        <v>75.5</v>
       </c>
       <c r="D80" t="n">
-        <v>5810</v>
+        <v>1027</v>
       </c>
       <c r="E80" t="n">
-        <v>2617.980935875217</v>
+        <v>668.9358717434869</v>
       </c>
       <c r="F80" t="n">
-        <v>121.9</v>
+        <v>53.5</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>30019000000</v>
+        <v>5500000000</v>
       </c>
       <c r="J80" t="n">
-        <v>6792000000</v>
+        <v>3208000000</v>
       </c>
       <c r="K80" t="n">
-        <v>3427000000</v>
+        <v>3702000000</v>
       </c>
       <c r="L80" t="n">
-        <v>119460000000</v>
+        <v>32145000000</v>
       </c>
       <c r="M80" t="n">
-        <v>40238000000</v>
+        <v>12410000000</v>
       </c>
       <c r="N80" t="n">
-        <v>207960618460</v>
+        <v>16446384162</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>株式会社Ａ＆Ｄホロンホールディングス</t>
+          <t>日本特殊塗料株式会社</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>7745</t>
+          <t>4619</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>19.9</v>
+        <v>72.5</v>
       </c>
       <c r="D81" t="n">
-        <v>2828</v>
+        <v>2625</v>
       </c>
       <c r="E81" t="n">
-        <v>2084.177692465894</v>
+        <v>1190</v>
       </c>
       <c r="F81" t="n">
-        <v>35.7</v>
+        <v>120.6</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>11012000000</v>
+        <v>8931000000</v>
       </c>
       <c r="J81" t="n">
-        <v>4106000000</v>
+        <v>9514000000</v>
       </c>
       <c r="K81" t="n">
-        <v>315000000</v>
+        <v>22055000000</v>
       </c>
       <c r="L81" t="n">
-        <v>27041000000</v>
+        <v>49725000000</v>
       </c>
       <c r="M81" t="n">
-        <v>15433000000</v>
+        <v>40500000000</v>
       </c>
       <c r="N81" t="n">
-        <v>77451343788</v>
+        <v>55891098375</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>株式会社セプテーニ・ホールディングス</t>
+          <t>株式会社エクセディ</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>4293</t>
+          <t>7278</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>13.3</v>
+        <v>19.1</v>
       </c>
       <c r="D82" t="n">
-        <v>506</v>
+        <v>5900</v>
       </c>
       <c r="E82" t="n">
-        <v>448.6811097117532</v>
+        <v>2617.980935875217</v>
       </c>
       <c r="F82" t="n">
-        <v>12.8</v>
+        <v>125.4</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>12184507000</v>
+        <v>30019000000</v>
       </c>
       <c r="J82" t="n">
-        <v>168073000</v>
+        <v>6792000000</v>
       </c>
       <c r="K82" t="n">
-        <v>1600720000</v>
+        <v>3427000000</v>
       </c>
       <c r="L82" t="n">
-        <v>11861578000</v>
+        <v>119460000000</v>
       </c>
       <c r="M82" t="n">
-        <v>13953300000</v>
+        <v>40238000000</v>
       </c>
       <c r="N82" t="n">
-        <v>104967225154</v>
+        <v>211182039400</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>株式会社シンクロ・フード</t>
+          <t>株式会社Ａ＆Ｄホロンホールディングス</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>7745</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>34.2</v>
+        <v>20.1</v>
       </c>
       <c r="D83" t="n">
-        <v>324</v>
+        <v>2801</v>
       </c>
       <c r="E83" t="n">
-        <v>421.6950726175476</v>
+        <v>2084.177692465894</v>
       </c>
       <c r="F83" t="n">
-        <v>-23.2</v>
+        <v>34.4</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3037851000</v>
+        <v>11012000000</v>
       </c>
       <c r="J83" t="n">
-        <v>56852000</v>
+        <v>4106000000</v>
       </c>
       <c r="K83" t="n">
-        <v>14952000</v>
+        <v>315000000</v>
       </c>
       <c r="L83" t="n">
-        <v>2871237000</v>
+        <v>27041000000</v>
       </c>
       <c r="M83" t="n">
-        <v>3109655000</v>
+        <v>15433000000</v>
       </c>
       <c r="N83" t="n">
-        <v>9085798512</v>
+        <v>76711886121</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>科研製薬株式会社</t>
+          <t>株式会社セプテーニ・ホールディングス</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>4293</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>73.2</v>
+        <v>13.1</v>
       </c>
       <c r="D84" t="n">
-        <v>3830</v>
+        <v>512</v>
       </c>
       <c r="E84" t="n">
-        <v>3530</v>
+        <v>448.6811097117532</v>
       </c>
       <c r="F84" t="n">
-        <v>8.5</v>
+        <v>14.1</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>74625000000</v>
+        <v>12184507000</v>
       </c>
       <c r="J84" t="n">
-        <v>15530000000</v>
+        <v>168073000</v>
       </c>
       <c r="K84" t="n">
-        <v>15992000000</v>
+        <v>1600720000</v>
       </c>
       <c r="L84" t="n">
-        <v>138325000000</v>
+        <v>11861578000</v>
       </c>
       <c r="M84" t="n">
-        <v>106147000000</v>
+        <v>13953300000</v>
       </c>
       <c r="N84" t="n">
-        <v>145035646450</v>
+        <v>106211895808</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>市光工業株式会社</t>
+          <t>株式会社シンクロ・フード</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>7244</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>35.8</v>
+        <v>33.6</v>
       </c>
       <c r="D85" t="n">
-        <v>554</v>
+        <v>330</v>
       </c>
       <c r="E85" t="n">
-        <v>549.4799823005444</v>
+        <v>421.6950726175476</v>
       </c>
       <c r="F85" t="n">
-        <v>0.8</v>
+        <v>-21.7</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>5720000000</v>
+        <v>3037851000</v>
       </c>
       <c r="J85" t="n">
-        <v>9921000000</v>
+        <v>56852000</v>
       </c>
       <c r="K85" t="n">
-        <v>3474000000</v>
+        <v>14952000</v>
       </c>
       <c r="L85" t="n">
-        <v>49523000000</v>
+        <v>2871237000</v>
       </c>
       <c r="M85" t="n">
-        <v>19115000000</v>
+        <v>3109655000</v>
       </c>
       <c r="N85" t="n">
-        <v>53352643140</v>
+        <v>9254054040</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>トーセイ株式会社</t>
+          <t>科研製薬株式会社</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>4521</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>47</v>
+        <v>72.2</v>
       </c>
       <c r="D86" t="n">
-        <v>1672</v>
+        <v>3885</v>
       </c>
       <c r="E86" t="n">
-        <v>1752.426893379333</v>
+        <v>3530</v>
       </c>
       <c r="F86" t="n">
-        <v>-4.6</v>
+        <v>10.1</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>20753937000</v>
+        <v>74625000000</v>
       </c>
       <c r="J86" t="n">
-        <v>46868512000</v>
+        <v>15530000000</v>
       </c>
       <c r="K86" t="n">
-        <v>8610046000</v>
+        <v>15992000000</v>
       </c>
       <c r="L86" t="n">
-        <v>59467346000</v>
+        <v>138325000000</v>
       </c>
       <c r="M86" t="n">
-        <v>76232495000</v>
+        <v>106147000000</v>
       </c>
       <c r="N86" t="n">
-        <v>162194199200</v>
+        <v>147118403775</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>トーセイ株式会社</t>
+          <t>市光工業株式会社</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>47</v>
+        <v>35.8</v>
       </c>
       <c r="D87" t="n">
-        <v>1672</v>
+        <v>554</v>
       </c>
       <c r="E87" t="n">
-        <v>1576.721867844292</v>
+        <v>549.4799823005444</v>
       </c>
       <c r="F87" t="n">
-        <v>6</v>
+        <v>0.8</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>20753937000</v>
+        <v>5720000000</v>
       </c>
       <c r="J87" t="n">
-        <v>46868512000</v>
+        <v>9921000000</v>
       </c>
       <c r="K87" t="n">
-        <v>8610046000</v>
+        <v>3474000000</v>
       </c>
       <c r="L87" t="n">
-        <v>59467346000</v>
+        <v>49523000000</v>
       </c>
       <c r="M87" t="n">
-        <v>76232495000</v>
+        <v>19115000000</v>
       </c>
       <c r="N87" t="n">
-        <v>162194199200</v>
+        <v>53352643140</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>株式会社髙島屋</t>
+          <t>トーセイ株式会社</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>65.40000000000001</v>
+        <v>46.7</v>
       </c>
       <c r="D88" t="n">
-        <v>2099.5</v>
+        <v>1683</v>
       </c>
       <c r="E88" t="n">
-        <v>1101.400153022188</v>
+        <v>1752.426893379333</v>
       </c>
       <c r="F88" t="n">
-        <v>90.59999999999999</v>
+        <v>-4</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>88996000000</v>
+        <v>20753937000</v>
       </c>
       <c r="J88" t="n">
-        <v>193090000000</v>
+        <v>46868512000</v>
       </c>
       <c r="K88" t="n">
-        <v>119967000000</v>
+        <v>8610046000</v>
       </c>
       <c r="L88" t="n">
-        <v>420489000000</v>
+        <v>59467346000</v>
       </c>
       <c r="M88" t="n">
-        <v>402053000000</v>
+        <v>76232495000</v>
       </c>
       <c r="N88" t="n">
-        <v>615183732800</v>
+        <v>163261266300</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>株式会社髙島屋</t>
+          <t>トーセイ株式会社</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>65.40000000000001</v>
+        <v>46.7</v>
       </c>
       <c r="D89" t="n">
-        <v>2099.5</v>
+        <v>1683</v>
       </c>
       <c r="E89" t="n">
-        <v>1101.400153022188</v>
+        <v>1576.721867844292</v>
       </c>
       <c r="F89" t="n">
-        <v>90.59999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>88996000000</v>
+        <v>20753937000</v>
       </c>
       <c r="J89" t="n">
-        <v>193090000000</v>
+        <v>46868512000</v>
       </c>
       <c r="K89" t="n">
-        <v>119967000000</v>
+        <v>8610046000</v>
       </c>
       <c r="L89" t="n">
-        <v>420489000000</v>
+        <v>59467346000</v>
       </c>
       <c r="M89" t="n">
-        <v>402053000000</v>
+        <v>76232495000</v>
       </c>
       <c r="N89" t="n">
-        <v>615183732800</v>
+        <v>163261266300</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>三井倉庫ホールディングス株式会社</t>
+          <t>株式会社髙島屋</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>9302</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>45.6</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D90" t="n">
-        <v>3295</v>
+        <v>2098</v>
       </c>
       <c r="E90" t="n">
-        <v>1492.806001579363</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="F90" t="n">
-        <v>120.7</v>
+        <v>90.5</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>22822000000</v>
+        <v>88996000000</v>
       </c>
       <c r="J90" t="n">
-        <v>72331000000</v>
+        <v>193090000000</v>
       </c>
       <c r="K90" t="n">
-        <v>17148000000</v>
+        <v>119967000000</v>
       </c>
       <c r="L90" t="n">
-        <v>88631000000</v>
+        <v>420489000000</v>
       </c>
       <c r="M90" t="n">
-        <v>112301000000</v>
+        <v>402053000000</v>
       </c>
       <c r="N90" t="n">
-        <v>246480119075</v>
+        <v>614744211200</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>京阪神ビルディング株式会社</t>
+          <t>株式会社髙島屋</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>8818</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>81.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D91" t="n">
-        <v>1118</v>
+        <v>2098</v>
       </c>
       <c r="E91" t="n">
-        <v>1341.977644710579</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="F91" t="n">
-        <v>-16.7</v>
+        <v>90.5</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>9876000000</v>
+        <v>88996000000</v>
       </c>
       <c r="J91" t="n">
-        <v>54379000000</v>
+        <v>193090000000</v>
       </c>
       <c r="K91" t="n">
-        <v>22399000000</v>
+        <v>119967000000</v>
       </c>
       <c r="L91" t="n">
-        <v>70510000000</v>
+        <v>420489000000</v>
       </c>
       <c r="M91" t="n">
-        <v>86654000000</v>
+        <v>402053000000</v>
       </c>
       <c r="N91" t="n">
-        <v>106662412116</v>
+        <v>614744211200</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>株式会社メルカリ</t>
+          <t>三井倉庫ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>9302</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>27.8</v>
+        <v>44.9</v>
       </c>
       <c r="D92" t="n">
-        <v>3826</v>
+        <v>3347</v>
       </c>
       <c r="E92" t="n">
-        <v>2006.059650428343</v>
+        <v>1492.806001579363</v>
       </c>
       <c r="F92" t="n">
-        <v>90.7</v>
+        <v>124.2</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>171463000000</v>
+        <v>22822000000</v>
       </c>
       <c r="J92" t="n">
-        <v>434000000</v>
+        <v>72331000000</v>
       </c>
       <c r="K92" t="n">
-        <v>1543000000</v>
+        <v>17148000000</v>
       </c>
       <c r="L92" t="n">
-        <v>40013000000</v>
+        <v>88631000000</v>
       </c>
       <c r="M92" t="n">
-        <v>173440000000</v>
+        <v>112301000000</v>
       </c>
       <c r="N92" t="n">
-        <v>624329040642</v>
+        <v>250369941895</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>サッポロホールディングス株式会社</t>
+          <t>京阪神ビルディング株式会社</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2501</t>
+          <t>8818</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>81.8</v>
       </c>
       <c r="D93" t="n">
-        <v>1838</v>
+        <v>1110</v>
       </c>
       <c r="E93" t="n">
-        <v>2697.360927565142</v>
+        <v>1341.977644710579</v>
       </c>
       <c r="F93" t="n">
-        <v>-31.9</v>
+        <v>-17.3</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2925000000</v>
+        <v>9876000000</v>
       </c>
       <c r="J93" t="n">
-        <v>23000000</v>
+        <v>54379000000</v>
       </c>
       <c r="K93" t="n">
-        <v>4391000000</v>
+        <v>22399000000</v>
       </c>
       <c r="L93" t="n">
-        <v>142395000000</v>
+        <v>70510000000</v>
       </c>
       <c r="M93" t="n">
-        <v>7339000000</v>
+        <v>86654000000</v>
       </c>
       <c r="N93" t="n">
-        <v>716770355620</v>
+        <v>105899174820</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>株式会社クレハ</t>
+          <t>株式会社メルカリ</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>18.1</v>
+        <v>27.4</v>
       </c>
       <c r="D94" t="n">
-        <v>4325</v>
+        <v>3886</v>
       </c>
       <c r="E94" t="n">
-        <v>7960</v>
+        <v>2006.059650428343</v>
       </c>
       <c r="F94" t="n">
-        <v>-45.7</v>
+        <v>93.7</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>5294000000</v>
+        <v>171463000000</v>
       </c>
       <c r="J94" t="n">
-        <v>5963000000</v>
+        <v>434000000</v>
       </c>
       <c r="K94" t="n">
-        <v>18608000000</v>
+        <v>1543000000</v>
       </c>
       <c r="L94" t="n">
-        <v>155874000000</v>
+        <v>40013000000</v>
       </c>
       <c r="M94" t="n">
-        <v>29865000000</v>
+        <v>173440000000</v>
       </c>
       <c r="N94" t="n">
-        <v>165306058550</v>
+        <v>634119877662</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>コムシスホールディングス株式会社</t>
+          <t>サッポロホールディングス株式会社</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>5372</v>
+        <v>1865</v>
       </c>
       <c r="E95" t="n">
-        <v>3735.709461270437</v>
+        <v>2697.360927565142</v>
       </c>
       <c r="F95" t="n">
-        <v>43.8</v>
+        <v>-30.9</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>34033000000</v>
+        <v>2925000000</v>
       </c>
       <c r="J95" t="n">
-        <v>45394000000</v>
+        <v>23000000</v>
       </c>
       <c r="K95" t="n">
-        <v>31261000000</v>
+        <v>4391000000</v>
       </c>
       <c r="L95" t="n">
-        <v>343489000000</v>
+        <v>142395000000</v>
       </c>
       <c r="M95" t="n">
-        <v>110688000000</v>
+        <v>7339000000</v>
       </c>
       <c r="N95" t="n">
-        <v>616620351732</v>
+        <v>727299626350</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>サクサ株式会社</t>
+          <t>株式会社クレハ</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>6675</t>
+          <t>4023</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>30.6</v>
+        <v>17.9</v>
       </c>
       <c r="D96" t="n">
-        <v>2102</v>
+        <v>4365</v>
       </c>
       <c r="E96" t="n">
-        <v>5463.67048346056</v>
+        <v>7960</v>
       </c>
       <c r="F96" t="n">
-        <v>-61.5</v>
+        <v>-45.2</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>6993000000</v>
+        <v>5294000000</v>
       </c>
       <c r="J96" t="n">
-        <v>1323000000</v>
+        <v>5963000000</v>
       </c>
       <c r="K96" t="n">
-        <v>2933000000</v>
+        <v>18608000000</v>
       </c>
       <c r="L96" t="n">
-        <v>23497000000</v>
+        <v>155874000000</v>
       </c>
       <c r="M96" t="n">
-        <v>11249000000</v>
+        <v>29865000000</v>
       </c>
       <c r="N96" t="n">
-        <v>36767322180</v>
+        <v>166834900710</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>株式会社ヨドコウ（旧会社名：株式会社淀川製鋼所）</t>
+          <t>コムシスホールディングス株式会社</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>5451</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>25.8</v>
+        <v>17.7</v>
       </c>
       <c r="D97" t="n">
-        <v>1414</v>
+        <v>5441</v>
       </c>
       <c r="E97" t="n">
-        <v>3234.727863989046</v>
+        <v>3735.709461270437</v>
       </c>
       <c r="F97" t="n">
-        <v>-56.3</v>
+        <v>45.6</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>30961000000</v>
+        <v>34033000000</v>
       </c>
       <c r="J97" t="n">
-        <v>18259000000</v>
+        <v>45394000000</v>
       </c>
       <c r="K97" t="n">
-        <v>2995000000</v>
+        <v>31261000000</v>
       </c>
       <c r="L97" t="n">
-        <v>191937000000</v>
+        <v>343489000000</v>
       </c>
       <c r="M97" t="n">
-        <v>52215000000</v>
+        <v>110688000000</v>
       </c>
       <c r="N97" t="n">
-        <v>202554849560</v>
+        <v>624540456771</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>愛知製鋼株式会社</t>
+          <t>サクサ株式会社</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>6675</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>35.2</v>
+        <v>30</v>
       </c>
       <c r="D98" t="n">
-        <v>3115</v>
+        <v>2145</v>
       </c>
       <c r="E98" t="n">
-        <v>3155.301177013616</v>
+        <v>5463.67048346056</v>
       </c>
       <c r="F98" t="n">
-        <v>-1.3</v>
+        <v>-60.7</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>32866000000</v>
+        <v>6993000000</v>
       </c>
       <c r="J98" t="n">
-        <v>11000000000</v>
+        <v>1323000000</v>
       </c>
       <c r="K98" t="n">
-        <v>26614000000</v>
+        <v>2933000000</v>
       </c>
       <c r="L98" t="n">
-        <v>186904000000</v>
+        <v>23497000000</v>
       </c>
       <c r="M98" t="n">
-        <v>70480000000</v>
+        <v>11249000000</v>
       </c>
       <c r="N98" t="n">
-        <v>200128775770</v>
+        <v>37519460550</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>株式会社インターネットイニシアティブ</t>
+          <t>愛知製鋼株式会社</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>3774</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>5.6</v>
+        <v>35.1</v>
       </c>
       <c r="D99" t="n">
-        <v>3340</v>
+        <v>3125</v>
       </c>
       <c r="E99" t="n">
-        <v>2655.311711736394</v>
+        <v>3155.301177013616</v>
       </c>
       <c r="F99" t="n">
-        <v>25.8</v>
+        <v>-1</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>16367000000</v>
+        <v>32866000000</v>
       </c>
       <c r="J99" t="n">
-        <v>1522000000</v>
+        <v>11000000000</v>
       </c>
       <c r="K99" t="n">
-        <v>15226000000</v>
+        <v>26614000000</v>
       </c>
       <c r="L99" t="n">
-        <v>87924000000</v>
+        <v>186904000000</v>
       </c>
       <c r="M99" t="n">
-        <v>33115000000</v>
+        <v>70480000000</v>
       </c>
       <c r="N99" t="n">
-        <v>592282216700</v>
+        <v>200771243750</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>コクヨ株式会社</t>
+          <t>株式会社インターネットイニシアティブ</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>7984</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>40.7</v>
+        <v>5.4</v>
       </c>
       <c r="D100" t="n">
-        <v>905.7999877929688</v>
+        <v>3448</v>
       </c>
       <c r="E100" t="n">
-        <v>2157.626835069302</v>
+        <v>2655.311711736394</v>
       </c>
       <c r="F100" t="n">
-        <v>-58</v>
+        <v>29.9</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -5602,182 +5602,182 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>100575000000</v>
+        <v>16367000000</v>
       </c>
       <c r="J100" t="n">
-        <v>22282000000</v>
+        <v>1522000000</v>
       </c>
       <c r="K100" t="n">
-        <v>30106000000</v>
+        <v>15226000000</v>
       </c>
       <c r="L100" t="n">
-        <v>230105000000</v>
+        <v>87924000000</v>
       </c>
       <c r="M100" t="n">
-        <v>152963000000</v>
+        <v>33115000000</v>
       </c>
       <c r="N100" t="n">
-        <v>375399811253</v>
+        <v>611433857240</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>三菱製紙株式会社</t>
+          <t>コクヨ株式会社</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>7984</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>98.2</v>
+        <v>41</v>
       </c>
       <c r="D101" t="n">
-        <v>1169</v>
+        <v>899.2999877929688</v>
       </c>
       <c r="E101" t="n">
-        <v>810</v>
+        <v>2157.626835069302</v>
       </c>
       <c r="F101" t="n">
-        <v>44.3</v>
+        <v>-58.3</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>9047000000</v>
+        <v>100575000000</v>
       </c>
       <c r="J101" t="n">
-        <v>16443000000</v>
+        <v>22282000000</v>
       </c>
       <c r="K101" t="n">
-        <v>24813000000</v>
+        <v>30106000000</v>
       </c>
       <c r="L101" t="n">
-        <v>69613000000</v>
+        <v>230105000000</v>
       </c>
       <c r="M101" t="n">
-        <v>50303000000</v>
+        <v>152963000000</v>
       </c>
       <c r="N101" t="n">
-        <v>51211761251</v>
+        <v>372705950791</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>株式会社プラスアルファ・コンサルティング</t>
+          <t>三菱製紙株式会社</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>4071</t>
+          <t>3864</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>10</v>
+        <v>97.2</v>
       </c>
       <c r="D102" t="n">
-        <v>2028</v>
+        <v>1181</v>
       </c>
       <c r="E102" t="n">
-        <v>2300.974351689521</v>
+        <v>810</v>
       </c>
       <c r="F102" t="n">
-        <v>-11.9</v>
+        <v>45.8</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>8278003000</v>
+        <v>9047000000</v>
       </c>
       <c r="J102" t="n">
-        <v>271170000</v>
+        <v>16443000000</v>
       </c>
       <c r="K102" t="n">
-        <v>0</v>
+        <v>24813000000</v>
       </c>
       <c r="L102" t="n">
-        <v>9445733000</v>
+        <v>69613000000</v>
       </c>
       <c r="M102" t="n">
-        <v>8549173000</v>
+        <v>50303000000</v>
       </c>
       <c r="N102" t="n">
-        <v>85085855400</v>
+        <v>51737459399</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>東亜道路工業株式会社</t>
+          <t>株式会社プラスアルファ・コンサルティング</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>4071</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>40.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D103" t="n">
-        <v>1585</v>
+        <v>2106</v>
       </c>
       <c r="E103" t="n">
-        <v>1180.253227905114</v>
+        <v>2300.974351689521</v>
       </c>
       <c r="F103" t="n">
-        <v>34.3</v>
+        <v>-8.5</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>11649000000</v>
+        <v>8278003000</v>
       </c>
       <c r="J103" t="n">
-        <v>13793000000</v>
+        <v>271170000</v>
       </c>
       <c r="K103" t="n">
-        <v>4087000000</v>
+        <v>0</v>
       </c>
       <c r="L103" t="n">
-        <v>50605000000</v>
+        <v>9445733000</v>
       </c>
       <c r="M103" t="n">
-        <v>29529000000</v>
+        <v>8549173000</v>
       </c>
       <c r="N103" t="n">
-        <v>73239026980</v>
+        <v>88358388300</v>
       </c>
     </row>
     <row r="104">
@@ -5792,16 +5792,16 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>40.3</v>
+        <v>39.8</v>
       </c>
       <c r="D104" t="n">
-        <v>1585</v>
+        <v>1606</v>
       </c>
       <c r="E104" t="n">
-        <v>1180.31326635551</v>
+        <v>1180.253227905114</v>
       </c>
       <c r="F104" t="n">
-        <v>34.3</v>
+        <v>36.1</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="I104" t="n">
@@ -5829,7 +5829,7 @@
         <v>29529000000</v>
       </c>
       <c r="N104" t="n">
-        <v>73239026980</v>
+        <v>74209386328</v>
       </c>
     </row>
     <row r="105">
@@ -5844,16 +5844,16 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>40.3</v>
+        <v>39.8</v>
       </c>
       <c r="D105" t="n">
-        <v>1585</v>
+        <v>1606</v>
       </c>
       <c r="E105" t="n">
-        <v>1180.406015389293</v>
+        <v>1180.31326635551</v>
       </c>
       <c r="F105" t="n">
-        <v>34.3</v>
+        <v>36.1</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="I105" t="n">
@@ -5881,7 +5881,7 @@
         <v>29529000000</v>
       </c>
       <c r="N105" t="n">
-        <v>73239026980</v>
+        <v>74209386328</v>
       </c>
     </row>
     <row r="106">
@@ -5896,16 +5896,16 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>40.3</v>
+        <v>39.8</v>
       </c>
       <c r="D106" t="n">
-        <v>1585</v>
+        <v>1606</v>
       </c>
       <c r="E106" t="n">
-        <v>1180.420176850555</v>
+        <v>1180.406015389293</v>
       </c>
       <c r="F106" t="n">
-        <v>34.3</v>
+        <v>36.1</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="I106" t="n">
@@ -5933,7 +5933,7 @@
         <v>29529000000</v>
       </c>
       <c r="N106" t="n">
-        <v>73239026980</v>
+        <v>74209386328</v>
       </c>
     </row>
     <row r="107">
@@ -5948,16 +5948,16 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>40.3</v>
+        <v>39.8</v>
       </c>
       <c r="D107" t="n">
-        <v>1585</v>
+        <v>1606</v>
       </c>
       <c r="E107" t="n">
-        <v>1180.431728045326</v>
+        <v>1180.420176850555</v>
       </c>
       <c r="F107" t="n">
-        <v>34.3</v>
+        <v>36.1</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="I107" t="n">
@@ -5985,7 +5985,7 @@
         <v>29529000000</v>
       </c>
       <c r="N107" t="n">
-        <v>73239026980</v>
+        <v>74209386328</v>
       </c>
     </row>
     <row r="108">
@@ -6000,16 +6000,16 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>40.3</v>
+        <v>39.8</v>
       </c>
       <c r="D108" t="n">
-        <v>1585</v>
+        <v>1606</v>
       </c>
       <c r="E108" t="n">
-        <v>1180.442269658324</v>
+        <v>1180.431728045326</v>
       </c>
       <c r="F108" t="n">
-        <v>34.3</v>
+        <v>36.1</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="I108" t="n">
@@ -6037,7 +6037,7 @@
         <v>29529000000</v>
       </c>
       <c r="N108" t="n">
-        <v>73239026980</v>
+        <v>74209386328</v>
       </c>
     </row>
     <row r="109">
@@ -6052,16 +6052,16 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>40.3</v>
+        <v>39.8</v>
       </c>
       <c r="D109" t="n">
-        <v>1585</v>
+        <v>1606</v>
       </c>
       <c r="E109" t="n">
-        <v>1180.450912709519</v>
+        <v>1180.442269658324</v>
       </c>
       <c r="F109" t="n">
-        <v>34.3</v>
+        <v>36.1</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="I109" t="n">
@@ -6089,7 +6089,7 @@
         <v>29529000000</v>
       </c>
       <c r="N109" t="n">
-        <v>73239026980</v>
+        <v>74209386328</v>
       </c>
     </row>
     <row r="110">
@@ -6104,16 +6104,16 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>40.3</v>
+        <v>39.8</v>
       </c>
       <c r="D110" t="n">
-        <v>1585</v>
+        <v>1606</v>
       </c>
       <c r="E110" t="n">
-        <v>1180.45745232471</v>
+        <v>1180.450912709519</v>
       </c>
       <c r="F110" t="n">
-        <v>34.3</v>
+        <v>36</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="I110" t="n">
@@ -6141,7 +6141,7 @@
         <v>29529000000</v>
       </c>
       <c r="N110" t="n">
-        <v>73239026980</v>
+        <v>74209386328</v>
       </c>
     </row>
     <row r="111">
@@ -6156,16 +6156,16 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>40.3</v>
+        <v>39.8</v>
       </c>
       <c r="D111" t="n">
-        <v>1585</v>
+        <v>1606</v>
       </c>
       <c r="E111" t="n">
-        <v>1180.463123164206</v>
+        <v>1180.45745232471</v>
       </c>
       <c r="F111" t="n">
-        <v>34.3</v>
+        <v>36</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="I111" t="n">
@@ -6193,7 +6193,7 @@
         <v>29529000000</v>
       </c>
       <c r="N111" t="n">
-        <v>73239026980</v>
+        <v>74209386328</v>
       </c>
     </row>
     <row r="112">
@@ -6208,16 +6208,16 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>40.3</v>
+        <v>39.8</v>
       </c>
       <c r="D112" t="n">
-        <v>1585</v>
+        <v>1606</v>
       </c>
       <c r="E112" t="n">
-        <v>1170.279952698077</v>
+        <v>1180.463123164206</v>
       </c>
       <c r="F112" t="n">
-        <v>35.4</v>
+        <v>36</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="I112" t="n">
@@ -6245,7 +6245,7 @@
         <v>29529000000</v>
       </c>
       <c r="N112" t="n">
-        <v>73239026980</v>
+        <v>74209386328</v>
       </c>
     </row>
     <row r="113">
@@ -6260,16 +6260,16 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>40.3</v>
+        <v>39.8</v>
       </c>
       <c r="D113" t="n">
-        <v>1585</v>
+        <v>1606</v>
       </c>
       <c r="E113" t="n">
-        <v>1169.924818603025</v>
+        <v>1170.279952698077</v>
       </c>
       <c r="F113" t="n">
-        <v>35.5</v>
+        <v>37.2</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="I113" t="n">
@@ -6297,7 +6297,7 @@
         <v>29529000000</v>
       </c>
       <c r="N113" t="n">
-        <v>73239026980</v>
+        <v>74209386328</v>
       </c>
     </row>
     <row r="114">
@@ -6312,16 +6312,16 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>40.3</v>
+        <v>39.8</v>
       </c>
       <c r="D114" t="n">
-        <v>1585</v>
+        <v>1606</v>
       </c>
       <c r="E114" t="n">
-        <v>1168.709522546084</v>
+        <v>1169.924818603025</v>
       </c>
       <c r="F114" t="n">
-        <v>35.6</v>
+        <v>37.3</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="I114" t="n">
@@ -6349,31 +6349,31 @@
         <v>29529000000</v>
       </c>
       <c r="N114" t="n">
-        <v>73239026980</v>
+        <v>74209386328</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>山洋電気株式会社</t>
+          <t>東亜道路工業株式会社</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>12</v>
+        <v>39.8</v>
       </c>
       <c r="D115" t="n">
-        <v>5180</v>
+        <v>1606</v>
       </c>
       <c r="E115" t="n">
-        <v>7052.737306843267</v>
+        <v>1168.709522546084</v>
       </c>
       <c r="F115" t="n">
-        <v>-26.6</v>
+        <v>37.4</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -6382,102 +6382,102 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>8317000000</v>
+        <v>11649000000</v>
       </c>
       <c r="J115" t="n">
-        <v>6048000000</v>
+        <v>13793000000</v>
       </c>
       <c r="K115" t="n">
-        <v>7673000000</v>
+        <v>4087000000</v>
       </c>
       <c r="L115" t="n">
-        <v>49734000000</v>
+        <v>50605000000</v>
       </c>
       <c r="M115" t="n">
-        <v>22038000000</v>
+        <v>29529000000</v>
       </c>
       <c r="N115" t="n">
-        <v>183967912380</v>
+        <v>74209386328</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ヘリオス テクノ ホールディング株式会社</t>
+          <t>山洋電気株式会社</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>54.5</v>
+        <v>12</v>
       </c>
       <c r="D116" t="n">
-        <v>967</v>
+        <v>5150</v>
       </c>
       <c r="E116" t="n">
-        <v>896.0103264198827</v>
+        <v>7052.737306843267</v>
       </c>
       <c r="F116" t="n">
-        <v>7.9</v>
+        <v>-27</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>7851015000</v>
+        <v>8317000000</v>
       </c>
       <c r="J116" t="n">
-        <v>640317000</v>
+        <v>6048000000</v>
       </c>
       <c r="K116" t="n">
-        <v>1079200000</v>
+        <v>7673000000</v>
       </c>
       <c r="L116" t="n">
-        <v>13746774000</v>
+        <v>49734000000</v>
       </c>
       <c r="M116" t="n">
-        <v>9570532000</v>
+        <v>22038000000</v>
       </c>
       <c r="N116" t="n">
-        <v>17552661989</v>
+        <v>182902461150</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>シェアリングテクノロジー株式会社</t>
+          <t>ヘリオス テクノ ホールディング株式会社</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>11.7</v>
+        <v>54.2</v>
       </c>
       <c r="D117" t="n">
-        <v>1544</v>
+        <v>972</v>
       </c>
       <c r="E117" t="n">
-        <v>653.0713101160862</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="F117" t="n">
-        <v>136.4</v>
+        <v>8.5</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -6486,50 +6486,50 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>4016706000</v>
+        <v>7851015000</v>
       </c>
       <c r="J117" t="n">
-        <v>309745000</v>
+        <v>640317000</v>
       </c>
       <c r="K117" t="n">
-        <v>0</v>
+        <v>1079200000</v>
       </c>
       <c r="L117" t="n">
-        <v>185001000</v>
+        <v>13746774000</v>
       </c>
       <c r="M117" t="n">
-        <v>4326451000</v>
+        <v>9570532000</v>
       </c>
       <c r="N117" t="n">
-        <v>36949879336</v>
+        <v>17643420324</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>栄研化学株式会社</t>
+          <t>シェアリングテクノロジー株式会社</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>31.3</v>
+        <v>11.7</v>
       </c>
       <c r="D118" t="n">
-        <v>2216</v>
+        <v>1544</v>
       </c>
       <c r="E118" t="n">
-        <v>1947.225264702313</v>
+        <v>653.0713101160862</v>
       </c>
       <c r="F118" t="n">
-        <v>13.8</v>
+        <v>136.4</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -6538,26 +6538,26 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>10900000000</v>
+        <v>4016706000</v>
       </c>
       <c r="J118" t="n">
-        <v>11585000000</v>
+        <v>309745000</v>
       </c>
       <c r="K118" t="n">
-        <v>408000000</v>
+        <v>0</v>
       </c>
       <c r="L118" t="n">
-        <v>45803000000</v>
+        <v>185001000</v>
       </c>
       <c r="M118" t="n">
-        <v>22893000000</v>
+        <v>4326451000</v>
       </c>
       <c r="N118" t="n">
-        <v>73051709768</v>
+        <v>36949879336</v>
       </c>
     </row>
     <row r="119">
@@ -6572,16 +6572,16 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>31.3</v>
+        <v>30.8</v>
       </c>
       <c r="D119" t="n">
-        <v>2216</v>
+        <v>2255</v>
       </c>
       <c r="E119" t="n">
-        <v>1678.083113259255</v>
+        <v>1947.225264702313</v>
       </c>
       <c r="F119" t="n">
-        <v>32.1</v>
+        <v>15.8</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="I119" t="n">
@@ -6609,215 +6609,215 @@
         <v>22893000000</v>
       </c>
       <c r="N119" t="n">
-        <v>73051709768</v>
+        <v>74337367115</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>株式会社ヤマダホールディングス</t>
+          <t>栄研化学株式会社</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>9831</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>58.1</v>
+        <v>30.8</v>
       </c>
       <c r="D120" t="n">
-        <v>717.7000122070312</v>
+        <v>2255</v>
       </c>
       <c r="E120" t="n">
-        <v>530</v>
+        <v>1678.083113259255</v>
       </c>
       <c r="F120" t="n">
-        <v>35.4</v>
+        <v>34.4</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>56470000000</v>
+        <v>10900000000</v>
       </c>
       <c r="J120" t="n">
-        <v>210733000000</v>
+        <v>11585000000</v>
       </c>
       <c r="K120" t="n">
-        <v>9997000000</v>
+        <v>408000000</v>
       </c>
       <c r="L120" t="n">
-        <v>676277000000</v>
+        <v>45803000000</v>
       </c>
       <c r="M120" t="n">
-        <v>277200000000</v>
+        <v>22893000000</v>
       </c>
       <c r="N120" t="n">
-        <v>477252876381</v>
+        <v>74337367115</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>日本化薬株式会社</t>
+          <t>株式会社ヤマダホールディングス</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>9831</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>35.9</v>
+        <v>57.8</v>
       </c>
       <c r="D121" t="n">
-        <v>2036</v>
+        <v>720.7999877929688</v>
       </c>
       <c r="E121" t="n">
-        <v>1111.90611839092</v>
+        <v>530</v>
       </c>
       <c r="F121" t="n">
-        <v>83.09999999999999</v>
+        <v>36</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>52962000000</v>
+        <v>56470000000</v>
       </c>
       <c r="J121" t="n">
-        <v>48231000000</v>
+        <v>210733000000</v>
       </c>
       <c r="K121" t="n">
-        <v>4337000000</v>
+        <v>9997000000</v>
       </c>
       <c r="L121" t="n">
-        <v>246425000000</v>
+        <v>676277000000</v>
       </c>
       <c r="M121" t="n">
-        <v>105530000000</v>
+        <v>277200000000</v>
       </c>
       <c r="N121" t="n">
-        <v>293567560004</v>
+        <v>479314283989</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>王子ホールディングス株式会社</t>
+          <t>日本化薬株式会社</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>41.8</v>
+        <v>35.7</v>
       </c>
       <c r="D122" t="n">
-        <v>867.2999877929688</v>
+        <v>2051.5</v>
       </c>
       <c r="E122" t="n">
-        <v>590</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="F122" t="n">
-        <v>47</v>
+        <v>84.5</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>55474000000</v>
+        <v>52962000000</v>
       </c>
       <c r="J122" t="n">
-        <v>244732000000</v>
+        <v>48231000000</v>
       </c>
       <c r="K122" t="n">
-        <v>7434000000</v>
+        <v>4337000000</v>
       </c>
       <c r="L122" t="n">
-        <v>875470000000</v>
+        <v>246425000000</v>
       </c>
       <c r="M122" t="n">
-        <v>307640000000</v>
+        <v>105530000000</v>
       </c>
       <c r="N122" t="n">
-        <v>736540891952</v>
+        <v>295802480034</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>東邦ホールディングス株式会社</t>
+          <t>王子ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>51.5</v>
+        <v>41.5</v>
       </c>
       <c r="D123" t="n">
-        <v>3940</v>
+        <v>872.7999877929688</v>
       </c>
       <c r="E123" t="n">
-        <v>3405.914389596362</v>
+        <v>590</v>
       </c>
       <c r="F123" t="n">
-        <v>15.7</v>
+        <v>47.9</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>90014000000</v>
+        <v>55474000000</v>
       </c>
       <c r="J123" t="n">
-        <v>34220000000</v>
+        <v>244732000000</v>
       </c>
       <c r="K123" t="n">
-        <v>7000000000</v>
+        <v>7434000000</v>
       </c>
       <c r="L123" t="n">
-        <v>241281000000</v>
+        <v>875470000000</v>
       </c>
       <c r="M123" t="n">
-        <v>131234000000</v>
+        <v>307640000000</v>
       </c>
       <c r="N123" t="n">
-        <v>254924394620</v>
+        <v>741211680564</v>
       </c>
     </row>
     <row r="124">
@@ -6832,16 +6832,16 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>51.5</v>
+        <v>50.6</v>
       </c>
       <c r="D124" t="n">
-        <v>3940</v>
+        <v>4005</v>
       </c>
       <c r="E124" t="n">
-        <v>2714.613787300615</v>
+        <v>3405.914389596362</v>
       </c>
       <c r="F124" t="n">
-        <v>45.1</v>
+        <v>17.6</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="I124" t="n">
@@ -6869,135 +6869,135 @@
         <v>131234000000</v>
       </c>
       <c r="N124" t="n">
-        <v>254924394620</v>
+        <v>259130000115</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>株式会社アイネス</t>
+          <t>東邦ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>9742</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>35.5</v>
+        <v>50.6</v>
       </c>
       <c r="D125" t="n">
-        <v>2045</v>
+        <v>4005</v>
       </c>
       <c r="E125" t="n">
-        <v>1879.137815927515</v>
+        <v>2714.613787300615</v>
       </c>
       <c r="F125" t="n">
-        <v>8.800000000000001</v>
+        <v>47.5</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>9731000000</v>
+        <v>90014000000</v>
       </c>
       <c r="J125" t="n">
-        <v>5286000000</v>
+        <v>34220000000</v>
       </c>
       <c r="K125" t="n">
-        <v>100000000</v>
+        <v>7000000000</v>
       </c>
       <c r="L125" t="n">
-        <v>34620000000</v>
+        <v>241281000000</v>
       </c>
       <c r="M125" t="n">
-        <v>15117000000</v>
+        <v>131234000000</v>
       </c>
       <c r="N125" t="n">
-        <v>42581904115</v>
+        <v>259130000115</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>日本ゼオン株式会社</t>
+          <t>株式会社アイネス</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>9742</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>36.2</v>
+        <v>34.4</v>
       </c>
       <c r="D126" t="n">
-        <v>2326</v>
+        <v>2113</v>
       </c>
       <c r="E126" t="n">
-        <v>1721.078563209627</v>
+        <v>1879.137815927515</v>
       </c>
       <c r="F126" t="n">
-        <v>35.1</v>
+        <v>12.4</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>44521000000</v>
+        <v>9731000000</v>
       </c>
       <c r="J126" t="n">
-        <v>45382000000</v>
+        <v>5286000000</v>
       </c>
       <c r="K126" t="n">
-        <v>71191000000</v>
+        <v>100000000</v>
       </c>
       <c r="L126" t="n">
-        <v>321836000000</v>
+        <v>34620000000</v>
       </c>
       <c r="M126" t="n">
-        <v>161094000000</v>
+        <v>15117000000</v>
       </c>
       <c r="N126" t="n">
-        <v>445069649282</v>
+        <v>43997830511</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>太陽ホールディングス株式会社</t>
+          <t>日本ゼオン株式会社</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>16.4</v>
+        <v>36.3</v>
       </c>
       <c r="D127" t="n">
-        <v>4720</v>
+        <v>2319</v>
       </c>
       <c r="E127" t="n">
-        <v>2199.643244598912</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="F127" t="n">
-        <v>114.6</v>
+        <v>34.7</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -7006,26 +7006,26 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>51152000000</v>
+        <v>44521000000</v>
       </c>
       <c r="J127" t="n">
-        <v>30337000000</v>
+        <v>45382000000</v>
       </c>
       <c r="K127" t="n">
-        <v>4870000000</v>
+        <v>71191000000</v>
       </c>
       <c r="L127" t="n">
-        <v>85466000000</v>
+        <v>321836000000</v>
       </c>
       <c r="M127" t="n">
-        <v>86359000000</v>
+        <v>161094000000</v>
       </c>
       <c r="N127" t="n">
-        <v>525225939040</v>
+        <v>443730230733</v>
       </c>
     </row>
     <row r="128">
@@ -7046,10 +7046,10 @@
         <v>4720</v>
       </c>
       <c r="E128" t="n">
-        <v>3565.648720929983</v>
+        <v>2199.643244598912</v>
       </c>
       <c r="F128" t="n">
-        <v>32.4</v>
+        <v>114.6</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="I128" t="n">
@@ -7083,25 +7083,25 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>株式会社エス・エム・エス</t>
+          <t>太陽ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>8.6</v>
+        <v>16.4</v>
       </c>
       <c r="D129" t="n">
-        <v>2583</v>
+        <v>4720</v>
       </c>
       <c r="E129" t="n">
-        <v>1478.127248828989</v>
+        <v>3565.648720929983</v>
       </c>
       <c r="F129" t="n">
-        <v>74.7</v>
+        <v>32.4</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -7110,458 +7110,458 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>14126000000</v>
+        <v>51152000000</v>
       </c>
       <c r="J129" t="n">
-        <v>1187000000</v>
+        <v>30337000000</v>
       </c>
       <c r="K129" t="n">
-        <v>2875000000</v>
+        <v>4870000000</v>
       </c>
       <c r="L129" t="n">
-        <v>29991000000</v>
+        <v>85466000000</v>
       </c>
       <c r="M129" t="n">
-        <v>18188000000</v>
+        <v>86359000000</v>
       </c>
       <c r="N129" t="n">
-        <v>212013799767</v>
+        <v>525225939040</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>アニコム ホールディングス株式会社</t>
+          <t>株式会社エス・エム・エス</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>8715</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>41.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D130" t="n">
-        <v>1017</v>
+        <v>2673</v>
       </c>
       <c r="E130" t="n">
-        <v>656.2604975855553</v>
+        <v>1478.127248828989</v>
       </c>
       <c r="F130" t="n">
-        <v>55</v>
+        <v>80.8</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>27691000000</v>
+        <v>14126000000</v>
       </c>
       <c r="J130" t="n">
-        <v>3070000000</v>
+        <v>1187000000</v>
       </c>
       <c r="K130" t="n">
-        <v>3000000</v>
+        <v>2875000000</v>
       </c>
       <c r="L130" t="n">
-        <v>27316000000</v>
+        <v>29991000000</v>
       </c>
       <c r="M130" t="n">
-        <v>30764000000</v>
+        <v>18188000000</v>
       </c>
       <c r="N130" t="n">
-        <v>74059180740</v>
+        <v>219401040177</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>東京製鐵株式会社</t>
+          <t>アニコム ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>8715</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>102</v>
+        <v>41</v>
       </c>
       <c r="D131" t="n">
-        <v>1706</v>
+        <v>1031</v>
       </c>
       <c r="E131" t="n">
-        <v>1605.452212379354</v>
+        <v>656.2604975855553</v>
       </c>
       <c r="F131" t="n">
-        <v>6.3</v>
+        <v>57.1</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>68644000000</v>
+        <v>27691000000</v>
       </c>
       <c r="J131" t="n">
-        <v>33060000000</v>
+        <v>3070000000</v>
       </c>
       <c r="K131" t="n">
-        <v>75000000000</v>
+        <v>3000000</v>
       </c>
       <c r="L131" t="n">
-        <v>158280000000</v>
+        <v>27316000000</v>
       </c>
       <c r="M131" t="n">
-        <v>176704000000</v>
+        <v>30764000000</v>
       </c>
       <c r="N131" t="n">
-        <v>173323016546</v>
+        <v>75078677820</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ウェーブロックホールディングス株式会社</t>
+          <t>東京製鐵株式会社</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>7940</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr"/>
-      <c r="D132" t="inlineStr"/>
+          <t>5423</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="D132" t="n">
+        <v>1755</v>
+      </c>
       <c r="E132" t="n">
-        <v>1010</v>
-      </c>
-      <c r="F132" t="inlineStr"/>
+        <v>1605.452212379354</v>
+      </c>
+      <c r="F132" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1961626000</v>
+        <v>68644000000</v>
       </c>
       <c r="J132" t="n">
-        <v>2544946000</v>
+        <v>33060000000</v>
       </c>
       <c r="K132" t="n">
-        <v>1068366000</v>
+        <v>75000000000</v>
       </c>
       <c r="L132" t="n">
-        <v>13761535000</v>
+        <v>158280000000</v>
       </c>
       <c r="M132" t="n">
-        <v>5574938000</v>
-      </c>
-      <c r="N132" t="inlineStr"/>
+        <v>176704000000</v>
+      </c>
+      <c r="N132" t="n">
+        <v>178301227455</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>近畿車輛株式会社</t>
+          <t>ウェーブロックホールディングス株式会社</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>7122</t>
-        </is>
-      </c>
-      <c r="C133" t="n">
-        <v>109.4</v>
-      </c>
-      <c r="D133" t="n">
-        <v>2358</v>
-      </c>
+          <t>7940</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="n">
-        <v>2144.894901144641</v>
-      </c>
-      <c r="F133" t="n">
-        <v>9.9</v>
-      </c>
+        <v>1010</v>
+      </c>
+      <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>6847000000</v>
+        <v>1961626000</v>
       </c>
       <c r="J133" t="n">
-        <v>4580000000</v>
+        <v>2544946000</v>
       </c>
       <c r="K133" t="n">
-        <v>6329000000</v>
+        <v>1068366000</v>
       </c>
       <c r="L133" t="n">
-        <v>24474000000</v>
+        <v>13761535000</v>
       </c>
       <c r="M133" t="n">
-        <v>17756000000</v>
-      </c>
-      <c r="N133" t="n">
-        <v>16223230998</v>
-      </c>
+        <v>5574938000</v>
+      </c>
+      <c r="N133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>株式会社三陽商会</t>
+          <t>近畿車輛株式会社</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>7122</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>66.40000000000001</v>
+        <v>108.9</v>
       </c>
       <c r="D134" t="n">
-        <v>1313</v>
+        <v>2370</v>
       </c>
       <c r="E134" t="n">
-        <v>3321.975331035734</v>
+        <v>2144.894901144641</v>
       </c>
       <c r="F134" t="n">
-        <v>-60.5</v>
+        <v>10.5</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>16287000000</v>
+        <v>6847000000</v>
       </c>
       <c r="J134" t="n">
-        <v>3021000000</v>
+        <v>4580000000</v>
       </c>
       <c r="K134" t="n">
-        <v>6298000000</v>
+        <v>6329000000</v>
       </c>
       <c r="L134" t="n">
-        <v>33920000000</v>
+        <v>24474000000</v>
       </c>
       <c r="M134" t="n">
-        <v>25606000000</v>
+        <v>17756000000</v>
       </c>
       <c r="N134" t="n">
-        <v>38583860016</v>
+        <v>16305791970</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>月島ホールディングス株式会社</t>
+          <t>株式会社三陽商会</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>6332</t>
+          <t>8011</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>48.3</v>
+        <v>62.3</v>
       </c>
       <c r="D135" t="n">
-        <v>2669</v>
+        <v>1398</v>
       </c>
       <c r="E135" t="n">
-        <v>1410</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="F135" t="n">
-        <v>89.3</v>
+        <v>-57.9</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>28795000000</v>
+        <v>16287000000</v>
       </c>
       <c r="J135" t="n">
-        <v>22203000000</v>
+        <v>3021000000</v>
       </c>
       <c r="K135" t="n">
-        <v>100000000</v>
+        <v>6298000000</v>
       </c>
       <c r="L135" t="n">
-        <v>80949000000</v>
+        <v>33920000000</v>
       </c>
       <c r="M135" t="n">
-        <v>51098000000</v>
+        <v>25606000000</v>
       </c>
       <c r="N135" t="n">
-        <v>105695664187</v>
+        <v>41081672736</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>マネックスグループ株式会社</t>
+          <t>月島ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>8698</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>15.3</v>
+        <v>48.6</v>
       </c>
       <c r="D136" t="n">
-        <v>714</v>
+        <v>2655</v>
       </c>
       <c r="E136" t="n">
-        <v>510.1850530906719</v>
+        <v>1410</v>
       </c>
       <c r="F136" t="n">
-        <v>39.9</v>
+        <v>88.3</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>17794000000</v>
+        <v>28795000000</v>
       </c>
       <c r="J136" t="n">
-        <v>412000000</v>
+        <v>22203000000</v>
       </c>
       <c r="K136" t="n">
-        <v>9312000000</v>
+        <v>100000000</v>
       </c>
       <c r="L136" t="n">
-        <v>98001000000</v>
+        <v>80949000000</v>
       </c>
       <c r="M136" t="n">
-        <v>27518000000</v>
+        <v>51098000000</v>
       </c>
       <c r="N136" t="n">
-        <v>179473670376</v>
+        <v>105141247065</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>株式会社あおぞら銀行</t>
+          <t>マネックスグループ株式会社</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>8698</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>226.6</v>
+        <v>15.1</v>
       </c>
       <c r="D137" t="n">
-        <v>3457</v>
+        <v>725</v>
       </c>
       <c r="E137" t="n">
-        <v>2190</v>
+        <v>510.1850530906719</v>
       </c>
       <c r="F137" t="n">
-        <v>57.9</v>
+        <v>42.1</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1061743000000</v>
+        <v>17794000000</v>
       </c>
       <c r="J137" t="n">
-        <v>22385000000</v>
+        <v>412000000</v>
       </c>
       <c r="K137" t="n">
-        <v>0</v>
+        <v>9312000000</v>
       </c>
       <c r="L137" t="n">
-        <v>487265000000</v>
+        <v>98001000000</v>
       </c>
       <c r="M137" t="n">
-        <v>1084128000000</v>
+        <v>27518000000</v>
       </c>
       <c r="N137" t="n">
-        <v>478383379732</v>
+        <v>182238670900</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>日本製紙株式会社</t>
+          <t>株式会社あおぞら銀行</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>307.8</v>
+        <v>221.1</v>
       </c>
       <c r="D138" t="n">
-        <v>1299</v>
+        <v>3544</v>
       </c>
       <c r="E138" t="n">
-        <v>1250</v>
+        <v>2190</v>
       </c>
       <c r="F138" t="n">
-        <v>3.9</v>
+        <v>61.8</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -7570,130 +7570,130 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>136216000000</v>
+        <v>1061743000000</v>
       </c>
       <c r="J138" t="n">
-        <v>151771000000</v>
+        <v>22385000000</v>
       </c>
       <c r="K138" t="n">
-        <v>172984000000</v>
+        <v>0</v>
       </c>
       <c r="L138" t="n">
-        <v>438604000000</v>
+        <v>487265000000</v>
       </c>
       <c r="M138" t="n">
-        <v>460971000000</v>
+        <v>1084128000000</v>
       </c>
       <c r="N138" t="n">
-        <v>149785745397</v>
+        <v>490422533344</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>カルビー株式会社</t>
+          <t>日本製紙株式会社</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>33.7</v>
+        <v>306.3</v>
       </c>
       <c r="D139" t="n">
-        <v>3009</v>
+        <v>1305</v>
       </c>
       <c r="E139" t="n">
-        <v>2919.137515755844</v>
+        <v>1250</v>
       </c>
       <c r="F139" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>49670000000</v>
+        <v>136216000000</v>
       </c>
       <c r="J139" t="n">
-        <v>70285000000</v>
+        <v>151771000000</v>
       </c>
       <c r="K139" t="n">
-        <v>3263000000</v>
+        <v>172984000000</v>
       </c>
       <c r="L139" t="n">
-        <v>183458000000</v>
+        <v>438604000000</v>
       </c>
       <c r="M139" t="n">
-        <v>123218000000</v>
+        <v>460971000000</v>
       </c>
       <c r="N139" t="n">
-        <v>365857852686</v>
+        <v>150477596415</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ＮＩＴＴＯＫＵ株式会社</t>
+          <t>カルビー株式会社</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>51.2</v>
+        <v>33.4</v>
       </c>
       <c r="D140" t="n">
-        <v>2439</v>
+        <v>3031</v>
       </c>
       <c r="E140" t="n">
-        <v>1710</v>
+        <v>2919.137515755844</v>
       </c>
       <c r="F140" t="n">
-        <v>42.6</v>
+        <v>3.8</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>11768000000</v>
+        <v>49670000000</v>
       </c>
       <c r="J140" t="n">
-        <v>6299000000</v>
+        <v>70285000000</v>
       </c>
       <c r="K140" t="n">
-        <v>2999000000</v>
+        <v>3263000000</v>
       </c>
       <c r="L140" t="n">
-        <v>33919000000</v>
+        <v>183458000000</v>
       </c>
       <c r="M140" t="n">
-        <v>21066000000</v>
+        <v>123218000000</v>
       </c>
       <c r="N140" t="n">
-        <v>41156861598</v>
+        <v>368532785474</v>
       </c>
     </row>
     <row r="141">
@@ -7708,16 +7708,16 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
       <c r="D141" t="n">
-        <v>2439</v>
+        <v>2435</v>
       </c>
       <c r="E141" t="n">
         <v>1710</v>
       </c>
       <c r="F141" t="n">
-        <v>42.6</v>
+        <v>42.4</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="I141" t="n">
@@ -7745,31 +7745,31 @@
         <v>21066000000</v>
       </c>
       <c r="N141" t="n">
-        <v>41156861598</v>
+        <v>41089363670</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>新光商事株式会社</t>
+          <t>ＮＩＴＴＯＫＵ株式会社</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>8141</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>30.8</v>
+        <v>51.3</v>
       </c>
       <c r="D142" t="n">
-        <v>1565</v>
+        <v>2435</v>
       </c>
       <c r="E142" t="n">
-        <v>930</v>
+        <v>1710</v>
       </c>
       <c r="F142" t="n">
-        <v>68.3</v>
+        <v>42.4</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -7778,50 +7778,50 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>10579000000</v>
+        <v>11768000000</v>
       </c>
       <c r="J142" t="n">
-        <v>195000000</v>
+        <v>6299000000</v>
       </c>
       <c r="K142" t="n">
-        <v>2995000000</v>
+        <v>2999000000</v>
       </c>
       <c r="L142" t="n">
-        <v>51945000000</v>
+        <v>33919000000</v>
       </c>
       <c r="M142" t="n">
-        <v>13769000000</v>
+        <v>21066000000</v>
       </c>
       <c r="N142" t="n">
-        <v>44680591935</v>
+        <v>41089363670</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>株式会社メガチップス</t>
+          <t>新光商事株式会社</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>6875</t>
+          <t>8141</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>89.59999999999999</v>
+        <v>30.8</v>
       </c>
       <c r="D143" t="n">
-        <v>10490</v>
+        <v>1566</v>
       </c>
       <c r="E143" t="n">
-        <v>4870</v>
+        <v>930</v>
       </c>
       <c r="F143" t="n">
-        <v>115.4</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -7830,158 +7830,158 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>25769446000</v>
+        <v>10579000000</v>
       </c>
       <c r="J143" t="n">
-        <v>2249411000</v>
+        <v>195000000</v>
       </c>
       <c r="K143" t="n">
-        <v>101636005000</v>
+        <v>2995000000</v>
       </c>
       <c r="L143" t="n">
-        <v>67428618000</v>
+        <v>51945000000</v>
       </c>
       <c r="M143" t="n">
-        <v>129654862000</v>
+        <v>13769000000</v>
       </c>
       <c r="N143" t="n">
-        <v>144771451490</v>
+        <v>44709141834</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>株式会社青山財産ネットワークス</t>
+          <t>株式会社メガチップス</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>8929</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>43.4</v>
+        <v>88.8</v>
       </c>
       <c r="D144" t="n">
-        <v>1335</v>
+        <v>10580</v>
       </c>
       <c r="E144" t="n">
-        <v>1347.74653160027</v>
+        <v>4870</v>
       </c>
       <c r="F144" t="n">
-        <v>-0.9</v>
+        <v>117.2</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>10862000000</v>
+        <v>25769446000</v>
       </c>
       <c r="J144" t="n">
-        <v>245000000</v>
+        <v>2249411000</v>
       </c>
       <c r="K144" t="n">
-        <v>2845000000</v>
+        <v>101636005000</v>
       </c>
       <c r="L144" t="n">
-        <v>7128000000</v>
+        <v>67428618000</v>
       </c>
       <c r="M144" t="n">
-        <v>13952000000</v>
+        <v>129654862000</v>
       </c>
       <c r="N144" t="n">
-        <v>32127092730</v>
+        <v>146013532580</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>平和不動産株式会社</t>
+          <t>株式会社青山財産ネットワークス</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>8803</t>
+          <t>8929</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>74.09999999999999</v>
+        <v>42.8</v>
       </c>
       <c r="D145" t="n">
-        <v>2318</v>
+        <v>1356</v>
       </c>
       <c r="E145" t="n">
-        <v>3610</v>
+        <v>1347.74653160027</v>
       </c>
       <c r="F145" t="n">
-        <v>-35.8</v>
+        <v>0.6</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>28111000000</v>
+        <v>10862000000</v>
       </c>
       <c r="J145" t="n">
-        <v>79319000000</v>
+        <v>245000000</v>
       </c>
       <c r="K145" t="n">
-        <v>5997000000</v>
+        <v>2845000000</v>
       </c>
       <c r="L145" t="n">
-        <v>119278000000</v>
+        <v>7128000000</v>
       </c>
       <c r="M145" t="n">
-        <v>113427000000</v>
+        <v>13952000000</v>
       </c>
       <c r="N145" t="n">
-        <v>153150858044</v>
+        <v>32632462728</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>小林製薬株式会社</t>
+          <t>平和不動産株式会社</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>30.2</v>
+        <v>73.2</v>
       </c>
       <c r="D146" t="n">
-        <v>5768</v>
+        <v>2344</v>
       </c>
       <c r="E146" t="n">
-        <v>2148.936934940886</v>
+        <v>3610</v>
       </c>
       <c r="F146" t="n">
-        <v>168.4</v>
+        <v>-35.1</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -7990,22 +7990,22 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>81987000000</v>
+        <v>28111000000</v>
       </c>
       <c r="J146" t="n">
-        <v>32461000000</v>
+        <v>79319000000</v>
       </c>
       <c r="K146" t="n">
-        <v>14872000000</v>
+        <v>5997000000</v>
       </c>
       <c r="L146" t="n">
-        <v>195600000000</v>
+        <v>119278000000</v>
       </c>
       <c r="M146" t="n">
-        <v>129320000000</v>
+        <v>113427000000</v>
       </c>
       <c r="N146" t="n">
-        <v>428785165928</v>
+        <v>154868684752</v>
       </c>
     </row>
     <row r="147">
@@ -8020,16 +8020,16 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>30.2</v>
+        <v>30</v>
       </c>
       <c r="D147" t="n">
-        <v>5768</v>
+        <v>5790</v>
       </c>
       <c r="E147" t="n">
-        <v>5066.092575838703</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="F147" t="n">
-        <v>13.9</v>
+        <v>169.4</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -8057,31 +8057,31 @@
         <v>129320000000</v>
       </c>
       <c r="N147" t="n">
-        <v>428785165928</v>
+        <v>430420615590</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>セーレン株式会社</t>
+          <t>小林製薬株式会社</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>3569</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>37.6</v>
+        <v>30</v>
       </c>
       <c r="D148" t="n">
-        <v>3195</v>
+        <v>5790</v>
       </c>
       <c r="E148" t="n">
-        <v>1359.655069733296</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="F148" t="n">
-        <v>135</v>
+        <v>14.3</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -8090,50 +8090,50 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>35451000000</v>
+        <v>81987000000</v>
       </c>
       <c r="J148" t="n">
-        <v>25813000000</v>
+        <v>32461000000</v>
       </c>
       <c r="K148" t="n">
-        <v>8891000000</v>
+        <v>14872000000</v>
       </c>
       <c r="L148" t="n">
-        <v>91845000000</v>
+        <v>195600000000</v>
       </c>
       <c r="M148" t="n">
-        <v>70155000000</v>
+        <v>129320000000</v>
       </c>
       <c r="N148" t="n">
-        <v>186458413995</v>
+        <v>430420615590</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>データセクション株式会社</t>
+          <t>セーレン株式会社</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>3569</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>2.5</v>
+        <v>37.2</v>
       </c>
       <c r="D149" t="n">
-        <v>1547</v>
+        <v>3230</v>
       </c>
       <c r="E149" t="n">
-        <v>5143.276404494382</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="F149" t="n">
-        <v>-69.90000000000001</v>
+        <v>137.6</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -8142,102 +8142,102 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1420430000</v>
+        <v>35451000000</v>
       </c>
       <c r="J149" t="n">
-        <v>1162000</v>
+        <v>25813000000</v>
       </c>
       <c r="K149" t="n">
-        <v>49326000</v>
+        <v>8891000000</v>
       </c>
       <c r="L149" t="n">
-        <v>2818110000</v>
+        <v>91845000000</v>
       </c>
       <c r="M149" t="n">
-        <v>1470918000</v>
+        <v>70155000000</v>
       </c>
       <c r="N149" t="n">
-        <v>57954187382</v>
+        <v>188500994430</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>愛眼株式会社</t>
+          <t>データセクション株式会社</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>9854</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>72.2</v>
+        <v>2.6</v>
       </c>
       <c r="D150" t="n">
-        <v>275</v>
+        <v>1483</v>
       </c>
       <c r="E150" t="n">
-        <v>246.9708756284982</v>
+        <v>5143.276404494382</v>
       </c>
       <c r="F150" t="n">
-        <v>11.3</v>
+        <v>-71.2</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2219000000</v>
+        <v>1420430000</v>
       </c>
       <c r="J150" t="n">
-        <v>1030000000</v>
+        <v>1162000</v>
       </c>
       <c r="K150" t="n">
-        <v>604000000</v>
+        <v>49326000</v>
       </c>
       <c r="L150" t="n">
-        <v>12920000000</v>
+        <v>2818110000</v>
       </c>
       <c r="M150" t="n">
-        <v>3853000000</v>
+        <v>1470918000</v>
       </c>
       <c r="N150" t="n">
-        <v>5336846625</v>
+        <v>55556599798</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>株式会社アシロ</t>
+          <t>愛眼株式会社</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>13.9</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="D151" t="n">
-        <v>1561</v>
+        <v>282</v>
       </c>
       <c r="E151" t="n">
-        <v>1396.628697042366</v>
+        <v>246.9708756284982</v>
       </c>
       <c r="F151" t="n">
-        <v>11.8</v>
+        <v>14.2</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -8246,546 +8246,598 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1428281000</v>
+        <v>2219000000</v>
       </c>
       <c r="J151" t="n">
-        <v>102238000</v>
+        <v>1030000000</v>
       </c>
       <c r="K151" t="n">
-        <v>0</v>
+        <v>604000000</v>
       </c>
       <c r="L151" t="n">
-        <v>1804458000</v>
+        <v>12920000000</v>
       </c>
       <c r="M151" t="n">
-        <v>1530519000</v>
+        <v>3853000000</v>
       </c>
       <c r="N151" t="n">
-        <v>10976307307</v>
+        <v>5472693630</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>三浦工業株式会社</t>
+          <t>株式会社アシロ</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>7378</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>12.1</v>
+        <v>14.4</v>
       </c>
       <c r="D152" t="n">
-        <v>3005</v>
+        <v>1507</v>
       </c>
       <c r="E152" t="n">
-        <v>3147.518794622453</v>
+        <v>1396.628697042366</v>
       </c>
       <c r="F152" t="n">
-        <v>-4.5</v>
+        <v>7.9</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>20794000000</v>
+        <v>1428281000</v>
       </c>
       <c r="J152" t="n">
-        <v>10600000000</v>
+        <v>102238000</v>
       </c>
       <c r="K152" t="n">
-        <v>10773000000</v>
+        <v>0</v>
       </c>
       <c r="L152" t="n">
-        <v>138378000000</v>
+        <v>1804458000</v>
       </c>
       <c r="M152" t="n">
-        <v>42167000000</v>
+        <v>1530519000</v>
       </c>
       <c r="N152" t="n">
-        <v>347826826800</v>
+        <v>10596601609</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>株式会社カカクコム</t>
+          <t>三浦工業株式会社</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>6.8</v>
+        <v>11.8</v>
       </c>
       <c r="D153" t="n">
-        <v>3796</v>
+        <v>3079</v>
       </c>
       <c r="E153" t="n">
-        <v>2318.314890576102</v>
+        <v>3147.518794622453</v>
       </c>
       <c r="F153" t="n">
-        <v>63.7</v>
+        <v>-2.2</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>46452000000</v>
+        <v>20794000000</v>
       </c>
       <c r="J153" t="n">
-        <v>68000000</v>
+        <v>10600000000</v>
       </c>
       <c r="K153" t="n">
-        <v>4669000000</v>
+        <v>10773000000</v>
       </c>
       <c r="L153" t="n">
-        <v>45479000000</v>
+        <v>138378000000</v>
       </c>
       <c r="M153" t="n">
-        <v>51189000000</v>
+        <v>42167000000</v>
       </c>
       <c r="N153" t="n">
-        <v>750986469532</v>
+        <v>356392279440</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>古河機械金属株式会社</t>
+          <t>株式会社カカクコム</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>47.1</v>
+        <v>6.7</v>
       </c>
       <c r="D154" t="n">
-        <v>4045</v>
+        <v>3850</v>
       </c>
       <c r="E154" t="n">
-        <v>1600</v>
+        <v>2318.314890576102</v>
       </c>
       <c r="F154" t="n">
-        <v>152.8</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>14468000000</v>
+        <v>46452000000</v>
       </c>
       <c r="J154" t="n">
-        <v>26121000000</v>
+        <v>68000000</v>
       </c>
       <c r="K154" t="n">
-        <v>19903000000</v>
+        <v>4669000000</v>
       </c>
       <c r="L154" t="n">
-        <v>100075000000</v>
+        <v>45479000000</v>
       </c>
       <c r="M154" t="n">
-        <v>60492000000</v>
+        <v>51189000000</v>
       </c>
       <c r="N154" t="n">
-        <v>128510123265</v>
+        <v>761669627950</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>多木化学株式会社</t>
+          <t>古河機械金属株式会社</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>4025</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>31.6</v>
+        <v>47.5</v>
       </c>
       <c r="D155" t="n">
-        <v>5550</v>
+        <v>4010</v>
       </c>
       <c r="E155" t="n">
-        <v>4695.956053243186</v>
+        <v>1600</v>
       </c>
       <c r="F155" t="n">
-        <v>18.2</v>
+        <v>150.6</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="I155" t="n">
-        <v>6433000000</v>
+        <v>14468000000</v>
       </c>
       <c r="J155" t="n">
-        <v>7985000000</v>
+        <v>26121000000</v>
       </c>
       <c r="K155" t="n">
-        <v>199000000</v>
+        <v>19903000000</v>
       </c>
       <c r="L155" t="n">
-        <v>29378000000</v>
+        <v>100075000000</v>
       </c>
       <c r="M155" t="n">
-        <v>14617000000</v>
+        <v>60492000000</v>
       </c>
       <c r="N155" t="n">
-        <v>46327897950</v>
+        <v>127398169170</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>エムスリー株式会社</t>
+          <t>多木化学株式会社</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2413</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>7.9</v>
+        <v>32.4</v>
       </c>
       <c r="D156" t="n">
-        <v>1690</v>
+        <v>5410</v>
       </c>
       <c r="E156" t="n">
-        <v>1638.585693292194</v>
+        <v>4695.956053243186</v>
       </c>
       <c r="F156" t="n">
-        <v>3.1</v>
+        <v>15.2</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I156" t="n">
-        <v>78812000000</v>
+        <v>6433000000</v>
       </c>
       <c r="J156" t="n">
-        <v>345000000</v>
+        <v>7985000000</v>
       </c>
       <c r="K156" t="n">
-        <v>9506000000</v>
+        <v>199000000</v>
       </c>
       <c r="L156" t="n">
-        <v>152472000000</v>
+        <v>29378000000</v>
       </c>
       <c r="M156" t="n">
-        <v>88663000000</v>
+        <v>14617000000</v>
       </c>
       <c r="N156" t="n">
-        <v>1126074481090</v>
+        <v>45159266290</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>三井松島ホールディングス株式会社</t>
+          <t>エムスリー株式会社</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>41.2</v>
+        <v>7.6</v>
       </c>
       <c r="D157" t="n">
-        <v>2223</v>
+        <v>1748.5</v>
       </c>
       <c r="E157" t="n">
-        <v>2920</v>
+        <v>1638.585693292194</v>
       </c>
       <c r="F157" t="n">
-        <v>-23.9</v>
+        <v>6.7</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I157" t="n">
-        <v>19413000000</v>
+        <v>78812000000</v>
       </c>
       <c r="J157" t="n">
-        <v>3540000000</v>
+        <v>345000000</v>
       </c>
       <c r="K157" t="n">
-        <v>10945000000</v>
+        <v>9506000000</v>
       </c>
       <c r="L157" t="n">
-        <v>35537000000</v>
+        <v>152472000000</v>
       </c>
       <c r="M157" t="n">
-        <v>33898000000</v>
+        <v>88663000000</v>
       </c>
       <c r="N157" t="n">
-        <v>82313155080</v>
+        <v>1165053982358</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ノリタケ株式会社</t>
+          <t>三井松島ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>39.8</v>
+        <v>41</v>
       </c>
       <c r="D158" t="n">
-        <v>3420</v>
+        <v>2233</v>
       </c>
       <c r="E158" t="n">
-        <v>3573.410502159827</v>
+        <v>2920</v>
       </c>
       <c r="F158" t="n">
-        <v>-4.3</v>
+        <v>-23.5</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>11733000000</v>
+        <v>19413000000</v>
       </c>
       <c r="J158" t="n">
-        <v>20204000000</v>
+        <v>3540000000</v>
       </c>
       <c r="K158" t="n">
-        <v>42879000000</v>
+        <v>10945000000</v>
       </c>
       <c r="L158" t="n">
-        <v>118800000000</v>
+        <v>35537000000</v>
       </c>
       <c r="M158" t="n">
-        <v>74816000000</v>
+        <v>33898000000</v>
       </c>
       <c r="N158" t="n">
-        <v>188148817080</v>
+        <v>82683434680</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>株式会社ＡＣＳＬ</t>
+          <t>ノリタケ株式会社</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>8.199999999999999</v>
+        <v>39</v>
       </c>
       <c r="D159" t="n">
-        <v>1303</v>
+        <v>3485</v>
       </c>
       <c r="E159" t="n">
-        <v>913.2768512341561</v>
+        <v>3573.410502159827</v>
       </c>
       <c r="F159" t="n">
-        <v>42.7</v>
+        <v>-2.5</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1891731000</v>
+        <v>11733000000</v>
       </c>
       <c r="J159" t="n">
-        <v>3724000</v>
+        <v>20204000000</v>
       </c>
       <c r="K159" t="n">
-        <v>197577000</v>
+        <v>42879000000</v>
       </c>
       <c r="L159" t="n">
-        <v>3572642000</v>
+        <v>118800000000</v>
       </c>
       <c r="M159" t="n">
-        <v>2093032000</v>
+        <v>74816000000</v>
       </c>
       <c r="N159" t="n">
-        <v>25502631326</v>
+        <v>191724744890</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>株式会社スズケン</t>
+          <t>株式会社ＡＣＳＬ</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>9987</t>
+          <t>6232</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>79</v>
+        <v>8.5</v>
       </c>
       <c r="D160" t="n">
-        <v>5173</v>
+        <v>1262</v>
       </c>
       <c r="E160" t="n">
-        <v>4137.137750115735</v>
+        <v>913.2768512341561</v>
       </c>
       <c r="F160" t="n">
-        <v>25</v>
+        <v>38.2</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>168215000000</v>
+        <v>1891731000</v>
       </c>
       <c r="J160" t="n">
-        <v>65453000000</v>
+        <v>3724000</v>
       </c>
       <c r="K160" t="n">
-        <v>38927000000</v>
+        <v>197577000</v>
       </c>
       <c r="L160" t="n">
-        <v>418062000000</v>
+        <v>3572642000</v>
       </c>
       <c r="M160" t="n">
-        <v>272595000000</v>
+        <v>2093032000</v>
       </c>
       <c r="N160" t="n">
-        <v>344957309697</v>
+        <v>24700169404</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
+          <t>株式会社スズケン</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="D161" t="n">
+        <v>5256</v>
+      </c>
+      <c r="E161" t="n">
+        <v>4137.137750115735</v>
+      </c>
+      <c r="F161" t="n">
+        <v>27</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
+        <v>168215000000</v>
+      </c>
+      <c r="J161" t="n">
+        <v>65453000000</v>
+      </c>
+      <c r="K161" t="n">
+        <v>38927000000</v>
+      </c>
+      <c r="L161" t="n">
+        <v>418062000000</v>
+      </c>
+      <c r="M161" t="n">
+        <v>272595000000</v>
+      </c>
+      <c r="N161" t="n">
+        <v>350492097384</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
           <t>フォスター電機株式会社</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
+      <c r="B162" t="inlineStr">
         <is>
           <t>6794</t>
         </is>
       </c>
-      <c r="C161" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="D161" t="n">
-        <v>2990</v>
-      </c>
-      <c r="E161" t="n">
+      <c r="C162" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="D162" t="n">
+        <v>3015</v>
+      </c>
+      <c r="E162" t="n">
         <v>2681.96152003832</v>
       </c>
-      <c r="F161" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="G161" t="inlineStr">
+      <c r="F162" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="G162" t="inlineStr">
         <is>
           <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
+      <c r="H162" t="inlineStr">
         <is>
           <t>2026-01-22</t>
         </is>
       </c>
-      <c r="I161" t="n">
+      <c r="I162" t="n">
         <v>12089000000</v>
       </c>
-      <c r="J161" t="n">
+      <c r="J162" t="n">
         <v>7327000000</v>
       </c>
-      <c r="K161" t="n">
+      <c r="K162" t="n">
         <v>1115000000</v>
       </c>
-      <c r="L161" t="n">
+      <c r="L162" t="n">
         <v>51632000000</v>
       </c>
-      <c r="M161" t="n">
+      <c r="M162" t="n">
         <v>20531000000</v>
       </c>
-      <c r="N161" t="n">
-        <v>67178742930</v>
+      <c r="N162" t="n">
+        <v>67740438105</v>
       </c>
     </row>
   </sheetData>

--- a/docs/アクティビスト銘柄_資産判定.xlsx
+++ b/docs/アクティビスト銘柄_資産判定.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N162"/>
+  <dimension ref="A1:N166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>44.9</v>
+        <v>44.8</v>
       </c>
       <c r="D2" t="n">
-        <v>1325.5</v>
+        <v>1328.5</v>
       </c>
       <c r="E2" t="n">
         <v>1111.251693601708</v>
       </c>
       <c r="F2" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -537,7 +537,7 @@
         <v>213563000000</v>
       </c>
       <c r="N2" t="n">
-        <v>475896969020</v>
+        <v>476974065140</v>
       </c>
     </row>
     <row r="3">
@@ -555,13 +555,13 @@
         <v>54.8</v>
       </c>
       <c r="D3" t="n">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="E3" t="n">
         <v>1019.677694332945</v>
       </c>
       <c r="F3" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         <v>106991000000</v>
       </c>
       <c r="N3" t="n">
-        <v>195170638000</v>
+        <v>195338888550</v>
       </c>
     </row>
     <row r="4">
@@ -607,13 +607,13 @@
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>3455</v>
+        <v>3443</v>
       </c>
       <c r="E4" t="n">
         <v>6116.356643776557</v>
       </c>
       <c r="F4" t="n">
-        <v>-43.5</v>
+        <v>-43.7</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         <v>219041000000</v>
       </c>
       <c r="N4" t="n">
-        <v>3125938869270</v>
+        <v>3115081773342</v>
       </c>
     </row>
     <row r="5">
@@ -656,16 +656,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30.2</v>
+        <v>30.7</v>
       </c>
       <c r="D5" t="n">
-        <v>2227</v>
+        <v>2193</v>
       </c>
       <c r="E5" t="n">
         <v>1815.198567455447</v>
       </c>
       <c r="F5" t="n">
-        <v>22.7</v>
+        <v>20.8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         <v>168499000000</v>
       </c>
       <c r="N5" t="n">
-        <v>558124620204</v>
+        <v>549603633636</v>
       </c>
     </row>
     <row r="6">
@@ -815,13 +815,13 @@
         <v>14.5</v>
       </c>
       <c r="D8" t="n">
-        <v>3855</v>
+        <v>3865</v>
       </c>
       <c r="E8" t="n">
         <v>1361.432492253209</v>
       </c>
       <c r="F8" t="n">
-        <v>183.2</v>
+        <v>183.9</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>12397436000</v>
       </c>
       <c r="N8" t="n">
-        <v>85516794975</v>
+        <v>85738628425</v>
       </c>
     </row>
     <row r="9">
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>29.8</v>
+        <v>30.1</v>
       </c>
       <c r="D9" t="n">
-        <v>3352</v>
+        <v>3323</v>
       </c>
       <c r="E9" t="n">
         <v>13739.64575539568</v>
       </c>
       <c r="F9" t="n">
-        <v>-75.59999999999999</v>
+        <v>-75.8</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>325393000000</v>
       </c>
       <c r="N9" t="n">
-        <v>1091854602560</v>
+        <v>1082408366440</v>
       </c>
     </row>
     <row r="10">
@@ -916,16 +916,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>47.2</v>
+        <v>46.5</v>
       </c>
       <c r="D10" t="n">
-        <v>2048.5</v>
+        <v>2078</v>
       </c>
       <c r="E10" t="n">
         <v>1198.150742177053</v>
       </c>
       <c r="F10" t="n">
-        <v>71</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>213966000000</v>
       </c>
       <c r="N10" t="n">
-        <v>453566048438</v>
+        <v>460097753798</v>
       </c>
     </row>
     <row r="11">
@@ -968,16 +968,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>47.2</v>
+        <v>46.5</v>
       </c>
       <c r="D11" t="n">
-        <v>2048.5</v>
+        <v>2078</v>
       </c>
       <c r="E11" t="n">
         <v>1188.162962482466</v>
       </c>
       <c r="F11" t="n">
-        <v>72.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>213966000000</v>
       </c>
       <c r="N11" t="n">
-        <v>453566048438</v>
+        <v>460097753798</v>
       </c>
     </row>
     <row r="12">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="D12" t="n">
-        <v>3682</v>
+        <v>3697</v>
       </c>
       <c r="E12" t="n">
         <v>2995.424821743842</v>
       </c>
       <c r="F12" t="n">
-        <v>22.9</v>
+        <v>23.4</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>129979000000</v>
       </c>
       <c r="N12" t="n">
-        <v>541127648488</v>
+        <v>543332133748</v>
       </c>
     </row>
     <row r="13">
@@ -1072,16 +1072,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>73.40000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="D13" t="n">
-        <v>4900</v>
+        <v>4815</v>
       </c>
       <c r="E13" t="n">
         <v>4991.027246539169</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.8</v>
+        <v>-3.5</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>1007966000000</v>
       </c>
       <c r="N13" t="n">
-        <v>1373086457400</v>
+        <v>1349267610690</v>
       </c>
     </row>
     <row r="14">
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="D14" t="n">
-        <v>1710</v>
+        <v>1696.5</v>
       </c>
       <c r="E14" t="n">
         <v>1512.21980974841</v>
       </c>
       <c r="F14" t="n">
-        <v>13.1</v>
+        <v>12.2</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>120816000000</v>
       </c>
       <c r="N14" t="n">
-        <v>563302664730</v>
+        <v>558855538430</v>
       </c>
     </row>
     <row r="15">
@@ -1176,16 +1176,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="D15" t="n">
-        <v>2582.5</v>
+        <v>2635</v>
       </c>
       <c r="E15" t="n">
         <v>1827.011042553346</v>
       </c>
       <c r="F15" t="n">
-        <v>41.4</v>
+        <v>44.2</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>48336000000</v>
       </c>
       <c r="N15" t="n">
-        <v>630317931108</v>
+        <v>643131751585</v>
       </c>
     </row>
     <row r="16">
@@ -1228,16 +1228,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>137.2</v>
+        <v>134.9</v>
       </c>
       <c r="D16" t="n">
-        <v>1567</v>
+        <v>1594</v>
       </c>
       <c r="E16" t="n">
         <v>2122.579027791042</v>
       </c>
       <c r="F16" t="n">
-        <v>-26.2</v>
+        <v>-24.9</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>80333000000</v>
       </c>
       <c r="N16" t="n">
-        <v>58531253109</v>
+        <v>59539768638</v>
       </c>
     </row>
     <row r="17">
@@ -1280,16 +1280,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="D17" t="n">
-        <v>2987</v>
+        <v>2996.5</v>
       </c>
       <c r="E17" t="n">
         <v>6272.971195510064</v>
       </c>
       <c r="F17" t="n">
-        <v>-52.4</v>
+        <v>-52.2</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>179622000000</v>
       </c>
       <c r="N17" t="n">
-        <v>1077337820058</v>
+        <v>1080764237631</v>
       </c>
     </row>
     <row r="18">
@@ -1332,16 +1332,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="D18" t="n">
-        <v>3760</v>
+        <v>3828</v>
       </c>
       <c r="E18" t="n">
         <v>1572.181660925393</v>
       </c>
       <c r="F18" t="n">
-        <v>139.2</v>
+        <v>143.5</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>35501000000</v>
       </c>
       <c r="N18" t="n">
-        <v>671397094320</v>
+        <v>683539382196</v>
       </c>
     </row>
     <row r="19">
@@ -1384,16 +1384,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="D19" t="n">
-        <v>3760</v>
+        <v>3828</v>
       </c>
       <c r="E19" t="n">
         <v>1141.512891683109</v>
       </c>
       <c r="F19" t="n">
-        <v>229.4</v>
+        <v>235.3</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>35501000000</v>
       </c>
       <c r="N19" t="n">
-        <v>671397094320</v>
+        <v>683539382196</v>
       </c>
     </row>
     <row r="20">
@@ -1436,16 +1436,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>44.6</v>
+        <v>46.8</v>
       </c>
       <c r="D20" t="n">
-        <v>6021</v>
+        <v>5734</v>
       </c>
       <c r="E20" t="n">
         <v>2836.942753814942</v>
       </c>
       <c r="F20" t="n">
-        <v>112.2</v>
+        <v>102.1</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>94351000000</v>
       </c>
       <c r="N20" t="n">
-        <v>211637674341</v>
+        <v>201549647014</v>
       </c>
     </row>
     <row r="21">
@@ -1488,16 +1488,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>55.9</v>
+        <v>55.5</v>
       </c>
       <c r="D21" t="n">
-        <v>4019</v>
+        <v>4044</v>
       </c>
       <c r="E21" t="n">
         <v>2863.970160821546</v>
       </c>
       <c r="F21" t="n">
-        <v>40.3</v>
+        <v>41.2</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>161529000000</v>
       </c>
       <c r="N21" t="n">
-        <v>289147610097</v>
+        <v>290946239172</v>
       </c>
     </row>
     <row r="22">
@@ -1540,16 +1540,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>53.1</v>
+        <v>53</v>
       </c>
       <c r="D22" t="n">
-        <v>4625</v>
+        <v>4637</v>
       </c>
       <c r="E22" t="n">
         <v>2566.284807227078</v>
       </c>
       <c r="F22" t="n">
-        <v>80.2</v>
+        <v>80.7</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>231575000000</v>
       </c>
       <c r="N22" t="n">
-        <v>436077837500</v>
+        <v>437209282700</v>
       </c>
     </row>
     <row r="23">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="D23" t="n">
-        <v>5140</v>
+        <v>5133</v>
       </c>
       <c r="E23" t="n">
         <v>2779.139169918938</v>
       </c>
       <c r="F23" t="n">
-        <v>84.90000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>183216000000</v>
       </c>
       <c r="N23" t="n">
-        <v>637526900940</v>
+        <v>636658673643</v>
       </c>
     </row>
     <row r="24">
@@ -1644,16 +1644,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="D24" t="n">
-        <v>4002</v>
+        <v>4027</v>
       </c>
       <c r="E24" t="n">
         <v>2420.370957920882</v>
       </c>
       <c r="F24" t="n">
-        <v>65.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>18167000000</v>
       </c>
       <c r="N24" t="n">
-        <v>197847190158</v>
+        <v>199083117133</v>
       </c>
     </row>
     <row r="25">
@@ -1699,7 +1699,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="E25" t="n">
         <v>1344.518957928979</v>
@@ -1733,7 +1733,7 @@
         <v>45956000000</v>
       </c>
       <c r="N25" t="n">
-        <v>560821148979</v>
+        <v>560499392726</v>
       </c>
     </row>
     <row r="26">
@@ -1748,16 +1748,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>59.5</v>
+        <v>59.8</v>
       </c>
       <c r="D26" t="n">
-        <v>5031</v>
+        <v>5008</v>
       </c>
       <c r="E26" t="n">
         <v>4154.626869982095</v>
       </c>
       <c r="F26" t="n">
-        <v>21.1</v>
+        <v>20.5</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>179086000000</v>
       </c>
       <c r="N26" t="n">
-        <v>300857200956</v>
+        <v>299481785408</v>
       </c>
     </row>
     <row r="27">
@@ -1800,16 +1800,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="D27" t="n">
-        <v>3964</v>
+        <v>3922</v>
       </c>
       <c r="E27" t="n">
         <v>2561.705402476645</v>
       </c>
       <c r="F27" t="n">
-        <v>54.7</v>
+        <v>53.1</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>100104000000</v>
       </c>
       <c r="N27" t="n">
-        <v>725338289420</v>
+        <v>717653070410</v>
       </c>
     </row>
     <row r="28">
@@ -1852,16 +1852,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>44.8</v>
+        <v>44.6</v>
       </c>
       <c r="D28" t="n">
-        <v>3447</v>
+        <v>3466</v>
       </c>
       <c r="E28" t="n">
         <v>2560</v>
       </c>
       <c r="F28" t="n">
-        <v>34.6</v>
+        <v>35.4</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>190312000000</v>
       </c>
       <c r="N28" t="n">
-        <v>424361224782</v>
+        <v>426700320596</v>
       </c>
     </row>
     <row r="29">
@@ -1904,16 +1904,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>90.8</v>
+        <v>89.8</v>
       </c>
       <c r="D29" t="n">
-        <v>4235</v>
+        <v>4280</v>
       </c>
       <c r="E29" t="n">
         <v>3449.780346820809</v>
       </c>
       <c r="F29" t="n">
-        <v>22.8</v>
+        <v>24.1</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>90928000000</v>
       </c>
       <c r="N29" t="n">
-        <v>100145095820</v>
+        <v>101209211360</v>
       </c>
     </row>
     <row r="30">
@@ -1956,16 +1956,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>57.9</v>
+        <v>56.7</v>
       </c>
       <c r="D30" t="n">
-        <v>1648</v>
+        <v>1683</v>
       </c>
       <c r="E30" t="n">
         <v>1746.940387696806</v>
       </c>
       <c r="F30" t="n">
-        <v>-5.7</v>
+        <v>-3.7</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>36070000000</v>
       </c>
       <c r="N30" t="n">
-        <v>62263900464</v>
+        <v>63586252719</v>
       </c>
     </row>
     <row r="31">
@@ -2008,16 +2008,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>104.9</v>
+        <v>104.5</v>
       </c>
       <c r="D31" t="n">
-        <v>1690</v>
+        <v>1697</v>
       </c>
       <c r="E31" t="n">
         <v>2298.672482457804</v>
       </c>
       <c r="F31" t="n">
-        <v>-26.5</v>
+        <v>-26.2</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>42752000000</v>
       </c>
       <c r="N31" t="n">
-        <v>40748751030</v>
+        <v>40917532839</v>
       </c>
     </row>
     <row r="32">
@@ -2060,16 +2060,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>67.09999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="D32" t="n">
-        <v>2666</v>
+        <v>2640</v>
       </c>
       <c r="E32" t="n">
         <v>1270</v>
       </c>
       <c r="F32" t="n">
-        <v>109.9</v>
+        <v>107.9</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>31108000000</v>
       </c>
       <c r="N32" t="n">
-        <v>46355237626</v>
+        <v>45903161040</v>
       </c>
     </row>
     <row r="33">
@@ -2112,16 +2112,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>67.09999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="D33" t="n">
-        <v>2666</v>
+        <v>2640</v>
       </c>
       <c r="E33" t="n">
         <v>1170</v>
       </c>
       <c r="F33" t="n">
-        <v>127.9</v>
+        <v>125.6</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>31108000000</v>
       </c>
       <c r="N33" t="n">
-        <v>46355237626</v>
+        <v>45903161040</v>
       </c>
     </row>
     <row r="34">
@@ -2164,16 +2164,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="D34" t="n">
-        <v>2869</v>
+        <v>2859.5</v>
       </c>
       <c r="E34" t="n">
         <v>2381.523440544182</v>
       </c>
       <c r="F34" t="n">
-        <v>20.5</v>
+        <v>20.1</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>168696000000</v>
       </c>
       <c r="N34" t="n">
-        <v>509507692479</v>
+        <v>507820580914</v>
       </c>
     </row>
     <row r="35">
@@ -2216,16 +2216,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>80.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>2564</v>
+        <v>2543</v>
       </c>
       <c r="E35" t="n">
-        <v>2939.562915943684</v>
+        <v>2987.584858837727</v>
       </c>
       <c r="F35" t="n">
-        <v>-12.8</v>
+        <v>-14.9</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -2253,863 +2253,863 @@
         <v>108430000000</v>
       </c>
       <c r="N35" t="n">
-        <v>134268690576</v>
+        <v>133168986012</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>イワブチ株式会社</t>
+          <t>ガンホー・オンライン・エンターテイメント株式会社</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5983</t>
+          <t>3765</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>46.2</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>14130</v>
+        <v>2543</v>
       </c>
       <c r="E36" t="n">
-        <v>7040.15625</v>
+        <v>3016.088716673414</v>
       </c>
       <c r="F36" t="n">
-        <v>100.7</v>
+        <v>-15.7</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>5250258000</v>
+        <v>102086000000</v>
       </c>
       <c r="J36" t="n">
-        <v>1349641000</v>
+        <v>1326000000</v>
       </c>
       <c r="K36" t="n">
-        <v>200000000</v>
+        <v>5018000000</v>
       </c>
       <c r="L36" t="n">
-        <v>18087189000</v>
+        <v>118672000000</v>
       </c>
       <c r="M36" t="n">
-        <v>6799899000</v>
+        <v>108430000000</v>
       </c>
       <c r="N36" t="n">
-        <v>14717341710</v>
+        <v>133168986012</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>イワブチ株式会社</t>
+          <t>ガンホー・オンライン・エンターテイメント株式会社</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5983</t>
+          <t>3765</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>46.2</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>14130</v>
+        <v>2543</v>
       </c>
       <c r="E37" t="n">
-        <v>7040.15625</v>
+        <v>3016.087384069568</v>
       </c>
       <c r="F37" t="n">
-        <v>100.7</v>
+        <v>-15.7</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5250258000</v>
+        <v>102086000000</v>
       </c>
       <c r="J37" t="n">
-        <v>1349641000</v>
+        <v>1326000000</v>
       </c>
       <c r="K37" t="n">
-        <v>200000000</v>
+        <v>5018000000</v>
       </c>
       <c r="L37" t="n">
-        <v>18087189000</v>
+        <v>118672000000</v>
       </c>
       <c r="M37" t="n">
-        <v>6799899000</v>
+        <v>108430000000</v>
       </c>
       <c r="N37" t="n">
-        <v>14717341710</v>
+        <v>133168986012</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>新家工業株式会社</t>
+          <t>ガンホー・オンライン・エンターテイメント株式会社</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>3765</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>86.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>2762</v>
+        <v>2543</v>
       </c>
       <c r="E38" t="n">
-        <v>4265.455132343447</v>
+        <v>2939.562915943684</v>
       </c>
       <c r="F38" t="n">
-        <v>-35.2</v>
+        <v>-13.5</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>8141000000</v>
+        <v>102086000000</v>
       </c>
       <c r="J38" t="n">
-        <v>5422000000</v>
+        <v>1326000000</v>
       </c>
       <c r="K38" t="n">
-        <v>9306000000</v>
+        <v>5018000000</v>
       </c>
       <c r="L38" t="n">
-        <v>28847000000</v>
+        <v>118672000000</v>
       </c>
       <c r="M38" t="n">
-        <v>22869000000</v>
+        <v>108430000000</v>
       </c>
       <c r="N38" t="n">
-        <v>26332405316</v>
+        <v>133168986012</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>カヤバ株式会社</t>
+          <t>イワブチ株式会社</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>7242</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>33.2</v>
+        <v>46.2</v>
       </c>
       <c r="D39" t="n">
-        <v>4640</v>
+        <v>14130</v>
       </c>
       <c r="E39" t="n">
-        <v>2824.318397803668</v>
+        <v>7040.15625</v>
       </c>
       <c r="F39" t="n">
-        <v>64.3</v>
+        <v>100.7</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>14514000000</v>
+        <v>5250258000</v>
       </c>
       <c r="J39" t="n">
-        <v>27587000000</v>
+        <v>1349641000</v>
       </c>
       <c r="K39" t="n">
-        <v>19874000000</v>
+        <v>200000000</v>
       </c>
       <c r="L39" t="n">
-        <v>86299000000</v>
+        <v>18087189000</v>
       </c>
       <c r="M39" t="n">
-        <v>61975000000</v>
+        <v>6799899000</v>
       </c>
       <c r="N39" t="n">
-        <v>186670239200</v>
+        <v>14717341710</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ニッタ株式会社</t>
+          <t>イワブチ株式会社</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5186</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>29.2</v>
+        <v>46.2</v>
       </c>
       <c r="D40" t="n">
-        <v>6610</v>
+        <v>14130</v>
       </c>
       <c r="E40" t="n">
-        <v>3096.322467304314</v>
+        <v>7040.15625</v>
       </c>
       <c r="F40" t="n">
-        <v>113.5</v>
+        <v>100.7</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>30872000000</v>
+        <v>5250258000</v>
       </c>
       <c r="J40" t="n">
-        <v>15392000000</v>
+        <v>1349641000</v>
       </c>
       <c r="K40" t="n">
-        <v>6697000000</v>
+        <v>200000000</v>
       </c>
       <c r="L40" t="n">
-        <v>119214000000</v>
+        <v>18087189000</v>
       </c>
       <c r="M40" t="n">
-        <v>52961000000</v>
+        <v>6799899000</v>
       </c>
       <c r="N40" t="n">
-        <v>181333253700</v>
+        <v>14717341710</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>東京瓦斯株式会社</t>
+          <t>新家工業株式会社</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>9531</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>23.5</v>
+        <v>87</v>
       </c>
       <c r="D41" t="n">
-        <v>6386</v>
+        <v>2756</v>
       </c>
       <c r="E41" t="n">
-        <v>3322.047887165483</v>
+        <v>4265.455132343447</v>
       </c>
       <c r="F41" t="n">
-        <v>92.2</v>
+        <v>-35.4</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>179699000000</v>
+        <v>8141000000</v>
       </c>
       <c r="J41" t="n">
-        <v>313045000000</v>
+        <v>5422000000</v>
       </c>
       <c r="K41" t="n">
-        <v>103000000</v>
+        <v>9306000000</v>
       </c>
       <c r="L41" t="n">
-        <v>1281150000000</v>
+        <v>28847000000</v>
       </c>
       <c r="M41" t="n">
-        <v>492847000000</v>
+        <v>22869000000</v>
       </c>
       <c r="N41" t="n">
-        <v>2097832597928</v>
+        <v>26275202408</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>株式会社イエローハット</t>
+          <t>カヤバ株式会社</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>9882</t>
+          <t>7242</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>35.4</v>
+        <v>33.1</v>
       </c>
       <c r="D42" t="n">
-        <v>1759</v>
+        <v>4650</v>
       </c>
       <c r="E42" t="n">
-        <v>2112.609181636727</v>
+        <v>2824.318397803668</v>
       </c>
       <c r="F42" t="n">
-        <v>-16.7</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>10902000000</v>
+        <v>14514000000</v>
       </c>
       <c r="J42" t="n">
-        <v>29975000000</v>
+        <v>27587000000</v>
       </c>
       <c r="K42" t="n">
-        <v>11341000000</v>
+        <v>19874000000</v>
       </c>
       <c r="L42" t="n">
-        <v>98298000000</v>
+        <v>86299000000</v>
       </c>
       <c r="M42" t="n">
-        <v>52218000000</v>
+        <v>61975000000</v>
       </c>
       <c r="N42" t="n">
-        <v>147685657590</v>
+        <v>187072545750</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>株式会社インフォマート</t>
+          <t>ニッタ株式会社</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3.7</v>
+        <v>29.2</v>
       </c>
       <c r="D43" t="n">
-        <v>714</v>
+        <v>6610</v>
       </c>
       <c r="E43" t="n">
-        <v>404.9347366248775</v>
+        <v>3096.322467304314</v>
       </c>
       <c r="F43" t="n">
-        <v>76.3</v>
+        <v>113.5</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>6410479000</v>
+        <v>30872000000</v>
       </c>
       <c r="J43" t="n">
-        <v>196639000</v>
+        <v>15392000000</v>
       </c>
       <c r="K43" t="n">
-        <v>437854000</v>
+        <v>6697000000</v>
       </c>
       <c r="L43" t="n">
-        <v>11425263000</v>
+        <v>119214000000</v>
       </c>
       <c r="M43" t="n">
-        <v>7044972000</v>
+        <v>52961000000</v>
       </c>
       <c r="N43" t="n">
-        <v>190342478970</v>
+        <v>181333253700</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ニデック株式会社</t>
+          <t>東京瓦斯株式会社</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6594</t>
+          <t>9531</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>6.8</v>
+        <v>23.7</v>
       </c>
       <c r="D44" t="n">
-        <v>2655</v>
+        <v>6335</v>
       </c>
       <c r="E44" t="n">
-        <v>2220.184278344451</v>
+        <v>3322.047887165483</v>
       </c>
       <c r="F44" t="n">
-        <v>19.6</v>
+        <v>90.7</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>163815000000</v>
+        <v>179699000000</v>
       </c>
       <c r="J44" t="n">
-        <v>17829000000</v>
+        <v>313045000000</v>
       </c>
       <c r="K44" t="n">
-        <v>25472000000</v>
+        <v>103000000</v>
       </c>
       <c r="L44" t="n">
-        <v>298063000000</v>
+        <v>1281150000000</v>
       </c>
       <c r="M44" t="n">
-        <v>207116000000</v>
+        <v>492847000000</v>
       </c>
       <c r="N44" t="n">
-        <v>3043452611925</v>
+        <v>2081078845580</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>株式会社堀場製作所</t>
+          <t>株式会社イエローハット</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>9882</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>21.2</v>
+        <v>35.5</v>
       </c>
       <c r="D45" t="n">
-        <v>21550</v>
+        <v>1752</v>
       </c>
       <c r="E45" t="n">
-        <v>11879.91675437757</v>
+        <v>2112.609181636727</v>
       </c>
       <c r="F45" t="n">
-        <v>81.40000000000001</v>
+        <v>-17.1</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>133938000000</v>
+        <v>10902000000</v>
       </c>
       <c r="J45" t="n">
-        <v>55958000000</v>
+        <v>29975000000</v>
       </c>
       <c r="K45" t="n">
-        <v>2062000000</v>
+        <v>11341000000</v>
       </c>
       <c r="L45" t="n">
-        <v>204493000000</v>
+        <v>98298000000</v>
       </c>
       <c r="M45" t="n">
-        <v>191958000000</v>
+        <v>52218000000</v>
       </c>
       <c r="N45" t="n">
-        <v>905564510250</v>
+        <v>147097937520</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ＫＰＰグループホールディングス株式会社</t>
+          <t>株式会社インフォマート</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>9274</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>75.40000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="D46" t="n">
-        <v>1087</v>
+        <v>712</v>
       </c>
       <c r="E46" t="n">
-        <v>730</v>
+        <v>404.9347366248775</v>
       </c>
       <c r="F46" t="n">
-        <v>48.9</v>
+        <v>75.8</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>22631000000</v>
+        <v>6410479000</v>
       </c>
       <c r="J46" t="n">
-        <v>7793000000</v>
+        <v>196639000</v>
       </c>
       <c r="K46" t="n">
-        <v>19603000000</v>
+        <v>437854000</v>
       </c>
       <c r="L46" t="n">
-        <v>56374000000</v>
+        <v>11425263000</v>
       </c>
       <c r="M46" t="n">
-        <v>50027000000</v>
+        <v>7044972000</v>
       </c>
       <c r="N46" t="n">
-        <v>66365900182</v>
+        <v>189809306760</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NIPPON EXPRESSホールディングス株式会社</t>
+          <t>ニデック株式会社</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>9147</t>
+          <t>6594</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>24.1</v>
+        <v>6.8</v>
       </c>
       <c r="D47" t="n">
-        <v>5435</v>
+        <v>2642</v>
       </c>
       <c r="E47" t="n">
-        <v>3341.42986565678</v>
+        <v>2220.184278344451</v>
       </c>
       <c r="F47" t="n">
-        <v>62.7</v>
+        <v>19</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>274075000000</v>
+        <v>163815000000</v>
       </c>
       <c r="J47" t="n">
-        <v>89000000</v>
+        <v>17829000000</v>
       </c>
       <c r="K47" t="n">
-        <v>36943000000</v>
+        <v>25472000000</v>
       </c>
       <c r="L47" t="n">
-        <v>771274000000</v>
+        <v>298063000000</v>
       </c>
       <c r="M47" t="n">
-        <v>311107000000</v>
+        <v>207116000000</v>
       </c>
       <c r="N47" t="n">
-        <v>1291485858455</v>
+        <v>3028550584070</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ＫＨネオケム株式会社</t>
+          <t>株式会社堀場製作所</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>4189</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>29.2</v>
+        <v>21.2</v>
       </c>
       <c r="D48" t="n">
-        <v>3160</v>
+        <v>21560</v>
       </c>
       <c r="E48" t="n">
-        <v>2550.198980592041</v>
+        <v>11879.91675437757</v>
       </c>
       <c r="F48" t="n">
-        <v>23.9</v>
+        <v>81.5</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>16934000000</v>
+        <v>133938000000</v>
       </c>
       <c r="J48" t="n">
-        <v>8038000000</v>
+        <v>55958000000</v>
       </c>
       <c r="K48" t="n">
-        <v>7370000000</v>
+        <v>2062000000</v>
       </c>
       <c r="L48" t="n">
-        <v>57505000000</v>
+        <v>204493000000</v>
       </c>
       <c r="M48" t="n">
-        <v>32342000000</v>
+        <v>191958000000</v>
       </c>
       <c r="N48" t="n">
-        <v>110656614560</v>
+        <v>905984725800</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>イオンフィナンシャルサービス株式会社</t>
+          <t>ＫＰＰグループホールディングス株式会社</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>8570</t>
+          <t>9274</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>210</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>1647.5</v>
+        <v>1102</v>
       </c>
       <c r="E49" t="n">
-        <v>1288.711724885291</v>
+        <v>730</v>
       </c>
       <c r="F49" t="n">
-        <v>27.8</v>
+        <v>51</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>697628000000</v>
+        <v>22631000000</v>
       </c>
       <c r="J49" t="n">
-        <v>34512000000</v>
+        <v>7793000000</v>
       </c>
       <c r="K49" t="n">
-        <v>14926000000</v>
+        <v>19603000000</v>
       </c>
       <c r="L49" t="n">
-        <v>509055000000</v>
+        <v>56374000000</v>
       </c>
       <c r="M49" t="n">
-        <v>747066000000</v>
+        <v>50027000000</v>
       </c>
       <c r="N49" t="n">
-        <v>355669175018</v>
+        <v>67281712972</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>株式会社フジ・メディア・ホールディングス</t>
+          <t>NIPPON EXPRESSホールディングス株式会社</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>9147</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>66.90000000000001</v>
+        <v>23.9</v>
       </c>
       <c r="D50" t="n">
-        <v>4108</v>
+        <v>5481</v>
       </c>
       <c r="E50" t="n">
-        <v>3141.424011416125</v>
+        <v>3341.42986565678</v>
       </c>
       <c r="F50" t="n">
-        <v>30.8</v>
+        <v>64</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>102598000000</v>
+        <v>274075000000</v>
       </c>
       <c r="J50" t="n">
-        <v>174990000000</v>
+        <v>89000000</v>
       </c>
       <c r="K50" t="n">
-        <v>113991000000</v>
+        <v>36943000000</v>
       </c>
       <c r="L50" t="n">
-        <v>808788000000</v>
+        <v>771274000000</v>
       </c>
       <c r="M50" t="n">
-        <v>391579000000</v>
+        <v>311107000000</v>
       </c>
       <c r="N50" t="n">
-        <v>585371941232</v>
+        <v>1302416557533</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>株式会社フジ・メディア・ホールディングス</t>
+          <t>ＫＨネオケム株式会社</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4189</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>66.90000000000001</v>
+        <v>29</v>
       </c>
       <c r="D51" t="n">
-        <v>4108</v>
+        <v>3185</v>
       </c>
       <c r="E51" t="n">
-        <v>2420</v>
+        <v>2550.198980592041</v>
       </c>
       <c r="F51" t="n">
-        <v>69.8</v>
+        <v>24.9</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>株式会社レノ代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>102598000000</v>
+        <v>16934000000</v>
       </c>
       <c r="J51" t="n">
-        <v>174990000000</v>
+        <v>8038000000</v>
       </c>
       <c r="K51" t="n">
-        <v>113991000000</v>
+        <v>7370000000</v>
       </c>
       <c r="L51" t="n">
-        <v>808788000000</v>
+        <v>57505000000</v>
       </c>
       <c r="M51" t="n">
-        <v>391579000000</v>
+        <v>32342000000</v>
       </c>
       <c r="N51" t="n">
-        <v>585371941232</v>
+        <v>111532062460</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>株式会社クスリのアオキホールディングス</t>
+          <t>イオンフィナンシャルサービス株式会社</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>3549</t>
+          <t>8570</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>41.9</v>
+        <v>210.4</v>
       </c>
       <c r="D52" t="n">
-        <v>4083</v>
+        <v>1645</v>
       </c>
       <c r="E52" t="n">
-        <v>3047.091476167608</v>
+        <v>1288.711724885291</v>
       </c>
       <c r="F52" t="n">
-        <v>34</v>
+        <v>27.6</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -3118,390 +3118,390 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>26348000000</v>
+        <v>697628000000</v>
       </c>
       <c r="J52" t="n">
-        <v>132363000000</v>
+        <v>34512000000</v>
       </c>
       <c r="K52" t="n">
-        <v>3747000000</v>
+        <v>14926000000</v>
       </c>
       <c r="L52" t="n">
-        <v>86930000000</v>
+        <v>509055000000</v>
       </c>
       <c r="M52" t="n">
-        <v>162458000000</v>
+        <v>747066000000</v>
       </c>
       <c r="N52" t="n">
-        <v>387734202561</v>
+        <v>355129464585</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>リンナイ株式会社</t>
+          <t>株式会社フジ・メディア・ホールディングス</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>45.3</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="D53" t="n">
-        <v>3497</v>
+        <v>4109</v>
       </c>
       <c r="E53" t="n">
-        <v>2844.704547285864</v>
+        <v>3141.424011416125</v>
       </c>
       <c r="F53" t="n">
-        <v>22.9</v>
+        <v>30.8</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>147972000000</v>
+        <v>102598000000</v>
       </c>
       <c r="J53" t="n">
-        <v>64736000000</v>
+        <v>174990000000</v>
       </c>
       <c r="K53" t="n">
-        <v>5967000000</v>
+        <v>113991000000</v>
       </c>
       <c r="L53" t="n">
-        <v>378856000000</v>
+        <v>808788000000</v>
       </c>
       <c r="M53" t="n">
-        <v>218675000000</v>
+        <v>391579000000</v>
       </c>
       <c r="N53" t="n">
-        <v>482829433164</v>
+        <v>585514436836</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>センコーグループホールディングス株式会社</t>
+          <t>株式会社フジ・メディア・ホールディングス</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>9069</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>54.4</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>2278.5</v>
+        <v>4109</v>
       </c>
       <c r="E54" t="n">
-        <v>1556.090471804319</v>
+        <v>2420</v>
       </c>
       <c r="F54" t="n">
-        <v>46.4</v>
+        <v>69.8</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社レノ代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>42193000000</v>
+        <v>102598000000</v>
       </c>
       <c r="J54" t="n">
-        <v>138228000000</v>
+        <v>174990000000</v>
       </c>
       <c r="K54" t="n">
-        <v>27045000000</v>
+        <v>113991000000</v>
       </c>
       <c r="L54" t="n">
-        <v>160854000000</v>
+        <v>808788000000</v>
       </c>
       <c r="M54" t="n">
-        <v>207466000000</v>
+        <v>391579000000</v>
       </c>
       <c r="N54" t="n">
-        <v>381463291492</v>
+        <v>585514436836</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ブロードメディア株式会社</t>
+          <t>株式会社クスリのアオキホールディングス</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>3549</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>46.4</v>
+        <v>42.2</v>
       </c>
       <c r="D55" t="n">
-        <v>1823</v>
+        <v>4057</v>
       </c>
       <c r="E55" t="n">
-        <v>1529.631984751819</v>
+        <v>3047.091476167608</v>
       </c>
       <c r="F55" t="n">
-        <v>19.2</v>
+        <v>33.1</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5301579000</v>
+        <v>26348000000</v>
       </c>
       <c r="J55" t="n">
-        <v>553048000</v>
+        <v>132363000000</v>
       </c>
       <c r="K55" t="n">
-        <v>169455000</v>
+        <v>3747000000</v>
       </c>
       <c r="L55" t="n">
-        <v>4610613000</v>
+        <v>86930000000</v>
       </c>
       <c r="M55" t="n">
-        <v>6024082000</v>
+        <v>162458000000</v>
       </c>
       <c r="N55" t="n">
-        <v>12992829087</v>
+        <v>385265162819</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ブロードメディア株式会社</t>
+          <t>リンナイ株式会社</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>5947</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>46.4</v>
+        <v>45.8</v>
       </c>
       <c r="D56" t="n">
-        <v>1823</v>
+        <v>3461</v>
       </c>
       <c r="E56" t="n">
-        <v>1449.995380693296</v>
+        <v>2844.704547285864</v>
       </c>
       <c r="F56" t="n">
-        <v>25.7</v>
+        <v>21.7</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5301579000</v>
+        <v>147972000000</v>
       </c>
       <c r="J56" t="n">
-        <v>553048000</v>
+        <v>64736000000</v>
       </c>
       <c r="K56" t="n">
-        <v>169455000</v>
+        <v>5967000000</v>
       </c>
       <c r="L56" t="n">
-        <v>4610613000</v>
+        <v>378856000000</v>
       </c>
       <c r="M56" t="n">
-        <v>6024082000</v>
+        <v>218675000000</v>
       </c>
       <c r="N56" t="n">
-        <v>12992829087</v>
+        <v>477858927132</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>株式会社ニップン</t>
+          <t>センコーグループホールディングス株式会社</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>9069</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>66.40000000000001</v>
+        <v>54.1</v>
       </c>
       <c r="D57" t="n">
-        <v>3010</v>
+        <v>2288.5</v>
       </c>
       <c r="E57" t="n">
-        <v>2723.418631349517</v>
+        <v>1556.090471804319</v>
       </c>
       <c r="F57" t="n">
-        <v>10.5</v>
+        <v>47.1</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>31215000000</v>
+        <v>42193000000</v>
       </c>
       <c r="J57" t="n">
-        <v>48537000000</v>
+        <v>138228000000</v>
       </c>
       <c r="K57" t="n">
-        <v>85530000000</v>
+        <v>27045000000</v>
       </c>
       <c r="L57" t="n">
-        <v>178697000000</v>
+        <v>160854000000</v>
       </c>
       <c r="M57" t="n">
-        <v>165282000000</v>
+        <v>207466000000</v>
       </c>
       <c r="N57" t="n">
-        <v>248820247340</v>
+        <v>383137477542</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>株式会社ニップン</t>
+          <t>ブロードメディア株式会社</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>66.40000000000001</v>
+        <v>45.9</v>
       </c>
       <c r="D58" t="n">
-        <v>3010</v>
+        <v>1843</v>
       </c>
       <c r="E58" t="n">
-        <v>2709.132103263819</v>
+        <v>1529.631984751819</v>
       </c>
       <c r="F58" t="n">
-        <v>11.1</v>
+        <v>20.5</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>31215000000</v>
+        <v>5301579000</v>
       </c>
       <c r="J58" t="n">
-        <v>48537000000</v>
+        <v>553048000</v>
       </c>
       <c r="K58" t="n">
-        <v>85530000000</v>
+        <v>169455000</v>
       </c>
       <c r="L58" t="n">
-        <v>178697000000</v>
+        <v>4610613000</v>
       </c>
       <c r="M58" t="n">
-        <v>165282000000</v>
+        <v>6024082000</v>
       </c>
       <c r="N58" t="n">
-        <v>248820247340</v>
+        <v>13135372467</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>株式会社ニップン</t>
+          <t>ブロードメディア株式会社</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>66.40000000000001</v>
+        <v>45.9</v>
       </c>
       <c r="D59" t="n">
-        <v>3010</v>
+        <v>1843</v>
       </c>
       <c r="E59" t="n">
-        <v>2696.128808062088</v>
+        <v>1449.995380693296</v>
       </c>
       <c r="F59" t="n">
-        <v>11.6</v>
+        <v>27.1</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>31215000000</v>
+        <v>5301579000</v>
       </c>
       <c r="J59" t="n">
-        <v>48537000000</v>
+        <v>553048000</v>
       </c>
       <c r="K59" t="n">
-        <v>85530000000</v>
+        <v>169455000</v>
       </c>
       <c r="L59" t="n">
-        <v>178697000000</v>
+        <v>4610613000</v>
       </c>
       <c r="M59" t="n">
-        <v>165282000000</v>
+        <v>6024082000</v>
       </c>
       <c r="N59" t="n">
-        <v>248820247340</v>
+        <v>13135372467</v>
       </c>
     </row>
     <row r="60">
@@ -3516,16 +3516,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>66.40000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="D60" t="n">
-        <v>3010</v>
+        <v>2994</v>
       </c>
       <c r="E60" t="n">
-        <v>2696.128808062088</v>
+        <v>2723.418631349517</v>
       </c>
       <c r="F60" t="n">
-        <v>11.6</v>
+        <v>9.9</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="I60" t="n">
@@ -3553,187 +3553,187 @@
         <v>165282000000</v>
       </c>
       <c r="N60" t="n">
-        <v>248820247340</v>
+        <v>247497614796</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>京浜急行電鉄株式会社</t>
+          <t>株式会社ニップン</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>119.1</v>
+        <v>66.8</v>
       </c>
       <c r="D61" t="n">
-        <v>1572</v>
+        <v>2994</v>
       </c>
       <c r="E61" t="n">
-        <v>1160.8</v>
+        <v>2709.132103263819</v>
       </c>
       <c r="F61" t="n">
-        <v>35.4</v>
+        <v>10.5</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>61234000000</v>
+        <v>31215000000</v>
       </c>
       <c r="J61" t="n">
-        <v>318113000000</v>
+        <v>48537000000</v>
       </c>
       <c r="K61" t="n">
-        <v>114136000000</v>
+        <v>85530000000</v>
       </c>
       <c r="L61" t="n">
-        <v>256898000000</v>
+        <v>178697000000</v>
       </c>
       <c r="M61" t="n">
-        <v>493483000000</v>
+        <v>165282000000</v>
       </c>
       <c r="N61" t="n">
-        <v>414232188132</v>
+        <v>247497614796</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>あいホールディングス株式会社</t>
+          <t>株式会社ニップン</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>3076</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>23.3</v>
+        <v>66.8</v>
       </c>
       <c r="D62" t="n">
-        <v>2996</v>
+        <v>2994</v>
       </c>
       <c r="E62" t="n">
-        <v>2007.754513143541</v>
+        <v>2696.128808062088</v>
       </c>
       <c r="F62" t="n">
-        <v>49.2</v>
+        <v>11</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>32012000000</v>
+        <v>31215000000</v>
       </c>
       <c r="J62" t="n">
-        <v>1646000000</v>
+        <v>48537000000</v>
       </c>
       <c r="K62" t="n">
-        <v>3550000000</v>
+        <v>85530000000</v>
       </c>
       <c r="L62" t="n">
-        <v>53765000000</v>
+        <v>178697000000</v>
       </c>
       <c r="M62" t="n">
-        <v>37208000000</v>
+        <v>165282000000</v>
       </c>
       <c r="N62" t="n">
-        <v>159605701276</v>
+        <v>247497614796</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>エア・ウォーター株式会社</t>
+          <t>株式会社ニップン</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>15</v>
+        <v>66.8</v>
       </c>
       <c r="D63" t="n">
-        <v>2972</v>
+        <v>2994</v>
       </c>
       <c r="E63" t="n">
-        <v>2261.880826568852</v>
+        <v>2696.128808062088</v>
       </c>
       <c r="F63" t="n">
-        <v>31.4</v>
+        <v>11</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>29189000000</v>
+        <v>31215000000</v>
       </c>
       <c r="J63" t="n">
-        <v>31318000000</v>
+        <v>48537000000</v>
       </c>
       <c r="K63" t="n">
-        <v>42001000000</v>
+        <v>85530000000</v>
       </c>
       <c r="L63" t="n">
-        <v>194657000000</v>
+        <v>178697000000</v>
       </c>
       <c r="M63" t="n">
-        <v>102508000000</v>
+        <v>165282000000</v>
       </c>
       <c r="N63" t="n">
-        <v>681372289996</v>
+        <v>247497614796</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>エア・ウォーター株式会社</t>
+          <t>京浜急行電鉄株式会社</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>15</v>
+        <v>118.9</v>
       </c>
       <c r="D64" t="n">
-        <v>2972</v>
+        <v>1574.5</v>
       </c>
       <c r="E64" t="n">
-        <v>1970</v>
+        <v>1160.8</v>
       </c>
       <c r="F64" t="n">
-        <v>50.9</v>
+        <v>35.6</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3742,1182 +3742,1182 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>29189000000</v>
+        <v>61234000000</v>
       </c>
       <c r="J64" t="n">
-        <v>31318000000</v>
+        <v>318113000000</v>
       </c>
       <c r="K64" t="n">
-        <v>42001000000</v>
+        <v>114136000000</v>
       </c>
       <c r="L64" t="n">
-        <v>194657000000</v>
+        <v>256898000000</v>
       </c>
       <c r="M64" t="n">
-        <v>102508000000</v>
+        <v>493483000000</v>
       </c>
       <c r="N64" t="n">
-        <v>681372289996</v>
+        <v>414890954334</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>株式会社電通総研</t>
+          <t>あいホールディングス株式会社</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>9.6</v>
+        <v>23.5</v>
       </c>
       <c r="D65" t="n">
-        <v>2864</v>
+        <v>2967</v>
       </c>
       <c r="E65" t="n">
-        <v>1910.426979628923</v>
+        <v>2007.754513143541</v>
       </c>
       <c r="F65" t="n">
-        <v>49.9</v>
+        <v>47.8</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>49748000000</v>
+        <v>32012000000</v>
       </c>
       <c r="J65" t="n">
-        <v>524000000</v>
+        <v>1646000000</v>
       </c>
       <c r="K65" t="n">
-        <v>3388000000</v>
+        <v>3550000000</v>
       </c>
       <c r="L65" t="n">
-        <v>65471000000</v>
+        <v>53765000000</v>
       </c>
       <c r="M65" t="n">
-        <v>53660000000</v>
+        <v>37208000000</v>
       </c>
       <c r="N65" t="n">
-        <v>558995869408</v>
+        <v>158060786277</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>わかもと製薬株式会社</t>
+          <t>エア・ウォーター株式会社</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>50.1</v>
+        <v>14.9</v>
       </c>
       <c r="D66" t="n">
-        <v>297</v>
+        <v>3000</v>
       </c>
       <c r="E66" t="n">
-        <v>290.3401328717133</v>
+        <v>2261.880826568852</v>
       </c>
       <c r="F66" t="n">
-        <v>2.3</v>
+        <v>32.6</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3231889000</v>
+        <v>29189000000</v>
       </c>
       <c r="J66" t="n">
-        <v>82947000</v>
+        <v>31318000000</v>
       </c>
       <c r="K66" t="n">
-        <v>1847919000</v>
+        <v>42001000000</v>
       </c>
       <c r="L66" t="n">
-        <v>11480803000</v>
+        <v>194657000000</v>
       </c>
       <c r="M66" t="n">
-        <v>5162755000</v>
+        <v>102508000000</v>
       </c>
       <c r="N66" t="n">
-        <v>10307634183</v>
+        <v>687791679000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>株式会社豊田自動織機</t>
+          <t>エア・ウォーター株式会社</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>6201</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
+          <t>4088</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="D67" t="n">
+        <v>3000</v>
+      </c>
       <c r="E67" t="n">
-        <v>16430.4430802409</v>
-      </c>
-      <c r="F67" t="inlineStr"/>
+        <v>1970</v>
+      </c>
+      <c r="F67" t="n">
+        <v>52.3</v>
+      </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>281605000000</v>
+        <v>29189000000</v>
       </c>
       <c r="J67" t="n">
-        <v>87540000000</v>
+        <v>31318000000</v>
       </c>
       <c r="K67" t="n">
-        <v>730709000000</v>
+        <v>42001000000</v>
       </c>
       <c r="L67" t="n">
-        <v>3246174000000</v>
+        <v>194657000000</v>
       </c>
       <c r="M67" t="n">
-        <v>1099854000000</v>
-      </c>
-      <c r="N67" t="inlineStr"/>
+        <v>102508000000</v>
+      </c>
+      <c r="N67" t="n">
+        <v>687791679000</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>株式会社豊田自動織機</t>
+          <t>株式会社電通総研</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>6201</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
+          <t>4812</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="D68" t="n">
+        <v>2864</v>
+      </c>
       <c r="E68" t="n">
-        <v>16430443.10823975</v>
-      </c>
-      <c r="F68" t="inlineStr"/>
+        <v>1910.426979628923</v>
+      </c>
+      <c r="F68" t="n">
+        <v>49.9</v>
+      </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>281605000000</v>
+        <v>49748000000</v>
       </c>
       <c r="J68" t="n">
-        <v>87540000000</v>
+        <v>524000000</v>
       </c>
       <c r="K68" t="n">
-        <v>730709000000</v>
+        <v>3388000000</v>
       </c>
       <c r="L68" t="n">
-        <v>3246174000000</v>
+        <v>65471000000</v>
       </c>
       <c r="M68" t="n">
-        <v>1099854000000</v>
-      </c>
-      <c r="N68" t="inlineStr"/>
+        <v>53660000000</v>
+      </c>
+      <c r="N68" t="n">
+        <v>558995869408</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>大阪製鐵株式会社</t>
+          <t>わかもと製薬株式会社</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>4512</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>92.40000000000001</v>
+        <v>49.3</v>
       </c>
       <c r="D69" t="n">
-        <v>2610</v>
+        <v>302</v>
       </c>
       <c r="E69" t="n">
-        <v>1748.071046781136</v>
+        <v>290.3401328717133</v>
       </c>
       <c r="F69" t="n">
-        <v>49.3</v>
+        <v>4</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>62396000000</v>
+        <v>3231889000</v>
       </c>
       <c r="J69" t="n">
-        <v>9241000000</v>
+        <v>82947000</v>
       </c>
       <c r="K69" t="n">
-        <v>553000000</v>
+        <v>1847919000</v>
       </c>
       <c r="L69" t="n">
-        <v>151028000000</v>
+        <v>11480803000</v>
       </c>
       <c r="M69" t="n">
-        <v>72190000000</v>
+        <v>5162755000</v>
       </c>
       <c r="N69" t="n">
-        <v>78087386790</v>
+        <v>10481163378</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>株式会社ディー・エヌ・エー</t>
+          <t>株式会社豊田自動織機</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2432</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="D70" t="n">
-        <v>2552</v>
-      </c>
+          <t>6201</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="n">
-        <v>2551.08574256026</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
+        <v>16430.4430802409</v>
+      </c>
+      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>85363000000</v>
+        <v>281605000000</v>
       </c>
       <c r="J70" t="n">
-        <v>221000000</v>
+        <v>87540000000</v>
       </c>
       <c r="K70" t="n">
-        <v>93552000000</v>
+        <v>730709000000</v>
       </c>
       <c r="L70" t="n">
-        <v>177857000000</v>
+        <v>3246174000000</v>
       </c>
       <c r="M70" t="n">
-        <v>179136000000</v>
-      </c>
-      <c r="N70" t="n">
-        <v>236089707832</v>
-      </c>
+        <v>1099854000000</v>
+      </c>
+      <c r="N70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>株式会社ディー・エヌ・エー</t>
+          <t>株式会社豊田自動織機</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2432</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="D71" t="n">
-        <v>2552</v>
-      </c>
+          <t>6201</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="n">
-        <v>2260</v>
-      </c>
-      <c r="F71" t="n">
-        <v>12.9</v>
-      </c>
+        <v>16430443.10823975</v>
+      </c>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>85363000000</v>
+        <v>281605000000</v>
       </c>
       <c r="J71" t="n">
-        <v>221000000</v>
+        <v>87540000000</v>
       </c>
       <c r="K71" t="n">
-        <v>93552000000</v>
+        <v>730709000000</v>
       </c>
       <c r="L71" t="n">
-        <v>177857000000</v>
+        <v>3246174000000</v>
       </c>
       <c r="M71" t="n">
-        <v>179136000000</v>
-      </c>
-      <c r="N71" t="n">
-        <v>236089707832</v>
-      </c>
+        <v>1099854000000</v>
+      </c>
+      <c r="N71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>株式会社ディー・エヌ・エー</t>
+          <t>大阪製鐵株式会社</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>5449</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>75.90000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="D72" t="n">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="E72" t="n">
-        <v>2260</v>
+        <v>1748.071046781136</v>
       </c>
       <c r="F72" t="n">
-        <v>12.9</v>
+        <v>45.9</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>85363000000</v>
+        <v>62396000000</v>
       </c>
       <c r="J72" t="n">
-        <v>221000000</v>
+        <v>9241000000</v>
       </c>
       <c r="K72" t="n">
-        <v>93552000000</v>
+        <v>553000000</v>
       </c>
       <c r="L72" t="n">
-        <v>177857000000</v>
+        <v>151028000000</v>
       </c>
       <c r="M72" t="n">
-        <v>179136000000</v>
+        <v>72190000000</v>
       </c>
       <c r="N72" t="n">
-        <v>236089707832</v>
+        <v>76322192989</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>株式会社オリエントコーポレーション</t>
+          <t>株式会社ディー・エヌ・エー</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>8585</t>
+          <t>2432</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>304.7</v>
+        <v>75.7</v>
       </c>
       <c r="D73" t="n">
-        <v>861</v>
+        <v>2558.5</v>
       </c>
       <c r="E73" t="n">
-        <v>798.3805136422309</v>
+        <v>2551.08574256026</v>
       </c>
       <c r="F73" t="n">
-        <v>7.8</v>
+        <v>0.3</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>408187000000</v>
+        <v>85363000000</v>
       </c>
       <c r="J73" t="n">
-        <v>18930000000</v>
+        <v>221000000</v>
       </c>
       <c r="K73" t="n">
-        <v>21921000000</v>
+        <v>93552000000</v>
       </c>
       <c r="L73" t="n">
-        <v>216837000000</v>
+        <v>177857000000</v>
       </c>
       <c r="M73" t="n">
-        <v>449038000000</v>
+        <v>179136000000</v>
       </c>
       <c r="N73" t="n">
-        <v>147391028904</v>
+        <v>236691033498</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>東ソー株式会社</t>
+          <t>株式会社ディー・エヌ・エー</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>4042</t>
+          <t>2432</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>43.5</v>
+        <v>75.7</v>
       </c>
       <c r="D74" t="n">
-        <v>2541</v>
+        <v>2558.5</v>
       </c>
       <c r="E74" t="n">
-        <v>2032.365850102071</v>
+        <v>2260</v>
       </c>
       <c r="F74" t="n">
-        <v>25</v>
+        <v>13.2</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>160812000000</v>
+        <v>85363000000</v>
       </c>
       <c r="J74" t="n">
-        <v>109648000000</v>
+        <v>221000000</v>
       </c>
       <c r="K74" t="n">
-        <v>70132000000</v>
+        <v>93552000000</v>
       </c>
       <c r="L74" t="n">
-        <v>759724000000</v>
+        <v>177857000000</v>
       </c>
       <c r="M74" t="n">
-        <v>340592000000</v>
+        <v>179136000000</v>
       </c>
       <c r="N74" t="n">
-        <v>782349877386</v>
+        <v>236691033498</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>株式会社西武ホールディングス</t>
+          <t>株式会社ディー・エヌ・エー</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>2432</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>61.6</v>
+        <v>75.7</v>
       </c>
       <c r="D75" t="n">
-        <v>3609</v>
+        <v>2558.5</v>
       </c>
       <c r="E75" t="n">
-        <v>1716.713876475349</v>
+        <v>2260</v>
       </c>
       <c r="F75" t="n">
-        <v>110.2</v>
+        <v>13.2</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>87210000000</v>
+        <v>85363000000</v>
       </c>
       <c r="J75" t="n">
-        <v>428181000000</v>
+        <v>221000000</v>
       </c>
       <c r="K75" t="n">
-        <v>49954000000</v>
+        <v>93552000000</v>
       </c>
       <c r="L75" t="n">
-        <v>387217000000</v>
+        <v>177857000000</v>
       </c>
       <c r="M75" t="n">
-        <v>565345000000</v>
+        <v>179136000000</v>
       </c>
       <c r="N75" t="n">
-        <v>917327636892</v>
+        <v>236691033498</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>株式会社オリエントコーポレーション</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>8585</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>307.5</v>
+      </c>
+      <c r="D76" t="n">
+        <v>853</v>
+      </c>
+      <c r="E76" t="n">
+        <v>798.3805136422309</v>
+      </c>
+      <c r="F76" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>株式会社ストラテジックキャピタル</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>408187000000</v>
+      </c>
+      <c r="J76" t="n">
+        <v>18930000000</v>
+      </c>
+      <c r="K76" t="n">
+        <v>21921000000</v>
+      </c>
+      <c r="L76" t="n">
+        <v>216837000000</v>
+      </c>
+      <c r="M76" t="n">
+        <v>449038000000</v>
+      </c>
+      <c r="N76" t="n">
+        <v>146021541992</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>東ソー株式会社</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>4042</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="D77" t="n">
+        <v>2561</v>
+      </c>
+      <c r="E77" t="n">
+        <v>2032.365850102071</v>
+      </c>
+      <c r="F77" t="n">
+        <v>26</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>2024-06-04</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>160812000000</v>
+      </c>
+      <c r="J77" t="n">
+        <v>109648000000</v>
+      </c>
+      <c r="K77" t="n">
+        <v>70132000000</v>
+      </c>
+      <c r="L77" t="n">
+        <v>759724000000</v>
+      </c>
+      <c r="M77" t="n">
+        <v>340592000000</v>
+      </c>
+      <c r="N77" t="n">
+        <v>788507688306</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>株式会社西武ホールディングス</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>9024</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="D78" t="n">
+        <v>3494</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1716.713876475349</v>
+      </c>
+      <c r="F78" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>87210000000</v>
+      </c>
+      <c r="J78" t="n">
+        <v>428181000000</v>
+      </c>
+      <c r="K78" t="n">
+        <v>49954000000</v>
+      </c>
+      <c r="L78" t="n">
+        <v>387217000000</v>
+      </c>
+      <c r="M78" t="n">
+        <v>565345000000</v>
+      </c>
+      <c r="N78" t="n">
+        <v>888097191272</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
           <t>株式会社フェローテック
 （旧会社名　株式会社フェローテックホールディングス）</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>6890</t>
         </is>
       </c>
-      <c r="C76" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="D76" t="n">
-        <v>8600</v>
-      </c>
-      <c r="E76" t="n">
+      <c r="C79" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="D79" t="n">
+        <v>8760</v>
+      </c>
+      <c r="E79" t="n">
         <v>4037.502552255647</v>
       </c>
-      <c r="F76" t="n">
-        <v>113</v>
-      </c>
-      <c r="G76" t="inlineStr">
+      <c r="F79" t="n">
+        <v>117</v>
+      </c>
+      <c r="G79" t="inlineStr">
         <is>
           <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="I76" t="n">
+      <c r="I79" t="n">
         <v>52579000000</v>
       </c>
-      <c r="J76" t="n">
+      <c r="J79" t="n">
         <v>90505000000</v>
       </c>
-      <c r="K76" t="n">
+      <c r="K79" t="n">
         <v>11654000000</v>
       </c>
-      <c r="L76" t="n">
+      <c r="L79" t="n">
         <v>160957000000</v>
       </c>
-      <c r="M76" t="n">
+      <c r="M79" t="n">
         <v>154738000000</v>
       </c>
-      <c r="N76" t="n">
-        <v>462712361800</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="N79" t="n">
+        <v>471320963880</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>株式会社フェローテック
 （旧会社名　株式会社フェローテックホールディングス）</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>6890</t>
         </is>
       </c>
-      <c r="C77" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="D77" t="n">
-        <v>8600</v>
-      </c>
-      <c r="E77" t="n">
+      <c r="C80" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="D80" t="n">
+        <v>8760</v>
+      </c>
+      <c r="E80" t="n">
         <v>3950.736048458928</v>
       </c>
-      <c r="F77" t="n">
-        <v>117.7</v>
-      </c>
-      <c r="G77" t="inlineStr">
+      <c r="F80" t="n">
+        <v>121.7</v>
+      </c>
+      <c r="G80" t="inlineStr">
         <is>
           <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="I77" t="n">
+      <c r="I80" t="n">
         <v>52579000000</v>
       </c>
-      <c r="J77" t="n">
+      <c r="J80" t="n">
         <v>90505000000</v>
       </c>
-      <c r="K77" t="n">
+      <c r="K80" t="n">
         <v>11654000000</v>
       </c>
-      <c r="L77" t="n">
+      <c r="L80" t="n">
         <v>160957000000</v>
       </c>
-      <c r="M77" t="n">
+      <c r="M80" t="n">
         <v>154738000000</v>
       </c>
-      <c r="N77" t="n">
-        <v>462712361800</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="N80" t="n">
+        <v>471320963880</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>株式会社フェローテック
 （旧会社名　株式会社フェローテックホールディングス）</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>6890</t>
         </is>
       </c>
-      <c r="C78" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="D78" t="n">
-        <v>8600</v>
-      </c>
-      <c r="E78" t="n">
+      <c r="C81" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="D81" t="n">
+        <v>8760</v>
+      </c>
+      <c r="E81" t="n">
         <v>2030</v>
       </c>
-      <c r="F78" t="n">
-        <v>323.6</v>
-      </c>
-      <c r="G78" t="inlineStr">
+      <c r="F81" t="n">
+        <v>331.5</v>
+      </c>
+      <c r="G81" t="inlineStr">
         <is>
           <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>2025-10-22</t>
         </is>
       </c>
-      <c r="I78" t="n">
+      <c r="I81" t="n">
         <v>52579000000</v>
       </c>
-      <c r="J78" t="n">
+      <c r="J81" t="n">
         <v>90505000000</v>
       </c>
-      <c r="K78" t="n">
+      <c r="K81" t="n">
         <v>11654000000</v>
       </c>
-      <c r="L78" t="n">
+      <c r="L81" t="n">
         <v>160957000000</v>
       </c>
-      <c r="M78" t="n">
+      <c r="M81" t="n">
         <v>154738000000</v>
       </c>
-      <c r="N78" t="n">
-        <v>462712361800</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="N81" t="n">
+        <v>471320963880</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>株式会社フェローテック
 （旧会社名　株式会社フェローテックホールディングス）</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>6890</t>
         </is>
       </c>
-      <c r="C79" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="D79" t="n">
-        <v>8600</v>
-      </c>
-      <c r="E79" t="n">
+      <c r="C82" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="D82" t="n">
+        <v>8760</v>
+      </c>
+      <c r="E82" t="n">
         <v>2387</v>
       </c>
-      <c r="F79" t="n">
-        <v>260.3</v>
-      </c>
-      <c r="G79" t="inlineStr">
+      <c r="F82" t="n">
+        <v>267</v>
+      </c>
+      <c r="G82" t="inlineStr">
         <is>
           <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>2025-03-07</t>
         </is>
       </c>
-      <c r="I79" t="n">
+      <c r="I82" t="n">
         <v>52579000000</v>
       </c>
-      <c r="J79" t="n">
+      <c r="J82" t="n">
         <v>90505000000</v>
       </c>
-      <c r="K79" t="n">
+      <c r="K82" t="n">
         <v>11654000000</v>
       </c>
-      <c r="L79" t="n">
+      <c r="L82" t="n">
         <v>160957000000</v>
       </c>
-      <c r="M79" t="n">
+      <c r="M82" t="n">
         <v>154738000000</v>
       </c>
-      <c r="N79" t="n">
-        <v>462712361800</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>アツギ株式会社</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>3529</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="D80" t="n">
-        <v>1027</v>
-      </c>
-      <c r="E80" t="n">
-        <v>668.9358717434869</v>
-      </c>
-      <c r="F80" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="I80" t="n">
-        <v>5500000000</v>
-      </c>
-      <c r="J80" t="n">
-        <v>3208000000</v>
-      </c>
-      <c r="K80" t="n">
-        <v>3702000000</v>
-      </c>
-      <c r="L80" t="n">
-        <v>32145000000</v>
-      </c>
-      <c r="M80" t="n">
-        <v>12410000000</v>
-      </c>
-      <c r="N80" t="n">
-        <v>16446384162</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>日本特殊塗料株式会社</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>4619</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="D81" t="n">
-        <v>2625</v>
-      </c>
-      <c r="E81" t="n">
-        <v>1190</v>
-      </c>
-      <c r="F81" t="n">
-        <v>120.6</v>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="I81" t="n">
-        <v>8931000000</v>
-      </c>
-      <c r="J81" t="n">
-        <v>9514000000</v>
-      </c>
-      <c r="K81" t="n">
-        <v>22055000000</v>
-      </c>
-      <c r="L81" t="n">
-        <v>49725000000</v>
-      </c>
-      <c r="M81" t="n">
-        <v>40500000000</v>
-      </c>
-      <c r="N81" t="n">
-        <v>55891098375</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>株式会社エクセディ</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>7278</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="D82" t="n">
-        <v>5900</v>
-      </c>
-      <c r="E82" t="n">
-        <v>2617.980935875217</v>
-      </c>
-      <c r="F82" t="n">
-        <v>125.4</v>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="I82" t="n">
-        <v>30019000000</v>
-      </c>
-      <c r="J82" t="n">
-        <v>6792000000</v>
-      </c>
-      <c r="K82" t="n">
-        <v>3427000000</v>
-      </c>
-      <c r="L82" t="n">
-        <v>119460000000</v>
-      </c>
-      <c r="M82" t="n">
-        <v>40238000000</v>
-      </c>
       <c r="N82" t="n">
-        <v>211182039400</v>
+        <v>471320963880</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>株式会社Ａ＆Ｄホロンホールディングス</t>
+          <t>アツギ株式会社</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>7745</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>20.1</v>
+        <v>74.2</v>
       </c>
       <c r="D83" t="n">
-        <v>2801</v>
+        <v>1045</v>
       </c>
       <c r="E83" t="n">
-        <v>2084.177692465894</v>
+        <v>668.9358717434869</v>
       </c>
       <c r="F83" t="n">
-        <v>34.4</v>
+        <v>56.2</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>11012000000</v>
+        <v>5500000000</v>
       </c>
       <c r="J83" t="n">
-        <v>4106000000</v>
+        <v>3208000000</v>
       </c>
       <c r="K83" t="n">
-        <v>315000000</v>
+        <v>3702000000</v>
       </c>
       <c r="L83" t="n">
-        <v>27041000000</v>
+        <v>32145000000</v>
       </c>
       <c r="M83" t="n">
-        <v>15433000000</v>
+        <v>12410000000</v>
       </c>
       <c r="N83" t="n">
-        <v>76711886121</v>
+        <v>16734636270</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>株式会社セプテーニ・ホールディングス</t>
+          <t>日本特殊塗料株式会社</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>4293</t>
+          <t>4619</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>13.1</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D84" t="n">
-        <v>512</v>
+        <v>2620</v>
       </c>
       <c r="E84" t="n">
-        <v>448.6811097117532</v>
+        <v>1190</v>
       </c>
       <c r="F84" t="n">
-        <v>14.1</v>
+        <v>120.2</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>12184507000</v>
+        <v>8931000000</v>
       </c>
       <c r="J84" t="n">
-        <v>168073000</v>
+        <v>9514000000</v>
       </c>
       <c r="K84" t="n">
-        <v>1600720000</v>
+        <v>22055000000</v>
       </c>
       <c r="L84" t="n">
-        <v>11861578000</v>
+        <v>49725000000</v>
       </c>
       <c r="M84" t="n">
-        <v>13953300000</v>
+        <v>40500000000</v>
       </c>
       <c r="N84" t="n">
-        <v>106211895808</v>
+        <v>55784639140</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>株式会社シンクロ・フード</t>
+          <t>株式会社エクセディ</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>7278</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>33.6</v>
+        <v>19.1</v>
       </c>
       <c r="D85" t="n">
-        <v>330</v>
+        <v>5880</v>
       </c>
       <c r="E85" t="n">
-        <v>421.6950726175476</v>
+        <v>2617.980935875217</v>
       </c>
       <c r="F85" t="n">
-        <v>-21.7</v>
+        <v>124.6</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3037851000</v>
+        <v>30019000000</v>
       </c>
       <c r="J85" t="n">
-        <v>56852000</v>
+        <v>6792000000</v>
       </c>
       <c r="K85" t="n">
-        <v>14952000</v>
+        <v>3427000000</v>
       </c>
       <c r="L85" t="n">
-        <v>2871237000</v>
+        <v>119460000000</v>
       </c>
       <c r="M85" t="n">
-        <v>3109655000</v>
+        <v>40238000000</v>
       </c>
       <c r="N85" t="n">
-        <v>9254054040</v>
+        <v>210466168080</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>科研製薬株式会社</t>
+          <t>株式会社Ａ＆Ｄホロンホールディングス</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>7745</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>72.2</v>
+        <v>19.9</v>
       </c>
       <c r="D86" t="n">
-        <v>3885</v>
+        <v>2831</v>
       </c>
       <c r="E86" t="n">
-        <v>3530</v>
+        <v>2084.177692465894</v>
       </c>
       <c r="F86" t="n">
-        <v>10.1</v>
+        <v>35.8</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>74625000000</v>
+        <v>11012000000</v>
       </c>
       <c r="J86" t="n">
-        <v>15530000000</v>
+        <v>4106000000</v>
       </c>
       <c r="K86" t="n">
-        <v>15992000000</v>
+        <v>315000000</v>
       </c>
       <c r="L86" t="n">
-        <v>138325000000</v>
+        <v>27041000000</v>
       </c>
       <c r="M86" t="n">
-        <v>106147000000</v>
+        <v>15433000000</v>
       </c>
       <c r="N86" t="n">
-        <v>147118403775</v>
+        <v>77533505751</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>市光工業株式会社</t>
+          <t>株式会社セプテーニ・ホールディングス</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>7244</t>
+          <t>4293</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>35.8</v>
+        <v>13.1</v>
       </c>
       <c r="D87" t="n">
-        <v>554</v>
+        <v>513</v>
       </c>
       <c r="E87" t="n">
-        <v>549.4799823005444</v>
+        <v>448.6811097117532</v>
       </c>
       <c r="F87" t="n">
-        <v>0.8</v>
+        <v>14.3</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -4926,414 +4926,414 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>5720000000</v>
+        <v>12184507000</v>
       </c>
       <c r="J87" t="n">
-        <v>9921000000</v>
+        <v>168073000</v>
       </c>
       <c r="K87" t="n">
-        <v>3474000000</v>
+        <v>1600720000</v>
       </c>
       <c r="L87" t="n">
-        <v>49523000000</v>
+        <v>11861578000</v>
       </c>
       <c r="M87" t="n">
-        <v>19115000000</v>
+        <v>13953300000</v>
       </c>
       <c r="N87" t="n">
-        <v>53352643140</v>
+        <v>106419340917</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>トーセイ株式会社</t>
+          <t>株式会社シンクロ・フード</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>46.7</v>
+        <v>33.9</v>
       </c>
       <c r="D88" t="n">
-        <v>1683</v>
+        <v>327</v>
       </c>
       <c r="E88" t="n">
-        <v>1752.426893379333</v>
+        <v>421.6950726175476</v>
       </c>
       <c r="F88" t="n">
-        <v>-4</v>
+        <v>-22.5</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>20753937000</v>
+        <v>3037851000</v>
       </c>
       <c r="J88" t="n">
-        <v>46868512000</v>
+        <v>56852000</v>
       </c>
       <c r="K88" t="n">
-        <v>8610046000</v>
+        <v>14952000</v>
       </c>
       <c r="L88" t="n">
-        <v>59467346000</v>
+        <v>2871237000</v>
       </c>
       <c r="M88" t="n">
-        <v>76232495000</v>
+        <v>3109655000</v>
       </c>
       <c r="N88" t="n">
-        <v>163261266300</v>
+        <v>9169926276</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>トーセイ株式会社</t>
+          <t>科研製薬株式会社</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>4521</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>46.7</v>
+        <v>71.8</v>
       </c>
       <c r="D89" t="n">
-        <v>1683</v>
+        <v>3905</v>
       </c>
       <c r="E89" t="n">
-        <v>1576.721867844292</v>
+        <v>3530</v>
       </c>
       <c r="F89" t="n">
-        <v>6.7</v>
+        <v>10.6</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>20753937000</v>
+        <v>74625000000</v>
       </c>
       <c r="J89" t="n">
-        <v>46868512000</v>
+        <v>15530000000</v>
       </c>
       <c r="K89" t="n">
-        <v>8610046000</v>
+        <v>15992000000</v>
       </c>
       <c r="L89" t="n">
-        <v>59467346000</v>
+        <v>138325000000</v>
       </c>
       <c r="M89" t="n">
-        <v>76232495000</v>
+        <v>106147000000</v>
       </c>
       <c r="N89" t="n">
-        <v>163261266300</v>
+        <v>147875770075</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>株式会社髙島屋</t>
+          <t>市光工業株式会社</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>65.40000000000001</v>
+        <v>35.7</v>
       </c>
       <c r="D90" t="n">
-        <v>2098</v>
+        <v>556</v>
       </c>
       <c r="E90" t="n">
-        <v>1101.400153022188</v>
+        <v>549.4799823005444</v>
       </c>
       <c r="F90" t="n">
-        <v>90.5</v>
+        <v>1.2</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>88996000000</v>
+        <v>5720000000</v>
       </c>
       <c r="J90" t="n">
-        <v>193090000000</v>
+        <v>9921000000</v>
       </c>
       <c r="K90" t="n">
-        <v>119967000000</v>
+        <v>3474000000</v>
       </c>
       <c r="L90" t="n">
-        <v>420489000000</v>
+        <v>49523000000</v>
       </c>
       <c r="M90" t="n">
-        <v>402053000000</v>
+        <v>19115000000</v>
       </c>
       <c r="N90" t="n">
-        <v>614744211200</v>
+        <v>53545251960</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>株式会社髙島屋</t>
+          <t>トーセイ株式会社</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>65.40000000000001</v>
+        <v>47.2</v>
       </c>
       <c r="D91" t="n">
-        <v>2098</v>
+        <v>1665</v>
       </c>
       <c r="E91" t="n">
-        <v>1101.400153022188</v>
+        <v>1752.426893379333</v>
       </c>
       <c r="F91" t="n">
-        <v>90.5</v>
+        <v>-5</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>88996000000</v>
+        <v>20753937000</v>
       </c>
       <c r="J91" t="n">
-        <v>193090000000</v>
+        <v>46868512000</v>
       </c>
       <c r="K91" t="n">
-        <v>119967000000</v>
+        <v>8610046000</v>
       </c>
       <c r="L91" t="n">
-        <v>420489000000</v>
+        <v>59467346000</v>
       </c>
       <c r="M91" t="n">
-        <v>402053000000</v>
+        <v>76232495000</v>
       </c>
       <c r="N91" t="n">
-        <v>614744211200</v>
+        <v>161515156500</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>三井倉庫ホールディングス株式会社</t>
+          <t>トーセイ株式会社</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>9302</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>44.9</v>
+        <v>47.2</v>
       </c>
       <c r="D92" t="n">
-        <v>3347</v>
+        <v>1665</v>
       </c>
       <c r="E92" t="n">
-        <v>1492.806001579363</v>
+        <v>1576.721867844292</v>
       </c>
       <c r="F92" t="n">
-        <v>124.2</v>
+        <v>5.6</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>22822000000</v>
+        <v>20753937000</v>
       </c>
       <c r="J92" t="n">
-        <v>72331000000</v>
+        <v>46868512000</v>
       </c>
       <c r="K92" t="n">
-        <v>17148000000</v>
+        <v>8610046000</v>
       </c>
       <c r="L92" t="n">
-        <v>88631000000</v>
+        <v>59467346000</v>
       </c>
       <c r="M92" t="n">
-        <v>112301000000</v>
+        <v>76232495000</v>
       </c>
       <c r="N92" t="n">
-        <v>250369941895</v>
+        <v>161515156500</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>京阪神ビルディング株式会社</t>
+          <t>株式会社髙島屋</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>8818</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>81.8</v>
+        <v>65.2</v>
       </c>
       <c r="D93" t="n">
-        <v>1110</v>
+        <v>2103</v>
       </c>
       <c r="E93" t="n">
-        <v>1341.977644710579</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="F93" t="n">
-        <v>-17.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>9876000000</v>
+        <v>88996000000</v>
       </c>
       <c r="J93" t="n">
-        <v>54379000000</v>
+        <v>193090000000</v>
       </c>
       <c r="K93" t="n">
-        <v>22399000000</v>
+        <v>119967000000</v>
       </c>
       <c r="L93" t="n">
-        <v>70510000000</v>
+        <v>420489000000</v>
       </c>
       <c r="M93" t="n">
-        <v>86654000000</v>
+        <v>402053000000</v>
       </c>
       <c r="N93" t="n">
-        <v>105899174820</v>
+        <v>616209283200</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>株式会社メルカリ</t>
+          <t>株式会社髙島屋</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>27.4</v>
+        <v>65.2</v>
       </c>
       <c r="D94" t="n">
-        <v>3886</v>
+        <v>2103</v>
       </c>
       <c r="E94" t="n">
-        <v>2006.059650428343</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="F94" t="n">
-        <v>93.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>171463000000</v>
+        <v>88996000000</v>
       </c>
       <c r="J94" t="n">
-        <v>434000000</v>
+        <v>193090000000</v>
       </c>
       <c r="K94" t="n">
-        <v>1543000000</v>
+        <v>119967000000</v>
       </c>
       <c r="L94" t="n">
-        <v>40013000000</v>
+        <v>420489000000</v>
       </c>
       <c r="M94" t="n">
-        <v>173440000000</v>
+        <v>402053000000</v>
       </c>
       <c r="N94" t="n">
-        <v>634119877662</v>
+        <v>616209283200</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>サッポロホールディングス株式会社</t>
+          <t>三井倉庫ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2501</t>
+          <t>9302</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>44.6</v>
       </c>
       <c r="D95" t="n">
-        <v>1865</v>
+        <v>3369</v>
       </c>
       <c r="E95" t="n">
-        <v>2697.360927565142</v>
+        <v>1492.806001579363</v>
       </c>
       <c r="F95" t="n">
-        <v>-30.9</v>
+        <v>125.7</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -5342,102 +5342,102 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2925000000</v>
+        <v>22822000000</v>
       </c>
       <c r="J95" t="n">
-        <v>23000000</v>
+        <v>72331000000</v>
       </c>
       <c r="K95" t="n">
-        <v>4391000000</v>
+        <v>17148000000</v>
       </c>
       <c r="L95" t="n">
-        <v>142395000000</v>
+        <v>88631000000</v>
       </c>
       <c r="M95" t="n">
-        <v>7339000000</v>
+        <v>112301000000</v>
       </c>
       <c r="N95" t="n">
-        <v>727299626350</v>
+        <v>252015636165</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>株式会社クレハ</t>
+          <t>京阪神ビルディング株式会社</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>8818</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>17.9</v>
+        <v>83.3</v>
       </c>
       <c r="D96" t="n">
-        <v>4365</v>
+        <v>1091</v>
       </c>
       <c r="E96" t="n">
-        <v>7960</v>
+        <v>1341.977644710579</v>
       </c>
       <c r="F96" t="n">
-        <v>-45.2</v>
+        <v>-18.7</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>5294000000</v>
+        <v>9876000000</v>
       </c>
       <c r="J96" t="n">
-        <v>5963000000</v>
+        <v>54379000000</v>
       </c>
       <c r="K96" t="n">
-        <v>18608000000</v>
+        <v>22399000000</v>
       </c>
       <c r="L96" t="n">
-        <v>155874000000</v>
+        <v>70510000000</v>
       </c>
       <c r="M96" t="n">
-        <v>29865000000</v>
+        <v>86654000000</v>
       </c>
       <c r="N96" t="n">
-        <v>166834900710</v>
+        <v>104086486242</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>コムシスホールディングス株式会社</t>
+          <t>株式会社メルカリ</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>17.7</v>
+        <v>27.5</v>
       </c>
       <c r="D97" t="n">
-        <v>5441</v>
+        <v>3867</v>
       </c>
       <c r="E97" t="n">
-        <v>3735.709461270437</v>
+        <v>2006.059650428343</v>
       </c>
       <c r="F97" t="n">
-        <v>45.6</v>
+        <v>92.8</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -5446,154 +5446,154 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>34033000000</v>
+        <v>171463000000</v>
       </c>
       <c r="J97" t="n">
-        <v>45394000000</v>
+        <v>434000000</v>
       </c>
       <c r="K97" t="n">
-        <v>31261000000</v>
+        <v>1543000000</v>
       </c>
       <c r="L97" t="n">
-        <v>343489000000</v>
+        <v>40013000000</v>
       </c>
       <c r="M97" t="n">
-        <v>110688000000</v>
+        <v>173440000000</v>
       </c>
       <c r="N97" t="n">
-        <v>624540456771</v>
+        <v>631019445939</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>サクサ株式会社</t>
+          <t>サッポロホールディングス株式会社</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>6675</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D98" t="n">
-        <v>2145</v>
+        <v>1859.5</v>
       </c>
       <c r="E98" t="n">
-        <v>5463.67048346056</v>
+        <v>2697.360927565142</v>
       </c>
       <c r="F98" t="n">
-        <v>-60.7</v>
+        <v>-31.1</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>6993000000</v>
+        <v>2925000000</v>
       </c>
       <c r="J98" t="n">
-        <v>1323000000</v>
+        <v>23000000</v>
       </c>
       <c r="K98" t="n">
-        <v>2933000000</v>
+        <v>4391000000</v>
       </c>
       <c r="L98" t="n">
-        <v>23497000000</v>
+        <v>142395000000</v>
       </c>
       <c r="M98" t="n">
-        <v>11249000000</v>
+        <v>7339000000</v>
       </c>
       <c r="N98" t="n">
-        <v>37519460550</v>
+        <v>725154774905</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>愛知製鋼株式会社</t>
+          <t>株式会社クレハ</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>4023</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>35.1</v>
+        <v>17.7</v>
       </c>
       <c r="D99" t="n">
-        <v>3125</v>
+        <v>4405</v>
       </c>
       <c r="E99" t="n">
-        <v>3155.301177013616</v>
+        <v>7960</v>
       </c>
       <c r="F99" t="n">
-        <v>-1</v>
+        <v>-44.7</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>32866000000</v>
+        <v>5294000000</v>
       </c>
       <c r="J99" t="n">
-        <v>11000000000</v>
+        <v>5963000000</v>
       </c>
       <c r="K99" t="n">
-        <v>26614000000</v>
+        <v>18608000000</v>
       </c>
       <c r="L99" t="n">
-        <v>186904000000</v>
+        <v>155874000000</v>
       </c>
       <c r="M99" t="n">
-        <v>70480000000</v>
+        <v>29865000000</v>
       </c>
       <c r="N99" t="n">
-        <v>200771243750</v>
+        <v>168363742870</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>株式会社インターネットイニシアティブ</t>
+          <t>コムシスホールディングス株式会社</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>3774</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>5.4</v>
+        <v>17.9</v>
       </c>
       <c r="D100" t="n">
-        <v>3448</v>
+        <v>5387</v>
       </c>
       <c r="E100" t="n">
-        <v>2655.311711736394</v>
+        <v>3953.24613842911</v>
       </c>
       <c r="F100" t="n">
-        <v>29.9</v>
+        <v>36.3</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -5602,50 +5602,50 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>16367000000</v>
+        <v>34033000000</v>
       </c>
       <c r="J100" t="n">
-        <v>1522000000</v>
+        <v>45394000000</v>
       </c>
       <c r="K100" t="n">
-        <v>15226000000</v>
+        <v>31261000000</v>
       </c>
       <c r="L100" t="n">
-        <v>87924000000</v>
+        <v>343489000000</v>
       </c>
       <c r="M100" t="n">
-        <v>33115000000</v>
+        <v>110688000000</v>
       </c>
       <c r="N100" t="n">
-        <v>611433857240</v>
+        <v>618342113697</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>コクヨ株式会社</t>
+          <t>コムシスホールディングス株式会社</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>7984</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>41</v>
+        <v>17.9</v>
       </c>
       <c r="D101" t="n">
-        <v>899.2999877929688</v>
+        <v>5387</v>
       </c>
       <c r="E101" t="n">
-        <v>2157.626835069302</v>
+        <v>3735.709461270437</v>
       </c>
       <c r="F101" t="n">
-        <v>-58.3</v>
+        <v>44.2</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -5654,338 +5654,338 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>100575000000</v>
+        <v>34033000000</v>
       </c>
       <c r="J101" t="n">
-        <v>22282000000</v>
+        <v>45394000000</v>
       </c>
       <c r="K101" t="n">
-        <v>30106000000</v>
+        <v>31261000000</v>
       </c>
       <c r="L101" t="n">
-        <v>230105000000</v>
+        <v>343489000000</v>
       </c>
       <c r="M101" t="n">
-        <v>152963000000</v>
+        <v>110688000000</v>
       </c>
       <c r="N101" t="n">
-        <v>372705950791</v>
+        <v>618342113697</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>三菱製紙株式会社</t>
+          <t>サクサ株式会社</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>6675</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>97.2</v>
+        <v>29.7</v>
       </c>
       <c r="D102" t="n">
-        <v>1181</v>
+        <v>2165</v>
       </c>
       <c r="E102" t="n">
-        <v>810</v>
+        <v>5463.67048346056</v>
       </c>
       <c r="F102" t="n">
-        <v>45.8</v>
+        <v>-60.4</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>9047000000</v>
+        <v>6993000000</v>
       </c>
       <c r="J102" t="n">
-        <v>16443000000</v>
+        <v>1323000000</v>
       </c>
       <c r="K102" t="n">
-        <v>24813000000</v>
+        <v>2933000000</v>
       </c>
       <c r="L102" t="n">
-        <v>69613000000</v>
+        <v>23497000000</v>
       </c>
       <c r="M102" t="n">
-        <v>50303000000</v>
+        <v>11249000000</v>
       </c>
       <c r="N102" t="n">
-        <v>51737459399</v>
+        <v>37869292350</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>株式会社プラスアルファ・コンサルティング</t>
+          <t>愛知製鋼株式会社</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>4071</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>9.699999999999999</v>
+        <v>34.8</v>
       </c>
       <c r="D103" t="n">
-        <v>2106</v>
+        <v>3150</v>
       </c>
       <c r="E103" t="n">
-        <v>2300.974351689521</v>
+        <v>3155.301177013616</v>
       </c>
       <c r="F103" t="n">
-        <v>-8.5</v>
+        <v>-0.2</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>8278003000</v>
+        <v>32866000000</v>
       </c>
       <c r="J103" t="n">
-        <v>271170000</v>
+        <v>11000000000</v>
       </c>
       <c r="K103" t="n">
-        <v>0</v>
+        <v>26614000000</v>
       </c>
       <c r="L103" t="n">
-        <v>9445733000</v>
+        <v>186904000000</v>
       </c>
       <c r="M103" t="n">
-        <v>8549173000</v>
+        <v>70480000000</v>
       </c>
       <c r="N103" t="n">
-        <v>88358388300</v>
+        <v>202377413700</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>東亜道路工業株式会社</t>
+          <t>株式会社インターネットイニシアティブ</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>39.8</v>
+        <v>5.5</v>
       </c>
       <c r="D104" t="n">
-        <v>1606</v>
+        <v>3399</v>
       </c>
       <c r="E104" t="n">
-        <v>1180.253227905114</v>
+        <v>2655.311711736394</v>
       </c>
       <c r="F104" t="n">
-        <v>36.1</v>
+        <v>28</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>11649000000</v>
+        <v>16367000000</v>
       </c>
       <c r="J104" t="n">
-        <v>13793000000</v>
+        <v>1522000000</v>
       </c>
       <c r="K104" t="n">
-        <v>4087000000</v>
+        <v>15226000000</v>
       </c>
       <c r="L104" t="n">
-        <v>50605000000</v>
+        <v>87924000000</v>
       </c>
       <c r="M104" t="n">
-        <v>29529000000</v>
+        <v>33115000000</v>
       </c>
       <c r="N104" t="n">
-        <v>74209386328</v>
+        <v>602744686995</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>東亜道路工業株式会社</t>
+          <t>コクヨ株式会社</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>7984</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>39.8</v>
+        <v>41</v>
       </c>
       <c r="D105" t="n">
-        <v>1606</v>
+        <v>899.5999755859375</v>
       </c>
       <c r="E105" t="n">
-        <v>1180.31326635551</v>
+        <v>2157.626835069302</v>
       </c>
       <c r="F105" t="n">
-        <v>36.1</v>
+        <v>-58.3</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>11649000000</v>
+        <v>100575000000</v>
       </c>
       <c r="J105" t="n">
-        <v>13793000000</v>
+        <v>22282000000</v>
       </c>
       <c r="K105" t="n">
-        <v>4087000000</v>
+        <v>30106000000</v>
       </c>
       <c r="L105" t="n">
-        <v>50605000000</v>
+        <v>230105000000</v>
       </c>
       <c r="M105" t="n">
-        <v>29529000000</v>
+        <v>152963000000</v>
       </c>
       <c r="N105" t="n">
-        <v>74209386328</v>
+        <v>372830277753</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>東亜道路工業株式会社</t>
+          <t>三菱製紙株式会社</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>3864</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>39.8</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="D106" t="n">
-        <v>1606</v>
+        <v>1197</v>
       </c>
       <c r="E106" t="n">
-        <v>1180.406015389293</v>
+        <v>810</v>
       </c>
       <c r="F106" t="n">
-        <v>36.1</v>
+        <v>47.8</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>11649000000</v>
+        <v>9047000000</v>
       </c>
       <c r="J106" t="n">
-        <v>13793000000</v>
+        <v>16443000000</v>
       </c>
       <c r="K106" t="n">
-        <v>4087000000</v>
+        <v>24813000000</v>
       </c>
       <c r="L106" t="n">
-        <v>50605000000</v>
+        <v>69613000000</v>
       </c>
       <c r="M106" t="n">
-        <v>29529000000</v>
+        <v>50303000000</v>
       </c>
       <c r="N106" t="n">
-        <v>74209386328</v>
+        <v>52438390263</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>東亜道路工業株式会社</t>
+          <t>株式会社プラスアルファ・コンサルティング</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>4071</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>39.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D107" t="n">
-        <v>1606</v>
+        <v>2092</v>
       </c>
       <c r="E107" t="n">
-        <v>1180.420176850555</v>
+        <v>2300.974351689521</v>
       </c>
       <c r="F107" t="n">
-        <v>36.1</v>
+        <v>-9.1</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>11649000000</v>
+        <v>8278003000</v>
       </c>
       <c r="J107" t="n">
-        <v>13793000000</v>
+        <v>271170000</v>
       </c>
       <c r="K107" t="n">
-        <v>4087000000</v>
+        <v>0</v>
       </c>
       <c r="L107" t="n">
-        <v>50605000000</v>
+        <v>9445733000</v>
       </c>
       <c r="M107" t="n">
-        <v>29529000000</v>
+        <v>8549173000</v>
       </c>
       <c r="N107" t="n">
-        <v>74209386328</v>
+        <v>87771010600</v>
       </c>
     </row>
     <row r="108">
@@ -6000,16 +6000,16 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>39.8</v>
+        <v>40</v>
       </c>
       <c r="D108" t="n">
-        <v>1606</v>
+        <v>1598</v>
       </c>
       <c r="E108" t="n">
-        <v>1180.431728045326</v>
+        <v>1180.253227905114</v>
       </c>
       <c r="F108" t="n">
-        <v>36.1</v>
+        <v>35.4</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="I108" t="n">
@@ -6037,7 +6037,7 @@
         <v>29529000000</v>
       </c>
       <c r="N108" t="n">
-        <v>74209386328</v>
+        <v>73839725624</v>
       </c>
     </row>
     <row r="109">
@@ -6052,16 +6052,16 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>39.8</v>
+        <v>40</v>
       </c>
       <c r="D109" t="n">
-        <v>1606</v>
+        <v>1598</v>
       </c>
       <c r="E109" t="n">
-        <v>1180.442269658324</v>
+        <v>1180.31326635551</v>
       </c>
       <c r="F109" t="n">
-        <v>36.1</v>
+        <v>35.4</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="I109" t="n">
@@ -6089,7 +6089,7 @@
         <v>29529000000</v>
       </c>
       <c r="N109" t="n">
-        <v>74209386328</v>
+        <v>73839725624</v>
       </c>
     </row>
     <row r="110">
@@ -6104,16 +6104,16 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>39.8</v>
+        <v>40</v>
       </c>
       <c r="D110" t="n">
-        <v>1606</v>
+        <v>1598</v>
       </c>
       <c r="E110" t="n">
-        <v>1180.450912709519</v>
+        <v>1180.406015389293</v>
       </c>
       <c r="F110" t="n">
-        <v>36</v>
+        <v>35.4</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="I110" t="n">
@@ -6141,7 +6141,7 @@
         <v>29529000000</v>
       </c>
       <c r="N110" t="n">
-        <v>74209386328</v>
+        <v>73839725624</v>
       </c>
     </row>
     <row r="111">
@@ -6156,16 +6156,16 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>39.8</v>
+        <v>40</v>
       </c>
       <c r="D111" t="n">
-        <v>1606</v>
+        <v>1598</v>
       </c>
       <c r="E111" t="n">
-        <v>1180.45745232471</v>
+        <v>1180.420176850555</v>
       </c>
       <c r="F111" t="n">
-        <v>36</v>
+        <v>35.4</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="I111" t="n">
@@ -6193,7 +6193,7 @@
         <v>29529000000</v>
       </c>
       <c r="N111" t="n">
-        <v>74209386328</v>
+        <v>73839725624</v>
       </c>
     </row>
     <row r="112">
@@ -6208,16 +6208,16 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>39.8</v>
+        <v>40</v>
       </c>
       <c r="D112" t="n">
-        <v>1606</v>
+        <v>1598</v>
       </c>
       <c r="E112" t="n">
-        <v>1180.463123164206</v>
+        <v>1180.431728045326</v>
       </c>
       <c r="F112" t="n">
-        <v>36</v>
+        <v>35.4</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="I112" t="n">
@@ -6245,7 +6245,7 @@
         <v>29529000000</v>
       </c>
       <c r="N112" t="n">
-        <v>74209386328</v>
+        <v>73839725624</v>
       </c>
     </row>
     <row r="113">
@@ -6260,16 +6260,16 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>39.8</v>
+        <v>40</v>
       </c>
       <c r="D113" t="n">
-        <v>1606</v>
+        <v>1598</v>
       </c>
       <c r="E113" t="n">
-        <v>1170.279952698077</v>
+        <v>1180.442269658324</v>
       </c>
       <c r="F113" t="n">
-        <v>37.2</v>
+        <v>35.4</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="I113" t="n">
@@ -6297,7 +6297,7 @@
         <v>29529000000</v>
       </c>
       <c r="N113" t="n">
-        <v>74209386328</v>
+        <v>73839725624</v>
       </c>
     </row>
     <row r="114">
@@ -6312,16 +6312,16 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>39.8</v>
+        <v>40</v>
       </c>
       <c r="D114" t="n">
-        <v>1606</v>
+        <v>1598</v>
       </c>
       <c r="E114" t="n">
-        <v>1169.924818603025</v>
+        <v>1180.450912709519</v>
       </c>
       <c r="F114" t="n">
-        <v>37.3</v>
+        <v>35.4</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="I114" t="n">
@@ -6349,7 +6349,7 @@
         <v>29529000000</v>
       </c>
       <c r="N114" t="n">
-        <v>74209386328</v>
+        <v>73839725624</v>
       </c>
     </row>
     <row r="115">
@@ -6364,16 +6364,16 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>39.8</v>
+        <v>40</v>
       </c>
       <c r="D115" t="n">
-        <v>1606</v>
+        <v>1598</v>
       </c>
       <c r="E115" t="n">
-        <v>1168.709522546084</v>
+        <v>1180.45745232471</v>
       </c>
       <c r="F115" t="n">
-        <v>37.4</v>
+        <v>35.4</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="I115" t="n">
@@ -6401,31 +6401,31 @@
         <v>29529000000</v>
       </c>
       <c r="N115" t="n">
-        <v>74209386328</v>
+        <v>73839725624</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>山洋電気株式会社</t>
+          <t>東亜道路工業株式会社</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="D116" t="n">
-        <v>5150</v>
+        <v>1598</v>
       </c>
       <c r="E116" t="n">
-        <v>7052.737306843267</v>
+        <v>1180.463123164206</v>
       </c>
       <c r="F116" t="n">
-        <v>-27</v>
+        <v>35.4</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -6434,830 +6434,830 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>8317000000</v>
+        <v>11649000000</v>
       </c>
       <c r="J116" t="n">
-        <v>6048000000</v>
+        <v>13793000000</v>
       </c>
       <c r="K116" t="n">
-        <v>7673000000</v>
+        <v>4087000000</v>
       </c>
       <c r="L116" t="n">
-        <v>49734000000</v>
+        <v>50605000000</v>
       </c>
       <c r="M116" t="n">
-        <v>22038000000</v>
+        <v>29529000000</v>
       </c>
       <c r="N116" t="n">
-        <v>182902461150</v>
+        <v>73839725624</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ヘリオス テクノ ホールディング株式会社</t>
+          <t>東亜道路工業株式会社</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>54.2</v>
+        <v>40</v>
       </c>
       <c r="D117" t="n">
-        <v>972</v>
+        <v>1598</v>
       </c>
       <c r="E117" t="n">
-        <v>896.0103264198827</v>
+        <v>1170.279952698077</v>
       </c>
       <c r="F117" t="n">
-        <v>8.5</v>
+        <v>36.5</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>7851015000</v>
+        <v>11649000000</v>
       </c>
       <c r="J117" t="n">
-        <v>640317000</v>
+        <v>13793000000</v>
       </c>
       <c r="K117" t="n">
-        <v>1079200000</v>
+        <v>4087000000</v>
       </c>
       <c r="L117" t="n">
-        <v>13746774000</v>
+        <v>50605000000</v>
       </c>
       <c r="M117" t="n">
-        <v>9570532000</v>
+        <v>29529000000</v>
       </c>
       <c r="N117" t="n">
-        <v>17643420324</v>
+        <v>73839725624</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>シェアリングテクノロジー株式会社</t>
+          <t>東亜道路工業株式会社</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>11.7</v>
+        <v>40</v>
       </c>
       <c r="D118" t="n">
-        <v>1544</v>
+        <v>1598</v>
       </c>
       <c r="E118" t="n">
-        <v>653.0713101160862</v>
+        <v>1169.924818603025</v>
       </c>
       <c r="F118" t="n">
-        <v>136.4</v>
+        <v>36.6</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4016706000</v>
+        <v>11649000000</v>
       </c>
       <c r="J118" t="n">
-        <v>309745000</v>
+        <v>13793000000</v>
       </c>
       <c r="K118" t="n">
-        <v>0</v>
+        <v>4087000000</v>
       </c>
       <c r="L118" t="n">
-        <v>185001000</v>
+        <v>50605000000</v>
       </c>
       <c r="M118" t="n">
-        <v>4326451000</v>
+        <v>29529000000</v>
       </c>
       <c r="N118" t="n">
-        <v>36949879336</v>
+        <v>73839725624</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>栄研化学株式会社</t>
+          <t>東亜道路工業株式会社</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>30.8</v>
+        <v>40</v>
       </c>
       <c r="D119" t="n">
-        <v>2255</v>
+        <v>1598</v>
       </c>
       <c r="E119" t="n">
-        <v>1947.225264702313</v>
+        <v>1168.709522546084</v>
       </c>
       <c r="F119" t="n">
-        <v>15.8</v>
+        <v>36.7</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>10900000000</v>
+        <v>11649000000</v>
       </c>
       <c r="J119" t="n">
-        <v>11585000000</v>
+        <v>13793000000</v>
       </c>
       <c r="K119" t="n">
-        <v>408000000</v>
+        <v>4087000000</v>
       </c>
       <c r="L119" t="n">
-        <v>45803000000</v>
+        <v>50605000000</v>
       </c>
       <c r="M119" t="n">
-        <v>22893000000</v>
+        <v>29529000000</v>
       </c>
       <c r="N119" t="n">
-        <v>74337367115</v>
+        <v>73839725624</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>栄研化学株式会社</t>
+          <t>山洋電気株式会社</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>30.8</v>
+        <v>12</v>
       </c>
       <c r="D120" t="n">
-        <v>2255</v>
+        <v>5160</v>
       </c>
       <c r="E120" t="n">
-        <v>1678.083113259255</v>
+        <v>7052.737306843267</v>
       </c>
       <c r="F120" t="n">
-        <v>34.4</v>
+        <v>-26.8</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>10900000000</v>
+        <v>8317000000</v>
       </c>
       <c r="J120" t="n">
-        <v>11585000000</v>
+        <v>6048000000</v>
       </c>
       <c r="K120" t="n">
-        <v>408000000</v>
+        <v>7673000000</v>
       </c>
       <c r="L120" t="n">
-        <v>45803000000</v>
+        <v>49734000000</v>
       </c>
       <c r="M120" t="n">
-        <v>22893000000</v>
+        <v>22038000000</v>
       </c>
       <c r="N120" t="n">
-        <v>74337367115</v>
+        <v>183257611560</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>株式会社ヤマダホールディングス</t>
+          <t>ヘリオス テクノ ホールディング株式会社</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>9831</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>57.8</v>
+        <v>54.1</v>
       </c>
       <c r="D121" t="n">
-        <v>720.7999877929688</v>
+        <v>974</v>
       </c>
       <c r="E121" t="n">
-        <v>530</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="F121" t="n">
-        <v>36</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>56470000000</v>
+        <v>7851015000</v>
       </c>
       <c r="J121" t="n">
-        <v>210733000000</v>
+        <v>640317000</v>
       </c>
       <c r="K121" t="n">
-        <v>9997000000</v>
+        <v>1079200000</v>
       </c>
       <c r="L121" t="n">
-        <v>676277000000</v>
+        <v>13746774000</v>
       </c>
       <c r="M121" t="n">
-        <v>277200000000</v>
+        <v>9570532000</v>
       </c>
       <c r="N121" t="n">
-        <v>479314283989</v>
+        <v>17679723658</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>日本化薬株式会社</t>
+          <t>シェアリングテクノロジー株式会社</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>35.7</v>
+        <v>11.7</v>
       </c>
       <c r="D122" t="n">
-        <v>2051.5</v>
+        <v>1545</v>
       </c>
       <c r="E122" t="n">
-        <v>1111.90611839092</v>
+        <v>653.0713101160862</v>
       </c>
       <c r="F122" t="n">
-        <v>84.5</v>
+        <v>136.6</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>52962000000</v>
+        <v>4016706000</v>
       </c>
       <c r="J122" t="n">
-        <v>48231000000</v>
+        <v>309745000</v>
       </c>
       <c r="K122" t="n">
-        <v>4337000000</v>
+        <v>0</v>
       </c>
       <c r="L122" t="n">
-        <v>246425000000</v>
+        <v>185001000</v>
       </c>
       <c r="M122" t="n">
-        <v>105530000000</v>
+        <v>4326451000</v>
       </c>
       <c r="N122" t="n">
-        <v>295802480034</v>
+        <v>36973810605</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>王子ホールディングス株式会社</t>
+          <t>栄研化学株式会社</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>41.5</v>
+        <v>30.7</v>
       </c>
       <c r="D123" t="n">
-        <v>872.7999877929688</v>
+        <v>2260</v>
       </c>
       <c r="E123" t="n">
-        <v>590</v>
+        <v>1947.225264702313</v>
       </c>
       <c r="F123" t="n">
-        <v>47.9</v>
+        <v>16.1</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>55474000000</v>
+        <v>10900000000</v>
       </c>
       <c r="J123" t="n">
-        <v>244732000000</v>
+        <v>11585000000</v>
       </c>
       <c r="K123" t="n">
-        <v>7434000000</v>
+        <v>408000000</v>
       </c>
       <c r="L123" t="n">
-        <v>875470000000</v>
+        <v>45803000000</v>
       </c>
       <c r="M123" t="n">
-        <v>307640000000</v>
+        <v>22893000000</v>
       </c>
       <c r="N123" t="n">
-        <v>741211680564</v>
+        <v>74502194980</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>東邦ホールディングス株式会社</t>
+          <t>栄研化学株式会社</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>50.6</v>
+        <v>30.7</v>
       </c>
       <c r="D124" t="n">
-        <v>4005</v>
+        <v>2260</v>
       </c>
       <c r="E124" t="n">
-        <v>3405.914389596362</v>
+        <v>1678.083113259255</v>
       </c>
       <c r="F124" t="n">
-        <v>17.6</v>
+        <v>34.7</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>90014000000</v>
+        <v>10900000000</v>
       </c>
       <c r="J124" t="n">
-        <v>34220000000</v>
+        <v>11585000000</v>
       </c>
       <c r="K124" t="n">
-        <v>7000000000</v>
+        <v>408000000</v>
       </c>
       <c r="L124" t="n">
-        <v>241281000000</v>
+        <v>45803000000</v>
       </c>
       <c r="M124" t="n">
-        <v>131234000000</v>
+        <v>22893000000</v>
       </c>
       <c r="N124" t="n">
-        <v>259130000115</v>
+        <v>74502194980</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>東邦ホールディングス株式会社</t>
+          <t>株式会社ヤマダホールディングス</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>9831</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>50.6</v>
+        <v>58.3</v>
       </c>
       <c r="D125" t="n">
-        <v>4005</v>
+        <v>715</v>
       </c>
       <c r="E125" t="n">
-        <v>2714.613787300615</v>
+        <v>530</v>
       </c>
       <c r="F125" t="n">
-        <v>47.5</v>
+        <v>34.9</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>90014000000</v>
+        <v>56470000000</v>
       </c>
       <c r="J125" t="n">
-        <v>34220000000</v>
+        <v>210733000000</v>
       </c>
       <c r="K125" t="n">
-        <v>7000000000</v>
+        <v>9997000000</v>
       </c>
       <c r="L125" t="n">
-        <v>241281000000</v>
+        <v>676277000000</v>
       </c>
       <c r="M125" t="n">
-        <v>131234000000</v>
+        <v>277200000000</v>
       </c>
       <c r="N125" t="n">
-        <v>259130000115</v>
+        <v>475457434595</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>株式会社アイネス</t>
+          <t>日本化薬株式会社</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>9742</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>34.4</v>
+        <v>35.6</v>
       </c>
       <c r="D126" t="n">
-        <v>2113</v>
+        <v>2053.5</v>
       </c>
       <c r="E126" t="n">
-        <v>1879.137815927515</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="F126" t="n">
-        <v>12.4</v>
+        <v>84.7</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>9731000000</v>
+        <v>52962000000</v>
       </c>
       <c r="J126" t="n">
-        <v>5286000000</v>
+        <v>48231000000</v>
       </c>
       <c r="K126" t="n">
-        <v>100000000</v>
+        <v>4337000000</v>
       </c>
       <c r="L126" t="n">
-        <v>34620000000</v>
+        <v>246425000000</v>
       </c>
       <c r="M126" t="n">
-        <v>15117000000</v>
+        <v>105530000000</v>
       </c>
       <c r="N126" t="n">
-        <v>43997830511</v>
+        <v>296090856812</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>日本ゼオン株式会社</t>
+          <t>王子ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>36.3</v>
+        <v>41.6</v>
       </c>
       <c r="D127" t="n">
-        <v>2319</v>
+        <v>869.7999877929688</v>
       </c>
       <c r="E127" t="n">
-        <v>1721.078563209627</v>
+        <v>590</v>
       </c>
       <c r="F127" t="n">
-        <v>34.7</v>
+        <v>47.4</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>44521000000</v>
+        <v>55474000000</v>
       </c>
       <c r="J127" t="n">
-        <v>45382000000</v>
+        <v>244732000000</v>
       </c>
       <c r="K127" t="n">
-        <v>71191000000</v>
+        <v>7434000000</v>
       </c>
       <c r="L127" t="n">
-        <v>321836000000</v>
+        <v>875470000000</v>
       </c>
       <c r="M127" t="n">
-        <v>161094000000</v>
+        <v>307640000000</v>
       </c>
       <c r="N127" t="n">
-        <v>443730230733</v>
+        <v>738663977685</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>太陽ホールディングス株式会社</t>
+          <t>東邦ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>16.4</v>
+        <v>50.6</v>
       </c>
       <c r="D128" t="n">
-        <v>4720</v>
+        <v>4005</v>
       </c>
       <c r="E128" t="n">
-        <v>2199.643244598912</v>
+        <v>3405.914389596362</v>
       </c>
       <c r="F128" t="n">
-        <v>114.6</v>
+        <v>17.6</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>51152000000</v>
+        <v>90014000000</v>
       </c>
       <c r="J128" t="n">
-        <v>30337000000</v>
+        <v>34220000000</v>
       </c>
       <c r="K128" t="n">
-        <v>4870000000</v>
+        <v>7000000000</v>
       </c>
       <c r="L128" t="n">
-        <v>85466000000</v>
+        <v>241281000000</v>
       </c>
       <c r="M128" t="n">
-        <v>86359000000</v>
+        <v>131234000000</v>
       </c>
       <c r="N128" t="n">
-        <v>525225939040</v>
+        <v>259130000115</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>太陽ホールディングス株式会社</t>
+          <t>東邦ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>16.4</v>
+        <v>50.6</v>
       </c>
       <c r="D129" t="n">
-        <v>4720</v>
+        <v>4005</v>
       </c>
       <c r="E129" t="n">
-        <v>3565.648720929983</v>
+        <v>2714.613787300615</v>
       </c>
       <c r="F129" t="n">
-        <v>32.4</v>
+        <v>47.5</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>51152000000</v>
+        <v>90014000000</v>
       </c>
       <c r="J129" t="n">
-        <v>30337000000</v>
+        <v>34220000000</v>
       </c>
       <c r="K129" t="n">
-        <v>4870000000</v>
+        <v>7000000000</v>
       </c>
       <c r="L129" t="n">
-        <v>85466000000</v>
+        <v>241281000000</v>
       </c>
       <c r="M129" t="n">
-        <v>86359000000</v>
+        <v>131234000000</v>
       </c>
       <c r="N129" t="n">
-        <v>525225939040</v>
+        <v>259130000115</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>株式会社エス・エム・エス</t>
+          <t>株式会社アイネス</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>9742</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>8.300000000000001</v>
+        <v>34.1</v>
       </c>
       <c r="D130" t="n">
-        <v>2673</v>
+        <v>2126</v>
       </c>
       <c r="E130" t="n">
-        <v>1478.127248828989</v>
+        <v>1879.137815927515</v>
       </c>
       <c r="F130" t="n">
-        <v>80.8</v>
+        <v>13.1</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>14126000000</v>
+        <v>9731000000</v>
       </c>
       <c r="J130" t="n">
-        <v>1187000000</v>
+        <v>5286000000</v>
       </c>
       <c r="K130" t="n">
-        <v>2875000000</v>
+        <v>100000000</v>
       </c>
       <c r="L130" t="n">
-        <v>29991000000</v>
+        <v>34620000000</v>
       </c>
       <c r="M130" t="n">
-        <v>18188000000</v>
+        <v>15117000000</v>
       </c>
       <c r="N130" t="n">
-        <v>219401040177</v>
+        <v>44268522322</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>アニコム ホールディングス株式会社</t>
+          <t>日本ゼオン株式会社</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>8715</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>41</v>
+        <v>35.9</v>
       </c>
       <c r="D131" t="n">
-        <v>1031</v>
+        <v>2345.5</v>
       </c>
       <c r="E131" t="n">
-        <v>656.2604975855553</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="F131" t="n">
-        <v>57.1</v>
+        <v>36.3</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>27691000000</v>
+        <v>44521000000</v>
       </c>
       <c r="J131" t="n">
-        <v>3070000000</v>
+        <v>45382000000</v>
       </c>
       <c r="K131" t="n">
-        <v>3000000</v>
+        <v>71191000000</v>
       </c>
       <c r="L131" t="n">
-        <v>27316000000</v>
+        <v>321836000000</v>
       </c>
       <c r="M131" t="n">
-        <v>30764000000</v>
+        <v>161094000000</v>
       </c>
       <c r="N131" t="n">
-        <v>75078677820</v>
+        <v>448800886668</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>東京製鐵株式会社</t>
+          <t>太陽ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>99.09999999999999</v>
+        <v>16.4</v>
       </c>
       <c r="D132" t="n">
-        <v>1755</v>
+        <v>4728</v>
       </c>
       <c r="E132" t="n">
-        <v>1605.452212379354</v>
+        <v>2199.643244598912</v>
       </c>
       <c r="F132" t="n">
-        <v>9.300000000000001</v>
+        <v>114.9</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -7266,94 +7266,102 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>68644000000</v>
+        <v>51152000000</v>
       </c>
       <c r="J132" t="n">
-        <v>33060000000</v>
+        <v>30337000000</v>
       </c>
       <c r="K132" t="n">
-        <v>75000000000</v>
+        <v>4870000000</v>
       </c>
       <c r="L132" t="n">
-        <v>158280000000</v>
+        <v>85466000000</v>
       </c>
       <c r="M132" t="n">
-        <v>176704000000</v>
+        <v>86359000000</v>
       </c>
       <c r="N132" t="n">
-        <v>178301227455</v>
+        <v>526116152496</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ウェーブロックホールディングス株式会社</t>
+          <t>太陽ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>7940</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr"/>
-      <c r="D133" t="inlineStr"/>
+          <t>4626</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="D133" t="n">
+        <v>4728</v>
+      </c>
       <c r="E133" t="n">
-        <v>1010</v>
-      </c>
-      <c r="F133" t="inlineStr"/>
+        <v>3565.648720929983</v>
+      </c>
+      <c r="F133" t="n">
+        <v>32.6</v>
+      </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1961626000</v>
+        <v>51152000000</v>
       </c>
       <c r="J133" t="n">
-        <v>2544946000</v>
+        <v>30337000000</v>
       </c>
       <c r="K133" t="n">
-        <v>1068366000</v>
+        <v>4870000000</v>
       </c>
       <c r="L133" t="n">
-        <v>13761535000</v>
+        <v>85466000000</v>
       </c>
       <c r="M133" t="n">
-        <v>5574938000</v>
-      </c>
-      <c r="N133" t="inlineStr"/>
+        <v>86359000000</v>
+      </c>
+      <c r="N133" t="n">
+        <v>526116152496</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>近畿車輛株式会社</t>
+          <t>株式会社エス・エム・エス</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>7122</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>108.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D134" t="n">
-        <v>2370</v>
+        <v>2666</v>
       </c>
       <c r="E134" t="n">
-        <v>2144.894901144641</v>
+        <v>1478.127248828989</v>
       </c>
       <c r="F134" t="n">
-        <v>10.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -7362,414 +7370,406 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>6847000000</v>
+        <v>14126000000</v>
       </c>
       <c r="J134" t="n">
-        <v>4580000000</v>
+        <v>1187000000</v>
       </c>
       <c r="K134" t="n">
-        <v>6329000000</v>
+        <v>2875000000</v>
       </c>
       <c r="L134" t="n">
-        <v>24474000000</v>
+        <v>29991000000</v>
       </c>
       <c r="M134" t="n">
-        <v>17756000000</v>
+        <v>18188000000</v>
       </c>
       <c r="N134" t="n">
-        <v>16305791970</v>
+        <v>218826477034</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>株式会社三陽商会</t>
+          <t>アニコム ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>8715</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>62.3</v>
+        <v>41.1</v>
       </c>
       <c r="D135" t="n">
-        <v>1398</v>
+        <v>1029</v>
       </c>
       <c r="E135" t="n">
-        <v>3321.975331035734</v>
+        <v>656.2604975855553</v>
       </c>
       <c r="F135" t="n">
-        <v>-57.9</v>
+        <v>56.8</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>16287000000</v>
+        <v>27691000000</v>
       </c>
       <c r="J135" t="n">
-        <v>3021000000</v>
+        <v>3070000000</v>
       </c>
       <c r="K135" t="n">
-        <v>6298000000</v>
+        <v>3000000</v>
       </c>
       <c r="L135" t="n">
-        <v>33920000000</v>
+        <v>27316000000</v>
       </c>
       <c r="M135" t="n">
-        <v>25606000000</v>
+        <v>30764000000</v>
       </c>
       <c r="N135" t="n">
-        <v>41081672736</v>
+        <v>74933035380</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>月島ホールディングス株式会社</t>
+          <t>東京製鐵株式会社</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>6332</t>
+          <t>5423</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>48.6</v>
+        <v>99.2</v>
       </c>
       <c r="D136" t="n">
-        <v>2655</v>
+        <v>1753</v>
       </c>
       <c r="E136" t="n">
-        <v>1410</v>
+        <v>1605.452212379354</v>
       </c>
       <c r="F136" t="n">
-        <v>88.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>28795000000</v>
+        <v>68644000000</v>
       </c>
       <c r="J136" t="n">
-        <v>22203000000</v>
+        <v>33060000000</v>
       </c>
       <c r="K136" t="n">
-        <v>100000000</v>
+        <v>75000000000</v>
       </c>
       <c r="L136" t="n">
-        <v>80949000000</v>
+        <v>158280000000</v>
       </c>
       <c r="M136" t="n">
-        <v>51098000000</v>
+        <v>176704000000</v>
       </c>
       <c r="N136" t="n">
-        <v>105141247065</v>
+        <v>178098035173</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>マネックスグループ株式会社</t>
+          <t>ウェーブロックホールディングス株式会社</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>8698</t>
-        </is>
-      </c>
-      <c r="C137" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="D137" t="n">
-        <v>725</v>
-      </c>
+          <t>7940</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr"/>
       <c r="E137" t="n">
-        <v>510.1850530906719</v>
-      </c>
-      <c r="F137" t="n">
-        <v>42.1</v>
-      </c>
+        <v>1010</v>
+      </c>
+      <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>17794000000</v>
+        <v>1961626000</v>
       </c>
       <c r="J137" t="n">
-        <v>412000000</v>
+        <v>2544946000</v>
       </c>
       <c r="K137" t="n">
-        <v>9312000000</v>
+        <v>1068366000</v>
       </c>
       <c r="L137" t="n">
-        <v>98001000000</v>
+        <v>13761535000</v>
       </c>
       <c r="M137" t="n">
-        <v>27518000000</v>
-      </c>
-      <c r="N137" t="n">
-        <v>182238670900</v>
-      </c>
+        <v>5574938000</v>
+      </c>
+      <c r="N137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>株式会社あおぞら銀行</t>
+          <t>近畿車輛株式会社</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>7122</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>221.1</v>
+        <v>107.4</v>
       </c>
       <c r="D138" t="n">
-        <v>3544</v>
+        <v>2403</v>
       </c>
       <c r="E138" t="n">
-        <v>2190</v>
+        <v>2144.894901144641</v>
       </c>
       <c r="F138" t="n">
-        <v>61.8</v>
+        <v>12</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1061743000000</v>
+        <v>6847000000</v>
       </c>
       <c r="J138" t="n">
-        <v>22385000000</v>
+        <v>4580000000</v>
       </c>
       <c r="K138" t="n">
-        <v>0</v>
+        <v>6329000000</v>
       </c>
       <c r="L138" t="n">
-        <v>487265000000</v>
+        <v>24474000000</v>
       </c>
       <c r="M138" t="n">
-        <v>1084128000000</v>
+        <v>17756000000</v>
       </c>
       <c r="N138" t="n">
-        <v>490422533344</v>
+        <v>16532834643</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>日本製紙株式会社</t>
+          <t>株式会社三陽商会</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>8011</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>306.3</v>
+        <v>63.8</v>
       </c>
       <c r="D139" t="n">
-        <v>1305</v>
+        <v>1365</v>
       </c>
       <c r="E139" t="n">
-        <v>1250</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="F139" t="n">
-        <v>4.4</v>
+        <v>-58.9</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>136216000000</v>
+        <v>16287000000</v>
       </c>
       <c r="J139" t="n">
-        <v>151771000000</v>
+        <v>3021000000</v>
       </c>
       <c r="K139" t="n">
-        <v>172984000000</v>
+        <v>6298000000</v>
       </c>
       <c r="L139" t="n">
-        <v>438604000000</v>
+        <v>33920000000</v>
       </c>
       <c r="M139" t="n">
-        <v>460971000000</v>
+        <v>25606000000</v>
       </c>
       <c r="N139" t="n">
-        <v>150477596415</v>
+        <v>40111933680</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>カルビー株式会社</t>
+          <t>月島ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>33.4</v>
+        <v>48.7</v>
       </c>
       <c r="D140" t="n">
-        <v>3031</v>
+        <v>2652</v>
       </c>
       <c r="E140" t="n">
-        <v>2919.137515755844</v>
+        <v>1410</v>
       </c>
       <c r="F140" t="n">
-        <v>3.8</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>49670000000</v>
+        <v>28795000000</v>
       </c>
       <c r="J140" t="n">
-        <v>70285000000</v>
+        <v>22203000000</v>
       </c>
       <c r="K140" t="n">
-        <v>3263000000</v>
+        <v>100000000</v>
       </c>
       <c r="L140" t="n">
-        <v>183458000000</v>
+        <v>80949000000</v>
       </c>
       <c r="M140" t="n">
-        <v>123218000000</v>
+        <v>51098000000</v>
       </c>
       <c r="N140" t="n">
-        <v>368532785474</v>
+        <v>105022443396</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ＮＩＴＴＯＫＵ株式会社</t>
+          <t>マネックスグループ株式会社</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>8698</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>51.3</v>
+        <v>15.1</v>
       </c>
       <c r="D141" t="n">
-        <v>2435</v>
+        <v>723</v>
       </c>
       <c r="E141" t="n">
-        <v>1710</v>
+        <v>510.1850530906719</v>
       </c>
       <c r="F141" t="n">
-        <v>42.4</v>
+        <v>41.7</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>11768000000</v>
+        <v>17794000000</v>
       </c>
       <c r="J141" t="n">
-        <v>6299000000</v>
+        <v>412000000</v>
       </c>
       <c r="K141" t="n">
-        <v>2999000000</v>
+        <v>9312000000</v>
       </c>
       <c r="L141" t="n">
-        <v>33919000000</v>
+        <v>98001000000</v>
       </c>
       <c r="M141" t="n">
-        <v>21066000000</v>
+        <v>27518000000</v>
       </c>
       <c r="N141" t="n">
-        <v>41089363670</v>
+        <v>181735943532</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ＮＩＴＴＯＫＵ株式会社</t>
+          <t>株式会社あおぞら銀行</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>51.3</v>
+        <v>225</v>
       </c>
       <c r="D142" t="n">
-        <v>2435</v>
+        <v>3482</v>
       </c>
       <c r="E142" t="n">
-        <v>1710</v>
+        <v>2190</v>
       </c>
       <c r="F142" t="n">
-        <v>42.4</v>
+        <v>59</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -7778,50 +7778,50 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>11768000000</v>
+        <v>1061743000000</v>
       </c>
       <c r="J142" t="n">
-        <v>6299000000</v>
+        <v>22385000000</v>
       </c>
       <c r="K142" t="n">
-        <v>2999000000</v>
+        <v>0</v>
       </c>
       <c r="L142" t="n">
-        <v>33919000000</v>
+        <v>487265000000</v>
       </c>
       <c r="M142" t="n">
-        <v>21066000000</v>
+        <v>1084128000000</v>
       </c>
       <c r="N142" t="n">
-        <v>41089363670</v>
+        <v>481842906632</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>新光商事株式会社</t>
+          <t>日本製紙株式会社</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>8141</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>30.8</v>
+        <v>301.9</v>
       </c>
       <c r="D143" t="n">
-        <v>1566</v>
+        <v>1324</v>
       </c>
       <c r="E143" t="n">
-        <v>930</v>
+        <v>1250</v>
       </c>
       <c r="F143" t="n">
-        <v>68.40000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -7830,154 +7830,154 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>10579000000</v>
+        <v>136216000000</v>
       </c>
       <c r="J143" t="n">
-        <v>195000000</v>
+        <v>151771000000</v>
       </c>
       <c r="K143" t="n">
-        <v>2995000000</v>
+        <v>172984000000</v>
       </c>
       <c r="L143" t="n">
-        <v>51945000000</v>
+        <v>438604000000</v>
       </c>
       <c r="M143" t="n">
-        <v>13769000000</v>
+        <v>460971000000</v>
       </c>
       <c r="N143" t="n">
-        <v>44709141834</v>
+        <v>152668457972</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>株式会社メガチップス</t>
+          <t>カルビー株式会社</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>6875</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>88.8</v>
+        <v>33.4</v>
       </c>
       <c r="D144" t="n">
-        <v>10580</v>
+        <v>3030</v>
       </c>
       <c r="E144" t="n">
-        <v>4870</v>
+        <v>2919.137515755844</v>
       </c>
       <c r="F144" t="n">
-        <v>117.2</v>
+        <v>3.8</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>25769446000</v>
+        <v>49670000000</v>
       </c>
       <c r="J144" t="n">
-        <v>2249411000</v>
+        <v>70285000000</v>
       </c>
       <c r="K144" t="n">
-        <v>101636005000</v>
+        <v>3263000000</v>
       </c>
       <c r="L144" t="n">
-        <v>67428618000</v>
+        <v>183458000000</v>
       </c>
       <c r="M144" t="n">
-        <v>129654862000</v>
+        <v>123218000000</v>
       </c>
       <c r="N144" t="n">
-        <v>146013532580</v>
+        <v>368411197620</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>株式会社青山財産ネットワークス</t>
+          <t>ＮＩＴＴＯＫＵ株式会社</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>8929</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>42.8</v>
+        <v>50.1</v>
       </c>
       <c r="D145" t="n">
-        <v>1356</v>
+        <v>2493</v>
       </c>
       <c r="E145" t="n">
-        <v>1347.74653160027</v>
+        <v>1710</v>
       </c>
       <c r="F145" t="n">
-        <v>0.6</v>
+        <v>45.8</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>10862000000</v>
+        <v>11768000000</v>
       </c>
       <c r="J145" t="n">
-        <v>245000000</v>
+        <v>6299000000</v>
       </c>
       <c r="K145" t="n">
-        <v>2845000000</v>
+        <v>2999000000</v>
       </c>
       <c r="L145" t="n">
-        <v>7128000000</v>
+        <v>33919000000</v>
       </c>
       <c r="M145" t="n">
-        <v>13952000000</v>
+        <v>21066000000</v>
       </c>
       <c r="N145" t="n">
-        <v>32632462728</v>
+        <v>42068083626</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>平和不動産株式会社</t>
+          <t>ＮＩＴＴＯＫＵ株式会社</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>8803</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>73.2</v>
+        <v>50.1</v>
       </c>
       <c r="D146" t="n">
-        <v>2344</v>
+        <v>2493</v>
       </c>
       <c r="E146" t="n">
-        <v>3610</v>
+        <v>1710</v>
       </c>
       <c r="F146" t="n">
-        <v>-35.1</v>
+        <v>45.8</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -7986,414 +7986,414 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>28111000000</v>
+        <v>11768000000</v>
       </c>
       <c r="J146" t="n">
-        <v>79319000000</v>
+        <v>6299000000</v>
       </c>
       <c r="K146" t="n">
-        <v>5997000000</v>
+        <v>2999000000</v>
       </c>
       <c r="L146" t="n">
-        <v>119278000000</v>
+        <v>33919000000</v>
       </c>
       <c r="M146" t="n">
-        <v>113427000000</v>
+        <v>21066000000</v>
       </c>
       <c r="N146" t="n">
-        <v>154868684752</v>
+        <v>42068083626</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>小林製薬株式会社</t>
+          <t>新光商事株式会社</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>8141</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>30</v>
+        <v>30.8</v>
       </c>
       <c r="D147" t="n">
-        <v>5790</v>
+        <v>1565</v>
       </c>
       <c r="E147" t="n">
-        <v>2148.936934940886</v>
+        <v>930</v>
       </c>
       <c r="F147" t="n">
-        <v>169.4</v>
+        <v>68.3</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>81987000000</v>
+        <v>10579000000</v>
       </c>
       <c r="J147" t="n">
-        <v>32461000000</v>
+        <v>195000000</v>
       </c>
       <c r="K147" t="n">
-        <v>14872000000</v>
+        <v>2995000000</v>
       </c>
       <c r="L147" t="n">
-        <v>195600000000</v>
+        <v>51945000000</v>
       </c>
       <c r="M147" t="n">
-        <v>129320000000</v>
+        <v>13769000000</v>
       </c>
       <c r="N147" t="n">
-        <v>430420615590</v>
+        <v>44680591935</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>小林製薬株式会社</t>
+          <t>株式会社メガチップス</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>30</v>
+        <v>89.8</v>
       </c>
       <c r="D148" t="n">
-        <v>5790</v>
+        <v>10460</v>
       </c>
       <c r="E148" t="n">
-        <v>5066.092575838703</v>
+        <v>4870</v>
       </c>
       <c r="F148" t="n">
-        <v>14.3</v>
+        <v>114.8</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>81987000000</v>
+        <v>25769446000</v>
       </c>
       <c r="J148" t="n">
-        <v>32461000000</v>
+        <v>2249411000</v>
       </c>
       <c r="K148" t="n">
-        <v>14872000000</v>
+        <v>101636005000</v>
       </c>
       <c r="L148" t="n">
-        <v>195600000000</v>
+        <v>67428618000</v>
       </c>
       <c r="M148" t="n">
-        <v>129320000000</v>
+        <v>129654862000</v>
       </c>
       <c r="N148" t="n">
-        <v>430420615590</v>
+        <v>144357424460</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>セーレン株式会社</t>
+          <t>株式会社青山財産ネットワークス</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>3569</t>
+          <t>8929</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>37.2</v>
+        <v>42.8</v>
       </c>
       <c r="D149" t="n">
-        <v>3230</v>
+        <v>1354</v>
       </c>
       <c r="E149" t="n">
-        <v>1359.655069733296</v>
+        <v>1347.74653160027</v>
       </c>
       <c r="F149" t="n">
-        <v>137.6</v>
+        <v>0.5</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>35451000000</v>
+        <v>10862000000</v>
       </c>
       <c r="J149" t="n">
-        <v>25813000000</v>
+        <v>245000000</v>
       </c>
       <c r="K149" t="n">
-        <v>8891000000</v>
+        <v>2845000000</v>
       </c>
       <c r="L149" t="n">
-        <v>91845000000</v>
+        <v>7128000000</v>
       </c>
       <c r="M149" t="n">
-        <v>70155000000</v>
+        <v>13952000000</v>
       </c>
       <c r="N149" t="n">
-        <v>188500994430</v>
+        <v>32584332252</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>データセクション株式会社</t>
+          <t>平和不動産株式会社</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>2.6</v>
+        <v>73.2</v>
       </c>
       <c r="D150" t="n">
-        <v>1483</v>
+        <v>2344</v>
       </c>
       <c r="E150" t="n">
-        <v>5143.276404494382</v>
+        <v>3610</v>
       </c>
       <c r="F150" t="n">
-        <v>-71.2</v>
+        <v>-35.1</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1420430000</v>
+        <v>28111000000</v>
       </c>
       <c r="J150" t="n">
-        <v>1162000</v>
+        <v>79319000000</v>
       </c>
       <c r="K150" t="n">
-        <v>49326000</v>
+        <v>5997000000</v>
       </c>
       <c r="L150" t="n">
-        <v>2818110000</v>
+        <v>119278000000</v>
       </c>
       <c r="M150" t="n">
-        <v>1470918000</v>
+        <v>113427000000</v>
       </c>
       <c r="N150" t="n">
-        <v>55556599798</v>
+        <v>154868684752</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>愛眼株式会社</t>
+          <t>小林製薬株式会社</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>9854</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>70.40000000000001</v>
+        <v>29.9</v>
       </c>
       <c r="D151" t="n">
-        <v>282</v>
+        <v>5814</v>
       </c>
       <c r="E151" t="n">
-        <v>246.9708756284982</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="F151" t="n">
-        <v>14.2</v>
+        <v>170.6</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2219000000</v>
+        <v>81987000000</v>
       </c>
       <c r="J151" t="n">
-        <v>1030000000</v>
+        <v>32461000000</v>
       </c>
       <c r="K151" t="n">
-        <v>604000000</v>
+        <v>14872000000</v>
       </c>
       <c r="L151" t="n">
-        <v>12920000000</v>
+        <v>195600000000</v>
       </c>
       <c r="M151" t="n">
-        <v>3853000000</v>
+        <v>129320000000</v>
       </c>
       <c r="N151" t="n">
-        <v>5472693630</v>
+        <v>432204742494</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>株式会社アシロ</t>
+          <t>小林製薬株式会社</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>14.4</v>
+        <v>29.9</v>
       </c>
       <c r="D152" t="n">
-        <v>1507</v>
+        <v>5814</v>
       </c>
       <c r="E152" t="n">
-        <v>1396.628697042366</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="F152" t="n">
-        <v>7.9</v>
+        <v>14.8</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1428281000</v>
+        <v>81987000000</v>
       </c>
       <c r="J152" t="n">
-        <v>102238000</v>
+        <v>32461000000</v>
       </c>
       <c r="K152" t="n">
-        <v>0</v>
+        <v>14872000000</v>
       </c>
       <c r="L152" t="n">
-        <v>1804458000</v>
+        <v>195600000000</v>
       </c>
       <c r="M152" t="n">
-        <v>1530519000</v>
+        <v>129320000000</v>
       </c>
       <c r="N152" t="n">
-        <v>10596601609</v>
+        <v>432204742494</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>三浦工業株式会社</t>
+          <t>セーレン株式会社</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>3569</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>11.8</v>
+        <v>37.2</v>
       </c>
       <c r="D153" t="n">
-        <v>3079</v>
+        <v>3230</v>
       </c>
       <c r="E153" t="n">
-        <v>3147.518794622453</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="F153" t="n">
-        <v>-2.2</v>
+        <v>137.6</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>20794000000</v>
+        <v>35451000000</v>
       </c>
       <c r="J153" t="n">
-        <v>10600000000</v>
+        <v>25813000000</v>
       </c>
       <c r="K153" t="n">
-        <v>10773000000</v>
+        <v>8891000000</v>
       </c>
       <c r="L153" t="n">
-        <v>138378000000</v>
+        <v>91845000000</v>
       </c>
       <c r="M153" t="n">
-        <v>42167000000</v>
+        <v>70155000000</v>
       </c>
       <c r="N153" t="n">
-        <v>356392279440</v>
+        <v>188500994430</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>株式会社カカクコム</t>
+          <t>データセクション株式会社</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>6.7</v>
+        <v>2.6</v>
       </c>
       <c r="D154" t="n">
-        <v>3850</v>
+        <v>1509</v>
       </c>
       <c r="E154" t="n">
-        <v>2318.314890576102</v>
+        <v>5143.276404494382</v>
       </c>
       <c r="F154" t="n">
-        <v>66.09999999999999</v>
+        <v>-70.7</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -8402,102 +8402,102 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>46452000000</v>
+        <v>1420430000</v>
       </c>
       <c r="J154" t="n">
-        <v>68000000</v>
+        <v>1162000</v>
       </c>
       <c r="K154" t="n">
-        <v>4669000000</v>
+        <v>49326000</v>
       </c>
       <c r="L154" t="n">
-        <v>45479000000</v>
+        <v>2818110000</v>
       </c>
       <c r="M154" t="n">
-        <v>51189000000</v>
+        <v>1470918000</v>
       </c>
       <c r="N154" t="n">
-        <v>761669627950</v>
+        <v>56530619754</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>古河機械金属株式会社</t>
+          <t>愛眼株式会社</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>47.5</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="D155" t="n">
-        <v>4010</v>
+        <v>282</v>
       </c>
       <c r="E155" t="n">
-        <v>1600</v>
+        <v>246.9708756284982</v>
       </c>
       <c r="F155" t="n">
-        <v>150.6</v>
+        <v>14.2</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="I155" t="n">
-        <v>14468000000</v>
+        <v>2219000000</v>
       </c>
       <c r="J155" t="n">
-        <v>26121000000</v>
+        <v>1030000000</v>
       </c>
       <c r="K155" t="n">
-        <v>19903000000</v>
+        <v>604000000</v>
       </c>
       <c r="L155" t="n">
-        <v>100075000000</v>
+        <v>12920000000</v>
       </c>
       <c r="M155" t="n">
-        <v>60492000000</v>
+        <v>3853000000</v>
       </c>
       <c r="N155" t="n">
-        <v>127398169170</v>
+        <v>5472693630</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>多木化学株式会社</t>
+          <t>株式会社アシロ</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>4025</t>
+          <t>7378</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>32.4</v>
+        <v>14.4</v>
       </c>
       <c r="D156" t="n">
-        <v>5410</v>
+        <v>1507</v>
       </c>
       <c r="E156" t="n">
-        <v>4695.956053243186</v>
+        <v>1396.628697042366</v>
       </c>
       <c r="F156" t="n">
-        <v>15.2</v>
+        <v>7.9</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -8506,338 +8506,546 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="I156" t="n">
-        <v>6433000000</v>
+        <v>1428281000</v>
       </c>
       <c r="J156" t="n">
-        <v>7985000000</v>
+        <v>102238000</v>
       </c>
       <c r="K156" t="n">
-        <v>199000000</v>
+        <v>0</v>
       </c>
       <c r="L156" t="n">
-        <v>29378000000</v>
+        <v>1804458000</v>
       </c>
       <c r="M156" t="n">
-        <v>14617000000</v>
+        <v>1530519000</v>
       </c>
       <c r="N156" t="n">
-        <v>45159266290</v>
+        <v>10596601609</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>エムスリー株式会社</t>
+          <t>三浦工業株式会社</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2413</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>7.6</v>
+        <v>11.8</v>
       </c>
       <c r="D157" t="n">
-        <v>1748.5</v>
+        <v>3085</v>
       </c>
       <c r="E157" t="n">
-        <v>1638.585693292194</v>
+        <v>3147.518794622453</v>
       </c>
       <c r="F157" t="n">
-        <v>6.7</v>
+        <v>-2</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I157" t="n">
-        <v>78812000000</v>
+        <v>20794000000</v>
       </c>
       <c r="J157" t="n">
-        <v>345000000</v>
+        <v>10600000000</v>
       </c>
       <c r="K157" t="n">
-        <v>9506000000</v>
+        <v>10773000000</v>
       </c>
       <c r="L157" t="n">
-        <v>152472000000</v>
+        <v>138378000000</v>
       </c>
       <c r="M157" t="n">
-        <v>88663000000</v>
+        <v>42167000000</v>
       </c>
       <c r="N157" t="n">
-        <v>1165053982358</v>
+        <v>357086775600</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>三井松島ホールディングス株式会社</t>
+          <t>株式会社カカクコム</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>41</v>
+        <v>6.7</v>
       </c>
       <c r="D158" t="n">
-        <v>2233</v>
+        <v>3839</v>
       </c>
       <c r="E158" t="n">
-        <v>2920</v>
+        <v>2318.314890576102</v>
       </c>
       <c r="F158" t="n">
-        <v>-23.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>19413000000</v>
+        <v>46452000000</v>
       </c>
       <c r="J158" t="n">
-        <v>3540000000</v>
+        <v>68000000</v>
       </c>
       <c r="K158" t="n">
-        <v>10945000000</v>
+        <v>4669000000</v>
       </c>
       <c r="L158" t="n">
-        <v>35537000000</v>
+        <v>45479000000</v>
       </c>
       <c r="M158" t="n">
-        <v>33898000000</v>
+        <v>51189000000</v>
       </c>
       <c r="N158" t="n">
-        <v>82683434680</v>
+        <v>759493429013</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ノリタケ株式会社</t>
+          <t>古河機械金属株式会社</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>39</v>
+        <v>48.1</v>
       </c>
       <c r="D159" t="n">
-        <v>3485</v>
+        <v>3955</v>
       </c>
       <c r="E159" t="n">
-        <v>3573.410502159827</v>
+        <v>1600</v>
       </c>
       <c r="F159" t="n">
-        <v>-2.5</v>
+        <v>147.2</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="I159" t="n">
-        <v>11733000000</v>
+        <v>14468000000</v>
       </c>
       <c r="J159" t="n">
-        <v>20204000000</v>
+        <v>26121000000</v>
       </c>
       <c r="K159" t="n">
-        <v>42879000000</v>
+        <v>19903000000</v>
       </c>
       <c r="L159" t="n">
-        <v>118800000000</v>
+        <v>100075000000</v>
       </c>
       <c r="M159" t="n">
-        <v>74816000000</v>
+        <v>60492000000</v>
       </c>
       <c r="N159" t="n">
-        <v>191724744890</v>
+        <v>125650812735</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>株式会社ＡＣＳＬ</t>
+          <t>多木化学株式会社</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>8.5</v>
+        <v>32.3</v>
       </c>
       <c r="D160" t="n">
-        <v>1262</v>
+        <v>5420</v>
       </c>
       <c r="E160" t="n">
-        <v>913.2768512341561</v>
+        <v>4695.956053243186</v>
       </c>
       <c r="F160" t="n">
-        <v>38.2</v>
+        <v>15.4</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1891731000</v>
+        <v>6433000000</v>
       </c>
       <c r="J160" t="n">
-        <v>3724000</v>
+        <v>7985000000</v>
       </c>
       <c r="K160" t="n">
-        <v>197577000</v>
+        <v>199000000</v>
       </c>
       <c r="L160" t="n">
-        <v>3572642000</v>
+        <v>29378000000</v>
       </c>
       <c r="M160" t="n">
-        <v>2093032000</v>
+        <v>14617000000</v>
       </c>
       <c r="N160" t="n">
-        <v>24700169404</v>
+        <v>45242739980</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>株式会社スズケン</t>
+          <t>エムスリー株式会社</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>9987</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>77.8</v>
+        <v>7.6</v>
       </c>
       <c r="D161" t="n">
-        <v>5256</v>
+        <v>1742.5</v>
       </c>
       <c r="E161" t="n">
-        <v>4137.137750115735</v>
+        <v>1638.585693292194</v>
       </c>
       <c r="F161" t="n">
-        <v>27</v>
+        <v>6.3</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I161" t="n">
-        <v>168215000000</v>
+        <v>78812000000</v>
       </c>
       <c r="J161" t="n">
-        <v>65453000000</v>
+        <v>345000000</v>
       </c>
       <c r="K161" t="n">
-        <v>38927000000</v>
+        <v>9506000000</v>
       </c>
       <c r="L161" t="n">
-        <v>418062000000</v>
+        <v>152472000000</v>
       </c>
       <c r="M161" t="n">
-        <v>272595000000</v>
+        <v>88663000000</v>
       </c>
       <c r="N161" t="n">
-        <v>350492097384</v>
+        <v>1161056084792</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
+          <t>三井松島ホールディングス株式会社</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>1518</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="D162" t="n">
+        <v>2223</v>
+      </c>
+      <c r="E162" t="n">
+        <v>2920</v>
+      </c>
+      <c r="F162" t="n">
+        <v>-23.9</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>19413000000</v>
+      </c>
+      <c r="J162" t="n">
+        <v>3540000000</v>
+      </c>
+      <c r="K162" t="n">
+        <v>10945000000</v>
+      </c>
+      <c r="L162" t="n">
+        <v>35537000000</v>
+      </c>
+      <c r="M162" t="n">
+        <v>33898000000</v>
+      </c>
+      <c r="N162" t="n">
+        <v>82313155080</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>ノリタケ株式会社</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>5331</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="D163" t="n">
+        <v>3505</v>
+      </c>
+      <c r="E163" t="n">
+        <v>3573.410502159827</v>
+      </c>
+      <c r="F163" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>株式会社ストラテジックキャピタル</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="I163" t="n">
+        <v>11733000000</v>
+      </c>
+      <c r="J163" t="n">
+        <v>20204000000</v>
+      </c>
+      <c r="K163" t="n">
+        <v>42879000000</v>
+      </c>
+      <c r="L163" t="n">
+        <v>118800000000</v>
+      </c>
+      <c r="M163" t="n">
+        <v>74816000000</v>
+      </c>
+      <c r="N163" t="n">
+        <v>192825030370</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>株式会社ＡＣＳＬ</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>6232</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="D164" t="n">
+        <v>1229</v>
+      </c>
+      <c r="E164" t="n">
+        <v>913.2768512341561</v>
+      </c>
+      <c r="F164" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
+        <v>1891731000</v>
+      </c>
+      <c r="J164" t="n">
+        <v>3724000</v>
+      </c>
+      <c r="K164" t="n">
+        <v>197577000</v>
+      </c>
+      <c r="L164" t="n">
+        <v>3572642000</v>
+      </c>
+      <c r="M164" t="n">
+        <v>2093032000</v>
+      </c>
+      <c r="N164" t="n">
+        <v>24054285418</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>株式会社スズケン</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="D165" t="n">
+        <v>5214</v>
+      </c>
+      <c r="E165" t="n">
+        <v>4137.137750115735</v>
+      </c>
+      <c r="F165" t="n">
+        <v>26</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="I165" t="n">
+        <v>168215000000</v>
+      </c>
+      <c r="J165" t="n">
+        <v>65453000000</v>
+      </c>
+      <c r="K165" t="n">
+        <v>38927000000</v>
+      </c>
+      <c r="L165" t="n">
+        <v>418062000000</v>
+      </c>
+      <c r="M165" t="n">
+        <v>272595000000</v>
+      </c>
+      <c r="N165" t="n">
+        <v>347691361446</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
           <t>フォスター電機株式会社</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
+      <c r="B166" t="inlineStr">
         <is>
           <t>6794</t>
         </is>
       </c>
-      <c r="C162" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="D162" t="n">
-        <v>3015</v>
-      </c>
-      <c r="E162" t="n">
+      <c r="C166" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="D166" t="n">
+        <v>3065</v>
+      </c>
+      <c r="E166" t="n">
         <v>2681.96152003832</v>
       </c>
-      <c r="F162" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="G162" t="inlineStr">
+      <c r="F166" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="G166" t="inlineStr">
         <is>
           <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
+      <c r="H166" t="inlineStr">
         <is>
           <t>2026-01-22</t>
         </is>
       </c>
-      <c r="I162" t="n">
+      <c r="I166" t="n">
         <v>12089000000</v>
       </c>
-      <c r="J162" t="n">
+      <c r="J166" t="n">
         <v>7327000000</v>
       </c>
-      <c r="K162" t="n">
+      <c r="K166" t="n">
         <v>1115000000</v>
       </c>
-      <c r="L162" t="n">
+      <c r="L166" t="n">
         <v>51632000000</v>
       </c>
-      <c r="M162" t="n">
+      <c r="M166" t="n">
         <v>20531000000</v>
       </c>
-      <c r="N162" t="n">
-        <v>67740438105</v>
+      <c r="N166" t="n">
+        <v>68863828455</v>
       </c>
     </row>
   </sheetData>

--- a/docs/アクティビスト銘柄_資産判定.xlsx
+++ b/docs/アクティビスト銘柄_資産判定.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N166"/>
+  <dimension ref="A1:N169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -552,16 +552,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>54.8</v>
+        <v>54.5</v>
       </c>
       <c r="D3" t="n">
-        <v>1161</v>
+        <v>1166</v>
       </c>
       <c r="E3" t="n">
         <v>1019.677694332945</v>
       </c>
       <c r="F3" t="n">
-        <v>13.9</v>
+        <v>14.3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         <v>106991000000</v>
       </c>
       <c r="N3" t="n">
-        <v>195338888550</v>
+        <v>196180141300</v>
       </c>
     </row>
     <row r="4">
@@ -607,13 +607,13 @@
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>3443</v>
+        <v>3436</v>
       </c>
       <c r="E4" t="n">
         <v>6116.356643776557</v>
       </c>
       <c r="F4" t="n">
-        <v>-43.7</v>
+        <v>-43.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         <v>219041000000</v>
       </c>
       <c r="N4" t="n">
-        <v>3115081773342</v>
+        <v>3108748467384</v>
       </c>
     </row>
     <row r="5">
@@ -656,16 +656,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30.7</v>
+        <v>30.5</v>
       </c>
       <c r="D5" t="n">
-        <v>2193</v>
+        <v>2203</v>
       </c>
       <c r="E5" t="n">
         <v>1815.198567455447</v>
       </c>
       <c r="F5" t="n">
-        <v>20.8</v>
+        <v>21.4</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         <v>168499000000</v>
       </c>
       <c r="N5" t="n">
-        <v>549603633636</v>
+        <v>552109806156</v>
       </c>
     </row>
     <row r="6">
@@ -708,16 +708,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>54.2</v>
+        <v>53.7</v>
       </c>
       <c r="D6" t="n">
-        <v>10790</v>
+        <v>10890</v>
       </c>
       <c r="E6" t="n">
         <v>5684.0003469471</v>
       </c>
       <c r="F6" t="n">
-        <v>89.8</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>91895000000</v>
       </c>
       <c r="N6" t="n">
-        <v>169522315820</v>
+        <v>171093421620</v>
       </c>
     </row>
     <row r="7">
@@ -760,16 +760,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>54.2</v>
+        <v>53.7</v>
       </c>
       <c r="D7" t="n">
-        <v>10790</v>
+        <v>10890</v>
       </c>
       <c r="E7" t="n">
         <v>4549.503641591014</v>
       </c>
       <c r="F7" t="n">
-        <v>137.2</v>
+        <v>139.4</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>91895000000</v>
       </c>
       <c r="N7" t="n">
-        <v>169522315820</v>
+        <v>171093421620</v>
       </c>
     </row>
     <row r="8">
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="D8" t="n">
-        <v>3865</v>
+        <v>3925</v>
       </c>
       <c r="E8" t="n">
         <v>1361.432492253209</v>
       </c>
       <c r="F8" t="n">
-        <v>183.9</v>
+        <v>188.3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>12397436000</v>
       </c>
       <c r="N8" t="n">
-        <v>85738628425</v>
+        <v>87067501775</v>
       </c>
     </row>
     <row r="9">
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>30.1</v>
+        <v>29.9</v>
       </c>
       <c r="D9" t="n">
-        <v>3323</v>
+        <v>3346</v>
       </c>
       <c r="E9" t="n">
         <v>13739.64575539568</v>
       </c>
       <c r="F9" t="n">
-        <v>-75.8</v>
+        <v>-75.59999999999999</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>325393000000</v>
       </c>
       <c r="N9" t="n">
-        <v>1082408366440</v>
+        <v>1089900208880</v>
       </c>
     </row>
     <row r="10">
@@ -916,16 +916,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>46.5</v>
+        <v>44.9</v>
       </c>
       <c r="D10" t="n">
-        <v>2078</v>
+        <v>2153.5</v>
       </c>
       <c r="E10" t="n">
         <v>1198.150742177053</v>
       </c>
       <c r="F10" t="n">
-        <v>73.40000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>213966000000</v>
       </c>
       <c r="N10" t="n">
-        <v>460097753798</v>
+        <v>476814491244</v>
       </c>
     </row>
     <row r="11">
@@ -968,16 +968,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>46.5</v>
+        <v>44.9</v>
       </c>
       <c r="D11" t="n">
-        <v>2078</v>
+        <v>2153.5</v>
       </c>
       <c r="E11" t="n">
         <v>1188.162962482466</v>
       </c>
       <c r="F11" t="n">
-        <v>74.90000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>213966000000</v>
       </c>
       <c r="N11" t="n">
-        <v>460097753798</v>
+        <v>476814491244</v>
       </c>
     </row>
     <row r="12">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.9</v>
+        <v>24.3</v>
       </c>
       <c r="D12" t="n">
-        <v>3697</v>
+        <v>3636</v>
       </c>
       <c r="E12" t="n">
         <v>2995.424821743842</v>
       </c>
       <c r="F12" t="n">
-        <v>23.4</v>
+        <v>21.4</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>129979000000</v>
       </c>
       <c r="N12" t="n">
-        <v>543332133748</v>
+        <v>534367227024</v>
       </c>
     </row>
     <row r="13">
@@ -1072,16 +1072,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>74.7</v>
+        <v>74.3</v>
       </c>
       <c r="D13" t="n">
-        <v>4815</v>
+        <v>4840</v>
       </c>
       <c r="E13" t="n">
         <v>4991.027246539169</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.5</v>
+        <v>-3</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>1007966000000</v>
       </c>
       <c r="N13" t="n">
-        <v>1349267610690</v>
+        <v>1356273153840</v>
       </c>
     </row>
     <row r="14">
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21.6</v>
+        <v>21.2</v>
       </c>
       <c r="D14" t="n">
-        <v>1696.5</v>
+        <v>1729.5</v>
       </c>
       <c r="E14" t="n">
         <v>1512.21980974841</v>
       </c>
       <c r="F14" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>120816000000</v>
       </c>
       <c r="N14" t="n">
-        <v>558855538430</v>
+        <v>569726291608</v>
       </c>
     </row>
     <row r="15">
@@ -1176,16 +1176,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="D15" t="n">
-        <v>2635</v>
+        <v>2671</v>
       </c>
       <c r="E15" t="n">
         <v>1827.011042553346</v>
       </c>
       <c r="F15" t="n">
-        <v>44.2</v>
+        <v>46.2</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>48336000000</v>
       </c>
       <c r="N15" t="n">
-        <v>643131751585</v>
+        <v>651918371341</v>
       </c>
     </row>
     <row r="16">
@@ -1228,16 +1228,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>134.9</v>
+        <v>134.2</v>
       </c>
       <c r="D16" t="n">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="E16" t="n">
         <v>2122.579027791042</v>
       </c>
       <c r="F16" t="n">
-        <v>-24.9</v>
+        <v>-24.5</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>80333000000</v>
       </c>
       <c r="N16" t="n">
-        <v>59539768638</v>
+        <v>59875940481</v>
       </c>
     </row>
     <row r="17">
@@ -1280,16 +1280,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.6</v>
+        <v>16.9</v>
       </c>
       <c r="D17" t="n">
-        <v>2996.5</v>
+        <v>2938.5</v>
       </c>
       <c r="E17" t="n">
         <v>6272.971195510064</v>
       </c>
       <c r="F17" t="n">
-        <v>-52.2</v>
+        <v>-53.2</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>179622000000</v>
       </c>
       <c r="N17" t="n">
-        <v>1080764237631</v>
+        <v>1059845056659</v>
       </c>
     </row>
     <row r="18">
@@ -1332,16 +1332,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="D18" t="n">
-        <v>3828</v>
+        <v>3915</v>
       </c>
       <c r="E18" t="n">
         <v>1572.181660925393</v>
       </c>
       <c r="F18" t="n">
-        <v>143.5</v>
+        <v>149</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>35501000000</v>
       </c>
       <c r="N18" t="n">
-        <v>683539382196</v>
+        <v>699074368155</v>
       </c>
     </row>
     <row r="19">
@@ -1384,16 +1384,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="D19" t="n">
-        <v>3828</v>
+        <v>3915</v>
       </c>
       <c r="E19" t="n">
         <v>1141.512891683109</v>
       </c>
       <c r="F19" t="n">
-        <v>235.3</v>
+        <v>243</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>35501000000</v>
       </c>
       <c r="N19" t="n">
-        <v>683539382196</v>
+        <v>699074368155</v>
       </c>
     </row>
     <row r="20">
@@ -1436,16 +1436,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>46.8</v>
+        <v>47.8</v>
       </c>
       <c r="D20" t="n">
-        <v>5734</v>
+        <v>5606</v>
       </c>
       <c r="E20" t="n">
         <v>2836.942753814942</v>
       </c>
       <c r="F20" t="n">
-        <v>102.1</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>94351000000</v>
       </c>
       <c r="N20" t="n">
-        <v>201549647014</v>
+        <v>197221440126</v>
       </c>
     </row>
     <row r="21">
@@ -1488,16 +1488,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>55.5</v>
+        <v>53.9</v>
       </c>
       <c r="D21" t="n">
-        <v>4044</v>
+        <v>4166</v>
       </c>
       <c r="E21" t="n">
         <v>2863.970160821546</v>
       </c>
       <c r="F21" t="n">
-        <v>41.2</v>
+        <v>45.5</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>161529000000</v>
       </c>
       <c r="N21" t="n">
-        <v>290946239172</v>
+        <v>299723549058</v>
       </c>
     </row>
     <row r="22">
@@ -1540,16 +1540,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>53</v>
+        <v>51.3</v>
       </c>
       <c r="D22" t="n">
-        <v>4637</v>
+        <v>4787</v>
       </c>
       <c r="E22" t="n">
         <v>2566.284807227078</v>
       </c>
       <c r="F22" t="n">
-        <v>80.7</v>
+        <v>86.5</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>231575000000</v>
       </c>
       <c r="N22" t="n">
-        <v>437209282700</v>
+        <v>451352347700</v>
       </c>
     </row>
     <row r="23">
@@ -1595,13 +1595,13 @@
         <v>28.8</v>
       </c>
       <c r="D23" t="n">
-        <v>5133</v>
+        <v>5136</v>
       </c>
       <c r="E23" t="n">
         <v>2779.139169918938</v>
       </c>
       <c r="F23" t="n">
-        <v>84.7</v>
+        <v>84.8</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>183216000000</v>
       </c>
       <c r="N23" t="n">
-        <v>636658673643</v>
+        <v>637030771056</v>
       </c>
     </row>
     <row r="24">
@@ -1644,16 +1644,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>4027</v>
+        <v>3994</v>
       </c>
       <c r="E24" t="n">
         <v>2420.370957920882</v>
       </c>
       <c r="F24" t="n">
-        <v>66.40000000000001</v>
+        <v>65</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>18167000000</v>
       </c>
       <c r="N24" t="n">
-        <v>199083117133</v>
+        <v>197451693526</v>
       </c>
     </row>
     <row r="25">
@@ -1696,16 +1696,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>1742</v>
+        <v>1725</v>
       </c>
       <c r="E25" t="n">
         <v>1344.518957928979</v>
       </c>
       <c r="F25" t="n">
-        <v>29.6</v>
+        <v>28.3</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>45956000000</v>
       </c>
       <c r="N25" t="n">
-        <v>560499392726</v>
+        <v>554094651975</v>
       </c>
     </row>
     <row r="26">
@@ -1748,16 +1748,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>59.8</v>
+        <v>59.7</v>
       </c>
       <c r="D26" t="n">
-        <v>5008</v>
+        <v>5018</v>
       </c>
       <c r="E26" t="n">
         <v>4154.626869982095</v>
       </c>
       <c r="F26" t="n">
-        <v>20.5</v>
+        <v>20.8</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>179086000000</v>
       </c>
       <c r="N26" t="n">
-        <v>299481785408</v>
+        <v>300079792168</v>
       </c>
     </row>
     <row r="27">
@@ -1800,16 +1800,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>13.9</v>
+        <v>14.2</v>
       </c>
       <c r="D27" t="n">
-        <v>3922</v>
+        <v>3858</v>
       </c>
       <c r="E27" t="n">
         <v>2561.705402476645</v>
       </c>
       <c r="F27" t="n">
-        <v>53.1</v>
+        <v>50.6</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>100104000000</v>
       </c>
       <c r="N27" t="n">
-        <v>717653070410</v>
+        <v>705942260490</v>
       </c>
     </row>
     <row r="28">
@@ -1852,16 +1852,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>44.6</v>
+        <v>44.1</v>
       </c>
       <c r="D28" t="n">
-        <v>3466</v>
+        <v>3504</v>
       </c>
       <c r="E28" t="n">
         <v>2560</v>
       </c>
       <c r="F28" t="n">
-        <v>35.4</v>
+        <v>36.9</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>190312000000</v>
       </c>
       <c r="N28" t="n">
-        <v>426700320596</v>
+        <v>431378512224</v>
       </c>
     </row>
     <row r="29">
@@ -1904,16 +1904,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>89.8</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>4280</v>
+        <v>4415</v>
       </c>
       <c r="E29" t="n">
         <v>3449.780346820809</v>
       </c>
       <c r="F29" t="n">
-        <v>24.1</v>
+        <v>28</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>90928000000</v>
       </c>
       <c r="N29" t="n">
-        <v>101209211360</v>
+        <v>104401557980</v>
       </c>
     </row>
     <row r="30">
@@ -1956,16 +1956,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>56.7</v>
+        <v>55.5</v>
       </c>
       <c r="D30" t="n">
-        <v>1683</v>
+        <v>1721</v>
       </c>
       <c r="E30" t="n">
         <v>1746.940387696806</v>
       </c>
       <c r="F30" t="n">
-        <v>-3.7</v>
+        <v>-1.5</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>36070000000</v>
       </c>
       <c r="N30" t="n">
-        <v>63586252719</v>
+        <v>65021949453</v>
       </c>
     </row>
     <row r="31">
@@ -2011,13 +2011,13 @@
         <v>104.5</v>
       </c>
       <c r="D31" t="n">
-        <v>1697</v>
+        <v>1702</v>
       </c>
       <c r="E31" t="n">
         <v>2298.672482457804</v>
       </c>
       <c r="F31" t="n">
-        <v>-26.2</v>
+        <v>-26</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>42752000000</v>
       </c>
       <c r="N31" t="n">
-        <v>40917532839</v>
+        <v>40917079074</v>
       </c>
     </row>
     <row r="32">
@@ -2060,16 +2060,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>67.8</v>
+        <v>66.7</v>
       </c>
       <c r="D32" t="n">
-        <v>2640</v>
+        <v>2684</v>
       </c>
       <c r="E32" t="n">
         <v>1270</v>
       </c>
       <c r="F32" t="n">
-        <v>107.9</v>
+        <v>111.3</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>31108000000</v>
       </c>
       <c r="N32" t="n">
-        <v>45903161040</v>
+        <v>46668213724</v>
       </c>
     </row>
     <row r="33">
@@ -2112,16 +2112,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>67.8</v>
+        <v>66.7</v>
       </c>
       <c r="D33" t="n">
-        <v>2640</v>
+        <v>2684</v>
       </c>
       <c r="E33" t="n">
         <v>1170</v>
       </c>
       <c r="F33" t="n">
-        <v>125.6</v>
+        <v>129.4</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>31108000000</v>
       </c>
       <c r="N33" t="n">
-        <v>45903161040</v>
+        <v>46668213724</v>
       </c>
     </row>
     <row r="34">
@@ -2167,13 +2167,13 @@
         <v>33.2</v>
       </c>
       <c r="D34" t="n">
-        <v>2859.5</v>
+        <v>2868</v>
       </c>
       <c r="E34" t="n">
         <v>2381.523440544182</v>
       </c>
       <c r="F34" t="n">
-        <v>20.1</v>
+        <v>20.4</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>168696000000</v>
       </c>
       <c r="N34" t="n">
-        <v>507820580914</v>
+        <v>508392991392</v>
       </c>
     </row>
     <row r="35">
@@ -2216,16 +2216,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>81.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="D35" t="n">
-        <v>2543</v>
+        <v>2486</v>
       </c>
       <c r="E35" t="n">
-        <v>2987.584858837727</v>
+        <v>2901.475903614458</v>
       </c>
       <c r="F35" t="n">
-        <v>-14.9</v>
+        <v>-14.3</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -2253,7 +2253,7 @@
         <v>108430000000</v>
       </c>
       <c r="N35" t="n">
-        <v>133168986012</v>
+        <v>130184073624</v>
       </c>
     </row>
     <row r="36">
@@ -2268,16 +2268,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>81.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="D36" t="n">
-        <v>2543</v>
+        <v>2486</v>
       </c>
       <c r="E36" t="n">
-        <v>3016.088716673414</v>
+        <v>2905.067038344418</v>
       </c>
       <c r="F36" t="n">
-        <v>-15.7</v>
+        <v>-14.4</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -2305,7 +2305,7 @@
         <v>108430000000</v>
       </c>
       <c r="N36" t="n">
-        <v>133168986012</v>
+        <v>130184073624</v>
       </c>
     </row>
     <row r="37">
@@ -2320,16 +2320,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>81.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="D37" t="n">
-        <v>2543</v>
+        <v>2486</v>
       </c>
       <c r="E37" t="n">
-        <v>3016.087384069568</v>
+        <v>2955.342465753425</v>
       </c>
       <c r="F37" t="n">
-        <v>-15.7</v>
+        <v>-15.9</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -2357,7 +2357,7 @@
         <v>108430000000</v>
       </c>
       <c r="N37" t="n">
-        <v>133168986012</v>
+        <v>130184073624</v>
       </c>
     </row>
     <row r="38">
@@ -2372,16 +2372,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>81.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="D38" t="n">
-        <v>2543</v>
+        <v>2486</v>
       </c>
       <c r="E38" t="n">
-        <v>2939.562915943684</v>
+        <v>2987.584858837727</v>
       </c>
       <c r="F38" t="n">
-        <v>-13.5</v>
+        <v>-16.8</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -2409,863 +2409,863 @@
         <v>108430000000</v>
       </c>
       <c r="N38" t="n">
-        <v>133168986012</v>
+        <v>130184073624</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>イワブチ株式会社</t>
+          <t>ガンホー・オンライン・エンターテイメント株式会社</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5983</t>
+          <t>3765</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>46.2</v>
+        <v>83.3</v>
       </c>
       <c r="D39" t="n">
-        <v>14130</v>
+        <v>2486</v>
       </c>
       <c r="E39" t="n">
-        <v>7040.15625</v>
+        <v>3016.088716673414</v>
       </c>
       <c r="F39" t="n">
-        <v>100.7</v>
+        <v>-17.6</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5250258000</v>
+        <v>102086000000</v>
       </c>
       <c r="J39" t="n">
-        <v>1349641000</v>
+        <v>1326000000</v>
       </c>
       <c r="K39" t="n">
-        <v>200000000</v>
+        <v>5018000000</v>
       </c>
       <c r="L39" t="n">
-        <v>18087189000</v>
+        <v>118672000000</v>
       </c>
       <c r="M39" t="n">
-        <v>6799899000</v>
+        <v>108430000000</v>
       </c>
       <c r="N39" t="n">
-        <v>14717341710</v>
+        <v>130184073624</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>イワブチ株式会社</t>
+          <t>ガンホー・オンライン・エンターテイメント株式会社</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5983</t>
+          <t>3765</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>46.2</v>
+        <v>83.3</v>
       </c>
       <c r="D40" t="n">
-        <v>14130</v>
+        <v>2486</v>
       </c>
       <c r="E40" t="n">
-        <v>7040.15625</v>
+        <v>3016.087384069568</v>
       </c>
       <c r="F40" t="n">
-        <v>100.7</v>
+        <v>-17.6</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5250258000</v>
+        <v>102086000000</v>
       </c>
       <c r="J40" t="n">
-        <v>1349641000</v>
+        <v>1326000000</v>
       </c>
       <c r="K40" t="n">
-        <v>200000000</v>
+        <v>5018000000</v>
       </c>
       <c r="L40" t="n">
-        <v>18087189000</v>
+        <v>118672000000</v>
       </c>
       <c r="M40" t="n">
-        <v>6799899000</v>
+        <v>108430000000</v>
       </c>
       <c r="N40" t="n">
-        <v>14717341710</v>
+        <v>130184073624</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>新家工業株式会社</t>
+          <t>ガンホー・オンライン・エンターテイメント株式会社</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>3765</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>87</v>
+        <v>83.3</v>
       </c>
       <c r="D41" t="n">
-        <v>2756</v>
+        <v>2486</v>
       </c>
       <c r="E41" t="n">
-        <v>4265.455132343447</v>
+        <v>2939.562915943684</v>
       </c>
       <c r="F41" t="n">
-        <v>-35.4</v>
+        <v>-15.4</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>8141000000</v>
+        <v>102086000000</v>
       </c>
       <c r="J41" t="n">
-        <v>5422000000</v>
+        <v>1326000000</v>
       </c>
       <c r="K41" t="n">
-        <v>9306000000</v>
+        <v>5018000000</v>
       </c>
       <c r="L41" t="n">
-        <v>28847000000</v>
+        <v>118672000000</v>
       </c>
       <c r="M41" t="n">
-        <v>22869000000</v>
+        <v>108430000000</v>
       </c>
       <c r="N41" t="n">
-        <v>26275202408</v>
+        <v>130184073624</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>カヤバ株式会社</t>
+          <t>イワブチ株式会社</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>7242</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>33.1</v>
+        <v>47.6</v>
       </c>
       <c r="D42" t="n">
-        <v>4650</v>
+        <v>13900</v>
       </c>
       <c r="E42" t="n">
-        <v>2824.318397803668</v>
+        <v>7040.15625</v>
       </c>
       <c r="F42" t="n">
-        <v>64.59999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>14514000000</v>
+        <v>5250258000</v>
       </c>
       <c r="J42" t="n">
-        <v>27587000000</v>
+        <v>1349641000</v>
       </c>
       <c r="K42" t="n">
-        <v>19874000000</v>
+        <v>200000000</v>
       </c>
       <c r="L42" t="n">
-        <v>86299000000</v>
+        <v>18087189000</v>
       </c>
       <c r="M42" t="n">
-        <v>61975000000</v>
+        <v>6799899000</v>
       </c>
       <c r="N42" t="n">
-        <v>187072545750</v>
+        <v>14281791300</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ニッタ株式会社</t>
+          <t>イワブチ株式会社</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5186</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>29.2</v>
+        <v>47.6</v>
       </c>
       <c r="D43" t="n">
-        <v>6610</v>
+        <v>13900</v>
       </c>
       <c r="E43" t="n">
-        <v>3096.322467304314</v>
+        <v>7040.15625</v>
       </c>
       <c r="F43" t="n">
-        <v>113.5</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>30872000000</v>
+        <v>5250258000</v>
       </c>
       <c r="J43" t="n">
-        <v>15392000000</v>
+        <v>1349641000</v>
       </c>
       <c r="K43" t="n">
-        <v>6697000000</v>
+        <v>200000000</v>
       </c>
       <c r="L43" t="n">
-        <v>119214000000</v>
+        <v>18087189000</v>
       </c>
       <c r="M43" t="n">
-        <v>52961000000</v>
+        <v>6799899000</v>
       </c>
       <c r="N43" t="n">
-        <v>181333253700</v>
+        <v>14281791300</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>東京瓦斯株式会社</t>
+          <t>新家工業株式会社</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>9531</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>23.7</v>
+        <v>86.7</v>
       </c>
       <c r="D44" t="n">
-        <v>6335</v>
+        <v>2768</v>
       </c>
       <c r="E44" t="n">
-        <v>3322.047887165483</v>
+        <v>4265.455132343447</v>
       </c>
       <c r="F44" t="n">
-        <v>90.7</v>
+        <v>-35.1</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>179699000000</v>
+        <v>8141000000</v>
       </c>
       <c r="J44" t="n">
-        <v>313045000000</v>
+        <v>5422000000</v>
       </c>
       <c r="K44" t="n">
-        <v>103000000</v>
+        <v>9306000000</v>
       </c>
       <c r="L44" t="n">
-        <v>1281150000000</v>
+        <v>28847000000</v>
       </c>
       <c r="M44" t="n">
-        <v>492847000000</v>
+        <v>22869000000</v>
       </c>
       <c r="N44" t="n">
-        <v>2081078845580</v>
+        <v>26389608224</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>株式会社イエローハット</t>
+          <t>カヤバ株式会社</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>9882</t>
+          <t>7242</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>35.5</v>
+        <v>33</v>
       </c>
       <c r="D45" t="n">
-        <v>1752</v>
+        <v>4675</v>
       </c>
       <c r="E45" t="n">
-        <v>2112.609181636727</v>
+        <v>2824.318397803668</v>
       </c>
       <c r="F45" t="n">
-        <v>-17.1</v>
+        <v>65.5</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>10902000000</v>
+        <v>14514000000</v>
       </c>
       <c r="J45" t="n">
-        <v>29975000000</v>
+        <v>27587000000</v>
       </c>
       <c r="K45" t="n">
-        <v>11341000000</v>
+        <v>19874000000</v>
       </c>
       <c r="L45" t="n">
-        <v>98298000000</v>
+        <v>86299000000</v>
       </c>
       <c r="M45" t="n">
-        <v>52218000000</v>
+        <v>61975000000</v>
       </c>
       <c r="N45" t="n">
-        <v>147097937520</v>
+        <v>188078312125</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>株式会社インフォマート</t>
+          <t>ニッタ株式会社</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3.7</v>
+        <v>28.6</v>
       </c>
       <c r="D46" t="n">
-        <v>712</v>
+        <v>6740</v>
       </c>
       <c r="E46" t="n">
-        <v>404.9347366248775</v>
+        <v>3096.322467304314</v>
       </c>
       <c r="F46" t="n">
-        <v>75.8</v>
+        <v>117.7</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>6410479000</v>
+        <v>30872000000</v>
       </c>
       <c r="J46" t="n">
-        <v>196639000</v>
+        <v>15392000000</v>
       </c>
       <c r="K46" t="n">
-        <v>437854000</v>
+        <v>6697000000</v>
       </c>
       <c r="L46" t="n">
-        <v>11425263000</v>
+        <v>119214000000</v>
       </c>
       <c r="M46" t="n">
-        <v>7044972000</v>
+        <v>52961000000</v>
       </c>
       <c r="N46" t="n">
-        <v>189809306760</v>
+        <v>184899565800</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ニデック株式会社</t>
+          <t>東京瓦斯株式会社</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>6594</t>
+          <t>9531</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6.8</v>
+        <v>23.5</v>
       </c>
       <c r="D47" t="n">
-        <v>2642</v>
+        <v>6424</v>
       </c>
       <c r="E47" t="n">
-        <v>2220.184278344451</v>
+        <v>3322.047887165483</v>
       </c>
       <c r="F47" t="n">
-        <v>19</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>163815000000</v>
+        <v>179699000000</v>
       </c>
       <c r="J47" t="n">
-        <v>17829000000</v>
+        <v>313045000000</v>
       </c>
       <c r="K47" t="n">
-        <v>25472000000</v>
+        <v>103000000</v>
       </c>
       <c r="L47" t="n">
-        <v>298063000000</v>
+        <v>1281150000000</v>
       </c>
       <c r="M47" t="n">
-        <v>207116000000</v>
+        <v>492847000000</v>
       </c>
       <c r="N47" t="n">
-        <v>3028550584070</v>
+        <v>2098501478216</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>株式会社堀場製作所</t>
+          <t>株式会社イエローハット</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>9882</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>21.2</v>
+        <v>35.4</v>
       </c>
       <c r="D48" t="n">
-        <v>21560</v>
+        <v>1757</v>
       </c>
       <c r="E48" t="n">
-        <v>11879.91675437757</v>
+        <v>2112.609181636727</v>
       </c>
       <c r="F48" t="n">
-        <v>81.5</v>
+        <v>-16.8</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>133938000000</v>
+        <v>10902000000</v>
       </c>
       <c r="J48" t="n">
-        <v>55958000000</v>
+        <v>29975000000</v>
       </c>
       <c r="K48" t="n">
-        <v>2062000000</v>
+        <v>11341000000</v>
       </c>
       <c r="L48" t="n">
-        <v>204493000000</v>
+        <v>98298000000</v>
       </c>
       <c r="M48" t="n">
-        <v>191958000000</v>
+        <v>52218000000</v>
       </c>
       <c r="N48" t="n">
-        <v>905984725800</v>
+        <v>147517737570</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ＫＰＰグループホールディングス株式会社</t>
+          <t>株式会社インフォマート</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>9274</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>74.40000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="D49" t="n">
-        <v>1102</v>
+        <v>708</v>
       </c>
       <c r="E49" t="n">
-        <v>730</v>
+        <v>404.9347366248775</v>
       </c>
       <c r="F49" t="n">
-        <v>51</v>
+        <v>74.8</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>22631000000</v>
+        <v>6410479000</v>
       </c>
       <c r="J49" t="n">
-        <v>7793000000</v>
+        <v>196639000</v>
       </c>
       <c r="K49" t="n">
-        <v>19603000000</v>
+        <v>437854000</v>
       </c>
       <c r="L49" t="n">
-        <v>56374000000</v>
+        <v>11425263000</v>
       </c>
       <c r="M49" t="n">
-        <v>50027000000</v>
+        <v>7044972000</v>
       </c>
       <c r="N49" t="n">
-        <v>67281712972</v>
+        <v>188742962340</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NIPPON EXPRESSホールディングス株式会社</t>
+          <t>ニデック株式会社</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>9147</t>
+          <t>6594</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>23.9</v>
+        <v>6.8</v>
       </c>
       <c r="D50" t="n">
-        <v>5481</v>
+        <v>2646</v>
       </c>
       <c r="E50" t="n">
-        <v>3341.42986565678</v>
+        <v>2220.184278344451</v>
       </c>
       <c r="F50" t="n">
-        <v>64</v>
+        <v>19.2</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>274075000000</v>
+        <v>163815000000</v>
       </c>
       <c r="J50" t="n">
-        <v>89000000</v>
+        <v>17829000000</v>
       </c>
       <c r="K50" t="n">
-        <v>36943000000</v>
+        <v>25472000000</v>
       </c>
       <c r="L50" t="n">
-        <v>771274000000</v>
+        <v>298063000000</v>
       </c>
       <c r="M50" t="n">
-        <v>311107000000</v>
+        <v>207116000000</v>
       </c>
       <c r="N50" t="n">
-        <v>1302416557533</v>
+        <v>3033135823410</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ＫＨネオケム株式会社</t>
+          <t>株式会社堀場製作所</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>4189</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>29</v>
+        <v>20.6</v>
       </c>
       <c r="D51" t="n">
-        <v>3185</v>
+        <v>22130</v>
       </c>
       <c r="E51" t="n">
-        <v>2550.198980592041</v>
+        <v>11879.91675437757</v>
       </c>
       <c r="F51" t="n">
-        <v>24.9</v>
+        <v>86.3</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>16934000000</v>
+        <v>133938000000</v>
       </c>
       <c r="J51" t="n">
-        <v>8038000000</v>
+        <v>55958000000</v>
       </c>
       <c r="K51" t="n">
-        <v>7370000000</v>
+        <v>2062000000</v>
       </c>
       <c r="L51" t="n">
-        <v>57505000000</v>
+        <v>204493000000</v>
       </c>
       <c r="M51" t="n">
-        <v>32342000000</v>
+        <v>191958000000</v>
       </c>
       <c r="N51" t="n">
-        <v>111532062460</v>
+        <v>929937012150</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>イオンフィナンシャルサービス株式会社</t>
+          <t>ＫＰＰグループホールディングス株式会社</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>8570</t>
+          <t>9274</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>210.4</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D52" t="n">
-        <v>1645</v>
+        <v>1131</v>
       </c>
       <c r="E52" t="n">
-        <v>1288.711724885291</v>
+        <v>730</v>
       </c>
       <c r="F52" t="n">
-        <v>27.6</v>
+        <v>54.9</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>697628000000</v>
+        <v>22631000000</v>
       </c>
       <c r="J52" t="n">
-        <v>34512000000</v>
+        <v>7793000000</v>
       </c>
       <c r="K52" t="n">
-        <v>14926000000</v>
+        <v>19603000000</v>
       </c>
       <c r="L52" t="n">
-        <v>509055000000</v>
+        <v>56374000000</v>
       </c>
       <c r="M52" t="n">
-        <v>747066000000</v>
+        <v>50027000000</v>
       </c>
       <c r="N52" t="n">
-        <v>355129464585</v>
+        <v>69052284366</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>株式会社フジ・メディア・ホールディングス</t>
+          <t>NIPPON EXPRESSホールディングス株式会社</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>9147</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>66.90000000000001</v>
+        <v>23.8</v>
       </c>
       <c r="D53" t="n">
-        <v>4109</v>
+        <v>5497</v>
       </c>
       <c r="E53" t="n">
-        <v>3141.424011416125</v>
+        <v>3341.42986565678</v>
       </c>
       <c r="F53" t="n">
-        <v>30.8</v>
+        <v>64.5</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>102598000000</v>
+        <v>274075000000</v>
       </c>
       <c r="J53" t="n">
-        <v>174990000000</v>
+        <v>89000000</v>
       </c>
       <c r="K53" t="n">
-        <v>113991000000</v>
+        <v>36943000000</v>
       </c>
       <c r="L53" t="n">
-        <v>808788000000</v>
+        <v>771274000000</v>
       </c>
       <c r="M53" t="n">
-        <v>391579000000</v>
+        <v>311107000000</v>
       </c>
       <c r="N53" t="n">
-        <v>585514436836</v>
+        <v>1306218539821</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>株式会社フジ・メディア・ホールディングス</t>
+          <t>ＫＨネオケム株式会社</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4189</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>66.90000000000001</v>
+        <v>28.4</v>
       </c>
       <c r="D54" t="n">
-        <v>4109</v>
+        <v>3255</v>
       </c>
       <c r="E54" t="n">
-        <v>2420</v>
+        <v>2550.198980592041</v>
       </c>
       <c r="F54" t="n">
-        <v>69.8</v>
+        <v>27.6</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>株式会社レノ代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>102598000000</v>
+        <v>16934000000</v>
       </c>
       <c r="J54" t="n">
-        <v>174990000000</v>
+        <v>8038000000</v>
       </c>
       <c r="K54" t="n">
-        <v>113991000000</v>
+        <v>7370000000</v>
       </c>
       <c r="L54" t="n">
-        <v>808788000000</v>
+        <v>57505000000</v>
       </c>
       <c r="M54" t="n">
-        <v>391579000000</v>
+        <v>32342000000</v>
       </c>
       <c r="N54" t="n">
-        <v>585514436836</v>
+        <v>113953045080</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>株式会社クスリのアオキホールディングス</t>
+          <t>イオンフィナンシャルサービス株式会社</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>3549</t>
+          <t>8570</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>42.2</v>
+        <v>211.1</v>
       </c>
       <c r="D55" t="n">
-        <v>4057</v>
+        <v>1639.5</v>
       </c>
       <c r="E55" t="n">
-        <v>3047.091476167608</v>
+        <v>1288.711724885291</v>
       </c>
       <c r="F55" t="n">
-        <v>33.1</v>
+        <v>27.2</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -3274,390 +3274,390 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>26348000000</v>
+        <v>697628000000</v>
       </c>
       <c r="J55" t="n">
-        <v>132363000000</v>
+        <v>34512000000</v>
       </c>
       <c r="K55" t="n">
-        <v>3747000000</v>
+        <v>14926000000</v>
       </c>
       <c r="L55" t="n">
-        <v>86930000000</v>
+        <v>509055000000</v>
       </c>
       <c r="M55" t="n">
-        <v>162458000000</v>
+        <v>747066000000</v>
       </c>
       <c r="N55" t="n">
-        <v>385265162819</v>
+        <v>353942101634</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>リンナイ株式会社</t>
+          <t>株式会社フジ・メディア・ホールディングス</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>45.8</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="D56" t="n">
-        <v>3461</v>
+        <v>4096</v>
       </c>
       <c r="E56" t="n">
-        <v>2844.704547285864</v>
+        <v>3141.424011416125</v>
       </c>
       <c r="F56" t="n">
-        <v>21.7</v>
+        <v>30.4</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>147972000000</v>
+        <v>102598000000</v>
       </c>
       <c r="J56" t="n">
-        <v>64736000000</v>
+        <v>174990000000</v>
       </c>
       <c r="K56" t="n">
-        <v>5967000000</v>
+        <v>113991000000</v>
       </c>
       <c r="L56" t="n">
-        <v>378856000000</v>
+        <v>808788000000</v>
       </c>
       <c r="M56" t="n">
-        <v>218675000000</v>
+        <v>391579000000</v>
       </c>
       <c r="N56" t="n">
-        <v>477858927132</v>
+        <v>583661993984</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>センコーグループホールディングス株式会社</t>
+          <t>株式会社フジ・メディア・ホールディングス</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>9069</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>54.1</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="D57" t="n">
-        <v>2288.5</v>
+        <v>4096</v>
       </c>
       <c r="E57" t="n">
-        <v>1556.090471804319</v>
+        <v>2420</v>
       </c>
       <c r="F57" t="n">
-        <v>47.1</v>
+        <v>69.3</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社レノ代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>42193000000</v>
+        <v>102598000000</v>
       </c>
       <c r="J57" t="n">
-        <v>138228000000</v>
+        <v>174990000000</v>
       </c>
       <c r="K57" t="n">
-        <v>27045000000</v>
+        <v>113991000000</v>
       </c>
       <c r="L57" t="n">
-        <v>160854000000</v>
+        <v>808788000000</v>
       </c>
       <c r="M57" t="n">
-        <v>207466000000</v>
+        <v>391579000000</v>
       </c>
       <c r="N57" t="n">
-        <v>383137477542</v>
+        <v>583661993984</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ブロードメディア株式会社</t>
+          <t>株式会社クスリのアオキホールディングス</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>3549</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>45.9</v>
+        <v>42.8</v>
       </c>
       <c r="D58" t="n">
-        <v>1843</v>
+        <v>3993</v>
       </c>
       <c r="E58" t="n">
-        <v>1529.631984751819</v>
+        <v>3047.091476167608</v>
       </c>
       <c r="F58" t="n">
-        <v>20.5</v>
+        <v>31</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5301579000</v>
+        <v>26348000000</v>
       </c>
       <c r="J58" t="n">
-        <v>553048000</v>
+        <v>132363000000</v>
       </c>
       <c r="K58" t="n">
-        <v>169455000</v>
+        <v>3747000000</v>
       </c>
       <c r="L58" t="n">
-        <v>4610613000</v>
+        <v>86930000000</v>
       </c>
       <c r="M58" t="n">
-        <v>6024082000</v>
+        <v>162458000000</v>
       </c>
       <c r="N58" t="n">
-        <v>13135372467</v>
+        <v>379187526531</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ブロードメディア株式会社</t>
+          <t>リンナイ株式会社</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>5947</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>45.9</v>
+        <v>45.8</v>
       </c>
       <c r="D59" t="n">
-        <v>1843</v>
+        <v>3456</v>
       </c>
       <c r="E59" t="n">
-        <v>1449.995380693296</v>
+        <v>2844.704547285864</v>
       </c>
       <c r="F59" t="n">
-        <v>27.1</v>
+        <v>21.5</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5301579000</v>
+        <v>147972000000</v>
       </c>
       <c r="J59" t="n">
-        <v>553048000</v>
+        <v>64736000000</v>
       </c>
       <c r="K59" t="n">
-        <v>169455000</v>
+        <v>5967000000</v>
       </c>
       <c r="L59" t="n">
-        <v>4610613000</v>
+        <v>378856000000</v>
       </c>
       <c r="M59" t="n">
-        <v>6024082000</v>
+        <v>218675000000</v>
       </c>
       <c r="N59" t="n">
-        <v>13135372467</v>
+        <v>477168579072</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>株式会社ニップン</t>
+          <t>センコーグループホールディングス株式会社</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>9069</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>66.8</v>
+        <v>53.4</v>
       </c>
       <c r="D60" t="n">
-        <v>2994</v>
+        <v>2323.5</v>
       </c>
       <c r="E60" t="n">
-        <v>2723.418631349517</v>
+        <v>1556.090471804319</v>
       </c>
       <c r="F60" t="n">
-        <v>9.9</v>
+        <v>49.3</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>31215000000</v>
+        <v>42193000000</v>
       </c>
       <c r="J60" t="n">
-        <v>48537000000</v>
+        <v>138228000000</v>
       </c>
       <c r="K60" t="n">
-        <v>85530000000</v>
+        <v>27045000000</v>
       </c>
       <c r="L60" t="n">
-        <v>178697000000</v>
+        <v>160854000000</v>
       </c>
       <c r="M60" t="n">
-        <v>165282000000</v>
+        <v>207466000000</v>
       </c>
       <c r="N60" t="n">
-        <v>247497614796</v>
+        <v>388619792318</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>株式会社ニップン</t>
+          <t>ブロードメディア株式会社</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>66.8</v>
+        <v>44.6</v>
       </c>
       <c r="D61" t="n">
-        <v>2994</v>
+        <v>1896</v>
       </c>
       <c r="E61" t="n">
-        <v>2709.132103263819</v>
+        <v>1529.631984751819</v>
       </c>
       <c r="F61" t="n">
-        <v>10.5</v>
+        <v>24</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>31215000000</v>
+        <v>5301579000</v>
       </c>
       <c r="J61" t="n">
-        <v>48537000000</v>
+        <v>553048000</v>
       </c>
       <c r="K61" t="n">
-        <v>85530000000</v>
+        <v>169455000</v>
       </c>
       <c r="L61" t="n">
-        <v>178697000000</v>
+        <v>4610613000</v>
       </c>
       <c r="M61" t="n">
-        <v>165282000000</v>
+        <v>6024082000</v>
       </c>
       <c r="N61" t="n">
-        <v>247497614796</v>
+        <v>13513112424</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>株式会社ニップン</t>
+          <t>ブロードメディア株式会社</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>66.8</v>
+        <v>44.6</v>
       </c>
       <c r="D62" t="n">
-        <v>2994</v>
+        <v>1896</v>
       </c>
       <c r="E62" t="n">
-        <v>2696.128808062088</v>
+        <v>1449.995380693296</v>
       </c>
       <c r="F62" t="n">
-        <v>11</v>
+        <v>30.8</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>31215000000</v>
+        <v>5301579000</v>
       </c>
       <c r="J62" t="n">
-        <v>48537000000</v>
+        <v>553048000</v>
       </c>
       <c r="K62" t="n">
-        <v>85530000000</v>
+        <v>169455000</v>
       </c>
       <c r="L62" t="n">
-        <v>178697000000</v>
+        <v>4610613000</v>
       </c>
       <c r="M62" t="n">
-        <v>165282000000</v>
+        <v>6024082000</v>
       </c>
       <c r="N62" t="n">
-        <v>247497614796</v>
+        <v>13513112424</v>
       </c>
     </row>
     <row r="63">
@@ -3672,16 +3672,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>66.8</v>
+        <v>67.3</v>
       </c>
       <c r="D63" t="n">
-        <v>2994</v>
+        <v>2973</v>
       </c>
       <c r="E63" t="n">
-        <v>2696.128808062088</v>
+        <v>2723.418631349517</v>
       </c>
       <c r="F63" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -3709,187 +3709,187 @@
         <v>165282000000</v>
       </c>
       <c r="N63" t="n">
-        <v>247497614796</v>
+        <v>245761659582</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>京浜急行電鉄株式会社</t>
+          <t>株式会社ニップン</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>118.9</v>
+        <v>67.3</v>
       </c>
       <c r="D64" t="n">
-        <v>1574.5</v>
+        <v>2973</v>
       </c>
       <c r="E64" t="n">
-        <v>1160.8</v>
+        <v>2709.132103263819</v>
       </c>
       <c r="F64" t="n">
-        <v>35.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>61234000000</v>
+        <v>31215000000</v>
       </c>
       <c r="J64" t="n">
-        <v>318113000000</v>
+        <v>48537000000</v>
       </c>
       <c r="K64" t="n">
-        <v>114136000000</v>
+        <v>85530000000</v>
       </c>
       <c r="L64" t="n">
-        <v>256898000000</v>
+        <v>178697000000</v>
       </c>
       <c r="M64" t="n">
-        <v>493483000000</v>
+        <v>165282000000</v>
       </c>
       <c r="N64" t="n">
-        <v>414890954334</v>
+        <v>245761659582</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>あいホールディングス株式会社</t>
+          <t>株式会社ニップン</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>3076</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>23.5</v>
+        <v>67.3</v>
       </c>
       <c r="D65" t="n">
-        <v>2967</v>
+        <v>2973</v>
       </c>
       <c r="E65" t="n">
-        <v>2007.754513143541</v>
+        <v>2696.128808062088</v>
       </c>
       <c r="F65" t="n">
-        <v>47.8</v>
+        <v>10.3</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>32012000000</v>
+        <v>31215000000</v>
       </c>
       <c r="J65" t="n">
-        <v>1646000000</v>
+        <v>48537000000</v>
       </c>
       <c r="K65" t="n">
-        <v>3550000000</v>
+        <v>85530000000</v>
       </c>
       <c r="L65" t="n">
-        <v>53765000000</v>
+        <v>178697000000</v>
       </c>
       <c r="M65" t="n">
-        <v>37208000000</v>
+        <v>165282000000</v>
       </c>
       <c r="N65" t="n">
-        <v>158060786277</v>
+        <v>245761659582</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>エア・ウォーター株式会社</t>
+          <t>株式会社ニップン</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>14.9</v>
+        <v>67.3</v>
       </c>
       <c r="D66" t="n">
-        <v>3000</v>
+        <v>2973</v>
       </c>
       <c r="E66" t="n">
-        <v>2261.880826568852</v>
+        <v>2696.128808062088</v>
       </c>
       <c r="F66" t="n">
-        <v>32.6</v>
+        <v>10.3</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>29189000000</v>
+        <v>31215000000</v>
       </c>
       <c r="J66" t="n">
-        <v>31318000000</v>
+        <v>48537000000</v>
       </c>
       <c r="K66" t="n">
-        <v>42001000000</v>
+        <v>85530000000</v>
       </c>
       <c r="L66" t="n">
-        <v>194657000000</v>
+        <v>178697000000</v>
       </c>
       <c r="M66" t="n">
-        <v>102508000000</v>
+        <v>165282000000</v>
       </c>
       <c r="N66" t="n">
-        <v>687791679000</v>
+        <v>245761659582</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>エア・ウォーター株式会社</t>
+          <t>京浜急行電鉄株式会社</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>14.9</v>
+        <v>119.7</v>
       </c>
       <c r="D67" t="n">
-        <v>3000</v>
+        <v>1565</v>
       </c>
       <c r="E67" t="n">
-        <v>1970</v>
+        <v>1160.8</v>
       </c>
       <c r="F67" t="n">
-        <v>52.3</v>
+        <v>34.8</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3898,1182 +3898,1182 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>29189000000</v>
+        <v>61234000000</v>
       </c>
       <c r="J67" t="n">
-        <v>31318000000</v>
+        <v>318113000000</v>
       </c>
       <c r="K67" t="n">
-        <v>42001000000</v>
+        <v>114136000000</v>
       </c>
       <c r="L67" t="n">
-        <v>194657000000</v>
+        <v>256898000000</v>
       </c>
       <c r="M67" t="n">
-        <v>102508000000</v>
+        <v>493483000000</v>
       </c>
       <c r="N67" t="n">
-        <v>687791679000</v>
+        <v>412387642765</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>株式会社電通総研</t>
+          <t>あいホールディングス株式会社</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>9.6</v>
+        <v>23.4</v>
       </c>
       <c r="D68" t="n">
-        <v>2864</v>
+        <v>2990</v>
       </c>
       <c r="E68" t="n">
-        <v>1910.426979628923</v>
+        <v>2007.754513143541</v>
       </c>
       <c r="F68" t="n">
-        <v>49.9</v>
+        <v>48.9</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>49748000000</v>
+        <v>32012000000</v>
       </c>
       <c r="J68" t="n">
-        <v>524000000</v>
+        <v>1646000000</v>
       </c>
       <c r="K68" t="n">
-        <v>3388000000</v>
+        <v>3550000000</v>
       </c>
       <c r="L68" t="n">
-        <v>65471000000</v>
+        <v>53765000000</v>
       </c>
       <c r="M68" t="n">
-        <v>53660000000</v>
+        <v>37208000000</v>
       </c>
       <c r="N68" t="n">
-        <v>558995869408</v>
+        <v>159286063690</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>わかもと製薬株式会社</t>
+          <t>エア・ウォーター株式会社</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>49.3</v>
+        <v>14.7</v>
       </c>
       <c r="D69" t="n">
-        <v>302</v>
+        <v>3040</v>
       </c>
       <c r="E69" t="n">
-        <v>290.3401328717133</v>
+        <v>2261.880826568852</v>
       </c>
       <c r="F69" t="n">
-        <v>4</v>
+        <v>34.4</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3231889000</v>
+        <v>29189000000</v>
       </c>
       <c r="J69" t="n">
-        <v>82947000</v>
+        <v>31318000000</v>
       </c>
       <c r="K69" t="n">
-        <v>1847919000</v>
+        <v>42001000000</v>
       </c>
       <c r="L69" t="n">
-        <v>11480803000</v>
+        <v>194657000000</v>
       </c>
       <c r="M69" t="n">
-        <v>5162755000</v>
+        <v>102508000000</v>
       </c>
       <c r="N69" t="n">
-        <v>10481163378</v>
+        <v>696962234720</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>株式会社豊田自動織機</t>
+          <t>エア・ウォーター株式会社</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>6201</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
+          <t>4088</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="D70" t="n">
+        <v>3040</v>
+      </c>
       <c r="E70" t="n">
-        <v>16430.4430802409</v>
-      </c>
-      <c r="F70" t="inlineStr"/>
+        <v>1970</v>
+      </c>
+      <c r="F70" t="n">
+        <v>54.3</v>
+      </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>281605000000</v>
+        <v>29189000000</v>
       </c>
       <c r="J70" t="n">
-        <v>87540000000</v>
+        <v>31318000000</v>
       </c>
       <c r="K70" t="n">
-        <v>730709000000</v>
+        <v>42001000000</v>
       </c>
       <c r="L70" t="n">
-        <v>3246174000000</v>
+        <v>194657000000</v>
       </c>
       <c r="M70" t="n">
-        <v>1099854000000</v>
-      </c>
-      <c r="N70" t="inlineStr"/>
+        <v>102508000000</v>
+      </c>
+      <c r="N70" t="n">
+        <v>696962234720</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>株式会社豊田自動織機</t>
+          <t>株式会社電通総研</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>6201</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
+          <t>4812</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="D71" t="n">
+        <v>2861</v>
+      </c>
       <c r="E71" t="n">
-        <v>16430443.10823975</v>
-      </c>
-      <c r="F71" t="inlineStr"/>
+        <v>1910.426979628923</v>
+      </c>
+      <c r="F71" t="n">
+        <v>49.8</v>
+      </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>281605000000</v>
+        <v>49748000000</v>
       </c>
       <c r="J71" t="n">
-        <v>87540000000</v>
+        <v>524000000</v>
       </c>
       <c r="K71" t="n">
-        <v>730709000000</v>
+        <v>3388000000</v>
       </c>
       <c r="L71" t="n">
-        <v>3246174000000</v>
+        <v>65471000000</v>
       </c>
       <c r="M71" t="n">
-        <v>1099854000000</v>
-      </c>
-      <c r="N71" t="inlineStr"/>
+        <v>53660000000</v>
+      </c>
+      <c r="N71" t="n">
+        <v>558410329042</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>大阪製鐵株式会社</t>
+          <t>わかもと製薬株式会社</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>4512</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>94.59999999999999</v>
+        <v>49.6</v>
       </c>
       <c r="D72" t="n">
-        <v>2551</v>
+        <v>300</v>
       </c>
       <c r="E72" t="n">
-        <v>1748.071046781136</v>
+        <v>290.3401328717133</v>
       </c>
       <c r="F72" t="n">
-        <v>45.9</v>
+        <v>3.3</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>62396000000</v>
+        <v>3231889000</v>
       </c>
       <c r="J72" t="n">
-        <v>9241000000</v>
+        <v>82947000</v>
       </c>
       <c r="K72" t="n">
-        <v>553000000</v>
+        <v>1847919000</v>
       </c>
       <c r="L72" t="n">
-        <v>151028000000</v>
+        <v>11480803000</v>
       </c>
       <c r="M72" t="n">
-        <v>72190000000</v>
+        <v>5162755000</v>
       </c>
       <c r="N72" t="n">
-        <v>76322192989</v>
+        <v>10411751700</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>株式会社ディー・エヌ・エー</t>
+          <t>株式会社豊田自動織機</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2432</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="D73" t="n">
-        <v>2558.5</v>
-      </c>
+          <t>6201</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="n">
-        <v>2551.08574256026</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0.3</v>
-      </c>
+        <v>16430.4430802409</v>
+      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>85363000000</v>
+        <v>281605000000</v>
       </c>
       <c r="J73" t="n">
-        <v>221000000</v>
+        <v>87540000000</v>
       </c>
       <c r="K73" t="n">
-        <v>93552000000</v>
+        <v>730709000000</v>
       </c>
       <c r="L73" t="n">
-        <v>177857000000</v>
+        <v>3246174000000</v>
       </c>
       <c r="M73" t="n">
-        <v>179136000000</v>
-      </c>
-      <c r="N73" t="n">
-        <v>236691033498</v>
-      </c>
+        <v>1099854000000</v>
+      </c>
+      <c r="N73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>株式会社ディー・エヌ・エー</t>
+          <t>株式会社豊田自動織機</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2432</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="D74" t="n">
-        <v>2558.5</v>
-      </c>
+          <t>6201</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="n">
-        <v>2260</v>
-      </c>
-      <c r="F74" t="n">
-        <v>13.2</v>
-      </c>
+        <v>16430443.10823975</v>
+      </c>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>85363000000</v>
+        <v>281605000000</v>
       </c>
       <c r="J74" t="n">
-        <v>221000000</v>
+        <v>87540000000</v>
       </c>
       <c r="K74" t="n">
-        <v>93552000000</v>
+        <v>730709000000</v>
       </c>
       <c r="L74" t="n">
-        <v>177857000000</v>
+        <v>3246174000000</v>
       </c>
       <c r="M74" t="n">
-        <v>179136000000</v>
-      </c>
-      <c r="N74" t="n">
-        <v>236691033498</v>
-      </c>
+        <v>1099854000000</v>
+      </c>
+      <c r="N74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>株式会社ディー・エヌ・エー</t>
+          <t>大阪製鐵株式会社</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>5449</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>75.7</v>
+        <v>95.5</v>
       </c>
       <c r="D75" t="n">
-        <v>2558.5</v>
+        <v>2527</v>
       </c>
       <c r="E75" t="n">
-        <v>2260</v>
+        <v>1748.071046781136</v>
       </c>
       <c r="F75" t="n">
-        <v>13.2</v>
+        <v>44.6</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>85363000000</v>
+        <v>62396000000</v>
       </c>
       <c r="J75" t="n">
-        <v>221000000</v>
+        <v>9241000000</v>
       </c>
       <c r="K75" t="n">
-        <v>93552000000</v>
+        <v>553000000</v>
       </c>
       <c r="L75" t="n">
-        <v>177857000000</v>
+        <v>151028000000</v>
       </c>
       <c r="M75" t="n">
-        <v>179136000000</v>
+        <v>72190000000</v>
       </c>
       <c r="N75" t="n">
-        <v>236691033498</v>
+        <v>75604148053</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>株式会社オリエントコーポレーション</t>
+          <t>株式会社ディー・エヌ・エー</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>8585</t>
+          <t>2432</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>307.5</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="D76" t="n">
-        <v>853</v>
+        <v>2535</v>
       </c>
       <c r="E76" t="n">
-        <v>798.3805136422309</v>
+        <v>2551.08574256026</v>
       </c>
       <c r="F76" t="n">
-        <v>6.8</v>
+        <v>-0.6</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>408187000000</v>
+        <v>85363000000</v>
       </c>
       <c r="J76" t="n">
-        <v>18930000000</v>
+        <v>221000000</v>
       </c>
       <c r="K76" t="n">
-        <v>21921000000</v>
+        <v>93552000000</v>
       </c>
       <c r="L76" t="n">
-        <v>216837000000</v>
+        <v>177857000000</v>
       </c>
       <c r="M76" t="n">
-        <v>449038000000</v>
+        <v>179136000000</v>
       </c>
       <c r="N76" t="n">
-        <v>146021541992</v>
+        <v>234517009935</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>東ソー株式会社</t>
+          <t>株式会社ディー・エヌ・エー</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>4042</t>
+          <t>2432</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>43.2</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="D77" t="n">
-        <v>2561</v>
+        <v>2535</v>
       </c>
       <c r="E77" t="n">
-        <v>2032.365850102071</v>
+        <v>2260</v>
       </c>
       <c r="F77" t="n">
-        <v>26</v>
+        <v>12.2</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>160812000000</v>
+        <v>85363000000</v>
       </c>
       <c r="J77" t="n">
-        <v>109648000000</v>
+        <v>221000000</v>
       </c>
       <c r="K77" t="n">
-        <v>70132000000</v>
+        <v>93552000000</v>
       </c>
       <c r="L77" t="n">
-        <v>759724000000</v>
+        <v>177857000000</v>
       </c>
       <c r="M77" t="n">
-        <v>340592000000</v>
+        <v>179136000000</v>
       </c>
       <c r="N77" t="n">
-        <v>788507688306</v>
+        <v>234517009935</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>株式会社西武ホールディングス</t>
+          <t>株式会社ディー・エヌ・エー</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>2432</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>63.7</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="D78" t="n">
-        <v>3494</v>
+        <v>2535</v>
       </c>
       <c r="E78" t="n">
-        <v>1716.713876475349</v>
+        <v>2260</v>
       </c>
       <c r="F78" t="n">
-        <v>103.5</v>
+        <v>12.2</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>87210000000</v>
+        <v>85363000000</v>
       </c>
       <c r="J78" t="n">
-        <v>428181000000</v>
+        <v>221000000</v>
       </c>
       <c r="K78" t="n">
-        <v>49954000000</v>
+        <v>93552000000</v>
       </c>
       <c r="L78" t="n">
-        <v>387217000000</v>
+        <v>177857000000</v>
       </c>
       <c r="M78" t="n">
-        <v>565345000000</v>
+        <v>179136000000</v>
       </c>
       <c r="N78" t="n">
-        <v>888097191272</v>
+        <v>234517009935</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>株式会社オリエントコーポレーション</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>8585</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>305.7</v>
+      </c>
+      <c r="D79" t="n">
+        <v>858</v>
+      </c>
+      <c r="E79" t="n">
+        <v>798.3805136422309</v>
+      </c>
+      <c r="F79" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>株式会社ストラテジックキャピタル</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>408187000000</v>
+      </c>
+      <c r="J79" t="n">
+        <v>18930000000</v>
+      </c>
+      <c r="K79" t="n">
+        <v>21921000000</v>
+      </c>
+      <c r="L79" t="n">
+        <v>216837000000</v>
+      </c>
+      <c r="M79" t="n">
+        <v>449038000000</v>
+      </c>
+      <c r="N79" t="n">
+        <v>146877471312</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>東ソー株式会社</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>4042</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="D80" t="n">
+        <v>2613.5</v>
+      </c>
+      <c r="E80" t="n">
+        <v>2032.365850102071</v>
+      </c>
+      <c r="F80" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>2024-06-04</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>160812000000</v>
+      </c>
+      <c r="J80" t="n">
+        <v>109648000000</v>
+      </c>
+      <c r="K80" t="n">
+        <v>70132000000</v>
+      </c>
+      <c r="L80" t="n">
+        <v>759724000000</v>
+      </c>
+      <c r="M80" t="n">
+        <v>340592000000</v>
+      </c>
+      <c r="N80" t="n">
+        <v>804671941971</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>株式会社西武ホールディングス</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>9024</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="D81" t="n">
+        <v>3551</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1716.713876475349</v>
+      </c>
+      <c r="F81" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>87210000000</v>
+      </c>
+      <c r="J81" t="n">
+        <v>428181000000</v>
+      </c>
+      <c r="K81" t="n">
+        <v>49954000000</v>
+      </c>
+      <c r="L81" t="n">
+        <v>387217000000</v>
+      </c>
+      <c r="M81" t="n">
+        <v>565345000000</v>
+      </c>
+      <c r="N81" t="n">
+        <v>902585325188</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
           <t>株式会社フェローテック
 （旧会社名　株式会社フェローテックホールディングス）</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>6890</t>
         </is>
       </c>
-      <c r="C79" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="D79" t="n">
-        <v>8760</v>
-      </c>
-      <c r="E79" t="n">
+      <c r="C82" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="D82" t="n">
+        <v>9100</v>
+      </c>
+      <c r="E82" t="n">
         <v>4037.502552255647</v>
       </c>
-      <c r="F79" t="n">
-        <v>117</v>
-      </c>
-      <c r="G79" t="inlineStr">
+      <c r="F82" t="n">
+        <v>125.4</v>
+      </c>
+      <c r="G82" t="inlineStr">
         <is>
           <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="I79" t="n">
+      <c r="I82" t="n">
         <v>52579000000</v>
       </c>
-      <c r="J79" t="n">
+      <c r="J82" t="n">
         <v>90505000000</v>
       </c>
-      <c r="K79" t="n">
+      <c r="K82" t="n">
         <v>11654000000</v>
       </c>
-      <c r="L79" t="n">
+      <c r="L82" t="n">
         <v>160957000000</v>
       </c>
-      <c r="M79" t="n">
+      <c r="M82" t="n">
         <v>154738000000</v>
       </c>
-      <c r="N79" t="n">
-        <v>471320963880</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="N82" t="n">
+        <v>489614243300</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t>株式会社フェローテック
 （旧会社名　株式会社フェローテックホールディングス）</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>6890</t>
         </is>
       </c>
-      <c r="C80" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="D80" t="n">
-        <v>8760</v>
-      </c>
-      <c r="E80" t="n">
+      <c r="C83" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="D83" t="n">
+        <v>9100</v>
+      </c>
+      <c r="E83" t="n">
         <v>3950.736048458928</v>
       </c>
-      <c r="F80" t="n">
-        <v>121.7</v>
-      </c>
-      <c r="G80" t="inlineStr">
+      <c r="F83" t="n">
+        <v>130.3</v>
+      </c>
+      <c r="G83" t="inlineStr">
         <is>
           <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="I80" t="n">
+      <c r="I83" t="n">
         <v>52579000000</v>
       </c>
-      <c r="J80" t="n">
+      <c r="J83" t="n">
         <v>90505000000</v>
       </c>
-      <c r="K80" t="n">
+      <c r="K83" t="n">
         <v>11654000000</v>
       </c>
-      <c r="L80" t="n">
+      <c r="L83" t="n">
         <v>160957000000</v>
       </c>
-      <c r="M80" t="n">
+      <c r="M83" t="n">
         <v>154738000000</v>
       </c>
-      <c r="N80" t="n">
-        <v>471320963880</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="N83" t="n">
+        <v>489614243300</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
         <is>
           <t>株式会社フェローテック
 （旧会社名　株式会社フェローテックホールディングス）</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>6890</t>
         </is>
       </c>
-      <c r="C81" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="D81" t="n">
-        <v>8760</v>
-      </c>
-      <c r="E81" t="n">
+      <c r="C84" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="D84" t="n">
+        <v>9100</v>
+      </c>
+      <c r="E84" t="n">
         <v>2030</v>
       </c>
-      <c r="F81" t="n">
-        <v>331.5</v>
-      </c>
-      <c r="G81" t="inlineStr">
+      <c r="F84" t="n">
+        <v>348.3</v>
+      </c>
+      <c r="G84" t="inlineStr">
         <is>
           <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>2025-10-22</t>
         </is>
       </c>
-      <c r="I81" t="n">
+      <c r="I84" t="n">
         <v>52579000000</v>
       </c>
-      <c r="J81" t="n">
+      <c r="J84" t="n">
         <v>90505000000</v>
       </c>
-      <c r="K81" t="n">
+      <c r="K84" t="n">
         <v>11654000000</v>
       </c>
-      <c r="L81" t="n">
+      <c r="L84" t="n">
         <v>160957000000</v>
       </c>
-      <c r="M81" t="n">
+      <c r="M84" t="n">
         <v>154738000000</v>
       </c>
-      <c r="N81" t="n">
-        <v>471320963880</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="N84" t="n">
+        <v>489614243300</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
         <is>
           <t>株式会社フェローテック
 （旧会社名　株式会社フェローテックホールディングス）</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>6890</t>
         </is>
       </c>
-      <c r="C82" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="D82" t="n">
-        <v>8760</v>
-      </c>
-      <c r="E82" t="n">
+      <c r="C85" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="D85" t="n">
+        <v>9100</v>
+      </c>
+      <c r="E85" t="n">
         <v>2387</v>
       </c>
-      <c r="F82" t="n">
-        <v>267</v>
-      </c>
-      <c r="G82" t="inlineStr">
+      <c r="F85" t="n">
+        <v>281.2</v>
+      </c>
+      <c r="G85" t="inlineStr">
         <is>
           <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>2025-03-07</t>
         </is>
       </c>
-      <c r="I82" t="n">
+      <c r="I85" t="n">
         <v>52579000000</v>
       </c>
-      <c r="J82" t="n">
+      <c r="J85" t="n">
         <v>90505000000</v>
       </c>
-      <c r="K82" t="n">
+      <c r="K85" t="n">
         <v>11654000000</v>
       </c>
-      <c r="L82" t="n">
+      <c r="L85" t="n">
         <v>160957000000</v>
       </c>
-      <c r="M82" t="n">
+      <c r="M85" t="n">
         <v>154738000000</v>
       </c>
-      <c r="N82" t="n">
-        <v>471320963880</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>アツギ株式会社</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>3529</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="D83" t="n">
-        <v>1045</v>
-      </c>
-      <c r="E83" t="n">
-        <v>668.9358717434869</v>
-      </c>
-      <c r="F83" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="I83" t="n">
-        <v>5500000000</v>
-      </c>
-      <c r="J83" t="n">
-        <v>3208000000</v>
-      </c>
-      <c r="K83" t="n">
-        <v>3702000000</v>
-      </c>
-      <c r="L83" t="n">
-        <v>32145000000</v>
-      </c>
-      <c r="M83" t="n">
-        <v>12410000000</v>
-      </c>
-      <c r="N83" t="n">
-        <v>16734636270</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>日本特殊塗料株式会社</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>4619</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="D84" t="n">
-        <v>2620</v>
-      </c>
-      <c r="E84" t="n">
-        <v>1190</v>
-      </c>
-      <c r="F84" t="n">
-        <v>120.2</v>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="I84" t="n">
-        <v>8931000000</v>
-      </c>
-      <c r="J84" t="n">
-        <v>9514000000</v>
-      </c>
-      <c r="K84" t="n">
-        <v>22055000000</v>
-      </c>
-      <c r="L84" t="n">
-        <v>49725000000</v>
-      </c>
-      <c r="M84" t="n">
-        <v>40500000000</v>
-      </c>
-      <c r="N84" t="n">
-        <v>55784639140</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>株式会社エクセディ</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>7278</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="D85" t="n">
-        <v>5880</v>
-      </c>
-      <c r="E85" t="n">
-        <v>2617.980935875217</v>
-      </c>
-      <c r="F85" t="n">
-        <v>124.6</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="I85" t="n">
-        <v>30019000000</v>
-      </c>
-      <c r="J85" t="n">
-        <v>6792000000</v>
-      </c>
-      <c r="K85" t="n">
-        <v>3427000000</v>
-      </c>
-      <c r="L85" t="n">
-        <v>119460000000</v>
-      </c>
-      <c r="M85" t="n">
-        <v>40238000000</v>
-      </c>
       <c r="N85" t="n">
-        <v>210466168080</v>
+        <v>489614243300</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>株式会社Ａ＆Ｄホロンホールディングス</t>
+          <t>アツギ株式会社</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>7745</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>19.9</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="D86" t="n">
-        <v>2831</v>
+        <v>1049</v>
       </c>
       <c r="E86" t="n">
-        <v>2084.177692465894</v>
+        <v>668.9358717434869</v>
       </c>
       <c r="F86" t="n">
-        <v>35.8</v>
+        <v>56.8</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>11012000000</v>
+        <v>5500000000</v>
       </c>
       <c r="J86" t="n">
-        <v>4106000000</v>
+        <v>3208000000</v>
       </c>
       <c r="K86" t="n">
-        <v>315000000</v>
+        <v>3702000000</v>
       </c>
       <c r="L86" t="n">
-        <v>27041000000</v>
+        <v>32145000000</v>
       </c>
       <c r="M86" t="n">
-        <v>15433000000</v>
+        <v>12410000000</v>
       </c>
       <c r="N86" t="n">
-        <v>77533505751</v>
+        <v>16798692294</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>株式会社セプテーニ・ホールディングス</t>
+          <t>日本特殊塗料株式会社</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>4293</t>
+          <t>4619</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>13.1</v>
+        <v>71.8</v>
       </c>
       <c r="D87" t="n">
-        <v>513</v>
+        <v>2651</v>
       </c>
       <c r="E87" t="n">
-        <v>448.6811097117532</v>
+        <v>1190</v>
       </c>
       <c r="F87" t="n">
-        <v>14.3</v>
+        <v>122.8</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>12184507000</v>
+        <v>8931000000</v>
       </c>
       <c r="J87" t="n">
-        <v>168073000</v>
+        <v>9514000000</v>
       </c>
       <c r="K87" t="n">
-        <v>1600720000</v>
+        <v>22055000000</v>
       </c>
       <c r="L87" t="n">
-        <v>11861578000</v>
+        <v>49725000000</v>
       </c>
       <c r="M87" t="n">
-        <v>13953300000</v>
+        <v>40500000000</v>
       </c>
       <c r="N87" t="n">
-        <v>106419340917</v>
+        <v>56444686397</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>株式会社シンクロ・フード</t>
+          <t>株式会社エクセディ</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>7278</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>33.9</v>
+        <v>19.1</v>
       </c>
       <c r="D88" t="n">
-        <v>327</v>
+        <v>5900</v>
       </c>
       <c r="E88" t="n">
-        <v>421.6950726175476</v>
+        <v>2617.980935875217</v>
       </c>
       <c r="F88" t="n">
-        <v>-22.5</v>
+        <v>125.4</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3037851000</v>
+        <v>30019000000</v>
       </c>
       <c r="J88" t="n">
-        <v>56852000</v>
+        <v>6792000000</v>
       </c>
       <c r="K88" t="n">
-        <v>14952000</v>
+        <v>3427000000</v>
       </c>
       <c r="L88" t="n">
-        <v>2871237000</v>
+        <v>119460000000</v>
       </c>
       <c r="M88" t="n">
-        <v>3109655000</v>
+        <v>40238000000</v>
       </c>
       <c r="N88" t="n">
-        <v>9169926276</v>
+        <v>211182039400</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>科研製薬株式会社</t>
+          <t>株式会社Ａ＆Ｄホロンホールディングス</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>7745</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>71.8</v>
+        <v>19.5</v>
       </c>
       <c r="D89" t="n">
-        <v>3905</v>
+        <v>2886</v>
       </c>
       <c r="E89" t="n">
-        <v>3530</v>
+        <v>2084.177692465894</v>
       </c>
       <c r="F89" t="n">
-        <v>10.6</v>
+        <v>38.5</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>74625000000</v>
+        <v>11012000000</v>
       </c>
       <c r="J89" t="n">
-        <v>15530000000</v>
+        <v>4106000000</v>
       </c>
       <c r="K89" t="n">
-        <v>15992000000</v>
+        <v>315000000</v>
       </c>
       <c r="L89" t="n">
-        <v>138325000000</v>
+        <v>27041000000</v>
       </c>
       <c r="M89" t="n">
-        <v>106147000000</v>
+        <v>15433000000</v>
       </c>
       <c r="N89" t="n">
-        <v>147875770075</v>
+        <v>79039808406</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>市光工業株式会社</t>
+          <t>株式会社セプテーニ・ホールディングス</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>7244</t>
+          <t>4293</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>35.7</v>
+        <v>13.5</v>
       </c>
       <c r="D90" t="n">
-        <v>556</v>
+        <v>507</v>
       </c>
       <c r="E90" t="n">
-        <v>549.4799823005444</v>
+        <v>448.6811097117532</v>
       </c>
       <c r="F90" t="n">
-        <v>1.2</v>
+        <v>13</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -5082,414 +5082,414 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>5720000000</v>
+        <v>12184507000</v>
       </c>
       <c r="J90" t="n">
-        <v>9921000000</v>
+        <v>168073000</v>
       </c>
       <c r="K90" t="n">
-        <v>3474000000</v>
+        <v>1600720000</v>
       </c>
       <c r="L90" t="n">
-        <v>49523000000</v>
+        <v>11861578000</v>
       </c>
       <c r="M90" t="n">
-        <v>19115000000</v>
+        <v>13953300000</v>
       </c>
       <c r="N90" t="n">
-        <v>53545251960</v>
+        <v>103562195802</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>トーセイ株式会社</t>
+          <t>株式会社シンクロ・フード</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>47.2</v>
+        <v>33.6</v>
       </c>
       <c r="D91" t="n">
-        <v>1665</v>
+        <v>330</v>
       </c>
       <c r="E91" t="n">
-        <v>1752.426893379333</v>
+        <v>421.6950726175476</v>
       </c>
       <c r="F91" t="n">
-        <v>-5</v>
+        <v>-21.7</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>20753937000</v>
+        <v>3037851000</v>
       </c>
       <c r="J91" t="n">
-        <v>46868512000</v>
+        <v>56852000</v>
       </c>
       <c r="K91" t="n">
-        <v>8610046000</v>
+        <v>14952000</v>
       </c>
       <c r="L91" t="n">
-        <v>59467346000</v>
+        <v>2871237000</v>
       </c>
       <c r="M91" t="n">
-        <v>76232495000</v>
+        <v>3109655000</v>
       </c>
       <c r="N91" t="n">
-        <v>161515156500</v>
+        <v>9254054040</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>トーセイ株式会社</t>
+          <t>科研製薬株式会社</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>4521</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>47.2</v>
+        <v>71.5</v>
       </c>
       <c r="D92" t="n">
-        <v>1665</v>
+        <v>3920</v>
       </c>
       <c r="E92" t="n">
-        <v>1576.721867844292</v>
+        <v>3530</v>
       </c>
       <c r="F92" t="n">
-        <v>5.6</v>
+        <v>11</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>20753937000</v>
+        <v>74625000000</v>
       </c>
       <c r="J92" t="n">
-        <v>46868512000</v>
+        <v>15530000000</v>
       </c>
       <c r="K92" t="n">
-        <v>8610046000</v>
+        <v>15992000000</v>
       </c>
       <c r="L92" t="n">
-        <v>59467346000</v>
+        <v>138325000000</v>
       </c>
       <c r="M92" t="n">
-        <v>76232495000</v>
+        <v>106147000000</v>
       </c>
       <c r="N92" t="n">
-        <v>161515156500</v>
+        <v>148443794800</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>株式会社髙島屋</t>
+          <t>市光工業株式会社</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>65.2</v>
+        <v>35.8</v>
       </c>
       <c r="D93" t="n">
-        <v>2103</v>
+        <v>555</v>
       </c>
       <c r="E93" t="n">
-        <v>1101.400153022188</v>
+        <v>549.4799823005444</v>
       </c>
       <c r="F93" t="n">
-        <v>90.90000000000001</v>
+        <v>1</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>88996000000</v>
+        <v>5720000000</v>
       </c>
       <c r="J93" t="n">
-        <v>193090000000</v>
+        <v>9921000000</v>
       </c>
       <c r="K93" t="n">
-        <v>119967000000</v>
+        <v>3474000000</v>
       </c>
       <c r="L93" t="n">
-        <v>420489000000</v>
+        <v>49523000000</v>
       </c>
       <c r="M93" t="n">
-        <v>402053000000</v>
+        <v>19115000000</v>
       </c>
       <c r="N93" t="n">
-        <v>616209283200</v>
+        <v>53448947550</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>株式会社髙島屋</t>
+          <t>トーセイ株式会社</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>65.2</v>
+        <v>47</v>
       </c>
       <c r="D94" t="n">
-        <v>2103</v>
+        <v>1673</v>
       </c>
       <c r="E94" t="n">
-        <v>1101.400153022188</v>
+        <v>1752.426893379333</v>
       </c>
       <c r="F94" t="n">
-        <v>90.90000000000001</v>
+        <v>-4.5</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>88996000000</v>
+        <v>20753937000</v>
       </c>
       <c r="J94" t="n">
-        <v>193090000000</v>
+        <v>46868512000</v>
       </c>
       <c r="K94" t="n">
-        <v>119967000000</v>
+        <v>8610046000</v>
       </c>
       <c r="L94" t="n">
-        <v>420489000000</v>
+        <v>59467346000</v>
       </c>
       <c r="M94" t="n">
-        <v>402053000000</v>
+        <v>76232495000</v>
       </c>
       <c r="N94" t="n">
-        <v>616209283200</v>
+        <v>162291205300</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>三井倉庫ホールディングス株式会社</t>
+          <t>トーセイ株式会社</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>9302</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>44.6</v>
+        <v>47</v>
       </c>
       <c r="D95" t="n">
-        <v>3369</v>
+        <v>1673</v>
       </c>
       <c r="E95" t="n">
-        <v>1492.806001579363</v>
+        <v>1576.721867844292</v>
       </c>
       <c r="F95" t="n">
-        <v>125.7</v>
+        <v>6.1</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>22822000000</v>
+        <v>20753937000</v>
       </c>
       <c r="J95" t="n">
-        <v>72331000000</v>
+        <v>46868512000</v>
       </c>
       <c r="K95" t="n">
-        <v>17148000000</v>
+        <v>8610046000</v>
       </c>
       <c r="L95" t="n">
-        <v>88631000000</v>
+        <v>59467346000</v>
       </c>
       <c r="M95" t="n">
-        <v>112301000000</v>
+        <v>76232495000</v>
       </c>
       <c r="N95" t="n">
-        <v>252015636165</v>
+        <v>162291205300</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>京阪神ビルディング株式会社</t>
+          <t>株式会社髙島屋</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>8818</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>83.3</v>
+        <v>65</v>
       </c>
       <c r="D96" t="n">
-        <v>1091</v>
+        <v>2111.5</v>
       </c>
       <c r="E96" t="n">
-        <v>1341.977644710579</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="F96" t="n">
-        <v>-18.7</v>
+        <v>91.7</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>9876000000</v>
+        <v>88996000000</v>
       </c>
       <c r="J96" t="n">
-        <v>54379000000</v>
+        <v>193090000000</v>
       </c>
       <c r="K96" t="n">
-        <v>22399000000</v>
+        <v>119967000000</v>
       </c>
       <c r="L96" t="n">
-        <v>70510000000</v>
+        <v>420489000000</v>
       </c>
       <c r="M96" t="n">
-        <v>86654000000</v>
+        <v>402053000000</v>
       </c>
       <c r="N96" t="n">
-        <v>104086486242</v>
+        <v>618699905600</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>株式会社メルカリ</t>
+          <t>株式会社髙島屋</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>27.5</v>
+        <v>65</v>
       </c>
       <c r="D97" t="n">
-        <v>3867</v>
+        <v>2111.5</v>
       </c>
       <c r="E97" t="n">
-        <v>2006.059650428343</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="F97" t="n">
-        <v>92.8</v>
+        <v>91.7</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>171463000000</v>
+        <v>88996000000</v>
       </c>
       <c r="J97" t="n">
-        <v>434000000</v>
+        <v>193090000000</v>
       </c>
       <c r="K97" t="n">
-        <v>1543000000</v>
+        <v>119967000000</v>
       </c>
       <c r="L97" t="n">
-        <v>40013000000</v>
+        <v>420489000000</v>
       </c>
       <c r="M97" t="n">
-        <v>173440000000</v>
+        <v>402053000000</v>
       </c>
       <c r="N97" t="n">
-        <v>631019445939</v>
+        <v>618699905600</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>サッポロホールディングス株式会社</t>
+          <t>三井倉庫ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2501</t>
+          <t>9302</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>44.2</v>
       </c>
       <c r="D98" t="n">
-        <v>1859.5</v>
+        <v>3397</v>
       </c>
       <c r="E98" t="n">
-        <v>2697.360927565142</v>
+        <v>1492.806001579363</v>
       </c>
       <c r="F98" t="n">
-        <v>-31.1</v>
+        <v>127.6</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -5498,102 +5498,102 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2925000000</v>
+        <v>22822000000</v>
       </c>
       <c r="J98" t="n">
-        <v>23000000</v>
+        <v>72331000000</v>
       </c>
       <c r="K98" t="n">
-        <v>4391000000</v>
+        <v>17148000000</v>
       </c>
       <c r="L98" t="n">
-        <v>142395000000</v>
+        <v>88631000000</v>
       </c>
       <c r="M98" t="n">
-        <v>7339000000</v>
+        <v>112301000000</v>
       </c>
       <c r="N98" t="n">
-        <v>725154774905</v>
+        <v>254110156145</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>株式会社クレハ</t>
+          <t>京阪神ビルディング株式会社</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>8818</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>17.7</v>
+        <v>81.8</v>
       </c>
       <c r="D99" t="n">
-        <v>4405</v>
+        <v>1110</v>
       </c>
       <c r="E99" t="n">
-        <v>7960</v>
+        <v>1341.977644710579</v>
       </c>
       <c r="F99" t="n">
-        <v>-44.7</v>
+        <v>-17.3</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>5294000000</v>
+        <v>9876000000</v>
       </c>
       <c r="J99" t="n">
-        <v>5963000000</v>
+        <v>54379000000</v>
       </c>
       <c r="K99" t="n">
-        <v>18608000000</v>
+        <v>22399000000</v>
       </c>
       <c r="L99" t="n">
-        <v>155874000000</v>
+        <v>70510000000</v>
       </c>
       <c r="M99" t="n">
-        <v>29865000000</v>
+        <v>86654000000</v>
       </c>
       <c r="N99" t="n">
-        <v>168363742870</v>
+        <v>105899174820</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>コムシスホールディングス株式会社</t>
+          <t>株式会社メルカリ</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>17.9</v>
+        <v>29.4</v>
       </c>
       <c r="D100" t="n">
-        <v>5387</v>
+        <v>3621</v>
       </c>
       <c r="E100" t="n">
-        <v>3953.24613842911</v>
+        <v>2006.059650428343</v>
       </c>
       <c r="F100" t="n">
-        <v>36.3</v>
+        <v>80.5</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -5602,206 +5602,206 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>34033000000</v>
+        <v>171463000000</v>
       </c>
       <c r="J100" t="n">
-        <v>45394000000</v>
+        <v>434000000</v>
       </c>
       <c r="K100" t="n">
-        <v>31261000000</v>
+        <v>1543000000</v>
       </c>
       <c r="L100" t="n">
-        <v>343489000000</v>
+        <v>40013000000</v>
       </c>
       <c r="M100" t="n">
-        <v>110688000000</v>
+        <v>173440000000</v>
       </c>
       <c r="N100" t="n">
-        <v>618342113697</v>
+        <v>590877014157</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>コムシスホールディングス株式会社</t>
+          <t>サッポロホールディングス株式会社</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>17.9</v>
+        <v>1</v>
       </c>
       <c r="D101" t="n">
-        <v>5387</v>
+        <v>1866</v>
       </c>
       <c r="E101" t="n">
-        <v>3735.709461270437</v>
+        <v>2697.360927565142</v>
       </c>
       <c r="F101" t="n">
-        <v>44.2</v>
+        <v>-30.8</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>34033000000</v>
+        <v>2925000000</v>
       </c>
       <c r="J101" t="n">
-        <v>45394000000</v>
+        <v>23000000</v>
       </c>
       <c r="K101" t="n">
-        <v>31261000000</v>
+        <v>4391000000</v>
       </c>
       <c r="L101" t="n">
-        <v>343489000000</v>
+        <v>142395000000</v>
       </c>
       <c r="M101" t="n">
-        <v>110688000000</v>
+        <v>7339000000</v>
       </c>
       <c r="N101" t="n">
-        <v>618342113697</v>
+        <v>727689599340</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>サクサ株式会社</t>
+          <t>株式会社クレハ</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>6675</t>
+          <t>4023</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>29.7</v>
+        <v>17.6</v>
       </c>
       <c r="D102" t="n">
-        <v>2165</v>
+        <v>4440</v>
       </c>
       <c r="E102" t="n">
-        <v>5463.67048346056</v>
+        <v>7960</v>
       </c>
       <c r="F102" t="n">
-        <v>-60.4</v>
+        <v>-44.2</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>6993000000</v>
+        <v>5294000000</v>
       </c>
       <c r="J102" t="n">
-        <v>1323000000</v>
+        <v>5963000000</v>
       </c>
       <c r="K102" t="n">
-        <v>2933000000</v>
+        <v>18608000000</v>
       </c>
       <c r="L102" t="n">
-        <v>23497000000</v>
+        <v>155874000000</v>
       </c>
       <c r="M102" t="n">
-        <v>11249000000</v>
+        <v>29865000000</v>
       </c>
       <c r="N102" t="n">
-        <v>37869292350</v>
+        <v>169701479760</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>愛知製鋼株式会社</t>
+          <t>コムシスホールディングス株式会社</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>34.8</v>
+        <v>17.6</v>
       </c>
       <c r="D103" t="n">
-        <v>3150</v>
+        <v>5493</v>
       </c>
       <c r="E103" t="n">
-        <v>3155.301177013616</v>
+        <v>3953.24613842911</v>
       </c>
       <c r="F103" t="n">
-        <v>-0.2</v>
+        <v>38.9</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>32866000000</v>
+        <v>34033000000</v>
       </c>
       <c r="J103" t="n">
-        <v>11000000000</v>
+        <v>45394000000</v>
       </c>
       <c r="K103" t="n">
-        <v>26614000000</v>
+        <v>31261000000</v>
       </c>
       <c r="L103" t="n">
-        <v>186904000000</v>
+        <v>343489000000</v>
       </c>
       <c r="M103" t="n">
-        <v>70480000000</v>
+        <v>110688000000</v>
       </c>
       <c r="N103" t="n">
-        <v>202377413700</v>
+        <v>628691158443</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>株式会社インターネットイニシアティブ</t>
+          <t>コムシスホールディングス株式会社</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>3774</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>5.5</v>
+        <v>17.6</v>
       </c>
       <c r="D104" t="n">
-        <v>3399</v>
+        <v>5493</v>
       </c>
       <c r="E104" t="n">
-        <v>2655.311711736394</v>
+        <v>3735.709461270437</v>
       </c>
       <c r="F104" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -5810,102 +5810,102 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>16367000000</v>
+        <v>34033000000</v>
       </c>
       <c r="J104" t="n">
-        <v>1522000000</v>
+        <v>45394000000</v>
       </c>
       <c r="K104" t="n">
-        <v>15226000000</v>
+        <v>31261000000</v>
       </c>
       <c r="L104" t="n">
-        <v>87924000000</v>
+        <v>343489000000</v>
       </c>
       <c r="M104" t="n">
-        <v>33115000000</v>
+        <v>110688000000</v>
       </c>
       <c r="N104" t="n">
-        <v>602744686995</v>
+        <v>628691158443</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>コクヨ株式会社</t>
+          <t>サクサ株式会社</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>7984</t>
+          <t>6675</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>41</v>
+        <v>29.4</v>
       </c>
       <c r="D105" t="n">
-        <v>899.5999755859375</v>
+        <v>2184</v>
       </c>
       <c r="E105" t="n">
-        <v>2157.626835069302</v>
+        <v>5463.67048346056</v>
       </c>
       <c r="F105" t="n">
-        <v>-58.3</v>
+        <v>-60</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>100575000000</v>
+        <v>6993000000</v>
       </c>
       <c r="J105" t="n">
-        <v>22282000000</v>
+        <v>1323000000</v>
       </c>
       <c r="K105" t="n">
-        <v>30106000000</v>
+        <v>2933000000</v>
       </c>
       <c r="L105" t="n">
-        <v>230105000000</v>
+        <v>23497000000</v>
       </c>
       <c r="M105" t="n">
-        <v>152963000000</v>
+        <v>11249000000</v>
       </c>
       <c r="N105" t="n">
-        <v>372830277753</v>
+        <v>38201632560</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>三菱製紙株式会社</t>
+          <t>愛知製鋼株式会社</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>95.90000000000001</v>
+        <v>34.4</v>
       </c>
       <c r="D106" t="n">
-        <v>1197</v>
+        <v>3190</v>
       </c>
       <c r="E106" t="n">
-        <v>810</v>
+        <v>3155.301177013616</v>
       </c>
       <c r="F106" t="n">
-        <v>47.8</v>
+        <v>1.1</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -5914,50 +5914,50 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>9047000000</v>
+        <v>32866000000</v>
       </c>
       <c r="J106" t="n">
-        <v>16443000000</v>
+        <v>11000000000</v>
       </c>
       <c r="K106" t="n">
-        <v>24813000000</v>
+        <v>26614000000</v>
       </c>
       <c r="L106" t="n">
-        <v>69613000000</v>
+        <v>186904000000</v>
       </c>
       <c r="M106" t="n">
-        <v>50303000000</v>
+        <v>70480000000</v>
       </c>
       <c r="N106" t="n">
-        <v>52438390263</v>
+        <v>204947285620</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>株式会社プラスアルファ・コンサルティング</t>
+          <t>株式会社インターネットイニシアティブ</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>4071</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>9.699999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="D107" t="n">
-        <v>2092</v>
+        <v>3398</v>
       </c>
       <c r="E107" t="n">
-        <v>2300.974351689521</v>
+        <v>2655.311711736394</v>
       </c>
       <c r="F107" t="n">
-        <v>-9.1</v>
+        <v>28</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -5966,182 +5966,182 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>8278003000</v>
+        <v>16367000000</v>
       </c>
       <c r="J107" t="n">
-        <v>271170000</v>
+        <v>1522000000</v>
       </c>
       <c r="K107" t="n">
-        <v>0</v>
+        <v>15226000000</v>
       </c>
       <c r="L107" t="n">
-        <v>9445733000</v>
+        <v>87924000000</v>
       </c>
       <c r="M107" t="n">
-        <v>8549173000</v>
+        <v>33115000000</v>
       </c>
       <c r="N107" t="n">
-        <v>87771010600</v>
+        <v>602567356990</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>東亜道路工業株式会社</t>
+          <t>コクヨ株式会社</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>7984</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>40</v>
+        <v>41.1</v>
       </c>
       <c r="D108" t="n">
-        <v>1598</v>
+        <v>897.7999877929688</v>
       </c>
       <c r="E108" t="n">
-        <v>1180.253227905114</v>
+        <v>2157.626835069302</v>
       </c>
       <c r="F108" t="n">
-        <v>35.4</v>
+        <v>-58.4</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>11649000000</v>
+        <v>100575000000</v>
       </c>
       <c r="J108" t="n">
-        <v>13793000000</v>
+        <v>22282000000</v>
       </c>
       <c r="K108" t="n">
-        <v>4087000000</v>
+        <v>30106000000</v>
       </c>
       <c r="L108" t="n">
-        <v>50605000000</v>
+        <v>230105000000</v>
       </c>
       <c r="M108" t="n">
-        <v>29529000000</v>
+        <v>152963000000</v>
       </c>
       <c r="N108" t="n">
-        <v>73839725624</v>
+        <v>372084290685</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>東亜道路工業株式会社</t>
+          <t>三菱製紙株式会社</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>3864</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>40</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="D109" t="n">
-        <v>1598</v>
+        <v>1210</v>
       </c>
       <c r="E109" t="n">
-        <v>1180.31326635551</v>
+        <v>810</v>
       </c>
       <c r="F109" t="n">
-        <v>35.4</v>
+        <v>49.4</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>11649000000</v>
+        <v>9047000000</v>
       </c>
       <c r="J109" t="n">
-        <v>13793000000</v>
+        <v>16443000000</v>
       </c>
       <c r="K109" t="n">
-        <v>4087000000</v>
+        <v>24813000000</v>
       </c>
       <c r="L109" t="n">
-        <v>50605000000</v>
+        <v>69613000000</v>
       </c>
       <c r="M109" t="n">
-        <v>29529000000</v>
+        <v>50303000000</v>
       </c>
       <c r="N109" t="n">
-        <v>73839725624</v>
+        <v>53007896590</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>東亜道路工業株式会社</t>
+          <t>株式会社プラスアルファ・コンサルティング</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>4071</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>40</v>
+        <v>9.9</v>
       </c>
       <c r="D110" t="n">
-        <v>1598</v>
+        <v>2066</v>
       </c>
       <c r="E110" t="n">
-        <v>1180.406015389293</v>
+        <v>2300.974351689521</v>
       </c>
       <c r="F110" t="n">
-        <v>35.4</v>
+        <v>-10.2</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>11649000000</v>
+        <v>8278003000</v>
       </c>
       <c r="J110" t="n">
-        <v>13793000000</v>
+        <v>271170000</v>
       </c>
       <c r="K110" t="n">
-        <v>4087000000</v>
+        <v>0</v>
       </c>
       <c r="L110" t="n">
-        <v>50605000000</v>
+        <v>9445733000</v>
       </c>
       <c r="M110" t="n">
-        <v>29529000000</v>
+        <v>8549173000</v>
       </c>
       <c r="N110" t="n">
-        <v>73839725624</v>
+        <v>86680166300</v>
       </c>
     </row>
     <row r="111">
@@ -6156,16 +6156,16 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
       <c r="D111" t="n">
-        <v>1598</v>
+        <v>1602</v>
       </c>
       <c r="E111" t="n">
-        <v>1180.420176850555</v>
+        <v>1180.253227905114</v>
       </c>
       <c r="F111" t="n">
-        <v>35.4</v>
+        <v>35.7</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="I111" t="n">
@@ -6193,7 +6193,7 @@
         <v>29529000000</v>
       </c>
       <c r="N111" t="n">
-        <v>73839725624</v>
+        <v>74030483376</v>
       </c>
     </row>
     <row r="112">
@@ -6208,16 +6208,16 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
       <c r="D112" t="n">
-        <v>1598</v>
+        <v>1602</v>
       </c>
       <c r="E112" t="n">
-        <v>1180.431728045326</v>
+        <v>1180.31326635551</v>
       </c>
       <c r="F112" t="n">
-        <v>35.4</v>
+        <v>35.7</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="I112" t="n">
@@ -6245,7 +6245,7 @@
         <v>29529000000</v>
       </c>
       <c r="N112" t="n">
-        <v>73839725624</v>
+        <v>74030483376</v>
       </c>
     </row>
     <row r="113">
@@ -6260,16 +6260,16 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
       <c r="D113" t="n">
-        <v>1598</v>
+        <v>1602</v>
       </c>
       <c r="E113" t="n">
-        <v>1180.442269658324</v>
+        <v>1180.406015389293</v>
       </c>
       <c r="F113" t="n">
-        <v>35.4</v>
+        <v>35.7</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="I113" t="n">
@@ -6297,7 +6297,7 @@
         <v>29529000000</v>
       </c>
       <c r="N113" t="n">
-        <v>73839725624</v>
+        <v>74030483376</v>
       </c>
     </row>
     <row r="114">
@@ -6312,16 +6312,16 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
       <c r="D114" t="n">
-        <v>1598</v>
+        <v>1602</v>
       </c>
       <c r="E114" t="n">
-        <v>1180.450912709519</v>
+        <v>1180.420176850555</v>
       </c>
       <c r="F114" t="n">
-        <v>35.4</v>
+        <v>35.7</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="I114" t="n">
@@ -6349,7 +6349,7 @@
         <v>29529000000</v>
       </c>
       <c r="N114" t="n">
-        <v>73839725624</v>
+        <v>74030483376</v>
       </c>
     </row>
     <row r="115">
@@ -6364,16 +6364,16 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
       <c r="D115" t="n">
-        <v>1598</v>
+        <v>1602</v>
       </c>
       <c r="E115" t="n">
-        <v>1180.45745232471</v>
+        <v>1180.431728045326</v>
       </c>
       <c r="F115" t="n">
-        <v>35.4</v>
+        <v>35.7</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="I115" t="n">
@@ -6401,7 +6401,7 @@
         <v>29529000000</v>
       </c>
       <c r="N115" t="n">
-        <v>73839725624</v>
+        <v>74030483376</v>
       </c>
     </row>
     <row r="116">
@@ -6416,16 +6416,16 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
       <c r="D116" t="n">
-        <v>1598</v>
+        <v>1602</v>
       </c>
       <c r="E116" t="n">
-        <v>1180.463123164206</v>
+        <v>1180.442269658324</v>
       </c>
       <c r="F116" t="n">
-        <v>35.4</v>
+        <v>35.7</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="I116" t="n">
@@ -6453,7 +6453,7 @@
         <v>29529000000</v>
       </c>
       <c r="N116" t="n">
-        <v>73839725624</v>
+        <v>74030483376</v>
       </c>
     </row>
     <row r="117">
@@ -6468,16 +6468,16 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
       <c r="D117" t="n">
-        <v>1598</v>
+        <v>1602</v>
       </c>
       <c r="E117" t="n">
-        <v>1170.279952698077</v>
+        <v>1180.450912709519</v>
       </c>
       <c r="F117" t="n">
-        <v>36.5</v>
+        <v>35.7</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="I117" t="n">
@@ -6505,7 +6505,7 @@
         <v>29529000000</v>
       </c>
       <c r="N117" t="n">
-        <v>73839725624</v>
+        <v>74030483376</v>
       </c>
     </row>
     <row r="118">
@@ -6520,16 +6520,16 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
       <c r="D118" t="n">
-        <v>1598</v>
+        <v>1602</v>
       </c>
       <c r="E118" t="n">
-        <v>1169.924818603025</v>
+        <v>1180.45745232471</v>
       </c>
       <c r="F118" t="n">
-        <v>36.6</v>
+        <v>35.7</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="I118" t="n">
@@ -6557,7 +6557,7 @@
         <v>29529000000</v>
       </c>
       <c r="N118" t="n">
-        <v>73839725624</v>
+        <v>74030483376</v>
       </c>
     </row>
     <row r="119">
@@ -6572,16 +6572,16 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
       <c r="D119" t="n">
-        <v>1598</v>
+        <v>1602</v>
       </c>
       <c r="E119" t="n">
-        <v>1168.709522546084</v>
+        <v>1180.463123164206</v>
       </c>
       <c r="F119" t="n">
-        <v>36.7</v>
+        <v>35.7</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="I119" t="n">
@@ -6609,31 +6609,31 @@
         <v>29529000000</v>
       </c>
       <c r="N119" t="n">
-        <v>73839725624</v>
+        <v>74030483376</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>山洋電気株式会社</t>
+          <t>東亜道路工業株式会社</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>12</v>
+        <v>39.9</v>
       </c>
       <c r="D120" t="n">
-        <v>5160</v>
+        <v>1602</v>
       </c>
       <c r="E120" t="n">
-        <v>7052.737306843267</v>
+        <v>1170.279952698077</v>
       </c>
       <c r="F120" t="n">
-        <v>-26.8</v>
+        <v>36.9</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -6642,206 +6642,206 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>8317000000</v>
+        <v>11649000000</v>
       </c>
       <c r="J120" t="n">
-        <v>6048000000</v>
+        <v>13793000000</v>
       </c>
       <c r="K120" t="n">
-        <v>7673000000</v>
+        <v>4087000000</v>
       </c>
       <c r="L120" t="n">
-        <v>49734000000</v>
+        <v>50605000000</v>
       </c>
       <c r="M120" t="n">
-        <v>22038000000</v>
+        <v>29529000000</v>
       </c>
       <c r="N120" t="n">
-        <v>183257611560</v>
+        <v>74030483376</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ヘリオス テクノ ホールディング株式会社</t>
+          <t>東亜道路工業株式会社</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>54.1</v>
+        <v>39.9</v>
       </c>
       <c r="D121" t="n">
-        <v>974</v>
+        <v>1602</v>
       </c>
       <c r="E121" t="n">
-        <v>896.0103264198827</v>
+        <v>1169.924818603025</v>
       </c>
       <c r="F121" t="n">
-        <v>8.699999999999999</v>
+        <v>36.9</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>7851015000</v>
+        <v>11649000000</v>
       </c>
       <c r="J121" t="n">
-        <v>640317000</v>
+        <v>13793000000</v>
       </c>
       <c r="K121" t="n">
-        <v>1079200000</v>
+        <v>4087000000</v>
       </c>
       <c r="L121" t="n">
-        <v>13746774000</v>
+        <v>50605000000</v>
       </c>
       <c r="M121" t="n">
-        <v>9570532000</v>
+        <v>29529000000</v>
       </c>
       <c r="N121" t="n">
-        <v>17679723658</v>
+        <v>74030483376</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>シェアリングテクノロジー株式会社</t>
+          <t>東亜道路工業株式会社</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>11.7</v>
+        <v>39.9</v>
       </c>
       <c r="D122" t="n">
-        <v>1545</v>
+        <v>1602</v>
       </c>
       <c r="E122" t="n">
-        <v>653.0713101160862</v>
+        <v>1168.709522546084</v>
       </c>
       <c r="F122" t="n">
-        <v>136.6</v>
+        <v>37.1</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>4016706000</v>
+        <v>11649000000</v>
       </c>
       <c r="J122" t="n">
-        <v>309745000</v>
+        <v>13793000000</v>
       </c>
       <c r="K122" t="n">
-        <v>0</v>
+        <v>4087000000</v>
       </c>
       <c r="L122" t="n">
-        <v>185001000</v>
+        <v>50605000000</v>
       </c>
       <c r="M122" t="n">
-        <v>4326451000</v>
+        <v>29529000000</v>
       </c>
       <c r="N122" t="n">
-        <v>36973810605</v>
+        <v>74030483376</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>栄研化学株式会社</t>
+          <t>山洋電気株式会社</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>30.7</v>
+        <v>11.8</v>
       </c>
       <c r="D123" t="n">
-        <v>2260</v>
+        <v>5240</v>
       </c>
       <c r="E123" t="n">
-        <v>1947.225264702313</v>
+        <v>7052.737306843267</v>
       </c>
       <c r="F123" t="n">
-        <v>16.1</v>
+        <v>-25.7</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>10900000000</v>
+        <v>8317000000</v>
       </c>
       <c r="J123" t="n">
-        <v>11585000000</v>
+        <v>6048000000</v>
       </c>
       <c r="K123" t="n">
-        <v>408000000</v>
+        <v>7673000000</v>
       </c>
       <c r="L123" t="n">
-        <v>45803000000</v>
+        <v>49734000000</v>
       </c>
       <c r="M123" t="n">
-        <v>22893000000</v>
+        <v>22038000000</v>
       </c>
       <c r="N123" t="n">
-        <v>74502194980</v>
+        <v>186098814840</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>栄研化学株式会社</t>
+          <t>ヘリオス テクノ ホールディング株式会社</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>30.7</v>
+        <v>54.3</v>
       </c>
       <c r="D124" t="n">
-        <v>2260</v>
+        <v>971</v>
       </c>
       <c r="E124" t="n">
-        <v>1678.083113259255</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="F124" t="n">
-        <v>34.7</v>
+        <v>8.4</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -6850,518 +6850,518 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>10900000000</v>
+        <v>7851015000</v>
       </c>
       <c r="J124" t="n">
-        <v>11585000000</v>
+        <v>640317000</v>
       </c>
       <c r="K124" t="n">
-        <v>408000000</v>
+        <v>1079200000</v>
       </c>
       <c r="L124" t="n">
-        <v>45803000000</v>
+        <v>13746774000</v>
       </c>
       <c r="M124" t="n">
-        <v>22893000000</v>
+        <v>9570532000</v>
       </c>
       <c r="N124" t="n">
-        <v>74502194980</v>
+        <v>17625268657</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>株式会社ヤマダホールディングス</t>
+          <t>シェアリングテクノロジー株式会社</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>9831</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>58.3</v>
+        <v>11.7</v>
       </c>
       <c r="D125" t="n">
-        <v>715</v>
+        <v>1545</v>
       </c>
       <c r="E125" t="n">
-        <v>530</v>
+        <v>653.0713101160862</v>
       </c>
       <c r="F125" t="n">
-        <v>34.9</v>
+        <v>136.6</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>56470000000</v>
+        <v>4016706000</v>
       </c>
       <c r="J125" t="n">
-        <v>210733000000</v>
+        <v>309745000</v>
       </c>
       <c r="K125" t="n">
-        <v>9997000000</v>
+        <v>0</v>
       </c>
       <c r="L125" t="n">
-        <v>676277000000</v>
+        <v>185001000</v>
       </c>
       <c r="M125" t="n">
-        <v>277200000000</v>
+        <v>4326451000</v>
       </c>
       <c r="N125" t="n">
-        <v>475457434595</v>
+        <v>36973810605</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>日本化薬株式会社</t>
+          <t>栄研化学株式会社</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>35.6</v>
+        <v>30.5</v>
       </c>
       <c r="D126" t="n">
-        <v>2053.5</v>
+        <v>2280</v>
       </c>
       <c r="E126" t="n">
-        <v>1111.90611839092</v>
+        <v>1947.225264702313</v>
       </c>
       <c r="F126" t="n">
-        <v>84.7</v>
+        <v>17.1</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>52962000000</v>
+        <v>10900000000</v>
       </c>
       <c r="J126" t="n">
-        <v>48231000000</v>
+        <v>11585000000</v>
       </c>
       <c r="K126" t="n">
-        <v>4337000000</v>
+        <v>408000000</v>
       </c>
       <c r="L126" t="n">
-        <v>246425000000</v>
+        <v>45803000000</v>
       </c>
       <c r="M126" t="n">
-        <v>105530000000</v>
+        <v>22893000000</v>
       </c>
       <c r="N126" t="n">
-        <v>296090856812</v>
+        <v>75161506440</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>王子ホールディングス株式会社</t>
+          <t>栄研化学株式会社</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>41.6</v>
+        <v>30.5</v>
       </c>
       <c r="D127" t="n">
-        <v>869.7999877929688</v>
+        <v>2280</v>
       </c>
       <c r="E127" t="n">
-        <v>590</v>
+        <v>1678.083113259255</v>
       </c>
       <c r="F127" t="n">
-        <v>47.4</v>
+        <v>35.9</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>55474000000</v>
+        <v>10900000000</v>
       </c>
       <c r="J127" t="n">
-        <v>244732000000</v>
+        <v>11585000000</v>
       </c>
       <c r="K127" t="n">
-        <v>7434000000</v>
+        <v>408000000</v>
       </c>
       <c r="L127" t="n">
-        <v>875470000000</v>
+        <v>45803000000</v>
       </c>
       <c r="M127" t="n">
-        <v>307640000000</v>
+        <v>22893000000</v>
       </c>
       <c r="N127" t="n">
-        <v>738663977685</v>
+        <v>75161506440</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>東邦ホールディングス株式会社</t>
+          <t>株式会社ヤマダホールディングス</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>9831</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>50.6</v>
+        <v>58</v>
       </c>
       <c r="D128" t="n">
-        <v>4005</v>
+        <v>718.4000244140625</v>
       </c>
       <c r="E128" t="n">
-        <v>3405.914389596362</v>
+        <v>530</v>
       </c>
       <c r="F128" t="n">
-        <v>17.6</v>
+        <v>35.5</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>90014000000</v>
+        <v>56470000000</v>
       </c>
       <c r="J128" t="n">
-        <v>34220000000</v>
+        <v>210733000000</v>
       </c>
       <c r="K128" t="n">
-        <v>7000000000</v>
+        <v>9997000000</v>
       </c>
       <c r="L128" t="n">
-        <v>241281000000</v>
+        <v>676277000000</v>
       </c>
       <c r="M128" t="n">
-        <v>131234000000</v>
+        <v>277200000000</v>
       </c>
       <c r="N128" t="n">
-        <v>259130000115</v>
+        <v>477718367302</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>東邦ホールディングス株式会社</t>
+          <t>日本化薬株式会社</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>50.6</v>
+        <v>34.9</v>
       </c>
       <c r="D129" t="n">
-        <v>4005</v>
+        <v>2098.5</v>
       </c>
       <c r="E129" t="n">
-        <v>2714.613787300615</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="F129" t="n">
-        <v>47.5</v>
+        <v>88.7</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>90014000000</v>
+        <v>52962000000</v>
       </c>
       <c r="J129" t="n">
-        <v>34220000000</v>
+        <v>48231000000</v>
       </c>
       <c r="K129" t="n">
-        <v>7000000000</v>
+        <v>4337000000</v>
       </c>
       <c r="L129" t="n">
-        <v>241281000000</v>
+        <v>246425000000</v>
       </c>
       <c r="M129" t="n">
-        <v>131234000000</v>
+        <v>105530000000</v>
       </c>
       <c r="N129" t="n">
-        <v>259130000115</v>
+        <v>302579334316</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>株式会社アイネス</t>
+          <t>王子ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>9742</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>34.1</v>
+        <v>41.5</v>
       </c>
       <c r="D130" t="n">
-        <v>2126</v>
+        <v>872.5999755859375</v>
       </c>
       <c r="E130" t="n">
-        <v>1879.137815927515</v>
+        <v>590</v>
       </c>
       <c r="F130" t="n">
-        <v>13.1</v>
+        <v>47.9</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>9731000000</v>
+        <v>55474000000</v>
       </c>
       <c r="J130" t="n">
-        <v>5286000000</v>
+        <v>244732000000</v>
       </c>
       <c r="K130" t="n">
-        <v>100000000</v>
+        <v>7434000000</v>
       </c>
       <c r="L130" t="n">
-        <v>34620000000</v>
+        <v>875470000000</v>
       </c>
       <c r="M130" t="n">
-        <v>15117000000</v>
+        <v>307640000000</v>
       </c>
       <c r="N130" t="n">
-        <v>44268522322</v>
+        <v>741041823339</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>日本ゼオン株式会社</t>
+          <t>東邦ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>35.9</v>
+        <v>50.8</v>
       </c>
       <c r="D131" t="n">
-        <v>2345.5</v>
+        <v>3989</v>
       </c>
       <c r="E131" t="n">
-        <v>1721.078563209627</v>
+        <v>3405.914389596362</v>
       </c>
       <c r="F131" t="n">
-        <v>36.3</v>
+        <v>17.1</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>44521000000</v>
+        <v>90014000000</v>
       </c>
       <c r="J131" t="n">
-        <v>45382000000</v>
+        <v>34220000000</v>
       </c>
       <c r="K131" t="n">
-        <v>71191000000</v>
+        <v>7000000000</v>
       </c>
       <c r="L131" t="n">
-        <v>321836000000</v>
+        <v>241281000000</v>
       </c>
       <c r="M131" t="n">
-        <v>161094000000</v>
+        <v>131234000000</v>
       </c>
       <c r="N131" t="n">
-        <v>448800886668</v>
+        <v>258094774147</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>太陽ホールディングス株式会社</t>
+          <t>東邦ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>16.4</v>
+        <v>50.8</v>
       </c>
       <c r="D132" t="n">
-        <v>4728</v>
+        <v>3989</v>
       </c>
       <c r="E132" t="n">
-        <v>2199.643244598912</v>
+        <v>2714.613787300615</v>
       </c>
       <c r="F132" t="n">
-        <v>114.9</v>
+        <v>46.9</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>51152000000</v>
+        <v>90014000000</v>
       </c>
       <c r="J132" t="n">
-        <v>30337000000</v>
+        <v>34220000000</v>
       </c>
       <c r="K132" t="n">
-        <v>4870000000</v>
+        <v>7000000000</v>
       </c>
       <c r="L132" t="n">
-        <v>85466000000</v>
+        <v>241281000000</v>
       </c>
       <c r="M132" t="n">
-        <v>86359000000</v>
+        <v>131234000000</v>
       </c>
       <c r="N132" t="n">
-        <v>526116152496</v>
+        <v>258094774147</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>太陽ホールディングス株式会社</t>
+          <t>株式会社アイネス</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>9742</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>16.4</v>
+        <v>34.2</v>
       </c>
       <c r="D133" t="n">
-        <v>4728</v>
+        <v>2121</v>
       </c>
       <c r="E133" t="n">
-        <v>3565.648720929983</v>
+        <v>1879.137815927515</v>
       </c>
       <c r="F133" t="n">
-        <v>32.6</v>
+        <v>12.9</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>51152000000</v>
+        <v>9731000000</v>
       </c>
       <c r="J133" t="n">
-        <v>30337000000</v>
+        <v>5286000000</v>
       </c>
       <c r="K133" t="n">
-        <v>4870000000</v>
+        <v>100000000</v>
       </c>
       <c r="L133" t="n">
-        <v>85466000000</v>
+        <v>34620000000</v>
       </c>
       <c r="M133" t="n">
-        <v>86359000000</v>
+        <v>15117000000</v>
       </c>
       <c r="N133" t="n">
-        <v>526116152496</v>
+        <v>44164410087</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>株式会社エス・エム・エス</t>
+          <t>日本ゼオン株式会社</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>8.300000000000001</v>
+        <v>35.3</v>
       </c>
       <c r="D134" t="n">
-        <v>2666</v>
+        <v>2388</v>
       </c>
       <c r="E134" t="n">
-        <v>1478.127248828989</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="F134" t="n">
-        <v>80.40000000000001</v>
+        <v>38.8</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -7370,102 +7370,102 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>14126000000</v>
+        <v>44521000000</v>
       </c>
       <c r="J134" t="n">
-        <v>1187000000</v>
+        <v>45382000000</v>
       </c>
       <c r="K134" t="n">
-        <v>2875000000</v>
+        <v>71191000000</v>
       </c>
       <c r="L134" t="n">
-        <v>29991000000</v>
+        <v>321836000000</v>
       </c>
       <c r="M134" t="n">
-        <v>18188000000</v>
+        <v>161094000000</v>
       </c>
       <c r="N134" t="n">
-        <v>218826477034</v>
+        <v>456933070716</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>アニコム ホールディングス株式会社</t>
+          <t>太陽ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>8715</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>41.1</v>
+        <v>16.4</v>
       </c>
       <c r="D135" t="n">
-        <v>1029</v>
+        <v>4730</v>
       </c>
       <c r="E135" t="n">
-        <v>656.2604975855553</v>
+        <v>2199.643244598912</v>
       </c>
       <c r="F135" t="n">
-        <v>56.8</v>
+        <v>115</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>27691000000</v>
+        <v>51152000000</v>
       </c>
       <c r="J135" t="n">
-        <v>3070000000</v>
+        <v>30337000000</v>
       </c>
       <c r="K135" t="n">
-        <v>3000000</v>
+        <v>4870000000</v>
       </c>
       <c r="L135" t="n">
-        <v>27316000000</v>
+        <v>85466000000</v>
       </c>
       <c r="M135" t="n">
-        <v>30764000000</v>
+        <v>86359000000</v>
       </c>
       <c r="N135" t="n">
-        <v>74933035380</v>
+        <v>526338705860</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>東京製鐵株式会社</t>
+          <t>太陽ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>99.2</v>
+        <v>16.4</v>
       </c>
       <c r="D136" t="n">
-        <v>1753</v>
+        <v>4730</v>
       </c>
       <c r="E136" t="n">
-        <v>1605.452212379354</v>
+        <v>3565.648720929983</v>
       </c>
       <c r="F136" t="n">
-        <v>9.199999999999999</v>
+        <v>32.7</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -7474,199 +7474,201 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>68644000000</v>
+        <v>51152000000</v>
       </c>
       <c r="J136" t="n">
-        <v>33060000000</v>
+        <v>30337000000</v>
       </c>
       <c r="K136" t="n">
-        <v>75000000000</v>
+        <v>4870000000</v>
       </c>
       <c r="L136" t="n">
-        <v>158280000000</v>
+        <v>85466000000</v>
       </c>
       <c r="M136" t="n">
-        <v>176704000000</v>
+        <v>86359000000</v>
       </c>
       <c r="N136" t="n">
-        <v>178098035173</v>
+        <v>526338705860</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ウェーブロックホールディングス株式会社</t>
+          <t>株式会社エス・エム・エス</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>7940</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr"/>
-      <c r="D137" t="inlineStr"/>
+          <t>2175</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="D137" t="n">
+        <v>2652</v>
+      </c>
       <c r="E137" t="n">
-        <v>1010</v>
-      </c>
-      <c r="F137" t="inlineStr"/>
+        <v>1478.127248828989</v>
+      </c>
+      <c r="F137" t="n">
+        <v>79.40000000000001</v>
+      </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1961626000</v>
+        <v>14126000000</v>
       </c>
       <c r="J137" t="n">
-        <v>2544946000</v>
+        <v>1187000000</v>
       </c>
       <c r="K137" t="n">
-        <v>1068366000</v>
+        <v>2875000000</v>
       </c>
       <c r="L137" t="n">
-        <v>13761535000</v>
+        <v>29991000000</v>
       </c>
       <c r="M137" t="n">
-        <v>5574938000</v>
-      </c>
-      <c r="N137" t="inlineStr"/>
+        <v>18188000000</v>
+      </c>
+      <c r="N137" t="n">
+        <v>217677350748</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>近畿車輛株式会社</t>
+          <t>アニコム ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>7122</t>
+          <t>8715</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>107.4</v>
+        <v>41</v>
       </c>
       <c r="D138" t="n">
-        <v>2403</v>
+        <v>1030</v>
       </c>
       <c r="E138" t="n">
-        <v>2144.894901144641</v>
+        <v>656.2604975855553</v>
       </c>
       <c r="F138" t="n">
-        <v>12</v>
+        <v>56.9</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>6847000000</v>
+        <v>27691000000</v>
       </c>
       <c r="J138" t="n">
-        <v>4580000000</v>
+        <v>3070000000</v>
       </c>
       <c r="K138" t="n">
-        <v>6329000000</v>
+        <v>3000000</v>
       </c>
       <c r="L138" t="n">
-        <v>24474000000</v>
+        <v>27316000000</v>
       </c>
       <c r="M138" t="n">
-        <v>17756000000</v>
+        <v>30764000000</v>
       </c>
       <c r="N138" t="n">
-        <v>16532834643</v>
+        <v>75005856600</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>株式会社三陽商会</t>
+          <t>東京製鐵株式会社</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>5423</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>63.8</v>
+        <v>98.5</v>
       </c>
       <c r="D139" t="n">
-        <v>1365</v>
+        <v>1766</v>
       </c>
       <c r="E139" t="n">
-        <v>3321.975331035734</v>
+        <v>1605.452212379354</v>
       </c>
       <c r="F139" t="n">
-        <v>-58.9</v>
+        <v>10</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>16287000000</v>
+        <v>68644000000</v>
       </c>
       <c r="J139" t="n">
-        <v>3021000000</v>
+        <v>33060000000</v>
       </c>
       <c r="K139" t="n">
-        <v>6298000000</v>
+        <v>75000000000</v>
       </c>
       <c r="L139" t="n">
-        <v>33920000000</v>
+        <v>158280000000</v>
       </c>
       <c r="M139" t="n">
-        <v>25606000000</v>
+        <v>176704000000</v>
       </c>
       <c r="N139" t="n">
-        <v>40111933680</v>
+        <v>179418785006</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>月島ホールディングス株式会社</t>
+          <t>ウェーブロックホールディングス株式会社</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>6332</t>
-        </is>
-      </c>
-      <c r="C140" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="D140" t="n">
-        <v>2652</v>
-      </c>
+          <t>7940</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr"/>
       <c r="E140" t="n">
-        <v>1410</v>
-      </c>
-      <c r="F140" t="n">
-        <v>88.09999999999999</v>
-      </c>
+        <v>1010</v>
+      </c>
+      <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
           <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
@@ -7674,50 +7676,48 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>28795000000</v>
+        <v>1961626000</v>
       </c>
       <c r="J140" t="n">
-        <v>22203000000</v>
+        <v>2544946000</v>
       </c>
       <c r="K140" t="n">
-        <v>100000000</v>
+        <v>1068366000</v>
       </c>
       <c r="L140" t="n">
-        <v>80949000000</v>
+        <v>13761535000</v>
       </c>
       <c r="M140" t="n">
-        <v>51098000000</v>
-      </c>
-      <c r="N140" t="n">
-        <v>105022443396</v>
-      </c>
+        <v>5574938000</v>
+      </c>
+      <c r="N140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>マネックスグループ株式会社</t>
+          <t>近畿車輛株式会社</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>8698</t>
+          <t>7122</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>15.1</v>
+        <v>107.8</v>
       </c>
       <c r="D141" t="n">
-        <v>723</v>
+        <v>2395</v>
       </c>
       <c r="E141" t="n">
-        <v>510.1850530906719</v>
+        <v>2144.894901144641</v>
       </c>
       <c r="F141" t="n">
-        <v>41.7</v>
+        <v>11.7</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -7726,102 +7726,102 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>17794000000</v>
+        <v>6847000000</v>
       </c>
       <c r="J141" t="n">
-        <v>412000000</v>
+        <v>4580000000</v>
       </c>
       <c r="K141" t="n">
-        <v>9312000000</v>
+        <v>6329000000</v>
       </c>
       <c r="L141" t="n">
-        <v>98001000000</v>
+        <v>24474000000</v>
       </c>
       <c r="M141" t="n">
-        <v>27518000000</v>
+        <v>17756000000</v>
       </c>
       <c r="N141" t="n">
-        <v>181735943532</v>
+        <v>16477793995</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>株式会社あおぞら銀行</t>
+          <t>株式会社三陽商会</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>8011</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>225</v>
+        <v>64.5</v>
       </c>
       <c r="D142" t="n">
-        <v>3482</v>
+        <v>1350</v>
       </c>
       <c r="E142" t="n">
-        <v>2190</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="F142" t="n">
-        <v>59</v>
+        <v>-59.4</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1061743000000</v>
+        <v>16287000000</v>
       </c>
       <c r="J142" t="n">
-        <v>22385000000</v>
+        <v>3021000000</v>
       </c>
       <c r="K142" t="n">
-        <v>0</v>
+        <v>6298000000</v>
       </c>
       <c r="L142" t="n">
-        <v>487265000000</v>
+        <v>33920000000</v>
       </c>
       <c r="M142" t="n">
-        <v>1084128000000</v>
+        <v>25606000000</v>
       </c>
       <c r="N142" t="n">
-        <v>481842906632</v>
+        <v>39671143200</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>日本製紙株式会社</t>
+          <t>月島ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>301.9</v>
+        <v>48.1</v>
       </c>
       <c r="D143" t="n">
-        <v>1324</v>
+        <v>2680</v>
       </c>
       <c r="E143" t="n">
-        <v>1250</v>
+        <v>1410</v>
       </c>
       <c r="F143" t="n">
-        <v>5.9</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -7830,50 +7830,50 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>136216000000</v>
+        <v>28795000000</v>
       </c>
       <c r="J143" t="n">
-        <v>151771000000</v>
+        <v>22203000000</v>
       </c>
       <c r="K143" t="n">
-        <v>172984000000</v>
+        <v>100000000</v>
       </c>
       <c r="L143" t="n">
-        <v>438604000000</v>
+        <v>80949000000</v>
       </c>
       <c r="M143" t="n">
-        <v>460971000000</v>
+        <v>51098000000</v>
       </c>
       <c r="N143" t="n">
-        <v>152668457972</v>
+        <v>106131277640</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>カルビー株式会社</t>
+          <t>マネックスグループ株式会社</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>8698</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>33.4</v>
+        <v>15.4</v>
       </c>
       <c r="D144" t="n">
-        <v>3030</v>
+        <v>713</v>
       </c>
       <c r="E144" t="n">
-        <v>2919.137515755844</v>
+        <v>510.1850530906719</v>
       </c>
       <c r="F144" t="n">
-        <v>3.8</v>
+        <v>39.8</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -7882,50 +7882,50 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>49670000000</v>
+        <v>17794000000</v>
       </c>
       <c r="J144" t="n">
-        <v>70285000000</v>
+        <v>412000000</v>
       </c>
       <c r="K144" t="n">
-        <v>3263000000</v>
+        <v>9312000000</v>
       </c>
       <c r="L144" t="n">
-        <v>183458000000</v>
+        <v>98001000000</v>
       </c>
       <c r="M144" t="n">
-        <v>123218000000</v>
+        <v>27518000000</v>
       </c>
       <c r="N144" t="n">
-        <v>368411197620</v>
+        <v>179222306692</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ＮＩＴＴＯＫＵ株式会社</t>
+          <t>株式会社あおぞら銀行</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>50.1</v>
+        <v>223.3</v>
       </c>
       <c r="D145" t="n">
-        <v>2493</v>
+        <v>3508</v>
       </c>
       <c r="E145" t="n">
-        <v>1710</v>
+        <v>2190</v>
       </c>
       <c r="F145" t="n">
-        <v>45.8</v>
+        <v>60.2</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -7934,50 +7934,50 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>11768000000</v>
+        <v>1061743000000</v>
       </c>
       <c r="J145" t="n">
-        <v>6299000000</v>
+        <v>22385000000</v>
       </c>
       <c r="K145" t="n">
-        <v>2999000000</v>
+        <v>0</v>
       </c>
       <c r="L145" t="n">
-        <v>33919000000</v>
+        <v>487265000000</v>
       </c>
       <c r="M145" t="n">
-        <v>21066000000</v>
+        <v>1084128000000</v>
       </c>
       <c r="N145" t="n">
-        <v>42068083626</v>
+        <v>485440982992</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ＮＩＴＴＯＫＵ株式会社</t>
+          <t>日本製紙株式会社</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>50.1</v>
+        <v>301.9</v>
       </c>
       <c r="D146" t="n">
-        <v>2493</v>
+        <v>1324</v>
       </c>
       <c r="E146" t="n">
-        <v>1710</v>
+        <v>1250</v>
       </c>
       <c r="F146" t="n">
-        <v>45.8</v>
+        <v>5.9</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -7986,102 +7986,102 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>11768000000</v>
+        <v>136216000000</v>
       </c>
       <c r="J146" t="n">
-        <v>6299000000</v>
+        <v>151771000000</v>
       </c>
       <c r="K146" t="n">
-        <v>2999000000</v>
+        <v>172984000000</v>
       </c>
       <c r="L146" t="n">
-        <v>33919000000</v>
+        <v>438604000000</v>
       </c>
       <c r="M146" t="n">
-        <v>21066000000</v>
+        <v>460971000000</v>
       </c>
       <c r="N146" t="n">
-        <v>42068083626</v>
+        <v>152668457972</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>新光商事株式会社</t>
+          <t>カルビー株式会社</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>8141</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>30.8</v>
+        <v>33.4</v>
       </c>
       <c r="D147" t="n">
-        <v>1565</v>
+        <v>3030</v>
       </c>
       <c r="E147" t="n">
-        <v>930</v>
+        <v>2919.137515755844</v>
       </c>
       <c r="F147" t="n">
-        <v>68.3</v>
+        <v>3.8</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>10579000000</v>
+        <v>49670000000</v>
       </c>
       <c r="J147" t="n">
-        <v>195000000</v>
+        <v>70285000000</v>
       </c>
       <c r="K147" t="n">
-        <v>2995000000</v>
+        <v>3263000000</v>
       </c>
       <c r="L147" t="n">
-        <v>51945000000</v>
+        <v>183458000000</v>
       </c>
       <c r="M147" t="n">
-        <v>13769000000</v>
+        <v>123218000000</v>
       </c>
       <c r="N147" t="n">
-        <v>44680591935</v>
+        <v>368411197620</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>株式会社メガチップス</t>
+          <t>ＮＩＴＴＯＫＵ株式会社</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>6875</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>89.8</v>
+        <v>48.7</v>
       </c>
       <c r="D148" t="n">
-        <v>10460</v>
+        <v>2563</v>
       </c>
       <c r="E148" t="n">
-        <v>4870</v>
+        <v>1710</v>
       </c>
       <c r="F148" t="n">
-        <v>114.8</v>
+        <v>49.9</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -8090,102 +8090,102 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>25769446000</v>
+        <v>11768000000</v>
       </c>
       <c r="J148" t="n">
-        <v>2249411000</v>
+        <v>6299000000</v>
       </c>
       <c r="K148" t="n">
-        <v>101636005000</v>
+        <v>2999000000</v>
       </c>
       <c r="L148" t="n">
-        <v>67428618000</v>
+        <v>33919000000</v>
       </c>
       <c r="M148" t="n">
-        <v>129654862000</v>
+        <v>21066000000</v>
       </c>
       <c r="N148" t="n">
-        <v>144357424460</v>
+        <v>43249297366</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>株式会社青山財産ネットワークス</t>
+          <t>ＮＩＴＴＯＫＵ株式会社</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>8929</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>42.8</v>
+        <v>48.7</v>
       </c>
       <c r="D149" t="n">
-        <v>1354</v>
+        <v>2563</v>
       </c>
       <c r="E149" t="n">
-        <v>1347.74653160027</v>
+        <v>1710</v>
       </c>
       <c r="F149" t="n">
-        <v>0.5</v>
+        <v>49.9</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>10862000000</v>
+        <v>11768000000</v>
       </c>
       <c r="J149" t="n">
-        <v>245000000</v>
+        <v>6299000000</v>
       </c>
       <c r="K149" t="n">
-        <v>2845000000</v>
+        <v>2999000000</v>
       </c>
       <c r="L149" t="n">
-        <v>7128000000</v>
+        <v>33919000000</v>
       </c>
       <c r="M149" t="n">
-        <v>13952000000</v>
+        <v>21066000000</v>
       </c>
       <c r="N149" t="n">
-        <v>32584332252</v>
+        <v>43249297366</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>平和不動産株式会社</t>
+          <t>新光商事株式会社</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>8803</t>
+          <t>8141</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>73.2</v>
+        <v>30.8</v>
       </c>
       <c r="D150" t="n">
-        <v>2344</v>
+        <v>1566</v>
       </c>
       <c r="E150" t="n">
-        <v>3610</v>
+        <v>930</v>
       </c>
       <c r="F150" t="n">
-        <v>-35.1</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -8194,206 +8194,206 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>28111000000</v>
+        <v>10579000000</v>
       </c>
       <c r="J150" t="n">
-        <v>79319000000</v>
+        <v>195000000</v>
       </c>
       <c r="K150" t="n">
-        <v>5997000000</v>
+        <v>2995000000</v>
       </c>
       <c r="L150" t="n">
-        <v>119278000000</v>
+        <v>51945000000</v>
       </c>
       <c r="M150" t="n">
-        <v>113427000000</v>
+        <v>13769000000</v>
       </c>
       <c r="N150" t="n">
-        <v>154868684752</v>
+        <v>44709141834</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>小林製薬株式会社</t>
+          <t>株式会社メガチップス</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>29.9</v>
+        <v>88.7</v>
       </c>
       <c r="D151" t="n">
-        <v>5814</v>
+        <v>10590</v>
       </c>
       <c r="E151" t="n">
-        <v>2148.936934940886</v>
+        <v>4870</v>
       </c>
       <c r="F151" t="n">
-        <v>170.6</v>
+        <v>117.5</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>81987000000</v>
+        <v>25769446000</v>
       </c>
       <c r="J151" t="n">
-        <v>32461000000</v>
+        <v>2249411000</v>
       </c>
       <c r="K151" t="n">
-        <v>14872000000</v>
+        <v>101636005000</v>
       </c>
       <c r="L151" t="n">
-        <v>195600000000</v>
+        <v>67428618000</v>
       </c>
       <c r="M151" t="n">
-        <v>129320000000</v>
+        <v>129654862000</v>
       </c>
       <c r="N151" t="n">
-        <v>432204742494</v>
+        <v>146151541590</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>小林製薬株式会社</t>
+          <t>株式会社青山財産ネットワークス</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>8929</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>29.9</v>
+        <v>42.8</v>
       </c>
       <c r="D152" t="n">
-        <v>5814</v>
+        <v>1356</v>
       </c>
       <c r="E152" t="n">
-        <v>5066.092575838703</v>
+        <v>1347.74653160027</v>
       </c>
       <c r="F152" t="n">
-        <v>14.8</v>
+        <v>0.6</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>81987000000</v>
+        <v>10862000000</v>
       </c>
       <c r="J152" t="n">
-        <v>32461000000</v>
+        <v>245000000</v>
       </c>
       <c r="K152" t="n">
-        <v>14872000000</v>
+        <v>2845000000</v>
       </c>
       <c r="L152" t="n">
-        <v>195600000000</v>
+        <v>7128000000</v>
       </c>
       <c r="M152" t="n">
-        <v>129320000000</v>
+        <v>13952000000</v>
       </c>
       <c r="N152" t="n">
-        <v>432204742494</v>
+        <v>32632462728</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>セーレン株式会社</t>
+          <t>平和不動産株式会社</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>3569</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>37.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D153" t="n">
-        <v>3230</v>
+        <v>2355</v>
       </c>
       <c r="E153" t="n">
-        <v>1359.655069733296</v>
+        <v>3610</v>
       </c>
       <c r="F153" t="n">
-        <v>137.6</v>
+        <v>-34.8</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>35451000000</v>
+        <v>28111000000</v>
       </c>
       <c r="J153" t="n">
-        <v>25813000000</v>
+        <v>79319000000</v>
       </c>
       <c r="K153" t="n">
-        <v>8891000000</v>
+        <v>5997000000</v>
       </c>
       <c r="L153" t="n">
-        <v>91845000000</v>
+        <v>119278000000</v>
       </c>
       <c r="M153" t="n">
-        <v>70155000000</v>
+        <v>113427000000</v>
       </c>
       <c r="N153" t="n">
-        <v>188500994430</v>
+        <v>155595457590</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>データセクション株式会社</t>
+          <t>小林製薬株式会社</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>2.6</v>
+        <v>30</v>
       </c>
       <c r="D154" t="n">
-        <v>1509</v>
+        <v>5797</v>
       </c>
       <c r="E154" t="n">
-        <v>5143.276404494382</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="F154" t="n">
-        <v>-70.7</v>
+        <v>169.8</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -8402,362 +8402,362 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1420430000</v>
+        <v>81987000000</v>
       </c>
       <c r="J154" t="n">
-        <v>1162000</v>
+        <v>32461000000</v>
       </c>
       <c r="K154" t="n">
-        <v>49326000</v>
+        <v>14872000000</v>
       </c>
       <c r="L154" t="n">
-        <v>2818110000</v>
+        <v>195600000000</v>
       </c>
       <c r="M154" t="n">
-        <v>1470918000</v>
+        <v>129320000000</v>
       </c>
       <c r="N154" t="n">
-        <v>56530619754</v>
+        <v>430940985937</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>愛眼株式会社</t>
+          <t>小林製薬株式会社</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>9854</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>70.40000000000001</v>
+        <v>30</v>
       </c>
       <c r="D155" t="n">
-        <v>282</v>
+        <v>5797</v>
       </c>
       <c r="E155" t="n">
-        <v>246.9708756284982</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="F155" t="n">
-        <v>14.2</v>
+        <v>14.4</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2219000000</v>
+        <v>81987000000</v>
       </c>
       <c r="J155" t="n">
-        <v>1030000000</v>
+        <v>32461000000</v>
       </c>
       <c r="K155" t="n">
-        <v>604000000</v>
+        <v>14872000000</v>
       </c>
       <c r="L155" t="n">
-        <v>12920000000</v>
+        <v>195600000000</v>
       </c>
       <c r="M155" t="n">
-        <v>3853000000</v>
+        <v>129320000000</v>
       </c>
       <c r="N155" t="n">
-        <v>5472693630</v>
+        <v>430940985937</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>株式会社アシロ</t>
+          <t>セーレン株式会社</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>3569</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>14.4</v>
+        <v>36.8</v>
       </c>
       <c r="D156" t="n">
-        <v>1507</v>
+        <v>3265</v>
       </c>
       <c r="E156" t="n">
-        <v>1396.628697042366</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="F156" t="n">
-        <v>7.9</v>
+        <v>140.1</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1428281000</v>
+        <v>35451000000</v>
       </c>
       <c r="J156" t="n">
-        <v>102238000</v>
+        <v>25813000000</v>
       </c>
       <c r="K156" t="n">
-        <v>0</v>
+        <v>8891000000</v>
       </c>
       <c r="L156" t="n">
-        <v>1804458000</v>
+        <v>91845000000</v>
       </c>
       <c r="M156" t="n">
-        <v>1530519000</v>
+        <v>70155000000</v>
       </c>
       <c r="N156" t="n">
-        <v>10596601609</v>
+        <v>190543574865</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>三浦工業株式会社</t>
+          <t>データセクション株式会社</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>11.8</v>
+        <v>2.7</v>
       </c>
       <c r="D157" t="n">
-        <v>3085</v>
+        <v>1446</v>
       </c>
       <c r="E157" t="n">
-        <v>3147.518794622453</v>
+        <v>5143.276404494382</v>
       </c>
       <c r="F157" t="n">
-        <v>-2</v>
+        <v>-71.90000000000001</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="I157" t="n">
-        <v>20794000000</v>
+        <v>1420430000</v>
       </c>
       <c r="J157" t="n">
-        <v>10600000000</v>
+        <v>1162000</v>
       </c>
       <c r="K157" t="n">
-        <v>10773000000</v>
+        <v>49326000</v>
       </c>
       <c r="L157" t="n">
-        <v>138378000000</v>
+        <v>2818110000</v>
       </c>
       <c r="M157" t="n">
-        <v>42167000000</v>
+        <v>1470918000</v>
       </c>
       <c r="N157" t="n">
-        <v>357086775600</v>
+        <v>54170494476</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>株式会社カカクコム</t>
+          <t>愛眼株式会社</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>6.7</v>
+        <v>70.2</v>
       </c>
       <c r="D158" t="n">
-        <v>3839</v>
+        <v>283</v>
       </c>
       <c r="E158" t="n">
-        <v>2318.314890576102</v>
+        <v>246.9708756284982</v>
       </c>
       <c r="F158" t="n">
-        <v>65.59999999999999</v>
+        <v>14.6</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>46452000000</v>
+        <v>2219000000</v>
       </c>
       <c r="J158" t="n">
-        <v>68000000</v>
+        <v>1030000000</v>
       </c>
       <c r="K158" t="n">
-        <v>4669000000</v>
+        <v>604000000</v>
       </c>
       <c r="L158" t="n">
-        <v>45479000000</v>
+        <v>12920000000</v>
       </c>
       <c r="M158" t="n">
-        <v>51189000000</v>
+        <v>3853000000</v>
       </c>
       <c r="N158" t="n">
-        <v>759493429013</v>
+        <v>5492100345</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>古河機械金属株式会社</t>
+          <t>株式会社アシロ</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>7378</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>48.1</v>
+        <v>14.2</v>
       </c>
       <c r="D159" t="n">
-        <v>3955</v>
+        <v>1530</v>
       </c>
       <c r="E159" t="n">
-        <v>1600</v>
+        <v>1396.628697042366</v>
       </c>
       <c r="F159" t="n">
-        <v>147.2</v>
+        <v>9.5</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="I159" t="n">
-        <v>14468000000</v>
+        <v>1428281000</v>
       </c>
       <c r="J159" t="n">
-        <v>26121000000</v>
+        <v>102238000</v>
       </c>
       <c r="K159" t="n">
-        <v>19903000000</v>
+        <v>0</v>
       </c>
       <c r="L159" t="n">
-        <v>100075000000</v>
+        <v>1804458000</v>
       </c>
       <c r="M159" t="n">
-        <v>60492000000</v>
+        <v>1530519000</v>
       </c>
       <c r="N159" t="n">
-        <v>125650812735</v>
+        <v>10758328110</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>多木化学株式会社</t>
+          <t>三浦工業株式会社</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>4025</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>32.3</v>
+        <v>11.6</v>
       </c>
       <c r="D160" t="n">
-        <v>5420</v>
+        <v>3128</v>
       </c>
       <c r="E160" t="n">
-        <v>4695.956053243186</v>
+        <v>3147.518794622453</v>
       </c>
       <c r="F160" t="n">
-        <v>15.4</v>
+        <v>-0.6</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>6433000000</v>
+        <v>20794000000</v>
       </c>
       <c r="J160" t="n">
-        <v>7985000000</v>
+        <v>10600000000</v>
       </c>
       <c r="K160" t="n">
-        <v>199000000</v>
+        <v>10773000000</v>
       </c>
       <c r="L160" t="n">
-        <v>29378000000</v>
+        <v>138378000000</v>
       </c>
       <c r="M160" t="n">
-        <v>14617000000</v>
+        <v>42167000000</v>
       </c>
       <c r="N160" t="n">
-        <v>45242739980</v>
+        <v>362063998080</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>エムスリー株式会社</t>
+          <t>株式会社カカクコム</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2413</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="D161" t="n">
-        <v>1742.5</v>
+        <v>3820</v>
       </c>
       <c r="E161" t="n">
-        <v>1638.585693292194</v>
+        <v>2318.314890576102</v>
       </c>
       <c r="F161" t="n">
-        <v>6.3</v>
+        <v>64.8</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -8766,50 +8766,50 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="I161" t="n">
-        <v>78812000000</v>
+        <v>46452000000</v>
       </c>
       <c r="J161" t="n">
-        <v>345000000</v>
+        <v>68000000</v>
       </c>
       <c r="K161" t="n">
-        <v>9506000000</v>
+        <v>4669000000</v>
       </c>
       <c r="L161" t="n">
-        <v>152472000000</v>
+        <v>45479000000</v>
       </c>
       <c r="M161" t="n">
-        <v>88663000000</v>
+        <v>51189000000</v>
       </c>
       <c r="N161" t="n">
-        <v>1161056084792</v>
+        <v>755734539940</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>三井松島ホールディングス株式会社</t>
+          <t>古河機械金属株式会社</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>41.2</v>
+        <v>46.8</v>
       </c>
       <c r="D162" t="n">
-        <v>2223</v>
+        <v>4070</v>
       </c>
       <c r="E162" t="n">
-        <v>2920</v>
+        <v>1600</v>
       </c>
       <c r="F162" t="n">
-        <v>-23.9</v>
+        <v>154.4</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -8818,102 +8818,102 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="I162" t="n">
-        <v>19413000000</v>
+        <v>14468000000</v>
       </c>
       <c r="J162" t="n">
-        <v>3540000000</v>
+        <v>26121000000</v>
       </c>
       <c r="K162" t="n">
-        <v>10945000000</v>
+        <v>19903000000</v>
       </c>
       <c r="L162" t="n">
-        <v>35537000000</v>
+        <v>100075000000</v>
       </c>
       <c r="M162" t="n">
-        <v>33898000000</v>
+        <v>60492000000</v>
       </c>
       <c r="N162" t="n">
-        <v>82313155080</v>
+        <v>129304376190</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ノリタケ株式会社</t>
+          <t>多木化学株式会社</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>38.8</v>
+        <v>30.7</v>
       </c>
       <c r="D163" t="n">
-        <v>3505</v>
+        <v>5710</v>
       </c>
       <c r="E163" t="n">
-        <v>3573.410502159827</v>
+        <v>4695.956053243186</v>
       </c>
       <c r="F163" t="n">
-        <v>-1.9</v>
+        <v>21.6</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I163" t="n">
-        <v>11733000000</v>
+        <v>6433000000</v>
       </c>
       <c r="J163" t="n">
-        <v>20204000000</v>
+        <v>7985000000</v>
       </c>
       <c r="K163" t="n">
-        <v>42879000000</v>
+        <v>199000000</v>
       </c>
       <c r="L163" t="n">
-        <v>118800000000</v>
+        <v>29378000000</v>
       </c>
       <c r="M163" t="n">
-        <v>74816000000</v>
+        <v>14617000000</v>
       </c>
       <c r="N163" t="n">
-        <v>192825030370</v>
+        <v>47663476990</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>株式会社ＡＣＳＬ</t>
+          <t>エムスリー株式会社</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>8.699999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="D164" t="n">
-        <v>1229</v>
+        <v>1751</v>
       </c>
       <c r="E164" t="n">
-        <v>913.2768512341561</v>
+        <v>1638.585693292194</v>
       </c>
       <c r="F164" t="n">
-        <v>34.6</v>
+        <v>6.9</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -8922,130 +8922,286 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1891731000</v>
+        <v>78812000000</v>
       </c>
       <c r="J164" t="n">
-        <v>3724000</v>
+        <v>345000000</v>
       </c>
       <c r="K164" t="n">
-        <v>197577000</v>
+        <v>9506000000</v>
       </c>
       <c r="L164" t="n">
-        <v>3572642000</v>
+        <v>152472000000</v>
       </c>
       <c r="M164" t="n">
-        <v>2093032000</v>
+        <v>88663000000</v>
       </c>
       <c r="N164" t="n">
-        <v>24054285418</v>
+        <v>1166719773011</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>株式会社スズケン</t>
+          <t>三井松島ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>9987</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>78.40000000000001</v>
+        <v>40.2</v>
       </c>
       <c r="D165" t="n">
-        <v>5214</v>
+        <v>2275</v>
       </c>
       <c r="E165" t="n">
-        <v>4137.137750115735</v>
+        <v>2920</v>
       </c>
       <c r="F165" t="n">
-        <v>26</v>
+        <v>-22.1</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="I165" t="n">
-        <v>168215000000</v>
+        <v>19413000000</v>
       </c>
       <c r="J165" t="n">
-        <v>65453000000</v>
+        <v>3540000000</v>
       </c>
       <c r="K165" t="n">
-        <v>38927000000</v>
+        <v>10945000000</v>
       </c>
       <c r="L165" t="n">
-        <v>418062000000</v>
+        <v>35537000000</v>
       </c>
       <c r="M165" t="n">
-        <v>272595000000</v>
+        <v>33898000000</v>
       </c>
       <c r="N165" t="n">
-        <v>347691361446</v>
+        <v>84238609000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
+          <t>ノリタケ株式会社</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>5331</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="D166" t="n">
+        <v>3590</v>
+      </c>
+      <c r="E166" t="n">
+        <v>3573.410502159827</v>
+      </c>
+      <c r="F166" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>株式会社ストラテジックキャピタル</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="I166" t="n">
+        <v>11733000000</v>
+      </c>
+      <c r="J166" t="n">
+        <v>20204000000</v>
+      </c>
+      <c r="K166" t="n">
+        <v>42879000000</v>
+      </c>
+      <c r="L166" t="n">
+        <v>118800000000</v>
+      </c>
+      <c r="M166" t="n">
+        <v>74816000000</v>
+      </c>
+      <c r="N166" t="n">
+        <v>197501243660</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>株式会社ＡＣＳＬ</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>6232</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="D167" t="n">
+        <v>1224</v>
+      </c>
+      <c r="E167" t="n">
+        <v>913.2768512341561</v>
+      </c>
+      <c r="F167" t="n">
+        <v>34</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="I167" t="n">
+        <v>1891731000</v>
+      </c>
+      <c r="J167" t="n">
+        <v>3724000</v>
+      </c>
+      <c r="K167" t="n">
+        <v>197577000</v>
+      </c>
+      <c r="L167" t="n">
+        <v>3572642000</v>
+      </c>
+      <c r="M167" t="n">
+        <v>2093032000</v>
+      </c>
+      <c r="N167" t="n">
+        <v>23956424208</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>株式会社スズケン</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="D168" t="n">
+        <v>5223</v>
+      </c>
+      <c r="E168" t="n">
+        <v>4137.137750115735</v>
+      </c>
+      <c r="F168" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
+        <v>168215000000</v>
+      </c>
+      <c r="J168" t="n">
+        <v>65453000000</v>
+      </c>
+      <c r="K168" t="n">
+        <v>38927000000</v>
+      </c>
+      <c r="L168" t="n">
+        <v>418062000000</v>
+      </c>
+      <c r="M168" t="n">
+        <v>272595000000</v>
+      </c>
+      <c r="N168" t="n">
+        <v>348291519147</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
           <t>フォスター電機株式会社</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
+      <c r="B169" t="inlineStr">
         <is>
           <t>6794</t>
         </is>
       </c>
-      <c r="C166" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="D166" t="n">
-        <v>3065</v>
-      </c>
-      <c r="E166" t="n">
+      <c r="C169" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="D169" t="n">
+        <v>3160</v>
+      </c>
+      <c r="E169" t="n">
         <v>2681.96152003832</v>
       </c>
-      <c r="F166" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="G166" t="inlineStr">
+      <c r="F169" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="G169" t="inlineStr">
         <is>
           <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
+      <c r="H169" t="inlineStr">
         <is>
           <t>2026-01-22</t>
         </is>
       </c>
-      <c r="I166" t="n">
+      <c r="I169" t="n">
         <v>12089000000</v>
       </c>
-      <c r="J166" t="n">
+      <c r="J169" t="n">
         <v>7327000000</v>
       </c>
-      <c r="K166" t="n">
+      <c r="K169" t="n">
         <v>1115000000</v>
       </c>
-      <c r="L166" t="n">
+      <c r="L169" t="n">
         <v>51632000000</v>
       </c>
-      <c r="M166" t="n">
+      <c r="M169" t="n">
         <v>20531000000</v>
       </c>
-      <c r="N166" t="n">
-        <v>68863828455</v>
+      <c r="N169" t="n">
+        <v>70998270120</v>
       </c>
     </row>
   </sheetData>

--- a/docs/アクティビスト銘柄_資産判定.xlsx
+++ b/docs/アクティビスト銘柄_資産判定.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N169"/>
+  <dimension ref="A1:N172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>44.8</v>
+        <v>44.3</v>
       </c>
       <c r="D2" t="n">
-        <v>1328.5</v>
+        <v>1342</v>
       </c>
       <c r="E2" t="n">
         <v>1111.251693601708</v>
       </c>
       <c r="F2" t="n">
-        <v>19.5</v>
+        <v>20.8</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -537,7 +537,7 @@
         <v>213563000000</v>
       </c>
       <c r="N2" t="n">
-        <v>476974065140</v>
+        <v>481820997680</v>
       </c>
     </row>
     <row r="3">
@@ -552,16 +552,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>54.5</v>
+        <v>53.7</v>
       </c>
       <c r="D3" t="n">
-        <v>1166</v>
+        <v>1185</v>
       </c>
       <c r="E3" t="n">
         <v>1019.677694332945</v>
       </c>
       <c r="F3" t="n">
-        <v>14.3</v>
+        <v>16.2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         <v>106991000000</v>
       </c>
       <c r="N3" t="n">
-        <v>196180141300</v>
+        <v>199376901750</v>
       </c>
     </row>
     <row r="4">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="D4" t="n">
-        <v>3436</v>
+        <v>3493</v>
       </c>
       <c r="E4" t="n">
         <v>6116.356643776557</v>
       </c>
       <c r="F4" t="n">
-        <v>-43.8</v>
+        <v>-42.9</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         <v>219041000000</v>
       </c>
       <c r="N4" t="n">
-        <v>3108748467384</v>
+        <v>3160319673042</v>
       </c>
     </row>
     <row r="5">
@@ -656,16 +656,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30.5</v>
+        <v>30.2</v>
       </c>
       <c r="D5" t="n">
-        <v>2203</v>
+        <v>2228</v>
       </c>
       <c r="E5" t="n">
         <v>1815.198567455447</v>
       </c>
       <c r="F5" t="n">
-        <v>21.4</v>
+        <v>22.7</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         <v>168499000000</v>
       </c>
       <c r="N5" t="n">
-        <v>552109806156</v>
+        <v>558375237456</v>
       </c>
     </row>
     <row r="6">
@@ -708,16 +708,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>53.7</v>
+        <v>52.3</v>
       </c>
       <c r="D6" t="n">
-        <v>10890</v>
+        <v>11180</v>
       </c>
       <c r="E6" t="n">
         <v>5684.0003469471</v>
       </c>
       <c r="F6" t="n">
-        <v>91.59999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>91895000000</v>
       </c>
       <c r="N6" t="n">
-        <v>171093421620</v>
+        <v>175649628440</v>
       </c>
     </row>
     <row r="7">
@@ -760,16 +760,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>53.7</v>
+        <v>52.3</v>
       </c>
       <c r="D7" t="n">
-        <v>10890</v>
+        <v>11180</v>
       </c>
       <c r="E7" t="n">
         <v>4549.503641591014</v>
       </c>
       <c r="F7" t="n">
-        <v>139.4</v>
+        <v>145.7</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>91895000000</v>
       </c>
       <c r="N7" t="n">
-        <v>171093421620</v>
+        <v>175649628440</v>
       </c>
     </row>
     <row r="8">
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="D8" t="n">
-        <v>3925</v>
+        <v>3905</v>
       </c>
       <c r="E8" t="n">
         <v>1361.432492253209</v>
       </c>
       <c r="F8" t="n">
-        <v>188.3</v>
+        <v>186.8</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>12397436000</v>
       </c>
       <c r="N8" t="n">
-        <v>87067501775</v>
+        <v>86625962225</v>
       </c>
     </row>
     <row r="9">
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>29.9</v>
+        <v>29.5</v>
       </c>
       <c r="D9" t="n">
-        <v>3346</v>
+        <v>3392</v>
       </c>
       <c r="E9" t="n">
         <v>13739.64575539568</v>
       </c>
       <c r="F9" t="n">
-        <v>-75.59999999999999</v>
+        <v>-75.3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>325393000000</v>
       </c>
       <c r="N9" t="n">
-        <v>1089900208880</v>
+        <v>1104883893760</v>
       </c>
     </row>
     <row r="10">
@@ -919,13 +919,13 @@
         <v>44.9</v>
       </c>
       <c r="D10" t="n">
-        <v>2153.5</v>
+        <v>2150</v>
       </c>
       <c r="E10" t="n">
         <v>1198.150742177053</v>
       </c>
       <c r="F10" t="n">
-        <v>79.7</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>213966000000</v>
       </c>
       <c r="N10" t="n">
-        <v>476814491244</v>
+        <v>476039543150</v>
       </c>
     </row>
     <row r="11">
@@ -971,13 +971,13 @@
         <v>44.9</v>
       </c>
       <c r="D11" t="n">
-        <v>2153.5</v>
+        <v>2150</v>
       </c>
       <c r="E11" t="n">
         <v>1188.162962482466</v>
       </c>
       <c r="F11" t="n">
-        <v>81.2</v>
+        <v>81</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>213966000000</v>
       </c>
       <c r="N11" t="n">
-        <v>476814491244</v>
+        <v>476039543150</v>
       </c>
     </row>
     <row r="12">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="D12" t="n">
-        <v>3636</v>
+        <v>3665</v>
       </c>
       <c r="E12" t="n">
         <v>2995.424821743842</v>
       </c>
       <c r="F12" t="n">
-        <v>21.4</v>
+        <v>22.4</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>129979000000</v>
       </c>
       <c r="N12" t="n">
-        <v>534367227024</v>
+        <v>538629231860</v>
       </c>
     </row>
     <row r="13">
@@ -1072,16 +1072,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>74.3</v>
+        <v>73.7</v>
       </c>
       <c r="D13" t="n">
-        <v>4840</v>
+        <v>4882</v>
       </c>
       <c r="E13" t="n">
         <v>4991.027246539169</v>
       </c>
       <c r="F13" t="n">
-        <v>-3</v>
+        <v>-2.2</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>1007966000000</v>
       </c>
       <c r="N13" t="n">
-        <v>1356273153840</v>
+        <v>1368042466332</v>
       </c>
     </row>
     <row r="14">
@@ -1127,13 +1127,13 @@
         <v>21.2</v>
       </c>
       <c r="D14" t="n">
-        <v>1729.5</v>
+        <v>1734</v>
       </c>
       <c r="E14" t="n">
         <v>1512.21980974841</v>
       </c>
       <c r="F14" t="n">
-        <v>14.4</v>
+        <v>14.7</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>120816000000</v>
       </c>
       <c r="N14" t="n">
-        <v>569726291608</v>
+        <v>571208667042</v>
       </c>
     </row>
     <row r="15">
@@ -1176,16 +1176,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="D15" t="n">
-        <v>2671</v>
+        <v>2707</v>
       </c>
       <c r="E15" t="n">
         <v>1827.011042553346</v>
       </c>
       <c r="F15" t="n">
-        <v>46.2</v>
+        <v>48.2</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>48336000000</v>
       </c>
       <c r="N15" t="n">
-        <v>651918371341</v>
+        <v>660704991097</v>
       </c>
     </row>
     <row r="16">
@@ -1228,16 +1228,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>134.2</v>
+        <v>134.8</v>
       </c>
       <c r="D16" t="n">
-        <v>1603</v>
+        <v>1595</v>
       </c>
       <c r="E16" t="n">
         <v>2122.579027791042</v>
       </c>
       <c r="F16" t="n">
-        <v>-24.5</v>
+        <v>-24.9</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>80333000000</v>
       </c>
       <c r="N16" t="n">
-        <v>59875940481</v>
+        <v>59577121065</v>
       </c>
     </row>
     <row r="17">
@@ -1280,16 +1280,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.9</v>
+        <v>16.5</v>
       </c>
       <c r="D17" t="n">
-        <v>2938.5</v>
+        <v>3022</v>
       </c>
       <c r="E17" t="n">
         <v>6272.971195510064</v>
       </c>
       <c r="F17" t="n">
-        <v>-53.2</v>
+        <v>-51.8</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>179622000000</v>
       </c>
       <c r="N17" t="n">
-        <v>1059845056659</v>
+        <v>1089961463748</v>
       </c>
     </row>
     <row r="18">
@@ -1335,13 +1335,13 @@
         <v>5.1</v>
       </c>
       <c r="D18" t="n">
-        <v>3915</v>
+        <v>3935</v>
       </c>
       <c r="E18" t="n">
         <v>1572.181660925393</v>
       </c>
       <c r="F18" t="n">
-        <v>149</v>
+        <v>150.3</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>35501000000</v>
       </c>
       <c r="N18" t="n">
-        <v>699074368155</v>
+        <v>702645629295</v>
       </c>
     </row>
     <row r="19">
@@ -1387,13 +1387,13 @@
         <v>5.1</v>
       </c>
       <c r="D19" t="n">
-        <v>3915</v>
+        <v>3935</v>
       </c>
       <c r="E19" t="n">
         <v>1141.512891683109</v>
       </c>
       <c r="F19" t="n">
-        <v>243</v>
+        <v>244.7</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>35501000000</v>
       </c>
       <c r="N19" t="n">
-        <v>699074368155</v>
+        <v>702645629295</v>
       </c>
     </row>
     <row r="20">
@@ -1436,16 +1436,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>47.8</v>
+        <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>5606</v>
+        <v>5583</v>
       </c>
       <c r="E20" t="n">
         <v>2836.942753814942</v>
       </c>
       <c r="F20" t="n">
-        <v>97.59999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>94351000000</v>
       </c>
       <c r="N20" t="n">
-        <v>197221440126</v>
+        <v>196412290443</v>
       </c>
     </row>
     <row r="21">
@@ -1488,16 +1488,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>53.9</v>
+        <v>53.5</v>
       </c>
       <c r="D21" t="n">
-        <v>4166</v>
+        <v>4199</v>
       </c>
       <c r="E21" t="n">
         <v>2863.970160821546</v>
       </c>
       <c r="F21" t="n">
-        <v>45.5</v>
+        <v>46.6</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>161529000000</v>
       </c>
       <c r="N21" t="n">
-        <v>299723549058</v>
+        <v>302097739437</v>
       </c>
     </row>
     <row r="22">
@@ -1540,16 +1540,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>51.3</v>
+        <v>50.7</v>
       </c>
       <c r="D22" t="n">
-        <v>4787</v>
+        <v>4843</v>
       </c>
       <c r="E22" t="n">
         <v>2566.284807227078</v>
       </c>
       <c r="F22" t="n">
-        <v>86.5</v>
+        <v>88.7</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>231575000000</v>
       </c>
       <c r="N22" t="n">
-        <v>451352347700</v>
+        <v>456632425300</v>
       </c>
     </row>
     <row r="23">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="D23" t="n">
-        <v>5136</v>
+        <v>5155</v>
       </c>
       <c r="E23" t="n">
         <v>2779.139169918938</v>
       </c>
       <c r="F23" t="n">
-        <v>84.8</v>
+        <v>85.5</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>183216000000</v>
       </c>
       <c r="N23" t="n">
-        <v>637030771056</v>
+        <v>639387388005</v>
       </c>
     </row>
     <row r="24">
@@ -1644,16 +1644,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="D24" t="n">
-        <v>3994</v>
+        <v>4037</v>
       </c>
       <c r="E24" t="n">
         <v>2420.370957920882</v>
       </c>
       <c r="F24" t="n">
-        <v>65</v>
+        <v>66.8</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>18167000000</v>
       </c>
       <c r="N24" t="n">
-        <v>197451693526</v>
+        <v>199577487923</v>
       </c>
     </row>
     <row r="25">
@@ -1696,16 +1696,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="D25" t="n">
-        <v>1725</v>
+        <v>1766</v>
       </c>
       <c r="E25" t="n">
         <v>1344.518957928979</v>
       </c>
       <c r="F25" t="n">
-        <v>28.3</v>
+        <v>31.3</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>45956000000</v>
       </c>
       <c r="N25" t="n">
-        <v>554094651975</v>
+        <v>567264437906</v>
       </c>
     </row>
     <row r="26">
@@ -1748,16 +1748,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>59.7</v>
+        <v>59.2</v>
       </c>
       <c r="D26" t="n">
-        <v>5018</v>
+        <v>5062</v>
       </c>
       <c r="E26" t="n">
         <v>4154.626869982095</v>
       </c>
       <c r="F26" t="n">
-        <v>20.8</v>
+        <v>21.8</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>179086000000</v>
       </c>
       <c r="N26" t="n">
-        <v>300079792168</v>
+        <v>302711021912</v>
       </c>
     </row>
     <row r="27">
@@ -1800,16 +1800,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>14.2</v>
+        <v>13.9</v>
       </c>
       <c r="D27" t="n">
-        <v>3858</v>
+        <v>3925</v>
       </c>
       <c r="E27" t="n">
         <v>2561.705402476645</v>
       </c>
       <c r="F27" t="n">
-        <v>50.6</v>
+        <v>53.2</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>100104000000</v>
       </c>
       <c r="N27" t="n">
-        <v>705942260490</v>
+        <v>718202014625</v>
       </c>
     </row>
     <row r="28">
@@ -1852,16 +1852,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>44.1</v>
+        <v>43.5</v>
       </c>
       <c r="D28" t="n">
-        <v>3504</v>
+        <v>3553</v>
       </c>
       <c r="E28" t="n">
         <v>2560</v>
       </c>
       <c r="F28" t="n">
-        <v>36.9</v>
+        <v>38.8</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>190312000000</v>
       </c>
       <c r="N28" t="n">
-        <v>431378512224</v>
+        <v>437410917218</v>
       </c>
     </row>
     <row r="29">
@@ -1904,16 +1904,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>87.09999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>4415</v>
+        <v>4530</v>
       </c>
       <c r="E29" t="n">
         <v>3449.780346820809</v>
       </c>
       <c r="F29" t="n">
-        <v>28</v>
+        <v>31.3</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>90928000000</v>
       </c>
       <c r="N29" t="n">
-        <v>104401557980</v>
+        <v>107120964360</v>
       </c>
     </row>
     <row r="30">
@@ -1956,16 +1956,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>55.5</v>
+        <v>54.9</v>
       </c>
       <c r="D30" t="n">
-        <v>1721</v>
+        <v>1738</v>
       </c>
       <c r="E30" t="n">
         <v>1746.940387696806</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.5</v>
+        <v>-0.5</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>36070000000</v>
       </c>
       <c r="N30" t="n">
-        <v>65021949453</v>
+        <v>65664234834</v>
       </c>
     </row>
     <row r="31">
@@ -2008,16 +2008,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>104.5</v>
+        <v>103.8</v>
       </c>
       <c r="D31" t="n">
-        <v>1702</v>
+        <v>1713</v>
       </c>
       <c r="E31" t="n">
         <v>2298.672482457804</v>
       </c>
       <c r="F31" t="n">
-        <v>-26</v>
+        <v>-25.5</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>42752000000</v>
       </c>
       <c r="N31" t="n">
-        <v>40917079074</v>
+        <v>41181525531</v>
       </c>
     </row>
     <row r="32">
@@ -2060,16 +2060,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>66.7</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>2684</v>
+        <v>2668</v>
       </c>
       <c r="E32" t="n">
         <v>1270</v>
       </c>
       <c r="F32" t="n">
-        <v>111.3</v>
+        <v>110.1</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>31108000000</v>
       </c>
       <c r="N32" t="n">
-        <v>46668213724</v>
+        <v>46390012748</v>
       </c>
     </row>
     <row r="33">
@@ -2112,16 +2112,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>66.7</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>2684</v>
+        <v>2668</v>
       </c>
       <c r="E33" t="n">
         <v>1170</v>
       </c>
       <c r="F33" t="n">
-        <v>129.4</v>
+        <v>128</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>31108000000</v>
       </c>
       <c r="N33" t="n">
-        <v>46668213724</v>
+        <v>46390012748</v>
       </c>
     </row>
     <row r="34">
@@ -2164,16 +2164,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>33.2</v>
+        <v>32.9</v>
       </c>
       <c r="D34" t="n">
-        <v>2868</v>
+        <v>2896</v>
       </c>
       <c r="E34" t="n">
         <v>2381.523440544182</v>
       </c>
       <c r="F34" t="n">
-        <v>20.4</v>
+        <v>21.6</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>168696000000</v>
       </c>
       <c r="N34" t="n">
-        <v>508392991392</v>
+        <v>513356381824</v>
       </c>
     </row>
     <row r="35">
@@ -2216,16 +2216,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>83.3</v>
+        <v>81.7</v>
       </c>
       <c r="D35" t="n">
-        <v>2486</v>
+        <v>2534</v>
       </c>
       <c r="E35" t="n">
         <v>2901.475903614458</v>
       </c>
       <c r="F35" t="n">
-        <v>-14.3</v>
+        <v>-12.7</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>108430000000</v>
       </c>
       <c r="N35" t="n">
-        <v>130184073624</v>
+        <v>132697684056</v>
       </c>
     </row>
     <row r="36">
@@ -2268,16 +2268,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>83.3</v>
+        <v>81.7</v>
       </c>
       <c r="D36" t="n">
-        <v>2486</v>
+        <v>2534</v>
       </c>
       <c r="E36" t="n">
         <v>2905.067038344418</v>
       </c>
       <c r="F36" t="n">
-        <v>-14.4</v>
+        <v>-12.8</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>108430000000</v>
       </c>
       <c r="N36" t="n">
-        <v>130184073624</v>
+        <v>132697684056</v>
       </c>
     </row>
     <row r="37">
@@ -2320,16 +2320,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>83.3</v>
+        <v>81.7</v>
       </c>
       <c r="D37" t="n">
-        <v>2486</v>
+        <v>2534</v>
       </c>
       <c r="E37" t="n">
         <v>2955.342465753425</v>
       </c>
       <c r="F37" t="n">
-        <v>-15.9</v>
+        <v>-14.3</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>108430000000</v>
       </c>
       <c r="N37" t="n">
-        <v>130184073624</v>
+        <v>132697684056</v>
       </c>
     </row>
     <row r="38">
@@ -2372,16 +2372,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>83.3</v>
+        <v>81.7</v>
       </c>
       <c r="D38" t="n">
-        <v>2486</v>
+        <v>2534</v>
       </c>
       <c r="E38" t="n">
         <v>2987.584858837727</v>
       </c>
       <c r="F38" t="n">
-        <v>-16.8</v>
+        <v>-15.2</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>108430000000</v>
       </c>
       <c r="N38" t="n">
-        <v>130184073624</v>
+        <v>132697684056</v>
       </c>
     </row>
     <row r="39">
@@ -2424,16 +2424,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>83.3</v>
+        <v>81.7</v>
       </c>
       <c r="D39" t="n">
-        <v>2486</v>
+        <v>2534</v>
       </c>
       <c r="E39" t="n">
         <v>3016.088716673414</v>
       </c>
       <c r="F39" t="n">
-        <v>-17.6</v>
+        <v>-16</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>108430000000</v>
       </c>
       <c r="N39" t="n">
-        <v>130184073624</v>
+        <v>132697684056</v>
       </c>
     </row>
     <row r="40">
@@ -2476,16 +2476,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>83.3</v>
+        <v>81.7</v>
       </c>
       <c r="D40" t="n">
-        <v>2486</v>
+        <v>2534</v>
       </c>
       <c r="E40" t="n">
         <v>3016.087384069568</v>
       </c>
       <c r="F40" t="n">
-        <v>-17.6</v>
+        <v>-16</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>108430000000</v>
       </c>
       <c r="N40" t="n">
-        <v>130184073624</v>
+        <v>132697684056</v>
       </c>
     </row>
     <row r="41">
@@ -2528,16 +2528,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>83.3</v>
+        <v>81.7</v>
       </c>
       <c r="D41" t="n">
-        <v>2486</v>
+        <v>2534</v>
       </c>
       <c r="E41" t="n">
         <v>2939.562915943684</v>
       </c>
       <c r="F41" t="n">
-        <v>-15.4</v>
+        <v>-13.8</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>108430000000</v>
       </c>
       <c r="N41" t="n">
-        <v>130184073624</v>
+        <v>132697684056</v>
       </c>
     </row>
     <row r="42">
@@ -2684,16 +2684,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>86.7</v>
+        <v>85.7</v>
       </c>
       <c r="D44" t="n">
-        <v>2768</v>
+        <v>2799</v>
       </c>
       <c r="E44" t="n">
         <v>4265.455132343447</v>
       </c>
       <c r="F44" t="n">
-        <v>-35.1</v>
+        <v>-34.4</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>22869000000</v>
       </c>
       <c r="N44" t="n">
-        <v>26389608224</v>
+        <v>26685156582</v>
       </c>
     </row>
     <row r="45">
@@ -2736,16 +2736,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>33</v>
+        <v>32.4</v>
       </c>
       <c r="D45" t="n">
-        <v>4675</v>
+        <v>4760</v>
       </c>
       <c r="E45" t="n">
         <v>2824.318397803668</v>
       </c>
       <c r="F45" t="n">
-        <v>65.5</v>
+        <v>68.5</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>61975000000</v>
       </c>
       <c r="N45" t="n">
-        <v>188078312125</v>
+        <v>191497917800</v>
       </c>
     </row>
     <row r="46">
@@ -2788,16 +2788,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>28.6</v>
+        <v>28.1</v>
       </c>
       <c r="D46" t="n">
-        <v>6740</v>
+        <v>6880</v>
       </c>
       <c r="E46" t="n">
         <v>3096.322467304314</v>
       </c>
       <c r="F46" t="n">
-        <v>117.7</v>
+        <v>122.2</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>52961000000</v>
       </c>
       <c r="N46" t="n">
-        <v>184899565800</v>
+        <v>188740209600</v>
       </c>
     </row>
     <row r="47">
@@ -2840,16 +2840,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="D47" t="n">
-        <v>6424</v>
+        <v>6450</v>
       </c>
       <c r="E47" t="n">
         <v>3322.047887165483</v>
       </c>
       <c r="F47" t="n">
-        <v>93.40000000000001</v>
+        <v>94.2</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>492847000000</v>
       </c>
       <c r="N47" t="n">
-        <v>2098501478216</v>
+        <v>2106994790550</v>
       </c>
     </row>
     <row r="48">
@@ -2892,16 +2892,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>35.4</v>
+        <v>35.1</v>
       </c>
       <c r="D48" t="n">
-        <v>1757</v>
+        <v>1772</v>
       </c>
       <c r="E48" t="n">
         <v>2112.609181636727</v>
       </c>
       <c r="F48" t="n">
-        <v>-16.8</v>
+        <v>-16.1</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>52218000000</v>
       </c>
       <c r="N48" t="n">
-        <v>147517737570</v>
+        <v>148777137720</v>
       </c>
     </row>
     <row r="49">
@@ -2947,13 +2947,13 @@
         <v>3.7</v>
       </c>
       <c r="D49" t="n">
-        <v>708</v>
+        <v>720</v>
       </c>
       <c r="E49" t="n">
         <v>404.9347366248775</v>
       </c>
       <c r="F49" t="n">
-        <v>74.8</v>
+        <v>77.8</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>7044972000</v>
       </c>
       <c r="N49" t="n">
-        <v>188742962340</v>
+        <v>191941995600</v>
       </c>
     </row>
     <row r="50">
@@ -2996,16 +2996,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="D50" t="n">
-        <v>2646</v>
+        <v>2724</v>
       </c>
       <c r="E50" t="n">
         <v>2220.184278344451</v>
       </c>
       <c r="F50" t="n">
-        <v>19.2</v>
+        <v>22.7</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>207116000000</v>
       </c>
       <c r="N50" t="n">
-        <v>3033135823410</v>
+        <v>3122547990540</v>
       </c>
     </row>
     <row r="51">
@@ -3048,16 +3048,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="D51" t="n">
-        <v>22130</v>
+        <v>22015</v>
       </c>
       <c r="E51" t="n">
         <v>11879.91675437757</v>
       </c>
       <c r="F51" t="n">
-        <v>86.3</v>
+        <v>85.3</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>191958000000</v>
       </c>
       <c r="N51" t="n">
-        <v>929937012150</v>
+        <v>925104533325</v>
       </c>
     </row>
     <row r="52">
@@ -3100,16 +3100,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="D52" t="n">
-        <v>1131</v>
+        <v>1134</v>
       </c>
       <c r="E52" t="n">
         <v>730</v>
       </c>
       <c r="F52" t="n">
-        <v>54.9</v>
+        <v>55.3</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>50027000000</v>
       </c>
       <c r="N52" t="n">
-        <v>69052284366</v>
+        <v>69235446924</v>
       </c>
     </row>
     <row r="53">
@@ -3152,16 +3152,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>23.8</v>
+        <v>23.3</v>
       </c>
       <c r="D53" t="n">
-        <v>5497</v>
+        <v>5623</v>
       </c>
       <c r="E53" t="n">
         <v>3341.42986565678</v>
       </c>
       <c r="F53" t="n">
-        <v>64.5</v>
+        <v>68.3</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>311107000000</v>
       </c>
       <c r="N53" t="n">
-        <v>1306218539821</v>
+        <v>1336159150339</v>
       </c>
     </row>
     <row r="54">
@@ -3204,16 +3204,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="D54" t="n">
-        <v>3255</v>
+        <v>3245</v>
       </c>
       <c r="E54" t="n">
-        <v>2550.198980592041</v>
+        <v>2566.161017239607</v>
       </c>
       <c r="F54" t="n">
-        <v>27.6</v>
+        <v>26.5</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -3241,527 +3241,527 @@
         <v>32342000000</v>
       </c>
       <c r="N54" t="n">
-        <v>113953045080</v>
+        <v>113633137420</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>イオンフィナンシャルサービス株式会社</t>
+          <t>ＫＨネオケム株式会社</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>8570</t>
+          <t>4189</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>211.1</v>
+        <v>28.5</v>
       </c>
       <c r="D55" t="n">
-        <v>1639.5</v>
+        <v>3245</v>
       </c>
       <c r="E55" t="n">
-        <v>1288.711724885291</v>
+        <v>2550.198980592041</v>
       </c>
       <c r="F55" t="n">
         <v>27.2</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>697628000000</v>
+        <v>16934000000</v>
       </c>
       <c r="J55" t="n">
-        <v>34512000000</v>
+        <v>8038000000</v>
       </c>
       <c r="K55" t="n">
-        <v>14926000000</v>
+        <v>7370000000</v>
       </c>
       <c r="L55" t="n">
-        <v>509055000000</v>
+        <v>57505000000</v>
       </c>
       <c r="M55" t="n">
-        <v>747066000000</v>
+        <v>32342000000</v>
       </c>
       <c r="N55" t="n">
-        <v>353942101634</v>
+        <v>113633137420</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>株式会社フジ・メディア・ホールディングス</t>
+          <t>ＫＨネオケム株式会社</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4189</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>67.09999999999999</v>
+        <v>28.5</v>
       </c>
       <c r="D56" t="n">
-        <v>4096</v>
+        <v>3245</v>
       </c>
       <c r="E56" t="n">
-        <v>3141.424011416125</v>
+        <v>2550.198980592041</v>
       </c>
       <c r="F56" t="n">
-        <v>30.4</v>
+        <v>27.2</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>102598000000</v>
+        <v>16934000000</v>
       </c>
       <c r="J56" t="n">
-        <v>174990000000</v>
+        <v>8038000000</v>
       </c>
       <c r="K56" t="n">
-        <v>113991000000</v>
+        <v>7370000000</v>
       </c>
       <c r="L56" t="n">
-        <v>808788000000</v>
+        <v>57505000000</v>
       </c>
       <c r="M56" t="n">
-        <v>391579000000</v>
+        <v>32342000000</v>
       </c>
       <c r="N56" t="n">
-        <v>583661993984</v>
+        <v>113633137420</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>株式会社フジ・メディア・ホールディングス</t>
+          <t>イオンフィナンシャルサービス株式会社</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>8570</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>67.09999999999999</v>
+        <v>210.4</v>
       </c>
       <c r="D57" t="n">
-        <v>4096</v>
+        <v>1644.5</v>
       </c>
       <c r="E57" t="n">
-        <v>2420</v>
+        <v>1288.711724885291</v>
       </c>
       <c r="F57" t="n">
-        <v>69.3</v>
+        <v>27.6</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>株式会社レノ代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>102598000000</v>
+        <v>697628000000</v>
       </c>
       <c r="J57" t="n">
-        <v>174990000000</v>
+        <v>34512000000</v>
       </c>
       <c r="K57" t="n">
-        <v>113991000000</v>
+        <v>14926000000</v>
       </c>
       <c r="L57" t="n">
-        <v>808788000000</v>
+        <v>509055000000</v>
       </c>
       <c r="M57" t="n">
-        <v>391579000000</v>
+        <v>747066000000</v>
       </c>
       <c r="N57" t="n">
-        <v>583661993984</v>
+        <v>355021522498</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>株式会社クスリのアオキホールディングス</t>
+          <t>株式会社フジ・メディア・ホールディングス</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>3549</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>42.8</v>
+        <v>66.2</v>
       </c>
       <c r="D58" t="n">
-        <v>3993</v>
+        <v>4154</v>
       </c>
       <c r="E58" t="n">
-        <v>3047.091476167608</v>
+        <v>3141.424011416125</v>
       </c>
       <c r="F58" t="n">
-        <v>31</v>
+        <v>32.2</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>26348000000</v>
+        <v>102598000000</v>
       </c>
       <c r="J58" t="n">
-        <v>132363000000</v>
+        <v>174990000000</v>
       </c>
       <c r="K58" t="n">
-        <v>3747000000</v>
+        <v>113991000000</v>
       </c>
       <c r="L58" t="n">
-        <v>86930000000</v>
+        <v>808788000000</v>
       </c>
       <c r="M58" t="n">
-        <v>162458000000</v>
+        <v>391579000000</v>
       </c>
       <c r="N58" t="n">
-        <v>379187526531</v>
+        <v>591926739016</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>リンナイ株式会社</t>
+          <t>株式会社フジ・メディア・ホールディングス</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>45.8</v>
+        <v>66.2</v>
       </c>
       <c r="D59" t="n">
-        <v>3456</v>
+        <v>4154</v>
       </c>
       <c r="E59" t="n">
-        <v>2844.704547285864</v>
+        <v>2420</v>
       </c>
       <c r="F59" t="n">
-        <v>21.5</v>
+        <v>71.7</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社レノ代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>147972000000</v>
+        <v>102598000000</v>
       </c>
       <c r="J59" t="n">
-        <v>64736000000</v>
+        <v>174990000000</v>
       </c>
       <c r="K59" t="n">
-        <v>5967000000</v>
+        <v>113991000000</v>
       </c>
       <c r="L59" t="n">
-        <v>378856000000</v>
+        <v>808788000000</v>
       </c>
       <c r="M59" t="n">
-        <v>218675000000</v>
+        <v>391579000000</v>
       </c>
       <c r="N59" t="n">
-        <v>477168579072</v>
+        <v>591926739016</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>センコーグループホールディングス株式会社</t>
+          <t>株式会社クスリのアオキホールディングス</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>9069</t>
+          <t>3549</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>53.4</v>
+        <v>41.7</v>
       </c>
       <c r="D60" t="n">
-        <v>2323.5</v>
+        <v>4100</v>
       </c>
       <c r="E60" t="n">
-        <v>1556.090471804319</v>
+        <v>3047.091476167608</v>
       </c>
       <c r="F60" t="n">
-        <v>49.3</v>
+        <v>34.6</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>42193000000</v>
+        <v>26348000000</v>
       </c>
       <c r="J60" t="n">
-        <v>138228000000</v>
+        <v>132363000000</v>
       </c>
       <c r="K60" t="n">
-        <v>27045000000</v>
+        <v>3747000000</v>
       </c>
       <c r="L60" t="n">
-        <v>160854000000</v>
+        <v>86930000000</v>
       </c>
       <c r="M60" t="n">
-        <v>207466000000</v>
+        <v>162458000000</v>
       </c>
       <c r="N60" t="n">
-        <v>388619792318</v>
+        <v>389348574700</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ブロードメディア株式会社</t>
+          <t>リンナイ株式会社</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>5947</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>44.6</v>
+        <v>45.3</v>
       </c>
       <c r="D61" t="n">
-        <v>1896</v>
+        <v>3500</v>
       </c>
       <c r="E61" t="n">
-        <v>1529.631984751819</v>
+        <v>2844.704547285864</v>
       </c>
       <c r="F61" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>5301579000</v>
+        <v>147972000000</v>
       </c>
       <c r="J61" t="n">
-        <v>553048000</v>
+        <v>64736000000</v>
       </c>
       <c r="K61" t="n">
-        <v>169455000</v>
+        <v>5967000000</v>
       </c>
       <c r="L61" t="n">
-        <v>4610613000</v>
+        <v>378856000000</v>
       </c>
       <c r="M61" t="n">
-        <v>6024082000</v>
+        <v>218675000000</v>
       </c>
       <c r="N61" t="n">
-        <v>13513112424</v>
+        <v>483243642000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ブロードメディア株式会社</t>
+          <t>センコーグループホールディングス株式会社</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>9069</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>44.6</v>
+        <v>52.4</v>
       </c>
       <c r="D62" t="n">
-        <v>1896</v>
+        <v>2365</v>
       </c>
       <c r="E62" t="n">
-        <v>1449.995380693296</v>
+        <v>1556.090471804319</v>
       </c>
       <c r="F62" t="n">
-        <v>30.8</v>
+        <v>52</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5301579000</v>
+        <v>42193000000</v>
       </c>
       <c r="J62" t="n">
-        <v>553048000</v>
+        <v>138228000000</v>
       </c>
       <c r="K62" t="n">
-        <v>169455000</v>
+        <v>27045000000</v>
       </c>
       <c r="L62" t="n">
-        <v>4610613000</v>
+        <v>160854000000</v>
       </c>
       <c r="M62" t="n">
-        <v>6024082000</v>
+        <v>207466000000</v>
       </c>
       <c r="N62" t="n">
-        <v>13513112424</v>
+        <v>395945000825</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>株式会社ニップン</t>
+          <t>ブロードメディア株式会社</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>67.3</v>
+        <v>45.4</v>
       </c>
       <c r="D63" t="n">
-        <v>2973</v>
+        <v>1860</v>
       </c>
       <c r="E63" t="n">
-        <v>2723.418631349517</v>
+        <v>1529.631984751819</v>
       </c>
       <c r="F63" t="n">
-        <v>9.199999999999999</v>
+        <v>21.6</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>31215000000</v>
+        <v>5301579000</v>
       </c>
       <c r="J63" t="n">
-        <v>48537000000</v>
+        <v>553048000</v>
       </c>
       <c r="K63" t="n">
-        <v>85530000000</v>
+        <v>169455000</v>
       </c>
       <c r="L63" t="n">
-        <v>178697000000</v>
+        <v>4610613000</v>
       </c>
       <c r="M63" t="n">
-        <v>165282000000</v>
+        <v>6024082000</v>
       </c>
       <c r="N63" t="n">
-        <v>245761659582</v>
+        <v>13256534340</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>株式会社ニップン</t>
+          <t>ブロードメディア株式会社</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>67.3</v>
+        <v>45.4</v>
       </c>
       <c r="D64" t="n">
-        <v>2973</v>
+        <v>1860</v>
       </c>
       <c r="E64" t="n">
-        <v>2709.132103263819</v>
+        <v>1449.995380693296</v>
       </c>
       <c r="F64" t="n">
-        <v>9.699999999999999</v>
+        <v>28.3</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>31215000000</v>
+        <v>5301579000</v>
       </c>
       <c r="J64" t="n">
-        <v>48537000000</v>
+        <v>553048000</v>
       </c>
       <c r="K64" t="n">
-        <v>85530000000</v>
+        <v>169455000</v>
       </c>
       <c r="L64" t="n">
-        <v>178697000000</v>
+        <v>4610613000</v>
       </c>
       <c r="M64" t="n">
-        <v>165282000000</v>
+        <v>6024082000</v>
       </c>
       <c r="N64" t="n">
-        <v>245761659582</v>
+        <v>13256534340</v>
       </c>
     </row>
     <row r="65">
@@ -3776,16 +3776,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>67.3</v>
+        <v>66.2</v>
       </c>
       <c r="D65" t="n">
-        <v>2973</v>
+        <v>3020</v>
       </c>
       <c r="E65" t="n">
-        <v>2696.128808062088</v>
+        <v>2723.418631349517</v>
       </c>
       <c r="F65" t="n">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="I65" t="n">
@@ -3813,7 +3813,7 @@
         <v>165282000000</v>
       </c>
       <c r="N65" t="n">
-        <v>245761659582</v>
+        <v>249646892680</v>
       </c>
     </row>
     <row r="66">
@@ -3828,16 +3828,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>67.3</v>
+        <v>66.2</v>
       </c>
       <c r="D66" t="n">
-        <v>2973</v>
+        <v>3020</v>
       </c>
       <c r="E66" t="n">
-        <v>2696.128808062088</v>
+        <v>2709.132103263819</v>
       </c>
       <c r="F66" t="n">
-        <v>10.3</v>
+        <v>11.5</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -3865,239 +3865,239 @@
         <v>165282000000</v>
       </c>
       <c r="N66" t="n">
-        <v>245761659582</v>
+        <v>249646892680</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>京浜急行電鉄株式会社</t>
+          <t>株式会社ニップン</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>119.7</v>
+        <v>66.2</v>
       </c>
       <c r="D67" t="n">
-        <v>1565</v>
+        <v>3020</v>
       </c>
       <c r="E67" t="n">
-        <v>1160.8</v>
+        <v>2696.128808062088</v>
       </c>
       <c r="F67" t="n">
-        <v>34.8</v>
+        <v>12</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>61234000000</v>
+        <v>31215000000</v>
       </c>
       <c r="J67" t="n">
-        <v>318113000000</v>
+        <v>48537000000</v>
       </c>
       <c r="K67" t="n">
-        <v>114136000000</v>
+        <v>85530000000</v>
       </c>
       <c r="L67" t="n">
-        <v>256898000000</v>
+        <v>178697000000</v>
       </c>
       <c r="M67" t="n">
-        <v>493483000000</v>
+        <v>165282000000</v>
       </c>
       <c r="N67" t="n">
-        <v>412387642765</v>
+        <v>249646892680</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>あいホールディングス株式会社</t>
+          <t>株式会社ニップン</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>3076</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>23.4</v>
+        <v>66.2</v>
       </c>
       <c r="D68" t="n">
-        <v>2990</v>
+        <v>3020</v>
       </c>
       <c r="E68" t="n">
-        <v>2007.754513143541</v>
+        <v>2696.128808062088</v>
       </c>
       <c r="F68" t="n">
-        <v>48.9</v>
+        <v>12</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>32012000000</v>
+        <v>31215000000</v>
       </c>
       <c r="J68" t="n">
-        <v>1646000000</v>
+        <v>48537000000</v>
       </c>
       <c r="K68" t="n">
-        <v>3550000000</v>
+        <v>85530000000</v>
       </c>
       <c r="L68" t="n">
-        <v>53765000000</v>
+        <v>178697000000</v>
       </c>
       <c r="M68" t="n">
-        <v>37208000000</v>
+        <v>165282000000</v>
       </c>
       <c r="N68" t="n">
-        <v>159286063690</v>
+        <v>249646892680</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>エア・ウォーター株式会社</t>
+          <t>京浜急行電鉄株式会社</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>14.7</v>
+        <v>118.3</v>
       </c>
       <c r="D69" t="n">
-        <v>3040</v>
+        <v>1583</v>
       </c>
       <c r="E69" t="n">
-        <v>2261.880826568852</v>
+        <v>1160.8</v>
       </c>
       <c r="F69" t="n">
-        <v>34.4</v>
+        <v>36.4</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>29189000000</v>
+        <v>61234000000</v>
       </c>
       <c r="J69" t="n">
-        <v>31318000000</v>
+        <v>318113000000</v>
       </c>
       <c r="K69" t="n">
-        <v>42001000000</v>
+        <v>114136000000</v>
       </c>
       <c r="L69" t="n">
-        <v>194657000000</v>
+        <v>256898000000</v>
       </c>
       <c r="M69" t="n">
-        <v>102508000000</v>
+        <v>493483000000</v>
       </c>
       <c r="N69" t="n">
-        <v>696962234720</v>
+        <v>417130759423</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>エア・ウォーター株式会社</t>
+          <t>あいホールディングス株式会社</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>14.7</v>
+        <v>23.1</v>
       </c>
       <c r="D70" t="n">
-        <v>3040</v>
+        <v>3030</v>
       </c>
       <c r="E70" t="n">
-        <v>1970</v>
+        <v>2007.754513143541</v>
       </c>
       <c r="F70" t="n">
-        <v>54.3</v>
+        <v>50.9</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>29189000000</v>
+        <v>32012000000</v>
       </c>
       <c r="J70" t="n">
-        <v>31318000000</v>
+        <v>1646000000</v>
       </c>
       <c r="K70" t="n">
-        <v>42001000000</v>
+        <v>3550000000</v>
       </c>
       <c r="L70" t="n">
-        <v>194657000000</v>
+        <v>53765000000</v>
       </c>
       <c r="M70" t="n">
-        <v>102508000000</v>
+        <v>37208000000</v>
       </c>
       <c r="N70" t="n">
-        <v>696962234720</v>
+        <v>161416980930</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>株式会社電通総研</t>
+          <t>エア・ウォーター株式会社</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>9.6</v>
+        <v>15.1</v>
       </c>
       <c r="D71" t="n">
-        <v>2861</v>
+        <v>2968</v>
       </c>
       <c r="E71" t="n">
-        <v>1910.426979628923</v>
+        <v>2261.880826568852</v>
       </c>
       <c r="F71" t="n">
-        <v>49.8</v>
+        <v>31.2</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -4106,322 +4106,322 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>49748000000</v>
+        <v>29189000000</v>
       </c>
       <c r="J71" t="n">
-        <v>524000000</v>
+        <v>31318000000</v>
       </c>
       <c r="K71" t="n">
-        <v>3388000000</v>
+        <v>42001000000</v>
       </c>
       <c r="L71" t="n">
-        <v>65471000000</v>
+        <v>194657000000</v>
       </c>
       <c r="M71" t="n">
-        <v>53660000000</v>
+        <v>102508000000</v>
       </c>
       <c r="N71" t="n">
-        <v>558410329042</v>
+        <v>680455234424</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>わかもと製薬株式会社</t>
+          <t>エア・ウォーター株式会社</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>49.6</v>
+        <v>15.1</v>
       </c>
       <c r="D72" t="n">
-        <v>300</v>
+        <v>2968</v>
       </c>
       <c r="E72" t="n">
-        <v>290.3401328717133</v>
+        <v>1970</v>
       </c>
       <c r="F72" t="n">
-        <v>3.3</v>
+        <v>50.7</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3231889000</v>
+        <v>29189000000</v>
       </c>
       <c r="J72" t="n">
-        <v>82947000</v>
+        <v>31318000000</v>
       </c>
       <c r="K72" t="n">
-        <v>1847919000</v>
+        <v>42001000000</v>
       </c>
       <c r="L72" t="n">
-        <v>11480803000</v>
+        <v>194657000000</v>
       </c>
       <c r="M72" t="n">
-        <v>5162755000</v>
+        <v>102508000000</v>
       </c>
       <c r="N72" t="n">
-        <v>10411751700</v>
+        <v>680455234424</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>株式会社豊田自動織機</t>
+          <t>株式会社電通総研</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>6201</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
+          <t>4812</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="D73" t="n">
+        <v>2864</v>
+      </c>
       <c r="E73" t="n">
-        <v>16430.4430802409</v>
-      </c>
-      <c r="F73" t="inlineStr"/>
+        <v>1910.426979628923</v>
+      </c>
+      <c r="F73" t="n">
+        <v>49.9</v>
+      </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>281605000000</v>
+        <v>49748000000</v>
       </c>
       <c r="J73" t="n">
-        <v>87540000000</v>
+        <v>524000000</v>
       </c>
       <c r="K73" t="n">
-        <v>730709000000</v>
+        <v>3388000000</v>
       </c>
       <c r="L73" t="n">
-        <v>3246174000000</v>
+        <v>65471000000</v>
       </c>
       <c r="M73" t="n">
-        <v>1099854000000</v>
-      </c>
-      <c r="N73" t="inlineStr"/>
+        <v>53660000000</v>
+      </c>
+      <c r="N73" t="n">
+        <v>558995869408</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>株式会社豊田自動織機</t>
+          <t>わかもと製薬株式会社</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>6201</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
+          <t>4512</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="D74" t="n">
+        <v>299</v>
+      </c>
       <c r="E74" t="n">
-        <v>16430443.10823975</v>
-      </c>
-      <c r="F74" t="inlineStr"/>
+        <v>290.3401328717133</v>
+      </c>
+      <c r="F74" t="n">
+        <v>3</v>
+      </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>281605000000</v>
+        <v>3231889000</v>
       </c>
       <c r="J74" t="n">
-        <v>87540000000</v>
+        <v>82947000</v>
       </c>
       <c r="K74" t="n">
-        <v>730709000000</v>
+        <v>1847919000</v>
       </c>
       <c r="L74" t="n">
-        <v>3246174000000</v>
+        <v>11480803000</v>
       </c>
       <c r="M74" t="n">
-        <v>1099854000000</v>
-      </c>
-      <c r="N74" t="inlineStr"/>
+        <v>5162755000</v>
+      </c>
+      <c r="N74" t="n">
+        <v>10377045861</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>大阪製鐵株式会社</t>
+          <t>株式会社豊田自動織機</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5449</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>95.5</v>
-      </c>
-      <c r="D75" t="n">
-        <v>2527</v>
-      </c>
+          <t>6201</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="n">
-        <v>1748.071046781136</v>
-      </c>
-      <c r="F75" t="n">
-        <v>44.6</v>
-      </c>
+        <v>16430.4430802409</v>
+      </c>
+      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>62396000000</v>
+        <v>281605000000</v>
       </c>
       <c r="J75" t="n">
-        <v>9241000000</v>
+        <v>87540000000</v>
       </c>
       <c r="K75" t="n">
-        <v>553000000</v>
+        <v>730709000000</v>
       </c>
       <c r="L75" t="n">
-        <v>151028000000</v>
+        <v>3246174000000</v>
       </c>
       <c r="M75" t="n">
-        <v>72190000000</v>
-      </c>
-      <c r="N75" t="n">
-        <v>75604148053</v>
-      </c>
+        <v>1099854000000</v>
+      </c>
+      <c r="N75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>株式会社ディー・エヌ・エー</t>
+          <t>株式会社豊田自動織機</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2432</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="D76" t="n">
-        <v>2535</v>
-      </c>
+          <t>6201</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="n">
-        <v>2551.08574256026</v>
-      </c>
-      <c r="F76" t="n">
-        <v>-0.6</v>
-      </c>
+        <v>16430443.10823975</v>
+      </c>
+      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>85363000000</v>
+        <v>281605000000</v>
       </c>
       <c r="J76" t="n">
-        <v>221000000</v>
+        <v>87540000000</v>
       </c>
       <c r="K76" t="n">
-        <v>93552000000</v>
+        <v>730709000000</v>
       </c>
       <c r="L76" t="n">
-        <v>177857000000</v>
+        <v>3246174000000</v>
       </c>
       <c r="M76" t="n">
-        <v>179136000000</v>
-      </c>
-      <c r="N76" t="n">
-        <v>234517009935</v>
-      </c>
+        <v>1099854000000</v>
+      </c>
+      <c r="N76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>株式会社ディー・エヌ・エー</t>
+          <t>大阪製鐵株式会社</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>5449</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>76.40000000000001</v>
+        <v>94.2</v>
       </c>
       <c r="D77" t="n">
-        <v>2535</v>
+        <v>2562</v>
       </c>
       <c r="E77" t="n">
-        <v>2260</v>
+        <v>1748.071046781136</v>
       </c>
       <c r="F77" t="n">
-        <v>12.2</v>
+        <v>46.6</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>85363000000</v>
+        <v>62396000000</v>
       </c>
       <c r="J77" t="n">
-        <v>221000000</v>
+        <v>9241000000</v>
       </c>
       <c r="K77" t="n">
-        <v>93552000000</v>
+        <v>553000000</v>
       </c>
       <c r="L77" t="n">
-        <v>177857000000</v>
+        <v>151028000000</v>
       </c>
       <c r="M77" t="n">
-        <v>179136000000</v>
+        <v>72190000000</v>
       </c>
       <c r="N77" t="n">
-        <v>234517009935</v>
+        <v>76651296918</v>
       </c>
     </row>
     <row r="78">
@@ -4436,16 +4436,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>76.40000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="D78" t="n">
-        <v>2535</v>
+        <v>2578</v>
       </c>
       <c r="E78" t="n">
-        <v>2260</v>
+        <v>2551.08574256026</v>
       </c>
       <c r="F78" t="n">
-        <v>12.2</v>
+        <v>1.1</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="I78" t="n">
@@ -4473,1647 +4473,1647 @@
         <v>179136000000</v>
       </c>
       <c r="N78" t="n">
-        <v>234517009935</v>
+        <v>238495010498</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>株式会社オリエントコーポレーション</t>
+          <t>株式会社ディー・エヌ・エー</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>8585</t>
+          <t>2432</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>305.7</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="D79" t="n">
-        <v>858</v>
+        <v>2578</v>
       </c>
       <c r="E79" t="n">
-        <v>798.3805136422309</v>
+        <v>2260</v>
       </c>
       <c r="F79" t="n">
-        <v>7.5</v>
+        <v>14.1</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>408187000000</v>
+        <v>85363000000</v>
       </c>
       <c r="J79" t="n">
-        <v>18930000000</v>
+        <v>221000000</v>
       </c>
       <c r="K79" t="n">
-        <v>21921000000</v>
+        <v>93552000000</v>
       </c>
       <c r="L79" t="n">
-        <v>216837000000</v>
+        <v>177857000000</v>
       </c>
       <c r="M79" t="n">
-        <v>449038000000</v>
+        <v>179136000000</v>
       </c>
       <c r="N79" t="n">
-        <v>146877471312</v>
+        <v>238495010498</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>東ソー株式会社</t>
+          <t>株式会社ディー・エヌ・エー</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>4042</t>
+          <t>2432</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>42.3</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="D80" t="n">
-        <v>2613.5</v>
+        <v>2578</v>
       </c>
       <c r="E80" t="n">
-        <v>2032.365850102071</v>
+        <v>2260</v>
       </c>
       <c r="F80" t="n">
-        <v>28.6</v>
+        <v>14.1</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>160812000000</v>
+        <v>85363000000</v>
       </c>
       <c r="J80" t="n">
-        <v>109648000000</v>
+        <v>221000000</v>
       </c>
       <c r="K80" t="n">
-        <v>70132000000</v>
+        <v>93552000000</v>
       </c>
       <c r="L80" t="n">
-        <v>759724000000</v>
+        <v>177857000000</v>
       </c>
       <c r="M80" t="n">
-        <v>340592000000</v>
+        <v>179136000000</v>
       </c>
       <c r="N80" t="n">
-        <v>804671941971</v>
+        <v>238495010498</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>株式会社西武ホールディングス</t>
+          <t>株式会社オリエントコーポレーション</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>8585</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>62.6</v>
+        <v>301.9</v>
       </c>
       <c r="D81" t="n">
-        <v>3551</v>
+        <v>869</v>
       </c>
       <c r="E81" t="n">
-        <v>1716.713876475349</v>
+        <v>798.3805136422309</v>
       </c>
       <c r="F81" t="n">
-        <v>106.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>87210000000</v>
+        <v>408187000000</v>
       </c>
       <c r="J81" t="n">
-        <v>428181000000</v>
+        <v>18930000000</v>
       </c>
       <c r="K81" t="n">
-        <v>49954000000</v>
+        <v>21921000000</v>
       </c>
       <c r="L81" t="n">
-        <v>387217000000</v>
+        <v>216837000000</v>
       </c>
       <c r="M81" t="n">
-        <v>565345000000</v>
+        <v>449038000000</v>
       </c>
       <c r="N81" t="n">
-        <v>902585325188</v>
+        <v>148760515816</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>東ソー株式会社</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>4042</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="D82" t="n">
+        <v>2644</v>
+      </c>
+      <c r="E82" t="n">
+        <v>2032.365850102071</v>
+      </c>
+      <c r="F82" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>2024-06-04</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>160812000000</v>
+      </c>
+      <c r="J82" t="n">
+        <v>109648000000</v>
+      </c>
+      <c r="K82" t="n">
+        <v>70132000000</v>
+      </c>
+      <c r="L82" t="n">
+        <v>759724000000</v>
+      </c>
+      <c r="M82" t="n">
+        <v>340592000000</v>
+      </c>
+      <c r="N82" t="n">
+        <v>814062603624</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>株式会社西武ホールディングス</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>9024</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="D83" t="n">
+        <v>3641</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1716.713876475349</v>
+      </c>
+      <c r="F83" t="n">
+        <v>112.1</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>87210000000</v>
+      </c>
+      <c r="J83" t="n">
+        <v>428181000000</v>
+      </c>
+      <c r="K83" t="n">
+        <v>49954000000</v>
+      </c>
+      <c r="L83" t="n">
+        <v>387217000000</v>
+      </c>
+      <c r="M83" t="n">
+        <v>565345000000</v>
+      </c>
+      <c r="N83" t="n">
+        <v>925461326108</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
           <t>株式会社フェローテック
 （旧会社名　株式会社フェローテックホールディングス）</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>6890</t>
         </is>
       </c>
-      <c r="C82" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="D82" t="n">
-        <v>9100</v>
-      </c>
-      <c r="E82" t="n">
+      <c r="C84" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="D84" t="n">
+        <v>9030</v>
+      </c>
+      <c r="E84" t="n">
         <v>4037.502552255647</v>
       </c>
-      <c r="F82" t="n">
-        <v>125.4</v>
-      </c>
-      <c r="G82" t="inlineStr">
+      <c r="F84" t="n">
+        <v>123.7</v>
+      </c>
+      <c r="G84" t="inlineStr">
         <is>
           <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="I82" t="n">
+      <c r="I84" t="n">
         <v>52579000000</v>
       </c>
-      <c r="J82" t="n">
+      <c r="J84" t="n">
         <v>90505000000</v>
       </c>
-      <c r="K82" t="n">
+      <c r="K84" t="n">
         <v>11654000000</v>
       </c>
-      <c r="L82" t="n">
+      <c r="L84" t="n">
         <v>160957000000</v>
       </c>
-      <c r="M82" t="n">
+      <c r="M84" t="n">
         <v>154738000000</v>
       </c>
-      <c r="N82" t="n">
-        <v>489614243300</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="N84" t="n">
+        <v>485847979890</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
         <is>
           <t>株式会社フェローテック
 （旧会社名　株式会社フェローテックホールディングス）</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>6890</t>
         </is>
       </c>
-      <c r="C83" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="D83" t="n">
-        <v>9100</v>
-      </c>
-      <c r="E83" t="n">
+      <c r="C85" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="D85" t="n">
+        <v>9030</v>
+      </c>
+      <c r="E85" t="n">
         <v>3950.736048458928</v>
       </c>
-      <c r="F83" t="n">
-        <v>130.3</v>
-      </c>
-      <c r="G83" t="inlineStr">
+      <c r="F85" t="n">
+        <v>128.6</v>
+      </c>
+      <c r="G85" t="inlineStr">
         <is>
           <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="I83" t="n">
+      <c r="I85" t="n">
         <v>52579000000</v>
       </c>
-      <c r="J83" t="n">
+      <c r="J85" t="n">
         <v>90505000000</v>
       </c>
-      <c r="K83" t="n">
+      <c r="K85" t="n">
         <v>11654000000</v>
       </c>
-      <c r="L83" t="n">
+      <c r="L85" t="n">
         <v>160957000000</v>
       </c>
-      <c r="M83" t="n">
+      <c r="M85" t="n">
         <v>154738000000</v>
       </c>
-      <c r="N83" t="n">
-        <v>489614243300</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="N85" t="n">
+        <v>485847979890</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
         <is>
           <t>株式会社フェローテック
 （旧会社名　株式会社フェローテックホールディングス）</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>6890</t>
         </is>
       </c>
-      <c r="C84" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="D84" t="n">
-        <v>9100</v>
-      </c>
-      <c r="E84" t="n">
+      <c r="C86" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="D86" t="n">
+        <v>9030</v>
+      </c>
+      <c r="E86" t="n">
         <v>2030</v>
       </c>
-      <c r="F84" t="n">
-        <v>348.3</v>
-      </c>
-      <c r="G84" t="inlineStr">
+      <c r="F86" t="n">
+        <v>344.8</v>
+      </c>
+      <c r="G86" t="inlineStr">
         <is>
           <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>2025-10-22</t>
         </is>
       </c>
-      <c r="I84" t="n">
+      <c r="I86" t="n">
         <v>52579000000</v>
       </c>
-      <c r="J84" t="n">
+      <c r="J86" t="n">
         <v>90505000000</v>
       </c>
-      <c r="K84" t="n">
+      <c r="K86" t="n">
         <v>11654000000</v>
       </c>
-      <c r="L84" t="n">
+      <c r="L86" t="n">
         <v>160957000000</v>
       </c>
-      <c r="M84" t="n">
+      <c r="M86" t="n">
         <v>154738000000</v>
       </c>
-      <c r="N84" t="n">
-        <v>489614243300</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="N86" t="n">
+        <v>485847979890</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
         <is>
           <t>株式会社フェローテック
 （旧会社名　株式会社フェローテックホールディングス）</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>6890</t>
         </is>
       </c>
-      <c r="C85" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="D85" t="n">
-        <v>9100</v>
-      </c>
-      <c r="E85" t="n">
+      <c r="C87" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="D87" t="n">
+        <v>9030</v>
+      </c>
+      <c r="E87" t="n">
         <v>2387</v>
       </c>
-      <c r="F85" t="n">
-        <v>281.2</v>
-      </c>
-      <c r="G85" t="inlineStr">
+      <c r="F87" t="n">
+        <v>278.3</v>
+      </c>
+      <c r="G87" t="inlineStr">
         <is>
           <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>2025-03-07</t>
         </is>
       </c>
-      <c r="I85" t="n">
+      <c r="I87" t="n">
         <v>52579000000</v>
       </c>
-      <c r="J85" t="n">
+      <c r="J87" t="n">
         <v>90505000000</v>
       </c>
-      <c r="K85" t="n">
+      <c r="K87" t="n">
         <v>11654000000</v>
       </c>
-      <c r="L85" t="n">
+      <c r="L87" t="n">
         <v>160957000000</v>
       </c>
-      <c r="M85" t="n">
+      <c r="M87" t="n">
         <v>154738000000</v>
       </c>
-      <c r="N85" t="n">
-        <v>489614243300</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>アツギ株式会社</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>3529</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="D86" t="n">
-        <v>1049</v>
-      </c>
-      <c r="E86" t="n">
-        <v>668.9358717434869</v>
-      </c>
-      <c r="F86" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="I86" t="n">
-        <v>5500000000</v>
-      </c>
-      <c r="J86" t="n">
-        <v>3208000000</v>
-      </c>
-      <c r="K86" t="n">
-        <v>3702000000</v>
-      </c>
-      <c r="L86" t="n">
-        <v>32145000000</v>
-      </c>
-      <c r="M86" t="n">
-        <v>12410000000</v>
-      </c>
-      <c r="N86" t="n">
-        <v>16798692294</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>日本特殊塗料株式会社</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>4619</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>71.8</v>
-      </c>
-      <c r="D87" t="n">
-        <v>2651</v>
-      </c>
-      <c r="E87" t="n">
-        <v>1190</v>
-      </c>
-      <c r="F87" t="n">
-        <v>122.8</v>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="I87" t="n">
-        <v>8931000000</v>
-      </c>
-      <c r="J87" t="n">
-        <v>9514000000</v>
-      </c>
-      <c r="K87" t="n">
-        <v>22055000000</v>
-      </c>
-      <c r="L87" t="n">
-        <v>49725000000</v>
-      </c>
-      <c r="M87" t="n">
-        <v>40500000000</v>
-      </c>
       <c r="N87" t="n">
-        <v>56444686397</v>
+        <v>485847979890</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>株式会社エクセディ</t>
+          <t>アツギ株式会社</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>7278</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>19.1</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="D88" t="n">
-        <v>5900</v>
+        <v>1046</v>
       </c>
       <c r="E88" t="n">
-        <v>2617.980935875217</v>
+        <v>668.9358717434869</v>
       </c>
       <c r="F88" t="n">
-        <v>125.4</v>
+        <v>56.4</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>30019000000</v>
+        <v>5500000000</v>
       </c>
       <c r="J88" t="n">
-        <v>6792000000</v>
+        <v>3208000000</v>
       </c>
       <c r="K88" t="n">
-        <v>3427000000</v>
+        <v>3702000000</v>
       </c>
       <c r="L88" t="n">
-        <v>119460000000</v>
+        <v>32145000000</v>
       </c>
       <c r="M88" t="n">
-        <v>40238000000</v>
+        <v>12410000000</v>
       </c>
       <c r="N88" t="n">
-        <v>211182039400</v>
+        <v>16750650276</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>株式会社Ａ＆Ｄホロンホールディングス</t>
+          <t>日本特殊塗料株式会社</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>7745</t>
+          <t>4619</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>19.5</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="D89" t="n">
-        <v>2886</v>
+        <v>2714</v>
       </c>
       <c r="E89" t="n">
-        <v>2084.177692465894</v>
+        <v>1190</v>
       </c>
       <c r="F89" t="n">
-        <v>38.5</v>
+        <v>128.1</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>11012000000</v>
+        <v>8931000000</v>
       </c>
       <c r="J89" t="n">
-        <v>4106000000</v>
+        <v>9514000000</v>
       </c>
       <c r="K89" t="n">
-        <v>315000000</v>
+        <v>22055000000</v>
       </c>
       <c r="L89" t="n">
-        <v>27041000000</v>
+        <v>49725000000</v>
       </c>
       <c r="M89" t="n">
-        <v>15433000000</v>
+        <v>40500000000</v>
       </c>
       <c r="N89" t="n">
-        <v>79039808406</v>
+        <v>57786072758</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>株式会社セプテーニ・ホールディングス</t>
+          <t>株式会社エクセディ</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>4293</t>
+          <t>7278</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>13.5</v>
+        <v>18.8</v>
       </c>
       <c r="D90" t="n">
-        <v>507</v>
+        <v>5990</v>
       </c>
       <c r="E90" t="n">
-        <v>448.6811097117532</v>
+        <v>2617.980935875217</v>
       </c>
       <c r="F90" t="n">
-        <v>13</v>
+        <v>128.8</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>12184507000</v>
+        <v>30019000000</v>
       </c>
       <c r="J90" t="n">
-        <v>168073000</v>
+        <v>6792000000</v>
       </c>
       <c r="K90" t="n">
-        <v>1600720000</v>
+        <v>3427000000</v>
       </c>
       <c r="L90" t="n">
-        <v>11861578000</v>
+        <v>119460000000</v>
       </c>
       <c r="M90" t="n">
-        <v>13953300000</v>
+        <v>40238000000</v>
       </c>
       <c r="N90" t="n">
-        <v>103562195802</v>
+        <v>214403460340</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>株式会社シンクロ・フード</t>
+          <t>株式会社Ａ＆Ｄホロンホールディングス</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>7745</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>33.6</v>
+        <v>19.5</v>
       </c>
       <c r="D91" t="n">
-        <v>330</v>
+        <v>2896</v>
       </c>
       <c r="E91" t="n">
-        <v>421.6950726175476</v>
+        <v>2084.177692465894</v>
       </c>
       <c r="F91" t="n">
-        <v>-21.7</v>
+        <v>39</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3037851000</v>
+        <v>11012000000</v>
       </c>
       <c r="J91" t="n">
-        <v>56852000</v>
+        <v>4106000000</v>
       </c>
       <c r="K91" t="n">
-        <v>14952000</v>
+        <v>315000000</v>
       </c>
       <c r="L91" t="n">
-        <v>2871237000</v>
+        <v>27041000000</v>
       </c>
       <c r="M91" t="n">
-        <v>3109655000</v>
+        <v>15433000000</v>
       </c>
       <c r="N91" t="n">
-        <v>9254054040</v>
+        <v>79313681616</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>科研製薬株式会社</t>
+          <t>株式会社セプテーニ・ホールディングス</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>4293</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>71.5</v>
+        <v>13.1</v>
       </c>
       <c r="D92" t="n">
-        <v>3920</v>
+        <v>514</v>
       </c>
       <c r="E92" t="n">
-        <v>3530</v>
+        <v>448.6811097117532</v>
       </c>
       <c r="F92" t="n">
-        <v>11</v>
+        <v>14.6</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>74625000000</v>
+        <v>12184507000</v>
       </c>
       <c r="J92" t="n">
-        <v>15530000000</v>
+        <v>168073000</v>
       </c>
       <c r="K92" t="n">
-        <v>15992000000</v>
+        <v>1600720000</v>
       </c>
       <c r="L92" t="n">
-        <v>138325000000</v>
+        <v>11861578000</v>
       </c>
       <c r="M92" t="n">
-        <v>106147000000</v>
+        <v>13953300000</v>
       </c>
       <c r="N92" t="n">
-        <v>148443794800</v>
+        <v>106626786026</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>市光工業株式会社</t>
+          <t>株式会社シンクロ・フード</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>7244</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>35.8</v>
+        <v>33.7</v>
       </c>
       <c r="D93" t="n">
-        <v>555</v>
+        <v>329</v>
       </c>
       <c r="E93" t="n">
-        <v>549.4799823005444</v>
+        <v>421.6950726175476</v>
       </c>
       <c r="F93" t="n">
-        <v>1</v>
+        <v>-22</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>5720000000</v>
+        <v>3037851000</v>
       </c>
       <c r="J93" t="n">
-        <v>9921000000</v>
+        <v>56852000</v>
       </c>
       <c r="K93" t="n">
-        <v>3474000000</v>
+        <v>14952000</v>
       </c>
       <c r="L93" t="n">
-        <v>49523000000</v>
+        <v>2871237000</v>
       </c>
       <c r="M93" t="n">
-        <v>19115000000</v>
+        <v>3109655000</v>
       </c>
       <c r="N93" t="n">
-        <v>53448947550</v>
+        <v>9226011452</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>トーセイ株式会社</t>
+          <t>科研製薬株式会社</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>4521</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="D94" t="n">
-        <v>1673</v>
+        <v>4005</v>
       </c>
       <c r="E94" t="n">
-        <v>1752.426893379333</v>
+        <v>3530</v>
       </c>
       <c r="F94" t="n">
-        <v>-4.5</v>
+        <v>13.5</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>20753937000</v>
+        <v>74625000000</v>
       </c>
       <c r="J94" t="n">
-        <v>46868512000</v>
+        <v>15530000000</v>
       </c>
       <c r="K94" t="n">
-        <v>8610046000</v>
+        <v>15992000000</v>
       </c>
       <c r="L94" t="n">
-        <v>59467346000</v>
+        <v>138325000000</v>
       </c>
       <c r="M94" t="n">
-        <v>76232495000</v>
+        <v>106147000000</v>
       </c>
       <c r="N94" t="n">
-        <v>162291205300</v>
+        <v>151662601575</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>トーセイ株式会社</t>
+          <t>市光工業株式会社</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>47</v>
+        <v>35.1</v>
       </c>
       <c r="D95" t="n">
-        <v>1673</v>
+        <v>566</v>
       </c>
       <c r="E95" t="n">
-        <v>1576.721867844292</v>
+        <v>549.4799823005444</v>
       </c>
       <c r="F95" t="n">
-        <v>6.1</v>
+        <v>3</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>20753937000</v>
+        <v>5720000000</v>
       </c>
       <c r="J95" t="n">
-        <v>46868512000</v>
+        <v>9921000000</v>
       </c>
       <c r="K95" t="n">
-        <v>8610046000</v>
+        <v>3474000000</v>
       </c>
       <c r="L95" t="n">
-        <v>59467346000</v>
+        <v>49523000000</v>
       </c>
       <c r="M95" t="n">
-        <v>76232495000</v>
+        <v>19115000000</v>
       </c>
       <c r="N95" t="n">
-        <v>162291205300</v>
+        <v>54508296060</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>株式会社髙島屋</t>
+          <t>トーセイ株式会社</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>65</v>
+        <v>46.4</v>
       </c>
       <c r="D96" t="n">
-        <v>2111.5</v>
+        <v>1692</v>
       </c>
       <c r="E96" t="n">
-        <v>1101.400153022188</v>
+        <v>1752.426893379333</v>
       </c>
       <c r="F96" t="n">
-        <v>91.7</v>
+        <v>-3.4</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>88996000000</v>
+        <v>20753937000</v>
       </c>
       <c r="J96" t="n">
-        <v>193090000000</v>
+        <v>46868512000</v>
       </c>
       <c r="K96" t="n">
-        <v>119967000000</v>
+        <v>8610046000</v>
       </c>
       <c r="L96" t="n">
-        <v>420489000000</v>
+        <v>59467346000</v>
       </c>
       <c r="M96" t="n">
-        <v>402053000000</v>
+        <v>76232495000</v>
       </c>
       <c r="N96" t="n">
-        <v>618699905600</v>
+        <v>164134321200</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>株式会社髙島屋</t>
+          <t>トーセイ株式会社</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>65</v>
+        <v>46.4</v>
       </c>
       <c r="D97" t="n">
-        <v>2111.5</v>
+        <v>1692</v>
       </c>
       <c r="E97" t="n">
-        <v>1101.400153022188</v>
+        <v>1576.721867844292</v>
       </c>
       <c r="F97" t="n">
-        <v>91.7</v>
+        <v>7.3</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>88996000000</v>
+        <v>20753937000</v>
       </c>
       <c r="J97" t="n">
-        <v>193090000000</v>
+        <v>46868512000</v>
       </c>
       <c r="K97" t="n">
-        <v>119967000000</v>
+        <v>8610046000</v>
       </c>
       <c r="L97" t="n">
-        <v>420489000000</v>
+        <v>59467346000</v>
       </c>
       <c r="M97" t="n">
-        <v>402053000000</v>
+        <v>76232495000</v>
       </c>
       <c r="N97" t="n">
-        <v>618699905600</v>
+        <v>164134321200</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>三井倉庫ホールディングス株式会社</t>
+          <t>株式会社髙島屋</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>9302</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>44.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="D98" t="n">
-        <v>3397</v>
+        <v>2140.5</v>
       </c>
       <c r="E98" t="n">
-        <v>1492.806001579363</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="F98" t="n">
-        <v>127.6</v>
+        <v>94.3</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>22822000000</v>
+        <v>88996000000</v>
       </c>
       <c r="J98" t="n">
-        <v>72331000000</v>
+        <v>193090000000</v>
       </c>
       <c r="K98" t="n">
-        <v>17148000000</v>
+        <v>119967000000</v>
       </c>
       <c r="L98" t="n">
-        <v>88631000000</v>
+        <v>420489000000</v>
       </c>
       <c r="M98" t="n">
-        <v>112301000000</v>
+        <v>402053000000</v>
       </c>
       <c r="N98" t="n">
-        <v>254110156145</v>
+        <v>627197323200</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>京阪神ビルディング株式会社</t>
+          <t>株式会社髙島屋</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>8818</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>81.8</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="D99" t="n">
-        <v>1110</v>
+        <v>2140.5</v>
       </c>
       <c r="E99" t="n">
-        <v>1341.977644710579</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="F99" t="n">
-        <v>-17.3</v>
+        <v>94.3</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>9876000000</v>
+        <v>88996000000</v>
       </c>
       <c r="J99" t="n">
-        <v>54379000000</v>
+        <v>193090000000</v>
       </c>
       <c r="K99" t="n">
-        <v>22399000000</v>
+        <v>119967000000</v>
       </c>
       <c r="L99" t="n">
-        <v>70510000000</v>
+        <v>420489000000</v>
       </c>
       <c r="M99" t="n">
-        <v>86654000000</v>
+        <v>402053000000</v>
       </c>
       <c r="N99" t="n">
-        <v>105899174820</v>
+        <v>627197323200</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>株式会社メルカリ</t>
+          <t>三井倉庫ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>9302</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>29.4</v>
+        <v>43.9</v>
       </c>
       <c r="D100" t="n">
-        <v>3621</v>
+        <v>3423</v>
       </c>
       <c r="E100" t="n">
-        <v>2006.059650428343</v>
+        <v>1492.806001579363</v>
       </c>
       <c r="F100" t="n">
-        <v>80.5</v>
+        <v>129.3</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>171463000000</v>
+        <v>22822000000</v>
       </c>
       <c r="J100" t="n">
-        <v>434000000</v>
+        <v>72331000000</v>
       </c>
       <c r="K100" t="n">
-        <v>1543000000</v>
+        <v>17148000000</v>
       </c>
       <c r="L100" t="n">
-        <v>40013000000</v>
+        <v>88631000000</v>
       </c>
       <c r="M100" t="n">
-        <v>173440000000</v>
+        <v>112301000000</v>
       </c>
       <c r="N100" t="n">
-        <v>590877014157</v>
+        <v>256055067555</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>サッポロホールディングス株式会社</t>
+          <t>京阪神ビルディング株式会社</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2501</t>
+          <t>8818</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>80.2</v>
       </c>
       <c r="D101" t="n">
-        <v>1866</v>
+        <v>1133</v>
       </c>
       <c r="E101" t="n">
-        <v>2697.360927565142</v>
+        <v>1341.977644710579</v>
       </c>
       <c r="F101" t="n">
-        <v>-30.8</v>
+        <v>-15.6</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2925000000</v>
+        <v>9876000000</v>
       </c>
       <c r="J101" t="n">
-        <v>23000000</v>
+        <v>54379000000</v>
       </c>
       <c r="K101" t="n">
-        <v>4391000000</v>
+        <v>22399000000</v>
       </c>
       <c r="L101" t="n">
-        <v>142395000000</v>
+        <v>70510000000</v>
       </c>
       <c r="M101" t="n">
-        <v>7339000000</v>
+        <v>86654000000</v>
       </c>
       <c r="N101" t="n">
-        <v>727689599340</v>
+        <v>108093482046</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>株式会社クレハ</t>
+          <t>株式会社メルカリ</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>17.6</v>
+        <v>28.9</v>
       </c>
       <c r="D102" t="n">
-        <v>4440</v>
+        <v>3672</v>
       </c>
       <c r="E102" t="n">
-        <v>7960</v>
+        <v>2006.059650428343</v>
       </c>
       <c r="F102" t="n">
-        <v>-44.2</v>
+        <v>83</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>5294000000</v>
+        <v>171463000000</v>
       </c>
       <c r="J102" t="n">
-        <v>5963000000</v>
+        <v>434000000</v>
       </c>
       <c r="K102" t="n">
-        <v>18608000000</v>
+        <v>1543000000</v>
       </c>
       <c r="L102" t="n">
-        <v>155874000000</v>
+        <v>40013000000</v>
       </c>
       <c r="M102" t="n">
-        <v>29865000000</v>
+        <v>173440000000</v>
       </c>
       <c r="N102" t="n">
-        <v>169701479760</v>
+        <v>599199225624</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>コムシスホールディングス株式会社</t>
+          <t>サッポロホールディングス株式会社</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>17.6</v>
+        <v>1</v>
       </c>
       <c r="D103" t="n">
-        <v>5493</v>
+        <v>1909</v>
       </c>
       <c r="E103" t="n">
-        <v>3953.24613842911</v>
+        <v>2697.360927565142</v>
       </c>
       <c r="F103" t="n">
-        <v>38.9</v>
+        <v>-29.2</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>34033000000</v>
+        <v>2925000000</v>
       </c>
       <c r="J103" t="n">
-        <v>45394000000</v>
+        <v>23000000</v>
       </c>
       <c r="K103" t="n">
-        <v>31261000000</v>
+        <v>4391000000</v>
       </c>
       <c r="L103" t="n">
-        <v>343489000000</v>
+        <v>142395000000</v>
       </c>
       <c r="M103" t="n">
-        <v>110688000000</v>
+        <v>7339000000</v>
       </c>
       <c r="N103" t="n">
-        <v>628691158443</v>
+        <v>744458437910</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>コムシスホールディングス株式会社</t>
+          <t>株式会社クレハ</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>4023</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>17.6</v>
+        <v>18.5</v>
       </c>
       <c r="D104" t="n">
-        <v>5493</v>
+        <v>4225</v>
       </c>
       <c r="E104" t="n">
-        <v>3735.709461270437</v>
+        <v>7960</v>
       </c>
       <c r="F104" t="n">
-        <v>47</v>
+        <v>-46.9</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>34033000000</v>
+        <v>5294000000</v>
       </c>
       <c r="J104" t="n">
-        <v>45394000000</v>
+        <v>5963000000</v>
       </c>
       <c r="K104" t="n">
-        <v>31261000000</v>
+        <v>18608000000</v>
       </c>
       <c r="L104" t="n">
-        <v>343489000000</v>
+        <v>155874000000</v>
       </c>
       <c r="M104" t="n">
-        <v>110688000000</v>
+        <v>29865000000</v>
       </c>
       <c r="N104" t="n">
-        <v>628691158443</v>
+        <v>161483953150</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>サクサ株式会社</t>
+          <t>コムシスホールディングス株式会社</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>6675</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>29.4</v>
+        <v>17.1</v>
       </c>
       <c r="D105" t="n">
-        <v>2184</v>
+        <v>5648</v>
       </c>
       <c r="E105" t="n">
-        <v>5463.67048346056</v>
+        <v>3953.24613842911</v>
       </c>
       <c r="F105" t="n">
-        <v>-60</v>
+        <v>42.9</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>6993000000</v>
+        <v>34033000000</v>
       </c>
       <c r="J105" t="n">
-        <v>1323000000</v>
+        <v>45394000000</v>
       </c>
       <c r="K105" t="n">
-        <v>2933000000</v>
+        <v>31261000000</v>
       </c>
       <c r="L105" t="n">
-        <v>23497000000</v>
+        <v>343489000000</v>
       </c>
       <c r="M105" t="n">
-        <v>11249000000</v>
+        <v>110688000000</v>
       </c>
       <c r="N105" t="n">
-        <v>38201632560</v>
+        <v>646431396848</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>愛知製鋼株式会社</t>
+          <t>コムシスホールディングス株式会社</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>34.4</v>
+        <v>17.1</v>
       </c>
       <c r="D106" t="n">
-        <v>3190</v>
+        <v>5648</v>
       </c>
       <c r="E106" t="n">
-        <v>3155.301177013616</v>
+        <v>3735.709461270437</v>
       </c>
       <c r="F106" t="n">
-        <v>1.1</v>
+        <v>51.2</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>32866000000</v>
+        <v>34033000000</v>
       </c>
       <c r="J106" t="n">
-        <v>11000000000</v>
+        <v>45394000000</v>
       </c>
       <c r="K106" t="n">
-        <v>26614000000</v>
+        <v>31261000000</v>
       </c>
       <c r="L106" t="n">
-        <v>186904000000</v>
+        <v>343489000000</v>
       </c>
       <c r="M106" t="n">
-        <v>70480000000</v>
+        <v>110688000000</v>
       </c>
       <c r="N106" t="n">
-        <v>204947285620</v>
+        <v>646431396848</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>株式会社インターネットイニシアティブ</t>
+          <t>サクサ株式会社</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>3774</t>
+          <t>6675</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>5.5</v>
+        <v>29.1</v>
       </c>
       <c r="D107" t="n">
-        <v>3398</v>
+        <v>2212</v>
       </c>
       <c r="E107" t="n">
-        <v>2655.311711736394</v>
+        <v>5463.67048346056</v>
       </c>
       <c r="F107" t="n">
-        <v>28</v>
+        <v>-59.5</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>16367000000</v>
+        <v>6993000000</v>
       </c>
       <c r="J107" t="n">
-        <v>1522000000</v>
+        <v>1323000000</v>
       </c>
       <c r="K107" t="n">
-        <v>15226000000</v>
+        <v>2933000000</v>
       </c>
       <c r="L107" t="n">
-        <v>87924000000</v>
+        <v>23497000000</v>
       </c>
       <c r="M107" t="n">
-        <v>33115000000</v>
+        <v>11249000000</v>
       </c>
       <c r="N107" t="n">
-        <v>602567356990</v>
+        <v>38691397080</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>コクヨ株式会社</t>
+          <t>愛知製鋼株式会社</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>7984</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>41.1</v>
+        <v>33.5</v>
       </c>
       <c r="D108" t="n">
-        <v>897.7999877929688</v>
+        <v>3275</v>
       </c>
       <c r="E108" t="n">
-        <v>2157.626835069302</v>
+        <v>3155.301177013616</v>
       </c>
       <c r="F108" t="n">
-        <v>-58.4</v>
+        <v>3.8</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>100575000000</v>
+        <v>32866000000</v>
       </c>
       <c r="J108" t="n">
-        <v>22282000000</v>
+        <v>11000000000</v>
       </c>
       <c r="K108" t="n">
-        <v>30106000000</v>
+        <v>26614000000</v>
       </c>
       <c r="L108" t="n">
-        <v>230105000000</v>
+        <v>186904000000</v>
       </c>
       <c r="M108" t="n">
-        <v>152963000000</v>
+        <v>70480000000</v>
       </c>
       <c r="N108" t="n">
-        <v>372084290685</v>
+        <v>210408263450</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>三菱製紙株式会社</t>
+          <t>株式会社インターネットイニシアティブ</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>94.90000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="D109" t="n">
-        <v>1210</v>
+        <v>3436</v>
       </c>
       <c r="E109" t="n">
-        <v>810</v>
+        <v>2655.311711736394</v>
       </c>
       <c r="F109" t="n">
-        <v>49.4</v>
+        <v>29.4</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>9047000000</v>
+        <v>16367000000</v>
       </c>
       <c r="J109" t="n">
-        <v>16443000000</v>
+        <v>1522000000</v>
       </c>
       <c r="K109" t="n">
-        <v>24813000000</v>
+        <v>15226000000</v>
       </c>
       <c r="L109" t="n">
-        <v>69613000000</v>
+        <v>87924000000</v>
       </c>
       <c r="M109" t="n">
-        <v>50303000000</v>
+        <v>33115000000</v>
       </c>
       <c r="N109" t="n">
-        <v>53007896590</v>
+        <v>609305897180</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>株式会社プラスアルファ・コンサルティング</t>
+          <t>コクヨ株式会社</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>4071</t>
+          <t>7984</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>9.9</v>
+        <v>40.6</v>
       </c>
       <c r="D110" t="n">
-        <v>2066</v>
+        <v>909.4000244140625</v>
       </c>
       <c r="E110" t="n">
-        <v>2300.974351689521</v>
+        <v>2157.626835069302</v>
       </c>
       <c r="F110" t="n">
-        <v>-10.2</v>
+        <v>-57.9</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -6122,182 +6122,182 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>8278003000</v>
+        <v>100575000000</v>
       </c>
       <c r="J110" t="n">
-        <v>271170000</v>
+        <v>22282000000</v>
       </c>
       <c r="K110" t="n">
-        <v>0</v>
+        <v>30106000000</v>
       </c>
       <c r="L110" t="n">
-        <v>9445733000</v>
+        <v>230105000000</v>
       </c>
       <c r="M110" t="n">
-        <v>8549173000</v>
+        <v>152963000000</v>
       </c>
       <c r="N110" t="n">
-        <v>86680166300</v>
+        <v>376891810686</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>東亜道路工業株式会社</t>
+          <t>株式会社メルカリ</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>39.9</v>
+        <v>35.5</v>
       </c>
       <c r="D111" t="n">
-        <v>1602</v>
+        <v>3672</v>
       </c>
       <c r="E111" t="n">
-        <v>1180.253227905114</v>
+        <v>2006.059650428343</v>
       </c>
       <c r="F111" t="n">
-        <v>35.7</v>
+        <v>83</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>11649000000</v>
+        <v>211406000000</v>
       </c>
       <c r="J111" t="n">
-        <v>13793000000</v>
+        <v>367000000</v>
       </c>
       <c r="K111" t="n">
-        <v>4087000000</v>
+        <v>1021000000</v>
       </c>
       <c r="L111" t="n">
-        <v>50605000000</v>
+        <v>37998000000</v>
       </c>
       <c r="M111" t="n">
-        <v>29529000000</v>
+        <v>212794000000</v>
       </c>
       <c r="N111" t="n">
-        <v>74030483376</v>
+        <v>599199225624</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>東亜道路工業株式会社</t>
+          <t>三菱製紙株式会社</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>3864</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>39.9</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D112" t="n">
-        <v>1602</v>
+        <v>1220</v>
       </c>
       <c r="E112" t="n">
-        <v>1180.31326635551</v>
+        <v>810</v>
       </c>
       <c r="F112" t="n">
-        <v>35.7</v>
+        <v>50.6</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>11649000000</v>
+        <v>9047000000</v>
       </c>
       <c r="J112" t="n">
-        <v>13793000000</v>
+        <v>16443000000</v>
       </c>
       <c r="K112" t="n">
-        <v>4087000000</v>
+        <v>24813000000</v>
       </c>
       <c r="L112" t="n">
-        <v>50605000000</v>
+        <v>69613000000</v>
       </c>
       <c r="M112" t="n">
-        <v>29529000000</v>
+        <v>50303000000</v>
       </c>
       <c r="N112" t="n">
-        <v>74030483376</v>
+        <v>53445978380</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>東亜道路工業株式会社</t>
+          <t>株式会社プラスアルファ・コンサルティング</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>4071</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>39.9</v>
+        <v>9.6</v>
       </c>
       <c r="D113" t="n">
-        <v>1602</v>
+        <v>2122</v>
       </c>
       <c r="E113" t="n">
-        <v>1180.406015389293</v>
+        <v>2300.974351689521</v>
       </c>
       <c r="F113" t="n">
-        <v>35.7</v>
+        <v>-7.8</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>11649000000</v>
+        <v>8278003000</v>
       </c>
       <c r="J113" t="n">
-        <v>13793000000</v>
+        <v>271170000</v>
       </c>
       <c r="K113" t="n">
-        <v>4087000000</v>
+        <v>0</v>
       </c>
       <c r="L113" t="n">
-        <v>50605000000</v>
+        <v>9445733000</v>
       </c>
       <c r="M113" t="n">
-        <v>29529000000</v>
+        <v>8549173000</v>
       </c>
       <c r="N113" t="n">
-        <v>74030483376</v>
+        <v>89029677100</v>
       </c>
     </row>
     <row r="114">
@@ -6312,16 +6312,16 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>39.9</v>
+        <v>39.4</v>
       </c>
       <c r="D114" t="n">
-        <v>1602</v>
+        <v>1620</v>
       </c>
       <c r="E114" t="n">
-        <v>1180.420176850555</v>
+        <v>1180.253227905114</v>
       </c>
       <c r="F114" t="n">
-        <v>35.7</v>
+        <v>37.3</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="I114" t="n">
@@ -6349,7 +6349,7 @@
         <v>29529000000</v>
       </c>
       <c r="N114" t="n">
-        <v>74030483376</v>
+        <v>74856292560</v>
       </c>
     </row>
     <row r="115">
@@ -6364,16 +6364,16 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>39.9</v>
+        <v>39.4</v>
       </c>
       <c r="D115" t="n">
-        <v>1602</v>
+        <v>1620</v>
       </c>
       <c r="E115" t="n">
-        <v>1180.431728045326</v>
+        <v>1180.31326635551</v>
       </c>
       <c r="F115" t="n">
-        <v>35.7</v>
+        <v>37.3</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="I115" t="n">
@@ -6401,7 +6401,7 @@
         <v>29529000000</v>
       </c>
       <c r="N115" t="n">
-        <v>74030483376</v>
+        <v>74856292560</v>
       </c>
     </row>
     <row r="116">
@@ -6416,16 +6416,16 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>39.9</v>
+        <v>39.4</v>
       </c>
       <c r="D116" t="n">
-        <v>1602</v>
+        <v>1620</v>
       </c>
       <c r="E116" t="n">
-        <v>1180.442269658324</v>
+        <v>1180.406015389293</v>
       </c>
       <c r="F116" t="n">
-        <v>35.7</v>
+        <v>37.2</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="I116" t="n">
@@ -6453,7 +6453,7 @@
         <v>29529000000</v>
       </c>
       <c r="N116" t="n">
-        <v>74030483376</v>
+        <v>74856292560</v>
       </c>
     </row>
     <row r="117">
@@ -6468,16 +6468,16 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>39.9</v>
+        <v>39.4</v>
       </c>
       <c r="D117" t="n">
-        <v>1602</v>
+        <v>1620</v>
       </c>
       <c r="E117" t="n">
-        <v>1180.450912709519</v>
+        <v>1180.420176850555</v>
       </c>
       <c r="F117" t="n">
-        <v>35.7</v>
+        <v>37.2</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="I117" t="n">
@@ -6505,7 +6505,7 @@
         <v>29529000000</v>
       </c>
       <c r="N117" t="n">
-        <v>74030483376</v>
+        <v>74856292560</v>
       </c>
     </row>
     <row r="118">
@@ -6520,16 +6520,16 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>39.9</v>
+        <v>39.4</v>
       </c>
       <c r="D118" t="n">
-        <v>1602</v>
+        <v>1620</v>
       </c>
       <c r="E118" t="n">
-        <v>1180.45745232471</v>
+        <v>1180.431728045326</v>
       </c>
       <c r="F118" t="n">
-        <v>35.7</v>
+        <v>37.2</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="I118" t="n">
@@ -6557,7 +6557,7 @@
         <v>29529000000</v>
       </c>
       <c r="N118" t="n">
-        <v>74030483376</v>
+        <v>74856292560</v>
       </c>
     </row>
     <row r="119">
@@ -6572,16 +6572,16 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>39.9</v>
+        <v>39.4</v>
       </c>
       <c r="D119" t="n">
-        <v>1602</v>
+        <v>1620</v>
       </c>
       <c r="E119" t="n">
-        <v>1180.463123164206</v>
+        <v>1180.442269658324</v>
       </c>
       <c r="F119" t="n">
-        <v>35.7</v>
+        <v>37.2</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="I119" t="n">
@@ -6609,7 +6609,7 @@
         <v>29529000000</v>
       </c>
       <c r="N119" t="n">
-        <v>74030483376</v>
+        <v>74856292560</v>
       </c>
     </row>
     <row r="120">
@@ -6624,16 +6624,16 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>39.9</v>
+        <v>39.4</v>
       </c>
       <c r="D120" t="n">
-        <v>1602</v>
+        <v>1620</v>
       </c>
       <c r="E120" t="n">
-        <v>1170.279952698077</v>
+        <v>1180.450912709519</v>
       </c>
       <c r="F120" t="n">
-        <v>36.9</v>
+        <v>37.2</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="I120" t="n">
@@ -6661,7 +6661,7 @@
         <v>29529000000</v>
       </c>
       <c r="N120" t="n">
-        <v>74030483376</v>
+        <v>74856292560</v>
       </c>
     </row>
     <row r="121">
@@ -6676,16 +6676,16 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>39.9</v>
+        <v>39.4</v>
       </c>
       <c r="D121" t="n">
-        <v>1602</v>
+        <v>1620</v>
       </c>
       <c r="E121" t="n">
-        <v>1169.924818603025</v>
+        <v>1180.45745232471</v>
       </c>
       <c r="F121" t="n">
-        <v>36.9</v>
+        <v>37.2</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="I121" t="n">
@@ -6713,7 +6713,7 @@
         <v>29529000000</v>
       </c>
       <c r="N121" t="n">
-        <v>74030483376</v>
+        <v>74856292560</v>
       </c>
     </row>
     <row r="122">
@@ -6728,16 +6728,16 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>39.9</v>
+        <v>39.4</v>
       </c>
       <c r="D122" t="n">
-        <v>1602</v>
+        <v>1620</v>
       </c>
       <c r="E122" t="n">
-        <v>1168.709522546084</v>
+        <v>1180.463123164206</v>
       </c>
       <c r="F122" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="I122" t="n">
@@ -6765,31 +6765,31 @@
         <v>29529000000</v>
       </c>
       <c r="N122" t="n">
-        <v>74030483376</v>
+        <v>74856292560</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>山洋電気株式会社</t>
+          <t>東亜道路工業株式会社</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>11.8</v>
+        <v>39.4</v>
       </c>
       <c r="D123" t="n">
-        <v>5240</v>
+        <v>1620</v>
       </c>
       <c r="E123" t="n">
-        <v>7052.737306843267</v>
+        <v>1170.279952698077</v>
       </c>
       <c r="F123" t="n">
-        <v>-25.7</v>
+        <v>38.4</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -6798,206 +6798,206 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>8317000000</v>
+        <v>11649000000</v>
       </c>
       <c r="J123" t="n">
-        <v>6048000000</v>
+        <v>13793000000</v>
       </c>
       <c r="K123" t="n">
-        <v>7673000000</v>
+        <v>4087000000</v>
       </c>
       <c r="L123" t="n">
-        <v>49734000000</v>
+        <v>50605000000</v>
       </c>
       <c r="M123" t="n">
-        <v>22038000000</v>
+        <v>29529000000</v>
       </c>
       <c r="N123" t="n">
-        <v>186098814840</v>
+        <v>74856292560</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ヘリオス テクノ ホールディング株式会社</t>
+          <t>東亜道路工業株式会社</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>54.3</v>
+        <v>39.4</v>
       </c>
       <c r="D124" t="n">
-        <v>971</v>
+        <v>1620</v>
       </c>
       <c r="E124" t="n">
-        <v>896.0103264198827</v>
+        <v>1169.924818603025</v>
       </c>
       <c r="F124" t="n">
-        <v>8.4</v>
+        <v>38.5</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>7851015000</v>
+        <v>11649000000</v>
       </c>
       <c r="J124" t="n">
-        <v>640317000</v>
+        <v>13793000000</v>
       </c>
       <c r="K124" t="n">
-        <v>1079200000</v>
+        <v>4087000000</v>
       </c>
       <c r="L124" t="n">
-        <v>13746774000</v>
+        <v>50605000000</v>
       </c>
       <c r="M124" t="n">
-        <v>9570532000</v>
+        <v>29529000000</v>
       </c>
       <c r="N124" t="n">
-        <v>17625268657</v>
+        <v>74856292560</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>シェアリングテクノロジー株式会社</t>
+          <t>東亜道路工業株式会社</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>11.7</v>
+        <v>39.4</v>
       </c>
       <c r="D125" t="n">
-        <v>1545</v>
+        <v>1620</v>
       </c>
       <c r="E125" t="n">
-        <v>653.0713101160862</v>
+        <v>1168.709522546084</v>
       </c>
       <c r="F125" t="n">
-        <v>136.6</v>
+        <v>38.6</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>4016706000</v>
+        <v>11649000000</v>
       </c>
       <c r="J125" t="n">
-        <v>309745000</v>
+        <v>13793000000</v>
       </c>
       <c r="K125" t="n">
-        <v>0</v>
+        <v>4087000000</v>
       </c>
       <c r="L125" t="n">
-        <v>185001000</v>
+        <v>50605000000</v>
       </c>
       <c r="M125" t="n">
-        <v>4326451000</v>
+        <v>29529000000</v>
       </c>
       <c r="N125" t="n">
-        <v>36973810605</v>
+        <v>74856292560</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>栄研化学株式会社</t>
+          <t>山洋電気株式会社</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>30.5</v>
+        <v>11.8</v>
       </c>
       <c r="D126" t="n">
-        <v>2280</v>
+        <v>5260</v>
       </c>
       <c r="E126" t="n">
-        <v>1947.225264702313</v>
+        <v>7052.737306843267</v>
       </c>
       <c r="F126" t="n">
-        <v>17.1</v>
+        <v>-25.4</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>10900000000</v>
+        <v>8317000000</v>
       </c>
       <c r="J126" t="n">
-        <v>11585000000</v>
+        <v>6048000000</v>
       </c>
       <c r="K126" t="n">
-        <v>408000000</v>
+        <v>7673000000</v>
       </c>
       <c r="L126" t="n">
-        <v>45803000000</v>
+        <v>49734000000</v>
       </c>
       <c r="M126" t="n">
-        <v>22893000000</v>
+        <v>22038000000</v>
       </c>
       <c r="N126" t="n">
-        <v>75161506440</v>
+        <v>186809115660</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>栄研化学株式会社</t>
+          <t>ヘリオス テクノ ホールディング株式会社</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>30.5</v>
+        <v>54.4</v>
       </c>
       <c r="D127" t="n">
-        <v>2280</v>
+        <v>969</v>
       </c>
       <c r="E127" t="n">
-        <v>1678.083113259255</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="F127" t="n">
-        <v>35.9</v>
+        <v>8.1</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -7006,518 +7006,518 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>10900000000</v>
+        <v>7851015000</v>
       </c>
       <c r="J127" t="n">
-        <v>11585000000</v>
+        <v>640317000</v>
       </c>
       <c r="K127" t="n">
-        <v>408000000</v>
+        <v>1079200000</v>
       </c>
       <c r="L127" t="n">
-        <v>45803000000</v>
+        <v>13746774000</v>
       </c>
       <c r="M127" t="n">
-        <v>22893000000</v>
+        <v>9570532000</v>
       </c>
       <c r="N127" t="n">
-        <v>75161506440</v>
+        <v>17588965323</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>株式会社ヤマダホールディングス</t>
+          <t>シェアリングテクノロジー株式会社</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>9831</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>58</v>
+        <v>11.7</v>
       </c>
       <c r="D128" t="n">
-        <v>718.4000244140625</v>
+        <v>1545</v>
       </c>
       <c r="E128" t="n">
-        <v>530</v>
+        <v>653.0713101160862</v>
       </c>
       <c r="F128" t="n">
-        <v>35.5</v>
+        <v>136.6</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>56470000000</v>
+        <v>4016706000</v>
       </c>
       <c r="J128" t="n">
-        <v>210733000000</v>
+        <v>309745000</v>
       </c>
       <c r="K128" t="n">
-        <v>9997000000</v>
+        <v>0</v>
       </c>
       <c r="L128" t="n">
-        <v>676277000000</v>
+        <v>185001000</v>
       </c>
       <c r="M128" t="n">
-        <v>277200000000</v>
+        <v>4326451000</v>
       </c>
       <c r="N128" t="n">
-        <v>477718367302</v>
+        <v>36973810605</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>日本化薬株式会社</t>
+          <t>栄研化学株式会社</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>34.9</v>
+        <v>29.4</v>
       </c>
       <c r="D129" t="n">
-        <v>2098.5</v>
+        <v>2361</v>
       </c>
       <c r="E129" t="n">
-        <v>1111.90611839092</v>
+        <v>1947.225264702313</v>
       </c>
       <c r="F129" t="n">
-        <v>88.7</v>
+        <v>21.2</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>52962000000</v>
+        <v>10900000000</v>
       </c>
       <c r="J129" t="n">
-        <v>48231000000</v>
+        <v>11585000000</v>
       </c>
       <c r="K129" t="n">
-        <v>4337000000</v>
+        <v>408000000</v>
       </c>
       <c r="L129" t="n">
-        <v>246425000000</v>
+        <v>45803000000</v>
       </c>
       <c r="M129" t="n">
-        <v>105530000000</v>
+        <v>22893000000</v>
       </c>
       <c r="N129" t="n">
-        <v>302579334316</v>
+        <v>77831717853</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>王子ホールディングス株式会社</t>
+          <t>栄研化学株式会社</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>41.5</v>
+        <v>29.4</v>
       </c>
       <c r="D130" t="n">
-        <v>872.5999755859375</v>
+        <v>2361</v>
       </c>
       <c r="E130" t="n">
-        <v>590</v>
+        <v>1678.083113259255</v>
       </c>
       <c r="F130" t="n">
-        <v>47.9</v>
+        <v>40.7</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>55474000000</v>
+        <v>10900000000</v>
       </c>
       <c r="J130" t="n">
-        <v>244732000000</v>
+        <v>11585000000</v>
       </c>
       <c r="K130" t="n">
-        <v>7434000000</v>
+        <v>408000000</v>
       </c>
       <c r="L130" t="n">
-        <v>875470000000</v>
+        <v>45803000000</v>
       </c>
       <c r="M130" t="n">
-        <v>307640000000</v>
+        <v>22893000000</v>
       </c>
       <c r="N130" t="n">
-        <v>741041823339</v>
+        <v>77831717853</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>東邦ホールディングス株式会社</t>
+          <t>株式会社ヤマダホールディングス</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>9831</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>50.8</v>
+        <v>57.5</v>
       </c>
       <c r="D131" t="n">
-        <v>3989</v>
+        <v>724.7999877929688</v>
       </c>
       <c r="E131" t="n">
-        <v>3405.914389596362</v>
+        <v>530</v>
       </c>
       <c r="F131" t="n">
-        <v>17.1</v>
+        <v>36.8</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>90014000000</v>
+        <v>56470000000</v>
       </c>
       <c r="J131" t="n">
-        <v>34220000000</v>
+        <v>210733000000</v>
       </c>
       <c r="K131" t="n">
-        <v>7000000000</v>
+        <v>9997000000</v>
       </c>
       <c r="L131" t="n">
-        <v>241281000000</v>
+        <v>676277000000</v>
       </c>
       <c r="M131" t="n">
-        <v>131234000000</v>
+        <v>277200000000</v>
       </c>
       <c r="N131" t="n">
-        <v>258094774147</v>
+        <v>481974185721</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>東邦ホールディングス株式会社</t>
+          <t>日本化薬株式会社</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>50.8</v>
+        <v>34.6</v>
       </c>
       <c r="D132" t="n">
-        <v>3989</v>
+        <v>2115</v>
       </c>
       <c r="E132" t="n">
-        <v>2714.613787300615</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="F132" t="n">
-        <v>46.9</v>
+        <v>90.2</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>90014000000</v>
+        <v>52962000000</v>
       </c>
       <c r="J132" t="n">
-        <v>34220000000</v>
+        <v>48231000000</v>
       </c>
       <c r="K132" t="n">
-        <v>7000000000</v>
+        <v>4337000000</v>
       </c>
       <c r="L132" t="n">
-        <v>241281000000</v>
+        <v>246425000000</v>
       </c>
       <c r="M132" t="n">
-        <v>131234000000</v>
+        <v>105530000000</v>
       </c>
       <c r="N132" t="n">
-        <v>258094774147</v>
+        <v>304958442735</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>株式会社アイネス</t>
+          <t>王子ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>9742</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>34.2</v>
+        <v>40.8</v>
       </c>
       <c r="D133" t="n">
-        <v>2121</v>
+        <v>888.9000244140625</v>
       </c>
       <c r="E133" t="n">
-        <v>1879.137815927515</v>
+        <v>590</v>
       </c>
       <c r="F133" t="n">
-        <v>12.9</v>
+        <v>50.7</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>9731000000</v>
+        <v>55474000000</v>
       </c>
       <c r="J133" t="n">
-        <v>5286000000</v>
+        <v>244732000000</v>
       </c>
       <c r="K133" t="n">
-        <v>100000000</v>
+        <v>7434000000</v>
       </c>
       <c r="L133" t="n">
-        <v>34620000000</v>
+        <v>875470000000</v>
       </c>
       <c r="M133" t="n">
-        <v>15117000000</v>
+        <v>307640000000</v>
       </c>
       <c r="N133" t="n">
-        <v>44164410087</v>
+        <v>754884383781</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>日本ゼオン株式会社</t>
+          <t>東邦ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>35.3</v>
+        <v>50.1</v>
       </c>
       <c r="D134" t="n">
-        <v>2388</v>
+        <v>4048</v>
       </c>
       <c r="E134" t="n">
-        <v>1721.078563209627</v>
+        <v>3405.914389596362</v>
       </c>
       <c r="F134" t="n">
-        <v>38.8</v>
+        <v>18.9</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>44521000000</v>
+        <v>90014000000</v>
       </c>
       <c r="J134" t="n">
-        <v>45382000000</v>
+        <v>34220000000</v>
       </c>
       <c r="K134" t="n">
-        <v>71191000000</v>
+        <v>7000000000</v>
       </c>
       <c r="L134" t="n">
-        <v>321836000000</v>
+        <v>241281000000</v>
       </c>
       <c r="M134" t="n">
-        <v>161094000000</v>
+        <v>131234000000</v>
       </c>
       <c r="N134" t="n">
-        <v>456933070716</v>
+        <v>261912169904</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>太陽ホールディングス株式会社</t>
+          <t>東邦ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>16.4</v>
+        <v>50.1</v>
       </c>
       <c r="D135" t="n">
-        <v>4730</v>
+        <v>4048</v>
       </c>
       <c r="E135" t="n">
-        <v>2199.643244598912</v>
+        <v>2714.613787300615</v>
       </c>
       <c r="F135" t="n">
-        <v>115</v>
+        <v>49.1</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>51152000000</v>
+        <v>90014000000</v>
       </c>
       <c r="J135" t="n">
-        <v>30337000000</v>
+        <v>34220000000</v>
       </c>
       <c r="K135" t="n">
-        <v>4870000000</v>
+        <v>7000000000</v>
       </c>
       <c r="L135" t="n">
-        <v>85466000000</v>
+        <v>241281000000</v>
       </c>
       <c r="M135" t="n">
-        <v>86359000000</v>
+        <v>131234000000</v>
       </c>
       <c r="N135" t="n">
-        <v>526338705860</v>
+        <v>261912169904</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>太陽ホールディングス株式会社</t>
+          <t>株式会社アイネス</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>9742</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>16.4</v>
+        <v>33.8</v>
       </c>
       <c r="D136" t="n">
-        <v>4730</v>
+        <v>2145</v>
       </c>
       <c r="E136" t="n">
-        <v>3565.648720929983</v>
+        <v>1879.137815927515</v>
       </c>
       <c r="F136" t="n">
-        <v>32.7</v>
+        <v>14.1</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>51152000000</v>
+        <v>9731000000</v>
       </c>
       <c r="J136" t="n">
-        <v>30337000000</v>
+        <v>5286000000</v>
       </c>
       <c r="K136" t="n">
-        <v>4870000000</v>
+        <v>100000000</v>
       </c>
       <c r="L136" t="n">
-        <v>85466000000</v>
+        <v>34620000000</v>
       </c>
       <c r="M136" t="n">
-        <v>86359000000</v>
+        <v>15117000000</v>
       </c>
       <c r="N136" t="n">
-        <v>526338705860</v>
+        <v>44664148815</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>株式会社エス・エム・エス</t>
+          <t>日本ゼオン株式会社</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>8.4</v>
+        <v>34.9</v>
       </c>
       <c r="D137" t="n">
-        <v>2652</v>
+        <v>2409.5</v>
       </c>
       <c r="E137" t="n">
-        <v>1478.127248828989</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="F137" t="n">
-        <v>79.40000000000001</v>
+        <v>40</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -7526,102 +7526,102 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>14126000000</v>
+        <v>44521000000</v>
       </c>
       <c r="J137" t="n">
-        <v>1187000000</v>
+        <v>45382000000</v>
       </c>
       <c r="K137" t="n">
-        <v>2875000000</v>
+        <v>71191000000</v>
       </c>
       <c r="L137" t="n">
-        <v>29991000000</v>
+        <v>321836000000</v>
       </c>
       <c r="M137" t="n">
-        <v>18188000000</v>
+        <v>161094000000</v>
       </c>
       <c r="N137" t="n">
-        <v>217677350748</v>
+        <v>461046999116</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>アニコム ホールディングス株式会社</t>
+          <t>太陽ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>8715</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>41</v>
+        <v>16.4</v>
       </c>
       <c r="D138" t="n">
-        <v>1030</v>
+        <v>4730</v>
       </c>
       <c r="E138" t="n">
-        <v>656.2604975855553</v>
+        <v>2199.643244598912</v>
       </c>
       <c r="F138" t="n">
-        <v>56.9</v>
+        <v>115</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>27691000000</v>
+        <v>51152000000</v>
       </c>
       <c r="J138" t="n">
-        <v>3070000000</v>
+        <v>30337000000</v>
       </c>
       <c r="K138" t="n">
-        <v>3000000</v>
+        <v>4870000000</v>
       </c>
       <c r="L138" t="n">
-        <v>27316000000</v>
+        <v>85466000000</v>
       </c>
       <c r="M138" t="n">
-        <v>30764000000</v>
+        <v>86359000000</v>
       </c>
       <c r="N138" t="n">
-        <v>75005856600</v>
+        <v>526338705860</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>東京製鐵株式会社</t>
+          <t>太陽ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>98.5</v>
+        <v>16.4</v>
       </c>
       <c r="D139" t="n">
-        <v>1766</v>
+        <v>4730</v>
       </c>
       <c r="E139" t="n">
-        <v>1605.452212379354</v>
+        <v>3565.648720929983</v>
       </c>
       <c r="F139" t="n">
-        <v>10</v>
+        <v>32.7</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -7630,199 +7630,201 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>68644000000</v>
+        <v>51152000000</v>
       </c>
       <c r="J139" t="n">
-        <v>33060000000</v>
+        <v>30337000000</v>
       </c>
       <c r="K139" t="n">
-        <v>75000000000</v>
+        <v>4870000000</v>
       </c>
       <c r="L139" t="n">
-        <v>158280000000</v>
+        <v>85466000000</v>
       </c>
       <c r="M139" t="n">
-        <v>176704000000</v>
+        <v>86359000000</v>
       </c>
       <c r="N139" t="n">
-        <v>179418785006</v>
+        <v>526338705860</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ウェーブロックホールディングス株式会社</t>
+          <t>株式会社エス・エム・エス</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>7940</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr"/>
-      <c r="D140" t="inlineStr"/>
+          <t>2175</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="D140" t="n">
+        <v>2676</v>
+      </c>
       <c r="E140" t="n">
-        <v>1010</v>
-      </c>
-      <c r="F140" t="inlineStr"/>
+        <v>1478.127248828989</v>
+      </c>
+      <c r="F140" t="n">
+        <v>81</v>
+      </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1961626000</v>
+        <v>14126000000</v>
       </c>
       <c r="J140" t="n">
-        <v>2544946000</v>
+        <v>1187000000</v>
       </c>
       <c r="K140" t="n">
-        <v>1068366000</v>
+        <v>2875000000</v>
       </c>
       <c r="L140" t="n">
-        <v>13761535000</v>
+        <v>29991000000</v>
       </c>
       <c r="M140" t="n">
-        <v>5574938000</v>
-      </c>
-      <c r="N140" t="inlineStr"/>
+        <v>18188000000</v>
+      </c>
+      <c r="N140" t="n">
+        <v>219647281524</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>近畿車輛株式会社</t>
+          <t>アニコム ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>7122</t>
+          <t>8715</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>107.8</v>
+        <v>40.2</v>
       </c>
       <c r="D141" t="n">
-        <v>2395</v>
+        <v>1052</v>
       </c>
       <c r="E141" t="n">
-        <v>2144.894901144641</v>
+        <v>656.2604975855553</v>
       </c>
       <c r="F141" t="n">
-        <v>11.7</v>
+        <v>60.3</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>6847000000</v>
+        <v>27691000000</v>
       </c>
       <c r="J141" t="n">
-        <v>4580000000</v>
+        <v>3070000000</v>
       </c>
       <c r="K141" t="n">
-        <v>6329000000</v>
+        <v>3000000</v>
       </c>
       <c r="L141" t="n">
-        <v>24474000000</v>
+        <v>27316000000</v>
       </c>
       <c r="M141" t="n">
-        <v>17756000000</v>
+        <v>30764000000</v>
       </c>
       <c r="N141" t="n">
-        <v>16477793995</v>
+        <v>76607923440</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>株式会社三陽商会</t>
+          <t>東京製鐵株式会社</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>5423</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>64.5</v>
+        <v>96.8</v>
       </c>
       <c r="D142" t="n">
-        <v>1350</v>
+        <v>1797</v>
       </c>
       <c r="E142" t="n">
-        <v>3321.975331035734</v>
+        <v>1605.452212379354</v>
       </c>
       <c r="F142" t="n">
-        <v>-59.4</v>
+        <v>11.9</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>16287000000</v>
+        <v>68644000000</v>
       </c>
       <c r="J142" t="n">
-        <v>3021000000</v>
+        <v>33060000000</v>
       </c>
       <c r="K142" t="n">
-        <v>6298000000</v>
+        <v>75000000000</v>
       </c>
       <c r="L142" t="n">
-        <v>33920000000</v>
+        <v>158280000000</v>
       </c>
       <c r="M142" t="n">
-        <v>25606000000</v>
+        <v>176704000000</v>
       </c>
       <c r="N142" t="n">
-        <v>39671143200</v>
+        <v>182568265377</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>月島ホールディングス株式会社</t>
+          <t>ウェーブロックホールディングス株式会社</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>6332</t>
-        </is>
-      </c>
-      <c r="C143" t="n">
-        <v>48.1</v>
-      </c>
-      <c r="D143" t="n">
-        <v>2680</v>
-      </c>
+          <t>7940</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr"/>
       <c r="E143" t="n">
-        <v>1410</v>
-      </c>
-      <c r="F143" t="n">
-        <v>90.09999999999999</v>
-      </c>
+        <v>1010</v>
+      </c>
+      <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
           <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
@@ -7830,50 +7832,48 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>28795000000</v>
+        <v>1961626000</v>
       </c>
       <c r="J143" t="n">
-        <v>22203000000</v>
+        <v>2544946000</v>
       </c>
       <c r="K143" t="n">
-        <v>100000000</v>
+        <v>1068366000</v>
       </c>
       <c r="L143" t="n">
-        <v>80949000000</v>
+        <v>13761535000</v>
       </c>
       <c r="M143" t="n">
-        <v>51098000000</v>
-      </c>
-      <c r="N143" t="n">
-        <v>106131277640</v>
-      </c>
+        <v>5574938000</v>
+      </c>
+      <c r="N143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>マネックスグループ株式会社</t>
+          <t>近畿車輛株式会社</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>8698</t>
+          <t>7122</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>15.4</v>
+        <v>105.4</v>
       </c>
       <c r="D144" t="n">
-        <v>713</v>
+        <v>2449</v>
       </c>
       <c r="E144" t="n">
-        <v>510.1850530906719</v>
+        <v>2144.894901144641</v>
       </c>
       <c r="F144" t="n">
-        <v>39.8</v>
+        <v>14.2</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -7882,102 +7882,102 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>17794000000</v>
+        <v>6847000000</v>
       </c>
       <c r="J144" t="n">
-        <v>412000000</v>
+        <v>4580000000</v>
       </c>
       <c r="K144" t="n">
-        <v>9312000000</v>
+        <v>6329000000</v>
       </c>
       <c r="L144" t="n">
-        <v>98001000000</v>
+        <v>24474000000</v>
       </c>
       <c r="M144" t="n">
-        <v>27518000000</v>
+        <v>17756000000</v>
       </c>
       <c r="N144" t="n">
-        <v>179222306692</v>
+        <v>16849318369</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>株式会社あおぞら銀行</t>
+          <t>株式会社三陽商会</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>8011</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>223.3</v>
+        <v>63.7</v>
       </c>
       <c r="D145" t="n">
-        <v>3508</v>
+        <v>1368</v>
       </c>
       <c r="E145" t="n">
-        <v>2190</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="F145" t="n">
-        <v>60.2</v>
+        <v>-58.8</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1061743000000</v>
+        <v>16287000000</v>
       </c>
       <c r="J145" t="n">
-        <v>22385000000</v>
+        <v>3021000000</v>
       </c>
       <c r="K145" t="n">
-        <v>0</v>
+        <v>6298000000</v>
       </c>
       <c r="L145" t="n">
-        <v>487265000000</v>
+        <v>33920000000</v>
       </c>
       <c r="M145" t="n">
-        <v>1084128000000</v>
+        <v>25606000000</v>
       </c>
       <c r="N145" t="n">
-        <v>485440982992</v>
+        <v>40200091776</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>日本製紙株式会社</t>
+          <t>月島ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>301.9</v>
+        <v>47.3</v>
       </c>
       <c r="D146" t="n">
-        <v>1324</v>
+        <v>2730</v>
       </c>
       <c r="E146" t="n">
-        <v>1250</v>
+        <v>1410</v>
       </c>
       <c r="F146" t="n">
-        <v>5.9</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -7986,50 +7986,50 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>136216000000</v>
+        <v>28795000000</v>
       </c>
       <c r="J146" t="n">
-        <v>151771000000</v>
+        <v>22203000000</v>
       </c>
       <c r="K146" t="n">
-        <v>172984000000</v>
+        <v>100000000</v>
       </c>
       <c r="L146" t="n">
-        <v>438604000000</v>
+        <v>80949000000</v>
       </c>
       <c r="M146" t="n">
-        <v>460971000000</v>
+        <v>51098000000</v>
       </c>
       <c r="N146" t="n">
-        <v>152668457972</v>
+        <v>108111338790</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>カルビー株式会社</t>
+          <t>マネックスグループ株式会社</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>8698</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>33.4</v>
+        <v>15.4</v>
       </c>
       <c r="D147" t="n">
-        <v>3030</v>
+        <v>713</v>
       </c>
       <c r="E147" t="n">
-        <v>2919.137515755844</v>
+        <v>510.1850530906719</v>
       </c>
       <c r="F147" t="n">
-        <v>3.8</v>
+        <v>39.8</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -8038,50 +8038,50 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>49670000000</v>
+        <v>17794000000</v>
       </c>
       <c r="J147" t="n">
-        <v>70285000000</v>
+        <v>412000000</v>
       </c>
       <c r="K147" t="n">
-        <v>3263000000</v>
+        <v>9312000000</v>
       </c>
       <c r="L147" t="n">
-        <v>183458000000</v>
+        <v>98001000000</v>
       </c>
       <c r="M147" t="n">
-        <v>123218000000</v>
+        <v>27518000000</v>
       </c>
       <c r="N147" t="n">
-        <v>368411197620</v>
+        <v>179222306692</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ＮＩＴＴＯＫＵ株式会社</t>
+          <t>株式会社あおぞら銀行</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>48.7</v>
+        <v>222.3</v>
       </c>
       <c r="D148" t="n">
-        <v>2563</v>
+        <v>3524</v>
       </c>
       <c r="E148" t="n">
-        <v>1710</v>
+        <v>2190</v>
       </c>
       <c r="F148" t="n">
-        <v>49.9</v>
+        <v>60.9</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -8090,50 +8090,50 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>11768000000</v>
+        <v>1061743000000</v>
       </c>
       <c r="J148" t="n">
-        <v>6299000000</v>
+        <v>22385000000</v>
       </c>
       <c r="K148" t="n">
-        <v>2999000000</v>
+        <v>0</v>
       </c>
       <c r="L148" t="n">
-        <v>33919000000</v>
+        <v>487265000000</v>
       </c>
       <c r="M148" t="n">
-        <v>21066000000</v>
+        <v>1084128000000</v>
       </c>
       <c r="N148" t="n">
-        <v>43249297366</v>
+        <v>487654911824</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ＮＩＴＴＯＫＵ株式会社</t>
+          <t>日本製紙株式会社</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>48.7</v>
+        <v>299.7</v>
       </c>
       <c r="D149" t="n">
-        <v>2563</v>
+        <v>1334</v>
       </c>
       <c r="E149" t="n">
-        <v>1710</v>
+        <v>1250</v>
       </c>
       <c r="F149" t="n">
-        <v>49.9</v>
+        <v>6.7</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -8142,102 +8142,102 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>11768000000</v>
+        <v>136216000000</v>
       </c>
       <c r="J149" t="n">
-        <v>6299000000</v>
+        <v>151771000000</v>
       </c>
       <c r="K149" t="n">
-        <v>2999000000</v>
+        <v>172984000000</v>
       </c>
       <c r="L149" t="n">
-        <v>33919000000</v>
+        <v>438604000000</v>
       </c>
       <c r="M149" t="n">
-        <v>21066000000</v>
+        <v>460971000000</v>
       </c>
       <c r="N149" t="n">
-        <v>43249297366</v>
+        <v>153821543002</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>新光商事株式会社</t>
+          <t>カルビー株式会社</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>8141</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>30.8</v>
+        <v>32.9</v>
       </c>
       <c r="D150" t="n">
-        <v>1566</v>
+        <v>3076</v>
       </c>
       <c r="E150" t="n">
-        <v>930</v>
+        <v>2919.137515755844</v>
       </c>
       <c r="F150" t="n">
-        <v>68.40000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>10579000000</v>
+        <v>49670000000</v>
       </c>
       <c r="J150" t="n">
-        <v>195000000</v>
+        <v>70285000000</v>
       </c>
       <c r="K150" t="n">
-        <v>2995000000</v>
+        <v>3263000000</v>
       </c>
       <c r="L150" t="n">
-        <v>51945000000</v>
+        <v>183458000000</v>
       </c>
       <c r="M150" t="n">
-        <v>13769000000</v>
+        <v>123218000000</v>
       </c>
       <c r="N150" t="n">
-        <v>44709141834</v>
+        <v>374004238904</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>株式会社メガチップス</t>
+          <t>ＮＩＴＴＯＫＵ株式会社</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>6875</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>88.7</v>
+        <v>47.7</v>
       </c>
       <c r="D151" t="n">
-        <v>10590</v>
+        <v>2618</v>
       </c>
       <c r="E151" t="n">
-        <v>4870</v>
+        <v>1710</v>
       </c>
       <c r="F151" t="n">
-        <v>117.5</v>
+        <v>53.1</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -8246,102 +8246,102 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>25769446000</v>
+        <v>11768000000</v>
       </c>
       <c r="J151" t="n">
-        <v>2249411000</v>
+        <v>6299000000</v>
       </c>
       <c r="K151" t="n">
-        <v>101636005000</v>
+        <v>2999000000</v>
       </c>
       <c r="L151" t="n">
-        <v>67428618000</v>
+        <v>33919000000</v>
       </c>
       <c r="M151" t="n">
-        <v>129654862000</v>
+        <v>21066000000</v>
       </c>
       <c r="N151" t="n">
-        <v>146151541590</v>
+        <v>44177393876</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>株式会社青山財産ネットワークス</t>
+          <t>ＮＩＴＴＯＫＵ株式会社</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>8929</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>42.8</v>
+        <v>47.7</v>
       </c>
       <c r="D152" t="n">
-        <v>1356</v>
+        <v>2618</v>
       </c>
       <c r="E152" t="n">
-        <v>1347.74653160027</v>
+        <v>1710</v>
       </c>
       <c r="F152" t="n">
-        <v>0.6</v>
+        <v>53.1</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>10862000000</v>
+        <v>11768000000</v>
       </c>
       <c r="J152" t="n">
-        <v>245000000</v>
+        <v>6299000000</v>
       </c>
       <c r="K152" t="n">
-        <v>2845000000</v>
+        <v>2999000000</v>
       </c>
       <c r="L152" t="n">
-        <v>7128000000</v>
+        <v>33919000000</v>
       </c>
       <c r="M152" t="n">
-        <v>13952000000</v>
+        <v>21066000000</v>
       </c>
       <c r="N152" t="n">
-        <v>32632462728</v>
+        <v>44177393876</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>平和不動産株式会社</t>
+          <t>新光商事株式会社</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>8803</t>
+          <t>8141</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>72.90000000000001</v>
+        <v>30.8</v>
       </c>
       <c r="D153" t="n">
-        <v>2355</v>
+        <v>1568</v>
       </c>
       <c r="E153" t="n">
-        <v>3610</v>
+        <v>930</v>
       </c>
       <c r="F153" t="n">
-        <v>-34.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -8350,206 +8350,206 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>28111000000</v>
+        <v>10579000000</v>
       </c>
       <c r="J153" t="n">
-        <v>79319000000</v>
+        <v>195000000</v>
       </c>
       <c r="K153" t="n">
-        <v>5997000000</v>
+        <v>2995000000</v>
       </c>
       <c r="L153" t="n">
-        <v>119278000000</v>
+        <v>51945000000</v>
       </c>
       <c r="M153" t="n">
-        <v>113427000000</v>
+        <v>13769000000</v>
       </c>
       <c r="N153" t="n">
-        <v>155595457590</v>
+        <v>44766241632</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>小林製薬株式会社</t>
+          <t>株式会社メガチップス</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>30</v>
+        <v>87.5</v>
       </c>
       <c r="D154" t="n">
-        <v>5797</v>
+        <v>10740</v>
       </c>
       <c r="E154" t="n">
-        <v>2148.936934940886</v>
+        <v>4870</v>
       </c>
       <c r="F154" t="n">
-        <v>169.8</v>
+        <v>120.5</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>81987000000</v>
+        <v>25769446000</v>
       </c>
       <c r="J154" t="n">
-        <v>32461000000</v>
+        <v>2249411000</v>
       </c>
       <c r="K154" t="n">
-        <v>14872000000</v>
+        <v>101636005000</v>
       </c>
       <c r="L154" t="n">
-        <v>195600000000</v>
+        <v>67428618000</v>
       </c>
       <c r="M154" t="n">
-        <v>129320000000</v>
+        <v>129654862000</v>
       </c>
       <c r="N154" t="n">
-        <v>430940985937</v>
+        <v>148221676740</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>小林製薬株式会社</t>
+          <t>株式会社青山財産ネットワークス</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>8929</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>30</v>
+        <v>41.9</v>
       </c>
       <c r="D155" t="n">
-        <v>5797</v>
+        <v>1384</v>
       </c>
       <c r="E155" t="n">
-        <v>5066.092575838703</v>
+        <v>1347.74653160027</v>
       </c>
       <c r="F155" t="n">
-        <v>14.4</v>
+        <v>2.7</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="I155" t="n">
-        <v>81987000000</v>
+        <v>10862000000</v>
       </c>
       <c r="J155" t="n">
-        <v>32461000000</v>
+        <v>245000000</v>
       </c>
       <c r="K155" t="n">
-        <v>14872000000</v>
+        <v>2845000000</v>
       </c>
       <c r="L155" t="n">
-        <v>195600000000</v>
+        <v>7128000000</v>
       </c>
       <c r="M155" t="n">
-        <v>129320000000</v>
+        <v>13952000000</v>
       </c>
       <c r="N155" t="n">
-        <v>430940985937</v>
+        <v>33306289392</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>セーレン株式会社</t>
+          <t>平和不動産株式会社</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>3569</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>36.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D156" t="n">
-        <v>3265</v>
+        <v>2388</v>
       </c>
       <c r="E156" t="n">
-        <v>1359.655069733296</v>
+        <v>3610</v>
       </c>
       <c r="F156" t="n">
-        <v>140.1</v>
+        <v>-33.9</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="I156" t="n">
-        <v>35451000000</v>
+        <v>28111000000</v>
       </c>
       <c r="J156" t="n">
-        <v>25813000000</v>
+        <v>79319000000</v>
       </c>
       <c r="K156" t="n">
-        <v>8891000000</v>
+        <v>5997000000</v>
       </c>
       <c r="L156" t="n">
-        <v>91845000000</v>
+        <v>119278000000</v>
       </c>
       <c r="M156" t="n">
-        <v>70155000000</v>
+        <v>113427000000</v>
       </c>
       <c r="N156" t="n">
-        <v>190543574865</v>
+        <v>157775776104</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>データセクション株式会社</t>
+          <t>小林製薬株式会社</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>2.7</v>
+        <v>29.7</v>
       </c>
       <c r="D157" t="n">
-        <v>1446</v>
+        <v>5862</v>
       </c>
       <c r="E157" t="n">
-        <v>5143.276404494382</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="F157" t="n">
-        <v>-71.90000000000001</v>
+        <v>172.8</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -8558,362 +8558,362 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1420430000</v>
+        <v>81987000000</v>
       </c>
       <c r="J157" t="n">
-        <v>1162000</v>
+        <v>32461000000</v>
       </c>
       <c r="K157" t="n">
-        <v>49326000</v>
+        <v>14872000000</v>
       </c>
       <c r="L157" t="n">
-        <v>2818110000</v>
+        <v>195600000000</v>
       </c>
       <c r="M157" t="n">
-        <v>1470918000</v>
+        <v>129320000000</v>
       </c>
       <c r="N157" t="n">
-        <v>54170494476</v>
+        <v>435772996302</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>愛眼株式会社</t>
+          <t>小林製薬株式会社</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>9854</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>70.2</v>
+        <v>29.7</v>
       </c>
       <c r="D158" t="n">
-        <v>283</v>
+        <v>5862</v>
       </c>
       <c r="E158" t="n">
-        <v>246.9708756284982</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="F158" t="n">
-        <v>14.6</v>
+        <v>15.7</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2219000000</v>
+        <v>81987000000</v>
       </c>
       <c r="J158" t="n">
-        <v>1030000000</v>
+        <v>32461000000</v>
       </c>
       <c r="K158" t="n">
-        <v>604000000</v>
+        <v>14872000000</v>
       </c>
       <c r="L158" t="n">
-        <v>12920000000</v>
+        <v>195600000000</v>
       </c>
       <c r="M158" t="n">
-        <v>3853000000</v>
+        <v>129320000000</v>
       </c>
       <c r="N158" t="n">
-        <v>5492100345</v>
+        <v>435772996302</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>株式会社アシロ</t>
+          <t>セーレン株式会社</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>3569</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>14.2</v>
+        <v>36.6</v>
       </c>
       <c r="D159" t="n">
-        <v>1530</v>
+        <v>3285</v>
       </c>
       <c r="E159" t="n">
-        <v>1396.628697042366</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="F159" t="n">
-        <v>9.5</v>
+        <v>141.6</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1428281000</v>
+        <v>35451000000</v>
       </c>
       <c r="J159" t="n">
-        <v>102238000</v>
+        <v>25813000000</v>
       </c>
       <c r="K159" t="n">
-        <v>0</v>
+        <v>8891000000</v>
       </c>
       <c r="L159" t="n">
-        <v>1804458000</v>
+        <v>91845000000</v>
       </c>
       <c r="M159" t="n">
-        <v>1530519000</v>
+        <v>70155000000</v>
       </c>
       <c r="N159" t="n">
-        <v>10758328110</v>
+        <v>191710763685</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>三浦工業株式会社</t>
+          <t>データセクション株式会社</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>11.6</v>
+        <v>2.7</v>
       </c>
       <c r="D160" t="n">
-        <v>3128</v>
+        <v>1438</v>
       </c>
       <c r="E160" t="n">
-        <v>3147.518794622453</v>
+        <v>5143.276404494382</v>
       </c>
       <c r="F160" t="n">
-        <v>-0.6</v>
+        <v>-72</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>20794000000</v>
+        <v>1420430000</v>
       </c>
       <c r="J160" t="n">
-        <v>10600000000</v>
+        <v>1162000</v>
       </c>
       <c r="K160" t="n">
-        <v>10773000000</v>
+        <v>49326000</v>
       </c>
       <c r="L160" t="n">
-        <v>138378000000</v>
+        <v>2818110000</v>
       </c>
       <c r="M160" t="n">
-        <v>42167000000</v>
+        <v>1470918000</v>
       </c>
       <c r="N160" t="n">
-        <v>362063998080</v>
+        <v>53870796028</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>株式会社カカクコム</t>
+          <t>愛眼株式会社</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>6.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="D161" t="n">
-        <v>3820</v>
+        <v>278</v>
       </c>
       <c r="E161" t="n">
-        <v>2318.314890576102</v>
+        <v>246.9708756284982</v>
       </c>
       <c r="F161" t="n">
-        <v>64.8</v>
+        <v>12.6</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="I161" t="n">
-        <v>46452000000</v>
+        <v>2219000000</v>
       </c>
       <c r="J161" t="n">
-        <v>68000000</v>
+        <v>1030000000</v>
       </c>
       <c r="K161" t="n">
-        <v>4669000000</v>
+        <v>604000000</v>
       </c>
       <c r="L161" t="n">
-        <v>45479000000</v>
+        <v>12920000000</v>
       </c>
       <c r="M161" t="n">
-        <v>51189000000</v>
+        <v>3853000000</v>
       </c>
       <c r="N161" t="n">
-        <v>755734539940</v>
+        <v>5395066770</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>古河機械金属株式会社</t>
+          <t>株式会社アシロ</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>7378</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>46.8</v>
+        <v>13.9</v>
       </c>
       <c r="D162" t="n">
-        <v>4070</v>
+        <v>1565</v>
       </c>
       <c r="E162" t="n">
-        <v>1600</v>
+        <v>1396.628697042366</v>
       </c>
       <c r="F162" t="n">
-        <v>154.4</v>
+        <v>12.1</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="I162" t="n">
-        <v>14468000000</v>
+        <v>1428281000</v>
       </c>
       <c r="J162" t="n">
-        <v>26121000000</v>
+        <v>102238000</v>
       </c>
       <c r="K162" t="n">
-        <v>19903000000</v>
+        <v>0</v>
       </c>
       <c r="L162" t="n">
-        <v>100075000000</v>
+        <v>1804458000</v>
       </c>
       <c r="M162" t="n">
-        <v>60492000000</v>
+        <v>1530519000</v>
       </c>
       <c r="N162" t="n">
-        <v>129304376190</v>
+        <v>11004433655</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>多木化学株式会社</t>
+          <t>三浦工業株式会社</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>4025</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>30.7</v>
+        <v>11.5</v>
       </c>
       <c r="D163" t="n">
-        <v>5710</v>
+        <v>3181</v>
       </c>
       <c r="E163" t="n">
-        <v>4695.956053243186</v>
+        <v>3147.518794622453</v>
       </c>
       <c r="F163" t="n">
-        <v>21.6</v>
+        <v>1.1</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I163" t="n">
-        <v>6433000000</v>
+        <v>20794000000</v>
       </c>
       <c r="J163" t="n">
-        <v>7985000000</v>
+        <v>10600000000</v>
       </c>
       <c r="K163" t="n">
-        <v>199000000</v>
+        <v>10773000000</v>
       </c>
       <c r="L163" t="n">
-        <v>29378000000</v>
+        <v>138378000000</v>
       </c>
       <c r="M163" t="n">
-        <v>14617000000</v>
+        <v>42167000000</v>
       </c>
       <c r="N163" t="n">
-        <v>47663476990</v>
+        <v>368198714160</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>エムスリー株式会社</t>
+          <t>株式会社カカクコム</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2413</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="D164" t="n">
-        <v>1751</v>
+        <v>3795</v>
       </c>
       <c r="E164" t="n">
-        <v>1638.585693292194</v>
+        <v>2318.314890576102</v>
       </c>
       <c r="F164" t="n">
-        <v>6.9</v>
+        <v>63.7</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -8922,50 +8922,50 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="I164" t="n">
-        <v>78812000000</v>
+        <v>46452000000</v>
       </c>
       <c r="J164" t="n">
-        <v>345000000</v>
+        <v>68000000</v>
       </c>
       <c r="K164" t="n">
-        <v>9506000000</v>
+        <v>4669000000</v>
       </c>
       <c r="L164" t="n">
-        <v>152472000000</v>
+        <v>45479000000</v>
       </c>
       <c r="M164" t="n">
-        <v>88663000000</v>
+        <v>51189000000</v>
       </c>
       <c r="N164" t="n">
-        <v>1166719773011</v>
+        <v>750788633265</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>三井松島ホールディングス株式会社</t>
+          <t>古河機械金属株式会社</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>40.2</v>
+        <v>46.5</v>
       </c>
       <c r="D165" t="n">
-        <v>2275</v>
+        <v>4095</v>
       </c>
       <c r="E165" t="n">
-        <v>2920</v>
+        <v>1600</v>
       </c>
       <c r="F165" t="n">
-        <v>-22.1</v>
+        <v>155.9</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -8974,102 +8974,102 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="I165" t="n">
-        <v>19413000000</v>
+        <v>14468000000</v>
       </c>
       <c r="J165" t="n">
-        <v>3540000000</v>
+        <v>26121000000</v>
       </c>
       <c r="K165" t="n">
-        <v>10945000000</v>
+        <v>19903000000</v>
       </c>
       <c r="L165" t="n">
-        <v>35537000000</v>
+        <v>100075000000</v>
       </c>
       <c r="M165" t="n">
-        <v>33898000000</v>
+        <v>60492000000</v>
       </c>
       <c r="N165" t="n">
-        <v>84238609000</v>
+        <v>130098629115</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ノリタケ株式会社</t>
+          <t>多木化学株式会社</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>37.9</v>
+        <v>30.6</v>
       </c>
       <c r="D166" t="n">
-        <v>3590</v>
+        <v>5730</v>
       </c>
       <c r="E166" t="n">
-        <v>3573.410502159827</v>
+        <v>4695.956053243186</v>
       </c>
       <c r="F166" t="n">
-        <v>0.5</v>
+        <v>22</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I166" t="n">
-        <v>11733000000</v>
+        <v>6433000000</v>
       </c>
       <c r="J166" t="n">
-        <v>20204000000</v>
+        <v>7985000000</v>
       </c>
       <c r="K166" t="n">
-        <v>42879000000</v>
+        <v>199000000</v>
       </c>
       <c r="L166" t="n">
-        <v>118800000000</v>
+        <v>29378000000</v>
       </c>
       <c r="M166" t="n">
-        <v>74816000000</v>
+        <v>14617000000</v>
       </c>
       <c r="N166" t="n">
-        <v>197501243660</v>
+        <v>47830424370</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>株式会社ＡＣＳＬ</t>
+          <t>エムスリー株式会社</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>8.699999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="D167" t="n">
-        <v>1224</v>
+        <v>1797.5</v>
       </c>
       <c r="E167" t="n">
-        <v>913.2768512341561</v>
+        <v>1638.585693292194</v>
       </c>
       <c r="F167" t="n">
-        <v>34</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -9078,130 +9078,286 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1891731000</v>
+        <v>78812000000</v>
       </c>
       <c r="J167" t="n">
-        <v>3724000</v>
+        <v>345000000</v>
       </c>
       <c r="K167" t="n">
-        <v>197577000</v>
+        <v>9506000000</v>
       </c>
       <c r="L167" t="n">
-        <v>3572642000</v>
+        <v>152472000000</v>
       </c>
       <c r="M167" t="n">
-        <v>2093032000</v>
+        <v>88663000000</v>
       </c>
       <c r="N167" t="n">
-        <v>23956424208</v>
+        <v>1197703479148</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>株式会社スズケン</t>
+          <t>三井松島ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>9987</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>78.3</v>
+        <v>40.1</v>
       </c>
       <c r="D168" t="n">
-        <v>5223</v>
+        <v>2285</v>
       </c>
       <c r="E168" t="n">
-        <v>4137.137750115735</v>
+        <v>2920</v>
       </c>
       <c r="F168" t="n">
-        <v>26.2</v>
+        <v>-21.7</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="I168" t="n">
-        <v>168215000000</v>
+        <v>19413000000</v>
       </c>
       <c r="J168" t="n">
-        <v>65453000000</v>
+        <v>3540000000</v>
       </c>
       <c r="K168" t="n">
-        <v>38927000000</v>
+        <v>10945000000</v>
       </c>
       <c r="L168" t="n">
-        <v>418062000000</v>
+        <v>35537000000</v>
       </c>
       <c r="M168" t="n">
-        <v>272595000000</v>
+        <v>33898000000</v>
       </c>
       <c r="N168" t="n">
-        <v>348291519147</v>
+        <v>84608888600</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
+          <t>ノリタケ株式会社</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>5331</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="D169" t="n">
+        <v>3600</v>
+      </c>
+      <c r="E169" t="n">
+        <v>3573.410502159827</v>
+      </c>
+      <c r="F169" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>株式会社ストラテジックキャピタル</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>11733000000</v>
+      </c>
+      <c r="J169" t="n">
+        <v>20204000000</v>
+      </c>
+      <c r="K169" t="n">
+        <v>42879000000</v>
+      </c>
+      <c r="L169" t="n">
+        <v>118800000000</v>
+      </c>
+      <c r="M169" t="n">
+        <v>74816000000</v>
+      </c>
+      <c r="N169" t="n">
+        <v>198051386400</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>株式会社ＡＣＳＬ</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>6232</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="D170" t="n">
+        <v>1359</v>
+      </c>
+      <c r="E170" t="n">
+        <v>913.2768512341561</v>
+      </c>
+      <c r="F170" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="I170" t="n">
+        <v>1891731000</v>
+      </c>
+      <c r="J170" t="n">
+        <v>3724000</v>
+      </c>
+      <c r="K170" t="n">
+        <v>197577000</v>
+      </c>
+      <c r="L170" t="n">
+        <v>3572642000</v>
+      </c>
+      <c r="M170" t="n">
+        <v>2093032000</v>
+      </c>
+      <c r="N170" t="n">
+        <v>26598676878</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>株式会社スズケン</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="D171" t="n">
+        <v>5346</v>
+      </c>
+      <c r="E171" t="n">
+        <v>4137.137750115735</v>
+      </c>
+      <c r="F171" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="I171" t="n">
+        <v>168215000000</v>
+      </c>
+      <c r="J171" t="n">
+        <v>65453000000</v>
+      </c>
+      <c r="K171" t="n">
+        <v>38927000000</v>
+      </c>
+      <c r="L171" t="n">
+        <v>418062000000</v>
+      </c>
+      <c r="M171" t="n">
+        <v>272595000000</v>
+      </c>
+      <c r="N171" t="n">
+        <v>356493674394</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
           <t>フォスター電機株式会社</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
+      <c r="B172" t="inlineStr">
         <is>
           <t>6794</t>
         </is>
       </c>
-      <c r="C169" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="D169" t="n">
-        <v>3160</v>
-      </c>
-      <c r="E169" t="n">
+      <c r="C172" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="D172" t="n">
+        <v>3190</v>
+      </c>
+      <c r="E172" t="n">
         <v>2681.96152003832</v>
       </c>
-      <c r="F169" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="G169" t="inlineStr">
+      <c r="F172" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G172" t="inlineStr">
         <is>
           <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
+      <c r="H172" t="inlineStr">
         <is>
           <t>2026-01-22</t>
         </is>
       </c>
-      <c r="I169" t="n">
+      <c r="I172" t="n">
         <v>12089000000</v>
       </c>
-      <c r="J169" t="n">
+      <c r="J172" t="n">
         <v>7327000000</v>
       </c>
-      <c r="K169" t="n">
+      <c r="K172" t="n">
         <v>1115000000</v>
       </c>
-      <c r="L169" t="n">
+      <c r="L172" t="n">
         <v>51632000000</v>
       </c>
-      <c r="M169" t="n">
+      <c r="M172" t="n">
         <v>20531000000</v>
       </c>
-      <c r="N169" t="n">
-        <v>70998270120</v>
+      <c r="N172" t="n">
+        <v>71672304330</v>
       </c>
     </row>
   </sheetData>

--- a/docs/アクティビスト銘柄_資産判定.xlsx
+++ b/docs/アクティビスト銘柄_資産判定.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N172"/>
+  <dimension ref="A1:N174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>44.3</v>
+        <v>45.9</v>
       </c>
       <c r="D2" t="n">
-        <v>1342</v>
+        <v>1295.5</v>
       </c>
       <c r="E2" t="n">
         <v>1111.251693601708</v>
       </c>
       <c r="F2" t="n">
-        <v>20.8</v>
+        <v>16.6</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -537,7 +537,7 @@
         <v>213563000000</v>
       </c>
       <c r="N2" t="n">
-        <v>481820997680</v>
+        <v>465126007820</v>
       </c>
     </row>
     <row r="3">
@@ -552,16 +552,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>53.7</v>
+        <v>54.1</v>
       </c>
       <c r="D3" t="n">
-        <v>1185</v>
+        <v>1176</v>
       </c>
       <c r="E3" t="n">
         <v>1019.677694332945</v>
       </c>
       <c r="F3" t="n">
-        <v>16.2</v>
+        <v>15.3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         <v>106991000000</v>
       </c>
       <c r="N3" t="n">
-        <v>199376901750</v>
+        <v>197862646800</v>
       </c>
     </row>
     <row r="4">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>3493</v>
+        <v>3478</v>
       </c>
       <c r="E4" t="n">
         <v>6116.356643776557</v>
       </c>
       <c r="F4" t="n">
-        <v>-42.9</v>
+        <v>-43.1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         <v>219041000000</v>
       </c>
       <c r="N4" t="n">
-        <v>3160319673042</v>
+        <v>3146748303132</v>
       </c>
     </row>
     <row r="5">
@@ -656,16 +656,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30.2</v>
+        <v>30.4</v>
       </c>
       <c r="D5" t="n">
-        <v>2228</v>
+        <v>2210</v>
       </c>
       <c r="E5" t="n">
         <v>1815.198567455447</v>
       </c>
       <c r="F5" t="n">
-        <v>22.7</v>
+        <v>21.7</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         <v>168499000000</v>
       </c>
       <c r="N5" t="n">
-        <v>558375237456</v>
+        <v>553864126920</v>
       </c>
     </row>
     <row r="6">
@@ -708,16 +708,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>52.3</v>
+        <v>51.7</v>
       </c>
       <c r="D6" t="n">
-        <v>11180</v>
+        <v>11320</v>
       </c>
       <c r="E6" t="n">
         <v>5684.0003469471</v>
       </c>
       <c r="F6" t="n">
-        <v>96.7</v>
+        <v>99.2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>91895000000</v>
       </c>
       <c r="N6" t="n">
-        <v>175649628440</v>
+        <v>177849176560</v>
       </c>
     </row>
     <row r="7">
@@ -760,16 +760,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>52.3</v>
+        <v>51.7</v>
       </c>
       <c r="D7" t="n">
-        <v>11180</v>
+        <v>11320</v>
       </c>
       <c r="E7" t="n">
         <v>4549.503641591014</v>
       </c>
       <c r="F7" t="n">
-        <v>145.7</v>
+        <v>148.8</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>91895000000</v>
       </c>
       <c r="N7" t="n">
-        <v>175649628440</v>
+        <v>177849176560</v>
       </c>
     </row>
     <row r="8">
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="D8" t="n">
-        <v>3905</v>
+        <v>3925</v>
       </c>
       <c r="E8" t="n">
         <v>1361.432492253209</v>
       </c>
       <c r="F8" t="n">
-        <v>186.8</v>
+        <v>188.3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>12397436000</v>
       </c>
       <c r="N8" t="n">
-        <v>86625962225</v>
+        <v>87069629125</v>
       </c>
     </row>
     <row r="9">
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>29.5</v>
+        <v>29.8</v>
       </c>
       <c r="D9" t="n">
-        <v>3392</v>
+        <v>3352</v>
       </c>
       <c r="E9" t="n">
         <v>13739.64575539568</v>
       </c>
       <c r="F9" t="n">
-        <v>-75.3</v>
+        <v>-75.59999999999999</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>325393000000</v>
       </c>
       <c r="N9" t="n">
-        <v>1104883893760</v>
+        <v>1091854602560</v>
       </c>
     </row>
     <row r="10">
@@ -916,16 +916,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>44.9</v>
+        <v>45.1</v>
       </c>
       <c r="D10" t="n">
-        <v>2150</v>
+        <v>2141</v>
       </c>
       <c r="E10" t="n">
         <v>1198.150742177053</v>
       </c>
       <c r="F10" t="n">
-        <v>79.40000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>213966000000</v>
       </c>
       <c r="N10" t="n">
-        <v>476039543150</v>
+        <v>474046819481</v>
       </c>
     </row>
     <row r="11">
@@ -968,16 +968,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>44.9</v>
+        <v>45.1</v>
       </c>
       <c r="D11" t="n">
-        <v>2150</v>
+        <v>2141</v>
       </c>
       <c r="E11" t="n">
         <v>1188.162962482466</v>
       </c>
       <c r="F11" t="n">
-        <v>81</v>
+        <v>80.2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>213966000000</v>
       </c>
       <c r="N11" t="n">
-        <v>476039543150</v>
+        <v>474046819481</v>
       </c>
     </row>
     <row r="12">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="D12" t="n">
-        <v>3665</v>
+        <v>3635</v>
       </c>
       <c r="E12" t="n">
         <v>2995.424821743842</v>
       </c>
       <c r="F12" t="n">
-        <v>22.4</v>
+        <v>21.4</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>129979000000</v>
       </c>
       <c r="N12" t="n">
-        <v>538629231860</v>
+        <v>534220261340</v>
       </c>
     </row>
     <row r="13">
@@ -1072,16 +1072,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>73.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>4882</v>
+        <v>4869</v>
       </c>
       <c r="E13" t="n">
         <v>4991.027246539169</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2</v>
+        <v>-2.4</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>1007966000000</v>
       </c>
       <c r="N13" t="n">
-        <v>1368042466332</v>
+        <v>1364399583894</v>
       </c>
     </row>
     <row r="14">
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="D14" t="n">
-        <v>1734</v>
+        <v>1746</v>
       </c>
       <c r="E14" t="n">
         <v>1512.21980974841</v>
       </c>
       <c r="F14" t="n">
-        <v>14.7</v>
+        <v>15.5</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>120816000000</v>
       </c>
       <c r="N14" t="n">
-        <v>571208667042</v>
+        <v>575161668198</v>
       </c>
     </row>
     <row r="15">
@@ -1176,16 +1176,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="D15" t="n">
-        <v>2707</v>
+        <v>2667</v>
       </c>
       <c r="E15" t="n">
         <v>1827.011042553346</v>
       </c>
       <c r="F15" t="n">
-        <v>48.2</v>
+        <v>46</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>48336000000</v>
       </c>
       <c r="N15" t="n">
-        <v>660704991097</v>
+        <v>650942080257</v>
       </c>
     </row>
     <row r="16">
@@ -1228,16 +1228,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>134.8</v>
+        <v>138.2</v>
       </c>
       <c r="D16" t="n">
-        <v>1595</v>
+        <v>1556</v>
       </c>
       <c r="E16" t="n">
         <v>2122.579027791042</v>
       </c>
       <c r="F16" t="n">
-        <v>-24.9</v>
+        <v>-26.7</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>80333000000</v>
       </c>
       <c r="N16" t="n">
-        <v>59577121065</v>
+        <v>58120376412</v>
       </c>
     </row>
     <row r="17">
@@ -1280,16 +1280,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="D17" t="n">
-        <v>3022</v>
+        <v>2994</v>
       </c>
       <c r="E17" t="n">
         <v>6272.971195510064</v>
       </c>
       <c r="F17" t="n">
-        <v>-51.8</v>
+        <v>-52.3</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>179622000000</v>
       </c>
       <c r="N17" t="n">
-        <v>1089961463748</v>
+        <v>1079862548796</v>
       </c>
     </row>
     <row r="18">
@@ -1332,16 +1332,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="D18" t="n">
-        <v>3935</v>
+        <v>4088</v>
       </c>
       <c r="E18" t="n">
         <v>1572.181660925393</v>
       </c>
       <c r="F18" t="n">
-        <v>150.3</v>
+        <v>160</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>35501000000</v>
       </c>
       <c r="N18" t="n">
-        <v>702645629295</v>
+        <v>729965777016</v>
       </c>
     </row>
     <row r="19">
@@ -1384,16 +1384,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="D19" t="n">
-        <v>3935</v>
+        <v>4088</v>
       </c>
       <c r="E19" t="n">
         <v>1141.512891683109</v>
       </c>
       <c r="F19" t="n">
-        <v>244.7</v>
+        <v>258.1</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>35501000000</v>
       </c>
       <c r="N19" t="n">
-        <v>702645629295</v>
+        <v>729965777016</v>
       </c>
     </row>
     <row r="20">
@@ -1436,16 +1436,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>48</v>
+        <v>48.6</v>
       </c>
       <c r="D20" t="n">
-        <v>5583</v>
+        <v>5519</v>
       </c>
       <c r="E20" t="n">
         <v>2836.942753814942</v>
       </c>
       <c r="F20" t="n">
-        <v>96.8</v>
+        <v>94.5</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>94351000000</v>
       </c>
       <c r="N20" t="n">
-        <v>196412290443</v>
+        <v>194160743499</v>
       </c>
     </row>
     <row r="21">
@@ -1488,16 +1488,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>53.5</v>
+        <v>53.7</v>
       </c>
       <c r="D21" t="n">
-        <v>4199</v>
+        <v>4181</v>
       </c>
       <c r="E21" t="n">
         <v>2863.970160821546</v>
       </c>
       <c r="F21" t="n">
-        <v>46.6</v>
+        <v>46</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>161529000000</v>
       </c>
       <c r="N21" t="n">
-        <v>302097739437</v>
+        <v>300802726503</v>
       </c>
     </row>
     <row r="22">
@@ -1540,16 +1540,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>50.7</v>
+        <v>51.7</v>
       </c>
       <c r="D22" t="n">
-        <v>4843</v>
+        <v>4755</v>
       </c>
       <c r="E22" t="n">
         <v>2566.284807227078</v>
       </c>
       <c r="F22" t="n">
-        <v>88.7</v>
+        <v>85.3</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>231575000000</v>
       </c>
       <c r="N22" t="n">
-        <v>456632425300</v>
+        <v>448335160500</v>
       </c>
     </row>
     <row r="23">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="D23" t="n">
-        <v>5155</v>
+        <v>5124</v>
       </c>
       <c r="E23" t="n">
         <v>2779.139169918938</v>
       </c>
       <c r="F23" t="n">
-        <v>85.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>183216000000</v>
       </c>
       <c r="N23" t="n">
-        <v>639387388005</v>
+        <v>635542381404</v>
       </c>
     </row>
     <row r="24">
@@ -1644,16 +1644,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>4037</v>
+        <v>3948</v>
       </c>
       <c r="E24" t="n">
         <v>2420.370957920882</v>
       </c>
       <c r="F24" t="n">
-        <v>66.8</v>
+        <v>63.1</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>18167000000</v>
       </c>
       <c r="N24" t="n">
-        <v>199577487923</v>
+        <v>195177587892</v>
       </c>
     </row>
     <row r="25">
@@ -1696,16 +1696,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="D25" t="n">
-        <v>1766</v>
+        <v>1710</v>
       </c>
       <c r="E25" t="n">
         <v>1344.518957928979</v>
       </c>
       <c r="F25" t="n">
-        <v>31.3</v>
+        <v>27.2</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>45956000000</v>
       </c>
       <c r="N25" t="n">
-        <v>567264437906</v>
+        <v>549276437610</v>
       </c>
     </row>
     <row r="26">
@@ -1748,16 +1748,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>59.2</v>
+        <v>59.4</v>
       </c>
       <c r="D26" t="n">
-        <v>5062</v>
+        <v>5038</v>
       </c>
       <c r="E26" t="n">
         <v>4154.626869982095</v>
       </c>
       <c r="F26" t="n">
-        <v>21.8</v>
+        <v>21.3</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>179086000000</v>
       </c>
       <c r="N26" t="n">
-        <v>302711021912</v>
+        <v>301275805688</v>
       </c>
     </row>
     <row r="27">
@@ -1800,16 +1800,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="D27" t="n">
-        <v>3925</v>
+        <v>3757</v>
       </c>
       <c r="E27" t="n">
         <v>2561.705402476645</v>
       </c>
       <c r="F27" t="n">
-        <v>53.2</v>
+        <v>46.7</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>100104000000</v>
       </c>
       <c r="N27" t="n">
-        <v>718202014625</v>
+        <v>687461138585</v>
       </c>
     </row>
     <row r="28">
@@ -1852,16 +1852,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>43.5</v>
+        <v>44</v>
       </c>
       <c r="D28" t="n">
-        <v>3553</v>
+        <v>3514</v>
       </c>
       <c r="E28" t="n">
         <v>2560</v>
       </c>
       <c r="F28" t="n">
-        <v>38.8</v>
+        <v>37.3</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>190312000000</v>
       </c>
       <c r="N28" t="n">
-        <v>437410917218</v>
+        <v>432609615284</v>
       </c>
     </row>
     <row r="29">
@@ -1904,16 +1904,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>84.90000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="D29" t="n">
-        <v>4530</v>
+        <v>4540</v>
       </c>
       <c r="E29" t="n">
         <v>3449.780346820809</v>
       </c>
       <c r="F29" t="n">
-        <v>31.3</v>
+        <v>31.6</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>90928000000</v>
       </c>
       <c r="N29" t="n">
-        <v>107120964360</v>
+        <v>107357434480</v>
       </c>
     </row>
     <row r="30">
@@ -1956,16 +1956,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>54.9</v>
+        <v>55.2</v>
       </c>
       <c r="D30" t="n">
-        <v>1738</v>
+        <v>1731</v>
       </c>
       <c r="E30" t="n">
         <v>1746.940387696806</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.5</v>
+        <v>-0.9</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>36070000000</v>
       </c>
       <c r="N30" t="n">
-        <v>65664234834</v>
+        <v>65399764383</v>
       </c>
     </row>
     <row r="31">
@@ -2008,16 +2008,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>103.8</v>
+        <v>105.2</v>
       </c>
       <c r="D31" t="n">
-        <v>1713</v>
+        <v>1690</v>
       </c>
       <c r="E31" t="n">
         <v>2298.672482457804</v>
       </c>
       <c r="F31" t="n">
-        <v>-25.5</v>
+        <v>-26.5</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>42752000000</v>
       </c>
       <c r="N31" t="n">
-        <v>41181525531</v>
+        <v>40628592030</v>
       </c>
     </row>
     <row r="32">
@@ -2063,13 +2063,13 @@
         <v>67.09999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="E32" t="n">
         <v>1270</v>
       </c>
       <c r="F32" t="n">
-        <v>110.1</v>
+        <v>110</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>31108000000</v>
       </c>
       <c r="N32" t="n">
-        <v>46390012748</v>
+        <v>46372625187</v>
       </c>
     </row>
     <row r="33">
@@ -2115,13 +2115,13 @@
         <v>67.09999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="E33" t="n">
         <v>1170</v>
       </c>
       <c r="F33" t="n">
-        <v>128</v>
+        <v>127.9</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>31108000000</v>
       </c>
       <c r="N33" t="n">
-        <v>46390012748</v>
+        <v>46372625187</v>
       </c>
     </row>
     <row r="34">
@@ -2164,16 +2164,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>32.9</v>
+        <v>33.6</v>
       </c>
       <c r="D34" t="n">
-        <v>2896</v>
+        <v>2836.5</v>
       </c>
       <c r="E34" t="n">
         <v>2381.523440544182</v>
       </c>
       <c r="F34" t="n">
-        <v>21.6</v>
+        <v>19.1</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>168696000000</v>
       </c>
       <c r="N34" t="n">
-        <v>513356381824</v>
+        <v>502809177156</v>
       </c>
     </row>
     <row r="35">
@@ -2216,16 +2216,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="D35" t="n">
-        <v>2534</v>
+        <v>2530</v>
       </c>
       <c r="E35" t="n">
         <v>2901.475903614458</v>
       </c>
       <c r="F35" t="n">
-        <v>-12.7</v>
+        <v>-12.8</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>108430000000</v>
       </c>
       <c r="N35" t="n">
-        <v>132697684056</v>
+        <v>132488216520</v>
       </c>
     </row>
     <row r="36">
@@ -2268,16 +2268,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="D36" t="n">
-        <v>2534</v>
+        <v>2530</v>
       </c>
       <c r="E36" t="n">
         <v>2905.067038344418</v>
       </c>
       <c r="F36" t="n">
-        <v>-12.8</v>
+        <v>-12.9</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>108430000000</v>
       </c>
       <c r="N36" t="n">
-        <v>132697684056</v>
+        <v>132488216520</v>
       </c>
     </row>
     <row r="37">
@@ -2320,16 +2320,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="D37" t="n">
-        <v>2534</v>
+        <v>2530</v>
       </c>
       <c r="E37" t="n">
         <v>2955.342465753425</v>
       </c>
       <c r="F37" t="n">
-        <v>-14.3</v>
+        <v>-14.4</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>108430000000</v>
       </c>
       <c r="N37" t="n">
-        <v>132697684056</v>
+        <v>132488216520</v>
       </c>
     </row>
     <row r="38">
@@ -2372,16 +2372,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="D38" t="n">
-        <v>2534</v>
+        <v>2530</v>
       </c>
       <c r="E38" t="n">
         <v>2987.584858837727</v>
       </c>
       <c r="F38" t="n">
-        <v>-15.2</v>
+        <v>-15.3</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>108430000000</v>
       </c>
       <c r="N38" t="n">
-        <v>132697684056</v>
+        <v>132488216520</v>
       </c>
     </row>
     <row r="39">
@@ -2424,16 +2424,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="D39" t="n">
-        <v>2534</v>
+        <v>2530</v>
       </c>
       <c r="E39" t="n">
         <v>3016.088716673414</v>
       </c>
       <c r="F39" t="n">
-        <v>-16</v>
+        <v>-16.1</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>108430000000</v>
       </c>
       <c r="N39" t="n">
-        <v>132697684056</v>
+        <v>132488216520</v>
       </c>
     </row>
     <row r="40">
@@ -2476,16 +2476,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="D40" t="n">
-        <v>2534</v>
+        <v>2530</v>
       </c>
       <c r="E40" t="n">
         <v>3016.087384069568</v>
       </c>
       <c r="F40" t="n">
-        <v>-16</v>
+        <v>-16.1</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>108430000000</v>
       </c>
       <c r="N40" t="n">
-        <v>132697684056</v>
+        <v>132488216520</v>
       </c>
     </row>
     <row r="41">
@@ -2528,16 +2528,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="D41" t="n">
-        <v>2534</v>
+        <v>2530</v>
       </c>
       <c r="E41" t="n">
         <v>2939.562915943684</v>
       </c>
       <c r="F41" t="n">
-        <v>-13.8</v>
+        <v>-13.9</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>108430000000</v>
       </c>
       <c r="N41" t="n">
-        <v>132697684056</v>
+        <v>132488216520</v>
       </c>
     </row>
     <row r="42">
@@ -2684,16 +2684,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>85.7</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>2799</v>
+        <v>2809</v>
       </c>
       <c r="E44" t="n">
         <v>4265.455132343447</v>
       </c>
       <c r="F44" t="n">
-        <v>-34.4</v>
+        <v>-34.1</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>22869000000</v>
       </c>
       <c r="N44" t="n">
-        <v>26685156582</v>
+        <v>26780494762</v>
       </c>
     </row>
     <row r="45">
@@ -2739,13 +2739,13 @@
         <v>32.4</v>
       </c>
       <c r="D45" t="n">
-        <v>4760</v>
+        <v>4750</v>
       </c>
       <c r="E45" t="n">
         <v>2824.318397803668</v>
       </c>
       <c r="F45" t="n">
-        <v>68.5</v>
+        <v>68.2</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>61975000000</v>
       </c>
       <c r="N45" t="n">
-        <v>191497917800</v>
+        <v>191095611250</v>
       </c>
     </row>
     <row r="46">
@@ -2791,13 +2791,13 @@
         <v>28.1</v>
       </c>
       <c r="D46" t="n">
-        <v>6880</v>
+        <v>6860</v>
       </c>
       <c r="E46" t="n">
         <v>3096.322467304314</v>
       </c>
       <c r="F46" t="n">
-        <v>122.2</v>
+        <v>121.6</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>52961000000</v>
       </c>
       <c r="N46" t="n">
-        <v>188740209600</v>
+        <v>188191546200</v>
       </c>
     </row>
     <row r="47">
@@ -2840,16 +2840,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>23.4</v>
+        <v>23.9</v>
       </c>
       <c r="D47" t="n">
-        <v>6450</v>
+        <v>6309</v>
       </c>
       <c r="E47" t="n">
         <v>3322.047887165483</v>
       </c>
       <c r="F47" t="n">
-        <v>94.2</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>492847000000</v>
       </c>
       <c r="N47" t="n">
-        <v>2106994790550</v>
+        <v>2060934904431</v>
       </c>
     </row>
     <row r="48">
@@ -2892,16 +2892,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>35.1</v>
+        <v>35.7</v>
       </c>
       <c r="D48" t="n">
-        <v>1772</v>
+        <v>1743</v>
       </c>
       <c r="E48" t="n">
         <v>2112.609181636727</v>
       </c>
       <c r="F48" t="n">
-        <v>-16.1</v>
+        <v>-17.5</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>52218000000</v>
       </c>
       <c r="N48" t="n">
-        <v>148777137720</v>
+        <v>146342297430</v>
       </c>
     </row>
     <row r="49">
@@ -2947,13 +2947,13 @@
         <v>3.7</v>
       </c>
       <c r="D49" t="n">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="E49" t="n">
         <v>404.9347366248775</v>
       </c>
       <c r="F49" t="n">
-        <v>77.8</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>7044972000</v>
       </c>
       <c r="N49" t="n">
-        <v>191941995600</v>
+        <v>190075892865</v>
       </c>
     </row>
     <row r="50">
@@ -2996,16 +2996,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="D50" t="n">
-        <v>2724</v>
+        <v>2856</v>
       </c>
       <c r="E50" t="n">
         <v>2220.184278344451</v>
       </c>
       <c r="F50" t="n">
-        <v>22.7</v>
+        <v>28.6</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>207116000000</v>
       </c>
       <c r="N50" t="n">
-        <v>3122547990540</v>
+        <v>3273860888760</v>
       </c>
     </row>
     <row r="51">
@@ -3048,16 +3048,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>20.7</v>
+        <v>20</v>
       </c>
       <c r="D51" t="n">
-        <v>22015</v>
+        <v>22885</v>
       </c>
       <c r="E51" t="n">
         <v>11879.91675437757</v>
       </c>
       <c r="F51" t="n">
-        <v>85.3</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>191958000000</v>
       </c>
       <c r="N51" t="n">
-        <v>925104533325</v>
+        <v>961663286175</v>
       </c>
     </row>
     <row r="52">
@@ -3100,16 +3100,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D52" t="n">
-        <v>1134</v>
+        <v>1131</v>
       </c>
       <c r="E52" t="n">
         <v>730</v>
       </c>
       <c r="F52" t="n">
-        <v>55.3</v>
+        <v>54.9</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>50027000000</v>
       </c>
       <c r="N52" t="n">
-        <v>69235446924</v>
+        <v>69052284366</v>
       </c>
     </row>
     <row r="53">
@@ -3152,16 +3152,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="D53" t="n">
-        <v>5623</v>
+        <v>5662</v>
       </c>
       <c r="E53" t="n">
         <v>3341.42986565678</v>
       </c>
       <c r="F53" t="n">
-        <v>68.3</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>311107000000</v>
       </c>
       <c r="N53" t="n">
-        <v>1336159150339</v>
+        <v>1345426482166</v>
       </c>
     </row>
     <row r="54">
@@ -3204,16 +3204,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>28.5</v>
+        <v>28.7</v>
       </c>
       <c r="D54" t="n">
-        <v>3245</v>
+        <v>3220</v>
       </c>
       <c r="E54" t="n">
-        <v>2566.161017239607</v>
+        <v>2650.592873897018</v>
       </c>
       <c r="F54" t="n">
-        <v>26.5</v>
+        <v>21.5</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -3241,7 +3241,7 @@
         <v>32342000000</v>
       </c>
       <c r="N54" t="n">
-        <v>113633137420</v>
+        <v>112757689520</v>
       </c>
     </row>
     <row r="55">
@@ -3256,16 +3256,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>28.5</v>
+        <v>28.7</v>
       </c>
       <c r="D55" t="n">
-        <v>3245</v>
+        <v>3220</v>
       </c>
       <c r="E55" t="n">
-        <v>2550.198980592041</v>
+        <v>2615.786410161549</v>
       </c>
       <c r="F55" t="n">
-        <v>27.2</v>
+        <v>23.1</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -3293,7 +3293,7 @@
         <v>32342000000</v>
       </c>
       <c r="N55" t="n">
-        <v>113633137420</v>
+        <v>112757689520</v>
       </c>
     </row>
     <row r="56">
@@ -3308,16 +3308,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>28.5</v>
+        <v>28.7</v>
       </c>
       <c r="D56" t="n">
-        <v>3245</v>
+        <v>3220</v>
       </c>
       <c r="E56" t="n">
-        <v>2550.198980592041</v>
+        <v>2566.161017239607</v>
       </c>
       <c r="F56" t="n">
-        <v>27.2</v>
+        <v>25.5</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -3345,527 +3345,527 @@
         <v>32342000000</v>
       </c>
       <c r="N56" t="n">
-        <v>113633137420</v>
+        <v>112757689520</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>イオンフィナンシャルサービス株式会社</t>
+          <t>ＫＨネオケム株式会社</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>8570</t>
+          <t>4189</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>210.4</v>
+        <v>28.7</v>
       </c>
       <c r="D57" t="n">
-        <v>1644.5</v>
+        <v>3220</v>
       </c>
       <c r="E57" t="n">
-        <v>1288.711724885291</v>
+        <v>2550.198980592041</v>
       </c>
       <c r="F57" t="n">
-        <v>27.6</v>
+        <v>26.3</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>697628000000</v>
+        <v>16934000000</v>
       </c>
       <c r="J57" t="n">
-        <v>34512000000</v>
+        <v>8038000000</v>
       </c>
       <c r="K57" t="n">
-        <v>14926000000</v>
+        <v>7370000000</v>
       </c>
       <c r="L57" t="n">
-        <v>509055000000</v>
+        <v>57505000000</v>
       </c>
       <c r="M57" t="n">
-        <v>747066000000</v>
+        <v>32342000000</v>
       </c>
       <c r="N57" t="n">
-        <v>355021522498</v>
+        <v>112757689520</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>株式会社フジ・メディア・ホールディングス</t>
+          <t>ＫＨネオケム株式会社</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4189</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>66.2</v>
+        <v>28.7</v>
       </c>
       <c r="D58" t="n">
-        <v>4154</v>
+        <v>3220</v>
       </c>
       <c r="E58" t="n">
-        <v>3141.424011416125</v>
+        <v>2550.198980592041</v>
       </c>
       <c r="F58" t="n">
-        <v>32.2</v>
+        <v>26.3</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>102598000000</v>
+        <v>16934000000</v>
       </c>
       <c r="J58" t="n">
-        <v>174990000000</v>
+        <v>8038000000</v>
       </c>
       <c r="K58" t="n">
-        <v>113991000000</v>
+        <v>7370000000</v>
       </c>
       <c r="L58" t="n">
-        <v>808788000000</v>
+        <v>57505000000</v>
       </c>
       <c r="M58" t="n">
-        <v>391579000000</v>
+        <v>32342000000</v>
       </c>
       <c r="N58" t="n">
-        <v>591926739016</v>
+        <v>112757689520</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>株式会社フジ・メディア・ホールディングス</t>
+          <t>イオンフィナンシャルサービス株式会社</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>8570</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>66.2</v>
+        <v>212.8</v>
       </c>
       <c r="D59" t="n">
-        <v>4154</v>
+        <v>1626</v>
       </c>
       <c r="E59" t="n">
-        <v>2420</v>
+        <v>1288.711724885291</v>
       </c>
       <c r="F59" t="n">
-        <v>71.7</v>
+        <v>26.2</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>株式会社レノ代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>102598000000</v>
+        <v>697628000000</v>
       </c>
       <c r="J59" t="n">
-        <v>174990000000</v>
+        <v>34512000000</v>
       </c>
       <c r="K59" t="n">
-        <v>113991000000</v>
+        <v>14926000000</v>
       </c>
       <c r="L59" t="n">
-        <v>808788000000</v>
+        <v>509055000000</v>
       </c>
       <c r="M59" t="n">
-        <v>391579000000</v>
+        <v>747066000000</v>
       </c>
       <c r="N59" t="n">
-        <v>591926739016</v>
+        <v>351027665298</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>株式会社クスリのアオキホールディングス</t>
+          <t>株式会社フジ・メディア・ホールディングス</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>3549</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>41.7</v>
+        <v>68</v>
       </c>
       <c r="D60" t="n">
-        <v>4100</v>
+        <v>4039</v>
       </c>
       <c r="E60" t="n">
-        <v>3047.091476167608</v>
+        <v>3141.424011416125</v>
       </c>
       <c r="F60" t="n">
-        <v>34.6</v>
+        <v>28.6</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>26348000000</v>
+        <v>102598000000</v>
       </c>
       <c r="J60" t="n">
-        <v>132363000000</v>
+        <v>174990000000</v>
       </c>
       <c r="K60" t="n">
-        <v>3747000000</v>
+        <v>113991000000</v>
       </c>
       <c r="L60" t="n">
-        <v>86930000000</v>
+        <v>808788000000</v>
       </c>
       <c r="M60" t="n">
-        <v>162458000000</v>
+        <v>391579000000</v>
       </c>
       <c r="N60" t="n">
-        <v>389348574700</v>
+        <v>575539744556</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>リンナイ株式会社</t>
+          <t>株式会社フジ・メディア・ホールディングス</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>45.3</v>
+        <v>68</v>
       </c>
       <c r="D61" t="n">
-        <v>3500</v>
+        <v>4039</v>
       </c>
       <c r="E61" t="n">
-        <v>2844.704547285864</v>
+        <v>2420</v>
       </c>
       <c r="F61" t="n">
-        <v>23</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社レノ代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>147972000000</v>
+        <v>102598000000</v>
       </c>
       <c r="J61" t="n">
-        <v>64736000000</v>
+        <v>174990000000</v>
       </c>
       <c r="K61" t="n">
-        <v>5967000000</v>
+        <v>113991000000</v>
       </c>
       <c r="L61" t="n">
-        <v>378856000000</v>
+        <v>808788000000</v>
       </c>
       <c r="M61" t="n">
-        <v>218675000000</v>
+        <v>391579000000</v>
       </c>
       <c r="N61" t="n">
-        <v>483243642000</v>
+        <v>575539744556</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>センコーグループホールディングス株式会社</t>
+          <t>株式会社クスリのアオキホールディングス</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>9069</t>
+          <t>3549</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>52.4</v>
+        <v>42.8</v>
       </c>
       <c r="D62" t="n">
-        <v>2365</v>
+        <v>4000</v>
       </c>
       <c r="E62" t="n">
-        <v>1556.090471804319</v>
+        <v>3047.091476167608</v>
       </c>
       <c r="F62" t="n">
-        <v>52</v>
+        <v>31.3</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>42193000000</v>
+        <v>26348000000</v>
       </c>
       <c r="J62" t="n">
-        <v>138228000000</v>
+        <v>132363000000</v>
       </c>
       <c r="K62" t="n">
-        <v>27045000000</v>
+        <v>3747000000</v>
       </c>
       <c r="L62" t="n">
-        <v>160854000000</v>
+        <v>86930000000</v>
       </c>
       <c r="M62" t="n">
-        <v>207466000000</v>
+        <v>162458000000</v>
       </c>
       <c r="N62" t="n">
-        <v>395945000825</v>
+        <v>379852268000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ブロードメディア株式会社</t>
+          <t>リンナイ株式会社</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>5947</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>45.4</v>
+        <v>46.9</v>
       </c>
       <c r="D63" t="n">
-        <v>1860</v>
+        <v>3377</v>
       </c>
       <c r="E63" t="n">
-        <v>1529.631984751819</v>
+        <v>2844.704547285864</v>
       </c>
       <c r="F63" t="n">
-        <v>21.6</v>
+        <v>18.7</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>5301579000</v>
+        <v>147972000000</v>
       </c>
       <c r="J63" t="n">
-        <v>553048000</v>
+        <v>64736000000</v>
       </c>
       <c r="K63" t="n">
-        <v>169455000</v>
+        <v>5967000000</v>
       </c>
       <c r="L63" t="n">
-        <v>4610613000</v>
+        <v>378856000000</v>
       </c>
       <c r="M63" t="n">
-        <v>6024082000</v>
+        <v>218675000000</v>
       </c>
       <c r="N63" t="n">
-        <v>13256534340</v>
+        <v>466261079724</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ブロードメディア株式会社</t>
+          <t>センコーグループホールディングス株式会社</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>9069</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>45.4</v>
+        <v>52.3</v>
       </c>
       <c r="D64" t="n">
-        <v>1860</v>
+        <v>2367.5</v>
       </c>
       <c r="E64" t="n">
-        <v>1449.995380693296</v>
+        <v>1556.090471804319</v>
       </c>
       <c r="F64" t="n">
-        <v>28.3</v>
+        <v>52.1</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5301579000</v>
+        <v>42193000000</v>
       </c>
       <c r="J64" t="n">
-        <v>553048000</v>
+        <v>138228000000</v>
       </c>
       <c r="K64" t="n">
-        <v>169455000</v>
+        <v>27045000000</v>
       </c>
       <c r="L64" t="n">
-        <v>4610613000</v>
+        <v>160854000000</v>
       </c>
       <c r="M64" t="n">
-        <v>6024082000</v>
+        <v>207466000000</v>
       </c>
       <c r="N64" t="n">
-        <v>13256534340</v>
+        <v>396363547338</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>株式会社ニップン</t>
+          <t>ブロードメディア株式会社</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>66.2</v>
+        <v>46.2</v>
       </c>
       <c r="D65" t="n">
-        <v>3020</v>
+        <v>1831</v>
       </c>
       <c r="E65" t="n">
-        <v>2723.418631349517</v>
+        <v>1529.631984751819</v>
       </c>
       <c r="F65" t="n">
-        <v>10.9</v>
+        <v>19.7</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>31215000000</v>
+        <v>5301579000</v>
       </c>
       <c r="J65" t="n">
-        <v>48537000000</v>
+        <v>553048000</v>
       </c>
       <c r="K65" t="n">
-        <v>85530000000</v>
+        <v>169455000</v>
       </c>
       <c r="L65" t="n">
-        <v>178697000000</v>
+        <v>4610613000</v>
       </c>
       <c r="M65" t="n">
-        <v>165282000000</v>
+        <v>6024082000</v>
       </c>
       <c r="N65" t="n">
-        <v>249646892680</v>
+        <v>13049846439</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>株式会社ニップン</t>
+          <t>ブロードメディア株式会社</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>66.2</v>
+        <v>46.2</v>
       </c>
       <c r="D66" t="n">
-        <v>3020</v>
+        <v>1831</v>
       </c>
       <c r="E66" t="n">
-        <v>2709.132103263819</v>
+        <v>1449.995380693296</v>
       </c>
       <c r="F66" t="n">
-        <v>11.5</v>
+        <v>26.3</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>31215000000</v>
+        <v>5301579000</v>
       </c>
       <c r="J66" t="n">
-        <v>48537000000</v>
+        <v>553048000</v>
       </c>
       <c r="K66" t="n">
-        <v>85530000000</v>
+        <v>169455000</v>
       </c>
       <c r="L66" t="n">
-        <v>178697000000</v>
+        <v>4610613000</v>
       </c>
       <c r="M66" t="n">
-        <v>165282000000</v>
+        <v>6024082000</v>
       </c>
       <c r="N66" t="n">
-        <v>249646892680</v>
+        <v>13049846439</v>
       </c>
     </row>
     <row r="67">
@@ -3880,16 +3880,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>66.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="D67" t="n">
-        <v>3020</v>
+        <v>2979</v>
       </c>
       <c r="E67" t="n">
-        <v>2696.128808062088</v>
+        <v>2723.418631349517</v>
       </c>
       <c r="F67" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="I67" t="n">
@@ -3917,7 +3917,7 @@
         <v>165282000000</v>
       </c>
       <c r="N67" t="n">
-        <v>249646892680</v>
+        <v>246257646786</v>
       </c>
     </row>
     <row r="68">
@@ -3932,16 +3932,16 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>66.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="D68" t="n">
-        <v>3020</v>
+        <v>2979</v>
       </c>
       <c r="E68" t="n">
-        <v>2696.128808062088</v>
+        <v>2709.132103263819</v>
       </c>
       <c r="F68" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="I68" t="n">
@@ -3969,239 +3969,239 @@
         <v>165282000000</v>
       </c>
       <c r="N68" t="n">
-        <v>249646892680</v>
+        <v>246257646786</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>京浜急行電鉄株式会社</t>
+          <t>株式会社ニップン</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>118.3</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="D69" t="n">
-        <v>1583</v>
+        <v>2979</v>
       </c>
       <c r="E69" t="n">
-        <v>1160.8</v>
+        <v>2696.128808062088</v>
       </c>
       <c r="F69" t="n">
-        <v>36.4</v>
+        <v>10.5</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>61234000000</v>
+        <v>31215000000</v>
       </c>
       <c r="J69" t="n">
-        <v>318113000000</v>
+        <v>48537000000</v>
       </c>
       <c r="K69" t="n">
-        <v>114136000000</v>
+        <v>85530000000</v>
       </c>
       <c r="L69" t="n">
-        <v>256898000000</v>
+        <v>178697000000</v>
       </c>
       <c r="M69" t="n">
-        <v>493483000000</v>
+        <v>165282000000</v>
       </c>
       <c r="N69" t="n">
-        <v>417130759423</v>
+        <v>246257646786</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>あいホールディングス株式会社</t>
+          <t>株式会社ニップン</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>3076</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>23.1</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="D70" t="n">
-        <v>3030</v>
+        <v>2979</v>
       </c>
       <c r="E70" t="n">
-        <v>2007.754513143541</v>
+        <v>2696.128808062088</v>
       </c>
       <c r="F70" t="n">
-        <v>50.9</v>
+        <v>10.5</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>32012000000</v>
+        <v>31215000000</v>
       </c>
       <c r="J70" t="n">
-        <v>1646000000</v>
+        <v>48537000000</v>
       </c>
       <c r="K70" t="n">
-        <v>3550000000</v>
+        <v>85530000000</v>
       </c>
       <c r="L70" t="n">
-        <v>53765000000</v>
+        <v>178697000000</v>
       </c>
       <c r="M70" t="n">
-        <v>37208000000</v>
+        <v>165282000000</v>
       </c>
       <c r="N70" t="n">
-        <v>161416980930</v>
+        <v>246257646786</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>エア・ウォーター株式会社</t>
+          <t>京浜急行電鉄株式会社</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>15.1</v>
+        <v>119.5</v>
       </c>
       <c r="D71" t="n">
-        <v>2968</v>
+        <v>1567.5</v>
       </c>
       <c r="E71" t="n">
-        <v>2261.880826568852</v>
+        <v>1160.8</v>
       </c>
       <c r="F71" t="n">
-        <v>31.2</v>
+        <v>35</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>29189000000</v>
+        <v>61234000000</v>
       </c>
       <c r="J71" t="n">
-        <v>31318000000</v>
+        <v>318113000000</v>
       </c>
       <c r="K71" t="n">
-        <v>42001000000</v>
+        <v>114136000000</v>
       </c>
       <c r="L71" t="n">
-        <v>194657000000</v>
+        <v>256898000000</v>
       </c>
       <c r="M71" t="n">
-        <v>102508000000</v>
+        <v>493483000000</v>
       </c>
       <c r="N71" t="n">
-        <v>680455234424</v>
+        <v>413046408968</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>エア・ウォーター株式会社</t>
+          <t>あいホールディングス株式会社</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>15.1</v>
+        <v>23.2</v>
       </c>
       <c r="D72" t="n">
-        <v>2968</v>
+        <v>3010</v>
       </c>
       <c r="E72" t="n">
-        <v>1970</v>
+        <v>2007.754513143541</v>
       </c>
       <c r="F72" t="n">
-        <v>50.7</v>
+        <v>49.9</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>29189000000</v>
+        <v>32012000000</v>
       </c>
       <c r="J72" t="n">
-        <v>31318000000</v>
+        <v>1646000000</v>
       </c>
       <c r="K72" t="n">
-        <v>42001000000</v>
+        <v>3550000000</v>
       </c>
       <c r="L72" t="n">
-        <v>194657000000</v>
+        <v>53765000000</v>
       </c>
       <c r="M72" t="n">
-        <v>102508000000</v>
+        <v>37208000000</v>
       </c>
       <c r="N72" t="n">
-        <v>680455234424</v>
+        <v>160351522310</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>株式会社電通総研</t>
+          <t>エア・ウォーター株式会社</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>9.6</v>
+        <v>15.1</v>
       </c>
       <c r="D73" t="n">
-        <v>2864</v>
+        <v>2953</v>
       </c>
       <c r="E73" t="n">
-        <v>1910.426979628923</v>
+        <v>2261.880826568852</v>
       </c>
       <c r="F73" t="n">
-        <v>49.9</v>
+        <v>30.6</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -4210,322 +4210,322 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>49748000000</v>
+        <v>29189000000</v>
       </c>
       <c r="J73" t="n">
-        <v>524000000</v>
+        <v>31318000000</v>
       </c>
       <c r="K73" t="n">
-        <v>3388000000</v>
+        <v>42001000000</v>
       </c>
       <c r="L73" t="n">
-        <v>65471000000</v>
+        <v>194657000000</v>
       </c>
       <c r="M73" t="n">
-        <v>53660000000</v>
+        <v>102508000000</v>
       </c>
       <c r="N73" t="n">
-        <v>558995869408</v>
+        <v>677016276029</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>わかもと製薬株式会社</t>
+          <t>エア・ウォーター株式会社</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>49.8</v>
+        <v>15.1</v>
       </c>
       <c r="D74" t="n">
-        <v>299</v>
+        <v>2953</v>
       </c>
       <c r="E74" t="n">
-        <v>290.3401328717133</v>
+        <v>1970</v>
       </c>
       <c r="F74" t="n">
-        <v>3</v>
+        <v>49.9</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3231889000</v>
+        <v>29189000000</v>
       </c>
       <c r="J74" t="n">
-        <v>82947000</v>
+        <v>31318000000</v>
       </c>
       <c r="K74" t="n">
-        <v>1847919000</v>
+        <v>42001000000</v>
       </c>
       <c r="L74" t="n">
-        <v>11480803000</v>
+        <v>194657000000</v>
       </c>
       <c r="M74" t="n">
-        <v>5162755000</v>
+        <v>102508000000</v>
       </c>
       <c r="N74" t="n">
-        <v>10377045861</v>
+        <v>677016276029</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>株式会社豊田自動織機</t>
+          <t>株式会社電通総研</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>6201</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
+          <t>4812</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2870</v>
+      </c>
       <c r="E75" t="n">
-        <v>16430.4430802409</v>
-      </c>
-      <c r="F75" t="inlineStr"/>
+        <v>1910.426979628923</v>
+      </c>
+      <c r="F75" t="n">
+        <v>50.2</v>
+      </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>281605000000</v>
+        <v>49748000000</v>
       </c>
       <c r="J75" t="n">
-        <v>87540000000</v>
+        <v>524000000</v>
       </c>
       <c r="K75" t="n">
-        <v>730709000000</v>
+        <v>3388000000</v>
       </c>
       <c r="L75" t="n">
-        <v>3246174000000</v>
+        <v>65471000000</v>
       </c>
       <c r="M75" t="n">
-        <v>1099854000000</v>
-      </c>
-      <c r="N75" t="inlineStr"/>
+        <v>53660000000</v>
+      </c>
+      <c r="N75" t="n">
+        <v>560166950140</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>株式会社豊田自動織機</t>
+          <t>わかもと製薬株式会社</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>6201</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
+          <t>4512</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="D76" t="n">
+        <v>298</v>
+      </c>
       <c r="E76" t="n">
-        <v>16430443.10823975</v>
-      </c>
-      <c r="F76" t="inlineStr"/>
+        <v>290.3401328717133</v>
+      </c>
+      <c r="F76" t="n">
+        <v>2.6</v>
+      </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>281605000000</v>
+        <v>3231889000</v>
       </c>
       <c r="J76" t="n">
-        <v>87540000000</v>
+        <v>82947000</v>
       </c>
       <c r="K76" t="n">
-        <v>730709000000</v>
+        <v>1847919000</v>
       </c>
       <c r="L76" t="n">
-        <v>3246174000000</v>
+        <v>11480803000</v>
       </c>
       <c r="M76" t="n">
-        <v>1099854000000</v>
-      </c>
-      <c r="N76" t="inlineStr"/>
+        <v>5162755000</v>
+      </c>
+      <c r="N76" t="n">
+        <v>10342340022</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>大阪製鐵株式会社</t>
+          <t>株式会社豊田自動織機</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5449</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="D77" t="n">
-        <v>2562</v>
-      </c>
+          <t>6201</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="n">
-        <v>1748.071046781136</v>
-      </c>
-      <c r="F77" t="n">
-        <v>46.6</v>
-      </c>
+        <v>16430.4430802409</v>
+      </c>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>62396000000</v>
+        <v>281605000000</v>
       </c>
       <c r="J77" t="n">
-        <v>9241000000</v>
+        <v>87540000000</v>
       </c>
       <c r="K77" t="n">
-        <v>553000000</v>
+        <v>730709000000</v>
       </c>
       <c r="L77" t="n">
-        <v>151028000000</v>
+        <v>3246174000000</v>
       </c>
       <c r="M77" t="n">
-        <v>72190000000</v>
-      </c>
-      <c r="N77" t="n">
-        <v>76651296918</v>
-      </c>
+        <v>1099854000000</v>
+      </c>
+      <c r="N77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>株式会社ディー・エヌ・エー</t>
+          <t>株式会社豊田自動織機</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2432</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>75.09999999999999</v>
-      </c>
-      <c r="D78" t="n">
-        <v>2578</v>
-      </c>
+          <t>6201</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="n">
-        <v>2551.08574256026</v>
-      </c>
-      <c r="F78" t="n">
-        <v>1.1</v>
-      </c>
+        <v>16430443.10823975</v>
+      </c>
+      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>85363000000</v>
+        <v>281605000000</v>
       </c>
       <c r="J78" t="n">
-        <v>221000000</v>
+        <v>87540000000</v>
       </c>
       <c r="K78" t="n">
-        <v>93552000000</v>
+        <v>730709000000</v>
       </c>
       <c r="L78" t="n">
-        <v>177857000000</v>
+        <v>3246174000000</v>
       </c>
       <c r="M78" t="n">
-        <v>179136000000</v>
-      </c>
-      <c r="N78" t="n">
-        <v>238495010498</v>
-      </c>
+        <v>1099854000000</v>
+      </c>
+      <c r="N78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>株式会社ディー・エヌ・エー</t>
+          <t>大阪製鐵株式会社</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>5449</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>75.09999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="D79" t="n">
-        <v>2578</v>
+        <v>2561</v>
       </c>
       <c r="E79" t="n">
-        <v>2260</v>
+        <v>1748.071046781136</v>
       </c>
       <c r="F79" t="n">
-        <v>14.1</v>
+        <v>46.5</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>85363000000</v>
+        <v>62396000000</v>
       </c>
       <c r="J79" t="n">
-        <v>221000000</v>
+        <v>9241000000</v>
       </c>
       <c r="K79" t="n">
-        <v>93552000000</v>
+        <v>553000000</v>
       </c>
       <c r="L79" t="n">
-        <v>177857000000</v>
+        <v>151028000000</v>
       </c>
       <c r="M79" t="n">
-        <v>179136000000</v>
+        <v>72190000000</v>
       </c>
       <c r="N79" t="n">
-        <v>238495010498</v>
+        <v>76621378379</v>
       </c>
     </row>
     <row r="80">
@@ -4540,16 +4540,16 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>75.09999999999999</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="D80" t="n">
-        <v>2578</v>
+        <v>2545.5</v>
       </c>
       <c r="E80" t="n">
-        <v>2260</v>
+        <v>2551.08574256026</v>
       </c>
       <c r="F80" t="n">
-        <v>14.1</v>
+        <v>-0.2</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -4577,1595 +4577,1595 @@
         <v>179136000000</v>
       </c>
       <c r="N80" t="n">
-        <v>238495010498</v>
+        <v>235488382166</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>株式会社オリエントコーポレーション</t>
+          <t>株式会社ディー・エヌ・エー</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>8585</t>
+          <t>2432</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>301.9</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="D81" t="n">
-        <v>869</v>
+        <v>2545.5</v>
       </c>
       <c r="E81" t="n">
-        <v>798.3805136422309</v>
+        <v>2260</v>
       </c>
       <c r="F81" t="n">
-        <v>8.800000000000001</v>
+        <v>12.6</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>408187000000</v>
+        <v>85363000000</v>
       </c>
       <c r="J81" t="n">
-        <v>18930000000</v>
+        <v>221000000</v>
       </c>
       <c r="K81" t="n">
-        <v>21921000000</v>
+        <v>93552000000</v>
       </c>
       <c r="L81" t="n">
-        <v>216837000000</v>
+        <v>177857000000</v>
       </c>
       <c r="M81" t="n">
-        <v>449038000000</v>
+        <v>179136000000</v>
       </c>
       <c r="N81" t="n">
-        <v>148760515816</v>
+        <v>235488382166</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>東ソー株式会社</t>
+          <t>株式会社ディー・エヌ・エー</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>4042</t>
+          <t>2432</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>41.8</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="D82" t="n">
-        <v>2644</v>
+        <v>2545.5</v>
       </c>
       <c r="E82" t="n">
-        <v>2032.365850102071</v>
+        <v>2260</v>
       </c>
       <c r="F82" t="n">
-        <v>30.1</v>
+        <v>12.6</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>160812000000</v>
+        <v>85363000000</v>
       </c>
       <c r="J82" t="n">
-        <v>109648000000</v>
+        <v>221000000</v>
       </c>
       <c r="K82" t="n">
-        <v>70132000000</v>
+        <v>93552000000</v>
       </c>
       <c r="L82" t="n">
-        <v>759724000000</v>
+        <v>177857000000</v>
       </c>
       <c r="M82" t="n">
-        <v>340592000000</v>
+        <v>179136000000</v>
       </c>
       <c r="N82" t="n">
-        <v>814062603624</v>
+        <v>235488382166</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>株式会社西武ホールディングス</t>
+          <t>株式会社オリエントコーポレーション</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>8585</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>61.1</v>
+        <v>306.8</v>
       </c>
       <c r="D83" t="n">
-        <v>3641</v>
+        <v>855</v>
       </c>
       <c r="E83" t="n">
-        <v>1716.713876475349</v>
+        <v>798.3805136422309</v>
       </c>
       <c r="F83" t="n">
-        <v>112.1</v>
+        <v>7.1</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>87210000000</v>
+        <v>408187000000</v>
       </c>
       <c r="J83" t="n">
-        <v>428181000000</v>
+        <v>18930000000</v>
       </c>
       <c r="K83" t="n">
-        <v>49954000000</v>
+        <v>21921000000</v>
       </c>
       <c r="L83" t="n">
-        <v>387217000000</v>
+        <v>216837000000</v>
       </c>
       <c r="M83" t="n">
-        <v>565345000000</v>
+        <v>449038000000</v>
       </c>
       <c r="N83" t="n">
-        <v>925461326108</v>
+        <v>146363913720</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>東ソー株式会社</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>4042</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="D84" t="n">
+        <v>2599.5</v>
+      </c>
+      <c r="E84" t="n">
+        <v>2032.365850102071</v>
+      </c>
+      <c r="F84" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>2024-06-04</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>160812000000</v>
+      </c>
+      <c r="J84" t="n">
+        <v>109648000000</v>
+      </c>
+      <c r="K84" t="n">
+        <v>70132000000</v>
+      </c>
+      <c r="L84" t="n">
+        <v>759724000000</v>
+      </c>
+      <c r="M84" t="n">
+        <v>340592000000</v>
+      </c>
+      <c r="N84" t="n">
+        <v>800361474327</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>株式会社西武ホールディングス</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>9024</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="D85" t="n">
+        <v>3614</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1716.713876475349</v>
+      </c>
+      <c r="F85" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>87210000000</v>
+      </c>
+      <c r="J85" t="n">
+        <v>428181000000</v>
+      </c>
+      <c r="K85" t="n">
+        <v>49954000000</v>
+      </c>
+      <c r="L85" t="n">
+        <v>387217000000</v>
+      </c>
+      <c r="M85" t="n">
+        <v>565345000000</v>
+      </c>
+      <c r="N85" t="n">
+        <v>918598525832</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
           <t>株式会社フェローテック
 （旧会社名　株式会社フェローテックホールディングス）</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>6890</t>
         </is>
       </c>
-      <c r="C84" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="D84" t="n">
-        <v>9030</v>
-      </c>
-      <c r="E84" t="n">
+      <c r="C86" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="D86" t="n">
+        <v>9130</v>
+      </c>
+      <c r="E86" t="n">
         <v>4037.502552255647</v>
       </c>
-      <c r="F84" t="n">
-        <v>123.7</v>
-      </c>
-      <c r="G84" t="inlineStr">
+      <c r="F86" t="n">
+        <v>126.1</v>
+      </c>
+      <c r="G86" t="inlineStr">
         <is>
           <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="I84" t="n">
+      <c r="I86" t="n">
         <v>52579000000</v>
       </c>
-      <c r="J84" t="n">
+      <c r="J86" t="n">
         <v>90505000000</v>
       </c>
-      <c r="K84" t="n">
+      <c r="K86" t="n">
         <v>11654000000</v>
       </c>
-      <c r="L84" t="n">
+      <c r="L86" t="n">
         <v>160957000000</v>
       </c>
-      <c r="M84" t="n">
+      <c r="M86" t="n">
         <v>154738000000</v>
       </c>
-      <c r="N84" t="n">
-        <v>485847979890</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="N86" t="n">
+        <v>491228356190</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
         <is>
           <t>株式会社フェローテック
 （旧会社名　株式会社フェローテックホールディングス）</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>6890</t>
         </is>
       </c>
-      <c r="C85" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="D85" t="n">
-        <v>9030</v>
-      </c>
-      <c r="E85" t="n">
+      <c r="C87" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="D87" t="n">
+        <v>9130</v>
+      </c>
+      <c r="E87" t="n">
         <v>3950.736048458928</v>
       </c>
-      <c r="F85" t="n">
-        <v>128.6</v>
-      </c>
-      <c r="G85" t="inlineStr">
+      <c r="F87" t="n">
+        <v>131.1</v>
+      </c>
+      <c r="G87" t="inlineStr">
         <is>
           <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="I85" t="n">
+      <c r="I87" t="n">
         <v>52579000000</v>
       </c>
-      <c r="J85" t="n">
+      <c r="J87" t="n">
         <v>90505000000</v>
       </c>
-      <c r="K85" t="n">
+      <c r="K87" t="n">
         <v>11654000000</v>
       </c>
-      <c r="L85" t="n">
+      <c r="L87" t="n">
         <v>160957000000</v>
       </c>
-      <c r="M85" t="n">
+      <c r="M87" t="n">
         <v>154738000000</v>
       </c>
-      <c r="N85" t="n">
-        <v>485847979890</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="N87" t="n">
+        <v>491228356190</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
         <is>
           <t>株式会社フェローテック
 （旧会社名　株式会社フェローテックホールディングス）</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>6890</t>
         </is>
       </c>
-      <c r="C86" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="D86" t="n">
-        <v>9030</v>
-      </c>
-      <c r="E86" t="n">
+      <c r="C88" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="D88" t="n">
+        <v>9130</v>
+      </c>
+      <c r="E88" t="n">
         <v>2030</v>
       </c>
-      <c r="F86" t="n">
-        <v>344.8</v>
-      </c>
-      <c r="G86" t="inlineStr">
+      <c r="F88" t="n">
+        <v>349.8</v>
+      </c>
+      <c r="G88" t="inlineStr">
         <is>
           <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>2025-10-22</t>
         </is>
       </c>
-      <c r="I86" t="n">
+      <c r="I88" t="n">
         <v>52579000000</v>
       </c>
-      <c r="J86" t="n">
+      <c r="J88" t="n">
         <v>90505000000</v>
       </c>
-      <c r="K86" t="n">
+      <c r="K88" t="n">
         <v>11654000000</v>
       </c>
-      <c r="L86" t="n">
+      <c r="L88" t="n">
         <v>160957000000</v>
       </c>
-      <c r="M86" t="n">
+      <c r="M88" t="n">
         <v>154738000000</v>
       </c>
-      <c r="N86" t="n">
-        <v>485847979890</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="N88" t="n">
+        <v>491228356190</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
         <is>
           <t>株式会社フェローテック
 （旧会社名　株式会社フェローテックホールディングス）</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>6890</t>
         </is>
       </c>
-      <c r="C87" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="D87" t="n">
-        <v>9030</v>
-      </c>
-      <c r="E87" t="n">
+      <c r="C89" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="D89" t="n">
+        <v>9130</v>
+      </c>
+      <c r="E89" t="n">
         <v>2387</v>
       </c>
-      <c r="F87" t="n">
-        <v>278.3</v>
-      </c>
-      <c r="G87" t="inlineStr">
+      <c r="F89" t="n">
+        <v>282.5</v>
+      </c>
+      <c r="G89" t="inlineStr">
         <is>
           <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>2025-03-07</t>
         </is>
       </c>
-      <c r="I87" t="n">
+      <c r="I89" t="n">
         <v>52579000000</v>
       </c>
-      <c r="J87" t="n">
+      <c r="J89" t="n">
         <v>90505000000</v>
       </c>
-      <c r="K87" t="n">
+      <c r="K89" t="n">
         <v>11654000000</v>
       </c>
-      <c r="L87" t="n">
+      <c r="L89" t="n">
         <v>160957000000</v>
       </c>
-      <c r="M87" t="n">
+      <c r="M89" t="n">
         <v>154738000000</v>
       </c>
-      <c r="N87" t="n">
-        <v>485847979890</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>アツギ株式会社</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>3529</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="D88" t="n">
-        <v>1046</v>
-      </c>
-      <c r="E88" t="n">
-        <v>668.9358717434869</v>
-      </c>
-      <c r="F88" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="I88" t="n">
-        <v>5500000000</v>
-      </c>
-      <c r="J88" t="n">
-        <v>3208000000</v>
-      </c>
-      <c r="K88" t="n">
-        <v>3702000000</v>
-      </c>
-      <c r="L88" t="n">
-        <v>32145000000</v>
-      </c>
-      <c r="M88" t="n">
-        <v>12410000000</v>
-      </c>
-      <c r="N88" t="n">
-        <v>16750650276</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>日本特殊塗料株式会社</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>4619</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>70.09999999999999</v>
-      </c>
-      <c r="D89" t="n">
-        <v>2714</v>
-      </c>
-      <c r="E89" t="n">
-        <v>1190</v>
-      </c>
-      <c r="F89" t="n">
-        <v>128.1</v>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="I89" t="n">
-        <v>8931000000</v>
-      </c>
-      <c r="J89" t="n">
-        <v>9514000000</v>
-      </c>
-      <c r="K89" t="n">
-        <v>22055000000</v>
-      </c>
-      <c r="L89" t="n">
-        <v>49725000000</v>
-      </c>
-      <c r="M89" t="n">
-        <v>40500000000</v>
-      </c>
       <c r="N89" t="n">
-        <v>57786072758</v>
+        <v>491228356190</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>株式会社エクセディ</t>
+          <t>アツギ株式会社</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>7278</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>18.8</v>
+        <v>74.5</v>
       </c>
       <c r="D90" t="n">
-        <v>5990</v>
+        <v>1040</v>
       </c>
       <c r="E90" t="n">
-        <v>2617.980935875217</v>
+        <v>668.9358717434869</v>
       </c>
       <c r="F90" t="n">
-        <v>128.8</v>
+        <v>55.5</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>30019000000</v>
+        <v>5500000000</v>
       </c>
       <c r="J90" t="n">
-        <v>6792000000</v>
+        <v>3208000000</v>
       </c>
       <c r="K90" t="n">
-        <v>3427000000</v>
+        <v>3702000000</v>
       </c>
       <c r="L90" t="n">
-        <v>119460000000</v>
+        <v>32145000000</v>
       </c>
       <c r="M90" t="n">
-        <v>40238000000</v>
+        <v>12410000000</v>
       </c>
       <c r="N90" t="n">
-        <v>214403460340</v>
+        <v>16654566240</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>株式会社Ａ＆Ｄホロンホールディングス</t>
+          <t>日本特殊塗料株式会社</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>7745</t>
+          <t>4619</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>19.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D91" t="n">
-        <v>2896</v>
+        <v>2696</v>
       </c>
       <c r="E91" t="n">
-        <v>2084.177692465894</v>
+        <v>1190</v>
       </c>
       <c r="F91" t="n">
-        <v>39</v>
+        <v>126.6</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>11012000000</v>
+        <v>8931000000</v>
       </c>
       <c r="J91" t="n">
-        <v>4106000000</v>
+        <v>9514000000</v>
       </c>
       <c r="K91" t="n">
-        <v>315000000</v>
+        <v>22055000000</v>
       </c>
       <c r="L91" t="n">
-        <v>27041000000</v>
+        <v>49725000000</v>
       </c>
       <c r="M91" t="n">
-        <v>15433000000</v>
+        <v>40500000000</v>
       </c>
       <c r="N91" t="n">
-        <v>79313681616</v>
+        <v>57402819512</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>株式会社セプテーニ・ホールディングス</t>
+          <t>株式会社エクセディ</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>4293</t>
+          <t>7278</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>13.1</v>
+        <v>19</v>
       </c>
       <c r="D92" t="n">
-        <v>514</v>
+        <v>5930</v>
       </c>
       <c r="E92" t="n">
-        <v>448.6811097117532</v>
+        <v>2617.980935875217</v>
       </c>
       <c r="F92" t="n">
-        <v>14.6</v>
+        <v>126.5</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>12184507000</v>
+        <v>30019000000</v>
       </c>
       <c r="J92" t="n">
-        <v>168073000</v>
+        <v>6792000000</v>
       </c>
       <c r="K92" t="n">
-        <v>1600720000</v>
+        <v>3427000000</v>
       </c>
       <c r="L92" t="n">
-        <v>11861578000</v>
+        <v>119460000000</v>
       </c>
       <c r="M92" t="n">
-        <v>13953300000</v>
+        <v>40238000000</v>
       </c>
       <c r="N92" t="n">
-        <v>106626786026</v>
+        <v>212255846380</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>株式会社シンクロ・フード</t>
+          <t>株式会社Ａ＆Ｄホロンホールディングス</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>7745</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>33.7</v>
+        <v>19.5</v>
       </c>
       <c r="D93" t="n">
-        <v>329</v>
+        <v>2894</v>
       </c>
       <c r="E93" t="n">
-        <v>421.6950726175476</v>
+        <v>2084.177692465894</v>
       </c>
       <c r="F93" t="n">
-        <v>-22</v>
+        <v>38.9</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3037851000</v>
+        <v>11012000000</v>
       </c>
       <c r="J93" t="n">
-        <v>56852000</v>
+        <v>4106000000</v>
       </c>
       <c r="K93" t="n">
-        <v>14952000</v>
+        <v>315000000</v>
       </c>
       <c r="L93" t="n">
-        <v>2871237000</v>
+        <v>27041000000</v>
       </c>
       <c r="M93" t="n">
-        <v>3109655000</v>
+        <v>15433000000</v>
       </c>
       <c r="N93" t="n">
-        <v>9226011452</v>
+        <v>79258906974</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>科研製薬株式会社</t>
+          <t>株式会社セプテーニ・ホールディングス</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>4293</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>70</v>
+        <v>13.3</v>
       </c>
       <c r="D94" t="n">
-        <v>4005</v>
+        <v>506</v>
       </c>
       <c r="E94" t="n">
-        <v>3530</v>
+        <v>448.6811097117532</v>
       </c>
       <c r="F94" t="n">
-        <v>13.5</v>
+        <v>12.8</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>74625000000</v>
+        <v>12184507000</v>
       </c>
       <c r="J94" t="n">
-        <v>15530000000</v>
+        <v>168073000</v>
       </c>
       <c r="K94" t="n">
-        <v>15992000000</v>
+        <v>1600720000</v>
       </c>
       <c r="L94" t="n">
-        <v>138325000000</v>
+        <v>11861578000</v>
       </c>
       <c r="M94" t="n">
-        <v>106147000000</v>
+        <v>13953300000</v>
       </c>
       <c r="N94" t="n">
-        <v>151662601575</v>
+        <v>104967225154</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>市光工業株式会社</t>
+          <t>株式会社シンクロ・フード</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>7244</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>35.1</v>
+        <v>33.6</v>
       </c>
       <c r="D95" t="n">
-        <v>566</v>
+        <v>330</v>
       </c>
       <c r="E95" t="n">
-        <v>549.4799823005444</v>
+        <v>421.6950726175476</v>
       </c>
       <c r="F95" t="n">
-        <v>3</v>
+        <v>-21.7</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>5720000000</v>
+        <v>3037851000</v>
       </c>
       <c r="J95" t="n">
-        <v>9921000000</v>
+        <v>56852000</v>
       </c>
       <c r="K95" t="n">
-        <v>3474000000</v>
+        <v>14952000</v>
       </c>
       <c r="L95" t="n">
-        <v>49523000000</v>
+        <v>2871237000</v>
       </c>
       <c r="M95" t="n">
-        <v>19115000000</v>
+        <v>3109655000</v>
       </c>
       <c r="N95" t="n">
-        <v>54508296060</v>
+        <v>9254054040</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>トーセイ株式会社</t>
+          <t>科研製薬株式会社</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>4521</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>46.4</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="D96" t="n">
-        <v>1692</v>
+        <v>3980</v>
       </c>
       <c r="E96" t="n">
-        <v>1752.426893379333</v>
+        <v>3530</v>
       </c>
       <c r="F96" t="n">
-        <v>-3.4</v>
+        <v>12.7</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>20753937000</v>
+        <v>74625000000</v>
       </c>
       <c r="J96" t="n">
-        <v>46868512000</v>
+        <v>15530000000</v>
       </c>
       <c r="K96" t="n">
-        <v>8610046000</v>
+        <v>15992000000</v>
       </c>
       <c r="L96" t="n">
-        <v>59467346000</v>
+        <v>138325000000</v>
       </c>
       <c r="M96" t="n">
-        <v>76232495000</v>
+        <v>106147000000</v>
       </c>
       <c r="N96" t="n">
-        <v>164134321200</v>
+        <v>150715893700</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>トーセイ株式会社</t>
+          <t>市光工業株式会社</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>46.4</v>
+        <v>35.1</v>
       </c>
       <c r="D97" t="n">
-        <v>1692</v>
+        <v>565</v>
       </c>
       <c r="E97" t="n">
-        <v>1576.721867844292</v>
+        <v>549.4799823005444</v>
       </c>
       <c r="F97" t="n">
-        <v>7.3</v>
+        <v>2.8</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>20753937000</v>
+        <v>5720000000</v>
       </c>
       <c r="J97" t="n">
-        <v>46868512000</v>
+        <v>9921000000</v>
       </c>
       <c r="K97" t="n">
-        <v>8610046000</v>
+        <v>3474000000</v>
       </c>
       <c r="L97" t="n">
-        <v>59467346000</v>
+        <v>49523000000</v>
       </c>
       <c r="M97" t="n">
-        <v>76232495000</v>
+        <v>19115000000</v>
       </c>
       <c r="N97" t="n">
-        <v>164134321200</v>
+        <v>54411991650</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>株式会社髙島屋</t>
+          <t>トーセイ株式会社</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>64.09999999999999</v>
+        <v>45.6</v>
       </c>
       <c r="D98" t="n">
-        <v>2140.5</v>
+        <v>1724</v>
       </c>
       <c r="E98" t="n">
-        <v>1101.400153022188</v>
+        <v>1752.426893379333</v>
       </c>
       <c r="F98" t="n">
-        <v>94.3</v>
+        <v>-1.6</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>88996000000</v>
+        <v>20753937000</v>
       </c>
       <c r="J98" t="n">
-        <v>193090000000</v>
+        <v>46868512000</v>
       </c>
       <c r="K98" t="n">
-        <v>119967000000</v>
+        <v>8610046000</v>
       </c>
       <c r="L98" t="n">
-        <v>420489000000</v>
+        <v>59467346000</v>
       </c>
       <c r="M98" t="n">
-        <v>402053000000</v>
+        <v>76232495000</v>
       </c>
       <c r="N98" t="n">
-        <v>627197323200</v>
+        <v>167238516400</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>株式会社髙島屋</t>
+          <t>トーセイ株式会社</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>64.09999999999999</v>
+        <v>45.6</v>
       </c>
       <c r="D99" t="n">
-        <v>2140.5</v>
+        <v>1724</v>
       </c>
       <c r="E99" t="n">
-        <v>1101.400153022188</v>
+        <v>1576.721867844292</v>
       </c>
       <c r="F99" t="n">
-        <v>94.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>88996000000</v>
+        <v>20753937000</v>
       </c>
       <c r="J99" t="n">
-        <v>193090000000</v>
+        <v>46868512000</v>
       </c>
       <c r="K99" t="n">
-        <v>119967000000</v>
+        <v>8610046000</v>
       </c>
       <c r="L99" t="n">
-        <v>420489000000</v>
+        <v>59467346000</v>
       </c>
       <c r="M99" t="n">
-        <v>402053000000</v>
+        <v>76232495000</v>
       </c>
       <c r="N99" t="n">
-        <v>627197323200</v>
+        <v>167238516400</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>三井倉庫ホールディングス株式会社</t>
+          <t>株式会社髙島屋</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>9302</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>43.9</v>
+        <v>64.8</v>
       </c>
       <c r="D100" t="n">
-        <v>3423</v>
+        <v>2117</v>
       </c>
       <c r="E100" t="n">
-        <v>1492.806001579363</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="F100" t="n">
-        <v>129.3</v>
+        <v>92.2</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>22822000000</v>
+        <v>88996000000</v>
       </c>
       <c r="J100" t="n">
-        <v>72331000000</v>
+        <v>193090000000</v>
       </c>
       <c r="K100" t="n">
-        <v>17148000000</v>
+        <v>119967000000</v>
       </c>
       <c r="L100" t="n">
-        <v>88631000000</v>
+        <v>420489000000</v>
       </c>
       <c r="M100" t="n">
-        <v>112301000000</v>
+        <v>402053000000</v>
       </c>
       <c r="N100" t="n">
-        <v>256055067555</v>
+        <v>620311484800</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>京阪神ビルディング株式会社</t>
+          <t>株式会社髙島屋</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>8818</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>80.2</v>
+        <v>64.8</v>
       </c>
       <c r="D101" t="n">
-        <v>1133</v>
+        <v>2117</v>
       </c>
       <c r="E101" t="n">
-        <v>1341.977644710579</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="F101" t="n">
-        <v>-15.6</v>
+        <v>92.2</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>9876000000</v>
+        <v>88996000000</v>
       </c>
       <c r="J101" t="n">
-        <v>54379000000</v>
+        <v>193090000000</v>
       </c>
       <c r="K101" t="n">
-        <v>22399000000</v>
+        <v>119967000000</v>
       </c>
       <c r="L101" t="n">
-        <v>70510000000</v>
+        <v>420489000000</v>
       </c>
       <c r="M101" t="n">
-        <v>86654000000</v>
+        <v>402053000000</v>
       </c>
       <c r="N101" t="n">
-        <v>108093482046</v>
+        <v>620311484800</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>株式会社メルカリ</t>
+          <t>三井倉庫ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>9302</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>28.9</v>
+        <v>44</v>
       </c>
       <c r="D102" t="n">
-        <v>3672</v>
+        <v>3409</v>
       </c>
       <c r="E102" t="n">
-        <v>2006.059650428343</v>
+        <v>1492.806001579363</v>
       </c>
       <c r="F102" t="n">
-        <v>83</v>
+        <v>128.4</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>171463000000</v>
+        <v>22822000000</v>
       </c>
       <c r="J102" t="n">
-        <v>434000000</v>
+        <v>72331000000</v>
       </c>
       <c r="K102" t="n">
-        <v>1543000000</v>
+        <v>17148000000</v>
       </c>
       <c r="L102" t="n">
-        <v>40013000000</v>
+        <v>88631000000</v>
       </c>
       <c r="M102" t="n">
-        <v>173440000000</v>
+        <v>112301000000</v>
       </c>
       <c r="N102" t="n">
-        <v>599199225624</v>
+        <v>255007807565</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>サッポロホールディングス株式会社</t>
+          <t>京阪神ビルディング株式会社</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2501</t>
+          <t>8818</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1</v>
+        <v>80.8</v>
       </c>
       <c r="D103" t="n">
-        <v>1909</v>
+        <v>1124</v>
       </c>
       <c r="E103" t="n">
-        <v>2697.360927565142</v>
+        <v>1341.977644710579</v>
       </c>
       <c r="F103" t="n">
-        <v>-29.2</v>
+        <v>-16.2</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2925000000</v>
+        <v>9876000000</v>
       </c>
       <c r="J103" t="n">
-        <v>23000000</v>
+        <v>54379000000</v>
       </c>
       <c r="K103" t="n">
-        <v>4391000000</v>
+        <v>22399000000</v>
       </c>
       <c r="L103" t="n">
-        <v>142395000000</v>
+        <v>70510000000</v>
       </c>
       <c r="M103" t="n">
-        <v>7339000000</v>
+        <v>86654000000</v>
       </c>
       <c r="N103" t="n">
-        <v>744458437910</v>
+        <v>107234840088</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>株式会社クレハ</t>
+          <t>株式会社メルカリ</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>18.5</v>
+        <v>28.7</v>
       </c>
       <c r="D104" t="n">
-        <v>4225</v>
+        <v>3699</v>
       </c>
       <c r="E104" t="n">
-        <v>7960</v>
+        <v>2006.059650428343</v>
       </c>
       <c r="F104" t="n">
-        <v>-46.9</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>5294000000</v>
+        <v>171463000000</v>
       </c>
       <c r="J104" t="n">
-        <v>5963000000</v>
+        <v>434000000</v>
       </c>
       <c r="K104" t="n">
-        <v>18608000000</v>
+        <v>1543000000</v>
       </c>
       <c r="L104" t="n">
-        <v>155874000000</v>
+        <v>40013000000</v>
       </c>
       <c r="M104" t="n">
-        <v>29865000000</v>
+        <v>173440000000</v>
       </c>
       <c r="N104" t="n">
-        <v>161483953150</v>
+        <v>603605102283</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>コムシスホールディングス株式会社</t>
+          <t>サッポロホールディングス株式会社</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>17.1</v>
+        <v>1</v>
       </c>
       <c r="D105" t="n">
-        <v>5648</v>
+        <v>1848</v>
       </c>
       <c r="E105" t="n">
-        <v>3953.24613842911</v>
+        <v>2697.360927565142</v>
       </c>
       <c r="F105" t="n">
-        <v>42.9</v>
+        <v>-31.5</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>34033000000</v>
+        <v>2925000000</v>
       </c>
       <c r="J105" t="n">
-        <v>45394000000</v>
+        <v>23000000</v>
       </c>
       <c r="K105" t="n">
-        <v>31261000000</v>
+        <v>4391000000</v>
       </c>
       <c r="L105" t="n">
-        <v>343489000000</v>
+        <v>142395000000</v>
       </c>
       <c r="M105" t="n">
-        <v>110688000000</v>
+        <v>7339000000</v>
       </c>
       <c r="N105" t="n">
-        <v>646431396848</v>
+        <v>720670085520</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>コムシスホールディングス株式会社</t>
+          <t>株式会社クレハ</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>4023</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>17.1</v>
+        <v>18.8</v>
       </c>
       <c r="D106" t="n">
-        <v>5648</v>
+        <v>4160</v>
       </c>
       <c r="E106" t="n">
-        <v>3735.709461270437</v>
+        <v>7960</v>
       </c>
       <c r="F106" t="n">
-        <v>51.2</v>
+        <v>-47.7</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>34033000000</v>
+        <v>5294000000</v>
       </c>
       <c r="J106" t="n">
-        <v>45394000000</v>
+        <v>5963000000</v>
       </c>
       <c r="K106" t="n">
-        <v>31261000000</v>
+        <v>18608000000</v>
       </c>
       <c r="L106" t="n">
-        <v>343489000000</v>
+        <v>155874000000</v>
       </c>
       <c r="M106" t="n">
-        <v>110688000000</v>
+        <v>29865000000</v>
       </c>
       <c r="N106" t="n">
-        <v>646431396848</v>
+        <v>158999584640</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>サクサ株式会社</t>
+          <t>コムシスホールディングス株式会社</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>6675</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>29.1</v>
+        <v>16.5</v>
       </c>
       <c r="D107" t="n">
-        <v>2212</v>
+        <v>5868</v>
       </c>
       <c r="E107" t="n">
-        <v>5463.67048346056</v>
+        <v>3953.24613842911</v>
       </c>
       <c r="F107" t="n">
-        <v>-59.5</v>
+        <v>48.4</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>6993000000</v>
+        <v>34033000000</v>
       </c>
       <c r="J107" t="n">
-        <v>1323000000</v>
+        <v>45394000000</v>
       </c>
       <c r="K107" t="n">
-        <v>2933000000</v>
+        <v>31261000000</v>
       </c>
       <c r="L107" t="n">
-        <v>23497000000</v>
+        <v>343489000000</v>
       </c>
       <c r="M107" t="n">
-        <v>11249000000</v>
+        <v>110688000000</v>
       </c>
       <c r="N107" t="n">
-        <v>38691397080</v>
+        <v>671611090068</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>愛知製鋼株式会社</t>
+          <t>コムシスホールディングス株式会社</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>33.5</v>
+        <v>16.5</v>
       </c>
       <c r="D108" t="n">
-        <v>3275</v>
+        <v>5868</v>
       </c>
       <c r="E108" t="n">
-        <v>3155.301177013616</v>
+        <v>3735.709461270437</v>
       </c>
       <c r="F108" t="n">
-        <v>3.8</v>
+        <v>57.1</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>32866000000</v>
+        <v>34033000000</v>
       </c>
       <c r="J108" t="n">
-        <v>11000000000</v>
+        <v>45394000000</v>
       </c>
       <c r="K108" t="n">
-        <v>26614000000</v>
+        <v>31261000000</v>
       </c>
       <c r="L108" t="n">
-        <v>186904000000</v>
+        <v>343489000000</v>
       </c>
       <c r="M108" t="n">
-        <v>70480000000</v>
+        <v>110688000000</v>
       </c>
       <c r="N108" t="n">
-        <v>210408263450</v>
+        <v>671611090068</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>株式会社インターネットイニシアティブ</t>
+          <t>サクサ株式会社</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>3774</t>
+          <t>6675</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>5.4</v>
+        <v>28.9</v>
       </c>
       <c r="D109" t="n">
-        <v>3436</v>
+        <v>2224</v>
       </c>
       <c r="E109" t="n">
-        <v>2655.311711736394</v>
+        <v>5463.67048346056</v>
       </c>
       <c r="F109" t="n">
-        <v>29.4</v>
+        <v>-59.3</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>16367000000</v>
+        <v>6993000000</v>
       </c>
       <c r="J109" t="n">
-        <v>1522000000</v>
+        <v>1323000000</v>
       </c>
       <c r="K109" t="n">
-        <v>15226000000</v>
+        <v>2933000000</v>
       </c>
       <c r="L109" t="n">
-        <v>87924000000</v>
+        <v>23497000000</v>
       </c>
       <c r="M109" t="n">
-        <v>33115000000</v>
+        <v>11249000000</v>
       </c>
       <c r="N109" t="n">
-        <v>609305897180</v>
+        <v>38901296160</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>コクヨ株式会社</t>
+          <t>愛知製鋼株式会社</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>7984</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>40.6</v>
+        <v>34</v>
       </c>
       <c r="D110" t="n">
-        <v>909.4000244140625</v>
+        <v>3230</v>
       </c>
       <c r="E110" t="n">
-        <v>2157.626835069302</v>
+        <v>3155.301177013616</v>
       </c>
       <c r="F110" t="n">
-        <v>-57.9</v>
+        <v>2.4</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>100575000000</v>
+        <v>32866000000</v>
       </c>
       <c r="J110" t="n">
-        <v>22282000000</v>
+        <v>11000000000</v>
       </c>
       <c r="K110" t="n">
-        <v>30106000000</v>
+        <v>26614000000</v>
       </c>
       <c r="L110" t="n">
-        <v>230105000000</v>
+        <v>186904000000</v>
       </c>
       <c r="M110" t="n">
-        <v>152963000000</v>
+        <v>70480000000</v>
       </c>
       <c r="N110" t="n">
-        <v>376891810686</v>
+        <v>207517157540</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>株式会社メルカリ</t>
+          <t>株式会社インターネットイニシアティブ</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>35.5</v>
+        <v>5.4</v>
       </c>
       <c r="D111" t="n">
-        <v>3672</v>
+        <v>3430</v>
       </c>
       <c r="E111" t="n">
-        <v>2006.059650428343</v>
+        <v>2655.311711736394</v>
       </c>
       <c r="F111" t="n">
-        <v>83</v>
+        <v>29.2</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -6174,102 +6174,102 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>211406000000</v>
+        <v>16367000000</v>
       </c>
       <c r="J111" t="n">
-        <v>367000000</v>
+        <v>1522000000</v>
       </c>
       <c r="K111" t="n">
-        <v>1021000000</v>
+        <v>15226000000</v>
       </c>
       <c r="L111" t="n">
-        <v>37998000000</v>
+        <v>87924000000</v>
       </c>
       <c r="M111" t="n">
-        <v>212794000000</v>
+        <v>33115000000</v>
       </c>
       <c r="N111" t="n">
-        <v>599199225624</v>
+        <v>608241917150</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>三菱製紙株式会社</t>
+          <t>コクヨ株式会社</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>7984</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>94.09999999999999</v>
+        <v>41.3</v>
       </c>
       <c r="D112" t="n">
-        <v>1220</v>
+        <v>892.7999877929688</v>
       </c>
       <c r="E112" t="n">
-        <v>810</v>
+        <v>2157.626835069302</v>
       </c>
       <c r="F112" t="n">
-        <v>50.6</v>
+        <v>-58.6</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>9047000000</v>
+        <v>100575000000</v>
       </c>
       <c r="J112" t="n">
-        <v>16443000000</v>
+        <v>22282000000</v>
       </c>
       <c r="K112" t="n">
-        <v>24813000000</v>
+        <v>30106000000</v>
       </c>
       <c r="L112" t="n">
-        <v>69613000000</v>
+        <v>230105000000</v>
       </c>
       <c r="M112" t="n">
-        <v>50303000000</v>
+        <v>152963000000</v>
       </c>
       <c r="N112" t="n">
-        <v>53445978380</v>
+        <v>370012090330</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>株式会社プラスアルファ・コンサルティング</t>
+          <t>株式会社メルカリ</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>4071</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>9.6</v>
+        <v>35.3</v>
       </c>
       <c r="D113" t="n">
-        <v>2122</v>
+        <v>3699</v>
       </c>
       <c r="E113" t="n">
-        <v>2300.974351689521</v>
+        <v>2006.059650428343</v>
       </c>
       <c r="F113" t="n">
-        <v>-7.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -6278,130 +6278,130 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>8278003000</v>
+        <v>211406000000</v>
       </c>
       <c r="J113" t="n">
-        <v>271170000</v>
+        <v>367000000</v>
       </c>
       <c r="K113" t="n">
-        <v>0</v>
+        <v>1021000000</v>
       </c>
       <c r="L113" t="n">
-        <v>9445733000</v>
+        <v>37998000000</v>
       </c>
       <c r="M113" t="n">
-        <v>8549173000</v>
+        <v>212794000000</v>
       </c>
       <c r="N113" t="n">
-        <v>89029677100</v>
+        <v>603605102283</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>東亜道路工業株式会社</t>
+          <t>三菱製紙株式会社</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>3864</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>39.4</v>
+        <v>93.7</v>
       </c>
       <c r="D114" t="n">
-        <v>1620</v>
+        <v>1225</v>
       </c>
       <c r="E114" t="n">
-        <v>1180.253227905114</v>
+        <v>810</v>
       </c>
       <c r="F114" t="n">
-        <v>37.3</v>
+        <v>51.2</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>11649000000</v>
+        <v>9047000000</v>
       </c>
       <c r="J114" t="n">
-        <v>13793000000</v>
+        <v>16443000000</v>
       </c>
       <c r="K114" t="n">
-        <v>4087000000</v>
+        <v>24813000000</v>
       </c>
       <c r="L114" t="n">
-        <v>50605000000</v>
+        <v>69613000000</v>
       </c>
       <c r="M114" t="n">
-        <v>29529000000</v>
+        <v>50303000000</v>
       </c>
       <c r="N114" t="n">
-        <v>74856292560</v>
+        <v>53665019275</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>東亜道路工業株式会社</t>
+          <t>株式会社プラスアルファ・コンサルティング</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>4071</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>39.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D115" t="n">
-        <v>1620</v>
+        <v>2100</v>
       </c>
       <c r="E115" t="n">
-        <v>1180.31326635551</v>
+        <v>2300.974351689521</v>
       </c>
       <c r="F115" t="n">
-        <v>37.3</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>11649000000</v>
+        <v>8278003000</v>
       </c>
       <c r="J115" t="n">
-        <v>13793000000</v>
+        <v>271170000</v>
       </c>
       <c r="K115" t="n">
-        <v>4087000000</v>
+        <v>0</v>
       </c>
       <c r="L115" t="n">
-        <v>50605000000</v>
+        <v>9445733000</v>
       </c>
       <c r="M115" t="n">
-        <v>29529000000</v>
+        <v>8549173000</v>
       </c>
       <c r="N115" t="n">
-        <v>74856292560</v>
+        <v>88106655000</v>
       </c>
     </row>
     <row r="116">
@@ -6416,16 +6416,16 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>39.4</v>
+        <v>39.7</v>
       </c>
       <c r="D116" t="n">
-        <v>1620</v>
+        <v>1610</v>
       </c>
       <c r="E116" t="n">
-        <v>1180.406015389293</v>
+        <v>1180.253227905114</v>
       </c>
       <c r="F116" t="n">
-        <v>37.2</v>
+        <v>36.4</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="I116" t="n">
@@ -6453,7 +6453,7 @@
         <v>29529000000</v>
       </c>
       <c r="N116" t="n">
-        <v>74856292560</v>
+        <v>74394216680</v>
       </c>
     </row>
     <row r="117">
@@ -6468,16 +6468,16 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>39.4</v>
+        <v>39.7</v>
       </c>
       <c r="D117" t="n">
-        <v>1620</v>
+        <v>1610</v>
       </c>
       <c r="E117" t="n">
-        <v>1180.420176850555</v>
+        <v>1180.31326635551</v>
       </c>
       <c r="F117" t="n">
-        <v>37.2</v>
+        <v>36.4</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="I117" t="n">
@@ -6505,7 +6505,7 @@
         <v>29529000000</v>
       </c>
       <c r="N117" t="n">
-        <v>74856292560</v>
+        <v>74394216680</v>
       </c>
     </row>
     <row r="118">
@@ -6520,16 +6520,16 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>39.4</v>
+        <v>39.7</v>
       </c>
       <c r="D118" t="n">
-        <v>1620</v>
+        <v>1610</v>
       </c>
       <c r="E118" t="n">
-        <v>1180.431728045326</v>
+        <v>1180.406015389293</v>
       </c>
       <c r="F118" t="n">
-        <v>37.2</v>
+        <v>36.4</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="I118" t="n">
@@ -6557,7 +6557,7 @@
         <v>29529000000</v>
       </c>
       <c r="N118" t="n">
-        <v>74856292560</v>
+        <v>74394216680</v>
       </c>
     </row>
     <row r="119">
@@ -6572,16 +6572,16 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>39.4</v>
+        <v>39.7</v>
       </c>
       <c r="D119" t="n">
-        <v>1620</v>
+        <v>1610</v>
       </c>
       <c r="E119" t="n">
-        <v>1180.442269658324</v>
+        <v>1180.420176850555</v>
       </c>
       <c r="F119" t="n">
-        <v>37.2</v>
+        <v>36.4</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="I119" t="n">
@@ -6609,7 +6609,7 @@
         <v>29529000000</v>
       </c>
       <c r="N119" t="n">
-        <v>74856292560</v>
+        <v>74394216680</v>
       </c>
     </row>
     <row r="120">
@@ -6624,16 +6624,16 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>39.4</v>
+        <v>39.7</v>
       </c>
       <c r="D120" t="n">
-        <v>1620</v>
+        <v>1610</v>
       </c>
       <c r="E120" t="n">
-        <v>1180.450912709519</v>
+        <v>1180.431728045326</v>
       </c>
       <c r="F120" t="n">
-        <v>37.2</v>
+        <v>36.4</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="I120" t="n">
@@ -6661,7 +6661,7 @@
         <v>29529000000</v>
       </c>
       <c r="N120" t="n">
-        <v>74856292560</v>
+        <v>74394216680</v>
       </c>
     </row>
     <row r="121">
@@ -6676,16 +6676,16 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>39.4</v>
+        <v>39.7</v>
       </c>
       <c r="D121" t="n">
-        <v>1620</v>
+        <v>1610</v>
       </c>
       <c r="E121" t="n">
-        <v>1180.45745232471</v>
+        <v>1180.442269658324</v>
       </c>
       <c r="F121" t="n">
-        <v>37.2</v>
+        <v>36.4</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="I121" t="n">
@@ -6713,7 +6713,7 @@
         <v>29529000000</v>
       </c>
       <c r="N121" t="n">
-        <v>74856292560</v>
+        <v>74394216680</v>
       </c>
     </row>
     <row r="122">
@@ -6728,16 +6728,16 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>39.4</v>
+        <v>39.7</v>
       </c>
       <c r="D122" t="n">
-        <v>1620</v>
+        <v>1610</v>
       </c>
       <c r="E122" t="n">
-        <v>1180.463123164206</v>
+        <v>1180.450912709519</v>
       </c>
       <c r="F122" t="n">
-        <v>37.2</v>
+        <v>36.4</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="I122" t="n">
@@ -6765,7 +6765,7 @@
         <v>29529000000</v>
       </c>
       <c r="N122" t="n">
-        <v>74856292560</v>
+        <v>74394216680</v>
       </c>
     </row>
     <row r="123">
@@ -6780,16 +6780,16 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>39.4</v>
+        <v>39.7</v>
       </c>
       <c r="D123" t="n">
-        <v>1620</v>
+        <v>1610</v>
       </c>
       <c r="E123" t="n">
-        <v>1170.279952698077</v>
+        <v>1180.45745232471</v>
       </c>
       <c r="F123" t="n">
-        <v>38.4</v>
+        <v>36.4</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="I123" t="n">
@@ -6817,7 +6817,7 @@
         <v>29529000000</v>
       </c>
       <c r="N123" t="n">
-        <v>74856292560</v>
+        <v>74394216680</v>
       </c>
     </row>
     <row r="124">
@@ -6832,16 +6832,16 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>39.4</v>
+        <v>39.7</v>
       </c>
       <c r="D124" t="n">
-        <v>1620</v>
+        <v>1610</v>
       </c>
       <c r="E124" t="n">
-        <v>1169.924818603025</v>
+        <v>1180.463123164206</v>
       </c>
       <c r="F124" t="n">
-        <v>38.5</v>
+        <v>36.4</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="I124" t="n">
@@ -6869,7 +6869,7 @@
         <v>29529000000</v>
       </c>
       <c r="N124" t="n">
-        <v>74856292560</v>
+        <v>74394216680</v>
       </c>
     </row>
     <row r="125">
@@ -6884,16 +6884,16 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>39.4</v>
+        <v>39.7</v>
       </c>
       <c r="D125" t="n">
-        <v>1620</v>
+        <v>1610</v>
       </c>
       <c r="E125" t="n">
-        <v>1168.709522546084</v>
+        <v>1170.279952698077</v>
       </c>
       <c r="F125" t="n">
-        <v>38.6</v>
+        <v>37.6</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="I125" t="n">
@@ -6921,31 +6921,31 @@
         <v>29529000000</v>
       </c>
       <c r="N125" t="n">
-        <v>74856292560</v>
+        <v>74394216680</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>山洋電気株式会社</t>
+          <t>東亜道路工業株式会社</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>11.8</v>
+        <v>39.7</v>
       </c>
       <c r="D126" t="n">
-        <v>5260</v>
+        <v>1610</v>
       </c>
       <c r="E126" t="n">
-        <v>7052.737306843267</v>
+        <v>1169.924818603025</v>
       </c>
       <c r="F126" t="n">
-        <v>-25.4</v>
+        <v>37.6</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -6954,154 +6954,154 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>8317000000</v>
+        <v>11649000000</v>
       </c>
       <c r="J126" t="n">
-        <v>6048000000</v>
+        <v>13793000000</v>
       </c>
       <c r="K126" t="n">
-        <v>7673000000</v>
+        <v>4087000000</v>
       </c>
       <c r="L126" t="n">
-        <v>49734000000</v>
+        <v>50605000000</v>
       </c>
       <c r="M126" t="n">
-        <v>22038000000</v>
+        <v>29529000000</v>
       </c>
       <c r="N126" t="n">
-        <v>186809115660</v>
+        <v>74394216680</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ヘリオス テクノ ホールディング株式会社</t>
+          <t>東亜道路工業株式会社</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>54.4</v>
+        <v>39.7</v>
       </c>
       <c r="D127" t="n">
-        <v>969</v>
+        <v>1610</v>
       </c>
       <c r="E127" t="n">
-        <v>896.0103264198827</v>
+        <v>1168.709522546084</v>
       </c>
       <c r="F127" t="n">
-        <v>8.1</v>
+        <v>37.8</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>7851015000</v>
+        <v>11649000000</v>
       </c>
       <c r="J127" t="n">
-        <v>640317000</v>
+        <v>13793000000</v>
       </c>
       <c r="K127" t="n">
-        <v>1079200000</v>
+        <v>4087000000</v>
       </c>
       <c r="L127" t="n">
-        <v>13746774000</v>
+        <v>50605000000</v>
       </c>
       <c r="M127" t="n">
-        <v>9570532000</v>
+        <v>29529000000</v>
       </c>
       <c r="N127" t="n">
-        <v>17588965323</v>
+        <v>74394216680</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>シェアリングテクノロジー株式会社</t>
+          <t>山洋電気株式会社</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="D128" t="n">
-        <v>1545</v>
+        <v>5330</v>
       </c>
       <c r="E128" t="n">
-        <v>653.0713101160862</v>
+        <v>7052.737306843267</v>
       </c>
       <c r="F128" t="n">
-        <v>136.6</v>
+        <v>-24.4</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>4016706000</v>
+        <v>8317000000</v>
       </c>
       <c r="J128" t="n">
-        <v>309745000</v>
+        <v>6048000000</v>
       </c>
       <c r="K128" t="n">
-        <v>0</v>
+        <v>7673000000</v>
       </c>
       <c r="L128" t="n">
-        <v>185001000</v>
+        <v>49734000000</v>
       </c>
       <c r="M128" t="n">
-        <v>4326451000</v>
+        <v>22038000000</v>
       </c>
       <c r="N128" t="n">
-        <v>36973810605</v>
+        <v>189295168530</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>栄研化学株式会社</t>
+          <t>ヘリオス テクノ ホールディング株式会社</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>29.4</v>
+        <v>54.4</v>
       </c>
       <c r="D129" t="n">
-        <v>2361</v>
+        <v>970</v>
       </c>
       <c r="E129" t="n">
-        <v>1947.225264702313</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="F129" t="n">
-        <v>21.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -7110,50 +7110,50 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>10900000000</v>
+        <v>7851015000</v>
       </c>
       <c r="J129" t="n">
-        <v>11585000000</v>
+        <v>640317000</v>
       </c>
       <c r="K129" t="n">
-        <v>408000000</v>
+        <v>1079200000</v>
       </c>
       <c r="L129" t="n">
-        <v>45803000000</v>
+        <v>13746774000</v>
       </c>
       <c r="M129" t="n">
-        <v>22893000000</v>
+        <v>9570532000</v>
       </c>
       <c r="N129" t="n">
-        <v>77831717853</v>
+        <v>17607116990</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>栄研化学株式会社</t>
+          <t>シェアリングテクノロジー株式会社</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>29.4</v>
+        <v>11.7</v>
       </c>
       <c r="D130" t="n">
-        <v>2361</v>
+        <v>1545</v>
       </c>
       <c r="E130" t="n">
-        <v>1678.083113259255</v>
+        <v>653.0713101160862</v>
       </c>
       <c r="F130" t="n">
-        <v>40.7</v>
+        <v>136.6</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -7162,154 +7162,154 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>10900000000</v>
+        <v>4016706000</v>
       </c>
       <c r="J130" t="n">
-        <v>11585000000</v>
+        <v>309745000</v>
       </c>
       <c r="K130" t="n">
-        <v>408000000</v>
+        <v>0</v>
       </c>
       <c r="L130" t="n">
-        <v>45803000000</v>
+        <v>185001000</v>
       </c>
       <c r="M130" t="n">
-        <v>22893000000</v>
+        <v>4326451000</v>
       </c>
       <c r="N130" t="n">
-        <v>77831717853</v>
+        <v>36973810605</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>株式会社ヤマダホールディングス</t>
+          <t>栄研化学株式会社</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>9831</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>57.5</v>
+        <v>29.3</v>
       </c>
       <c r="D131" t="n">
-        <v>724.7999877929688</v>
+        <v>2370</v>
       </c>
       <c r="E131" t="n">
-        <v>530</v>
+        <v>1947.225264702313</v>
       </c>
       <c r="F131" t="n">
-        <v>36.8</v>
+        <v>21.7</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>56470000000</v>
+        <v>10900000000</v>
       </c>
       <c r="J131" t="n">
-        <v>210733000000</v>
+        <v>11585000000</v>
       </c>
       <c r="K131" t="n">
-        <v>9997000000</v>
+        <v>408000000</v>
       </c>
       <c r="L131" t="n">
-        <v>676277000000</v>
+        <v>45803000000</v>
       </c>
       <c r="M131" t="n">
-        <v>277200000000</v>
+        <v>22893000000</v>
       </c>
       <c r="N131" t="n">
-        <v>481974185721</v>
+        <v>78128408010</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>日本化薬株式会社</t>
+          <t>栄研化学株式会社</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>34.6</v>
+        <v>29.3</v>
       </c>
       <c r="D132" t="n">
-        <v>2115</v>
+        <v>2370</v>
       </c>
       <c r="E132" t="n">
-        <v>1111.90611839092</v>
+        <v>1678.083113259255</v>
       </c>
       <c r="F132" t="n">
-        <v>90.2</v>
+        <v>41.2</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>52962000000</v>
+        <v>10900000000</v>
       </c>
       <c r="J132" t="n">
-        <v>48231000000</v>
+        <v>11585000000</v>
       </c>
       <c r="K132" t="n">
-        <v>4337000000</v>
+        <v>408000000</v>
       </c>
       <c r="L132" t="n">
-        <v>246425000000</v>
+        <v>45803000000</v>
       </c>
       <c r="M132" t="n">
-        <v>105530000000</v>
+        <v>22893000000</v>
       </c>
       <c r="N132" t="n">
-        <v>304958442735</v>
+        <v>78128408010</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>王子ホールディングス株式会社</t>
+          <t>株式会社ヤマダホールディングス</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>9831</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>40.8</v>
+        <v>58.2</v>
       </c>
       <c r="D133" t="n">
-        <v>888.9000244140625</v>
+        <v>715.7000122070312</v>
       </c>
       <c r="E133" t="n">
-        <v>590</v>
+        <v>530</v>
       </c>
       <c r="F133" t="n">
-        <v>50.7</v>
+        <v>35</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -7318,310 +7318,310 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>55474000000</v>
+        <v>56470000000</v>
       </c>
       <c r="J133" t="n">
-        <v>244732000000</v>
+        <v>210733000000</v>
       </c>
       <c r="K133" t="n">
-        <v>7434000000</v>
+        <v>9997000000</v>
       </c>
       <c r="L133" t="n">
-        <v>875470000000</v>
+        <v>676277000000</v>
       </c>
       <c r="M133" t="n">
-        <v>307640000000</v>
+        <v>277200000000</v>
       </c>
       <c r="N133" t="n">
-        <v>754884383781</v>
+        <v>475922925515</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>東邦ホールディングス株式会社</t>
+          <t>日本化薬株式会社</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>50.1</v>
+        <v>35.4</v>
       </c>
       <c r="D134" t="n">
-        <v>4048</v>
+        <v>2067.5</v>
       </c>
       <c r="E134" t="n">
-        <v>3405.914389596362</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="F134" t="n">
-        <v>18.9</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>90014000000</v>
+        <v>52962000000</v>
       </c>
       <c r="J134" t="n">
-        <v>34220000000</v>
+        <v>48231000000</v>
       </c>
       <c r="K134" t="n">
-        <v>7000000000</v>
+        <v>4337000000</v>
       </c>
       <c r="L134" t="n">
-        <v>241281000000</v>
+        <v>246425000000</v>
       </c>
       <c r="M134" t="n">
-        <v>131234000000</v>
+        <v>105530000000</v>
       </c>
       <c r="N134" t="n">
-        <v>261912169904</v>
+        <v>298109494258</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>東邦ホールディングス株式会社</t>
+          <t>王子ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>50.1</v>
+        <v>41.4</v>
       </c>
       <c r="D135" t="n">
-        <v>4048</v>
+        <v>875.7000122070312</v>
       </c>
       <c r="E135" t="n">
-        <v>2714.613787300615</v>
+        <v>590</v>
       </c>
       <c r="F135" t="n">
-        <v>49.1</v>
+        <v>48.4</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>90014000000</v>
+        <v>55474000000</v>
       </c>
       <c r="J135" t="n">
-        <v>34220000000</v>
+        <v>244732000000</v>
       </c>
       <c r="K135" t="n">
-        <v>7000000000</v>
+        <v>7434000000</v>
       </c>
       <c r="L135" t="n">
-        <v>241281000000</v>
+        <v>875470000000</v>
       </c>
       <c r="M135" t="n">
-        <v>131234000000</v>
+        <v>307640000000</v>
       </c>
       <c r="N135" t="n">
-        <v>261912169904</v>
+        <v>743674480747</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>株式会社アイネス</t>
+          <t>東邦ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>9742</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>33.8</v>
+        <v>51</v>
       </c>
       <c r="D136" t="n">
-        <v>2145</v>
+        <v>3979</v>
       </c>
       <c r="E136" t="n">
-        <v>1879.137815927515</v>
+        <v>3405.914389596362</v>
       </c>
       <c r="F136" t="n">
-        <v>14.1</v>
+        <v>16.8</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>9731000000</v>
+        <v>90014000000</v>
       </c>
       <c r="J136" t="n">
-        <v>5286000000</v>
+        <v>34220000000</v>
       </c>
       <c r="K136" t="n">
-        <v>100000000</v>
+        <v>7000000000</v>
       </c>
       <c r="L136" t="n">
-        <v>34620000000</v>
+        <v>241281000000</v>
       </c>
       <c r="M136" t="n">
-        <v>15117000000</v>
+        <v>131234000000</v>
       </c>
       <c r="N136" t="n">
-        <v>44664148815</v>
+        <v>257447757917</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>日本ゼオン株式会社</t>
+          <t>東邦ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>34.9</v>
+        <v>51</v>
       </c>
       <c r="D137" t="n">
-        <v>2409.5</v>
+        <v>3979</v>
       </c>
       <c r="E137" t="n">
-        <v>1721.078563209627</v>
+        <v>2714.613787300615</v>
       </c>
       <c r="F137" t="n">
-        <v>40</v>
+        <v>46.6</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>44521000000</v>
+        <v>90014000000</v>
       </c>
       <c r="J137" t="n">
-        <v>45382000000</v>
+        <v>34220000000</v>
       </c>
       <c r="K137" t="n">
-        <v>71191000000</v>
+        <v>7000000000</v>
       </c>
       <c r="L137" t="n">
-        <v>321836000000</v>
+        <v>241281000000</v>
       </c>
       <c r="M137" t="n">
-        <v>161094000000</v>
+        <v>131234000000</v>
       </c>
       <c r="N137" t="n">
-        <v>461046999116</v>
+        <v>257447757917</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>太陽ホールディングス株式会社</t>
+          <t>株式会社アイネス</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>9742</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>16.4</v>
+        <v>33.8</v>
       </c>
       <c r="D138" t="n">
-        <v>4730</v>
+        <v>2151</v>
       </c>
       <c r="E138" t="n">
-        <v>2199.643244598912</v>
+        <v>1879.137815927515</v>
       </c>
       <c r="F138" t="n">
-        <v>115</v>
+        <v>14.5</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>51152000000</v>
+        <v>9731000000</v>
       </c>
       <c r="J138" t="n">
-        <v>30337000000</v>
+        <v>5286000000</v>
       </c>
       <c r="K138" t="n">
-        <v>4870000000</v>
+        <v>100000000</v>
       </c>
       <c r="L138" t="n">
-        <v>85466000000</v>
+        <v>34620000000</v>
       </c>
       <c r="M138" t="n">
-        <v>86359000000</v>
+        <v>15117000000</v>
       </c>
       <c r="N138" t="n">
-        <v>526338705860</v>
+        <v>44789083497</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>太陽ホールディングス株式会社</t>
+          <t>日本ゼオン株式会社</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>16.4</v>
+        <v>35.2</v>
       </c>
       <c r="D139" t="n">
-        <v>4730</v>
+        <v>2394</v>
       </c>
       <c r="E139" t="n">
-        <v>3565.648720929983</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="F139" t="n">
-        <v>32.7</v>
+        <v>39.1</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -7630,50 +7630,50 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>51152000000</v>
+        <v>44521000000</v>
       </c>
       <c r="J139" t="n">
-        <v>30337000000</v>
+        <v>45382000000</v>
       </c>
       <c r="K139" t="n">
-        <v>4870000000</v>
+        <v>71191000000</v>
       </c>
       <c r="L139" t="n">
-        <v>85466000000</v>
+        <v>321836000000</v>
       </c>
       <c r="M139" t="n">
-        <v>86359000000</v>
+        <v>161094000000</v>
       </c>
       <c r="N139" t="n">
-        <v>526338705860</v>
+        <v>458081143758</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>株式会社エス・エム・エス</t>
+          <t>太陽ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>8.300000000000001</v>
+        <v>16.4</v>
       </c>
       <c r="D140" t="n">
-        <v>2676</v>
+        <v>4744</v>
       </c>
       <c r="E140" t="n">
-        <v>1478.127248828989</v>
+        <v>2199.643244598912</v>
       </c>
       <c r="F140" t="n">
-        <v>81</v>
+        <v>115.7</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -7682,102 +7682,102 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>14126000000</v>
+        <v>51152000000</v>
       </c>
       <c r="J140" t="n">
-        <v>1187000000</v>
+        <v>30337000000</v>
       </c>
       <c r="K140" t="n">
-        <v>2875000000</v>
+        <v>4870000000</v>
       </c>
       <c r="L140" t="n">
-        <v>29991000000</v>
+        <v>85466000000</v>
       </c>
       <c r="M140" t="n">
-        <v>18188000000</v>
+        <v>86359000000</v>
       </c>
       <c r="N140" t="n">
-        <v>219647281524</v>
+        <v>527896579408</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>アニコム ホールディングス株式会社</t>
+          <t>太陽ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>8715</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>40.2</v>
+        <v>16.4</v>
       </c>
       <c r="D141" t="n">
-        <v>1052</v>
+        <v>4744</v>
       </c>
       <c r="E141" t="n">
-        <v>656.2604975855553</v>
+        <v>3565.648720929983</v>
       </c>
       <c r="F141" t="n">
-        <v>60.3</v>
+        <v>33</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>27691000000</v>
+        <v>51152000000</v>
       </c>
       <c r="J141" t="n">
-        <v>3070000000</v>
+        <v>30337000000</v>
       </c>
       <c r="K141" t="n">
-        <v>3000000</v>
+        <v>4870000000</v>
       </c>
       <c r="L141" t="n">
-        <v>27316000000</v>
+        <v>85466000000</v>
       </c>
       <c r="M141" t="n">
-        <v>30764000000</v>
+        <v>86359000000</v>
       </c>
       <c r="N141" t="n">
-        <v>76607923440</v>
+        <v>527896579408</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>東京製鐵株式会社</t>
+          <t>株式会社エス・エム・エス</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>96.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D142" t="n">
-        <v>1797</v>
+        <v>2673</v>
       </c>
       <c r="E142" t="n">
-        <v>1605.452212379354</v>
+        <v>1478.127248828989</v>
       </c>
       <c r="F142" t="n">
-        <v>11.9</v>
+        <v>80.8</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -7786,94 +7786,102 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>68644000000</v>
+        <v>14126000000</v>
       </c>
       <c r="J142" t="n">
-        <v>33060000000</v>
+        <v>1187000000</v>
       </c>
       <c r="K142" t="n">
-        <v>75000000000</v>
+        <v>2875000000</v>
       </c>
       <c r="L142" t="n">
-        <v>158280000000</v>
+        <v>29991000000</v>
       </c>
       <c r="M142" t="n">
-        <v>176704000000</v>
+        <v>18188000000</v>
       </c>
       <c r="N142" t="n">
-        <v>182568265377</v>
+        <v>219401040177</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ウェーブロックホールディングス株式会社</t>
+          <t>アニコム ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>7940</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr"/>
-      <c r="D143" t="inlineStr"/>
+          <t>8715</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="D143" t="n">
+        <v>1050</v>
+      </c>
       <c r="E143" t="n">
-        <v>1010</v>
-      </c>
-      <c r="F143" t="inlineStr"/>
+        <v>656.2604975855553</v>
+      </c>
+      <c r="F143" t="n">
+        <v>60</v>
+      </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1961626000</v>
+        <v>27691000000</v>
       </c>
       <c r="J143" t="n">
-        <v>2544946000</v>
+        <v>3070000000</v>
       </c>
       <c r="K143" t="n">
-        <v>1068366000</v>
+        <v>3000000</v>
       </c>
       <c r="L143" t="n">
-        <v>13761535000</v>
+        <v>27316000000</v>
       </c>
       <c r="M143" t="n">
-        <v>5574938000</v>
-      </c>
-      <c r="N143" t="inlineStr"/>
+        <v>30764000000</v>
+      </c>
+      <c r="N143" t="n">
+        <v>76462281000</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>近畿車輛株式会社</t>
+          <t>東京製鐵株式会社</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>7122</t>
+          <t>5423</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>105.4</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="D144" t="n">
-        <v>2449</v>
+        <v>1776</v>
       </c>
       <c r="E144" t="n">
-        <v>2144.894901144641</v>
+        <v>1605.452212379354</v>
       </c>
       <c r="F144" t="n">
-        <v>14.2</v>
+        <v>10.6</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -7882,206 +7890,198 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>6847000000</v>
+        <v>68644000000</v>
       </c>
       <c r="J144" t="n">
-        <v>4580000000</v>
+        <v>33060000000</v>
       </c>
       <c r="K144" t="n">
-        <v>6329000000</v>
+        <v>75000000000</v>
       </c>
       <c r="L144" t="n">
-        <v>24474000000</v>
+        <v>158280000000</v>
       </c>
       <c r="M144" t="n">
-        <v>17756000000</v>
+        <v>176704000000</v>
       </c>
       <c r="N144" t="n">
-        <v>16849318369</v>
+        <v>180434746416</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>株式会社三陽商会</t>
+          <t>ウェーブロックホールディングス株式会社</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>8011</t>
-        </is>
-      </c>
-      <c r="C145" t="n">
-        <v>63.7</v>
-      </c>
-      <c r="D145" t="n">
-        <v>1368</v>
-      </c>
+          <t>7940</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr"/>
       <c r="E145" t="n">
-        <v>3321.975331035734</v>
-      </c>
-      <c r="F145" t="n">
-        <v>-58.8</v>
-      </c>
+        <v>1010</v>
+      </c>
+      <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>16287000000</v>
+        <v>1961626000</v>
       </c>
       <c r="J145" t="n">
-        <v>3021000000</v>
+        <v>2544946000</v>
       </c>
       <c r="K145" t="n">
-        <v>6298000000</v>
+        <v>1068366000</v>
       </c>
       <c r="L145" t="n">
-        <v>33920000000</v>
+        <v>13761535000</v>
       </c>
       <c r="M145" t="n">
-        <v>25606000000</v>
-      </c>
-      <c r="N145" t="n">
-        <v>40200091776</v>
-      </c>
+        <v>5574938000</v>
+      </c>
+      <c r="N145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>月島ホールディングス株式会社</t>
+          <t>近畿車輛株式会社</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>6332</t>
+          <t>7122</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>47.3</v>
+        <v>105.6</v>
       </c>
       <c r="D146" t="n">
-        <v>2730</v>
+        <v>2444</v>
       </c>
       <c r="E146" t="n">
-        <v>1410</v>
+        <v>2144.894901144641</v>
       </c>
       <c r="F146" t="n">
-        <v>93.59999999999999</v>
+        <v>13.9</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>28795000000</v>
+        <v>6847000000</v>
       </c>
       <c r="J146" t="n">
-        <v>22203000000</v>
+        <v>4580000000</v>
       </c>
       <c r="K146" t="n">
-        <v>100000000</v>
+        <v>6329000000</v>
       </c>
       <c r="L146" t="n">
-        <v>80949000000</v>
+        <v>24474000000</v>
       </c>
       <c r="M146" t="n">
-        <v>51098000000</v>
+        <v>17756000000</v>
       </c>
       <c r="N146" t="n">
-        <v>108111338790</v>
+        <v>16814917964</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>マネックスグループ株式会社</t>
+          <t>株式会社三陽商会</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>8698</t>
+          <t>8011</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>15.4</v>
+        <v>63.7</v>
       </c>
       <c r="D147" t="n">
-        <v>713</v>
+        <v>1368</v>
       </c>
       <c r="E147" t="n">
-        <v>510.1850530906719</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="F147" t="n">
-        <v>39.8</v>
+        <v>-58.8</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>17794000000</v>
+        <v>16287000000</v>
       </c>
       <c r="J147" t="n">
-        <v>412000000</v>
+        <v>3021000000</v>
       </c>
       <c r="K147" t="n">
-        <v>9312000000</v>
+        <v>6298000000</v>
       </c>
       <c r="L147" t="n">
-        <v>98001000000</v>
+        <v>33920000000</v>
       </c>
       <c r="M147" t="n">
-        <v>27518000000</v>
+        <v>25606000000</v>
       </c>
       <c r="N147" t="n">
-        <v>179222306692</v>
+        <v>40200091776</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>株式会社あおぞら銀行</t>
+          <t>月島ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>222.3</v>
+        <v>49.5</v>
       </c>
       <c r="D148" t="n">
-        <v>3524</v>
+        <v>2608</v>
       </c>
       <c r="E148" t="n">
-        <v>2190</v>
+        <v>1410</v>
       </c>
       <c r="F148" t="n">
-        <v>60.9</v>
+        <v>85</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -8090,154 +8090,154 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1061743000000</v>
+        <v>28795000000</v>
       </c>
       <c r="J148" t="n">
-        <v>22385000000</v>
+        <v>22203000000</v>
       </c>
       <c r="K148" t="n">
-        <v>0</v>
+        <v>100000000</v>
       </c>
       <c r="L148" t="n">
-        <v>487265000000</v>
+        <v>80949000000</v>
       </c>
       <c r="M148" t="n">
-        <v>1084128000000</v>
+        <v>51098000000</v>
       </c>
       <c r="N148" t="n">
-        <v>487654911824</v>
+        <v>103279989584</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>日本製紙株式会社</t>
+          <t>マネックスグループ株式会社</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>8698</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>299.7</v>
+        <v>15.4</v>
       </c>
       <c r="D149" t="n">
-        <v>1334</v>
+        <v>712</v>
       </c>
       <c r="E149" t="n">
-        <v>1250</v>
+        <v>510.1850530906719</v>
       </c>
       <c r="F149" t="n">
-        <v>6.7</v>
+        <v>39.6</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>136216000000</v>
+        <v>17794000000</v>
       </c>
       <c r="J149" t="n">
-        <v>151771000000</v>
+        <v>412000000</v>
       </c>
       <c r="K149" t="n">
-        <v>172984000000</v>
+        <v>9312000000</v>
       </c>
       <c r="L149" t="n">
-        <v>438604000000</v>
+        <v>98001000000</v>
       </c>
       <c r="M149" t="n">
-        <v>460971000000</v>
+        <v>27518000000</v>
       </c>
       <c r="N149" t="n">
-        <v>153821543002</v>
+        <v>178970943008</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>カルビー株式会社</t>
+          <t>株式会社あおぞら銀行</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>32.9</v>
+        <v>224.7</v>
       </c>
       <c r="D150" t="n">
-        <v>3076</v>
+        <v>3486</v>
       </c>
       <c r="E150" t="n">
-        <v>2919.137515755844</v>
+        <v>2190</v>
       </c>
       <c r="F150" t="n">
-        <v>5.4</v>
+        <v>59.2</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>49670000000</v>
+        <v>1061743000000</v>
       </c>
       <c r="J150" t="n">
-        <v>70285000000</v>
+        <v>22385000000</v>
       </c>
       <c r="K150" t="n">
-        <v>3263000000</v>
+        <v>0</v>
       </c>
       <c r="L150" t="n">
-        <v>183458000000</v>
+        <v>487265000000</v>
       </c>
       <c r="M150" t="n">
-        <v>123218000000</v>
+        <v>1084128000000</v>
       </c>
       <c r="N150" t="n">
-        <v>374004238904</v>
+        <v>482396430936</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ＮＩＴＴＯＫＵ株式会社</t>
+          <t>日本製紙株式会社</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>47.7</v>
+        <v>301.5</v>
       </c>
       <c r="D151" t="n">
-        <v>2618</v>
+        <v>1326</v>
       </c>
       <c r="E151" t="n">
-        <v>1710</v>
+        <v>1250</v>
       </c>
       <c r="F151" t="n">
-        <v>53.1</v>
+        <v>6.1</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -8246,102 +8246,102 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>11768000000</v>
+        <v>136216000000</v>
       </c>
       <c r="J151" t="n">
-        <v>6299000000</v>
+        <v>151771000000</v>
       </c>
       <c r="K151" t="n">
-        <v>2999000000</v>
+        <v>172984000000</v>
       </c>
       <c r="L151" t="n">
-        <v>33919000000</v>
+        <v>438604000000</v>
       </c>
       <c r="M151" t="n">
-        <v>21066000000</v>
+        <v>460971000000</v>
       </c>
       <c r="N151" t="n">
-        <v>44177393876</v>
+        <v>152899074978</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ＮＩＴＴＯＫＵ株式会社</t>
+          <t>カルビー株式会社</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>47.7</v>
+        <v>33.5</v>
       </c>
       <c r="D152" t="n">
-        <v>2618</v>
+        <v>3027</v>
       </c>
       <c r="E152" t="n">
-        <v>1710</v>
+        <v>2919.137515755844</v>
       </c>
       <c r="F152" t="n">
-        <v>53.1</v>
+        <v>3.7</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>11768000000</v>
+        <v>49670000000</v>
       </c>
       <c r="J152" t="n">
-        <v>6299000000</v>
+        <v>70285000000</v>
       </c>
       <c r="K152" t="n">
-        <v>2999000000</v>
+        <v>3263000000</v>
       </c>
       <c r="L152" t="n">
-        <v>33919000000</v>
+        <v>183458000000</v>
       </c>
       <c r="M152" t="n">
-        <v>21066000000</v>
+        <v>123218000000</v>
       </c>
       <c r="N152" t="n">
-        <v>44177393876</v>
+        <v>368046434058</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>新光商事株式会社</t>
+          <t>ＮＩＴＴＯＫＵ株式会社</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>8141</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>30.8</v>
+        <v>47.9</v>
       </c>
       <c r="D153" t="n">
-        <v>1568</v>
+        <v>2607</v>
       </c>
       <c r="E153" t="n">
-        <v>930</v>
+        <v>1710</v>
       </c>
       <c r="F153" t="n">
-        <v>68.59999999999999</v>
+        <v>52.5</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -8350,50 +8350,50 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>10579000000</v>
+        <v>11768000000</v>
       </c>
       <c r="J153" t="n">
-        <v>195000000</v>
+        <v>6299000000</v>
       </c>
       <c r="K153" t="n">
-        <v>2995000000</v>
+        <v>2999000000</v>
       </c>
       <c r="L153" t="n">
-        <v>51945000000</v>
+        <v>33919000000</v>
       </c>
       <c r="M153" t="n">
-        <v>13769000000</v>
+        <v>21066000000</v>
       </c>
       <c r="N153" t="n">
-        <v>44766241632</v>
+        <v>43991774574</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>株式会社メガチップス</t>
+          <t>ＮＩＴＴＯＫＵ株式会社</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>6875</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>87.5</v>
+        <v>47.9</v>
       </c>
       <c r="D154" t="n">
-        <v>10740</v>
+        <v>2607</v>
       </c>
       <c r="E154" t="n">
-        <v>4870</v>
+        <v>1710</v>
       </c>
       <c r="F154" t="n">
-        <v>120.5</v>
+        <v>52.5</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -8402,102 +8402,102 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>25769446000</v>
+        <v>11768000000</v>
       </c>
       <c r="J154" t="n">
-        <v>2249411000</v>
+        <v>6299000000</v>
       </c>
       <c r="K154" t="n">
-        <v>101636005000</v>
+        <v>2999000000</v>
       </c>
       <c r="L154" t="n">
-        <v>67428618000</v>
+        <v>33919000000</v>
       </c>
       <c r="M154" t="n">
-        <v>129654862000</v>
+        <v>21066000000</v>
       </c>
       <c r="N154" t="n">
-        <v>148221676740</v>
+        <v>43991774574</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>株式会社青山財産ネットワークス</t>
+          <t>新光商事株式会社</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>8929</t>
+          <t>8141</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>41.9</v>
+        <v>30.8</v>
       </c>
       <c r="D155" t="n">
-        <v>1384</v>
+        <v>1564</v>
       </c>
       <c r="E155" t="n">
-        <v>1347.74653160027</v>
+        <v>930</v>
       </c>
       <c r="F155" t="n">
-        <v>2.7</v>
+        <v>68.2</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="I155" t="n">
-        <v>10862000000</v>
+        <v>10579000000</v>
       </c>
       <c r="J155" t="n">
-        <v>245000000</v>
+        <v>195000000</v>
       </c>
       <c r="K155" t="n">
-        <v>2845000000</v>
+        <v>2995000000</v>
       </c>
       <c r="L155" t="n">
-        <v>7128000000</v>
+        <v>51945000000</v>
       </c>
       <c r="M155" t="n">
-        <v>13952000000</v>
+        <v>13769000000</v>
       </c>
       <c r="N155" t="n">
-        <v>33306289392</v>
+        <v>44652042036</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>平和不動産株式会社</t>
+          <t>株式会社メガチップス</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>8803</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>71.90000000000001</v>
+        <v>86</v>
       </c>
       <c r="D156" t="n">
-        <v>2388</v>
+        <v>10930</v>
       </c>
       <c r="E156" t="n">
-        <v>3610</v>
+        <v>4870</v>
       </c>
       <c r="F156" t="n">
-        <v>-33.9</v>
+        <v>124.4</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -8506,106 +8506,106 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="I156" t="n">
-        <v>28111000000</v>
+        <v>25769446000</v>
       </c>
       <c r="J156" t="n">
-        <v>79319000000</v>
+        <v>2249411000</v>
       </c>
       <c r="K156" t="n">
-        <v>5997000000</v>
+        <v>101636005000</v>
       </c>
       <c r="L156" t="n">
-        <v>119278000000</v>
+        <v>67428618000</v>
       </c>
       <c r="M156" t="n">
-        <v>113427000000</v>
+        <v>129654862000</v>
       </c>
       <c r="N156" t="n">
-        <v>157775776104</v>
+        <v>150843847930</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>小林製薬株式会社</t>
+          <t>株式会社青山財産ネットワークス</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>8929</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>29.7</v>
+        <v>41.8</v>
       </c>
       <c r="D157" t="n">
-        <v>5862</v>
+        <v>1388</v>
       </c>
       <c r="E157" t="n">
-        <v>2148.936934940886</v>
+        <v>1347.74653160027</v>
       </c>
       <c r="F157" t="n">
-        <v>172.8</v>
+        <v>3</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="I157" t="n">
-        <v>81987000000</v>
+        <v>10862000000</v>
       </c>
       <c r="J157" t="n">
-        <v>32461000000</v>
+        <v>245000000</v>
       </c>
       <c r="K157" t="n">
-        <v>14872000000</v>
+        <v>2845000000</v>
       </c>
       <c r="L157" t="n">
-        <v>195600000000</v>
+        <v>7128000000</v>
       </c>
       <c r="M157" t="n">
-        <v>129320000000</v>
+        <v>13952000000</v>
       </c>
       <c r="N157" t="n">
-        <v>435772996302</v>
+        <v>33402550344</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>小林製薬株式会社</t>
+          <t>平和不動産株式会社</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>29.7</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D158" t="n">
-        <v>5862</v>
+        <v>2380</v>
       </c>
       <c r="E158" t="n">
-        <v>5066.092575838703</v>
+        <v>3610</v>
       </c>
       <c r="F158" t="n">
-        <v>15.7</v>
+        <v>-34.1</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -8614,46 +8614,46 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>81987000000</v>
+        <v>28111000000</v>
       </c>
       <c r="J158" t="n">
-        <v>32461000000</v>
+        <v>79319000000</v>
       </c>
       <c r="K158" t="n">
-        <v>14872000000</v>
+        <v>5997000000</v>
       </c>
       <c r="L158" t="n">
-        <v>195600000000</v>
+        <v>119278000000</v>
       </c>
       <c r="M158" t="n">
-        <v>129320000000</v>
+        <v>113427000000</v>
       </c>
       <c r="N158" t="n">
-        <v>435772996302</v>
+        <v>157247214040</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>セーレン株式会社</t>
+          <t>小林製薬株式会社</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>3569</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>36.6</v>
+        <v>29.7</v>
       </c>
       <c r="D159" t="n">
-        <v>3285</v>
+        <v>5860</v>
       </c>
       <c r="E159" t="n">
-        <v>1359.655069733296</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="F159" t="n">
-        <v>141.6</v>
+        <v>172.7</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -8662,50 +8662,50 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="I159" t="n">
-        <v>35451000000</v>
+        <v>81987000000</v>
       </c>
       <c r="J159" t="n">
-        <v>25813000000</v>
+        <v>32461000000</v>
       </c>
       <c r="K159" t="n">
-        <v>8891000000</v>
+        <v>14872000000</v>
       </c>
       <c r="L159" t="n">
-        <v>91845000000</v>
+        <v>195600000000</v>
       </c>
       <c r="M159" t="n">
-        <v>70155000000</v>
+        <v>129320000000</v>
       </c>
       <c r="N159" t="n">
-        <v>191710763685</v>
+        <v>435624319060</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>データセクション株式会社</t>
+          <t>小林製薬株式会社</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>2.7</v>
+        <v>29.7</v>
       </c>
       <c r="D160" t="n">
-        <v>1438</v>
+        <v>5860</v>
       </c>
       <c r="E160" t="n">
-        <v>5143.276404494382</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="F160" t="n">
-        <v>-72</v>
+        <v>15.7</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -8714,650 +8714,754 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1420430000</v>
+        <v>81987000000</v>
       </c>
       <c r="J160" t="n">
-        <v>1162000</v>
+        <v>32461000000</v>
       </c>
       <c r="K160" t="n">
-        <v>49326000</v>
+        <v>14872000000</v>
       </c>
       <c r="L160" t="n">
-        <v>2818110000</v>
+        <v>195600000000</v>
       </c>
       <c r="M160" t="n">
-        <v>1470918000</v>
+        <v>129320000000</v>
       </c>
       <c r="N160" t="n">
-        <v>53870796028</v>
+        <v>435624319060</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>愛眼株式会社</t>
+          <t>セーレン株式会社</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>9854</t>
+          <t>3569</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>71.40000000000001</v>
+        <v>36.2</v>
       </c>
       <c r="D161" t="n">
-        <v>278</v>
+        <v>3320</v>
       </c>
       <c r="E161" t="n">
-        <v>246.9708756284982</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="F161" t="n">
-        <v>12.6</v>
+        <v>144.2</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2219000000</v>
+        <v>35451000000</v>
       </c>
       <c r="J161" t="n">
-        <v>1030000000</v>
+        <v>25813000000</v>
       </c>
       <c r="K161" t="n">
-        <v>604000000</v>
+        <v>8891000000</v>
       </c>
       <c r="L161" t="n">
-        <v>12920000000</v>
+        <v>91845000000</v>
       </c>
       <c r="M161" t="n">
-        <v>3853000000</v>
+        <v>70155000000</v>
       </c>
       <c r="N161" t="n">
-        <v>5395066770</v>
+        <v>193753344120</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>株式会社アシロ</t>
+          <t>データセクション株式会社</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>13.9</v>
+        <v>2.5</v>
       </c>
       <c r="D162" t="n">
-        <v>1565</v>
+        <v>1542</v>
       </c>
       <c r="E162" t="n">
-        <v>1396.628697042366</v>
+        <v>5143.276404494382</v>
       </c>
       <c r="F162" t="n">
-        <v>12.1</v>
+        <v>-70</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1428281000</v>
+        <v>1420430000</v>
       </c>
       <c r="J162" t="n">
-        <v>102238000</v>
+        <v>1162000</v>
       </c>
       <c r="K162" t="n">
-        <v>0</v>
+        <v>49326000</v>
       </c>
       <c r="L162" t="n">
-        <v>1804458000</v>
+        <v>2818110000</v>
       </c>
       <c r="M162" t="n">
-        <v>1530519000</v>
+        <v>1470918000</v>
       </c>
       <c r="N162" t="n">
-        <v>11004433655</v>
+        <v>57766875852</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>三浦工業株式会社</t>
+          <t>愛眼株式会社</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>11.5</v>
+        <v>72.2</v>
       </c>
       <c r="D163" t="n">
-        <v>3181</v>
+        <v>275</v>
       </c>
       <c r="E163" t="n">
-        <v>3147.518794622453</v>
+        <v>246.9708756284982</v>
       </c>
       <c r="F163" t="n">
-        <v>1.1</v>
+        <v>11.3</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="I163" t="n">
-        <v>20794000000</v>
+        <v>2219000000</v>
       </c>
       <c r="J163" t="n">
-        <v>10600000000</v>
+        <v>1030000000</v>
       </c>
       <c r="K163" t="n">
-        <v>10773000000</v>
+        <v>604000000</v>
       </c>
       <c r="L163" t="n">
-        <v>138378000000</v>
+        <v>12920000000</v>
       </c>
       <c r="M163" t="n">
-        <v>42167000000</v>
+        <v>3853000000</v>
       </c>
       <c r="N163" t="n">
-        <v>368198714160</v>
+        <v>5336846625</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>株式会社カカクコム</t>
+          <t>株式会社アシロ</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>7378</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>6.8</v>
+        <v>13.9</v>
       </c>
       <c r="D164" t="n">
-        <v>3795</v>
+        <v>1571</v>
       </c>
       <c r="E164" t="n">
-        <v>2318.314890576102</v>
+        <v>1396.628697042366</v>
       </c>
       <c r="F164" t="n">
-        <v>63.7</v>
+        <v>12.5</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="I164" t="n">
-        <v>46452000000</v>
+        <v>1428281000</v>
       </c>
       <c r="J164" t="n">
-        <v>68000000</v>
+        <v>102238000</v>
       </c>
       <c r="K164" t="n">
-        <v>4669000000</v>
+        <v>0</v>
       </c>
       <c r="L164" t="n">
-        <v>45479000000</v>
+        <v>1804458000</v>
       </c>
       <c r="M164" t="n">
-        <v>51189000000</v>
+        <v>1530519000</v>
       </c>
       <c r="N164" t="n">
-        <v>750788633265</v>
+        <v>11046623177</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>古河機械金属株式会社</t>
+          <t>三浦工業株式会社</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>46.5</v>
+        <v>11.6</v>
       </c>
       <c r="D165" t="n">
-        <v>4095</v>
+        <v>3154</v>
       </c>
       <c r="E165" t="n">
-        <v>1600</v>
+        <v>3147.518794622453</v>
       </c>
       <c r="F165" t="n">
-        <v>155.9</v>
+        <v>0.2</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I165" t="n">
-        <v>14468000000</v>
+        <v>20794000000</v>
       </c>
       <c r="J165" t="n">
-        <v>26121000000</v>
+        <v>10600000000</v>
       </c>
       <c r="K165" t="n">
-        <v>19903000000</v>
+        <v>10773000000</v>
       </c>
       <c r="L165" t="n">
-        <v>100075000000</v>
+        <v>138378000000</v>
       </c>
       <c r="M165" t="n">
-        <v>60492000000</v>
+        <v>42167000000</v>
       </c>
       <c r="N165" t="n">
-        <v>130098629115</v>
+        <v>365073481440</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>多木化学株式会社</t>
+          <t>株式会社カカクコム</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>4025</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>30.6</v>
+        <v>6.7</v>
       </c>
       <c r="D166" t="n">
-        <v>5730</v>
+        <v>3835</v>
       </c>
       <c r="E166" t="n">
-        <v>4695.956053243186</v>
+        <v>2318.314890576102</v>
       </c>
       <c r="F166" t="n">
-        <v>22</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="I166" t="n">
-        <v>6433000000</v>
+        <v>46452000000</v>
       </c>
       <c r="J166" t="n">
-        <v>7985000000</v>
+        <v>68000000</v>
       </c>
       <c r="K166" t="n">
-        <v>199000000</v>
+        <v>4669000000</v>
       </c>
       <c r="L166" t="n">
-        <v>29378000000</v>
+        <v>45479000000</v>
       </c>
       <c r="M166" t="n">
-        <v>14617000000</v>
+        <v>51189000000</v>
       </c>
       <c r="N166" t="n">
-        <v>47830424370</v>
+        <v>758702083945</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>エムスリー株式会社</t>
+          <t>古河機械金属株式会社</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2413</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>7.4</v>
+        <v>45.1</v>
       </c>
       <c r="D167" t="n">
-        <v>1797.5</v>
+        <v>4225</v>
       </c>
       <c r="E167" t="n">
-        <v>1638.585693292194</v>
+        <v>1600</v>
       </c>
       <c r="F167" t="n">
-        <v>9.699999999999999</v>
+        <v>164.1</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="I167" t="n">
-        <v>78812000000</v>
+        <v>14468000000</v>
       </c>
       <c r="J167" t="n">
-        <v>345000000</v>
+        <v>26121000000</v>
       </c>
       <c r="K167" t="n">
-        <v>9506000000</v>
+        <v>19903000000</v>
       </c>
       <c r="L167" t="n">
-        <v>152472000000</v>
+        <v>100075000000</v>
       </c>
       <c r="M167" t="n">
-        <v>88663000000</v>
+        <v>60492000000</v>
       </c>
       <c r="N167" t="n">
-        <v>1197703479148</v>
+        <v>134228744325</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>三井松島ホールディングス株式会社</t>
+          <t>多木化学株式会社</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>40.1</v>
+        <v>29.9</v>
       </c>
       <c r="D168" t="n">
-        <v>2285</v>
+        <v>5860</v>
       </c>
       <c r="E168" t="n">
-        <v>2920</v>
+        <v>4695.956053243186</v>
       </c>
       <c r="F168" t="n">
-        <v>-21.7</v>
+        <v>24.8</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I168" t="n">
-        <v>19413000000</v>
+        <v>6433000000</v>
       </c>
       <c r="J168" t="n">
-        <v>3540000000</v>
+        <v>7985000000</v>
       </c>
       <c r="K168" t="n">
-        <v>10945000000</v>
+        <v>199000000</v>
       </c>
       <c r="L168" t="n">
-        <v>35537000000</v>
+        <v>29378000000</v>
       </c>
       <c r="M168" t="n">
-        <v>33898000000</v>
+        <v>14617000000</v>
       </c>
       <c r="N168" t="n">
-        <v>84608888600</v>
+        <v>48915582340</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ノリタケ株式会社</t>
+          <t>エムスリー株式会社</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>37.8</v>
+        <v>7.5</v>
       </c>
       <c r="D169" t="n">
-        <v>3600</v>
+        <v>1773</v>
       </c>
       <c r="E169" t="n">
-        <v>3573.410502159827</v>
+        <v>1638.585693292194</v>
       </c>
       <c r="F169" t="n">
-        <v>0.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I169" t="n">
-        <v>11733000000</v>
+        <v>78812000000</v>
       </c>
       <c r="J169" t="n">
-        <v>20204000000</v>
+        <v>345000000</v>
       </c>
       <c r="K169" t="n">
-        <v>42879000000</v>
+        <v>9506000000</v>
       </c>
       <c r="L169" t="n">
-        <v>118800000000</v>
+        <v>152472000000</v>
       </c>
       <c r="M169" t="n">
-        <v>74816000000</v>
+        <v>88663000000</v>
       </c>
       <c r="N169" t="n">
-        <v>198051386400</v>
+        <v>1181378730753</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>株式会社ＡＣＳＬ</t>
+          <t>三井松島ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>7.9</v>
+        <v>39.9</v>
       </c>
       <c r="D170" t="n">
-        <v>1359</v>
+        <v>2296</v>
       </c>
       <c r="E170" t="n">
-        <v>913.2768512341561</v>
+        <v>2920</v>
       </c>
       <c r="F170" t="n">
-        <v>48.8</v>
+        <v>-21.4</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1891731000</v>
+        <v>19413000000</v>
       </c>
       <c r="J170" t="n">
-        <v>3724000</v>
+        <v>3540000000</v>
       </c>
       <c r="K170" t="n">
-        <v>197577000</v>
+        <v>10945000000</v>
       </c>
       <c r="L170" t="n">
-        <v>3572642000</v>
+        <v>35537000000</v>
       </c>
       <c r="M170" t="n">
-        <v>2093032000</v>
+        <v>33898000000</v>
       </c>
       <c r="N170" t="n">
-        <v>26598676878</v>
+        <v>85016196160</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>株式会社スズケン</t>
+          <t>ノリタケ株式会社</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>9987</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>76.5</v>
+        <v>37.1</v>
       </c>
       <c r="D171" t="n">
-        <v>5346</v>
+        <v>3665</v>
       </c>
       <c r="E171" t="n">
-        <v>4137.137750115735</v>
+        <v>3573.410502159827</v>
       </c>
       <c r="F171" t="n">
-        <v>29.2</v>
+        <v>2.6</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="I171" t="n">
-        <v>168215000000</v>
+        <v>11733000000</v>
       </c>
       <c r="J171" t="n">
-        <v>65453000000</v>
+        <v>20204000000</v>
       </c>
       <c r="K171" t="n">
-        <v>38927000000</v>
+        <v>42879000000</v>
       </c>
       <c r="L171" t="n">
-        <v>418062000000</v>
+        <v>118800000000</v>
       </c>
       <c r="M171" t="n">
-        <v>272595000000</v>
+        <v>74816000000</v>
       </c>
       <c r="N171" t="n">
-        <v>356493674394</v>
+        <v>201627314210</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
+          <t>株式会社ＡＣＳＬ</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>6232</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="D172" t="n">
+        <v>1398</v>
+      </c>
+      <c r="E172" t="n">
+        <v>913.2768512341561</v>
+      </c>
+      <c r="F172" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="I172" t="n">
+        <v>1891731000</v>
+      </c>
+      <c r="J172" t="n">
+        <v>3724000</v>
+      </c>
+      <c r="K172" t="n">
+        <v>197577000</v>
+      </c>
+      <c r="L172" t="n">
+        <v>3572642000</v>
+      </c>
+      <c r="M172" t="n">
+        <v>2093032000</v>
+      </c>
+      <c r="N172" t="n">
+        <v>27361994316</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>株式会社スズケン</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="D173" t="n">
+        <v>5268</v>
+      </c>
+      <c r="E173" t="n">
+        <v>4137.137750115735</v>
+      </c>
+      <c r="F173" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="I173" t="n">
+        <v>168215000000</v>
+      </c>
+      <c r="J173" t="n">
+        <v>65453000000</v>
+      </c>
+      <c r="K173" t="n">
+        <v>38927000000</v>
+      </c>
+      <c r="L173" t="n">
+        <v>418062000000</v>
+      </c>
+      <c r="M173" t="n">
+        <v>272595000000</v>
+      </c>
+      <c r="N173" t="n">
+        <v>351292307652</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
           <t>フォスター電機株式会社</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
+      <c r="B174" t="inlineStr">
         <is>
           <t>6794</t>
         </is>
       </c>
-      <c r="C172" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="D172" t="n">
-        <v>3190</v>
-      </c>
-      <c r="E172" t="n">
+      <c r="C174" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="D174" t="n">
+        <v>3240</v>
+      </c>
+      <c r="E174" t="n">
         <v>2681.96152003832</v>
       </c>
-      <c r="F172" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G172" t="inlineStr">
+      <c r="F174" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="G174" t="inlineStr">
         <is>
           <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
+      <c r="H174" t="inlineStr">
         <is>
           <t>2026-01-22</t>
         </is>
       </c>
-      <c r="I172" t="n">
+      <c r="I174" t="n">
         <v>12089000000</v>
       </c>
-      <c r="J172" t="n">
+      <c r="J174" t="n">
         <v>7327000000</v>
       </c>
-      <c r="K172" t="n">
+      <c r="K174" t="n">
         <v>1115000000</v>
       </c>
-      <c r="L172" t="n">
+      <c r="L174" t="n">
         <v>51632000000</v>
       </c>
-      <c r="M172" t="n">
+      <c r="M174" t="n">
         <v>20531000000</v>
       </c>
-      <c r="N172" t="n">
-        <v>71672304330</v>
+      <c r="N174" t="n">
+        <v>72795694680</v>
       </c>
     </row>
   </sheetData>

--- a/docs/アクティビスト銘柄_資産判定.xlsx
+++ b/docs/アクティビスト銘柄_資産判定.xlsx
@@ -849,7 +849,7 @@
         <v>12397436000</v>
       </c>
       <c r="N8" t="n">
-        <v>87069629125</v>
+        <v>87067501775</v>
       </c>
     </row>
     <row r="9">
@@ -3241,7 +3241,7 @@
         <v>32342000000</v>
       </c>
       <c r="N54" t="n">
-        <v>112757689520</v>
+        <v>112727743520</v>
       </c>
     </row>
     <row r="55">
@@ -3293,7 +3293,7 @@
         <v>32342000000</v>
       </c>
       <c r="N55" t="n">
-        <v>112757689520</v>
+        <v>112727743520</v>
       </c>
     </row>
     <row r="56">
@@ -3345,7 +3345,7 @@
         <v>32342000000</v>
       </c>
       <c r="N56" t="n">
-        <v>112757689520</v>
+        <v>112727743520</v>
       </c>
     </row>
     <row r="57">
@@ -3397,7 +3397,7 @@
         <v>32342000000</v>
       </c>
       <c r="N57" t="n">
-        <v>112757689520</v>
+        <v>112727743520</v>
       </c>
     </row>
     <row r="58">
@@ -3449,7 +3449,7 @@
         <v>32342000000</v>
       </c>
       <c r="N58" t="n">
-        <v>112757689520</v>
+        <v>112727743520</v>
       </c>
     </row>
     <row r="59">
@@ -3724,7 +3724,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
       <c r="D64" t="n">
         <v>2367.5</v>
@@ -3761,7 +3761,7 @@
         <v>207466000000</v>
       </c>
       <c r="N64" t="n">
-        <v>396363547338</v>
+        <v>395979065338</v>
       </c>
     </row>
     <row r="65">
@@ -5272,7 +5272,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="D94" t="n">
         <v>506</v>
@@ -5309,7 +5309,7 @@
         <v>13953300000</v>
       </c>
       <c r="N94" t="n">
-        <v>104967225154</v>
+        <v>103357931116</v>
       </c>
     </row>
     <row r="95">
@@ -6453,7 +6453,7 @@
         <v>29529000000</v>
       </c>
       <c r="N116" t="n">
-        <v>74394216680</v>
+        <v>74400173680</v>
       </c>
     </row>
     <row r="117">
@@ -6505,7 +6505,7 @@
         <v>29529000000</v>
       </c>
       <c r="N117" t="n">
-        <v>74394216680</v>
+        <v>74400173680</v>
       </c>
     </row>
     <row r="118">
@@ -6557,7 +6557,7 @@
         <v>29529000000</v>
       </c>
       <c r="N118" t="n">
-        <v>74394216680</v>
+        <v>74400173680</v>
       </c>
     </row>
     <row r="119">
@@ -6609,7 +6609,7 @@
         <v>29529000000</v>
       </c>
       <c r="N119" t="n">
-        <v>74394216680</v>
+        <v>74400173680</v>
       </c>
     </row>
     <row r="120">
@@ -6661,7 +6661,7 @@
         <v>29529000000</v>
       </c>
       <c r="N120" t="n">
-        <v>74394216680</v>
+        <v>74400173680</v>
       </c>
     </row>
     <row r="121">
@@ -6713,7 +6713,7 @@
         <v>29529000000</v>
       </c>
       <c r="N121" t="n">
-        <v>74394216680</v>
+        <v>74400173680</v>
       </c>
     </row>
     <row r="122">
@@ -6765,7 +6765,7 @@
         <v>29529000000</v>
       </c>
       <c r="N122" t="n">
-        <v>74394216680</v>
+        <v>74400173680</v>
       </c>
     </row>
     <row r="123">
@@ -6817,7 +6817,7 @@
         <v>29529000000</v>
       </c>
       <c r="N123" t="n">
-        <v>74394216680</v>
+        <v>74400173680</v>
       </c>
     </row>
     <row r="124">
@@ -6869,7 +6869,7 @@
         <v>29529000000</v>
       </c>
       <c r="N124" t="n">
-        <v>74394216680</v>
+        <v>74400173680</v>
       </c>
     </row>
     <row r="125">
@@ -6921,7 +6921,7 @@
         <v>29529000000</v>
       </c>
       <c r="N125" t="n">
-        <v>74394216680</v>
+        <v>74400173680</v>
       </c>
     </row>
     <row r="126">
@@ -6973,7 +6973,7 @@
         <v>29529000000</v>
       </c>
       <c r="N126" t="n">
-        <v>74394216680</v>
+        <v>74400173680</v>
       </c>
     </row>
     <row r="127">
@@ -7025,7 +7025,7 @@
         <v>29529000000</v>
       </c>
       <c r="N127" t="n">
-        <v>74394216680</v>
+        <v>74400173680</v>
       </c>
     </row>
     <row r="128">
@@ -8213,7 +8213,7 @@
         <v>1084128000000</v>
       </c>
       <c r="N150" t="n">
-        <v>482396430936</v>
+        <v>482396598264</v>
       </c>
     </row>
     <row r="151">

--- a/docs/アクティビスト銘柄_資産判定.xlsx
+++ b/docs/アクティビスト銘柄_資産判定.xlsx
@@ -849,7 +849,7 @@
         <v>12397436000</v>
       </c>
       <c r="N8" t="n">
-        <v>87067501775</v>
+        <v>87069629125</v>
       </c>
     </row>
     <row r="9">
@@ -3241,7 +3241,7 @@
         <v>32342000000</v>
       </c>
       <c r="N54" t="n">
-        <v>112727743520</v>
+        <v>112757689520</v>
       </c>
     </row>
     <row r="55">
@@ -3293,7 +3293,7 @@
         <v>32342000000</v>
       </c>
       <c r="N55" t="n">
-        <v>112727743520</v>
+        <v>112757689520</v>
       </c>
     </row>
     <row r="56">
@@ -3345,7 +3345,7 @@
         <v>32342000000</v>
       </c>
       <c r="N56" t="n">
-        <v>112727743520</v>
+        <v>112757689520</v>
       </c>
     </row>
     <row r="57">
@@ -3397,7 +3397,7 @@
         <v>32342000000</v>
       </c>
       <c r="N57" t="n">
-        <v>112727743520</v>
+        <v>112757689520</v>
       </c>
     </row>
     <row r="58">
@@ -3449,7 +3449,7 @@
         <v>32342000000</v>
       </c>
       <c r="N58" t="n">
-        <v>112727743520</v>
+        <v>112757689520</v>
       </c>
     </row>
     <row r="59">
@@ -3724,7 +3724,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
       <c r="D64" t="n">
         <v>2367.5</v>
@@ -3761,7 +3761,7 @@
         <v>207466000000</v>
       </c>
       <c r="N64" t="n">
-        <v>395979065338</v>
+        <v>396363547338</v>
       </c>
     </row>
     <row r="65">
@@ -5272,7 +5272,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>13.5</v>
+        <v>13.3</v>
       </c>
       <c r="D94" t="n">
         <v>506</v>
@@ -5309,7 +5309,7 @@
         <v>13953300000</v>
       </c>
       <c r="N94" t="n">
-        <v>103357931116</v>
+        <v>104967225154</v>
       </c>
     </row>
     <row r="95">
@@ -6453,7 +6453,7 @@
         <v>29529000000</v>
       </c>
       <c r="N116" t="n">
-        <v>74400173680</v>
+        <v>74394216680</v>
       </c>
     </row>
     <row r="117">
@@ -6505,7 +6505,7 @@
         <v>29529000000</v>
       </c>
       <c r="N117" t="n">
-        <v>74400173680</v>
+        <v>74394216680</v>
       </c>
     </row>
     <row r="118">
@@ -6557,7 +6557,7 @@
         <v>29529000000</v>
       </c>
       <c r="N118" t="n">
-        <v>74400173680</v>
+        <v>74394216680</v>
       </c>
     </row>
     <row r="119">
@@ -6609,7 +6609,7 @@
         <v>29529000000</v>
       </c>
       <c r="N119" t="n">
-        <v>74400173680</v>
+        <v>74394216680</v>
       </c>
     </row>
     <row r="120">
@@ -6661,7 +6661,7 @@
         <v>29529000000</v>
       </c>
       <c r="N120" t="n">
-        <v>74400173680</v>
+        <v>74394216680</v>
       </c>
     </row>
     <row r="121">
@@ -6713,7 +6713,7 @@
         <v>29529000000</v>
       </c>
       <c r="N121" t="n">
-        <v>74400173680</v>
+        <v>74394216680</v>
       </c>
     </row>
     <row r="122">
@@ -6765,7 +6765,7 @@
         <v>29529000000</v>
       </c>
       <c r="N122" t="n">
-        <v>74400173680</v>
+        <v>74394216680</v>
       </c>
     </row>
     <row r="123">
@@ -6817,7 +6817,7 @@
         <v>29529000000</v>
       </c>
       <c r="N123" t="n">
-        <v>74400173680</v>
+        <v>74394216680</v>
       </c>
     </row>
     <row r="124">
@@ -6869,7 +6869,7 @@
         <v>29529000000</v>
       </c>
       <c r="N124" t="n">
-        <v>74400173680</v>
+        <v>74394216680</v>
       </c>
     </row>
     <row r="125">
@@ -6921,7 +6921,7 @@
         <v>29529000000</v>
       </c>
       <c r="N125" t="n">
-        <v>74400173680</v>
+        <v>74394216680</v>
       </c>
     </row>
     <row r="126">
@@ -6973,7 +6973,7 @@
         <v>29529000000</v>
       </c>
       <c r="N126" t="n">
-        <v>74400173680</v>
+        <v>74394216680</v>
       </c>
     </row>
     <row r="127">
@@ -7025,7 +7025,7 @@
         <v>29529000000</v>
       </c>
       <c r="N127" t="n">
-        <v>74400173680</v>
+        <v>74394216680</v>
       </c>
     </row>
     <row r="128">
@@ -8213,7 +8213,7 @@
         <v>1084128000000</v>
       </c>
       <c r="N150" t="n">
-        <v>482396598264</v>
+        <v>482396430936</v>
       </c>
     </row>
     <row r="151">

--- a/docs/アクティビスト銘柄_資産判定.xlsx
+++ b/docs/アクティビスト銘柄_資産判定.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N174"/>
+  <dimension ref="A1:N173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8115,77 +8115,77 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>マネックスグループ株式会社</t>
+          <t>株式会社あおぞら銀行</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>8698</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>15.4</v>
+        <v>224.7</v>
       </c>
       <c r="D149" t="n">
-        <v>712</v>
+        <v>3486</v>
       </c>
       <c r="E149" t="n">
-        <v>510.1850530906719</v>
+        <v>2190</v>
       </c>
       <c r="F149" t="n">
-        <v>39.6</v>
+        <v>59.2</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>17794000000</v>
+        <v>1061743000000</v>
       </c>
       <c r="J149" t="n">
-        <v>412000000</v>
+        <v>22385000000</v>
       </c>
       <c r="K149" t="n">
-        <v>9312000000</v>
+        <v>0</v>
       </c>
       <c r="L149" t="n">
-        <v>98001000000</v>
+        <v>487265000000</v>
       </c>
       <c r="M149" t="n">
-        <v>27518000000</v>
+        <v>1084128000000</v>
       </c>
       <c r="N149" t="n">
-        <v>178970943008</v>
+        <v>482396430936</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>株式会社あおぞら銀行</t>
+          <t>日本製紙株式会社</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>224.7</v>
+        <v>301.5</v>
       </c>
       <c r="D150" t="n">
-        <v>3486</v>
+        <v>1326</v>
       </c>
       <c r="E150" t="n">
-        <v>2190</v>
+        <v>1250</v>
       </c>
       <c r="F150" t="n">
-        <v>59.2</v>
+        <v>6.1</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -8194,130 +8194,130 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1061743000000</v>
+        <v>136216000000</v>
       </c>
       <c r="J150" t="n">
-        <v>22385000000</v>
+        <v>151771000000</v>
       </c>
       <c r="K150" t="n">
-        <v>0</v>
+        <v>172984000000</v>
       </c>
       <c r="L150" t="n">
-        <v>487265000000</v>
+        <v>438604000000</v>
       </c>
       <c r="M150" t="n">
-        <v>1084128000000</v>
+        <v>460971000000</v>
       </c>
       <c r="N150" t="n">
-        <v>482396430936</v>
+        <v>152899074978</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>日本製紙株式会社</t>
+          <t>カルビー株式会社</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>301.5</v>
+        <v>33.5</v>
       </c>
       <c r="D151" t="n">
-        <v>1326</v>
+        <v>3027</v>
       </c>
       <c r="E151" t="n">
-        <v>1250</v>
+        <v>2919.137515755844</v>
       </c>
       <c r="F151" t="n">
-        <v>6.1</v>
+        <v>3.7</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>136216000000</v>
+        <v>49670000000</v>
       </c>
       <c r="J151" t="n">
-        <v>151771000000</v>
+        <v>70285000000</v>
       </c>
       <c r="K151" t="n">
-        <v>172984000000</v>
+        <v>3263000000</v>
       </c>
       <c r="L151" t="n">
-        <v>438604000000</v>
+        <v>183458000000</v>
       </c>
       <c r="M151" t="n">
-        <v>460971000000</v>
+        <v>123218000000</v>
       </c>
       <c r="N151" t="n">
-        <v>152899074978</v>
+        <v>368046434058</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>カルビー株式会社</t>
+          <t>ＮＩＴＴＯＫＵ株式会社</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>33.5</v>
+        <v>47.9</v>
       </c>
       <c r="D152" t="n">
-        <v>3027</v>
+        <v>2607</v>
       </c>
       <c r="E152" t="n">
-        <v>2919.137515755844</v>
+        <v>1710</v>
       </c>
       <c r="F152" t="n">
-        <v>3.7</v>
+        <v>52.5</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>49670000000</v>
+        <v>11768000000</v>
       </c>
       <c r="J152" t="n">
-        <v>70285000000</v>
+        <v>6299000000</v>
       </c>
       <c r="K152" t="n">
-        <v>3263000000</v>
+        <v>2999000000</v>
       </c>
       <c r="L152" t="n">
-        <v>183458000000</v>
+        <v>33919000000</v>
       </c>
       <c r="M152" t="n">
-        <v>123218000000</v>
+        <v>21066000000</v>
       </c>
       <c r="N152" t="n">
-        <v>368046434058</v>
+        <v>43991774574</v>
       </c>
     </row>
     <row r="153">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="I153" t="n">
@@ -8375,25 +8375,25 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ＮＩＴＴＯＫＵ株式会社</t>
+          <t>新光商事株式会社</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>8141</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>47.9</v>
+        <v>30.8</v>
       </c>
       <c r="D154" t="n">
-        <v>2607</v>
+        <v>1564</v>
       </c>
       <c r="E154" t="n">
-        <v>1710</v>
+        <v>930</v>
       </c>
       <c r="F154" t="n">
-        <v>52.5</v>
+        <v>68.2</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -8402,50 +8402,50 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>11768000000</v>
+        <v>10579000000</v>
       </c>
       <c r="J154" t="n">
-        <v>6299000000</v>
+        <v>195000000</v>
       </c>
       <c r="K154" t="n">
-        <v>2999000000</v>
+        <v>2995000000</v>
       </c>
       <c r="L154" t="n">
-        <v>33919000000</v>
+        <v>51945000000</v>
       </c>
       <c r="M154" t="n">
-        <v>21066000000</v>
+        <v>13769000000</v>
       </c>
       <c r="N154" t="n">
-        <v>43991774574</v>
+        <v>44652042036</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>新光商事株式会社</t>
+          <t>株式会社メガチップス</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>8141</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>30.8</v>
+        <v>86</v>
       </c>
       <c r="D155" t="n">
-        <v>1564</v>
+        <v>10930</v>
       </c>
       <c r="E155" t="n">
-        <v>930</v>
+        <v>4870</v>
       </c>
       <c r="F155" t="n">
-        <v>68.2</v>
+        <v>124.4</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -8454,158 +8454,158 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="I155" t="n">
-        <v>10579000000</v>
+        <v>25769446000</v>
       </c>
       <c r="J155" t="n">
-        <v>195000000</v>
+        <v>2249411000</v>
       </c>
       <c r="K155" t="n">
-        <v>2995000000</v>
+        <v>101636005000</v>
       </c>
       <c r="L155" t="n">
-        <v>51945000000</v>
+        <v>67428618000</v>
       </c>
       <c r="M155" t="n">
-        <v>13769000000</v>
+        <v>129654862000</v>
       </c>
       <c r="N155" t="n">
-        <v>44652042036</v>
+        <v>150843847930</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>株式会社メガチップス</t>
+          <t>株式会社青山財産ネットワークス</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>6875</t>
+          <t>8929</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>86</v>
+        <v>41.8</v>
       </c>
       <c r="D156" t="n">
-        <v>10930</v>
+        <v>1388</v>
       </c>
       <c r="E156" t="n">
-        <v>4870</v>
+        <v>1347.74653160027</v>
       </c>
       <c r="F156" t="n">
-        <v>124.4</v>
+        <v>3</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="I156" t="n">
-        <v>25769446000</v>
+        <v>10862000000</v>
       </c>
       <c r="J156" t="n">
-        <v>2249411000</v>
+        <v>245000000</v>
       </c>
       <c r="K156" t="n">
-        <v>101636005000</v>
+        <v>2845000000</v>
       </c>
       <c r="L156" t="n">
-        <v>67428618000</v>
+        <v>7128000000</v>
       </c>
       <c r="M156" t="n">
-        <v>129654862000</v>
+        <v>13952000000</v>
       </c>
       <c r="N156" t="n">
-        <v>150843847930</v>
+        <v>33402550344</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>株式会社青山財産ネットワークス</t>
+          <t>平和不動産株式会社</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>8929</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>41.8</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D157" t="n">
-        <v>1388</v>
+        <v>2380</v>
       </c>
       <c r="E157" t="n">
-        <v>1347.74653160027</v>
+        <v>3610</v>
       </c>
       <c r="F157" t="n">
-        <v>3</v>
+        <v>-34.1</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="I157" t="n">
-        <v>10862000000</v>
+        <v>28111000000</v>
       </c>
       <c r="J157" t="n">
-        <v>245000000</v>
+        <v>79319000000</v>
       </c>
       <c r="K157" t="n">
-        <v>2845000000</v>
+        <v>5997000000</v>
       </c>
       <c r="L157" t="n">
-        <v>7128000000</v>
+        <v>119278000000</v>
       </c>
       <c r="M157" t="n">
-        <v>13952000000</v>
+        <v>113427000000</v>
       </c>
       <c r="N157" t="n">
-        <v>33402550344</v>
+        <v>157247214040</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>平和不動産株式会社</t>
+          <t>小林製薬株式会社</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>8803</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>72.09999999999999</v>
+        <v>29.7</v>
       </c>
       <c r="D158" t="n">
-        <v>2380</v>
+        <v>5860</v>
       </c>
       <c r="E158" t="n">
-        <v>3610</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="F158" t="n">
-        <v>-34.1</v>
+        <v>172.7</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -8614,22 +8614,22 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>28111000000</v>
+        <v>81987000000</v>
       </c>
       <c r="J158" t="n">
-        <v>79319000000</v>
+        <v>32461000000</v>
       </c>
       <c r="K158" t="n">
-        <v>5997000000</v>
+        <v>14872000000</v>
       </c>
       <c r="L158" t="n">
-        <v>119278000000</v>
+        <v>195600000000</v>
       </c>
       <c r="M158" t="n">
-        <v>113427000000</v>
+        <v>129320000000</v>
       </c>
       <c r="N158" t="n">
-        <v>157247214040</v>
+        <v>435624319060</v>
       </c>
     </row>
     <row r="159">
@@ -8650,10 +8650,10 @@
         <v>5860</v>
       </c>
       <c r="E159" t="n">
-        <v>2148.936934940886</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="F159" t="n">
-        <v>172.7</v>
+        <v>15.7</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -8687,25 +8687,25 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>小林製薬株式会社</t>
+          <t>セーレン株式会社</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>3569</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>29.7</v>
+        <v>36.2</v>
       </c>
       <c r="D160" t="n">
-        <v>5860</v>
+        <v>3320</v>
       </c>
       <c r="E160" t="n">
-        <v>5066.092575838703</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="F160" t="n">
-        <v>15.7</v>
+        <v>144.2</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -8714,50 +8714,50 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>81987000000</v>
+        <v>35451000000</v>
       </c>
       <c r="J160" t="n">
-        <v>32461000000</v>
+        <v>25813000000</v>
       </c>
       <c r="K160" t="n">
-        <v>14872000000</v>
+        <v>8891000000</v>
       </c>
       <c r="L160" t="n">
-        <v>195600000000</v>
+        <v>91845000000</v>
       </c>
       <c r="M160" t="n">
-        <v>129320000000</v>
+        <v>70155000000</v>
       </c>
       <c r="N160" t="n">
-        <v>435624319060</v>
+        <v>193753344120</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>セーレン株式会社</t>
+          <t>データセクション株式会社</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>3569</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>36.2</v>
+        <v>2.5</v>
       </c>
       <c r="D161" t="n">
-        <v>3320</v>
+        <v>1542</v>
       </c>
       <c r="E161" t="n">
-        <v>1359.655069733296</v>
+        <v>5143.276404494382</v>
       </c>
       <c r="F161" t="n">
-        <v>144.2</v>
+        <v>-70</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -8766,102 +8766,102 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="I161" t="n">
-        <v>35451000000</v>
+        <v>1420430000</v>
       </c>
       <c r="J161" t="n">
-        <v>25813000000</v>
+        <v>1162000</v>
       </c>
       <c r="K161" t="n">
-        <v>8891000000</v>
+        <v>49326000</v>
       </c>
       <c r="L161" t="n">
-        <v>91845000000</v>
+        <v>2818110000</v>
       </c>
       <c r="M161" t="n">
-        <v>70155000000</v>
+        <v>1470918000</v>
       </c>
       <c r="N161" t="n">
-        <v>193753344120</v>
+        <v>57766875852</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>データセクション株式会社</t>
+          <t>愛眼株式会社</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>2.5</v>
+        <v>72.2</v>
       </c>
       <c r="D162" t="n">
-        <v>1542</v>
+        <v>275</v>
       </c>
       <c r="E162" t="n">
-        <v>5143.276404494382</v>
+        <v>246.9708756284982</v>
       </c>
       <c r="F162" t="n">
-        <v>-70</v>
+        <v>11.3</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1420430000</v>
+        <v>2219000000</v>
       </c>
       <c r="J162" t="n">
-        <v>1162000</v>
+        <v>1030000000</v>
       </c>
       <c r="K162" t="n">
-        <v>49326000</v>
+        <v>604000000</v>
       </c>
       <c r="L162" t="n">
-        <v>2818110000</v>
+        <v>12920000000</v>
       </c>
       <c r="M162" t="n">
-        <v>1470918000</v>
+        <v>3853000000</v>
       </c>
       <c r="N162" t="n">
-        <v>57766875852</v>
+        <v>5336846625</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>愛眼株式会社</t>
+          <t>株式会社アシロ</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>9854</t>
+          <t>7378</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>72.2</v>
+        <v>13.9</v>
       </c>
       <c r="D163" t="n">
-        <v>275</v>
+        <v>1571</v>
       </c>
       <c r="E163" t="n">
-        <v>246.9708756284982</v>
+        <v>1396.628697042366</v>
       </c>
       <c r="F163" t="n">
-        <v>11.3</v>
+        <v>12.5</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -8870,597 +8870,545 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2219000000</v>
+        <v>1428281000</v>
       </c>
       <c r="J163" t="n">
-        <v>1030000000</v>
+        <v>102238000</v>
       </c>
       <c r="K163" t="n">
-        <v>604000000</v>
+        <v>0</v>
       </c>
       <c r="L163" t="n">
-        <v>12920000000</v>
+        <v>1804458000</v>
       </c>
       <c r="M163" t="n">
-        <v>3853000000</v>
+        <v>1530519000</v>
       </c>
       <c r="N163" t="n">
-        <v>5336846625</v>
+        <v>11046623177</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>株式会社アシロ</t>
+          <t>三浦工業株式会社</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>13.9</v>
+        <v>11.6</v>
       </c>
       <c r="D164" t="n">
-        <v>1571</v>
+        <v>3154</v>
       </c>
       <c r="E164" t="n">
-        <v>1396.628697042366</v>
+        <v>3147.518794622453</v>
       </c>
       <c r="F164" t="n">
-        <v>12.5</v>
+        <v>0.2</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1428281000</v>
+        <v>20794000000</v>
       </c>
       <c r="J164" t="n">
-        <v>102238000</v>
+        <v>10600000000</v>
       </c>
       <c r="K164" t="n">
-        <v>0</v>
+        <v>10773000000</v>
       </c>
       <c r="L164" t="n">
-        <v>1804458000</v>
+        <v>138378000000</v>
       </c>
       <c r="M164" t="n">
-        <v>1530519000</v>
+        <v>42167000000</v>
       </c>
       <c r="N164" t="n">
-        <v>11046623177</v>
+        <v>365073481440</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>三浦工業株式会社</t>
+          <t>株式会社カカクコム</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>11.6</v>
+        <v>6.7</v>
       </c>
       <c r="D165" t="n">
-        <v>3154</v>
+        <v>3835</v>
       </c>
       <c r="E165" t="n">
-        <v>3147.518794622453</v>
+        <v>2318.314890576102</v>
       </c>
       <c r="F165" t="n">
-        <v>0.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="I165" t="n">
-        <v>20794000000</v>
+        <v>46452000000</v>
       </c>
       <c r="J165" t="n">
-        <v>10600000000</v>
+        <v>68000000</v>
       </c>
       <c r="K165" t="n">
-        <v>10773000000</v>
+        <v>4669000000</v>
       </c>
       <c r="L165" t="n">
-        <v>138378000000</v>
+        <v>45479000000</v>
       </c>
       <c r="M165" t="n">
-        <v>42167000000</v>
+        <v>51189000000</v>
       </c>
       <c r="N165" t="n">
-        <v>365073481440</v>
+        <v>758702083945</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>株式会社カカクコム</t>
+          <t>古河機械金属株式会社</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>6.7</v>
+        <v>45.1</v>
       </c>
       <c r="D166" t="n">
-        <v>3835</v>
+        <v>4225</v>
       </c>
       <c r="E166" t="n">
-        <v>2318.314890576102</v>
+        <v>1600</v>
       </c>
       <c r="F166" t="n">
-        <v>65.40000000000001</v>
+        <v>164.1</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="I166" t="n">
-        <v>46452000000</v>
+        <v>14468000000</v>
       </c>
       <c r="J166" t="n">
-        <v>68000000</v>
+        <v>26121000000</v>
       </c>
       <c r="K166" t="n">
-        <v>4669000000</v>
+        <v>19903000000</v>
       </c>
       <c r="L166" t="n">
-        <v>45479000000</v>
+        <v>100075000000</v>
       </c>
       <c r="M166" t="n">
-        <v>51189000000</v>
+        <v>60492000000</v>
       </c>
       <c r="N166" t="n">
-        <v>758702083945</v>
+        <v>134228744325</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>古河機械金属株式会社</t>
+          <t>多木化学株式会社</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>45.1</v>
+        <v>29.9</v>
       </c>
       <c r="D167" t="n">
-        <v>4225</v>
+        <v>5860</v>
       </c>
       <c r="E167" t="n">
-        <v>1600</v>
+        <v>4695.956053243186</v>
       </c>
       <c r="F167" t="n">
-        <v>164.1</v>
+        <v>24.8</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I167" t="n">
-        <v>14468000000</v>
+        <v>6433000000</v>
       </c>
       <c r="J167" t="n">
-        <v>26121000000</v>
+        <v>7985000000</v>
       </c>
       <c r="K167" t="n">
-        <v>19903000000</v>
+        <v>199000000</v>
       </c>
       <c r="L167" t="n">
-        <v>100075000000</v>
+        <v>29378000000</v>
       </c>
       <c r="M167" t="n">
-        <v>60492000000</v>
+        <v>14617000000</v>
       </c>
       <c r="N167" t="n">
-        <v>134228744325</v>
+        <v>48915582340</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>多木化学株式会社</t>
+          <t>エムスリー株式会社</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>4025</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>29.9</v>
+        <v>7.5</v>
       </c>
       <c r="D168" t="n">
-        <v>5860</v>
+        <v>1773</v>
       </c>
       <c r="E168" t="n">
-        <v>4695.956053243186</v>
+        <v>1638.585693292194</v>
       </c>
       <c r="F168" t="n">
-        <v>24.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I168" t="n">
-        <v>6433000000</v>
+        <v>78812000000</v>
       </c>
       <c r="J168" t="n">
-        <v>7985000000</v>
+        <v>345000000</v>
       </c>
       <c r="K168" t="n">
-        <v>199000000</v>
+        <v>9506000000</v>
       </c>
       <c r="L168" t="n">
-        <v>29378000000</v>
+        <v>152472000000</v>
       </c>
       <c r="M168" t="n">
-        <v>14617000000</v>
+        <v>88663000000</v>
       </c>
       <c r="N168" t="n">
-        <v>48915582340</v>
+        <v>1181378730753</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>エムスリー株式会社</t>
+          <t>三井松島ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2413</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>7.5</v>
+        <v>39.9</v>
       </c>
       <c r="D169" t="n">
-        <v>1773</v>
+        <v>2296</v>
       </c>
       <c r="E169" t="n">
-        <v>1638.585693292194</v>
+        <v>2920</v>
       </c>
       <c r="F169" t="n">
-        <v>8.199999999999999</v>
+        <v>-21.4</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="I169" t="n">
-        <v>78812000000</v>
+        <v>19413000000</v>
       </c>
       <c r="J169" t="n">
-        <v>345000000</v>
+        <v>3540000000</v>
       </c>
       <c r="K169" t="n">
-        <v>9506000000</v>
+        <v>10945000000</v>
       </c>
       <c r="L169" t="n">
-        <v>152472000000</v>
+        <v>35537000000</v>
       </c>
       <c r="M169" t="n">
-        <v>88663000000</v>
+        <v>33898000000</v>
       </c>
       <c r="N169" t="n">
-        <v>1181378730753</v>
+        <v>85016196160</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>三井松島ホールディングス株式会社</t>
+          <t>ノリタケ株式会社</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>39.9</v>
+        <v>37.1</v>
       </c>
       <c r="D170" t="n">
-        <v>2296</v>
+        <v>3665</v>
       </c>
       <c r="E170" t="n">
-        <v>2920</v>
+        <v>3573.410502159827</v>
       </c>
       <c r="F170" t="n">
-        <v>-21.4</v>
+        <v>2.6</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="I170" t="n">
-        <v>19413000000</v>
+        <v>11733000000</v>
       </c>
       <c r="J170" t="n">
-        <v>3540000000</v>
+        <v>20204000000</v>
       </c>
       <c r="K170" t="n">
-        <v>10945000000</v>
+        <v>42879000000</v>
       </c>
       <c r="L170" t="n">
-        <v>35537000000</v>
+        <v>118800000000</v>
       </c>
       <c r="M170" t="n">
-        <v>33898000000</v>
+        <v>74816000000</v>
       </c>
       <c r="N170" t="n">
-        <v>85016196160</v>
+        <v>201627314210</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ノリタケ株式会社</t>
+          <t>株式会社ＡＣＳＬ</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>6232</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>37.1</v>
+        <v>7.6</v>
       </c>
       <c r="D171" t="n">
-        <v>3665</v>
+        <v>1398</v>
       </c>
       <c r="E171" t="n">
-        <v>3573.410502159827</v>
+        <v>913.2768512341561</v>
       </c>
       <c r="F171" t="n">
-        <v>2.6</v>
+        <v>53.1</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="I171" t="n">
-        <v>11733000000</v>
+        <v>1891731000</v>
       </c>
       <c r="J171" t="n">
-        <v>20204000000</v>
+        <v>3724000</v>
       </c>
       <c r="K171" t="n">
-        <v>42879000000</v>
+        <v>197577000</v>
       </c>
       <c r="L171" t="n">
-        <v>118800000000</v>
+        <v>3572642000</v>
       </c>
       <c r="M171" t="n">
-        <v>74816000000</v>
+        <v>2093032000</v>
       </c>
       <c r="N171" t="n">
-        <v>201627314210</v>
+        <v>27361994316</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>株式会社ＡＣＳＬ</t>
+          <t>株式会社スズケン</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>9987</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>7.6</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="D172" t="n">
-        <v>1398</v>
+        <v>5268</v>
       </c>
       <c r="E172" t="n">
-        <v>913.2768512341561</v>
+        <v>4137.137750115735</v>
       </c>
       <c r="F172" t="n">
-        <v>53.1</v>
+        <v>27.3</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1891731000</v>
+        <v>168215000000</v>
       </c>
       <c r="J172" t="n">
-        <v>3724000</v>
+        <v>65453000000</v>
       </c>
       <c r="K172" t="n">
-        <v>197577000</v>
+        <v>38927000000</v>
       </c>
       <c r="L172" t="n">
-        <v>3572642000</v>
+        <v>418062000000</v>
       </c>
       <c r="M172" t="n">
-        <v>2093032000</v>
+        <v>272595000000</v>
       </c>
       <c r="N172" t="n">
-        <v>27361994316</v>
+        <v>351292307652</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>株式会社スズケン</t>
+          <t>フォスター電機株式会社</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>9987</t>
+          <t>6794</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>77.59999999999999</v>
+        <v>28.2</v>
       </c>
       <c r="D173" t="n">
-        <v>5268</v>
+        <v>3240</v>
       </c>
       <c r="E173" t="n">
-        <v>4137.137750115735</v>
+        <v>2681.96152003832</v>
       </c>
       <c r="F173" t="n">
-        <v>27.3</v>
+        <v>20.8</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="I173" t="n">
-        <v>168215000000</v>
+        <v>12089000000</v>
       </c>
       <c r="J173" t="n">
-        <v>65453000000</v>
+        <v>7327000000</v>
       </c>
       <c r="K173" t="n">
-        <v>38927000000</v>
+        <v>1115000000</v>
       </c>
       <c r="L173" t="n">
-        <v>418062000000</v>
+        <v>51632000000</v>
       </c>
       <c r="M173" t="n">
-        <v>272595000000</v>
+        <v>20531000000</v>
       </c>
       <c r="N173" t="n">
-        <v>351292307652</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>フォスター電機株式会社</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>6794</t>
-        </is>
-      </c>
-      <c r="C174" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="D174" t="n">
-        <v>3240</v>
-      </c>
-      <c r="E174" t="n">
-        <v>2681.96152003832</v>
-      </c>
-      <c r="F174" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>2026-01-22</t>
-        </is>
-      </c>
-      <c r="I174" t="n">
-        <v>12089000000</v>
-      </c>
-      <c r="J174" t="n">
-        <v>7327000000</v>
-      </c>
-      <c r="K174" t="n">
-        <v>1115000000</v>
-      </c>
-      <c r="L174" t="n">
-        <v>51632000000</v>
-      </c>
-      <c r="M174" t="n">
-        <v>20531000000</v>
-      </c>
-      <c r="N174" t="n">
         <v>72795694680</v>
       </c>
     </row>

--- a/docs/アクティビスト銘柄_資産判定.xlsx
+++ b/docs/アクティビスト銘柄_資産判定.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N175"/>
+  <dimension ref="A1:N178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>93.7</v>
+        <v>93.5</v>
       </c>
       <c r="D2" t="n">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="E2" t="n">
         <v>810</v>
       </c>
       <c r="F2" t="n">
-        <v>51.4</v>
+        <v>51.6</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -537,7 +537,7 @@
         <v>50303000000</v>
       </c>
       <c r="N2" t="n">
-        <v>53708827454</v>
+        <v>53796443812</v>
       </c>
     </row>
     <row r="3">
@@ -552,16 +552,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>68.3</v>
+        <v>67.7</v>
       </c>
       <c r="D3" t="n">
-        <v>2926</v>
+        <v>2952</v>
       </c>
       <c r="E3" t="n">
         <v>2723.418631349517</v>
       </c>
       <c r="F3" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         <v>165282000000</v>
       </c>
       <c r="N3" t="n">
-        <v>241876426484</v>
+        <v>244025704368</v>
       </c>
     </row>
     <row r="4">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>68.3</v>
+        <v>67.7</v>
       </c>
       <c r="D4" t="n">
-        <v>2926</v>
+        <v>2952</v>
       </c>
       <c r="E4" t="n">
         <v>2709.132103263819</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         <v>165282000000</v>
       </c>
       <c r="N4" t="n">
-        <v>241876426484</v>
+        <v>244025704368</v>
       </c>
     </row>
     <row r="5">
@@ -656,16 +656,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>68.3</v>
+        <v>67.7</v>
       </c>
       <c r="D5" t="n">
-        <v>2926</v>
+        <v>2952</v>
       </c>
       <c r="E5" t="n">
         <v>2696.128808062088</v>
       </c>
       <c r="F5" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         <v>165282000000</v>
       </c>
       <c r="N5" t="n">
-        <v>241876426484</v>
+        <v>244025704368</v>
       </c>
     </row>
     <row r="6">
@@ -708,16 +708,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>68.3</v>
+        <v>67.7</v>
       </c>
       <c r="D6" t="n">
-        <v>2926</v>
+        <v>2952</v>
       </c>
       <c r="E6" t="n">
         <v>2696.128808062088</v>
       </c>
       <c r="F6" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>165282000000</v>
       </c>
       <c r="N6" t="n">
-        <v>241876426484</v>
+        <v>244025704368</v>
       </c>
     </row>
     <row r="7">
@@ -763,13 +763,13 @@
         <v>57.9</v>
       </c>
       <c r="D7" t="n">
-        <v>719.4000244140625</v>
+        <v>719.5</v>
       </c>
       <c r="E7" t="n">
         <v>530</v>
       </c>
       <c r="F7" t="n">
-        <v>35.7</v>
+        <v>35.8</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>277200000000</v>
       </c>
       <c r="N7" t="n">
-        <v>478383342735</v>
+        <v>478449824044</v>
       </c>
     </row>
     <row r="8">
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="D8" t="n">
-        <v>5656</v>
+        <v>5793</v>
       </c>
       <c r="E8" t="n">
         <v>3341.42986565678</v>
       </c>
       <c r="F8" t="n">
-        <v>69.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>311107000000</v>
       </c>
       <c r="N8" t="n">
-        <v>1344000738808</v>
+        <v>1376555212149</v>
       </c>
     </row>
     <row r="9">
@@ -867,13 +867,13 @@
         <v>67.40000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>4076</v>
+        <v>4075</v>
       </c>
       <c r="E9" t="n">
         <v>3141.424011416125</v>
       </c>
       <c r="F9" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>391579000000</v>
       </c>
       <c r="N9" t="n">
-        <v>580812081904</v>
+        <v>580834599350</v>
       </c>
     </row>
     <row r="10">
@@ -919,7 +919,7 @@
         <v>67.40000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>4076</v>
+        <v>4075</v>
       </c>
       <c r="E10" t="n">
         <v>2420</v>
@@ -953,7 +953,7 @@
         <v>391579000000</v>
       </c>
       <c r="N10" t="n">
-        <v>580812081904</v>
+        <v>580834599350</v>
       </c>
     </row>
     <row r="11">
@@ -968,16 +968,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="D11" t="n">
-        <v>1730.5</v>
+        <v>1767.5</v>
       </c>
       <c r="E11" t="n">
         <v>1638.585693292194</v>
       </c>
       <c r="F11" t="n">
-        <v>5.6</v>
+        <v>7.9</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>88663000000</v>
       </c>
       <c r="N11" t="n">
-        <v>1153060289660</v>
+        <v>1177713991318</v>
       </c>
     </row>
     <row r="12">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>50.5</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>11580</v>
+        <v>11690</v>
       </c>
       <c r="E12" t="n">
         <v>5684.0003469471</v>
       </c>
       <c r="F12" t="n">
-        <v>103.7</v>
+        <v>105.7</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>91895000000</v>
       </c>
       <c r="N12" t="n">
-        <v>181934051640</v>
+        <v>183662268020</v>
       </c>
     </row>
     <row r="13">
@@ -1072,16 +1072,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>50.5</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>11580</v>
+        <v>11690</v>
       </c>
       <c r="E13" t="n">
         <v>4549.503641591014</v>
       </c>
       <c r="F13" t="n">
-        <v>154.5</v>
+        <v>157</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>91895000000</v>
       </c>
       <c r="N13" t="n">
-        <v>181934051640</v>
+        <v>183662268020</v>
       </c>
     </row>
     <row r="14">
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>28.1</v>
+        <v>27.8</v>
       </c>
       <c r="D14" t="n">
-        <v>3255</v>
+        <v>3285</v>
       </c>
       <c r="E14" t="n">
         <v>2681.96152003832</v>
       </c>
       <c r="F14" t="n">
-        <v>21.4</v>
+        <v>22.5</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>20531000000</v>
       </c>
       <c r="N14" t="n">
-        <v>73132711785</v>
+        <v>73806745995</v>
       </c>
     </row>
     <row r="15">
@@ -1176,16 +1176,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
       <c r="D15" t="n">
-        <v>14020</v>
+        <v>13990</v>
       </c>
       <c r="E15" t="n">
         <v>7040.15625</v>
       </c>
       <c r="F15" t="n">
-        <v>99.09999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>6799899000</v>
       </c>
       <c r="N15" t="n">
-        <v>14405087340</v>
+        <v>14374263330</v>
       </c>
     </row>
     <row r="16">
@@ -1228,16 +1228,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
       <c r="D16" t="n">
-        <v>14020</v>
+        <v>13990</v>
       </c>
       <c r="E16" t="n">
         <v>7040.15625</v>
       </c>
       <c r="F16" t="n">
-        <v>99.09999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>6799899000</v>
       </c>
       <c r="N16" t="n">
-        <v>14405087340</v>
+        <v>14374263330</v>
       </c>
     </row>
     <row r="17">
@@ -1280,16 +1280,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>42.4</v>
+        <v>41.7</v>
       </c>
       <c r="D17" t="n">
-        <v>1368</v>
+        <v>1389</v>
       </c>
       <c r="E17" t="n">
         <v>1347.74653160027</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>13952000000</v>
       </c>
       <c r="N17" t="n">
-        <v>32921245584</v>
+        <v>33426615582</v>
       </c>
     </row>
     <row r="18">
@@ -1335,13 +1335,13 @@
         <v>6.9</v>
       </c>
       <c r="D18" t="n">
-        <v>3485</v>
+        <v>3513</v>
       </c>
       <c r="E18" t="n">
         <v>6116.356643776557</v>
       </c>
       <c r="F18" t="n">
-        <v>-43</v>
+        <v>-42.6</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>219041000000</v>
       </c>
       <c r="N18" t="n">
-        <v>3153081609090</v>
+        <v>3178414832922</v>
       </c>
     </row>
     <row r="19">
@@ -1387,13 +1387,13 @@
         <v>34</v>
       </c>
       <c r="D19" t="n">
-        <v>3230</v>
+        <v>3225</v>
       </c>
       <c r="E19" t="n">
         <v>3155.301177013616</v>
       </c>
       <c r="F19" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>70480000000</v>
       </c>
       <c r="N19" t="n">
-        <v>207517157540</v>
+        <v>207195923550</v>
       </c>
     </row>
     <row r="20">
@@ -1436,16 +1436,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>32.5</v>
+        <v>32.7</v>
       </c>
       <c r="D20" t="n">
-        <v>4745</v>
+        <v>4715</v>
       </c>
       <c r="E20" t="n">
         <v>2824.318397803668</v>
       </c>
       <c r="F20" t="n">
-        <v>68</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>61975000000</v>
       </c>
       <c r="N20" t="n">
-        <v>190894457975</v>
+        <v>189687538325</v>
       </c>
     </row>
     <row r="21">
@@ -1488,16 +1488,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>216.4</v>
+        <v>213.3</v>
       </c>
       <c r="D21" t="n">
-        <v>1599</v>
+        <v>1622</v>
       </c>
       <c r="E21" t="n">
         <v>1288.711724885291</v>
       </c>
       <c r="F21" t="n">
-        <v>24.1</v>
+        <v>25.9</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>747066000000</v>
       </c>
       <c r="N21" t="n">
-        <v>345198792627</v>
+        <v>350164128606</v>
       </c>
     </row>
     <row r="22">
@@ -1540,16 +1540,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>43</v>
+        <v>43.3</v>
       </c>
       <c r="D22" t="n">
-        <v>3976</v>
+        <v>3948</v>
       </c>
       <c r="E22" t="n">
         <v>3047.091476167608</v>
       </c>
       <c r="F22" t="n">
-        <v>30.5</v>
+        <v>29.6</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>162458000000</v>
       </c>
       <c r="N22" t="n">
-        <v>377573154392</v>
+        <v>374914188516</v>
       </c>
     </row>
     <row r="23">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>52.9</v>
+        <v>52.5</v>
       </c>
       <c r="D23" t="n">
-        <v>996</v>
+        <v>1004</v>
       </c>
       <c r="E23" t="n">
         <v>896.0103264198827</v>
       </c>
       <c r="F23" t="n">
-        <v>11.2</v>
+        <v>12.1</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>9570532000</v>
       </c>
       <c r="N23" t="n">
-        <v>18079060332</v>
+        <v>18224273668</v>
       </c>
     </row>
     <row r="24">
@@ -1644,16 +1644,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>53.8</v>
+        <v>54.2</v>
       </c>
       <c r="D24" t="n">
-        <v>1181</v>
+        <v>1173</v>
       </c>
       <c r="E24" t="n">
         <v>1019.677694332945</v>
       </c>
       <c r="F24" t="n">
-        <v>15.8</v>
+        <v>15</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>106991000000</v>
       </c>
       <c r="N24" t="n">
-        <v>198703899550</v>
+        <v>197357895150</v>
       </c>
     </row>
     <row r="25">
@@ -1699,13 +1699,13 @@
         <v>49.9</v>
       </c>
       <c r="D25" t="n">
-        <v>4063</v>
+        <v>4061</v>
       </c>
       <c r="E25" t="n">
         <v>3405.914389596362</v>
       </c>
       <c r="F25" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>131234000000</v>
       </c>
       <c r="N25" t="n">
-        <v>262882694249</v>
+        <v>262753291003</v>
       </c>
     </row>
     <row r="26">
@@ -1751,13 +1751,13 @@
         <v>49.9</v>
       </c>
       <c r="D26" t="n">
-        <v>4063</v>
+        <v>4061</v>
       </c>
       <c r="E26" t="n">
         <v>2714.613787300615</v>
       </c>
       <c r="F26" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>131234000000</v>
       </c>
       <c r="N26" t="n">
-        <v>262882694249</v>
+        <v>262753291003</v>
       </c>
     </row>
     <row r="27">
@@ -1803,13 +1803,13 @@
         <v>14.1</v>
       </c>
       <c r="D27" t="n">
-        <v>3877</v>
+        <v>3885</v>
       </c>
       <c r="E27" t="n">
         <v>2561.705402476645</v>
       </c>
       <c r="F27" t="n">
-        <v>51.3</v>
+        <v>51.7</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>100104000000</v>
       </c>
       <c r="N27" t="n">
-        <v>709418907185</v>
+        <v>710882758425</v>
       </c>
     </row>
     <row r="28">
@@ -1855,13 +1855,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>1736</v>
+        <v>1748.5</v>
       </c>
       <c r="E28" t="n">
         <v>1344.518957928979</v>
       </c>
       <c r="F28" t="n">
-        <v>29.1</v>
+        <v>30</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>45956000000</v>
       </c>
       <c r="N28" t="n">
-        <v>557628009176</v>
+        <v>561643187814</v>
       </c>
     </row>
     <row r="29">
@@ -1904,16 +1904,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>29.6</v>
+        <v>25.3</v>
       </c>
       <c r="D29" t="n">
-        <v>5885</v>
+        <v>6885</v>
       </c>
       <c r="E29" t="n">
         <v>2148.936934940886</v>
       </c>
       <c r="F29" t="n">
-        <v>173.9</v>
+        <v>220.4</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>129320000000</v>
       </c>
       <c r="N29" t="n">
-        <v>437482784585</v>
+        <v>511821405585</v>
       </c>
     </row>
     <row r="30">
@@ -1956,16 +1956,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>29.6</v>
+        <v>25.3</v>
       </c>
       <c r="D30" t="n">
-        <v>5885</v>
+        <v>6885</v>
       </c>
       <c r="E30" t="n">
         <v>5066.092575838703</v>
       </c>
       <c r="F30" t="n">
-        <v>16.2</v>
+        <v>35.9</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>129320000000</v>
       </c>
       <c r="N30" t="n">
-        <v>437482784585</v>
+        <v>511821405585</v>
       </c>
     </row>
     <row r="31">
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="D31" t="n">
-        <v>2370</v>
+        <v>2373</v>
       </c>
       <c r="E31" t="n">
         <v>3610</v>
@@ -2045,7 +2045,7 @@
         <v>113427000000</v>
       </c>
       <c r="N31" t="n">
-        <v>156586511460</v>
+        <v>156784722234</v>
       </c>
     </row>
     <row r="32">
@@ -2063,13 +2063,13 @@
         <v>16.8</v>
       </c>
       <c r="D32" t="n">
-        <v>2964</v>
+        <v>2958</v>
       </c>
       <c r="E32" t="n">
         <v>6272.971195510064</v>
       </c>
       <c r="F32" t="n">
-        <v>-52.7</v>
+        <v>-52.8</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>179622000000</v>
       </c>
       <c r="N32" t="n">
-        <v>1069042282776</v>
+        <v>1066878229572</v>
       </c>
     </row>
     <row r="33">
@@ -2112,16 +2112,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>41.6</v>
+        <v>41.4</v>
       </c>
       <c r="D33" t="n">
-        <v>870.2999877929688</v>
+        <v>875.7999877929688</v>
       </c>
       <c r="E33" t="n">
         <v>590</v>
       </c>
       <c r="F33" t="n">
-        <v>47.5</v>
+        <v>48.4</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>307640000000</v>
       </c>
       <c r="N33" t="n">
-        <v>739088594831</v>
+        <v>743759383443</v>
       </c>
     </row>
     <row r="34">
@@ -2164,16 +2164,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="D34" t="n">
-        <v>4110</v>
+        <v>4165</v>
       </c>
       <c r="E34" t="n">
         <v>7960</v>
       </c>
       <c r="F34" t="n">
-        <v>-48.4</v>
+        <v>-47.7</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>29865000000</v>
       </c>
       <c r="N34" t="n">
-        <v>157088531940</v>
+        <v>159190689910</v>
       </c>
     </row>
     <row r="35">
@@ -2268,16 +2268,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>75.7</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>5400</v>
+        <v>5386</v>
       </c>
       <c r="E36" t="n">
         <v>4137.137750115735</v>
       </c>
       <c r="F36" t="n">
-        <v>30.5</v>
+        <v>30.2</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>272595000000</v>
       </c>
       <c r="N36" t="n">
-        <v>360094620600</v>
+        <v>359161041954</v>
       </c>
     </row>
     <row r="37">
@@ -2323,13 +2323,13 @@
         <v>30.8</v>
       </c>
       <c r="D37" t="n">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="E37" t="n">
         <v>930</v>
       </c>
       <c r="F37" t="n">
-        <v>68.40000000000001</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>13769000000</v>
       </c>
       <c r="N37" t="n">
-        <v>44709141834</v>
+        <v>44766241632</v>
       </c>
     </row>
     <row r="38">
@@ -2372,16 +2372,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="D38" t="n">
-        <v>1571</v>
+        <v>1581</v>
       </c>
       <c r="E38" t="n">
         <v>1396.628697042366</v>
       </c>
       <c r="F38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>1530519000</v>
       </c>
       <c r="N38" t="n">
-        <v>11046623177</v>
+        <v>11116939047</v>
       </c>
     </row>
     <row r="39">
@@ -2424,16 +2424,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="D39" t="n">
-        <v>2194</v>
+        <v>2200</v>
       </c>
       <c r="E39" t="n">
         <v>5463.67048346056</v>
       </c>
       <c r="F39" t="n">
-        <v>-59.8</v>
+        <v>-59.7</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>11249000000</v>
       </c>
       <c r="N39" t="n">
-        <v>38376548460</v>
+        <v>38481498000</v>
       </c>
     </row>
     <row r="40">
@@ -2476,16 +2476,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>29.1</v>
+        <v>29</v>
       </c>
       <c r="D40" t="n">
-        <v>2388</v>
+        <v>2391</v>
       </c>
       <c r="E40" t="n">
         <v>1947.225264702313</v>
       </c>
       <c r="F40" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>22893000000</v>
       </c>
       <c r="N40" t="n">
-        <v>78721788324</v>
+        <v>78820685043</v>
       </c>
     </row>
     <row r="41">
@@ -2528,16 +2528,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>29.1</v>
+        <v>29</v>
       </c>
       <c r="D41" t="n">
-        <v>2388</v>
+        <v>2391</v>
       </c>
       <c r="E41" t="n">
         <v>1678.083113259255</v>
       </c>
       <c r="F41" t="n">
-        <v>42.3</v>
+        <v>42.5</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>22893000000</v>
       </c>
       <c r="N41" t="n">
-        <v>78721788324</v>
+        <v>78820685043</v>
       </c>
     </row>
     <row r="42">
@@ -2580,16 +2580,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>15.3</v>
+        <v>15</v>
       </c>
       <c r="D42" t="n">
-        <v>716</v>
+        <v>729</v>
       </c>
       <c r="E42" t="n">
         <v>510.1850530906719</v>
       </c>
       <c r="F42" t="n">
-        <v>40.3</v>
+        <v>42.9</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>27518000000</v>
       </c>
       <c r="N42" t="n">
-        <v>179976397744</v>
+        <v>183244125636</v>
       </c>
     </row>
     <row r="43">
@@ -2632,16 +2632,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>45</v>
+        <v>44.6</v>
       </c>
       <c r="D43" t="n">
-        <v>3337</v>
+        <v>3367</v>
       </c>
       <c r="E43" t="n">
         <v>1492.806001579363</v>
       </c>
       <c r="F43" t="n">
-        <v>123.5</v>
+        <v>125.5</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>112301000000</v>
       </c>
       <c r="N43" t="n">
-        <v>249621899045</v>
+        <v>251866027595</v>
       </c>
     </row>
     <row r="44">
@@ -2684,16 +2684,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>62.6</v>
+        <v>62</v>
       </c>
       <c r="D44" t="n">
-        <v>3551</v>
+        <v>3586</v>
       </c>
       <c r="E44" t="n">
         <v>1716.713876475349</v>
       </c>
       <c r="F44" t="n">
-        <v>106.8</v>
+        <v>108.9</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>565345000000</v>
       </c>
       <c r="N44" t="n">
-        <v>902585325188</v>
+        <v>911481547768</v>
       </c>
     </row>
     <row r="45">
@@ -2736,16 +2736,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>75.90000000000001</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>4740</v>
+        <v>4869</v>
       </c>
       <c r="E45" t="n">
         <v>4991.027246539169</v>
       </c>
       <c r="F45" t="n">
-        <v>-5</v>
+        <v>-2.4</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>1007966000000</v>
       </c>
       <c r="N45" t="n">
-        <v>1328250981240</v>
+        <v>1364399583894</v>
       </c>
     </row>
     <row r="46">
@@ -2788,16 +2788,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>30.5</v>
+        <v>30.3</v>
       </c>
       <c r="D46" t="n">
-        <v>2203.5</v>
+        <v>2219.5</v>
       </c>
       <c r="E46" t="n">
         <v>1815.198567455447</v>
       </c>
       <c r="F46" t="n">
-        <v>21.4</v>
+        <v>22.3</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>168499000000</v>
       </c>
       <c r="N46" t="n">
-        <v>552235114782</v>
+        <v>556358371752</v>
       </c>
     </row>
     <row r="47">
@@ -2840,16 +2840,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>19.4</v>
+        <v>19.1</v>
       </c>
       <c r="D47" t="n">
-        <v>23530</v>
+        <v>23855</v>
       </c>
       <c r="E47" t="n">
         <v>11879.91675437757</v>
       </c>
       <c r="F47" t="n">
-        <v>98.09999999999999</v>
+        <v>100.8</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>191958000000</v>
       </c>
       <c r="N47" t="n">
-        <v>988767189150</v>
+        <v>1002424194525</v>
       </c>
     </row>
     <row r="48">
@@ -2892,16 +2892,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="D48" t="n">
-        <v>6000</v>
+        <v>5980</v>
       </c>
       <c r="E48" t="n">
         <v>2617.980935875217</v>
       </c>
       <c r="F48" t="n">
-        <v>129.2</v>
+        <v>128.4</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>40238000000</v>
       </c>
       <c r="N48" t="n">
-        <v>214761396000</v>
+        <v>214045524680</v>
       </c>
     </row>
     <row r="49">
@@ -2944,16 +2944,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>50.6</v>
+        <v>50.3</v>
       </c>
       <c r="D49" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E49" t="n">
         <v>290.3401328717133</v>
       </c>
       <c r="F49" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>5162755000</v>
       </c>
       <c r="N49" t="n">
-        <v>10203516666</v>
+        <v>10272928344</v>
       </c>
     </row>
     <row r="50">
@@ -2996,16 +2996,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>64.7</v>
+        <v>64.3</v>
       </c>
       <c r="D50" t="n">
-        <v>2120.5</v>
+        <v>2135</v>
       </c>
       <c r="E50" t="n">
         <v>1101.400153022188</v>
       </c>
       <c r="F50" t="n">
-        <v>92.5</v>
+        <v>93.8</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>402053000000</v>
       </c>
       <c r="N50" t="n">
-        <v>621337035200</v>
+        <v>625585744000</v>
       </c>
     </row>
     <row r="51">
@@ -3048,16 +3048,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>64.7</v>
+        <v>64.3</v>
       </c>
       <c r="D51" t="n">
-        <v>2120.5</v>
+        <v>2135</v>
       </c>
       <c r="E51" t="n">
         <v>1101.400153022188</v>
       </c>
       <c r="F51" t="n">
-        <v>92.5</v>
+        <v>93.8</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>402053000000</v>
       </c>
       <c r="N51" t="n">
-        <v>621337035200</v>
+        <v>625585744000</v>
       </c>
     </row>
     <row r="52">
@@ -3204,16 +3204,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>32.1</v>
+        <v>31.6</v>
       </c>
       <c r="D54" t="n">
-        <v>2259</v>
+        <v>2297</v>
       </c>
       <c r="E54" t="n">
         <v>1879.137815927515</v>
       </c>
       <c r="F54" t="n">
-        <v>20.2</v>
+        <v>22.2</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>15117000000</v>
       </c>
       <c r="N54" t="n">
-        <v>47037907773</v>
+        <v>47829160759</v>
       </c>
     </row>
     <row r="55">
@@ -3256,16 +3256,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>76</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="D55" t="n">
-        <v>2548.5</v>
+        <v>2545.5</v>
       </c>
       <c r="E55" t="n">
         <v>2551.08574256026</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>179136000000</v>
       </c>
       <c r="N55" t="n">
-        <v>235765917088</v>
+        <v>235488382166</v>
       </c>
     </row>
     <row r="56">
@@ -3308,16 +3308,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>76</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="D56" t="n">
-        <v>2548.5</v>
+        <v>2545.5</v>
       </c>
       <c r="E56" t="n">
         <v>2260</v>
       </c>
       <c r="F56" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>179136000000</v>
       </c>
       <c r="N56" t="n">
-        <v>235765917088</v>
+        <v>235488382166</v>
       </c>
     </row>
     <row r="57">
@@ -3360,16 +3360,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>76</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="D57" t="n">
-        <v>2548.5</v>
+        <v>2545.5</v>
       </c>
       <c r="E57" t="n">
         <v>2260</v>
       </c>
       <c r="F57" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>179136000000</v>
       </c>
       <c r="N57" t="n">
-        <v>235765917088</v>
+        <v>235488382166</v>
       </c>
     </row>
     <row r="58">
@@ -3464,16 +3464,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="D59" t="n">
-        <v>4744</v>
+        <v>4780</v>
       </c>
       <c r="E59" t="n">
         <v>2199.643244598912</v>
       </c>
       <c r="F59" t="n">
-        <v>115.7</v>
+        <v>117.3</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>86359000000</v>
       </c>
       <c r="N59" t="n">
-        <v>527896579408</v>
+        <v>531902539960</v>
       </c>
     </row>
     <row r="60">
@@ -3516,16 +3516,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="D60" t="n">
-        <v>4744</v>
+        <v>4780</v>
       </c>
       <c r="E60" t="n">
         <v>3565.648720929983</v>
       </c>
       <c r="F60" t="n">
-        <v>33</v>
+        <v>34.1</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>86359000000</v>
       </c>
       <c r="N60" t="n">
-        <v>527896579408</v>
+        <v>531902539960</v>
       </c>
     </row>
     <row r="61">
@@ -3612,16 +3612,16 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>43.3</v>
+        <v>43.1</v>
       </c>
       <c r="D62" t="n">
-        <v>3574</v>
+        <v>3584</v>
       </c>
       <c r="E62" t="n">
         <v>2560</v>
       </c>
       <c r="F62" t="n">
-        <v>39.6</v>
+        <v>40</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>190312000000</v>
       </c>
       <c r="N62" t="n">
-        <v>439996233644</v>
+        <v>441227336704</v>
       </c>
     </row>
     <row r="63">
@@ -3664,16 +3664,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>63.7</v>
+        <v>64.3</v>
       </c>
       <c r="D63" t="n">
-        <v>1368</v>
+        <v>1356</v>
       </c>
       <c r="E63" t="n">
         <v>3321.975331035734</v>
       </c>
       <c r="F63" t="n">
-        <v>-58.8</v>
+        <v>-59.2</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>25606000000</v>
       </c>
       <c r="N63" t="n">
-        <v>40200091776</v>
+        <v>39847459392</v>
       </c>
     </row>
     <row r="64">
@@ -3716,16 +3716,16 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>72.2</v>
+        <v>72.7</v>
       </c>
       <c r="D64" t="n">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E64" t="n">
         <v>246.9708756284982</v>
       </c>
       <c r="F64" t="n">
-        <v>11.3</v>
+        <v>10.5</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>3853000000</v>
       </c>
       <c r="N64" t="n">
-        <v>5336846625</v>
+        <v>5298033195</v>
       </c>
     </row>
     <row r="65">
@@ -3768,16 +3768,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>120.9</v>
+        <v>120.8</v>
       </c>
       <c r="D65" t="n">
-        <v>1548.5</v>
+        <v>1550</v>
       </c>
       <c r="E65" t="n">
         <v>1160.8</v>
       </c>
       <c r="F65" t="n">
-        <v>33.4</v>
+        <v>33.5</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>493483000000</v>
       </c>
       <c r="N65" t="n">
-        <v>408039785828</v>
+        <v>408435045550</v>
       </c>
     </row>
     <row r="66">
@@ -3820,16 +3820,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>91.90000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="D66" t="n">
-        <v>2626</v>
+        <v>2650</v>
       </c>
       <c r="E66" t="n">
         <v>1748.071046781136</v>
       </c>
       <c r="F66" t="n">
-        <v>50.2</v>
+        <v>51.6</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3857,111 +3857,111 @@
         <v>72190000000</v>
       </c>
       <c r="N66" t="n">
-        <v>78566083414</v>
+        <v>79284128350</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>株式会社Ａ＆Ｄホロンホールディングス</t>
+          <t>あいホールディングス株式会社</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>7745</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>19.1</v>
+        <v>28.7</v>
       </c>
       <c r="D67" t="n">
-        <v>2943</v>
+        <v>3020</v>
       </c>
       <c r="E67" t="n">
-        <v>2084.177692465894</v>
+        <v>2007.754513143541</v>
       </c>
       <c r="F67" t="n">
-        <v>41.2</v>
+        <v>50.4</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>11012000000</v>
+        <v>36435000000</v>
       </c>
       <c r="J67" t="n">
-        <v>4106000000</v>
+        <v>4565000000</v>
       </c>
       <c r="K67" t="n">
-        <v>315000000</v>
+        <v>5138000000</v>
       </c>
       <c r="L67" t="n">
-        <v>27041000000</v>
+        <v>61337000000</v>
       </c>
       <c r="M67" t="n">
-        <v>15433000000</v>
+        <v>46138000000</v>
       </c>
       <c r="N67" t="n">
-        <v>80600885703</v>
+        <v>160884251620</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ＮＩＴＴＯＫＵ株式会社</t>
+          <t>株式会社Ａ＆Ｄホロンホールディングス</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>7745</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>46.9</v>
+        <v>18.7</v>
       </c>
       <c r="D68" t="n">
-        <v>2663</v>
+        <v>3010</v>
       </c>
       <c r="E68" t="n">
-        <v>1710</v>
+        <v>2084.177692465894</v>
       </c>
       <c r="F68" t="n">
-        <v>55.7</v>
+        <v>44.4</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>11768000000</v>
+        <v>11012000000</v>
       </c>
       <c r="J68" t="n">
-        <v>6299000000</v>
+        <v>4106000000</v>
       </c>
       <c r="K68" t="n">
-        <v>2999000000</v>
+        <v>315000000</v>
       </c>
       <c r="L68" t="n">
-        <v>33919000000</v>
+        <v>27041000000</v>
       </c>
       <c r="M68" t="n">
-        <v>21066000000</v>
+        <v>15433000000</v>
       </c>
       <c r="N68" t="n">
-        <v>44936745566</v>
+        <v>82435836210</v>
       </c>
     </row>
     <row r="69">
@@ -3976,16 +3976,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>46.9</v>
+        <v>46.6</v>
       </c>
       <c r="D69" t="n">
-        <v>2663</v>
+        <v>2678</v>
       </c>
       <c r="E69" t="n">
         <v>1710</v>
       </c>
       <c r="F69" t="n">
-        <v>55.7</v>
+        <v>56.6</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -4013,427 +4013,427 @@
         <v>21066000000</v>
       </c>
       <c r="N69" t="n">
-        <v>44936745566</v>
+        <v>45189862796</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>ＮＩＴＴＯＫＵ株式会社</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>6145</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="D70" t="n">
+        <v>2678</v>
+      </c>
+      <c r="E70" t="n">
+        <v>1710</v>
+      </c>
+      <c r="F70" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>11768000000</v>
+      </c>
+      <c r="J70" t="n">
+        <v>6299000000</v>
+      </c>
+      <c r="K70" t="n">
+        <v>2999000000</v>
+      </c>
+      <c r="L70" t="n">
+        <v>33919000000</v>
+      </c>
+      <c r="M70" t="n">
+        <v>21066000000</v>
+      </c>
+      <c r="N70" t="n">
+        <v>45189862796</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
           <t>株式会社フェローテック
 （旧会社名　株式会社フェローテックホールディングス）</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>6890</t>
         </is>
       </c>
-      <c r="C70" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="D70" t="n">
-        <v>10300</v>
-      </c>
-      <c r="E70" t="n">
+      <c r="C71" t="n">
+        <v>27</v>
+      </c>
+      <c r="D71" t="n">
+        <v>10640</v>
+      </c>
+      <c r="E71" t="n">
         <v>4037.502552255647</v>
       </c>
-      <c r="F70" t="n">
-        <v>155.1</v>
-      </c>
-      <c r="G70" t="inlineStr">
+      <c r="F71" t="n">
+        <v>163.5</v>
+      </c>
+      <c r="G71" t="inlineStr">
         <is>
           <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="I70" t="n">
+      <c r="I71" t="n">
         <v>52579000000</v>
       </c>
-      <c r="J70" t="n">
+      <c r="J71" t="n">
         <v>90505000000</v>
       </c>
-      <c r="K70" t="n">
+      <c r="K71" t="n">
         <v>11654000000</v>
       </c>
-      <c r="L70" t="n">
+      <c r="L71" t="n">
         <v>160957000000</v>
       </c>
-      <c r="M70" t="n">
+      <c r="M71" t="n">
         <v>154738000000</v>
       </c>
-      <c r="N70" t="n">
-        <v>554178758900</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="N71" t="n">
+        <v>572472038320</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>株式会社フェローテック
 （旧会社名　株式会社フェローテックホールディングス）</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>6890</t>
         </is>
       </c>
-      <c r="C71" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="D71" t="n">
-        <v>10300</v>
-      </c>
-      <c r="E71" t="n">
+      <c r="C72" t="n">
+        <v>27</v>
+      </c>
+      <c r="D72" t="n">
+        <v>10640</v>
+      </c>
+      <c r="E72" t="n">
         <v>3950.736048458928</v>
       </c>
-      <c r="F71" t="n">
-        <v>160.7</v>
-      </c>
-      <c r="G71" t="inlineStr">
+      <c r="F72" t="n">
+        <v>169.3</v>
+      </c>
+      <c r="G72" t="inlineStr">
         <is>
           <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="I71" t="n">
+      <c r="I72" t="n">
         <v>52579000000</v>
       </c>
-      <c r="J71" t="n">
+      <c r="J72" t="n">
         <v>90505000000</v>
       </c>
-      <c r="K71" t="n">
+      <c r="K72" t="n">
         <v>11654000000</v>
       </c>
-      <c r="L71" t="n">
+      <c r="L72" t="n">
         <v>160957000000</v>
       </c>
-      <c r="M71" t="n">
+      <c r="M72" t="n">
         <v>154738000000</v>
       </c>
-      <c r="N71" t="n">
-        <v>554178758900</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="N72" t="n">
+        <v>572472038320</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>株式会社フェローテック
 （旧会社名　株式会社フェローテックホールディングス）</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>6890</t>
         </is>
       </c>
-      <c r="C72" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="D72" t="n">
-        <v>10300</v>
-      </c>
-      <c r="E72" t="n">
+      <c r="C73" t="n">
+        <v>27</v>
+      </c>
+      <c r="D73" t="n">
+        <v>10640</v>
+      </c>
+      <c r="E73" t="n">
         <v>2030</v>
       </c>
-      <c r="F72" t="n">
-        <v>407.4</v>
-      </c>
-      <c r="G72" t="inlineStr">
+      <c r="F73" t="n">
+        <v>424.1</v>
+      </c>
+      <c r="G73" t="inlineStr">
         <is>
           <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>2025-10-22</t>
         </is>
       </c>
-      <c r="I72" t="n">
+      <c r="I73" t="n">
         <v>52579000000</v>
       </c>
-      <c r="J72" t="n">
+      <c r="J73" t="n">
         <v>90505000000</v>
       </c>
-      <c r="K72" t="n">
+      <c r="K73" t="n">
         <v>11654000000</v>
       </c>
-      <c r="L72" t="n">
+      <c r="L73" t="n">
         <v>160957000000</v>
       </c>
-      <c r="M72" t="n">
+      <c r="M73" t="n">
         <v>154738000000</v>
       </c>
-      <c r="N72" t="n">
-        <v>554178758900</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="N73" t="n">
+        <v>572472038320</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>株式会社フェローテック
 （旧会社名　株式会社フェローテックホールディングス）</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>6890</t>
         </is>
       </c>
-      <c r="C73" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="D73" t="n">
-        <v>10300</v>
-      </c>
-      <c r="E73" t="n">
+      <c r="C74" t="n">
+        <v>27</v>
+      </c>
+      <c r="D74" t="n">
+        <v>10640</v>
+      </c>
+      <c r="E74" t="n">
         <v>2387</v>
       </c>
-      <c r="F73" t="n">
-        <v>331.5</v>
-      </c>
-      <c r="G73" t="inlineStr">
+      <c r="F74" t="n">
+        <v>345.7</v>
+      </c>
+      <c r="G74" t="inlineStr">
         <is>
           <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>2025-03-07</t>
         </is>
       </c>
-      <c r="I73" t="n">
+      <c r="I74" t="n">
         <v>52579000000</v>
       </c>
-      <c r="J73" t="n">
+      <c r="J74" t="n">
         <v>90505000000</v>
       </c>
-      <c r="K73" t="n">
+      <c r="K74" t="n">
         <v>11654000000</v>
       </c>
-      <c r="L73" t="n">
+      <c r="L74" t="n">
         <v>160957000000</v>
       </c>
-      <c r="M73" t="n">
+      <c r="M74" t="n">
         <v>154738000000</v>
       </c>
-      <c r="N73" t="n">
-        <v>554178758900</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>株式会社電通総研</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>4812</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="D74" t="n">
-        <v>2861</v>
-      </c>
-      <c r="E74" t="n">
-        <v>1910.426979628923</v>
-      </c>
-      <c r="F74" t="n">
-        <v>49.8</v>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="I74" t="n">
-        <v>49748000000</v>
-      </c>
-      <c r="J74" t="n">
-        <v>524000000</v>
-      </c>
-      <c r="K74" t="n">
-        <v>3388000000</v>
-      </c>
-      <c r="L74" t="n">
-        <v>65471000000</v>
-      </c>
-      <c r="M74" t="n">
-        <v>53660000000</v>
-      </c>
       <c r="N74" t="n">
-        <v>558410329042</v>
+        <v>572472038320</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ノリタケ株式会社</t>
+          <t>株式会社電通総研</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>4812</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>36.8</v>
+        <v>9.6</v>
       </c>
       <c r="D75" t="n">
-        <v>3695</v>
+        <v>2860</v>
       </c>
       <c r="E75" t="n">
-        <v>3573.410502159827</v>
+        <v>1910.426979628923</v>
       </c>
       <c r="F75" t="n">
-        <v>3.4</v>
+        <v>49.7</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>11733000000</v>
+        <v>49748000000</v>
       </c>
       <c r="J75" t="n">
-        <v>20204000000</v>
+        <v>524000000</v>
       </c>
       <c r="K75" t="n">
-        <v>42879000000</v>
+        <v>3388000000</v>
       </c>
       <c r="L75" t="n">
-        <v>118800000000</v>
+        <v>65471000000</v>
       </c>
       <c r="M75" t="n">
-        <v>74816000000</v>
+        <v>53660000000</v>
       </c>
       <c r="N75" t="n">
-        <v>203277742430</v>
+        <v>558215148920</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>株式会社メガチップス</t>
+          <t>ノリタケ株式会社</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>6875</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>86.40000000000001</v>
+        <v>36.7</v>
       </c>
       <c r="D76" t="n">
-        <v>10870</v>
+        <v>3710</v>
       </c>
       <c r="E76" t="n">
-        <v>4870</v>
+        <v>3573.410502159827</v>
       </c>
       <c r="F76" t="n">
-        <v>123.2</v>
+        <v>3.8</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>25769446000</v>
+        <v>11733000000</v>
       </c>
       <c r="J76" t="n">
-        <v>2249411000</v>
+        <v>20204000000</v>
       </c>
       <c r="K76" t="n">
-        <v>101636005000</v>
+        <v>42879000000</v>
       </c>
       <c r="L76" t="n">
-        <v>67428618000</v>
+        <v>118800000000</v>
       </c>
       <c r="M76" t="n">
-        <v>129654862000</v>
+        <v>74816000000</v>
       </c>
       <c r="N76" t="n">
-        <v>150015793870</v>
+        <v>204102956540</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>カシオ計算機株式会社</t>
+          <t>株式会社メガチップス</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>44.3</v>
+        <v>84.3</v>
       </c>
       <c r="D77" t="n">
-        <v>2183</v>
+        <v>11150</v>
       </c>
       <c r="E77" t="n">
-        <v>1198.150742177053</v>
+        <v>4870</v>
       </c>
       <c r="F77" t="n">
-        <v>82.2</v>
+        <v>129</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>133904000000</v>
+        <v>25769446000</v>
       </c>
       <c r="J77" t="n">
-        <v>11109000000</v>
+        <v>2249411000</v>
       </c>
       <c r="K77" t="n">
-        <v>68953000000</v>
+        <v>101636005000</v>
       </c>
       <c r="L77" t="n">
-        <v>218897000000</v>
+        <v>67428618000</v>
       </c>
       <c r="M77" t="n">
-        <v>213966000000</v>
+        <v>129654862000</v>
       </c>
       <c r="N77" t="n">
-        <v>483346196603</v>
+        <v>153880046150</v>
       </c>
     </row>
     <row r="78">
@@ -4448,25 +4448,25 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>44.3</v>
+        <v>43.9</v>
       </c>
       <c r="D78" t="n">
-        <v>2183</v>
+        <v>2201.5</v>
       </c>
       <c r="E78" t="n">
-        <v>1188.162962482466</v>
+        <v>1198.150742177053</v>
       </c>
       <c r="F78" t="n">
         <v>83.7</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="I78" t="n">
@@ -4485,135 +4485,135 @@
         <v>213966000000</v>
       </c>
       <c r="N78" t="n">
-        <v>483346196603</v>
+        <v>487442350812</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>株式会社あおぞら銀行</t>
+          <t>カシオ計算機株式会社</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>28</v>
+        <v>43.9</v>
       </c>
       <c r="D79" t="n">
-        <v>3403</v>
+        <v>2201.5</v>
       </c>
       <c r="E79" t="n">
-        <v>2190</v>
+        <v>1188.162962482466</v>
       </c>
       <c r="F79" t="n">
-        <v>55.4</v>
+        <v>85.3</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1061743000000</v>
+        <v>133904000000</v>
       </c>
       <c r="J79" t="n">
-        <v>22385000000</v>
+        <v>11109000000</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>68953000000</v>
       </c>
       <c r="L79" t="n">
-        <v>487265000000</v>
+        <v>218897000000</v>
       </c>
       <c r="M79" t="n">
-        <v>1084128000000</v>
+        <v>213966000000</v>
       </c>
       <c r="N79" t="n">
-        <v>3874165448118</v>
+        <v>487442350812</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>カルビー株式会社</t>
+          <t>株式会社あおぞら銀行</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>33.4</v>
+        <v>27</v>
       </c>
       <c r="D80" t="n">
-        <v>3037</v>
+        <v>3526</v>
       </c>
       <c r="E80" t="n">
-        <v>2919.137515755844</v>
+        <v>2190</v>
       </c>
       <c r="F80" t="n">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>49670000000</v>
+        <v>1061743000000</v>
       </c>
       <c r="J80" t="n">
-        <v>70285000000</v>
+        <v>22385000000</v>
       </c>
       <c r="K80" t="n">
-        <v>3263000000</v>
+        <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>183458000000</v>
+        <v>487265000000</v>
       </c>
       <c r="M80" t="n">
-        <v>123218000000</v>
+        <v>1084128000000</v>
       </c>
       <c r="N80" t="n">
-        <v>369262312598</v>
+        <v>4014195524556</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>株式会社ＫＡＤＯＫＡＷＡ</t>
+          <t>カルビー株式会社</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>9468</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>24.2</v>
+        <v>33.1</v>
       </c>
       <c r="D81" t="n">
-        <v>3656</v>
+        <v>3059</v>
       </c>
       <c r="E81" t="n">
-        <v>2995.424821743842</v>
+        <v>2919.137515755844</v>
       </c>
       <c r="F81" t="n">
-        <v>22.1</v>
+        <v>4.8</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -4622,50 +4622,50 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>97579000000</v>
+        <v>49670000000</v>
       </c>
       <c r="J81" t="n">
-        <v>31592000000</v>
+        <v>70285000000</v>
       </c>
       <c r="K81" t="n">
-        <v>808000000</v>
+        <v>3263000000</v>
       </c>
       <c r="L81" t="n">
-        <v>175740000000</v>
+        <v>183458000000</v>
       </c>
       <c r="M81" t="n">
-        <v>129979000000</v>
+        <v>123218000000</v>
       </c>
       <c r="N81" t="n">
-        <v>537306540704</v>
+        <v>371937245386</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>株式会社パソナグループ</t>
+          <t>株式会社ＫＡＤＯＫＡＷＡ</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2168</t>
+          <t>9468</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>138</v>
+        <v>24.1</v>
       </c>
       <c r="D82" t="n">
-        <v>1558</v>
+        <v>3665</v>
       </c>
       <c r="E82" t="n">
-        <v>2122.579027791042</v>
+        <v>2995.424821743842</v>
       </c>
       <c r="F82" t="n">
-        <v>-26.6</v>
+        <v>22.4</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -4674,50 +4674,50 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>56578000000</v>
+        <v>97579000000</v>
       </c>
       <c r="J82" t="n">
-        <v>9255000000</v>
+        <v>31592000000</v>
       </c>
       <c r="K82" t="n">
-        <v>14500000000</v>
+        <v>808000000</v>
       </c>
       <c r="L82" t="n">
-        <v>67162000000</v>
+        <v>175740000000</v>
       </c>
       <c r="M82" t="n">
-        <v>80333000000</v>
+        <v>129979000000</v>
       </c>
       <c r="N82" t="n">
-        <v>58195081266</v>
+        <v>538629231860</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>株式会社インフォマート</t>
+          <t>株式会社パソナグループ</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>2168</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3.7</v>
+        <v>138.2</v>
       </c>
       <c r="D83" t="n">
-        <v>709</v>
+        <v>1556</v>
       </c>
       <c r="E83" t="n">
-        <v>404.9347366248775</v>
+        <v>2122.579027791042</v>
       </c>
       <c r="F83" t="n">
-        <v>75.09999999999999</v>
+        <v>-26.7</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -4726,50 +4726,50 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>6410479000</v>
+        <v>56578000000</v>
       </c>
       <c r="J83" t="n">
-        <v>196639000</v>
+        <v>9255000000</v>
       </c>
       <c r="K83" t="n">
-        <v>437854000</v>
+        <v>14500000000</v>
       </c>
       <c r="L83" t="n">
-        <v>11425263000</v>
+        <v>67162000000</v>
       </c>
       <c r="M83" t="n">
-        <v>7044972000</v>
+        <v>80333000000</v>
       </c>
       <c r="N83" t="n">
-        <v>189009548445</v>
+        <v>58120376412</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>東京製鐵株式会社</t>
+          <t>株式会社インフォマート</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>101.6</v>
+        <v>3.7</v>
       </c>
       <c r="D84" t="n">
-        <v>1712</v>
+        <v>712</v>
       </c>
       <c r="E84" t="n">
-        <v>1605.452212379354</v>
+        <v>404.9347366248775</v>
       </c>
       <c r="F84" t="n">
-        <v>6.6</v>
+        <v>75.8</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -4778,286 +4778,286 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>68644000000</v>
+        <v>6410479000</v>
       </c>
       <c r="J84" t="n">
-        <v>33060000000</v>
+        <v>196639000</v>
       </c>
       <c r="K84" t="n">
-        <v>75000000000</v>
+        <v>437854000</v>
       </c>
       <c r="L84" t="n">
-        <v>158280000000</v>
+        <v>11425263000</v>
       </c>
       <c r="M84" t="n">
-        <v>176704000000</v>
+        <v>7044972000</v>
       </c>
       <c r="N84" t="n">
-        <v>173932593392</v>
+        <v>189809306760</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>三浦工業株式会社</t>
+          <t>東京製鐵株式会社</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>5423</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>11.4</v>
+        <v>101.4</v>
       </c>
       <c r="D85" t="n">
-        <v>3201</v>
+        <v>1716</v>
       </c>
       <c r="E85" t="n">
-        <v>3147.518794622453</v>
+        <v>1605.452212379354</v>
       </c>
       <c r="F85" t="n">
-        <v>1.7</v>
+        <v>6.9</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>20794000000</v>
+        <v>68644000000</v>
       </c>
       <c r="J85" t="n">
-        <v>10600000000</v>
+        <v>33060000000</v>
       </c>
       <c r="K85" t="n">
-        <v>10773000000</v>
+        <v>75000000000</v>
       </c>
       <c r="L85" t="n">
-        <v>138378000000</v>
+        <v>158280000000</v>
       </c>
       <c r="M85" t="n">
-        <v>42167000000</v>
+        <v>176704000000</v>
       </c>
       <c r="N85" t="n">
-        <v>370513701360</v>
+        <v>174338977956</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>株式会社トクヤマ</t>
+          <t>三浦工業株式会社</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>53</v>
+        <v>11.4</v>
       </c>
       <c r="D86" t="n">
-        <v>4238</v>
+        <v>3200</v>
       </c>
       <c r="E86" t="n">
-        <v>2863.970160821546</v>
+        <v>3147.518794622453</v>
       </c>
       <c r="F86" t="n">
-        <v>48</v>
+        <v>1.7</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>82496000000</v>
+        <v>20794000000</v>
       </c>
       <c r="J86" t="n">
-        <v>42983000000</v>
+        <v>10600000000</v>
       </c>
       <c r="K86" t="n">
-        <v>36050000000</v>
+        <v>10773000000</v>
       </c>
       <c r="L86" t="n">
-        <v>232917000000</v>
+        <v>138378000000</v>
       </c>
       <c r="M86" t="n">
-        <v>161529000000</v>
+        <v>42167000000</v>
       </c>
       <c r="N86" t="n">
-        <v>304903600794</v>
+        <v>370397952000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>新家工業株式会社</t>
+          <t>株式会社トクヤマ</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>85.90000000000001</v>
+        <v>53.2</v>
       </c>
       <c r="D87" t="n">
-        <v>2794</v>
+        <v>4223</v>
       </c>
       <c r="E87" t="n">
-        <v>4265.455132343447</v>
+        <v>2863.970160821546</v>
       </c>
       <c r="F87" t="n">
-        <v>-34.5</v>
+        <v>47.5</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>8141000000</v>
+        <v>82496000000</v>
       </c>
       <c r="J87" t="n">
-        <v>5422000000</v>
+        <v>42983000000</v>
       </c>
       <c r="K87" t="n">
-        <v>9306000000</v>
+        <v>36050000000</v>
       </c>
       <c r="L87" t="n">
-        <v>28847000000</v>
+        <v>232917000000</v>
       </c>
       <c r="M87" t="n">
-        <v>22869000000</v>
+        <v>161529000000</v>
       </c>
       <c r="N87" t="n">
-        <v>26637487492</v>
+        <v>303824423349</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>株式会社プラスアルファ・コンサルティング</t>
+          <t>新家工業株式会社</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>4071</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>9.6</v>
+        <v>86.5</v>
       </c>
       <c r="D88" t="n">
-        <v>2113</v>
+        <v>2773</v>
       </c>
       <c r="E88" t="n">
-        <v>2300.974351689521</v>
+        <v>4265.455132343447</v>
       </c>
       <c r="F88" t="n">
-        <v>-8.199999999999999</v>
+        <v>-35</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>8278003000</v>
+        <v>8141000000</v>
       </c>
       <c r="J88" t="n">
-        <v>271170000</v>
+        <v>5422000000</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>9306000000</v>
       </c>
       <c r="L88" t="n">
-        <v>9445733000</v>
+        <v>28847000000</v>
       </c>
       <c r="M88" t="n">
-        <v>8549173000</v>
+        <v>22869000000</v>
       </c>
       <c r="N88" t="n">
-        <v>88652077150</v>
+        <v>26437277314</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>東亜道路工業株式会社</t>
+          <t>株式会社プラスアルファ・コンサルティング</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>4071</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>39.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D89" t="n">
-        <v>1616</v>
+        <v>2107</v>
       </c>
       <c r="E89" t="n">
-        <v>1180.253227905114</v>
+        <v>2300.974351689521</v>
       </c>
       <c r="F89" t="n">
-        <v>36.9</v>
+        <v>-8.4</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>11649000000</v>
+        <v>8278003000</v>
       </c>
       <c r="J89" t="n">
-        <v>13793000000</v>
+        <v>271170000</v>
       </c>
       <c r="K89" t="n">
-        <v>4087000000</v>
+        <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>50605000000</v>
+        <v>9445733000</v>
       </c>
       <c r="M89" t="n">
-        <v>29529000000</v>
+        <v>8549173000</v>
       </c>
       <c r="N89" t="n">
-        <v>74671462208</v>
+        <v>88400343850</v>
       </c>
     </row>
     <row r="90">
@@ -5072,16 +5072,16 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="D90" t="n">
-        <v>1616</v>
+        <v>1620</v>
       </c>
       <c r="E90" t="n">
-        <v>1180.31326635551</v>
+        <v>1180.253227905114</v>
       </c>
       <c r="F90" t="n">
-        <v>36.9</v>
+        <v>37.3</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="I90" t="n">
@@ -5109,7 +5109,7 @@
         <v>29529000000</v>
       </c>
       <c r="N90" t="n">
-        <v>74671462208</v>
+        <v>74856292560</v>
       </c>
     </row>
     <row r="91">
@@ -5124,16 +5124,16 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="D91" t="n">
-        <v>1616</v>
+        <v>1620</v>
       </c>
       <c r="E91" t="n">
-        <v>1180.406015389293</v>
+        <v>1180.31326635551</v>
       </c>
       <c r="F91" t="n">
-        <v>36.9</v>
+        <v>37.3</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="I91" t="n">
@@ -5161,7 +5161,7 @@
         <v>29529000000</v>
       </c>
       <c r="N91" t="n">
-        <v>74671462208</v>
+        <v>74856292560</v>
       </c>
     </row>
     <row r="92">
@@ -5176,16 +5176,16 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="D92" t="n">
-        <v>1616</v>
+        <v>1620</v>
       </c>
       <c r="E92" t="n">
-        <v>1180.420176850555</v>
+        <v>1180.406015389293</v>
       </c>
       <c r="F92" t="n">
-        <v>36.9</v>
+        <v>37.2</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="I92" t="n">
@@ -5213,7 +5213,7 @@
         <v>29529000000</v>
       </c>
       <c r="N92" t="n">
-        <v>74671462208</v>
+        <v>74856292560</v>
       </c>
     </row>
     <row r="93">
@@ -5228,16 +5228,16 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="D93" t="n">
-        <v>1616</v>
+        <v>1620</v>
       </c>
       <c r="E93" t="n">
-        <v>1180.431728045326</v>
+        <v>1180.420176850555</v>
       </c>
       <c r="F93" t="n">
-        <v>36.9</v>
+        <v>37.2</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="I93" t="n">
@@ -5265,7 +5265,7 @@
         <v>29529000000</v>
       </c>
       <c r="N93" t="n">
-        <v>74671462208</v>
+        <v>74856292560</v>
       </c>
     </row>
     <row r="94">
@@ -5280,16 +5280,16 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="D94" t="n">
-        <v>1616</v>
+        <v>1620</v>
       </c>
       <c r="E94" t="n">
-        <v>1180.442269658324</v>
+        <v>1180.431728045326</v>
       </c>
       <c r="F94" t="n">
-        <v>36.9</v>
+        <v>37.2</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="I94" t="n">
@@ -5317,7 +5317,7 @@
         <v>29529000000</v>
       </c>
       <c r="N94" t="n">
-        <v>74671462208</v>
+        <v>74856292560</v>
       </c>
     </row>
     <row r="95">
@@ -5332,16 +5332,16 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="D95" t="n">
-        <v>1616</v>
+        <v>1620</v>
       </c>
       <c r="E95" t="n">
-        <v>1180.450912709519</v>
+        <v>1180.442269658324</v>
       </c>
       <c r="F95" t="n">
-        <v>36.9</v>
+        <v>37.2</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="I95" t="n">
@@ -5369,7 +5369,7 @@
         <v>29529000000</v>
       </c>
       <c r="N95" t="n">
-        <v>74671462208</v>
+        <v>74856292560</v>
       </c>
     </row>
     <row r="96">
@@ -5384,16 +5384,16 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="D96" t="n">
-        <v>1616</v>
+        <v>1620</v>
       </c>
       <c r="E96" t="n">
-        <v>1180.45745232471</v>
+        <v>1180.450912709519</v>
       </c>
       <c r="F96" t="n">
-        <v>36.9</v>
+        <v>37.2</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="I96" t="n">
@@ -5421,7 +5421,7 @@
         <v>29529000000</v>
       </c>
       <c r="N96" t="n">
-        <v>74671462208</v>
+        <v>74856292560</v>
       </c>
     </row>
     <row r="97">
@@ -5436,16 +5436,16 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="D97" t="n">
-        <v>1616</v>
+        <v>1620</v>
       </c>
       <c r="E97" t="n">
-        <v>1180.463123164206</v>
+        <v>1180.45745232471</v>
       </c>
       <c r="F97" t="n">
-        <v>36.9</v>
+        <v>37.2</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="I97" t="n">
@@ -5473,7 +5473,7 @@
         <v>29529000000</v>
       </c>
       <c r="N97" t="n">
-        <v>74671462208</v>
+        <v>74856292560</v>
       </c>
     </row>
     <row r="98">
@@ -5488,16 +5488,16 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="D98" t="n">
-        <v>1616</v>
+        <v>1620</v>
       </c>
       <c r="E98" t="n">
-        <v>1170.279952698077</v>
+        <v>1180.463123164206</v>
       </c>
       <c r="F98" t="n">
-        <v>38.1</v>
+        <v>37.2</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="I98" t="n">
@@ -5525,7 +5525,7 @@
         <v>29529000000</v>
       </c>
       <c r="N98" t="n">
-        <v>74671462208</v>
+        <v>74856292560</v>
       </c>
     </row>
     <row r="99">
@@ -5540,16 +5540,16 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="D99" t="n">
-        <v>1616</v>
+        <v>1620</v>
       </c>
       <c r="E99" t="n">
-        <v>1169.924818603025</v>
+        <v>1170.279952698077</v>
       </c>
       <c r="F99" t="n">
-        <v>38.1</v>
+        <v>38.4</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="I99" t="n">
@@ -5577,7 +5577,7 @@
         <v>29529000000</v>
       </c>
       <c r="N99" t="n">
-        <v>74671462208</v>
+        <v>74856292560</v>
       </c>
     </row>
     <row r="100">
@@ -5592,16 +5592,16 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="D100" t="n">
-        <v>1616</v>
+        <v>1620</v>
       </c>
       <c r="E100" t="n">
-        <v>1168.709522546084</v>
+        <v>1169.924818603025</v>
       </c>
       <c r="F100" t="n">
-        <v>38.3</v>
+        <v>38.5</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="I100" t="n">
@@ -5629,104 +5629,112 @@
         <v>29529000000</v>
       </c>
       <c r="N100" t="n">
-        <v>74671462208</v>
+        <v>74856292560</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>センコーグループホールディングス株式会社</t>
+          <t>東亜道路工業株式会社</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>9069</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>52.6</v>
+        <v>39.4</v>
       </c>
       <c r="D101" t="n">
-        <v>2355</v>
+        <v>1620</v>
       </c>
       <c r="E101" t="n">
-        <v>1556.090471804319</v>
+        <v>1168.709522546084</v>
       </c>
       <c r="F101" t="n">
-        <v>51.3</v>
+        <v>38.6</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>42193000000</v>
+        <v>11649000000</v>
       </c>
       <c r="J101" t="n">
-        <v>138228000000</v>
+        <v>13793000000</v>
       </c>
       <c r="K101" t="n">
-        <v>27045000000</v>
+        <v>4087000000</v>
       </c>
       <c r="L101" t="n">
-        <v>160854000000</v>
+        <v>50605000000</v>
       </c>
       <c r="M101" t="n">
-        <v>207466000000</v>
+        <v>29529000000</v>
       </c>
       <c r="N101" t="n">
-        <v>394270814775</v>
+        <v>74856292560</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>株式会社豊田自動織機</t>
+          <t>センコーグループホールディングス株式会社</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>6201</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr"/>
+          <t>9069</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="D102" t="n">
+        <v>2380.5</v>
+      </c>
       <c r="E102" t="n">
-        <v>16430443.10823975</v>
-      </c>
-      <c r="F102" t="inlineStr"/>
+        <v>1556.090471804319</v>
+      </c>
+      <c r="F102" t="n">
+        <v>53</v>
+      </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>281605000000</v>
+        <v>42193000000</v>
       </c>
       <c r="J102" t="n">
-        <v>87540000000</v>
+        <v>138228000000</v>
       </c>
       <c r="K102" t="n">
-        <v>730709000000</v>
+        <v>27045000000</v>
       </c>
       <c r="L102" t="n">
-        <v>3246174000000</v>
+        <v>160854000000</v>
       </c>
       <c r="M102" t="n">
-        <v>1099854000000</v>
-      </c>
-      <c r="N102" t="inlineStr"/>
+        <v>207466000000</v>
+      </c>
+      <c r="N102" t="n">
+        <v>398539989202</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5742,7 +5750,7 @@
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="n">
-        <v>16430.4430802409</v>
+        <v>16430443.10823975</v>
       </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
@@ -5775,157 +5783,149 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>サッポロホールディングス株式会社</t>
+          <t>株式会社豊田自動織機</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2501</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>1</v>
-      </c>
-      <c r="D104" t="n">
-        <v>1803</v>
-      </c>
+          <t>6201</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="n">
-        <v>2697.360927565142</v>
-      </c>
-      <c r="F104" t="n">
-        <v>-33.2</v>
-      </c>
+        <v>16430.4430802409</v>
+      </c>
+      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2925000000</v>
+        <v>281605000000</v>
       </c>
       <c r="J104" t="n">
-        <v>23000000</v>
+        <v>87540000000</v>
       </c>
       <c r="K104" t="n">
-        <v>4391000000</v>
+        <v>730709000000</v>
       </c>
       <c r="L104" t="n">
-        <v>142395000000</v>
+        <v>3246174000000</v>
       </c>
       <c r="M104" t="n">
-        <v>7339000000</v>
-      </c>
-      <c r="N104" t="n">
-        <v>703121300970</v>
-      </c>
+        <v>1099854000000</v>
+      </c>
+      <c r="N104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>大東建託株式会社</t>
+          <t>サッポロホールディングス株式会社</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>30.3</v>
+        <v>1</v>
       </c>
       <c r="D105" t="n">
-        <v>3295</v>
+        <v>1820</v>
       </c>
       <c r="E105" t="n">
-        <v>13739.64575539568</v>
+        <v>2697.360927565142</v>
       </c>
       <c r="F105" t="n">
-        <v>-76</v>
+        <v>-32.5</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>258825000000</v>
+        <v>2925000000</v>
       </c>
       <c r="J105" t="n">
-        <v>63562000000</v>
+        <v>23000000</v>
       </c>
       <c r="K105" t="n">
-        <v>3006000000</v>
+        <v>4391000000</v>
       </c>
       <c r="L105" t="n">
-        <v>365787000000</v>
+        <v>142395000000</v>
       </c>
       <c r="M105" t="n">
-        <v>325393000000</v>
+        <v>7339000000</v>
       </c>
       <c r="N105" t="n">
-        <v>1073287862600</v>
+        <v>709750841800</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>マクニカホールディングス株式会社</t>
+          <t>大東建託株式会社</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>3132</t>
+          <t>1878</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>4.7</v>
+        <v>30.3</v>
       </c>
       <c r="D106" t="n">
-        <v>4214</v>
+        <v>3300</v>
       </c>
       <c r="E106" t="n">
-        <v>1572.181660925393</v>
+        <v>13739.64575539568</v>
       </c>
       <c r="F106" t="n">
-        <v>168</v>
+        <v>-76</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>25099000000</v>
+        <v>258825000000</v>
       </c>
       <c r="J106" t="n">
-        <v>2444000000</v>
+        <v>63562000000</v>
       </c>
       <c r="K106" t="n">
-        <v>7958000000</v>
+        <v>3006000000</v>
       </c>
       <c r="L106" t="n">
-        <v>179764000000</v>
+        <v>365787000000</v>
       </c>
       <c r="M106" t="n">
-        <v>35501000000</v>
+        <v>325393000000</v>
       </c>
       <c r="N106" t="n">
-        <v>752464722198</v>
+        <v>1074916524000</v>
       </c>
     </row>
     <row r="107">
@@ -5940,25 +5940,25 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="D107" t="n">
-        <v>4214</v>
+        <v>4287</v>
       </c>
       <c r="E107" t="n">
-        <v>1141.512891683109</v>
+        <v>1572.181660925393</v>
       </c>
       <c r="F107" t="n">
-        <v>269.2</v>
+        <v>172.7</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="I107" t="n">
@@ -5977,83 +5977,83 @@
         <v>35501000000</v>
       </c>
       <c r="N107" t="n">
-        <v>752464722198</v>
+        <v>765499825359</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ＤＩＣ株式会社</t>
+          <t>マクニカホールディングス株式会社</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>3132</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>51</v>
+        <v>4.6</v>
       </c>
       <c r="D108" t="n">
-        <v>4813</v>
+        <v>4287</v>
       </c>
       <c r="E108" t="n">
-        <v>2566.284807227078</v>
+        <v>1141.512891683109</v>
       </c>
       <c r="F108" t="n">
-        <v>87.5</v>
+        <v>275.6</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>37572000000</v>
+        <v>25099000000</v>
       </c>
       <c r="J108" t="n">
-        <v>133918000000</v>
+        <v>2444000000</v>
       </c>
       <c r="K108" t="n">
-        <v>60085000000</v>
+        <v>7958000000</v>
       </c>
       <c r="L108" t="n">
-        <v>381008000000</v>
+        <v>179764000000</v>
       </c>
       <c r="M108" t="n">
-        <v>231575000000</v>
+        <v>35501000000</v>
       </c>
       <c r="N108" t="n">
-        <v>453803812300</v>
+        <v>765499825359</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>セーレン株式会社</t>
+          <t>ＤＩＣ株式会社</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>3569</t>
+          <t>4631</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>36.5</v>
+        <v>50.7</v>
       </c>
       <c r="D109" t="n">
-        <v>3290</v>
+        <v>4846</v>
       </c>
       <c r="E109" t="n">
-        <v>1359.655069733296</v>
+        <v>2566.284807227078</v>
       </c>
       <c r="F109" t="n">
-        <v>142</v>
+        <v>88.8</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -6062,50 +6062,50 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>35451000000</v>
+        <v>37572000000</v>
       </c>
       <c r="J109" t="n">
-        <v>25813000000</v>
+        <v>133918000000</v>
       </c>
       <c r="K109" t="n">
-        <v>8891000000</v>
+        <v>60085000000</v>
       </c>
       <c r="L109" t="n">
-        <v>91845000000</v>
+        <v>381008000000</v>
       </c>
       <c r="M109" t="n">
-        <v>70155000000</v>
+        <v>231575000000</v>
       </c>
       <c r="N109" t="n">
-        <v>192002560890</v>
+        <v>456915286600</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ニデック株式会社</t>
+          <t>セーレン株式会社</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>6594</t>
+          <t>3569</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>6.4</v>
+        <v>36</v>
       </c>
       <c r="D110" t="n">
-        <v>2822</v>
+        <v>3335</v>
       </c>
       <c r="E110" t="n">
-        <v>2220.184278344451</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="F110" t="n">
-        <v>27.1</v>
+        <v>145.3</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -6114,154 +6114,154 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>163815000000</v>
+        <v>35451000000</v>
       </c>
       <c r="J110" t="n">
-        <v>17829000000</v>
+        <v>25813000000</v>
       </c>
       <c r="K110" t="n">
-        <v>25472000000</v>
+        <v>8891000000</v>
       </c>
       <c r="L110" t="n">
-        <v>298063000000</v>
+        <v>91845000000</v>
       </c>
       <c r="M110" t="n">
-        <v>207116000000</v>
+        <v>70155000000</v>
       </c>
       <c r="N110" t="n">
-        <v>3234886354370</v>
+        <v>194628735735</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>株式会社ニコン</t>
+          <t>ニデック株式会社</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>7731</t>
+          <t>6594</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>19.7</v>
+        <v>6.4</v>
       </c>
       <c r="D111" t="n">
-        <v>1858.5</v>
+        <v>2840</v>
       </c>
       <c r="E111" t="n">
-        <v>1512.21980974841</v>
+        <v>2220.184278344451</v>
       </c>
       <c r="F111" t="n">
-        <v>22.9</v>
+        <v>27.9</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>45228000000</v>
+        <v>163815000000</v>
       </c>
       <c r="J111" t="n">
-        <v>8297000000</v>
+        <v>17829000000</v>
       </c>
       <c r="K111" t="n">
-        <v>67291000000</v>
+        <v>25472000000</v>
       </c>
       <c r="L111" t="n">
-        <v>362281000000</v>
+        <v>298063000000</v>
       </c>
       <c r="M111" t="n">
-        <v>120816000000</v>
+        <v>207116000000</v>
       </c>
       <c r="N111" t="n">
-        <v>612221054036</v>
+        <v>3255519931400</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>株式会社アインホールディングス</t>
+          <t>株式会社ニコン</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>9627</t>
+          <t>7731</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>48.9</v>
+        <v>19.6</v>
       </c>
       <c r="D112" t="n">
-        <v>5490</v>
+        <v>1873.5</v>
       </c>
       <c r="E112" t="n">
-        <v>2836.942753814942</v>
+        <v>1512.21980974841</v>
       </c>
       <c r="F112" t="n">
-        <v>93.5</v>
+        <v>23.9</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>59470000000</v>
+        <v>45228000000</v>
       </c>
       <c r="J112" t="n">
-        <v>31648000000</v>
+        <v>8297000000</v>
       </c>
       <c r="K112" t="n">
-        <v>3233000000</v>
+        <v>67291000000</v>
       </c>
       <c r="L112" t="n">
-        <v>119010000000</v>
+        <v>362281000000</v>
       </c>
       <c r="M112" t="n">
-        <v>94351000000</v>
+        <v>120816000000</v>
       </c>
       <c r="N112" t="n">
-        <v>193140511290</v>
+        <v>617162305480</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>市光工業株式会社</t>
+          <t>株式会社アインホールディングス</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>7244</t>
+          <t>9627</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>35.1</v>
+        <v>49.1</v>
       </c>
       <c r="D113" t="n">
-        <v>566</v>
+        <v>5463</v>
       </c>
       <c r="E113" t="n">
-        <v>549.4799823005444</v>
+        <v>2836.942753814942</v>
       </c>
       <c r="F113" t="n">
-        <v>3</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -6270,390 +6270,390 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>5720000000</v>
+        <v>59470000000</v>
       </c>
       <c r="J113" t="n">
-        <v>9921000000</v>
+        <v>31648000000</v>
       </c>
       <c r="K113" t="n">
-        <v>3474000000</v>
+        <v>3233000000</v>
       </c>
       <c r="L113" t="n">
-        <v>49523000000</v>
+        <v>119010000000</v>
       </c>
       <c r="M113" t="n">
-        <v>19115000000</v>
+        <v>94351000000</v>
       </c>
       <c r="N113" t="n">
-        <v>54508296060</v>
+        <v>192190639923</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>山洋電気株式会社</t>
+          <t>市光工業株式会社</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>11.4</v>
+        <v>34.9</v>
       </c>
       <c r="D114" t="n">
-        <v>5420</v>
+        <v>569</v>
       </c>
       <c r="E114" t="n">
-        <v>7052.737306843267</v>
+        <v>549.4799823005444</v>
       </c>
       <c r="F114" t="n">
-        <v>-23.2</v>
+        <v>3.6</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>8317000000</v>
+        <v>5720000000</v>
       </c>
       <c r="J114" t="n">
-        <v>6048000000</v>
+        <v>9921000000</v>
       </c>
       <c r="K114" t="n">
-        <v>7673000000</v>
+        <v>3474000000</v>
       </c>
       <c r="L114" t="n">
-        <v>49734000000</v>
+        <v>49523000000</v>
       </c>
       <c r="M114" t="n">
-        <v>22038000000</v>
+        <v>19115000000</v>
       </c>
       <c r="N114" t="n">
-        <v>192491522220</v>
+        <v>54797209290</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>日本特殊塗料株式会社</t>
+          <t>山洋電気株式会社</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>4619</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>70.59999999999999</v>
+        <v>11.4</v>
       </c>
       <c r="D115" t="n">
-        <v>2694</v>
+        <v>5430</v>
       </c>
       <c r="E115" t="n">
-        <v>1190</v>
+        <v>7052.737306843267</v>
       </c>
       <c r="F115" t="n">
-        <v>126.4</v>
+        <v>-23</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>8931000000</v>
+        <v>8317000000</v>
       </c>
       <c r="J115" t="n">
-        <v>9514000000</v>
+        <v>6048000000</v>
       </c>
       <c r="K115" t="n">
-        <v>22055000000</v>
+        <v>7673000000</v>
       </c>
       <c r="L115" t="n">
-        <v>49725000000</v>
+        <v>49734000000</v>
       </c>
       <c r="M115" t="n">
-        <v>40500000000</v>
+        <v>22038000000</v>
       </c>
       <c r="N115" t="n">
-        <v>57360235818</v>
+        <v>192846672630</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>株式会社ＡＣＳＬ</t>
+          <t>日本特殊塗料株式会社</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>4619</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>7.9</v>
+        <v>70.5</v>
       </c>
       <c r="D116" t="n">
-        <v>1359</v>
+        <v>2698</v>
       </c>
       <c r="E116" t="n">
-        <v>913.2768512341561</v>
+        <v>1190</v>
       </c>
       <c r="F116" t="n">
-        <v>48.8</v>
+        <v>126.7</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1891731000</v>
+        <v>8931000000</v>
       </c>
       <c r="J116" t="n">
-        <v>3724000</v>
+        <v>9514000000</v>
       </c>
       <c r="K116" t="n">
-        <v>197577000</v>
+        <v>22055000000</v>
       </c>
       <c r="L116" t="n">
-        <v>3572642000</v>
+        <v>49725000000</v>
       </c>
       <c r="M116" t="n">
-        <v>2093032000</v>
+        <v>40500000000</v>
       </c>
       <c r="N116" t="n">
-        <v>26598676878</v>
+        <v>57445403206</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>東京瓦斯株式会社</t>
+          <t>株式会社ＡＣＳＬ</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>9531</t>
+          <t>6232</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>24.5</v>
+        <v>8</v>
       </c>
       <c r="D117" t="n">
-        <v>6167</v>
+        <v>1342</v>
       </c>
       <c r="E117" t="n">
-        <v>3322.047887165483</v>
+        <v>913.2768512341561</v>
       </c>
       <c r="F117" t="n">
-        <v>85.59999999999999</v>
+        <v>46.9</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>179699000000</v>
+        <v>1891731000</v>
       </c>
       <c r="J117" t="n">
-        <v>313045000000</v>
+        <v>3724000</v>
       </c>
       <c r="K117" t="n">
-        <v>103000000</v>
+        <v>197577000</v>
       </c>
       <c r="L117" t="n">
-        <v>1281150000000</v>
+        <v>3572642000</v>
       </c>
       <c r="M117" t="n">
-        <v>492847000000</v>
+        <v>2093032000</v>
       </c>
       <c r="N117" t="n">
-        <v>2014548352453</v>
+        <v>26265948764</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>株式会社イワキ</t>
+          <t>東京瓦斯株式会社</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>6237</t>
+          <t>9531</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>13.7</v>
+        <v>24.2</v>
       </c>
       <c r="D118" t="n">
-        <v>4080</v>
+        <v>6226</v>
       </c>
       <c r="E118" t="n">
-        <v>1361.432492253209</v>
+        <v>3322.047887165483</v>
       </c>
       <c r="F118" t="n">
-        <v>199.7</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>8573897000</v>
+        <v>179699000000</v>
       </c>
       <c r="J118" t="n">
-        <v>3742606000</v>
+        <v>313045000000</v>
       </c>
       <c r="K118" t="n">
-        <v>80933000</v>
+        <v>103000000</v>
       </c>
       <c r="L118" t="n">
-        <v>25251541000</v>
+        <v>1281150000000</v>
       </c>
       <c r="M118" t="n">
-        <v>12397436000</v>
+        <v>492847000000</v>
       </c>
       <c r="N118" t="n">
-        <v>90508047600</v>
+        <v>2033821638134</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>株式会社パイオラックス</t>
+          <t>株式会社イワキ</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>104.9</v>
+        <v>13.6</v>
       </c>
       <c r="D119" t="n">
-        <v>1696</v>
+        <v>4110</v>
       </c>
       <c r="E119" t="n">
-        <v>2298.672482457804</v>
+        <v>1361.432492253209</v>
       </c>
       <c r="F119" t="n">
-        <v>-26.2</v>
+        <v>201.9</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>29925000000</v>
+        <v>8573897000</v>
       </c>
       <c r="J119" t="n">
-        <v>12031000000</v>
+        <v>3742606000</v>
       </c>
       <c r="K119" t="n">
-        <v>796000000</v>
+        <v>80933000</v>
       </c>
       <c r="L119" t="n">
-        <v>98332000000</v>
+        <v>25251541000</v>
       </c>
       <c r="M119" t="n">
-        <v>42752000000</v>
+        <v>12397436000</v>
       </c>
       <c r="N119" t="n">
-        <v>40772835552</v>
+        <v>91173547950</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ブロードメディア株式会社</t>
+          <t>株式会社パイオラックス</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>5988</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>44.5</v>
+        <v>104</v>
       </c>
       <c r="D120" t="n">
-        <v>1899</v>
+        <v>1710</v>
       </c>
       <c r="E120" t="n">
-        <v>1529.631984751819</v>
+        <v>2298.672482457804</v>
       </c>
       <c r="F120" t="n">
-        <v>24.1</v>
+        <v>-25.6</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>5301579000</v>
+        <v>29925000000</v>
       </c>
       <c r="J120" t="n">
-        <v>553048000</v>
+        <v>12031000000</v>
       </c>
       <c r="K120" t="n">
-        <v>169455000</v>
+        <v>796000000</v>
       </c>
       <c r="L120" t="n">
-        <v>4610613000</v>
+        <v>98332000000</v>
       </c>
       <c r="M120" t="n">
-        <v>6024082000</v>
+        <v>42752000000</v>
       </c>
       <c r="N120" t="n">
-        <v>13534493931</v>
+        <v>41109403770</v>
       </c>
     </row>
     <row r="121">
@@ -6668,16 +6668,16 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>44.5</v>
+        <v>44.8</v>
       </c>
       <c r="D121" t="n">
-        <v>1899</v>
+        <v>1887</v>
       </c>
       <c r="E121" t="n">
-        <v>1449.995380693296</v>
+        <v>1529.631984751819</v>
       </c>
       <c r="F121" t="n">
-        <v>31</v>
+        <v>23.4</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="I121" t="n">
@@ -6705,83 +6705,83 @@
         <v>6024082000</v>
       </c>
       <c r="N121" t="n">
-        <v>13534493931</v>
+        <v>13448967903</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>芝浦機械株式会社</t>
+          <t>ブロードメディア株式会社</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>6104</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>83</v>
+        <v>44.8</v>
       </c>
       <c r="D122" t="n">
-        <v>4635</v>
+        <v>1887</v>
       </c>
       <c r="E122" t="n">
-        <v>3449.780346820809</v>
+        <v>1449.995380693296</v>
       </c>
       <c r="F122" t="n">
-        <v>34.4</v>
+        <v>30.1</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>51710000000</v>
+        <v>5301579000</v>
       </c>
       <c r="J122" t="n">
-        <v>21218000000</v>
+        <v>553048000</v>
       </c>
       <c r="K122" t="n">
-        <v>18000000000</v>
+        <v>169455000</v>
       </c>
       <c r="L122" t="n">
-        <v>83515000000</v>
+        <v>4610613000</v>
       </c>
       <c r="M122" t="n">
-        <v>90928000000</v>
+        <v>6024082000</v>
       </c>
       <c r="N122" t="n">
-        <v>109603900620</v>
+        <v>13448967903</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>エン株式会社 (旧会社名　エン・ジャパン株式会社)</t>
+          <t>芝浦機械株式会社</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>6104</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>55.7</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="D123" t="n">
-        <v>1713</v>
+        <v>4685</v>
       </c>
       <c r="E123" t="n">
-        <v>1746.940387696806</v>
+        <v>3449.780346820809</v>
       </c>
       <c r="F123" t="n">
-        <v>-1.9</v>
+        <v>35.8</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -6790,154 +6790,154 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>33389000000</v>
+        <v>51710000000</v>
       </c>
       <c r="J123" t="n">
-        <v>681000000</v>
+        <v>21218000000</v>
       </c>
       <c r="K123" t="n">
-        <v>2000000000</v>
+        <v>18000000000</v>
       </c>
       <c r="L123" t="n">
-        <v>41160000000</v>
+        <v>83515000000</v>
       </c>
       <c r="M123" t="n">
-        <v>36070000000</v>
+        <v>90928000000</v>
       </c>
       <c r="N123" t="n">
-        <v>64719697509</v>
+        <v>110786251220</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>株式会社シンクロ・フード</t>
+          <t>エン株式会社 (旧会社名　エン・ジャパン株式会社)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>4849</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>34.1</v>
+        <v>55.3</v>
       </c>
       <c r="D124" t="n">
-        <v>325</v>
+        <v>1727</v>
       </c>
       <c r="E124" t="n">
-        <v>421.6950726175476</v>
+        <v>1746.940387696806</v>
       </c>
       <c r="F124" t="n">
-        <v>-22.9</v>
+        <v>-1.1</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3037851000</v>
+        <v>33389000000</v>
       </c>
       <c r="J124" t="n">
-        <v>56852000</v>
+        <v>681000000</v>
       </c>
       <c r="K124" t="n">
-        <v>14952000</v>
+        <v>2000000000</v>
       </c>
       <c r="L124" t="n">
-        <v>2871237000</v>
+        <v>41160000000</v>
       </c>
       <c r="M124" t="n">
-        <v>3109655000</v>
+        <v>36070000000</v>
       </c>
       <c r="N124" t="n">
-        <v>9113841100</v>
+        <v>65248638411</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>日本ゼオン株式会社</t>
+          <t>株式会社シンクロ・フード</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>34.8</v>
+        <v>34.2</v>
       </c>
       <c r="D125" t="n">
-        <v>2420.5</v>
+        <v>324</v>
       </c>
       <c r="E125" t="n">
-        <v>1721.078563209627</v>
+        <v>421.6950726175476</v>
       </c>
       <c r="F125" t="n">
-        <v>40.6</v>
+        <v>-23.2</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>44521000000</v>
+        <v>3037851000</v>
       </c>
       <c r="J125" t="n">
-        <v>45382000000</v>
+        <v>56852000</v>
       </c>
       <c r="K125" t="n">
-        <v>71191000000</v>
+        <v>14952000</v>
       </c>
       <c r="L125" t="n">
-        <v>321836000000</v>
+        <v>2871237000</v>
       </c>
       <c r="M125" t="n">
-        <v>161094000000</v>
+        <v>3109655000</v>
       </c>
       <c r="N125" t="n">
-        <v>463151799694</v>
+        <v>9085798512</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>株式会社インターネットイニシアティブ</t>
+          <t>日本ゼオン株式会社</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>3774</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>5.4</v>
+        <v>34.5</v>
       </c>
       <c r="D126" t="n">
-        <v>3443</v>
+        <v>2440</v>
       </c>
       <c r="E126" t="n">
-        <v>2655.311711736394</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="F126" t="n">
-        <v>29.7</v>
+        <v>41.8</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -6946,390 +6946,390 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>16367000000</v>
+        <v>44521000000</v>
       </c>
       <c r="J126" t="n">
-        <v>1522000000</v>
+        <v>45382000000</v>
       </c>
       <c r="K126" t="n">
-        <v>15226000000</v>
+        <v>71191000000</v>
       </c>
       <c r="L126" t="n">
-        <v>87924000000</v>
+        <v>321836000000</v>
       </c>
       <c r="M126" t="n">
-        <v>33115000000</v>
+        <v>161094000000</v>
       </c>
       <c r="N126" t="n">
-        <v>610547207215</v>
+        <v>466883037080</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>リンナイ株式会社</t>
+          <t>株式会社インターネットイニシアティブ</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>46.1</v>
+        <v>5.4</v>
       </c>
       <c r="D127" t="n">
-        <v>3438</v>
+        <v>3465</v>
       </c>
       <c r="E127" t="n">
-        <v>2844.704547285864</v>
+        <v>2655.311711736394</v>
       </c>
       <c r="F127" t="n">
-        <v>20.9</v>
+        <v>30.5</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>147972000000</v>
+        <v>16367000000</v>
       </c>
       <c r="J127" t="n">
-        <v>64736000000</v>
+        <v>1522000000</v>
       </c>
       <c r="K127" t="n">
-        <v>5967000000</v>
+        <v>15226000000</v>
       </c>
       <c r="L127" t="n">
-        <v>378856000000</v>
+        <v>87924000000</v>
       </c>
       <c r="M127" t="n">
-        <v>218675000000</v>
+        <v>33115000000</v>
       </c>
       <c r="N127" t="n">
-        <v>474683326056</v>
+        <v>614448467325</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>京阪神ビルディング株式会社</t>
+          <t>リンナイ株式会社</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>8818</t>
+          <t>5947</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>84</v>
+        <v>45.9</v>
       </c>
       <c r="D128" t="n">
-        <v>1081</v>
+        <v>3450</v>
       </c>
       <c r="E128" t="n">
-        <v>1341.977644710579</v>
+        <v>2844.704547285864</v>
       </c>
       <c r="F128" t="n">
-        <v>-19.4</v>
+        <v>21.3</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>9876000000</v>
+        <v>147972000000</v>
       </c>
       <c r="J128" t="n">
-        <v>54379000000</v>
+        <v>64736000000</v>
       </c>
       <c r="K128" t="n">
-        <v>22399000000</v>
+        <v>5967000000</v>
       </c>
       <c r="L128" t="n">
-        <v>70510000000</v>
+        <v>378856000000</v>
       </c>
       <c r="M128" t="n">
-        <v>86654000000</v>
+        <v>218675000000</v>
       </c>
       <c r="N128" t="n">
-        <v>103132439622</v>
+        <v>476340161400</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>株式会社ワコールホールディングス</t>
+          <t>京阪神ビルディング株式会社</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>8818</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>9.300000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D129" t="n">
-        <v>3960</v>
+        <v>1086</v>
       </c>
       <c r="E129" t="n">
-        <v>2420.370957920882</v>
+        <v>1341.977644710579</v>
       </c>
       <c r="F129" t="n">
-        <v>63.6</v>
+        <v>-19.1</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2951000000</v>
+        <v>9876000000</v>
       </c>
       <c r="J129" t="n">
-        <v>14983000000</v>
+        <v>54379000000</v>
       </c>
       <c r="K129" t="n">
-        <v>233000000</v>
+        <v>22399000000</v>
       </c>
       <c r="L129" t="n">
-        <v>138332000000</v>
+        <v>70510000000</v>
       </c>
       <c r="M129" t="n">
-        <v>18167000000</v>
+        <v>86654000000</v>
       </c>
       <c r="N129" t="n">
-        <v>195770832840</v>
+        <v>103609462932</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>株式会社カカクコム</t>
+          <t>株式会社ワコールホールディングス</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>6.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D130" t="n">
-        <v>3805</v>
+        <v>3968</v>
       </c>
       <c r="E130" t="n">
-        <v>2318.314890576102</v>
+        <v>2420.370957920882</v>
       </c>
       <c r="F130" t="n">
-        <v>64.09999999999999</v>
+        <v>63.9</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>46452000000</v>
+        <v>2951000000</v>
       </c>
       <c r="J130" t="n">
-        <v>68000000</v>
+        <v>14983000000</v>
       </c>
       <c r="K130" t="n">
-        <v>4669000000</v>
+        <v>233000000</v>
       </c>
       <c r="L130" t="n">
-        <v>45479000000</v>
+        <v>138332000000</v>
       </c>
       <c r="M130" t="n">
-        <v>51189000000</v>
+        <v>18167000000</v>
       </c>
       <c r="N130" t="n">
-        <v>752766995935</v>
+        <v>196166329472</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>あいホールディングス株式会社</t>
+          <t>株式会社カカクコム</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>3076</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>23.5</v>
+        <v>6.8</v>
       </c>
       <c r="D131" t="n">
-        <v>2966</v>
+        <v>3812</v>
       </c>
       <c r="E131" t="n">
-        <v>2007.754513143541</v>
+        <v>2318.314890576102</v>
       </c>
       <c r="F131" t="n">
-        <v>47.7</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>32012000000</v>
+        <v>46452000000</v>
       </c>
       <c r="J131" t="n">
-        <v>1646000000</v>
+        <v>68000000</v>
       </c>
       <c r="K131" t="n">
-        <v>3550000000</v>
+        <v>4669000000</v>
       </c>
       <c r="L131" t="n">
-        <v>53765000000</v>
+        <v>45479000000</v>
       </c>
       <c r="M131" t="n">
-        <v>37208000000</v>
+        <v>51189000000</v>
       </c>
       <c r="N131" t="n">
-        <v>158007513346</v>
+        <v>754151849804</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>多木化学株式会社</t>
+          <t>あいホールディングス株式会社</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>4025</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>30.5</v>
+        <v>23.1</v>
       </c>
       <c r="D132" t="n">
-        <v>5750</v>
+        <v>3020</v>
       </c>
       <c r="E132" t="n">
-        <v>4695.956053243186</v>
+        <v>2007.754513143541</v>
       </c>
       <c r="F132" t="n">
-        <v>22.4</v>
+        <v>50.4</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>6433000000</v>
+        <v>32012000000</v>
       </c>
       <c r="J132" t="n">
-        <v>7985000000</v>
+        <v>1646000000</v>
       </c>
       <c r="K132" t="n">
-        <v>199000000</v>
+        <v>3550000000</v>
       </c>
       <c r="L132" t="n">
-        <v>29378000000</v>
+        <v>53765000000</v>
       </c>
       <c r="M132" t="n">
-        <v>14617000000</v>
+        <v>37208000000</v>
       </c>
       <c r="N132" t="n">
-        <v>47997371750</v>
+        <v>160884251620</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ガンホー・オンライン・エンターテイメント株式会社</t>
+          <t>多木化学株式会社</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>3765</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>82.2</v>
+        <v>30.1</v>
       </c>
       <c r="D133" t="n">
-        <v>2519</v>
+        <v>5810</v>
       </c>
       <c r="E133" t="n">
-        <v>2901.475903614458</v>
+        <v>4695.956053243186</v>
       </c>
       <c r="F133" t="n">
-        <v>-13.2</v>
+        <v>23.7</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>102086000000</v>
+        <v>6433000000</v>
       </c>
       <c r="J133" t="n">
-        <v>1326000000</v>
+        <v>7985000000</v>
       </c>
       <c r="K133" t="n">
-        <v>5018000000</v>
+        <v>199000000</v>
       </c>
       <c r="L133" t="n">
-        <v>118672000000</v>
+        <v>29378000000</v>
       </c>
       <c r="M133" t="n">
-        <v>108430000000</v>
+        <v>14617000000</v>
       </c>
       <c r="N133" t="n">
-        <v>131912180796</v>
+        <v>48498213890</v>
       </c>
     </row>
     <row r="134">
@@ -7344,16 +7344,16 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>82.2</v>
+        <v>83.2</v>
       </c>
       <c r="D134" t="n">
-        <v>2519</v>
+        <v>2489</v>
       </c>
       <c r="E134" t="n">
-        <v>2905.067038344418</v>
+        <v>2901.475903614458</v>
       </c>
       <c r="F134" t="n">
-        <v>-13.3</v>
+        <v>-14.2</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="I134" t="n">
@@ -7381,7 +7381,7 @@
         <v>108430000000</v>
       </c>
       <c r="N134" t="n">
-        <v>131912180796</v>
+        <v>130341174276</v>
       </c>
     </row>
     <row r="135">
@@ -7396,16 +7396,16 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>82.2</v>
+        <v>83.2</v>
       </c>
       <c r="D135" t="n">
-        <v>2519</v>
+        <v>2489</v>
       </c>
       <c r="E135" t="n">
-        <v>2955.342465753425</v>
+        <v>2905.067038344418</v>
       </c>
       <c r="F135" t="n">
-        <v>-14.8</v>
+        <v>-14.3</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="I135" t="n">
@@ -7433,7 +7433,7 @@
         <v>108430000000</v>
       </c>
       <c r="N135" t="n">
-        <v>131912180796</v>
+        <v>130341174276</v>
       </c>
     </row>
     <row r="136">
@@ -7448,16 +7448,16 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>82.2</v>
+        <v>83.2</v>
       </c>
       <c r="D136" t="n">
-        <v>2519</v>
+        <v>2489</v>
       </c>
       <c r="E136" t="n">
-        <v>2987.584858837727</v>
+        <v>2955.342465753425</v>
       </c>
       <c r="F136" t="n">
-        <v>-15.7</v>
+        <v>-15.8</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="I136" t="n">
@@ -7485,7 +7485,7 @@
         <v>108430000000</v>
       </c>
       <c r="N136" t="n">
-        <v>131912180796</v>
+        <v>130341174276</v>
       </c>
     </row>
     <row r="137">
@@ -7500,16 +7500,16 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>82.2</v>
+        <v>83.2</v>
       </c>
       <c r="D137" t="n">
-        <v>2519</v>
+        <v>2489</v>
       </c>
       <c r="E137" t="n">
-        <v>3016.088716673414</v>
+        <v>2987.584858837727</v>
       </c>
       <c r="F137" t="n">
-        <v>-16.5</v>
+        <v>-16.7</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="I137" t="n">
@@ -7537,7 +7537,7 @@
         <v>108430000000</v>
       </c>
       <c r="N137" t="n">
-        <v>131912180796</v>
+        <v>130341174276</v>
       </c>
     </row>
     <row r="138">
@@ -7552,16 +7552,16 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>82.2</v>
+        <v>83.2</v>
       </c>
       <c r="D138" t="n">
-        <v>2519</v>
+        <v>2489</v>
       </c>
       <c r="E138" t="n">
-        <v>3016.087384069568</v>
+        <v>3016.088716673414</v>
       </c>
       <c r="F138" t="n">
-        <v>-16.5</v>
+        <v>-17.5</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="I138" t="n">
@@ -7589,7 +7589,7 @@
         <v>108430000000</v>
       </c>
       <c r="N138" t="n">
-        <v>131912180796</v>
+        <v>130341174276</v>
       </c>
     </row>
     <row r="139">
@@ -7604,16 +7604,16 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>82.2</v>
+        <v>83.2</v>
       </c>
       <c r="D139" t="n">
-        <v>2519</v>
+        <v>2489</v>
       </c>
       <c r="E139" t="n">
-        <v>2939.562915943684</v>
+        <v>3016.087384069568</v>
       </c>
       <c r="F139" t="n">
-        <v>-14.3</v>
+        <v>-17.5</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="I139" t="n">
@@ -7641,187 +7641,187 @@
         <v>108430000000</v>
       </c>
       <c r="N139" t="n">
-        <v>131912180796</v>
+        <v>130341174276</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>近畿車輛株式会社</t>
+          <t>ガンホー・オンライン・エンターテイメント株式会社</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>7122</t>
+          <t>3765</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>105.7</v>
+        <v>83.2</v>
       </c>
       <c r="D140" t="n">
-        <v>2442</v>
+        <v>2489</v>
       </c>
       <c r="E140" t="n">
-        <v>2144.894901144641</v>
+        <v>2939.562915943684</v>
       </c>
       <c r="F140" t="n">
-        <v>13.9</v>
+        <v>-15.3</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>6847000000</v>
+        <v>102086000000</v>
       </c>
       <c r="J140" t="n">
-        <v>4580000000</v>
+        <v>1326000000</v>
       </c>
       <c r="K140" t="n">
-        <v>6329000000</v>
+        <v>5018000000</v>
       </c>
       <c r="L140" t="n">
-        <v>24474000000</v>
+        <v>118672000000</v>
       </c>
       <c r="M140" t="n">
-        <v>17756000000</v>
+        <v>108430000000</v>
       </c>
       <c r="N140" t="n">
-        <v>16801157802</v>
+        <v>130341174276</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>シェアリングテクノロジー株式会社</t>
+          <t>近畿車輛株式会社</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>7122</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>11.7</v>
+        <v>105.6</v>
       </c>
       <c r="D141" t="n">
-        <v>1545</v>
+        <v>2444</v>
       </c>
       <c r="E141" t="n">
-        <v>653.0713101160862</v>
+        <v>2144.894901144641</v>
       </c>
       <c r="F141" t="n">
-        <v>136.6</v>
+        <v>13.9</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>4016706000</v>
+        <v>6847000000</v>
       </c>
       <c r="J141" t="n">
-        <v>309745000</v>
+        <v>4580000000</v>
       </c>
       <c r="K141" t="n">
-        <v>0</v>
+        <v>6329000000</v>
       </c>
       <c r="L141" t="n">
-        <v>185001000</v>
+        <v>24474000000</v>
       </c>
       <c r="M141" t="n">
-        <v>4326451000</v>
+        <v>17756000000</v>
       </c>
       <c r="N141" t="n">
-        <v>36973810605</v>
+        <v>16814917964</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>日本化薬株式会社</t>
+          <t>シェアリングテクノロジー株式会社</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>34.3</v>
+        <v>11.7</v>
       </c>
       <c r="D142" t="n">
-        <v>2131.5</v>
+        <v>1545</v>
       </c>
       <c r="E142" t="n">
-        <v>1111.90611839092</v>
+        <v>653.0713101160862</v>
       </c>
       <c r="F142" t="n">
-        <v>91.7</v>
+        <v>136.6</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>52962000000</v>
+        <v>4016706000</v>
       </c>
       <c r="J142" t="n">
-        <v>48231000000</v>
+        <v>309745000</v>
       </c>
       <c r="K142" t="n">
-        <v>4337000000</v>
+        <v>0</v>
       </c>
       <c r="L142" t="n">
-        <v>246425000000</v>
+        <v>185001000</v>
       </c>
       <c r="M142" t="n">
-        <v>105530000000</v>
+        <v>4326451000</v>
       </c>
       <c r="N142" t="n">
-        <v>307337551154</v>
+        <v>36973810605</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>株式会社博報堂ＤＹホールディングス</t>
+          <t>日本化薬株式会社</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2433</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>45.4</v>
+        <v>34.4</v>
       </c>
       <c r="D143" t="n">
-        <v>1309.5</v>
+        <v>2129.5</v>
       </c>
       <c r="E143" t="n">
-        <v>1111.251693601708</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="F143" t="n">
-        <v>17.8</v>
+        <v>91.5</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -7830,182 +7830,182 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>180697000000</v>
+        <v>52962000000</v>
       </c>
       <c r="J143" t="n">
-        <v>21890000000</v>
+        <v>48231000000</v>
       </c>
       <c r="K143" t="n">
-        <v>10976000000</v>
+        <v>4337000000</v>
       </c>
       <c r="L143" t="n">
-        <v>387414000000</v>
+        <v>246425000000</v>
       </c>
       <c r="M143" t="n">
-        <v>213563000000</v>
+        <v>105530000000</v>
       </c>
       <c r="N143" t="n">
-        <v>470152456380</v>
+        <v>307049174376</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>データセクション株式会社</t>
+          <t>株式会社博報堂ＤＹホールディングス</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>2433</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>2.2</v>
+        <v>44.7</v>
       </c>
       <c r="D144" t="n">
-        <v>1807</v>
+        <v>1330.5</v>
       </c>
       <c r="E144" t="n">
-        <v>5143.276404494382</v>
+        <v>1111.251693601708</v>
       </c>
       <c r="F144" t="n">
-        <v>-64.90000000000001</v>
+        <v>19.7</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1420430000</v>
+        <v>180697000000</v>
       </c>
       <c r="J144" t="n">
-        <v>1162000</v>
+        <v>21890000000</v>
       </c>
       <c r="K144" t="n">
-        <v>49326000</v>
+        <v>10976000000</v>
       </c>
       <c r="L144" t="n">
-        <v>2818110000</v>
+        <v>387414000000</v>
       </c>
       <c r="M144" t="n">
-        <v>1470918000</v>
+        <v>213563000000</v>
       </c>
       <c r="N144" t="n">
-        <v>67694386942</v>
+        <v>477692129220</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>東ソー株式会社</t>
+          <t>データセクション株式会社</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>4042</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>41.8</v>
+        <v>1.9</v>
       </c>
       <c r="D145" t="n">
-        <v>2647.5</v>
+        <v>2077</v>
       </c>
       <c r="E145" t="n">
-        <v>2032.365850102071</v>
+        <v>5143.276404494382</v>
       </c>
       <c r="F145" t="n">
-        <v>30.3</v>
+        <v>-59.6</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>160812000000</v>
+        <v>1420430000</v>
       </c>
       <c r="J145" t="n">
-        <v>109648000000</v>
+        <v>1162000</v>
       </c>
       <c r="K145" t="n">
-        <v>70132000000</v>
+        <v>49326000</v>
       </c>
       <c r="L145" t="n">
-        <v>759724000000</v>
+        <v>2818110000</v>
       </c>
       <c r="M145" t="n">
-        <v>340592000000</v>
+        <v>1470918000</v>
       </c>
       <c r="N145" t="n">
-        <v>815140220535</v>
+        <v>77809209562</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>大平洋金属株式会社</t>
+          <t>東ソー株式会社</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>5541</t>
+          <t>4042</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>67.3</v>
+        <v>41.6</v>
       </c>
       <c r="D146" t="n">
-        <v>2660</v>
+        <v>2656.5</v>
       </c>
       <c r="E146" t="n">
-        <v>1270</v>
+        <v>2032.365850102071</v>
       </c>
       <c r="F146" t="n">
-        <v>109.4</v>
+        <v>30.7</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>26631000000</v>
+        <v>160812000000</v>
       </c>
       <c r="J146" t="n">
-        <v>1877000000</v>
+        <v>109648000000</v>
       </c>
       <c r="K146" t="n">
-        <v>2600000000</v>
+        <v>70132000000</v>
       </c>
       <c r="L146" t="n">
-        <v>80153000000</v>
+        <v>759724000000</v>
       </c>
       <c r="M146" t="n">
-        <v>31108000000</v>
+        <v>340592000000</v>
       </c>
       <c r="N146" t="n">
-        <v>46250912260</v>
+        <v>817911235449</v>
       </c>
     </row>
     <row r="147">
@@ -8020,16 +8020,16 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>67.3</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D147" t="n">
-        <v>2660</v>
+        <v>2713</v>
       </c>
       <c r="E147" t="n">
-        <v>1170</v>
+        <v>1270</v>
       </c>
       <c r="F147" t="n">
-        <v>127.4</v>
+        <v>113.6</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="I147" t="n">
@@ -8057,239 +8057,239 @@
         <v>31108000000</v>
       </c>
       <c r="N147" t="n">
-        <v>46250912260</v>
+        <v>47172452993</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>株式会社イエローハット</t>
+          <t>大平洋金属株式会社</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>9882</t>
+          <t>5541</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>36</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D148" t="n">
-        <v>1728</v>
+        <v>2713</v>
       </c>
       <c r="E148" t="n">
-        <v>2112.609181636727</v>
+        <v>1170</v>
       </c>
       <c r="F148" t="n">
-        <v>-18.2</v>
+        <v>131.9</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>10902000000</v>
+        <v>26631000000</v>
       </c>
       <c r="J148" t="n">
-        <v>29975000000</v>
+        <v>1877000000</v>
       </c>
       <c r="K148" t="n">
-        <v>11341000000</v>
+        <v>2600000000</v>
       </c>
       <c r="L148" t="n">
-        <v>98298000000</v>
+        <v>80153000000</v>
       </c>
       <c r="M148" t="n">
-        <v>52218000000</v>
+        <v>31108000000</v>
       </c>
       <c r="N148" t="n">
-        <v>145082897280</v>
+        <v>47172452993</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>三井松島ホールディングス株式会社</t>
+          <t>株式会社イエローハット</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>9882</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>40.2</v>
+        <v>35.6</v>
       </c>
       <c r="D149" t="n">
-        <v>2280</v>
+        <v>1745</v>
       </c>
       <c r="E149" t="n">
-        <v>2920</v>
+        <v>2112.609181636727</v>
       </c>
       <c r="F149" t="n">
-        <v>-21.9</v>
+        <v>-17.4</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>19413000000</v>
+        <v>10902000000</v>
       </c>
       <c r="J149" t="n">
-        <v>3540000000</v>
+        <v>29975000000</v>
       </c>
       <c r="K149" t="n">
-        <v>10945000000</v>
+        <v>11341000000</v>
       </c>
       <c r="L149" t="n">
-        <v>35537000000</v>
+        <v>98298000000</v>
       </c>
       <c r="M149" t="n">
-        <v>33898000000</v>
+        <v>52218000000</v>
       </c>
       <c r="N149" t="n">
-        <v>84423748800</v>
+        <v>146510217450</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>アツギ株式会社</t>
+          <t>三井松島ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>76.40000000000001</v>
+        <v>39.8</v>
       </c>
       <c r="D150" t="n">
-        <v>1014</v>
+        <v>2300</v>
       </c>
       <c r="E150" t="n">
-        <v>668.9358717434869</v>
+        <v>2920</v>
       </c>
       <c r="F150" t="n">
-        <v>51.6</v>
+        <v>-21.2</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>5500000000</v>
+        <v>19413000000</v>
       </c>
       <c r="J150" t="n">
-        <v>3208000000</v>
+        <v>3540000000</v>
       </c>
       <c r="K150" t="n">
-        <v>3702000000</v>
+        <v>10945000000</v>
       </c>
       <c r="L150" t="n">
-        <v>32145000000</v>
+        <v>35537000000</v>
       </c>
       <c r="M150" t="n">
-        <v>12410000000</v>
+        <v>33898000000</v>
       </c>
       <c r="N150" t="n">
-        <v>16238202084</v>
+        <v>85164308000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ニッコンホールディングス株式会社</t>
+          <t>アツギ株式会社</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>9072</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>29.2</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="D151" t="n">
-        <v>5062</v>
+        <v>1014</v>
       </c>
       <c r="E151" t="n">
-        <v>2779.139169918938</v>
+        <v>668.9358717434869</v>
       </c>
       <c r="F151" t="n">
-        <v>82.09999999999999</v>
+        <v>51.6</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>29157000000</v>
+        <v>5500000000</v>
       </c>
       <c r="J151" t="n">
-        <v>126028000000</v>
+        <v>3208000000</v>
       </c>
       <c r="K151" t="n">
-        <v>28031000000</v>
+        <v>3702000000</v>
       </c>
       <c r="L151" t="n">
-        <v>219035000000</v>
+        <v>32145000000</v>
       </c>
       <c r="M151" t="n">
-        <v>183216000000</v>
+        <v>12410000000</v>
       </c>
       <c r="N151" t="n">
-        <v>627852368202</v>
+        <v>16238202084</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>株式会社セプテーニ・ホールディングス</t>
+          <t>ニッコンホールディングス株式会社</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>4293</t>
+          <t>9072</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>13.3</v>
+        <v>28.8</v>
       </c>
       <c r="D152" t="n">
-        <v>505</v>
+        <v>5125</v>
       </c>
       <c r="E152" t="n">
-        <v>448.6811097117532</v>
+        <v>2779.139169918938</v>
       </c>
       <c r="F152" t="n">
-        <v>12.6</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -8298,234 +8298,234 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>12184507000</v>
+        <v>29157000000</v>
       </c>
       <c r="J152" t="n">
-        <v>168073000</v>
+        <v>126028000000</v>
       </c>
       <c r="K152" t="n">
-        <v>1600720000</v>
+        <v>28031000000</v>
       </c>
       <c r="L152" t="n">
-        <v>11861578000</v>
+        <v>219035000000</v>
       </c>
       <c r="M152" t="n">
-        <v>13953300000</v>
+        <v>183216000000</v>
       </c>
       <c r="N152" t="n">
-        <v>104759780045</v>
+        <v>635666413875</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ニッタ株式会社</t>
+          <t>株式会社セプテーニ・ホールディングス</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>5186</t>
+          <t>4293</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>28</v>
+        <v>13.5</v>
       </c>
       <c r="D153" t="n">
-        <v>6890</v>
+        <v>500</v>
       </c>
       <c r="E153" t="n">
-        <v>3096.322467304314</v>
+        <v>448.6811097117532</v>
       </c>
       <c r="F153" t="n">
-        <v>122.5</v>
+        <v>11.4</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>30872000000</v>
+        <v>12184507000</v>
       </c>
       <c r="J153" t="n">
-        <v>15392000000</v>
+        <v>168073000</v>
       </c>
       <c r="K153" t="n">
-        <v>6697000000</v>
+        <v>1600720000</v>
       </c>
       <c r="L153" t="n">
-        <v>119214000000</v>
+        <v>11861578000</v>
       </c>
       <c r="M153" t="n">
-        <v>52961000000</v>
+        <v>13953300000</v>
       </c>
       <c r="N153" t="n">
-        <v>189014541300</v>
+        <v>103722554500</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>株式会社エス・エム・エス</t>
+          <t>ニッタ株式会社</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>8.4</v>
+        <v>28.1</v>
       </c>
       <c r="D154" t="n">
-        <v>2652</v>
+        <v>6880</v>
       </c>
       <c r="E154" t="n">
-        <v>1478.127248828989</v>
+        <v>3096.322467304314</v>
       </c>
       <c r="F154" t="n">
-        <v>79.40000000000001</v>
+        <v>122.2</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>14126000000</v>
+        <v>30872000000</v>
       </c>
       <c r="J154" t="n">
-        <v>1187000000</v>
+        <v>15392000000</v>
       </c>
       <c r="K154" t="n">
-        <v>2875000000</v>
+        <v>6697000000</v>
       </c>
       <c r="L154" t="n">
-        <v>29991000000</v>
+        <v>119214000000</v>
       </c>
       <c r="M154" t="n">
-        <v>18188000000</v>
+        <v>52961000000</v>
       </c>
       <c r="N154" t="n">
-        <v>217677350748</v>
+        <v>188740209600</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>株式会社オリエントコーポレーション</t>
+          <t>株式会社エス・エム・エス</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>8585</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>310.4</v>
+        <v>8.4</v>
       </c>
       <c r="D155" t="n">
-        <v>845</v>
+        <v>2630</v>
       </c>
       <c r="E155" t="n">
-        <v>798.3805136422309</v>
+        <v>1478.127248828989</v>
       </c>
       <c r="F155" t="n">
-        <v>5.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="I155" t="n">
-        <v>408187000000</v>
+        <v>14126000000</v>
       </c>
       <c r="J155" t="n">
-        <v>18930000000</v>
+        <v>1187000000</v>
       </c>
       <c r="K155" t="n">
-        <v>21921000000</v>
+        <v>2875000000</v>
       </c>
       <c r="L155" t="n">
-        <v>216837000000</v>
+        <v>29991000000</v>
       </c>
       <c r="M155" t="n">
-        <v>449038000000</v>
+        <v>18188000000</v>
       </c>
       <c r="N155" t="n">
-        <v>144652055080</v>
+        <v>215871580870</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>トーセイ株式会社</t>
+          <t>株式会社オリエントコーポレーション</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>8585</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>45.8</v>
+        <v>309.7</v>
       </c>
       <c r="D156" t="n">
-        <v>1717</v>
+        <v>847</v>
       </c>
       <c r="E156" t="n">
-        <v>1752.426893379333</v>
+        <v>798.3805136422309</v>
       </c>
       <c r="F156" t="n">
-        <v>-2</v>
+        <v>6.1</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="I156" t="n">
-        <v>20753937000</v>
+        <v>408187000000</v>
       </c>
       <c r="J156" t="n">
-        <v>46868512000</v>
+        <v>18930000000</v>
       </c>
       <c r="K156" t="n">
-        <v>8610046000</v>
+        <v>21921000000</v>
       </c>
       <c r="L156" t="n">
-        <v>59467346000</v>
+        <v>216837000000</v>
       </c>
       <c r="M156" t="n">
-        <v>76232495000</v>
+        <v>449038000000</v>
       </c>
       <c r="N156" t="n">
-        <v>166559473700</v>
+        <v>144994426808</v>
       </c>
     </row>
     <row r="157">
@@ -8540,16 +8540,16 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>45.8</v>
+        <v>45.6</v>
       </c>
       <c r="D157" t="n">
-        <v>1717</v>
+        <v>1722</v>
       </c>
       <c r="E157" t="n">
-        <v>1576.721867844292</v>
+        <v>1752.426893379333</v>
       </c>
       <c r="F157" t="n">
-        <v>8.9</v>
+        <v>-1.7</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="I157" t="n">
@@ -8577,215 +8577,215 @@
         <v>76232495000</v>
       </c>
       <c r="N157" t="n">
-        <v>166559473700</v>
+        <v>167044504200</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>関西ペイント株式会社</t>
+          <t>トーセイ株式会社</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>4613</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>33.4</v>
+        <v>45.6</v>
       </c>
       <c r="D158" t="n">
-        <v>2851</v>
+        <v>1722</v>
       </c>
       <c r="E158" t="n">
-        <v>2381.523440544182</v>
+        <v>1576.721867844292</v>
       </c>
       <c r="F158" t="n">
-        <v>19.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>59709000000</v>
+        <v>20753937000</v>
       </c>
       <c r="J158" t="n">
-        <v>76498000000</v>
+        <v>46868512000</v>
       </c>
       <c r="K158" t="n">
-        <v>32489000000</v>
+        <v>8610046000</v>
       </c>
       <c r="L158" t="n">
-        <v>375114000000</v>
+        <v>59467346000</v>
       </c>
       <c r="M158" t="n">
-        <v>168696000000</v>
+        <v>76232495000</v>
       </c>
       <c r="N158" t="n">
-        <v>505379504344</v>
+        <v>167044504200</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>株式会社メルカリ</t>
+          <t>関西ペイント株式会社</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>4613</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>36.7</v>
+        <v>33.2</v>
       </c>
       <c r="D159" t="n">
-        <v>3554</v>
+        <v>2867</v>
       </c>
       <c r="E159" t="n">
-        <v>2006.059650428343</v>
+        <v>2381.523440544182</v>
       </c>
       <c r="F159" t="n">
-        <v>77.2</v>
+        <v>20.4</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="I159" t="n">
-        <v>211406000000</v>
+        <v>59709000000</v>
       </c>
       <c r="J159" t="n">
-        <v>367000000</v>
+        <v>76498000000</v>
       </c>
       <c r="K159" t="n">
-        <v>1021000000</v>
+        <v>32489000000</v>
       </c>
       <c r="L159" t="n">
-        <v>37998000000</v>
+        <v>375114000000</v>
       </c>
       <c r="M159" t="n">
-        <v>212794000000</v>
+        <v>168696000000</v>
       </c>
       <c r="N159" t="n">
-        <v>579943912818</v>
+        <v>508215727448</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>江崎グリコ株式会社</t>
+          <t>株式会社メルカリ</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>59.7</v>
+        <v>35.9</v>
       </c>
       <c r="D160" t="n">
-        <v>5015</v>
+        <v>3635</v>
       </c>
       <c r="E160" t="n">
-        <v>4154.626869982095</v>
+        <v>2006.059650428343</v>
       </c>
       <c r="F160" t="n">
-        <v>20.7</v>
+        <v>81.2</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>89463000000</v>
+        <v>211406000000</v>
       </c>
       <c r="J160" t="n">
-        <v>42929000000</v>
+        <v>367000000</v>
       </c>
       <c r="K160" t="n">
-        <v>46694000000</v>
+        <v>1021000000</v>
       </c>
       <c r="L160" t="n">
-        <v>241177000000</v>
+        <v>37998000000</v>
       </c>
       <c r="M160" t="n">
-        <v>179086000000</v>
+        <v>212794000000</v>
       </c>
       <c r="N160" t="n">
-        <v>299900390140</v>
+        <v>593161542795</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>エア・ウォーター株式会社</t>
+          <t>江崎グリコ株式会社</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>15.1</v>
+        <v>59.3</v>
       </c>
       <c r="D161" t="n">
-        <v>2964</v>
+        <v>5050</v>
       </c>
       <c r="E161" t="n">
-        <v>2261.880826568852</v>
+        <v>4154.626869982095</v>
       </c>
       <c r="F161" t="n">
-        <v>31</v>
+        <v>21.6</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="I161" t="n">
-        <v>29189000000</v>
+        <v>89463000000</v>
       </c>
       <c r="J161" t="n">
-        <v>31318000000</v>
+        <v>42929000000</v>
       </c>
       <c r="K161" t="n">
-        <v>42001000000</v>
+        <v>46694000000</v>
       </c>
       <c r="L161" t="n">
-        <v>194657000000</v>
+        <v>241177000000</v>
       </c>
       <c r="M161" t="n">
-        <v>102508000000</v>
+        <v>179086000000</v>
       </c>
       <c r="N161" t="n">
-        <v>679538178852</v>
+        <v>301993413800</v>
       </c>
     </row>
     <row r="162">
@@ -8800,25 +8800,25 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>15.1</v>
+        <v>15.4</v>
       </c>
       <c r="D162" t="n">
-        <v>2964</v>
+        <v>2911</v>
       </c>
       <c r="E162" t="n">
-        <v>1970</v>
+        <v>2261.880826568852</v>
       </c>
       <c r="F162" t="n">
-        <v>50.5</v>
+        <v>28.7</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I162" t="n">
@@ -8837,32 +8837,32 @@
         <v>102508000000</v>
       </c>
       <c r="N162" t="n">
-        <v>679538178852</v>
+        <v>667387192523</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>月島ホールディングス株式会社</t>
+          <t>エア・ウォーター株式会社</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>6332</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="C163" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="D163" t="n">
+        <v>2911</v>
+      </c>
+      <c r="E163" t="n">
+        <v>1970</v>
+      </c>
+      <c r="F163" t="n">
         <v>47.8</v>
       </c>
-      <c r="D163" t="n">
-        <v>2700</v>
-      </c>
-      <c r="E163" t="n">
-        <v>1410</v>
-      </c>
-      <c r="F163" t="n">
-        <v>91.5</v>
-      </c>
       <c r="G163" t="inlineStr">
         <is>
           <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
@@ -8870,50 +8870,50 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I163" t="n">
-        <v>28795000000</v>
+        <v>29189000000</v>
       </c>
       <c r="J163" t="n">
-        <v>22203000000</v>
+        <v>31318000000</v>
       </c>
       <c r="K163" t="n">
-        <v>100000000</v>
+        <v>42001000000</v>
       </c>
       <c r="L163" t="n">
-        <v>80949000000</v>
+        <v>194657000000</v>
       </c>
       <c r="M163" t="n">
-        <v>51098000000</v>
+        <v>102508000000</v>
       </c>
       <c r="N163" t="n">
-        <v>106923302100</v>
+        <v>667387192523</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>日本製紙株式会社</t>
+          <t>月島ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>303.3</v>
+        <v>47.9</v>
       </c>
       <c r="D164" t="n">
-        <v>1318</v>
+        <v>2694</v>
       </c>
       <c r="E164" t="n">
-        <v>1250</v>
+        <v>1410</v>
       </c>
       <c r="F164" t="n">
-        <v>5.4</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -8922,50 +8922,50 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="I164" t="n">
-        <v>136216000000</v>
+        <v>28795000000</v>
       </c>
       <c r="J164" t="n">
-        <v>151771000000</v>
+        <v>22203000000</v>
       </c>
       <c r="K164" t="n">
-        <v>172984000000</v>
+        <v>100000000</v>
       </c>
       <c r="L164" t="n">
-        <v>438604000000</v>
+        <v>80949000000</v>
       </c>
       <c r="M164" t="n">
-        <v>460971000000</v>
+        <v>51098000000</v>
       </c>
       <c r="N164" t="n">
-        <v>151976606954</v>
+        <v>106685694762</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ＫＰＰグループホールディングス株式会社</t>
+          <t>日本製紙株式会社</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>9274</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>72</v>
+        <v>299.9</v>
       </c>
       <c r="D165" t="n">
-        <v>1138</v>
+        <v>1333</v>
       </c>
       <c r="E165" t="n">
-        <v>730</v>
+        <v>1250</v>
       </c>
       <c r="F165" t="n">
-        <v>55.9</v>
+        <v>6.6</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -8974,182 +8974,182 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I165" t="n">
-        <v>22631000000</v>
+        <v>136216000000</v>
       </c>
       <c r="J165" t="n">
-        <v>7793000000</v>
+        <v>151771000000</v>
       </c>
       <c r="K165" t="n">
-        <v>19603000000</v>
+        <v>172984000000</v>
       </c>
       <c r="L165" t="n">
-        <v>56374000000</v>
+        <v>438604000000</v>
       </c>
       <c r="M165" t="n">
-        <v>50027000000</v>
+        <v>460971000000</v>
       </c>
       <c r="N165" t="n">
-        <v>69479663668</v>
+        <v>153706234499</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>コクヨ株式会社</t>
+          <t>ＫＰＰグループホールディングス株式会社</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>7984</t>
+          <t>9274</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>41.2</v>
+        <v>69.7</v>
       </c>
       <c r="D166" t="n">
-        <v>896.7000122070312</v>
+        <v>1176</v>
       </c>
       <c r="E166" t="n">
-        <v>2157.626835069302</v>
+        <v>730</v>
       </c>
       <c r="F166" t="n">
-        <v>-58.4</v>
+        <v>61.1</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I166" t="n">
-        <v>100575000000</v>
+        <v>22631000000</v>
       </c>
       <c r="J166" t="n">
-        <v>22282000000</v>
+        <v>7793000000</v>
       </c>
       <c r="K166" t="n">
-        <v>30106000000</v>
+        <v>19603000000</v>
       </c>
       <c r="L166" t="n">
-        <v>230105000000</v>
+        <v>56374000000</v>
       </c>
       <c r="M166" t="n">
-        <v>152963000000</v>
+        <v>50027000000</v>
       </c>
       <c r="N166" t="n">
-        <v>371628416725</v>
+        <v>71799722736</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Ｊ.フロント リテイリング株式会社</t>
+          <t>コクヨ株式会社</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>3086</t>
+          <t>7984</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>7.4</v>
+        <v>41.1</v>
       </c>
       <c r="D167" t="n">
-        <v>2676.5</v>
+        <v>898.9000244140625</v>
       </c>
       <c r="E167" t="n">
-        <v>1827.011042553346</v>
+        <v>2157.626835069302</v>
       </c>
       <c r="F167" t="n">
-        <v>46.5</v>
+        <v>-58.3</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="I167" t="n">
-        <v>46053000000</v>
+        <v>100575000000</v>
       </c>
       <c r="J167" t="n">
-        <v>223000000</v>
+        <v>22282000000</v>
       </c>
       <c r="K167" t="n">
-        <v>2060000000</v>
+        <v>30106000000</v>
       </c>
       <c r="L167" t="n">
-        <v>335241000000</v>
+        <v>230105000000</v>
       </c>
       <c r="M167" t="n">
-        <v>48336000000</v>
+        <v>152963000000</v>
       </c>
       <c r="N167" t="n">
-        <v>653260771582</v>
+        <v>372540189940</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ＫＨネオケム株式会社</t>
+          <t>Ｊ.フロント リテイリング株式会社</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>4189</t>
+          <t>3086</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>28.5</v>
+        <v>7.3</v>
       </c>
       <c r="D168" t="n">
-        <v>3235</v>
+        <v>2708.5</v>
       </c>
       <c r="E168" t="n">
-        <v>2673.3867000123</v>
+        <v>1827.011042553346</v>
       </c>
       <c r="F168" t="n">
-        <v>21</v>
+        <v>48.2</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I168" t="n">
-        <v>16934000000</v>
+        <v>46053000000</v>
       </c>
       <c r="J168" t="n">
-        <v>8038000000</v>
+        <v>223000000</v>
       </c>
       <c r="K168" t="n">
-        <v>7370000000</v>
+        <v>2060000000</v>
       </c>
       <c r="L168" t="n">
-        <v>57505000000</v>
+        <v>335241000000</v>
       </c>
       <c r="M168" t="n">
-        <v>32342000000</v>
+        <v>48336000000</v>
       </c>
       <c r="N168" t="n">
-        <v>113282958260</v>
+        <v>661071100254</v>
       </c>
     </row>
     <row r="169">
@@ -9164,13 +9164,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>28.5</v>
+        <v>28</v>
       </c>
       <c r="D169" t="n">
-        <v>3235</v>
+        <v>3300</v>
       </c>
       <c r="E169" t="n">
-        <v>2651.028089511613</v>
+        <v>2704.850301500491</v>
       </c>
       <c r="F169" t="n">
         <v>22</v>
@@ -9182,7 +9182,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="I169" t="n">
@@ -9201,7 +9201,7 @@
         <v>32342000000</v>
       </c>
       <c r="N169" t="n">
-        <v>113282958260</v>
+        <v>115559122800</v>
       </c>
     </row>
     <row r="170">
@@ -9216,16 +9216,16 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>28.5</v>
+        <v>28</v>
       </c>
       <c r="D170" t="n">
-        <v>3235</v>
+        <v>3300</v>
       </c>
       <c r="E170" t="n">
-        <v>2650.592873897018</v>
+        <v>2694.658240666079</v>
       </c>
       <c r="F170" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="I170" t="n">
@@ -9253,7 +9253,7 @@
         <v>32342000000</v>
       </c>
       <c r="N170" t="n">
-        <v>113282958260</v>
+        <v>115559122800</v>
       </c>
     </row>
     <row r="171">
@@ -9268,16 +9268,16 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>28.5</v>
+        <v>28</v>
       </c>
       <c r="D171" t="n">
-        <v>3235</v>
+        <v>3300</v>
       </c>
       <c r="E171" t="n">
-        <v>2615.786410161549</v>
+        <v>2673.3867000123</v>
       </c>
       <c r="F171" t="n">
-        <v>23.7</v>
+        <v>23.4</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="I171" t="n">
@@ -9305,7 +9305,7 @@
         <v>32342000000</v>
       </c>
       <c r="N171" t="n">
-        <v>113282958260</v>
+        <v>115559122800</v>
       </c>
     </row>
     <row r="172">
@@ -9320,16 +9320,16 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>28.5</v>
+        <v>28</v>
       </c>
       <c r="D172" t="n">
-        <v>3235</v>
+        <v>3300</v>
       </c>
       <c r="E172" t="n">
-        <v>2566.161017239607</v>
+        <v>2651.028089511613</v>
       </c>
       <c r="F172" t="n">
-        <v>26.1</v>
+        <v>24.5</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="I172" t="n">
@@ -9357,7 +9357,7 @@
         <v>32342000000</v>
       </c>
       <c r="N172" t="n">
-        <v>113282958260</v>
+        <v>115559122800</v>
       </c>
     </row>
     <row r="173">
@@ -9372,16 +9372,16 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>28.5</v>
+        <v>28</v>
       </c>
       <c r="D173" t="n">
-        <v>3235</v>
+        <v>3300</v>
       </c>
       <c r="E173" t="n">
-        <v>2550.198980592041</v>
+        <v>2650.592873897018</v>
       </c>
       <c r="F173" t="n">
-        <v>26.9</v>
+        <v>24.5</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="I173" t="n">
@@ -9409,7 +9409,7 @@
         <v>32342000000</v>
       </c>
       <c r="N173" t="n">
-        <v>113282958260</v>
+        <v>115559122800</v>
       </c>
     </row>
     <row r="174">
@@ -9424,16 +9424,16 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>28.5</v>
+        <v>28</v>
       </c>
       <c r="D174" t="n">
-        <v>3235</v>
+        <v>3300</v>
       </c>
       <c r="E174" t="n">
-        <v>2550.198980592041</v>
+        <v>2615.786410161549</v>
       </c>
       <c r="F174" t="n">
-        <v>26.9</v>
+        <v>26.2</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="I174" t="n">
@@ -9461,59 +9461,215 @@
         <v>32342000000</v>
       </c>
       <c r="N174" t="n">
-        <v>113282958260</v>
+        <v>115559122800</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
+          <t>ＫＨネオケム株式会社</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>4189</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>28</v>
+      </c>
+      <c r="D175" t="n">
+        <v>3300</v>
+      </c>
+      <c r="E175" t="n">
+        <v>2566.161017239607</v>
+      </c>
+      <c r="F175" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>株式会社ストラテジックキャピタル</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="I175" t="n">
+        <v>16934000000</v>
+      </c>
+      <c r="J175" t="n">
+        <v>8038000000</v>
+      </c>
+      <c r="K175" t="n">
+        <v>7370000000</v>
+      </c>
+      <c r="L175" t="n">
+        <v>57505000000</v>
+      </c>
+      <c r="M175" t="n">
+        <v>32342000000</v>
+      </c>
+      <c r="N175" t="n">
+        <v>115559122800</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>ＫＨネオケム株式会社</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>4189</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>28</v>
+      </c>
+      <c r="D176" t="n">
+        <v>3300</v>
+      </c>
+      <c r="E176" t="n">
+        <v>2550.198980592041</v>
+      </c>
+      <c r="F176" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>株式会社ストラテジックキャピタル</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="I176" t="n">
+        <v>16934000000</v>
+      </c>
+      <c r="J176" t="n">
+        <v>8038000000</v>
+      </c>
+      <c r="K176" t="n">
+        <v>7370000000</v>
+      </c>
+      <c r="L176" t="n">
+        <v>57505000000</v>
+      </c>
+      <c r="M176" t="n">
+        <v>32342000000</v>
+      </c>
+      <c r="N176" t="n">
+        <v>115559122800</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>ＫＨネオケム株式会社</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>4189</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>28</v>
+      </c>
+      <c r="D177" t="n">
+        <v>3300</v>
+      </c>
+      <c r="E177" t="n">
+        <v>2550.198980592041</v>
+      </c>
+      <c r="F177" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>株式会社ストラテジックキャピタル</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="I177" t="n">
+        <v>16934000000</v>
+      </c>
+      <c r="J177" t="n">
+        <v>8038000000</v>
+      </c>
+      <c r="K177" t="n">
+        <v>7370000000</v>
+      </c>
+      <c r="L177" t="n">
+        <v>57505000000</v>
+      </c>
+      <c r="M177" t="n">
+        <v>32342000000</v>
+      </c>
+      <c r="N177" t="n">
+        <v>115559122800</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
           <t>古河機械金属株式会社</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
+      <c r="B178" t="inlineStr">
         <is>
           <t>5715</t>
         </is>
       </c>
-      <c r="C175" t="n">
-        <v>46</v>
-      </c>
-      <c r="D175" t="n">
-        <v>4140</v>
-      </c>
-      <c r="E175" t="n">
+      <c r="C178" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="D178" t="n">
+        <v>4145</v>
+      </c>
+      <c r="E178" t="n">
         <v>1600</v>
       </c>
-      <c r="F175" t="n">
-        <v>158.8</v>
-      </c>
-      <c r="G175" t="inlineStr">
+      <c r="F178" t="n">
+        <v>159.1</v>
+      </c>
+      <c r="G178" t="inlineStr">
         <is>
           <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
+      <c r="H178" t="inlineStr">
         <is>
           <t>2025-01-10</t>
         </is>
       </c>
-      <c r="I175" t="n">
+      <c r="I178" t="n">
         <v>14468000000</v>
       </c>
-      <c r="J175" t="n">
+      <c r="J178" t="n">
         <v>26121000000</v>
       </c>
-      <c r="K175" t="n">
+      <c r="K178" t="n">
         <v>19903000000</v>
       </c>
-      <c r="L175" t="n">
+      <c r="L178" t="n">
         <v>100075000000</v>
       </c>
-      <c r="M175" t="n">
+      <c r="M178" t="n">
         <v>60492000000</v>
       </c>
-      <c r="N175" t="n">
-        <v>131528284380</v>
+      <c r="N178" t="n">
+        <v>131687134965</v>
       </c>
     </row>
   </sheetData>

--- a/docs/アクティビスト銘柄_資産判定.xlsx
+++ b/docs/アクティビスト銘柄_資産判定.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N178"/>
+  <dimension ref="A1:N176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>28.7</v>
+        <v>28.6</v>
       </c>
       <c r="D67" t="n">
         <v>3020</v>
@@ -3909,7 +3909,7 @@
         <v>46138000000</v>
       </c>
       <c r="N67" t="n">
-        <v>160884251620</v>
+        <v>161072560700</v>
       </c>
     </row>
     <row r="68">
@@ -6139,129 +6139,129 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ニデック株式会社</t>
+          <t>株式会社ニコン</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>6594</t>
+          <t>7731</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>6.4</v>
+        <v>19.6</v>
       </c>
       <c r="D111" t="n">
-        <v>2840</v>
+        <v>1873.5</v>
       </c>
       <c r="E111" t="n">
-        <v>2220.184278344451</v>
+        <v>1512.21980974841</v>
       </c>
       <c r="F111" t="n">
-        <v>27.9</v>
+        <v>23.9</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>163815000000</v>
+        <v>45228000000</v>
       </c>
       <c r="J111" t="n">
-        <v>17829000000</v>
+        <v>8297000000</v>
       </c>
       <c r="K111" t="n">
-        <v>25472000000</v>
+        <v>67291000000</v>
       </c>
       <c r="L111" t="n">
-        <v>298063000000</v>
+        <v>362281000000</v>
       </c>
       <c r="M111" t="n">
-        <v>207116000000</v>
+        <v>120816000000</v>
       </c>
       <c r="N111" t="n">
-        <v>3255519931400</v>
+        <v>617162305480</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>株式会社ニコン</t>
+          <t>株式会社アインホールディングス</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>7731</t>
+          <t>9627</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>19.6</v>
+        <v>49.1</v>
       </c>
       <c r="D112" t="n">
-        <v>1873.5</v>
+        <v>5463</v>
       </c>
       <c r="E112" t="n">
-        <v>1512.21980974841</v>
+        <v>2836.942753814942</v>
       </c>
       <c r="F112" t="n">
-        <v>23.9</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>45228000000</v>
+        <v>59470000000</v>
       </c>
       <c r="J112" t="n">
-        <v>8297000000</v>
+        <v>31648000000</v>
       </c>
       <c r="K112" t="n">
-        <v>67291000000</v>
+        <v>3233000000</v>
       </c>
       <c r="L112" t="n">
-        <v>362281000000</v>
+        <v>119010000000</v>
       </c>
       <c r="M112" t="n">
-        <v>120816000000</v>
+        <v>94351000000</v>
       </c>
       <c r="N112" t="n">
-        <v>617162305480</v>
+        <v>192190639923</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>株式会社アインホールディングス</t>
+          <t>市光工業株式会社</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>9627</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>49.1</v>
+        <v>34.9</v>
       </c>
       <c r="D113" t="n">
-        <v>5463</v>
+        <v>569</v>
       </c>
       <c r="E113" t="n">
-        <v>2836.942753814942</v>
+        <v>549.4799823005444</v>
       </c>
       <c r="F113" t="n">
-        <v>92.59999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -6270,390 +6270,390 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>59470000000</v>
+        <v>5720000000</v>
       </c>
       <c r="J113" t="n">
-        <v>31648000000</v>
+        <v>9921000000</v>
       </c>
       <c r="K113" t="n">
-        <v>3233000000</v>
+        <v>3474000000</v>
       </c>
       <c r="L113" t="n">
-        <v>119010000000</v>
+        <v>49523000000</v>
       </c>
       <c r="M113" t="n">
-        <v>94351000000</v>
+        <v>19115000000</v>
       </c>
       <c r="N113" t="n">
-        <v>192190639923</v>
+        <v>54797209290</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>市光工業株式会社</t>
+          <t>山洋電気株式会社</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>7244</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>34.9</v>
+        <v>11.4</v>
       </c>
       <c r="D114" t="n">
-        <v>569</v>
+        <v>5430</v>
       </c>
       <c r="E114" t="n">
-        <v>549.4799823005444</v>
+        <v>7052.737306843267</v>
       </c>
       <c r="F114" t="n">
-        <v>3.6</v>
+        <v>-23</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>5720000000</v>
+        <v>8317000000</v>
       </c>
       <c r="J114" t="n">
-        <v>9921000000</v>
+        <v>6048000000</v>
       </c>
       <c r="K114" t="n">
-        <v>3474000000</v>
+        <v>7673000000</v>
       </c>
       <c r="L114" t="n">
-        <v>49523000000</v>
+        <v>49734000000</v>
       </c>
       <c r="M114" t="n">
-        <v>19115000000</v>
+        <v>22038000000</v>
       </c>
       <c r="N114" t="n">
-        <v>54797209290</v>
+        <v>192846672630</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>山洋電気株式会社</t>
+          <t>日本特殊塗料株式会社</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>4619</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>11.4</v>
+        <v>70.5</v>
       </c>
       <c r="D115" t="n">
-        <v>5430</v>
+        <v>2698</v>
       </c>
       <c r="E115" t="n">
-        <v>7052.737306843267</v>
+        <v>1190</v>
       </c>
       <c r="F115" t="n">
-        <v>-23</v>
+        <v>126.7</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>8317000000</v>
+        <v>8931000000</v>
       </c>
       <c r="J115" t="n">
-        <v>6048000000</v>
+        <v>9514000000</v>
       </c>
       <c r="K115" t="n">
-        <v>7673000000</v>
+        <v>22055000000</v>
       </c>
       <c r="L115" t="n">
-        <v>49734000000</v>
+        <v>49725000000</v>
       </c>
       <c r="M115" t="n">
-        <v>22038000000</v>
+        <v>40500000000</v>
       </c>
       <c r="N115" t="n">
-        <v>192846672630</v>
+        <v>57445403206</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>日本特殊塗料株式会社</t>
+          <t>株式会社ＡＣＳＬ</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>4619</t>
+          <t>6232</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>70.5</v>
+        <v>8</v>
       </c>
       <c r="D116" t="n">
-        <v>2698</v>
+        <v>1342</v>
       </c>
       <c r="E116" t="n">
-        <v>1190</v>
+        <v>913.2768512341561</v>
       </c>
       <c r="F116" t="n">
-        <v>126.7</v>
+        <v>46.9</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>8931000000</v>
+        <v>1891731000</v>
       </c>
       <c r="J116" t="n">
-        <v>9514000000</v>
+        <v>3724000</v>
       </c>
       <c r="K116" t="n">
-        <v>22055000000</v>
+        <v>197577000</v>
       </c>
       <c r="L116" t="n">
-        <v>49725000000</v>
+        <v>3572642000</v>
       </c>
       <c r="M116" t="n">
-        <v>40500000000</v>
+        <v>2093032000</v>
       </c>
       <c r="N116" t="n">
-        <v>57445403206</v>
+        <v>26265948764</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>株式会社ＡＣＳＬ</t>
+          <t>東京瓦斯株式会社</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>9531</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>8</v>
+        <v>24.2</v>
       </c>
       <c r="D117" t="n">
-        <v>1342</v>
+        <v>6226</v>
       </c>
       <c r="E117" t="n">
-        <v>913.2768512341561</v>
+        <v>3322.047887165483</v>
       </c>
       <c r="F117" t="n">
-        <v>46.9</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1891731000</v>
+        <v>179699000000</v>
       </c>
       <c r="J117" t="n">
-        <v>3724000</v>
+        <v>313045000000</v>
       </c>
       <c r="K117" t="n">
-        <v>197577000</v>
+        <v>103000000</v>
       </c>
       <c r="L117" t="n">
-        <v>3572642000</v>
+        <v>1281150000000</v>
       </c>
       <c r="M117" t="n">
-        <v>2093032000</v>
+        <v>492847000000</v>
       </c>
       <c r="N117" t="n">
-        <v>26265948764</v>
+        <v>2033821638134</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>東京瓦斯株式会社</t>
+          <t>株式会社イワキ</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>9531</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>24.2</v>
+        <v>13.6</v>
       </c>
       <c r="D118" t="n">
-        <v>6226</v>
+        <v>4110</v>
       </c>
       <c r="E118" t="n">
-        <v>3322.047887165483</v>
+        <v>1361.432492253209</v>
       </c>
       <c r="F118" t="n">
-        <v>87.40000000000001</v>
+        <v>201.9</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>179699000000</v>
+        <v>8573897000</v>
       </c>
       <c r="J118" t="n">
-        <v>313045000000</v>
+        <v>3742606000</v>
       </c>
       <c r="K118" t="n">
-        <v>103000000</v>
+        <v>80933000</v>
       </c>
       <c r="L118" t="n">
-        <v>1281150000000</v>
+        <v>25251541000</v>
       </c>
       <c r="M118" t="n">
-        <v>492847000000</v>
+        <v>12397436000</v>
       </c>
       <c r="N118" t="n">
-        <v>2033821638134</v>
+        <v>91461486330</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>株式会社イワキ</t>
+          <t>株式会社パイオラックス</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>6237</t>
+          <t>5988</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>13.6</v>
+        <v>104</v>
       </c>
       <c r="D119" t="n">
-        <v>4110</v>
+        <v>1710</v>
       </c>
       <c r="E119" t="n">
-        <v>1361.432492253209</v>
+        <v>2298.672482457804</v>
       </c>
       <c r="F119" t="n">
-        <v>201.9</v>
+        <v>-25.6</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>8573897000</v>
+        <v>29925000000</v>
       </c>
       <c r="J119" t="n">
-        <v>3742606000</v>
+        <v>12031000000</v>
       </c>
       <c r="K119" t="n">
-        <v>80933000</v>
+        <v>796000000</v>
       </c>
       <c r="L119" t="n">
-        <v>25251541000</v>
+        <v>98332000000</v>
       </c>
       <c r="M119" t="n">
-        <v>12397436000</v>
+        <v>42752000000</v>
       </c>
       <c r="N119" t="n">
-        <v>91173547950</v>
+        <v>41109403770</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>株式会社パイオラックス</t>
+          <t>ブロードメディア株式会社</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>104</v>
+        <v>44.8</v>
       </c>
       <c r="D120" t="n">
-        <v>1710</v>
+        <v>1887</v>
       </c>
       <c r="E120" t="n">
-        <v>2298.672482457804</v>
+        <v>1529.631984751819</v>
       </c>
       <c r="F120" t="n">
-        <v>-25.6</v>
+        <v>23.4</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>29925000000</v>
+        <v>5301579000</v>
       </c>
       <c r="J120" t="n">
-        <v>12031000000</v>
+        <v>553048000</v>
       </c>
       <c r="K120" t="n">
-        <v>796000000</v>
+        <v>169455000</v>
       </c>
       <c r="L120" t="n">
-        <v>98332000000</v>
+        <v>4610613000</v>
       </c>
       <c r="M120" t="n">
-        <v>42752000000</v>
+        <v>6024082000</v>
       </c>
       <c r="N120" t="n">
-        <v>41109403770</v>
+        <v>13448967903</v>
       </c>
     </row>
     <row r="121">
@@ -6674,10 +6674,10 @@
         <v>1887</v>
       </c>
       <c r="E121" t="n">
-        <v>1529.631984751819</v>
+        <v>1449.995380693296</v>
       </c>
       <c r="F121" t="n">
-        <v>23.4</v>
+        <v>30.1</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="I121" t="n">
@@ -6711,77 +6711,77 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ブロードメディア株式会社</t>
+          <t>芝浦機械株式会社</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>6104</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>44.8</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="D122" t="n">
-        <v>1887</v>
+        <v>4685</v>
       </c>
       <c r="E122" t="n">
-        <v>1449.995380693296</v>
+        <v>3449.780346820809</v>
       </c>
       <c r="F122" t="n">
-        <v>30.1</v>
+        <v>35.8</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>5301579000</v>
+        <v>51710000000</v>
       </c>
       <c r="J122" t="n">
-        <v>553048000</v>
+        <v>21218000000</v>
       </c>
       <c r="K122" t="n">
-        <v>169455000</v>
+        <v>18000000000</v>
       </c>
       <c r="L122" t="n">
-        <v>4610613000</v>
+        <v>83515000000</v>
       </c>
       <c r="M122" t="n">
-        <v>6024082000</v>
+        <v>90928000000</v>
       </c>
       <c r="N122" t="n">
-        <v>13448967903</v>
+        <v>110786251220</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>芝浦機械株式会社</t>
+          <t>エン株式会社 (旧会社名　エン・ジャパン株式会社)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>6104</t>
+          <t>4849</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>82.09999999999999</v>
+        <v>55.3</v>
       </c>
       <c r="D123" t="n">
-        <v>4685</v>
+        <v>1727</v>
       </c>
       <c r="E123" t="n">
-        <v>3449.780346820809</v>
+        <v>1746.940387696806</v>
       </c>
       <c r="F123" t="n">
-        <v>35.8</v>
+        <v>-1.1</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -6790,154 +6790,154 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>51710000000</v>
+        <v>33389000000</v>
       </c>
       <c r="J123" t="n">
-        <v>21218000000</v>
+        <v>681000000</v>
       </c>
       <c r="K123" t="n">
-        <v>18000000000</v>
+        <v>2000000000</v>
       </c>
       <c r="L123" t="n">
-        <v>83515000000</v>
+        <v>41160000000</v>
       </c>
       <c r="M123" t="n">
-        <v>90928000000</v>
+        <v>36070000000</v>
       </c>
       <c r="N123" t="n">
-        <v>110786251220</v>
+        <v>65248638411</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>エン株式会社 (旧会社名　エン・ジャパン株式会社)</t>
+          <t>株式会社シンクロ・フード</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>55.3</v>
+        <v>34.2</v>
       </c>
       <c r="D124" t="n">
-        <v>1727</v>
+        <v>324</v>
       </c>
       <c r="E124" t="n">
-        <v>1746.940387696806</v>
+        <v>421.6950726175476</v>
       </c>
       <c r="F124" t="n">
-        <v>-1.1</v>
+        <v>-23.2</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>33389000000</v>
+        <v>3037851000</v>
       </c>
       <c r="J124" t="n">
-        <v>681000000</v>
+        <v>56852000</v>
       </c>
       <c r="K124" t="n">
-        <v>2000000000</v>
+        <v>14952000</v>
       </c>
       <c r="L124" t="n">
-        <v>41160000000</v>
+        <v>2871237000</v>
       </c>
       <c r="M124" t="n">
-        <v>36070000000</v>
+        <v>3109655000</v>
       </c>
       <c r="N124" t="n">
-        <v>65248638411</v>
+        <v>9085798512</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>株式会社シンクロ・フード</t>
+          <t>日本ゼオン株式会社</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>34.2</v>
+        <v>34.5</v>
       </c>
       <c r="D125" t="n">
-        <v>324</v>
+        <v>2440</v>
       </c>
       <c r="E125" t="n">
-        <v>421.6950726175476</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="F125" t="n">
-        <v>-23.2</v>
+        <v>41.8</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>3037851000</v>
+        <v>44521000000</v>
       </c>
       <c r="J125" t="n">
-        <v>56852000</v>
+        <v>45382000000</v>
       </c>
       <c r="K125" t="n">
-        <v>14952000</v>
+        <v>71191000000</v>
       </c>
       <c r="L125" t="n">
-        <v>2871237000</v>
+        <v>321836000000</v>
       </c>
       <c r="M125" t="n">
-        <v>3109655000</v>
+        <v>161094000000</v>
       </c>
       <c r="N125" t="n">
-        <v>9085798512</v>
+        <v>466883037080</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>日本ゼオン株式会社</t>
+          <t>株式会社インターネットイニシアティブ</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>34.5</v>
+        <v>5.4</v>
       </c>
       <c r="D126" t="n">
-        <v>2440</v>
+        <v>3465</v>
       </c>
       <c r="E126" t="n">
-        <v>1721.078563209627</v>
+        <v>2655.311711736394</v>
       </c>
       <c r="F126" t="n">
-        <v>41.8</v>
+        <v>30.5</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -6946,390 +6946,390 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>44521000000</v>
+        <v>16367000000</v>
       </c>
       <c r="J126" t="n">
-        <v>45382000000</v>
+        <v>1522000000</v>
       </c>
       <c r="K126" t="n">
-        <v>71191000000</v>
+        <v>15226000000</v>
       </c>
       <c r="L126" t="n">
-        <v>321836000000</v>
+        <v>87924000000</v>
       </c>
       <c r="M126" t="n">
-        <v>161094000000</v>
+        <v>33115000000</v>
       </c>
       <c r="N126" t="n">
-        <v>466883037080</v>
+        <v>614448467325</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>株式会社インターネットイニシアティブ</t>
+          <t>リンナイ株式会社</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>3774</t>
+          <t>5947</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>5.4</v>
+        <v>45.9</v>
       </c>
       <c r="D127" t="n">
-        <v>3465</v>
+        <v>3450</v>
       </c>
       <c r="E127" t="n">
-        <v>2655.311711736394</v>
+        <v>2844.704547285864</v>
       </c>
       <c r="F127" t="n">
-        <v>30.5</v>
+        <v>21.3</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>16367000000</v>
+        <v>147972000000</v>
       </c>
       <c r="J127" t="n">
-        <v>1522000000</v>
+        <v>64736000000</v>
       </c>
       <c r="K127" t="n">
-        <v>15226000000</v>
+        <v>5967000000</v>
       </c>
       <c r="L127" t="n">
-        <v>87924000000</v>
+        <v>378856000000</v>
       </c>
       <c r="M127" t="n">
-        <v>33115000000</v>
+        <v>218675000000</v>
       </c>
       <c r="N127" t="n">
-        <v>614448467325</v>
+        <v>476340161400</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>リンナイ株式会社</t>
+          <t>京阪神ビルディング株式会社</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>8818</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>45.9</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D128" t="n">
-        <v>3450</v>
+        <v>1086</v>
       </c>
       <c r="E128" t="n">
-        <v>2844.704547285864</v>
+        <v>1341.977644710579</v>
       </c>
       <c r="F128" t="n">
-        <v>21.3</v>
+        <v>-19.1</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>147972000000</v>
+        <v>9876000000</v>
       </c>
       <c r="J128" t="n">
-        <v>64736000000</v>
+        <v>54379000000</v>
       </c>
       <c r="K128" t="n">
-        <v>5967000000</v>
+        <v>22399000000</v>
       </c>
       <c r="L128" t="n">
-        <v>378856000000</v>
+        <v>70510000000</v>
       </c>
       <c r="M128" t="n">
-        <v>218675000000</v>
+        <v>86654000000</v>
       </c>
       <c r="N128" t="n">
-        <v>476340161400</v>
+        <v>103609462932</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>京阪神ビルディング株式会社</t>
+          <t>株式会社ワコールホールディングス</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>8818</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>83.59999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D129" t="n">
-        <v>1086</v>
+        <v>3968</v>
       </c>
       <c r="E129" t="n">
-        <v>1341.977644710579</v>
+        <v>2420.370957920882</v>
       </c>
       <c r="F129" t="n">
-        <v>-19.1</v>
+        <v>63.9</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>9876000000</v>
+        <v>2951000000</v>
       </c>
       <c r="J129" t="n">
-        <v>54379000000</v>
+        <v>14983000000</v>
       </c>
       <c r="K129" t="n">
-        <v>22399000000</v>
+        <v>233000000</v>
       </c>
       <c r="L129" t="n">
-        <v>70510000000</v>
+        <v>138332000000</v>
       </c>
       <c r="M129" t="n">
-        <v>86654000000</v>
+        <v>18167000000</v>
       </c>
       <c r="N129" t="n">
-        <v>103609462932</v>
+        <v>196166329472</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>株式会社ワコールホールディングス</t>
+          <t>株式会社カカクコム</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>9.300000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="D130" t="n">
-        <v>3968</v>
+        <v>3812</v>
       </c>
       <c r="E130" t="n">
-        <v>2420.370957920882</v>
+        <v>2318.314890576102</v>
       </c>
       <c r="F130" t="n">
-        <v>63.9</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2951000000</v>
+        <v>46452000000</v>
       </c>
       <c r="J130" t="n">
-        <v>14983000000</v>
+        <v>68000000</v>
       </c>
       <c r="K130" t="n">
-        <v>233000000</v>
+        <v>4669000000</v>
       </c>
       <c r="L130" t="n">
-        <v>138332000000</v>
+        <v>45479000000</v>
       </c>
       <c r="M130" t="n">
-        <v>18167000000</v>
+        <v>51189000000</v>
       </c>
       <c r="N130" t="n">
-        <v>196166329472</v>
+        <v>754151849804</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>株式会社カカクコム</t>
+          <t>多木化学株式会社</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>6.8</v>
+        <v>30.1</v>
       </c>
       <c r="D131" t="n">
-        <v>3812</v>
+        <v>5810</v>
       </c>
       <c r="E131" t="n">
-        <v>2318.314890576102</v>
+        <v>4695.956053243186</v>
       </c>
       <c r="F131" t="n">
-        <v>64.40000000000001</v>
+        <v>23.7</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>46452000000</v>
+        <v>6433000000</v>
       </c>
       <c r="J131" t="n">
-        <v>68000000</v>
+        <v>7985000000</v>
       </c>
       <c r="K131" t="n">
-        <v>4669000000</v>
+        <v>199000000</v>
       </c>
       <c r="L131" t="n">
-        <v>45479000000</v>
+        <v>29378000000</v>
       </c>
       <c r="M131" t="n">
-        <v>51189000000</v>
+        <v>14617000000</v>
       </c>
       <c r="N131" t="n">
-        <v>754151849804</v>
+        <v>48498213890</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>あいホールディングス株式会社</t>
+          <t>ガンホー・オンライン・エンターテイメント株式会社</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>3076</t>
+          <t>3765</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>23.1</v>
+        <v>83.2</v>
       </c>
       <c r="D132" t="n">
-        <v>3020</v>
+        <v>2489</v>
       </c>
       <c r="E132" t="n">
-        <v>2007.754513143541</v>
+        <v>2901.475903614458</v>
       </c>
       <c r="F132" t="n">
-        <v>50.4</v>
+        <v>-14.2</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>32012000000</v>
+        <v>102086000000</v>
       </c>
       <c r="J132" t="n">
-        <v>1646000000</v>
+        <v>1326000000</v>
       </c>
       <c r="K132" t="n">
-        <v>3550000000</v>
+        <v>5018000000</v>
       </c>
       <c r="L132" t="n">
-        <v>53765000000</v>
+        <v>118672000000</v>
       </c>
       <c r="M132" t="n">
-        <v>37208000000</v>
+        <v>108430000000</v>
       </c>
       <c r="N132" t="n">
-        <v>160884251620</v>
+        <v>130341174276</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>多木化学株式会社</t>
+          <t>ガンホー・オンライン・エンターテイメント株式会社</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>4025</t>
+          <t>3765</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>30.1</v>
+        <v>83.2</v>
       </c>
       <c r="D133" t="n">
-        <v>5810</v>
+        <v>2489</v>
       </c>
       <c r="E133" t="n">
-        <v>4695.956053243186</v>
+        <v>2905.067038344418</v>
       </c>
       <c r="F133" t="n">
-        <v>23.7</v>
+        <v>-14.3</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>6433000000</v>
+        <v>102086000000</v>
       </c>
       <c r="J133" t="n">
-        <v>7985000000</v>
+        <v>1326000000</v>
       </c>
       <c r="K133" t="n">
-        <v>199000000</v>
+        <v>5018000000</v>
       </c>
       <c r="L133" t="n">
-        <v>29378000000</v>
+        <v>118672000000</v>
       </c>
       <c r="M133" t="n">
-        <v>14617000000</v>
+        <v>108430000000</v>
       </c>
       <c r="N133" t="n">
-        <v>48498213890</v>
+        <v>130341174276</v>
       </c>
     </row>
     <row r="134">
@@ -7350,10 +7350,10 @@
         <v>2489</v>
       </c>
       <c r="E134" t="n">
-        <v>2901.475903614458</v>
+        <v>2955.342465753425</v>
       </c>
       <c r="F134" t="n">
-        <v>-14.2</v>
+        <v>-15.8</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="I134" t="n">
@@ -7402,10 +7402,10 @@
         <v>2489</v>
       </c>
       <c r="E135" t="n">
-        <v>2905.067038344418</v>
+        <v>2987.584858837727</v>
       </c>
       <c r="F135" t="n">
-        <v>-14.3</v>
+        <v>-16.7</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="I135" t="n">
@@ -7454,10 +7454,10 @@
         <v>2489</v>
       </c>
       <c r="E136" t="n">
-        <v>2955.342465753425</v>
+        <v>3016.088716673414</v>
       </c>
       <c r="F136" t="n">
-        <v>-15.8</v>
+        <v>-17.5</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="I136" t="n">
@@ -7506,10 +7506,10 @@
         <v>2489</v>
       </c>
       <c r="E137" t="n">
-        <v>2987.584858837727</v>
+        <v>3016.087384069568</v>
       </c>
       <c r="F137" t="n">
-        <v>-16.7</v>
+        <v>-17.5</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="I137" t="n">
@@ -7558,10 +7558,10 @@
         <v>2489</v>
       </c>
       <c r="E138" t="n">
-        <v>3016.088716673414</v>
+        <v>2939.562915943684</v>
       </c>
       <c r="F138" t="n">
-        <v>-17.5</v>
+        <v>-15.3</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="I138" t="n">
@@ -7595,285 +7595,285 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ガンホー・オンライン・エンターテイメント株式会社</t>
+          <t>近畿車輛株式会社</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>3765</t>
+          <t>7122</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>83.2</v>
+        <v>105.6</v>
       </c>
       <c r="D139" t="n">
-        <v>2489</v>
+        <v>2444</v>
       </c>
       <c r="E139" t="n">
-        <v>3016.087384069568</v>
+        <v>2144.894901144641</v>
       </c>
       <c r="F139" t="n">
-        <v>-17.5</v>
+        <v>13.9</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>102086000000</v>
+        <v>6847000000</v>
       </c>
       <c r="J139" t="n">
-        <v>1326000000</v>
+        <v>4580000000</v>
       </c>
       <c r="K139" t="n">
-        <v>5018000000</v>
+        <v>6329000000</v>
       </c>
       <c r="L139" t="n">
-        <v>118672000000</v>
+        <v>24474000000</v>
       </c>
       <c r="M139" t="n">
-        <v>108430000000</v>
+        <v>17756000000</v>
       </c>
       <c r="N139" t="n">
-        <v>130341174276</v>
+        <v>16814917964</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ガンホー・オンライン・エンターテイメント株式会社</t>
+          <t>シェアリングテクノロジー株式会社</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>3765</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>83.2</v>
+        <v>11.7</v>
       </c>
       <c r="D140" t="n">
-        <v>2489</v>
+        <v>1545</v>
       </c>
       <c r="E140" t="n">
-        <v>2939.562915943684</v>
+        <v>653.0713101160862</v>
       </c>
       <c r="F140" t="n">
-        <v>-15.3</v>
+        <v>136.6</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>102086000000</v>
+        <v>4016706000</v>
       </c>
       <c r="J140" t="n">
-        <v>1326000000</v>
+        <v>309745000</v>
       </c>
       <c r="K140" t="n">
-        <v>5018000000</v>
+        <v>0</v>
       </c>
       <c r="L140" t="n">
-        <v>118672000000</v>
+        <v>185001000</v>
       </c>
       <c r="M140" t="n">
-        <v>108430000000</v>
+        <v>4326451000</v>
       </c>
       <c r="N140" t="n">
-        <v>130341174276</v>
+        <v>36973810605</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>近畿車輛株式会社</t>
+          <t>日本化薬株式会社</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>7122</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>105.6</v>
+        <v>34.4</v>
       </c>
       <c r="D141" t="n">
-        <v>2444</v>
+        <v>2129.5</v>
       </c>
       <c r="E141" t="n">
-        <v>2144.894901144641</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="F141" t="n">
-        <v>13.9</v>
+        <v>91.5</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>6847000000</v>
+        <v>52962000000</v>
       </c>
       <c r="J141" t="n">
-        <v>4580000000</v>
+        <v>48231000000</v>
       </c>
       <c r="K141" t="n">
-        <v>6329000000</v>
+        <v>4337000000</v>
       </c>
       <c r="L141" t="n">
-        <v>24474000000</v>
+        <v>246425000000</v>
       </c>
       <c r="M141" t="n">
-        <v>17756000000</v>
+        <v>105530000000</v>
       </c>
       <c r="N141" t="n">
-        <v>16814917964</v>
+        <v>307049174376</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>シェアリングテクノロジー株式会社</t>
+          <t>株式会社博報堂ＤＹホールディングス</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>2433</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>11.7</v>
+        <v>44.7</v>
       </c>
       <c r="D142" t="n">
-        <v>1545</v>
+        <v>1330.5</v>
       </c>
       <c r="E142" t="n">
-        <v>653.0713101160862</v>
+        <v>1111.251693601708</v>
       </c>
       <c r="F142" t="n">
-        <v>136.6</v>
+        <v>19.7</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>4016706000</v>
+        <v>180697000000</v>
       </c>
       <c r="J142" t="n">
-        <v>309745000</v>
+        <v>21890000000</v>
       </c>
       <c r="K142" t="n">
-        <v>0</v>
+        <v>10976000000</v>
       </c>
       <c r="L142" t="n">
-        <v>185001000</v>
+        <v>387414000000</v>
       </c>
       <c r="M142" t="n">
-        <v>4326451000</v>
+        <v>213563000000</v>
       </c>
       <c r="N142" t="n">
-        <v>36973810605</v>
+        <v>477692129220</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>日本化薬株式会社</t>
+          <t>データセクション株式会社</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>34.4</v>
+        <v>1.9</v>
       </c>
       <c r="D143" t="n">
-        <v>2129.5</v>
+        <v>2077</v>
       </c>
       <c r="E143" t="n">
-        <v>1111.90611839092</v>
+        <v>5143.276404494382</v>
       </c>
       <c r="F143" t="n">
-        <v>91.5</v>
+        <v>-59.6</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>52962000000</v>
+        <v>1420430000</v>
       </c>
       <c r="J143" t="n">
-        <v>48231000000</v>
+        <v>1162000</v>
       </c>
       <c r="K143" t="n">
-        <v>4337000000</v>
+        <v>49326000</v>
       </c>
       <c r="L143" t="n">
-        <v>246425000000</v>
+        <v>2818110000</v>
       </c>
       <c r="M143" t="n">
-        <v>105530000000</v>
+        <v>1470918000</v>
       </c>
       <c r="N143" t="n">
-        <v>307049174376</v>
+        <v>77809209562</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>株式会社博報堂ＤＹホールディングス</t>
+          <t>東ソー株式会社</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2433</t>
+          <t>4042</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>44.7</v>
+        <v>41.6</v>
       </c>
       <c r="D144" t="n">
-        <v>1330.5</v>
+        <v>2656.5</v>
       </c>
       <c r="E144" t="n">
-        <v>1111.251693601708</v>
+        <v>2032.365850102071</v>
       </c>
       <c r="F144" t="n">
-        <v>19.7</v>
+        <v>30.7</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -7882,206 +7882,206 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>180697000000</v>
+        <v>160812000000</v>
       </c>
       <c r="J144" t="n">
-        <v>21890000000</v>
+        <v>109648000000</v>
       </c>
       <c r="K144" t="n">
-        <v>10976000000</v>
+        <v>70132000000</v>
       </c>
       <c r="L144" t="n">
-        <v>387414000000</v>
+        <v>759724000000</v>
       </c>
       <c r="M144" t="n">
-        <v>213563000000</v>
+        <v>340592000000</v>
       </c>
       <c r="N144" t="n">
-        <v>477692129220</v>
+        <v>817911235449</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>データセクション株式会社</t>
+          <t>大平洋金属株式会社</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>5541</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1.9</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D145" t="n">
-        <v>2077</v>
+        <v>2713</v>
       </c>
       <c r="E145" t="n">
-        <v>5143.276404494382</v>
+        <v>1270</v>
       </c>
       <c r="F145" t="n">
-        <v>-59.6</v>
+        <v>113.6</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1420430000</v>
+        <v>26631000000</v>
       </c>
       <c r="J145" t="n">
-        <v>1162000</v>
+        <v>1877000000</v>
       </c>
       <c r="K145" t="n">
-        <v>49326000</v>
+        <v>2600000000</v>
       </c>
       <c r="L145" t="n">
-        <v>2818110000</v>
+        <v>80153000000</v>
       </c>
       <c r="M145" t="n">
-        <v>1470918000</v>
+        <v>31108000000</v>
       </c>
       <c r="N145" t="n">
-        <v>77809209562</v>
+        <v>47172452993</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>東ソー株式会社</t>
+          <t>大平洋金属株式会社</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>4042</t>
+          <t>5541</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>41.6</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D146" t="n">
-        <v>2656.5</v>
+        <v>2713</v>
       </c>
       <c r="E146" t="n">
-        <v>2032.365850102071</v>
+        <v>1170</v>
       </c>
       <c r="F146" t="n">
-        <v>30.7</v>
+        <v>131.9</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>160812000000</v>
+        <v>26631000000</v>
       </c>
       <c r="J146" t="n">
-        <v>109648000000</v>
+        <v>1877000000</v>
       </c>
       <c r="K146" t="n">
-        <v>70132000000</v>
+        <v>2600000000</v>
       </c>
       <c r="L146" t="n">
-        <v>759724000000</v>
+        <v>80153000000</v>
       </c>
       <c r="M146" t="n">
-        <v>340592000000</v>
+        <v>31108000000</v>
       </c>
       <c r="N146" t="n">
-        <v>817911235449</v>
+        <v>47172452993</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>大平洋金属株式会社</t>
+          <t>株式会社イエローハット</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>5541</t>
+          <t>9882</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>65.90000000000001</v>
+        <v>35.6</v>
       </c>
       <c r="D147" t="n">
-        <v>2713</v>
+        <v>1745</v>
       </c>
       <c r="E147" t="n">
-        <v>1270</v>
+        <v>2112.609181636727</v>
       </c>
       <c r="F147" t="n">
-        <v>113.6</v>
+        <v>-17.4</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>26631000000</v>
+        <v>10902000000</v>
       </c>
       <c r="J147" t="n">
-        <v>1877000000</v>
+        <v>29975000000</v>
       </c>
       <c r="K147" t="n">
-        <v>2600000000</v>
+        <v>11341000000</v>
       </c>
       <c r="L147" t="n">
-        <v>80153000000</v>
+        <v>98298000000</v>
       </c>
       <c r="M147" t="n">
-        <v>31108000000</v>
+        <v>52218000000</v>
       </c>
       <c r="N147" t="n">
-        <v>47172452993</v>
+        <v>146510217450</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>大平洋金属株式会社</t>
+          <t>三井松島ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>5541</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>65.90000000000001</v>
+        <v>39.8</v>
       </c>
       <c r="D148" t="n">
-        <v>2713</v>
+        <v>2300</v>
       </c>
       <c r="E148" t="n">
-        <v>1170</v>
+        <v>2920</v>
       </c>
       <c r="F148" t="n">
-        <v>131.9</v>
+        <v>-21.2</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -8090,258 +8090,258 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>26631000000</v>
+        <v>19413000000</v>
       </c>
       <c r="J148" t="n">
-        <v>1877000000</v>
+        <v>3540000000</v>
       </c>
       <c r="K148" t="n">
-        <v>2600000000</v>
+        <v>10945000000</v>
       </c>
       <c r="L148" t="n">
-        <v>80153000000</v>
+        <v>35537000000</v>
       </c>
       <c r="M148" t="n">
-        <v>31108000000</v>
+        <v>33898000000</v>
       </c>
       <c r="N148" t="n">
-        <v>47172452993</v>
+        <v>85164308000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>株式会社イエローハット</t>
+          <t>アツギ株式会社</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>9882</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>35.6</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="D149" t="n">
-        <v>1745</v>
+        <v>1014</v>
       </c>
       <c r="E149" t="n">
-        <v>2112.609181636727</v>
+        <v>668.9358717434869</v>
       </c>
       <c r="F149" t="n">
-        <v>-17.4</v>
+        <v>51.6</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>10902000000</v>
+        <v>5500000000</v>
       </c>
       <c r="J149" t="n">
-        <v>29975000000</v>
+        <v>3208000000</v>
       </c>
       <c r="K149" t="n">
-        <v>11341000000</v>
+        <v>3702000000</v>
       </c>
       <c r="L149" t="n">
-        <v>98298000000</v>
+        <v>32145000000</v>
       </c>
       <c r="M149" t="n">
-        <v>52218000000</v>
+        <v>12410000000</v>
       </c>
       <c r="N149" t="n">
-        <v>146510217450</v>
+        <v>16238202084</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>三井松島ホールディングス株式会社</t>
+          <t>ニッコンホールディングス株式会社</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>9072</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>39.8</v>
+        <v>28.8</v>
       </c>
       <c r="D150" t="n">
-        <v>2300</v>
+        <v>5125</v>
       </c>
       <c r="E150" t="n">
-        <v>2920</v>
+        <v>2779.139169918938</v>
       </c>
       <c r="F150" t="n">
-        <v>-21.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>19413000000</v>
+        <v>29157000000</v>
       </c>
       <c r="J150" t="n">
-        <v>3540000000</v>
+        <v>126028000000</v>
       </c>
       <c r="K150" t="n">
-        <v>10945000000</v>
+        <v>28031000000</v>
       </c>
       <c r="L150" t="n">
-        <v>35537000000</v>
+        <v>219035000000</v>
       </c>
       <c r="M150" t="n">
-        <v>33898000000</v>
+        <v>183216000000</v>
       </c>
       <c r="N150" t="n">
-        <v>85164308000</v>
+        <v>635666413875</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>アツギ株式会社</t>
+          <t>株式会社セプテーニ・ホールディングス</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>4293</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>76.40000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="D151" t="n">
-        <v>1014</v>
+        <v>500</v>
       </c>
       <c r="E151" t="n">
-        <v>668.9358717434869</v>
+        <v>448.6811097117532</v>
       </c>
       <c r="F151" t="n">
-        <v>51.6</v>
+        <v>11.4</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>5500000000</v>
+        <v>12184507000</v>
       </c>
       <c r="J151" t="n">
-        <v>3208000000</v>
+        <v>168073000</v>
       </c>
       <c r="K151" t="n">
-        <v>3702000000</v>
+        <v>1600720000</v>
       </c>
       <c r="L151" t="n">
-        <v>32145000000</v>
+        <v>11861578000</v>
       </c>
       <c r="M151" t="n">
-        <v>12410000000</v>
+        <v>13953300000</v>
       </c>
       <c r="N151" t="n">
-        <v>16238202084</v>
+        <v>103722554500</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ニッコンホールディングス株式会社</t>
+          <t>ニッタ株式会社</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>9072</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>28.8</v>
+        <v>28.1</v>
       </c>
       <c r="D152" t="n">
-        <v>5125</v>
+        <v>6880</v>
       </c>
       <c r="E152" t="n">
-        <v>2779.139169918938</v>
+        <v>3096.322467304314</v>
       </c>
       <c r="F152" t="n">
-        <v>84.40000000000001</v>
+        <v>122.2</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>29157000000</v>
+        <v>30872000000</v>
       </c>
       <c r="J152" t="n">
-        <v>126028000000</v>
+        <v>15392000000</v>
       </c>
       <c r="K152" t="n">
-        <v>28031000000</v>
+        <v>6697000000</v>
       </c>
       <c r="L152" t="n">
-        <v>219035000000</v>
+        <v>119214000000</v>
       </c>
       <c r="M152" t="n">
-        <v>183216000000</v>
+        <v>52961000000</v>
       </c>
       <c r="N152" t="n">
-        <v>635666413875</v>
+        <v>188740209600</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>株式会社セプテーニ・ホールディングス</t>
+          <t>株式会社エス・エム・エス</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>4293</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>13.5</v>
+        <v>8.4</v>
       </c>
       <c r="D153" t="n">
-        <v>500</v>
+        <v>2630</v>
       </c>
       <c r="E153" t="n">
-        <v>448.6811097117532</v>
+        <v>1478.127248828989</v>
       </c>
       <c r="F153" t="n">
-        <v>11.4</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -8350,362 +8350,362 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>12184507000</v>
+        <v>14126000000</v>
       </c>
       <c r="J153" t="n">
-        <v>168073000</v>
+        <v>1187000000</v>
       </c>
       <c r="K153" t="n">
-        <v>1600720000</v>
+        <v>2875000000</v>
       </c>
       <c r="L153" t="n">
-        <v>11861578000</v>
+        <v>29991000000</v>
       </c>
       <c r="M153" t="n">
-        <v>13953300000</v>
+        <v>18188000000</v>
       </c>
       <c r="N153" t="n">
-        <v>103722554500</v>
+        <v>215871580870</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ニッタ株式会社</t>
+          <t>株式会社オリエントコーポレーション</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>5186</t>
+          <t>8585</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>28.1</v>
+        <v>309.7</v>
       </c>
       <c r="D154" t="n">
-        <v>6880</v>
+        <v>847</v>
       </c>
       <c r="E154" t="n">
-        <v>3096.322467304314</v>
+        <v>798.3805136422309</v>
       </c>
       <c r="F154" t="n">
-        <v>122.2</v>
+        <v>6.1</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>30872000000</v>
+        <v>408187000000</v>
       </c>
       <c r="J154" t="n">
-        <v>15392000000</v>
+        <v>18930000000</v>
       </c>
       <c r="K154" t="n">
-        <v>6697000000</v>
+        <v>21921000000</v>
       </c>
       <c r="L154" t="n">
-        <v>119214000000</v>
+        <v>216837000000</v>
       </c>
       <c r="M154" t="n">
-        <v>52961000000</v>
+        <v>449038000000</v>
       </c>
       <c r="N154" t="n">
-        <v>188740209600</v>
+        <v>144994426808</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>株式会社エス・エム・エス</t>
+          <t>トーセイ株式会社</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>8.4</v>
+        <v>45.6</v>
       </c>
       <c r="D155" t="n">
-        <v>2630</v>
+        <v>1722</v>
       </c>
       <c r="E155" t="n">
-        <v>1478.127248828989</v>
+        <v>1752.426893379333</v>
       </c>
       <c r="F155" t="n">
-        <v>77.90000000000001</v>
+        <v>-1.7</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="I155" t="n">
-        <v>14126000000</v>
+        <v>20753937000</v>
       </c>
       <c r="J155" t="n">
-        <v>1187000000</v>
+        <v>46868512000</v>
       </c>
       <c r="K155" t="n">
-        <v>2875000000</v>
+        <v>8610046000</v>
       </c>
       <c r="L155" t="n">
-        <v>29991000000</v>
+        <v>59467346000</v>
       </c>
       <c r="M155" t="n">
-        <v>18188000000</v>
+        <v>76232495000</v>
       </c>
       <c r="N155" t="n">
-        <v>215871580870</v>
+        <v>167044504200</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>株式会社オリエントコーポレーション</t>
+          <t>トーセイ株式会社</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>8585</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>309.7</v>
+        <v>45.6</v>
       </c>
       <c r="D156" t="n">
-        <v>847</v>
+        <v>1722</v>
       </c>
       <c r="E156" t="n">
-        <v>798.3805136422309</v>
+        <v>1576.721867844292</v>
       </c>
       <c r="F156" t="n">
-        <v>6.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="I156" t="n">
-        <v>408187000000</v>
+        <v>20753937000</v>
       </c>
       <c r="J156" t="n">
-        <v>18930000000</v>
+        <v>46868512000</v>
       </c>
       <c r="K156" t="n">
-        <v>21921000000</v>
+        <v>8610046000</v>
       </c>
       <c r="L156" t="n">
-        <v>216837000000</v>
+        <v>59467346000</v>
       </c>
       <c r="M156" t="n">
-        <v>449038000000</v>
+        <v>76232495000</v>
       </c>
       <c r="N156" t="n">
-        <v>144994426808</v>
+        <v>167044504200</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>トーセイ株式会社</t>
+          <t>関西ペイント株式会社</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>4613</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>45.6</v>
+        <v>33.2</v>
       </c>
       <c r="D157" t="n">
-        <v>1722</v>
+        <v>2867</v>
       </c>
       <c r="E157" t="n">
-        <v>1752.426893379333</v>
+        <v>2381.523440544182</v>
       </c>
       <c r="F157" t="n">
-        <v>-1.7</v>
+        <v>20.4</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="I157" t="n">
-        <v>20753937000</v>
+        <v>59709000000</v>
       </c>
       <c r="J157" t="n">
-        <v>46868512000</v>
+        <v>76498000000</v>
       </c>
       <c r="K157" t="n">
-        <v>8610046000</v>
+        <v>32489000000</v>
       </c>
       <c r="L157" t="n">
-        <v>59467346000</v>
+        <v>375114000000</v>
       </c>
       <c r="M157" t="n">
-        <v>76232495000</v>
+        <v>168696000000</v>
       </c>
       <c r="N157" t="n">
-        <v>167044504200</v>
+        <v>508215727448</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>トーセイ株式会社</t>
+          <t>株式会社メルカリ</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>45.6</v>
+        <v>35.9</v>
       </c>
       <c r="D158" t="n">
-        <v>1722</v>
+        <v>3635</v>
       </c>
       <c r="E158" t="n">
-        <v>1576.721867844292</v>
+        <v>2006.059650428343</v>
       </c>
       <c r="F158" t="n">
-        <v>9.199999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>20753937000</v>
+        <v>211406000000</v>
       </c>
       <c r="J158" t="n">
-        <v>46868512000</v>
+        <v>367000000</v>
       </c>
       <c r="K158" t="n">
-        <v>8610046000</v>
+        <v>1021000000</v>
       </c>
       <c r="L158" t="n">
-        <v>59467346000</v>
+        <v>37998000000</v>
       </c>
       <c r="M158" t="n">
-        <v>76232495000</v>
+        <v>212794000000</v>
       </c>
       <c r="N158" t="n">
-        <v>167044504200</v>
+        <v>593161542795</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>関西ペイント株式会社</t>
+          <t>江崎グリコ株式会社</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>4613</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>33.2</v>
+        <v>59.3</v>
       </c>
       <c r="D159" t="n">
-        <v>2867</v>
+        <v>5050</v>
       </c>
       <c r="E159" t="n">
-        <v>2381.523440544182</v>
+        <v>4154.626869982095</v>
       </c>
       <c r="F159" t="n">
-        <v>20.4</v>
+        <v>21.6</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="I159" t="n">
-        <v>59709000000</v>
+        <v>89463000000</v>
       </c>
       <c r="J159" t="n">
-        <v>76498000000</v>
+        <v>42929000000</v>
       </c>
       <c r="K159" t="n">
-        <v>32489000000</v>
+        <v>46694000000</v>
       </c>
       <c r="L159" t="n">
-        <v>375114000000</v>
+        <v>241177000000</v>
       </c>
       <c r="M159" t="n">
-        <v>168696000000</v>
+        <v>179086000000</v>
       </c>
       <c r="N159" t="n">
-        <v>508215727448</v>
+        <v>301993413800</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>株式会社メルカリ</t>
+          <t>エア・ウォーター株式会社</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>35.9</v>
+        <v>15.4</v>
       </c>
       <c r="D160" t="n">
-        <v>3635</v>
+        <v>2911</v>
       </c>
       <c r="E160" t="n">
-        <v>2006.059650428343</v>
+        <v>2261.880826568852</v>
       </c>
       <c r="F160" t="n">
-        <v>81.2</v>
+        <v>28.7</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -8714,154 +8714,154 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>211406000000</v>
+        <v>29189000000</v>
       </c>
       <c r="J160" t="n">
-        <v>367000000</v>
+        <v>31318000000</v>
       </c>
       <c r="K160" t="n">
-        <v>1021000000</v>
+        <v>42001000000</v>
       </c>
       <c r="L160" t="n">
-        <v>37998000000</v>
+        <v>194657000000</v>
       </c>
       <c r="M160" t="n">
-        <v>212794000000</v>
+        <v>102508000000</v>
       </c>
       <c r="N160" t="n">
-        <v>593161542795</v>
+        <v>667387192523</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>江崎グリコ株式会社</t>
+          <t>エア・ウォーター株式会社</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>59.3</v>
+        <v>15.4</v>
       </c>
       <c r="D161" t="n">
-        <v>5050</v>
+        <v>2911</v>
       </c>
       <c r="E161" t="n">
-        <v>4154.626869982095</v>
+        <v>1970</v>
       </c>
       <c r="F161" t="n">
-        <v>21.6</v>
+        <v>47.8</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I161" t="n">
-        <v>89463000000</v>
+        <v>29189000000</v>
       </c>
       <c r="J161" t="n">
-        <v>42929000000</v>
+        <v>31318000000</v>
       </c>
       <c r="K161" t="n">
-        <v>46694000000</v>
+        <v>42001000000</v>
       </c>
       <c r="L161" t="n">
-        <v>241177000000</v>
+        <v>194657000000</v>
       </c>
       <c r="M161" t="n">
-        <v>179086000000</v>
+        <v>102508000000</v>
       </c>
       <c r="N161" t="n">
-        <v>301993413800</v>
+        <v>667387192523</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>エア・ウォーター株式会社</t>
+          <t>月島ホールディングス株式会社</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>15.4</v>
+        <v>47.9</v>
       </c>
       <c r="D162" t="n">
-        <v>2911</v>
+        <v>2694</v>
       </c>
       <c r="E162" t="n">
-        <v>2261.880826568852</v>
+        <v>1410</v>
       </c>
       <c r="F162" t="n">
-        <v>28.7</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="I162" t="n">
-        <v>29189000000</v>
+        <v>28795000000</v>
       </c>
       <c r="J162" t="n">
-        <v>31318000000</v>
+        <v>22203000000</v>
       </c>
       <c r="K162" t="n">
-        <v>42001000000</v>
+        <v>100000000</v>
       </c>
       <c r="L162" t="n">
-        <v>194657000000</v>
+        <v>80949000000</v>
       </c>
       <c r="M162" t="n">
-        <v>102508000000</v>
+        <v>51098000000</v>
       </c>
       <c r="N162" t="n">
-        <v>667387192523</v>
+        <v>106685694762</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>エア・ウォーター株式会社</t>
+          <t>日本製紙株式会社</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>15.4</v>
+        <v>299.9</v>
       </c>
       <c r="D163" t="n">
-        <v>2911</v>
+        <v>1333</v>
       </c>
       <c r="E163" t="n">
-        <v>1970</v>
+        <v>1250</v>
       </c>
       <c r="F163" t="n">
-        <v>47.8</v>
+        <v>6.6</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -8870,50 +8870,50 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I163" t="n">
-        <v>29189000000</v>
+        <v>136216000000</v>
       </c>
       <c r="J163" t="n">
-        <v>31318000000</v>
+        <v>151771000000</v>
       </c>
       <c r="K163" t="n">
-        <v>42001000000</v>
+        <v>172984000000</v>
       </c>
       <c r="L163" t="n">
-        <v>194657000000</v>
+        <v>438604000000</v>
       </c>
       <c r="M163" t="n">
-        <v>102508000000</v>
+        <v>460971000000</v>
       </c>
       <c r="N163" t="n">
-        <v>667387192523</v>
+        <v>153706234499</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>月島ホールディングス株式会社</t>
+          <t>ＫＰＰグループホールディングス株式会社</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>6332</t>
+          <t>9274</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>47.9</v>
+        <v>69.7</v>
       </c>
       <c r="D164" t="n">
-        <v>2694</v>
+        <v>1176</v>
       </c>
       <c r="E164" t="n">
-        <v>1410</v>
+        <v>730</v>
       </c>
       <c r="F164" t="n">
-        <v>91.09999999999999</v>
+        <v>61.1</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -8922,234 +8922,234 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I164" t="n">
-        <v>28795000000</v>
+        <v>22631000000</v>
       </c>
       <c r="J164" t="n">
-        <v>22203000000</v>
+        <v>7793000000</v>
       </c>
       <c r="K164" t="n">
-        <v>100000000</v>
+        <v>19603000000</v>
       </c>
       <c r="L164" t="n">
-        <v>80949000000</v>
+        <v>56374000000</v>
       </c>
       <c r="M164" t="n">
-        <v>51098000000</v>
+        <v>50027000000</v>
       </c>
       <c r="N164" t="n">
-        <v>106685694762</v>
+        <v>71799722736</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>日本製紙株式会社</t>
+          <t>コクヨ株式会社</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>7984</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>299.